--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Consulta" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$140</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$128</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Base!$1:$1</definedName>
   </definedNames>
@@ -4457,7 +4457,7 @@
         <v>228</v>
       </c>
       <c r="E105" s="27" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="F105" s="26" t="s">
         <v>177</v>
@@ -10780,7 +10780,7 @@
       <c r="F1027" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H133">
+  <autoFilter ref="A1:H140">
     <sortState ref="A2:H127">
       <sortCondition ref="A2:A127"/>
       <sortCondition ref="B2:B127"/>

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Consulta" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$140</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$143</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$131</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Base!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="334">
   <si>
     <t>Grupo</t>
   </si>
@@ -558,9 +558,6 @@
     <t>EUCLIDES ROXO</t>
   </si>
   <si>
-    <t>21815-050</t>
-  </si>
-  <si>
     <t>ESTRADA MARAVILHA</t>
   </si>
   <si>
@@ -1012,6 +1009,24 @@
   </si>
   <si>
     <t>21750-290</t>
+  </si>
+  <si>
+    <t>21765-590</t>
+  </si>
+  <si>
+    <t>SÃO LINO</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t xml:space="preserve">SÃO DIMAS </t>
+  </si>
+  <si>
+    <t>SÃO OTO</t>
+  </si>
+  <si>
+    <t>21740-530</t>
   </si>
 </sst>
 </file>
@@ -1540,7 +1555,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H1027"/>
+  <dimension ref="A1:H1030"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.453125" customWidth="1"/>
@@ -1571,7 +1586,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="25" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
@@ -1579,7 +1594,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C2" s="34">
         <v>13</v>
@@ -1588,7 +1603,7 @@
         <v>22</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F2" s="32" t="s">
         <v>26</v>
@@ -1635,7 +1650,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C4" s="34">
         <v>13</v>
@@ -1644,7 +1659,7 @@
         <v>22</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F4" s="32" t="s">
         <v>26</v>
@@ -1663,7 +1678,7 @@
         <v>13</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C5" s="34">
         <v>13</v>
@@ -1672,7 +1687,7 @@
         <v>22</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F5" s="32" t="s">
         <v>26</v>
@@ -1719,7 +1734,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C7" s="34">
         <v>13</v>
@@ -1728,7 +1743,7 @@
         <v>22</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F7" s="32" t="s">
         <v>26</v>
@@ -1747,7 +1762,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C8" s="34">
         <v>13</v>
@@ -1756,7 +1771,7 @@
         <v>22</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F8" s="32" t="s">
         <v>26</v>
@@ -1803,7 +1818,7 @@
         <v>13</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C10" s="34">
         <v>13</v>
@@ -1812,7 +1827,7 @@
         <v>22</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F10" s="32" t="s">
         <v>26</v>
@@ -1837,7 +1852,7 @@
         <v>13</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E11" s="33" t="s">
         <v>8</v>
@@ -1859,7 +1874,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C12" s="34">
         <v>13</v>
@@ -1868,7 +1883,7 @@
         <v>22</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F12" s="32" t="s">
         <v>26</v>
@@ -1915,7 +1930,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C14" s="34">
         <v>13</v>
@@ -1924,7 +1939,7 @@
         <v>22</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F14" s="32" t="s">
         <v>26</v>
@@ -2033,10 +2048,10 @@
         <v>15</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F18" s="26" t="s">
         <v>77</v>
@@ -2061,7 +2076,7 @@
         <v>15</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E19" s="27" t="s">
         <v>8</v>
@@ -2089,7 +2104,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E20" s="27" t="s">
         <v>8</v>
@@ -2117,7 +2132,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E21" s="27" t="s">
         <v>8</v>
@@ -2145,7 +2160,7 @@
         <v>15</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E22" s="27" t="s">
         <v>8</v>
@@ -2167,16 +2182,16 @@
         <v>15</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C23" s="28">
         <v>15</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F23" s="26" t="s">
         <v>66</v>
@@ -2195,7 +2210,7 @@
         <v>15</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C24" s="28">
         <v>15</v>
@@ -2207,7 +2222,7 @@
         <v>8</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G24" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B24),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E24),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F24),0)&gt;0), MAX($G$1:G23)+1, ""))</f>
@@ -2229,7 +2244,7 @@
         <v>15</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E25" s="27" t="s">
         <v>8</v>
@@ -2251,13 +2266,13 @@
         <v>15</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C26" s="28">
         <v>15</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E26" s="27" t="s">
         <v>8</v>
@@ -2279,7 +2294,7 @@
         <v>15</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C27" s="28">
         <v>15</v>
@@ -2288,10 +2303,10 @@
         <v>2.1</v>
       </c>
       <c r="E27" s="27" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G27" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B27),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E27),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F27),0)&gt;0), MAX($G$1:G26)+1, ""))</f>
@@ -2313,7 +2328,7 @@
         <v>15</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E28" s="27" t="s">
         <v>8</v>
@@ -2335,13 +2350,13 @@
         <v>15</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C29" s="28">
         <v>15</v>
       </c>
       <c r="D29" s="26" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E29" s="27" t="s">
         <v>8</v>
@@ -2363,7 +2378,7 @@
         <v>15</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C30" s="28">
         <v>15</v>
@@ -2375,7 +2390,7 @@
         <v>8</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G30" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B30),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E30),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F30),0)&gt;0), MAX($G$1:G29)+1, ""))</f>
@@ -2391,7 +2406,7 @@
         <v>15</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C31" s="28">
         <v>15</v>
@@ -2403,7 +2418,7 @@
         <v>8</v>
       </c>
       <c r="F31" s="26" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G31" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B31),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E31),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F31),0)&gt;0), MAX($G$1:G30)+1, ""))</f>
@@ -2425,7 +2440,7 @@
         <v>15</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E32" s="27" t="s">
         <v>8</v>
@@ -2453,7 +2468,7 @@
         <v>15</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E33" s="27" t="s">
         <v>8</v>
@@ -2481,7 +2496,7 @@
         <v>15</v>
       </c>
       <c r="D34" s="26" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E34" s="27" t="s">
         <v>8</v>
@@ -2509,7 +2524,7 @@
         <v>15</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E35" s="27" t="s">
         <v>8</v>
@@ -2537,7 +2552,7 @@
         <v>15</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E36" s="27" t="s">
         <v>8</v>
@@ -2559,7 +2574,7 @@
         <v>15</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C37" s="28">
         <v>15</v>
@@ -2571,7 +2586,7 @@
         <v>8</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G37" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F37),0)&gt;0), MAX($G$1:G36)+1, ""))</f>
@@ -2587,7 +2602,7 @@
         <v>15</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C38" s="28">
         <v>15</v>
@@ -2596,10 +2611,10 @@
         <v>2.1</v>
       </c>
       <c r="E38" s="27" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F38" s="26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G38" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F38),0)&gt;0), MAX($G$1:G37)+1, ""))</f>
@@ -2621,7 +2636,7 @@
         <v>15</v>
       </c>
       <c r="D39" s="26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E39" s="27" t="s">
         <v>8</v>
@@ -2649,7 +2664,7 @@
         <v>15</v>
       </c>
       <c r="D40" s="26" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E40" s="27" t="s">
         <v>8</v>
@@ -2671,16 +2686,16 @@
         <v>15</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C41" s="28">
         <v>15</v>
       </c>
       <c r="D41" s="26" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E41" s="27" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F41" s="26" t="s">
         <v>34</v>
@@ -2705,7 +2720,7 @@
         <v>17</v>
       </c>
       <c r="D42" s="35" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E42" s="36" t="s">
         <v>8</v>
@@ -2727,13 +2742,13 @@
         <v>17</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C43" s="37">
         <v>17</v>
       </c>
       <c r="D43" s="35" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E43" s="36" t="s">
         <v>61</v>
@@ -2755,7 +2770,7 @@
         <v>17</v>
       </c>
       <c r="B44" s="27" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C44" s="28">
         <v>17</v>
@@ -2767,7 +2782,7 @@
         <v>61</v>
       </c>
       <c r="F44" s="26" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G44" s="29"/>
       <c r="H44" s="21" t="b">
@@ -2786,7 +2801,7 @@
         <v>17</v>
       </c>
       <c r="D45" s="35" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E45" s="36" t="s">
         <v>8</v>
@@ -2814,7 +2829,7 @@
         <v>17</v>
       </c>
       <c r="D46" s="35" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E46" s="36" t="s">
         <v>61</v>
@@ -2836,7 +2851,7 @@
         <v>17</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C47" s="28">
         <v>17</v>
@@ -2848,7 +2863,7 @@
         <v>61</v>
       </c>
       <c r="F47" s="26" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G47" s="29"/>
       <c r="H47" s="21" t="b">
@@ -2861,7 +2876,7 @@
         <v>17</v>
       </c>
       <c r="B48" s="27" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C48" s="28">
         <v>17</v>
@@ -2873,7 +2888,7 @@
         <v>61</v>
       </c>
       <c r="F48" s="26" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G48" s="29"/>
       <c r="H48" s="21" t="b">
@@ -2886,13 +2901,13 @@
         <v>17</v>
       </c>
       <c r="B49" s="39" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C49" s="40">
         <v>17</v>
       </c>
       <c r="D49" s="38" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E49" s="39" t="s">
         <v>61</v>
@@ -2914,7 +2929,7 @@
         <v>17</v>
       </c>
       <c r="B50" s="27" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C50" s="28">
         <v>17</v>
@@ -2926,7 +2941,7 @@
         <v>61</v>
       </c>
       <c r="F50" s="26" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G50" s="29"/>
       <c r="H50" s="21" t="b">
@@ -2939,7 +2954,7 @@
         <v>17</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C51" s="28">
         <v>17</v>
@@ -2951,7 +2966,7 @@
         <v>61</v>
       </c>
       <c r="F51" s="26" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G51" s="29"/>
       <c r="H51" s="21" t="b">
@@ -2970,7 +2985,7 @@
         <v>17</v>
       </c>
       <c r="D52" s="38" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E52" s="39" t="s">
         <v>8</v>
@@ -2992,16 +3007,16 @@
         <v>17</v>
       </c>
       <c r="B53" s="39" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C53" s="40">
         <v>17</v>
       </c>
       <c r="D53" s="38" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E53" s="39" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F53" s="38" t="s">
         <v>107</v>
@@ -3026,7 +3041,7 @@
         <v>17</v>
       </c>
       <c r="D54" s="35" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E54" s="36" t="s">
         <v>8</v>
@@ -3054,7 +3069,7 @@
         <v>17</v>
       </c>
       <c r="D55" s="35" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E55" s="36" t="s">
         <v>8</v>
@@ -3082,7 +3097,7 @@
         <v>17</v>
       </c>
       <c r="D56" s="38" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E56" s="39" t="s">
         <v>8</v>
@@ -3110,7 +3125,7 @@
         <v>17</v>
       </c>
       <c r="D57" s="38" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E57" s="39" t="s">
         <v>8</v>
@@ -3132,54 +3147,50 @@
         <v>17</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>37</v>
+        <v>331</v>
       </c>
       <c r="C58" s="37">
         <v>17</v>
       </c>
-      <c r="D58" s="35" t="s">
-        <v>218</v>
+      <c r="D58" s="35">
+        <v>1.9</v>
       </c>
       <c r="E58" s="36" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="F58" s="35" t="s">
-        <v>38</v>
-      </c>
-      <c r="G58" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F58),0)&gt;0), MAX($G$1:G57)+1, ""))</f>
-        <v/>
+        <v>333</v>
+      </c>
+      <c r="G58" s="29" t="s">
+        <v>330</v>
       </c>
       <c r="H58" s="21" t="b">
-        <f>A58=C58</f>
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A59" s="38">
+      <c r="A59" s="35">
         <v>17</v>
       </c>
-      <c r="B59" s="39" t="s">
-        <v>85</v>
-      </c>
-      <c r="C59" s="40">
+      <c r="B59" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="C59" s="37">
         <v>17</v>
       </c>
-      <c r="D59" s="38" t="s">
-        <v>223</v>
-      </c>
-      <c r="E59" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F59" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="G59" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F59),0)&gt;0), MAX($G$1:G58)+1, ""))</f>
-        <v/>
+      <c r="D59" s="35">
+        <v>1.9</v>
+      </c>
+      <c r="E59" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="F59" s="35" t="s">
+        <v>333</v>
+      </c>
+      <c r="G59" s="29" t="s">
+        <v>330</v>
       </c>
       <c r="H59" s="21" t="b">
-        <f>A59=C59</f>
         <v>1</v>
       </c>
     </row>
@@ -3188,26 +3199,24 @@
         <v>17</v>
       </c>
       <c r="B60" s="36" t="s">
-        <v>32</v>
+        <v>332</v>
       </c>
       <c r="C60" s="37">
         <v>17</v>
       </c>
-      <c r="D60" s="35" t="s">
-        <v>212</v>
+      <c r="D60" s="35">
+        <v>1.9</v>
       </c>
       <c r="E60" s="36" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="F60" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="G60" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F60),0)&gt;0), MAX($G$1:G59)+1, ""))</f>
-        <v/>
+        <v>333</v>
+      </c>
+      <c r="G60" s="29" t="s">
+        <v>330</v>
       </c>
       <c r="H60" s="21" t="b">
-        <f>A60=C60</f>
         <v>1</v>
       </c>
     </row>
@@ -3216,19 +3225,19 @@
         <v>17</v>
       </c>
       <c r="B61" s="36" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C61" s="37">
         <v>17</v>
       </c>
       <c r="D61" s="35" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="E61" s="36" t="s">
         <v>8</v>
       </c>
       <c r="F61" s="35" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G61" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F61),0)&gt;0), MAX($G$1:G60)+1, ""))</f>
@@ -3240,23 +3249,23 @@
       </c>
     </row>
     <row r="62" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A62" s="32">
-        <v>20</v>
-      </c>
-      <c r="B62" s="33" t="s">
-        <v>148</v>
-      </c>
-      <c r="C62" s="34">
-        <v>20</v>
-      </c>
-      <c r="D62" s="32" t="s">
-        <v>210</v>
-      </c>
-      <c r="E62" s="33" t="s">
+      <c r="A62" s="38">
+        <v>17</v>
+      </c>
+      <c r="B62" s="39" t="s">
+        <v>85</v>
+      </c>
+      <c r="C62" s="40">
+        <v>17</v>
+      </c>
+      <c r="D62" s="38" t="s">
+        <v>222</v>
+      </c>
+      <c r="E62" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="F62" s="32" t="s">
-        <v>149</v>
+      <c r="F62" s="38" t="s">
+        <v>86</v>
       </c>
       <c r="G62" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F62),0)&gt;0), MAX($G$1:G61)+1, ""))</f>
@@ -3268,23 +3277,23 @@
       </c>
     </row>
     <row r="63" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A63" s="32">
-        <v>20</v>
-      </c>
-      <c r="B63" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="C63" s="34">
-        <v>20</v>
-      </c>
-      <c r="D63" s="32" t="s">
-        <v>213</v>
-      </c>
-      <c r="E63" s="33" t="s">
+      <c r="A63" s="35">
+        <v>17</v>
+      </c>
+      <c r="B63" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C63" s="37">
+        <v>17</v>
+      </c>
+      <c r="D63" s="35" t="s">
+        <v>211</v>
+      </c>
+      <c r="E63" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="F63" s="32" t="s">
-        <v>147</v>
+      <c r="F63" s="35" t="s">
+        <v>33</v>
       </c>
       <c r="G63" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F63),0)&gt;0), MAX($G$1:G62)+1, ""))</f>
@@ -3296,30 +3305,28 @@
       </c>
     </row>
     <row r="64" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A64" s="32">
-        <v>20</v>
-      </c>
-      <c r="B64" s="33" t="s">
-        <v>144</v>
-      </c>
-      <c r="C64" s="34">
-        <v>20</v>
-      </c>
-      <c r="D64" s="32" t="s">
-        <v>215</v>
-      </c>
-      <c r="E64" s="33" t="s">
+      <c r="A64" s="35">
+        <v>17</v>
+      </c>
+      <c r="B64" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C64" s="37">
+        <v>17</v>
+      </c>
+      <c r="D64" s="35" t="s">
+        <v>210</v>
+      </c>
+      <c r="E64" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="F64" s="32" t="s">
-        <v>145</v>
-      </c>
-      <c r="G64" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F64),0)&gt;0), MAX($G$1:G63)+1, ""))</f>
-        <v/>
+      <c r="F64" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="G64" s="29" t="s">
+        <v>330</v>
       </c>
       <c r="H64" s="21" t="b">
-        <f>A64=C64</f>
         <v>1</v>
       </c>
     </row>
@@ -3328,22 +3335,22 @@
         <v>20</v>
       </c>
       <c r="B65" s="33" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C65" s="34">
         <v>20</v>
       </c>
       <c r="D65" s="32" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="E65" s="33" t="s">
-        <v>310</v>
+        <v>8</v>
       </c>
       <c r="F65" s="32" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="G65" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F65),0)&gt;0), MAX($G$1:G64)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F65),0)&gt;0), MAX($G$1:G61)+1, ""))</f>
         <v/>
       </c>
       <c r="H65" s="21" t="b">
@@ -3356,19 +3363,19 @@
         <v>20</v>
       </c>
       <c r="B66" s="33" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="C66" s="34">
         <v>20</v>
       </c>
       <c r="D66" s="32" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="E66" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F66" s="32" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G66" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F66),0)&gt;0), MAX($G$1:G65)+1, ""))</f>
@@ -3384,19 +3391,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="33" t="s">
-        <v>260</v>
+        <v>144</v>
       </c>
       <c r="C67" s="34">
         <v>20</v>
       </c>
       <c r="D67" s="32" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="E67" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F67" s="32" t="s">
-        <v>261</v>
+        <v>145</v>
       </c>
       <c r="G67" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F67),0)&gt;0), MAX($G$1:G66)+1, ""))</f>
@@ -3412,19 +3419,19 @@
         <v>20</v>
       </c>
       <c r="B68" s="33" t="s">
-        <v>259</v>
+        <v>142</v>
       </c>
       <c r="C68" s="34">
         <v>20</v>
       </c>
-      <c r="D68" s="32">
-        <v>4.2</v>
+      <c r="D68" s="32" t="s">
+        <v>219</v>
       </c>
       <c r="E68" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="F68" s="32">
-        <v>21765430</v>
+        <v>309</v>
+      </c>
+      <c r="F68" s="32" t="s">
+        <v>143</v>
       </c>
       <c r="G68" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F68),0)&gt;0), MAX($G$1:G67)+1, ""))</f>
@@ -3440,19 +3447,19 @@
         <v>20</v>
       </c>
       <c r="B69" s="33" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C69" s="34">
         <v>20</v>
       </c>
       <c r="D69" s="32" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="E69" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F69" s="32" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G69" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F69),0)&gt;0), MAX($G$1:G68)+1, ""))</f>
@@ -3468,19 +3475,19 @@
         <v>20</v>
       </c>
       <c r="B70" s="33" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="C70" s="34">
         <v>20</v>
       </c>
       <c r="D70" s="32" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E70" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F70" s="32" t="s">
-        <v>137</v>
+        <v>260</v>
       </c>
       <c r="G70" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F70),0)&gt;0), MAX($G$1:G69)+1, ""))</f>
@@ -3496,19 +3503,19 @@
         <v>20</v>
       </c>
       <c r="B71" s="33" t="s">
-        <v>135</v>
+        <v>258</v>
       </c>
       <c r="C71" s="34">
         <v>20</v>
       </c>
-      <c r="D71" s="32" t="s">
-        <v>223</v>
+      <c r="D71" s="32">
+        <v>4.2</v>
       </c>
       <c r="E71" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="F71" s="32" t="s">
-        <v>136</v>
+        <v>309</v>
+      </c>
+      <c r="F71" s="32">
+        <v>21765430</v>
       </c>
       <c r="G71" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F71),0)&gt;0), MAX($G$1:G70)+1, ""))</f>
@@ -3524,19 +3531,19 @@
         <v>20</v>
       </c>
       <c r="B72" s="33" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C72" s="34">
         <v>20</v>
       </c>
       <c r="D72" s="32" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E72" s="33" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="F72" s="32" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G72" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F72),0)&gt;0), MAX($G$1:G71)+1, ""))</f>
@@ -3548,23 +3555,23 @@
       </c>
     </row>
     <row r="73" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A73" s="26">
+      <c r="A73" s="32">
         <v>20</v>
       </c>
-      <c r="B73" s="27" t="s">
-        <v>317</v>
-      </c>
-      <c r="C73" s="28">
+      <c r="B73" s="33" t="s">
+        <v>269</v>
+      </c>
+      <c r="C73" s="34">
         <v>20</v>
       </c>
-      <c r="D73" s="26">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="E73" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="F73" s="26" t="s">
-        <v>323</v>
+      <c r="D73" s="32" t="s">
+        <v>225</v>
+      </c>
+      <c r="E73" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F73" s="32" t="s">
+        <v>137</v>
       </c>
       <c r="G73" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F73),0)&gt;0), MAX($G$1:G72)+1, ""))</f>
@@ -3580,19 +3587,19 @@
         <v>20</v>
       </c>
       <c r="B74" s="33" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C74" s="34">
         <v>20</v>
       </c>
       <c r="D74" s="32" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E74" s="33" t="s">
-        <v>8</v>
+        <v>309</v>
       </c>
       <c r="F74" s="32" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="G74" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F74),0)&gt;0), MAX($G$1:G73)+1, ""))</f>
@@ -3608,19 +3615,19 @@
         <v>20</v>
       </c>
       <c r="B75" s="33" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C75" s="34">
         <v>20</v>
       </c>
       <c r="D75" s="32" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="E75" s="33" t="s">
-        <v>310</v>
+        <v>133</v>
       </c>
       <c r="F75" s="32" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="G75" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F75),0)&gt;0), MAX($G$1:G74)+1, ""))</f>
@@ -3632,23 +3639,23 @@
       </c>
     </row>
     <row r="76" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A76" s="32">
+      <c r="A76" s="26">
         <v>20</v>
       </c>
-      <c r="B76" s="33" t="s">
-        <v>126</v>
-      </c>
-      <c r="C76" s="34">
+      <c r="B76" s="27" t="s">
+        <v>316</v>
+      </c>
+      <c r="C76" s="28">
         <v>20</v>
       </c>
-      <c r="D76" s="32" t="s">
-        <v>234</v>
-      </c>
-      <c r="E76" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F76" s="32" t="s">
-        <v>127</v>
+      <c r="D76" s="26">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E76" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="F76" s="26" t="s">
+        <v>322</v>
       </c>
       <c r="G76" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F76),0)&gt;0), MAX($G$1:G75)+1, ""))</f>
@@ -3664,19 +3671,19 @@
         <v>20</v>
       </c>
       <c r="B77" s="33" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C77" s="34">
         <v>20</v>
       </c>
       <c r="D77" s="32" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E77" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F77" s="32" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="G77" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F77),0)&gt;0), MAX($G$1:G76)+1, ""))</f>
@@ -3692,19 +3699,19 @@
         <v>20</v>
       </c>
       <c r="B78" s="33" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C78" s="34">
         <v>20</v>
       </c>
       <c r="D78" s="32" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="E78" s="33" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F78" s="32" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="G78" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F78),0)&gt;0), MAX($G$1:G77)+1, ""))</f>
@@ -3720,19 +3727,19 @@
         <v>20</v>
       </c>
       <c r="B79" s="33" t="s">
-        <v>262</v>
+        <v>126</v>
       </c>
       <c r="C79" s="34">
         <v>20</v>
       </c>
       <c r="D79" s="32" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E79" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F79" s="32" t="s">
-        <v>263</v>
+        <v>127</v>
       </c>
       <c r="G79" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F79),0)&gt;0), MAX($G$1:G78)+1, ""))</f>
@@ -3748,19 +3755,19 @@
         <v>20</v>
       </c>
       <c r="B80" s="33" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C80" s="34">
         <v>20</v>
       </c>
       <c r="D80" s="32" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="E80" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F80" s="32" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G80" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F80),0)&gt;0), MAX($G$1:G79)+1, ""))</f>
@@ -3776,19 +3783,19 @@
         <v>20</v>
       </c>
       <c r="B81" s="33" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C81" s="34">
         <v>20</v>
       </c>
       <c r="D81" s="32" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="E81" s="33" t="s">
-        <v>8</v>
+        <v>309</v>
       </c>
       <c r="F81" s="32" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G81" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F81),0)&gt;0), MAX($G$1:G80)+1, ""))</f>
@@ -3804,19 +3811,19 @@
         <v>20</v>
       </c>
       <c r="B82" s="33" t="s">
-        <v>116</v>
+        <v>261</v>
       </c>
       <c r="C82" s="34">
         <v>20</v>
       </c>
       <c r="D82" s="32" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="E82" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F82" s="32" t="s">
-        <v>117</v>
+        <v>262</v>
       </c>
       <c r="G82" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F82),0)&gt;0), MAX($G$1:G81)+1, ""))</f>
@@ -3828,23 +3835,23 @@
       </c>
     </row>
     <row r="83" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A83" s="26">
+      <c r="A83" s="32">
         <v>20</v>
       </c>
-      <c r="B83" s="27" t="s">
-        <v>302</v>
-      </c>
-      <c r="C83" s="28">
+      <c r="B83" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="C83" s="34">
         <v>20</v>
       </c>
-      <c r="D83" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E83" s="27" t="s">
-        <v>304</v>
-      </c>
-      <c r="F83" s="26" t="s">
-        <v>303</v>
+      <c r="D83" s="32" t="s">
+        <v>230</v>
+      </c>
+      <c r="E83" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" s="32" t="s">
+        <v>121</v>
       </c>
       <c r="G83" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F83),0)&gt;0), MAX($G$1:G82)+1, ""))</f>
@@ -3860,19 +3867,19 @@
         <v>20</v>
       </c>
       <c r="B84" s="33" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C84" s="34">
         <v>20</v>
       </c>
       <c r="D84" s="32" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="E84" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F84" s="32" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G84" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F84),0)&gt;0), MAX($G$1:G83)+1, ""))</f>
@@ -3888,19 +3895,19 @@
         <v>20</v>
       </c>
       <c r="B85" s="33" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C85" s="34">
         <v>20</v>
       </c>
       <c r="D85" s="32" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="E85" s="33" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="F85" s="32" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G85" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F85),0)&gt;0), MAX($G$1:G84)+1, ""))</f>
@@ -3912,23 +3919,23 @@
       </c>
     </row>
     <row r="86" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A86" s="32">
+      <c r="A86" s="26">
         <v>20</v>
       </c>
-      <c r="B86" s="33" t="s">
-        <v>110</v>
-      </c>
-      <c r="C86" s="34">
+      <c r="B86" s="27" t="s">
+        <v>301</v>
+      </c>
+      <c r="C86" s="28">
         <v>20</v>
       </c>
-      <c r="D86" s="32" t="s">
-        <v>222</v>
-      </c>
-      <c r="E86" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F86" s="32" t="s">
-        <v>111</v>
+      <c r="D86" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E86" s="27" t="s">
+        <v>303</v>
+      </c>
+      <c r="F86" s="26" t="s">
+        <v>302</v>
       </c>
       <c r="G86" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F86),0)&gt;0), MAX($G$1:G85)+1, ""))</f>
@@ -3940,23 +3947,23 @@
       </c>
     </row>
     <row r="87" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A87" s="26">
+      <c r="A87" s="32">
         <v>20</v>
       </c>
-      <c r="B87" s="27" t="s">
-        <v>307</v>
-      </c>
-      <c r="C87" s="28">
+      <c r="B87" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="C87" s="34">
         <v>20</v>
       </c>
-      <c r="D87" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E87" s="27" t="s">
-        <v>304</v>
-      </c>
-      <c r="F87" s="26" t="s">
-        <v>306</v>
+      <c r="D87" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E87" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F87" s="32" t="s">
+        <v>115</v>
       </c>
       <c r="G87" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F87),0)&gt;0), MAX($G$1:G86)+1, ""))</f>
@@ -3972,19 +3979,19 @@
         <v>20</v>
       </c>
       <c r="B88" s="33" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C88" s="34">
         <v>20</v>
       </c>
       <c r="D88" s="32" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="E88" s="33" t="s">
-        <v>61</v>
+        <v>303</v>
       </c>
       <c r="F88" s="32" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="G88" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F88),0)&gt;0), MAX($G$1:G87)+1, ""))</f>
@@ -4000,19 +4007,19 @@
         <v>20</v>
       </c>
       <c r="B89" s="33" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C89" s="34">
         <v>20</v>
       </c>
       <c r="D89" s="32" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="E89" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F89" s="32" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G89" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F89),0)&gt;0), MAX($G$1:G88)+1, ""))</f>
@@ -4024,23 +4031,23 @@
       </c>
     </row>
     <row r="90" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A90" s="32">
+      <c r="A90" s="26">
         <v>20</v>
       </c>
-      <c r="B90" s="33" t="s">
-        <v>268</v>
-      </c>
-      <c r="C90" s="34">
+      <c r="B90" s="27" t="s">
+        <v>306</v>
+      </c>
+      <c r="C90" s="28">
         <v>20</v>
       </c>
-      <c r="D90" s="32">
-        <v>6.2</v>
-      </c>
-      <c r="E90" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F90" s="32" t="s">
-        <v>269</v>
+      <c r="D90" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E90" s="27" t="s">
+        <v>303</v>
+      </c>
+      <c r="F90" s="26" t="s">
+        <v>305</v>
       </c>
       <c r="G90" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F90),0)&gt;0), MAX($G$1:G89)+1, ""))</f>
@@ -4056,19 +4063,19 @@
         <v>20</v>
       </c>
       <c r="B91" s="33" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C91" s="34">
         <v>20</v>
       </c>
       <c r="D91" s="32" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E91" s="33" t="s">
-        <v>304</v>
+        <v>61</v>
       </c>
       <c r="F91" s="32" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G91" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F91),0)&gt;0), MAX($G$1:G90)+1, ""))</f>
@@ -4080,23 +4087,23 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A92" s="26">
+      <c r="A92" s="32">
         <v>20</v>
       </c>
-      <c r="B92" s="27" t="s">
-        <v>305</v>
-      </c>
-      <c r="C92" s="28">
+      <c r="B92" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="C92" s="34">
         <v>20</v>
       </c>
-      <c r="D92" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E92" s="27" t="s">
-        <v>304</v>
-      </c>
-      <c r="F92" s="26" t="s">
-        <v>306</v>
+      <c r="D92" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="E92" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F92" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G92" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F92),0)&gt;0), MAX($G$1:G91)+1, ""))</f>
@@ -4112,19 +4119,19 @@
         <v>20</v>
       </c>
       <c r="B93" s="33" t="s">
-        <v>97</v>
+        <v>267</v>
       </c>
       <c r="C93" s="34">
         <v>20</v>
       </c>
-      <c r="D93" s="32" t="s">
-        <v>220</v>
+      <c r="D93" s="32">
+        <v>6.2</v>
       </c>
       <c r="E93" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F93" s="32" t="s">
-        <v>98</v>
+        <v>268</v>
       </c>
       <c r="G93" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F93),0)&gt;0), MAX($G$1:G92)+1, ""))</f>
@@ -4140,19 +4147,19 @@
         <v>20</v>
       </c>
       <c r="B94" s="33" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C94" s="34">
         <v>20</v>
       </c>
       <c r="D94" s="32" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E94" s="33" t="s">
-        <v>8</v>
+        <v>303</v>
       </c>
       <c r="F94" s="32" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="G94" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F94),0)&gt;0), MAX($G$1:G93)+1, ""))</f>
@@ -4164,23 +4171,23 @@
       </c>
     </row>
     <row r="95" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A95" s="32">
+      <c r="A95" s="26">
         <v>20</v>
       </c>
-      <c r="B95" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="C95" s="34">
+      <c r="B95" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="C95" s="28">
         <v>20</v>
       </c>
-      <c r="D95" s="32" t="s">
-        <v>227</v>
-      </c>
-      <c r="E95" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F95" s="32" t="s">
-        <v>92</v>
+      <c r="D95" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E95" s="27" t="s">
+        <v>303</v>
+      </c>
+      <c r="F95" s="26" t="s">
+        <v>305</v>
       </c>
       <c r="G95" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F95),0)&gt;0), MAX($G$1:G94)+1, ""))</f>
@@ -4196,19 +4203,19 @@
         <v>20</v>
       </c>
       <c r="B96" s="33" t="s">
-        <v>295</v>
+        <v>97</v>
       </c>
       <c r="C96" s="34">
         <v>20</v>
       </c>
-      <c r="D96" s="32">
-        <v>1.8</v>
+      <c r="D96" s="32" t="s">
+        <v>219</v>
       </c>
       <c r="E96" s="33" t="s">
-        <v>296</v>
+        <v>8</v>
       </c>
       <c r="F96" s="32" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G96" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F96),0)&gt;0), MAX($G$1:G95)+1, ""))</f>
@@ -4224,19 +4231,19 @@
         <v>20</v>
       </c>
       <c r="B97" s="33" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C97" s="34">
         <v>20</v>
       </c>
       <c r="D97" s="32" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E97" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F97" s="32" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G97" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F97),0)&gt;0), MAX($G$1:G96)+1, ""))</f>
@@ -4252,19 +4259,19 @@
         <v>20</v>
       </c>
       <c r="B98" s="33" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C98" s="34">
         <v>20</v>
       </c>
       <c r="D98" s="32" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E98" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F98" s="32" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G98" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F98),0)&gt;0), MAX($G$1:G97)+1, ""))</f>
@@ -4280,19 +4287,19 @@
         <v>20</v>
       </c>
       <c r="B99" s="33" t="s">
-        <v>82</v>
+        <v>294</v>
       </c>
       <c r="C99" s="34">
         <v>20</v>
       </c>
-      <c r="D99" s="32" t="s">
-        <v>222</v>
+      <c r="D99" s="32">
+        <v>1.8</v>
       </c>
       <c r="E99" s="33" t="s">
-        <v>83</v>
+        <v>295</v>
       </c>
       <c r="F99" s="32" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G99" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F99),0)&gt;0), MAX($G$1:G98)+1, ""))</f>
@@ -4308,19 +4315,19 @@
         <v>20</v>
       </c>
       <c r="B100" s="33" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C100" s="34">
         <v>20</v>
       </c>
       <c r="D100" s="32" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="E100" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F100" s="32" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G100" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F100),0)&gt;0), MAX($G$1:G99)+1, ""))</f>
@@ -4336,19 +4343,19 @@
         <v>20</v>
       </c>
       <c r="B101" s="33" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C101" s="34">
         <v>20</v>
       </c>
       <c r="D101" s="32" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E101" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F101" s="32" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G101" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F101),0)&gt;0), MAX($G$1:G100)+1, ""))</f>
@@ -4360,23 +4367,23 @@
       </c>
     </row>
     <row r="102" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A102" s="26">
-        <v>25</v>
-      </c>
-      <c r="B102" s="27" t="s">
-        <v>182</v>
-      </c>
-      <c r="C102" s="28">
-        <v>25</v>
-      </c>
-      <c r="D102" s="26" t="s">
-        <v>229</v>
-      </c>
-      <c r="E102" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F102" s="26" t="s">
-        <v>183</v>
+      <c r="A102" s="32">
+        <v>20</v>
+      </c>
+      <c r="B102" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C102" s="34">
+        <v>20</v>
+      </c>
+      <c r="D102" s="32" t="s">
+        <v>221</v>
+      </c>
+      <c r="E102" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="F102" s="32" t="s">
+        <v>84</v>
       </c>
       <c r="G102" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F102),0)&gt;0), MAX($G$1:G101)+1, ""))</f>
@@ -4388,23 +4395,23 @@
       </c>
     </row>
     <row r="103" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A103" s="26">
-        <v>25</v>
-      </c>
-      <c r="B103" s="27" t="s">
-        <v>180</v>
-      </c>
-      <c r="C103" s="28">
-        <v>25</v>
-      </c>
-      <c r="D103" s="26" t="s">
-        <v>242</v>
-      </c>
-      <c r="E103" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F103" s="26" t="s">
-        <v>181</v>
+      <c r="A103" s="32">
+        <v>20</v>
+      </c>
+      <c r="B103" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C103" s="34">
+        <v>20</v>
+      </c>
+      <c r="D103" s="32" t="s">
+        <v>220</v>
+      </c>
+      <c r="E103" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F103" s="32" t="s">
+        <v>81</v>
       </c>
       <c r="G103" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F103),0)&gt;0), MAX($G$1:G102)+1, ""))</f>
@@ -4416,23 +4423,23 @@
       </c>
     </row>
     <row r="104" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A104" s="26">
-        <v>25</v>
-      </c>
-      <c r="B104" s="27" t="s">
-        <v>178</v>
-      </c>
-      <c r="C104" s="28">
-        <v>25</v>
-      </c>
-      <c r="D104" s="26" t="s">
-        <v>235</v>
-      </c>
-      <c r="E104" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F104" s="26" t="s">
-        <v>179</v>
+      <c r="A104" s="32">
+        <v>20</v>
+      </c>
+      <c r="B104" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="C104" s="34">
+        <v>20</v>
+      </c>
+      <c r="D104" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="E104" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F104" s="32" t="s">
+        <v>79</v>
       </c>
       <c r="G104" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F104),0)&gt;0), MAX($G$1:G103)+1, ""))</f>
@@ -4448,7 +4455,7 @@
         <v>25</v>
       </c>
       <c r="B105" s="27" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C105" s="28">
         <v>25</v>
@@ -4460,7 +4467,7 @@
         <v>8</v>
       </c>
       <c r="F105" s="26" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="G105" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F105),0)&gt;0), MAX($G$1:G104)+1, ""))</f>
@@ -4476,7 +4483,7 @@
         <v>25</v>
       </c>
       <c r="B106" s="27" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C106" s="28">
         <v>25</v>
@@ -4488,7 +4495,7 @@
         <v>133</v>
       </c>
       <c r="F106" s="26" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G106" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F106),0)&gt;0), MAX($G$1:G105)+1, ""))</f>
@@ -4500,23 +4507,23 @@
       </c>
     </row>
     <row r="107" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A107" s="32">
+      <c r="A107" s="26">
         <v>25</v>
       </c>
-      <c r="B107" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="C107" s="34">
+      <c r="B107" s="27" t="s">
+        <v>177</v>
+      </c>
+      <c r="C107" s="28">
         <v>25</v>
       </c>
-      <c r="D107" s="32" t="s">
-        <v>211</v>
-      </c>
-      <c r="E107" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="F107" s="32" t="s">
-        <v>104</v>
+      <c r="D107" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="E107" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="F107" s="26" t="s">
+        <v>178</v>
       </c>
       <c r="G107" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F107),0)&gt;0), MAX($G$1:G106)+1, ""))</f>
@@ -4528,23 +4535,23 @@
       </c>
     </row>
     <row r="108" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A108" s="32">
+      <c r="A108" s="26">
         <v>25</v>
       </c>
-      <c r="B108" s="33" t="s">
-        <v>287</v>
-      </c>
-      <c r="C108" s="34">
+      <c r="B108" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="C108" s="28">
         <v>25</v>
       </c>
-      <c r="D108" s="32" t="s">
-        <v>211</v>
-      </c>
-      <c r="E108" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="F108" s="32" t="s">
-        <v>104</v>
+      <c r="D108" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="E108" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F108" s="26" t="s">
+        <v>328</v>
       </c>
       <c r="G108" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F108),0)&gt;0), MAX($G$1:G107)+1, ""))</f>
@@ -4560,19 +4567,19 @@
         <v>25</v>
       </c>
       <c r="B109" s="27" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C109" s="28">
         <v>25</v>
       </c>
       <c r="D109" s="26" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E109" s="27" t="s">
         <v>133</v>
       </c>
       <c r="F109" s="26" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G109" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F109),0)&gt;0), MAX($G$1:G108)+1, ""))</f>
@@ -4584,23 +4591,23 @@
       </c>
     </row>
     <row r="110" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A110" s="26">
+      <c r="A110" s="32">
         <v>25</v>
       </c>
-      <c r="B110" s="27" t="s">
-        <v>170</v>
-      </c>
-      <c r="C110" s="28">
+      <c r="B110" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="C110" s="34">
         <v>25</v>
       </c>
-      <c r="D110" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="E110" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F110" s="26" t="s">
-        <v>171</v>
+      <c r="D110" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="E110" s="33" t="s">
+        <v>287</v>
+      </c>
+      <c r="F110" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G110" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F110),0)&gt;0), MAX($G$1:G109)+1, ""))</f>
@@ -4616,16 +4623,16 @@
         <v>25</v>
       </c>
       <c r="B111" s="33" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C111" s="34">
         <v>25</v>
       </c>
       <c r="D111" s="32" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E111" s="33" t="s">
-        <v>8</v>
+        <v>287</v>
       </c>
       <c r="F111" s="32" t="s">
         <v>104</v>
@@ -4644,19 +4651,19 @@
         <v>25</v>
       </c>
       <c r="B112" s="27" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C112" s="28">
         <v>25</v>
       </c>
       <c r="D112" s="26" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="E112" s="27" t="s">
         <v>133</v>
       </c>
       <c r="F112" s="26" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G112" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F112),0)&gt;0), MAX($G$1:G111)+1, ""))</f>
@@ -4672,19 +4679,19 @@
         <v>25</v>
       </c>
       <c r="B113" s="27" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C113" s="28">
         <v>25</v>
       </c>
       <c r="D113" s="26" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="E113" s="27" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="F113" s="26" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="G113" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F113),0)&gt;0), MAX($G$1:G112)+1, ""))</f>
@@ -4696,23 +4703,23 @@
       </c>
     </row>
     <row r="114" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A114" s="26">
+      <c r="A114" s="32">
         <v>25</v>
       </c>
-      <c r="B114" s="27" t="s">
-        <v>164</v>
-      </c>
-      <c r="C114" s="28">
+      <c r="B114" s="33" t="s">
+        <v>282</v>
+      </c>
+      <c r="C114" s="34">
         <v>25</v>
       </c>
-      <c r="D114" s="26" t="s">
-        <v>236</v>
-      </c>
-      <c r="E114" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="F114" s="26" t="s">
-        <v>165</v>
+      <c r="D114" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="E114" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F114" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G114" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F114),0)&gt;0), MAX($G$1:G113)+1, ""))</f>
@@ -4728,19 +4735,19 @@
         <v>25</v>
       </c>
       <c r="B115" s="27" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="C115" s="28">
         <v>25</v>
       </c>
       <c r="D115" s="26" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="E115" s="27" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="F115" s="26" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="G115" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F115),0)&gt;0), MAX($G$1:G114)+1, ""))</f>
@@ -4756,7 +4763,7 @@
         <v>25</v>
       </c>
       <c r="B116" s="27" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C116" s="28">
         <v>25</v>
@@ -4765,10 +4772,10 @@
         <v>232</v>
       </c>
       <c r="E116" s="27" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="F116" s="26" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="G116" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F116),0)&gt;0), MAX($G$1:G115)+1, ""))</f>
@@ -4784,22 +4791,22 @@
         <v>25</v>
       </c>
       <c r="B117" s="27" t="s">
-        <v>315</v>
+        <v>164</v>
       </c>
       <c r="C117" s="28">
         <v>25</v>
       </c>
-      <c r="D117" s="26">
-        <v>3.9</v>
+      <c r="D117" s="26" t="s">
+        <v>235</v>
       </c>
       <c r="E117" s="27" t="s">
-        <v>314</v>
+        <v>83</v>
       </c>
       <c r="F117" s="26" t="s">
-        <v>316</v>
+        <v>165</v>
       </c>
       <c r="G117" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F117),0)&gt;0), MAX($G$1:G115)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F117),0)&gt;0), MAX($G$1:G116)+1, ""))</f>
         <v/>
       </c>
       <c r="H117" s="21" t="b">
@@ -4812,19 +4819,19 @@
         <v>25</v>
       </c>
       <c r="B118" s="27" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C118" s="28">
         <v>25</v>
       </c>
       <c r="D118" s="26" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="E118" s="27" t="s">
         <v>83</v>
       </c>
       <c r="F118" s="26" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="G118" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F118),0)&gt;0), MAX($G$1:G117)+1, ""))</f>
@@ -4840,19 +4847,19 @@
         <v>25</v>
       </c>
       <c r="B119" s="27" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C119" s="28">
         <v>25</v>
       </c>
       <c r="D119" s="26" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E119" s="27" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="F119" s="26" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G119" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F119),0)&gt;0), MAX($G$1:G118)+1, ""))</f>
@@ -4868,22 +4875,22 @@
         <v>25</v>
       </c>
       <c r="B120" s="27" t="s">
-        <v>154</v>
+        <v>314</v>
       </c>
       <c r="C120" s="28">
         <v>25</v>
       </c>
-      <c r="D120" s="26" t="s">
-        <v>234</v>
+      <c r="D120" s="26">
+        <v>3.9</v>
       </c>
       <c r="E120" s="27" t="s">
-        <v>133</v>
+        <v>313</v>
       </c>
       <c r="F120" s="26" t="s">
-        <v>155</v>
+        <v>315</v>
       </c>
       <c r="G120" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F120),0)&gt;0), MAX($G$1:G119)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F120),0)&gt;0), MAX($G$1:G118)+1, ""))</f>
         <v/>
       </c>
       <c r="H120" s="21" t="b">
@@ -4896,19 +4903,19 @@
         <v>25</v>
       </c>
       <c r="B121" s="27" t="s">
-        <v>252</v>
+        <v>158</v>
       </c>
       <c r="C121" s="28">
         <v>25</v>
       </c>
-      <c r="D121" s="41" t="s">
-        <v>233</v>
+      <c r="D121" s="26" t="s">
+        <v>230</v>
       </c>
       <c r="E121" s="27" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="F121" s="26" t="s">
-        <v>253</v>
+        <v>159</v>
       </c>
       <c r="G121" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F121),0)&gt;0), MAX($G$1:G120)+1, ""))</f>
@@ -4924,19 +4931,19 @@
         <v>25</v>
       </c>
       <c r="B122" s="27" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C122" s="28">
         <v>25</v>
       </c>
       <c r="D122" s="26" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="E122" s="27" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="F122" s="26" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G122" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F122),0)&gt;0), MAX($G$1:G121)+1, ""))</f>
@@ -4948,23 +4955,23 @@
       </c>
     </row>
     <row r="123" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A123" s="32">
+      <c r="A123" s="26">
         <v>25</v>
       </c>
-      <c r="B123" s="33" t="s">
-        <v>293</v>
-      </c>
-      <c r="C123" s="34">
+      <c r="B123" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="C123" s="28">
         <v>25</v>
       </c>
-      <c r="D123" s="32" t="s">
-        <v>211</v>
-      </c>
-      <c r="E123" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="F123" s="32" t="s">
-        <v>104</v>
+      <c r="D123" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="E123" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="F123" s="26" t="s">
+        <v>155</v>
       </c>
       <c r="G123" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F123),0)&gt;0), MAX($G$1:G122)+1, ""))</f>
@@ -4976,23 +4983,23 @@
       </c>
     </row>
     <row r="124" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A124" s="32">
+      <c r="A124" s="26">
         <v>25</v>
       </c>
-      <c r="B124" s="33" t="s">
-        <v>291</v>
-      </c>
-      <c r="C124" s="34">
+      <c r="B124" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="C124" s="28">
         <v>25</v>
       </c>
-      <c r="D124" s="32" t="s">
-        <v>211</v>
-      </c>
-      <c r="E124" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="F124" s="32" t="s">
-        <v>104</v>
+      <c r="D124" s="41" t="s">
+        <v>232</v>
+      </c>
+      <c r="E124" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F124" s="26" t="s">
+        <v>252</v>
       </c>
       <c r="G124" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F124),0)&gt;0), MAX($G$1:G123)+1, ""))</f>
@@ -5004,23 +5011,23 @@
       </c>
     </row>
     <row r="125" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A125" s="32">
+      <c r="A125" s="26">
         <v>25</v>
       </c>
-      <c r="B125" s="33" t="s">
-        <v>292</v>
-      </c>
-      <c r="C125" s="34">
+      <c r="B125" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="C125" s="28">
         <v>25</v>
       </c>
-      <c r="D125" s="32" t="s">
-        <v>211</v>
-      </c>
-      <c r="E125" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="F125" s="32" t="s">
-        <v>104</v>
+      <c r="D125" s="26" t="s">
+        <v>238</v>
+      </c>
+      <c r="E125" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="F125" s="26" t="s">
+        <v>153</v>
       </c>
       <c r="G125" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F125),0)&gt;0), MAX($G$1:G124)+1, ""))</f>
@@ -5032,23 +5039,23 @@
       </c>
     </row>
     <row r="126" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A126" s="26">
+      <c r="A126" s="32">
         <v>25</v>
       </c>
-      <c r="B126" s="27" t="s">
-        <v>257</v>
-      </c>
-      <c r="C126" s="28">
+      <c r="B126" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="C126" s="34">
         <v>25</v>
       </c>
-      <c r="D126" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E126" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F126" s="26" t="s">
-        <v>258</v>
+      <c r="D126" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="E126" s="33" t="s">
+        <v>287</v>
+      </c>
+      <c r="F126" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G126" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F126),0)&gt;0), MAX($G$1:G125)+1, ""))</f>
@@ -5070,10 +5077,10 @@
         <v>25</v>
       </c>
       <c r="D127" s="32" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E127" s="33" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F127" s="32" t="s">
         <v>104</v>
@@ -5088,26 +5095,26 @@
       </c>
     </row>
     <row r="128" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A128" s="26">
+      <c r="A128" s="32">
         <v>25</v>
       </c>
-      <c r="B128" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="C128" s="28">
+      <c r="B128" s="33" t="s">
+        <v>291</v>
+      </c>
+      <c r="C128" s="34">
         <v>25</v>
       </c>
-      <c r="D128" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="E128" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="F128" s="26" t="s">
-        <v>151</v>
+      <c r="D128" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="E128" s="33" t="s">
+        <v>287</v>
+      </c>
+      <c r="F128" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G128" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F128),0)&gt;0), MAX($G$1:G126)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F128),0)&gt;0), MAX($G$1:G127)+1, ""))</f>
         <v/>
       </c>
       <c r="H128" s="21" t="b">
@@ -5116,23 +5123,23 @@
       </c>
     </row>
     <row r="129" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A129" s="32">
-        <v>30</v>
-      </c>
-      <c r="B129" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="C129" s="34">
-        <v>30</v>
-      </c>
-      <c r="D129" s="32" t="s">
-        <v>236</v>
-      </c>
-      <c r="E129" s="33" t="s">
+      <c r="A129" s="26">
+        <v>25</v>
+      </c>
+      <c r="B129" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="C129" s="28">
+        <v>25</v>
+      </c>
+      <c r="D129" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E129" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="F129" s="32" t="s">
-        <v>197</v>
+      <c r="F129" s="26" t="s">
+        <v>257</v>
       </c>
       <c r="G129" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F129),0)&gt;0), MAX($G$1:G128)+1, ""))</f>
@@ -5145,22 +5152,22 @@
     </row>
     <row r="130" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A130" s="32">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B130" s="33" t="s">
-        <v>195</v>
+        <v>289</v>
       </c>
       <c r="C130" s="34">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D130" s="32" t="s">
-        <v>246</v>
+        <v>210</v>
       </c>
       <c r="E130" s="33" t="s">
-        <v>133</v>
+        <v>287</v>
       </c>
       <c r="F130" s="32" t="s">
-        <v>194</v>
+        <v>104</v>
       </c>
       <c r="G130" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F130),0)&gt;0), MAX($G$1:G129)+1, ""))</f>
@@ -5172,26 +5179,26 @@
       </c>
     </row>
     <row r="131" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A131" s="32">
-        <v>30</v>
-      </c>
-      <c r="B131" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="C131" s="34">
-        <v>30</v>
-      </c>
-      <c r="D131" s="32" t="s">
-        <v>245</v>
-      </c>
-      <c r="E131" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="F131" s="32" t="s">
-        <v>194</v>
+      <c r="A131" s="26">
+        <v>25</v>
+      </c>
+      <c r="B131" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C131" s="28">
+        <v>25</v>
+      </c>
+      <c r="D131" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="E131" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="F131" s="26" t="s">
+        <v>151</v>
       </c>
       <c r="G131" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F131),0)&gt;0), MAX($G$1:G130)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F131),0)&gt;0), MAX($G$1:G129)+1, ""))</f>
         <v/>
       </c>
       <c r="H131" s="21" t="b">
@@ -5204,19 +5211,19 @@
         <v>30</v>
       </c>
       <c r="B132" s="33" t="s">
-        <v>251</v>
+        <v>195</v>
       </c>
       <c r="C132" s="34">
         <v>30</v>
       </c>
       <c r="D132" s="32" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="E132" s="33" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="F132" s="32" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="G132" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B132),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E132),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F132),0)&gt;0), MAX($G$1:G131)+1, ""))</f>
@@ -5232,19 +5239,19 @@
         <v>30</v>
       </c>
       <c r="B133" s="33" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C133" s="34">
         <v>30</v>
       </c>
       <c r="D133" s="32" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="E133" s="33" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="F133" s="32" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G133" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F133),0)&gt;0), MAX($G$1:G132)+1, ""))</f>
@@ -5260,19 +5267,19 @@
         <v>30</v>
       </c>
       <c r="B134" s="33" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C134" s="34">
         <v>30</v>
       </c>
       <c r="D134" s="32" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="E134" s="33" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="F134" s="32" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="G134" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F134),0)&gt;0), MAX($G$1:G133)+1, ""))</f>
@@ -5288,19 +5295,19 @@
         <v>30</v>
       </c>
       <c r="B135" s="33" t="s">
-        <v>186</v>
+        <v>250</v>
       </c>
       <c r="C135" s="34">
         <v>30</v>
       </c>
       <c r="D135" s="32" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="E135" s="33" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="F135" s="32" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="G135" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F135),0)&gt;0), MAX($G$1:G134)+1, ""))</f>
@@ -5316,19 +5323,19 @@
         <v>30</v>
       </c>
       <c r="B136" s="33" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C136" s="34">
         <v>30</v>
       </c>
       <c r="D136" s="32" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="E136" s="33" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="F136" s="32" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="G136" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F136),0)&gt;0), MAX($G$1:G135)+1, ""))</f>
@@ -5340,23 +5347,23 @@
       </c>
     </row>
     <row r="137" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A137" s="26">
-        <v>40</v>
-      </c>
-      <c r="B137" s="27" t="s">
-        <v>201</v>
-      </c>
-      <c r="C137" s="28">
-        <v>40</v>
-      </c>
-      <c r="D137" s="26" t="s">
-        <v>248</v>
-      </c>
-      <c r="E137" s="27" t="s">
-        <v>202</v>
-      </c>
-      <c r="F137" s="26" t="s">
-        <v>203</v>
+      <c r="A137" s="32">
+        <v>30</v>
+      </c>
+      <c r="B137" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="C137" s="34">
+        <v>30</v>
+      </c>
+      <c r="D137" s="32" t="s">
+        <v>231</v>
+      </c>
+      <c r="E137" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="F137" s="32" t="s">
+        <v>188</v>
       </c>
       <c r="G137" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F137),0)&gt;0), MAX($G$1:G136)+1, ""))</f>
@@ -5368,23 +5375,23 @@
       </c>
     </row>
     <row r="138" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A138" s="26">
-        <v>40</v>
-      </c>
-      <c r="B138" s="27" t="s">
-        <v>198</v>
-      </c>
-      <c r="C138" s="28">
-        <v>40</v>
-      </c>
-      <c r="D138" s="26" t="s">
-        <v>247</v>
-      </c>
-      <c r="E138" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="F138" s="26" t="s">
-        <v>200</v>
+      <c r="A138" s="32">
+        <v>30</v>
+      </c>
+      <c r="B138" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="C138" s="34">
+        <v>30</v>
+      </c>
+      <c r="D138" s="32" t="s">
+        <v>243</v>
+      </c>
+      <c r="E138" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="F138" s="32" t="s">
+        <v>186</v>
       </c>
       <c r="G138" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F138),0)&gt;0), MAX($G$1:G137)+1, ""))</f>
@@ -5396,23 +5403,23 @@
       </c>
     </row>
     <row r="139" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A139" s="26">
-        <v>40</v>
-      </c>
-      <c r="B139" s="27" t="s">
-        <v>254</v>
-      </c>
-      <c r="C139" s="28">
-        <v>40</v>
-      </c>
-      <c r="D139" s="26">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="E139" s="27" t="s">
-        <v>255</v>
-      </c>
-      <c r="F139" s="26" t="s">
-        <v>256</v>
+      <c r="A139" s="32">
+        <v>30</v>
+      </c>
+      <c r="B139" s="33" t="s">
+        <v>183</v>
+      </c>
+      <c r="C139" s="34">
+        <v>30</v>
+      </c>
+      <c r="D139" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="E139" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="F139" s="32" t="s">
+        <v>184</v>
       </c>
       <c r="G139" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F139),0)&gt;0), MAX($G$1:G138)+1, ""))</f>
@@ -5425,22 +5432,22 @@
     </row>
     <row r="140" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A140" s="26">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B140" s="27" t="s">
-        <v>299</v>
+        <v>200</v>
       </c>
       <c r="C140" s="28">
-        <v>45</v>
-      </c>
-      <c r="D140" s="26">
-        <v>10.199999999999999</v>
+        <v>40</v>
+      </c>
+      <c r="D140" s="26" t="s">
+        <v>247</v>
       </c>
       <c r="E140" s="27" t="s">
-        <v>300</v>
+        <v>201</v>
       </c>
       <c r="F140" s="26" t="s">
-        <v>301</v>
+        <v>202</v>
       </c>
       <c r="G140" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F140),0)&gt;0), MAX($G$1:G139)+1, ""))</f>
@@ -5452,126 +5459,192 @@
       </c>
     </row>
     <row r="141" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A141" s="30"/>
-      <c r="B141" s="31"/>
-      <c r="C141" s="30"/>
-      <c r="D141" s="30"/>
-      <c r="E141" s="31"/>
-      <c r="F141" s="30"/>
-      <c r="G141" s="31"/>
+      <c r="A141" s="26">
+        <v>40</v>
+      </c>
+      <c r="B141" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="C141" s="28">
+        <v>40</v>
+      </c>
+      <c r="D141" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="E141" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="F141" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="G141" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F141),0)&gt;0), MAX($G$1:G140)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H141" s="21" t="b">
+        <f>A141=C141</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="142" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A142" s="30"/>
-      <c r="B142" s="31"/>
-      <c r="C142" s="30"/>
-      <c r="D142" s="30"/>
-      <c r="E142" s="31"/>
-      <c r="F142" s="30"/>
-      <c r="G142" s="31"/>
+      <c r="A142" s="26">
+        <v>40</v>
+      </c>
+      <c r="B142" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="C142" s="28">
+        <v>40</v>
+      </c>
+      <c r="D142" s="26">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E142" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="F142" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="G142" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F142),0)&gt;0), MAX($G$1:G141)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H142" s="21" t="b">
+        <f>A142=C142</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="143" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A143" s="1"/>
-      <c r="C143" s="1"/>
-      <c r="D143" s="1"/>
-      <c r="F143" s="1"/>
+      <c r="A143" s="26">
+        <v>45</v>
+      </c>
+      <c r="B143" s="27" t="s">
+        <v>298</v>
+      </c>
+      <c r="C143" s="28">
+        <v>45</v>
+      </c>
+      <c r="D143" s="26">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E143" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="F143" s="26" t="s">
+        <v>300</v>
+      </c>
+      <c r="G143" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F143),0)&gt;0), MAX($G$1:G142)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H143" s="21" t="b">
+        <f>A143=C143</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="144" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A144" s="1"/>
-      <c r="C144" s="1"/>
-      <c r="D144" s="1"/>
-      <c r="F144" s="1"/>
-    </row>
-    <row r="145" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A145" s="1"/>
-      <c r="C145" s="1"/>
-      <c r="D145" s="1"/>
-      <c r="F145" s="1"/>
-    </row>
-    <row r="146" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A144" s="30"/>
+      <c r="B144" s="31"/>
+      <c r="C144" s="30"/>
+      <c r="D144" s="30"/>
+      <c r="E144" s="31"/>
+      <c r="F144" s="30"/>
+      <c r="G144" s="31"/>
+    </row>
+    <row r="145" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A145" s="30"/>
+      <c r="B145" s="31"/>
+      <c r="C145" s="30"/>
+      <c r="D145" s="30"/>
+      <c r="E145" s="31"/>
+      <c r="F145" s="30"/>
+      <c r="G145" s="31"/>
+    </row>
+    <row r="146" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="C146" s="1"/>
       <c r="D146" s="1"/>
       <c r="F146" s="1"/>
     </row>
-    <row r="147" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="C147" s="1"/>
       <c r="D147" s="1"/>
       <c r="F147" s="1"/>
     </row>
-    <row r="148" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="C148" s="1"/>
       <c r="D148" s="1"/>
       <c r="F148" s="1"/>
     </row>
-    <row r="149" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="C149" s="1"/>
       <c r="D149" s="1"/>
       <c r="F149" s="1"/>
     </row>
-    <row r="150" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="C150" s="1"/>
       <c r="D150" s="1"/>
       <c r="F150" s="1"/>
     </row>
-    <row r="151" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="C151" s="1"/>
       <c r="D151" s="1"/>
       <c r="F151" s="1"/>
     </row>
-    <row r="152" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="C152" s="1"/>
       <c r="D152" s="1"/>
       <c r="F152" s="1"/>
     </row>
-    <row r="153" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="C153" s="1"/>
       <c r="D153" s="1"/>
       <c r="F153" s="1"/>
     </row>
-    <row r="154" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="C154" s="1"/>
       <c r="D154" s="1"/>
       <c r="F154" s="1"/>
     </row>
-    <row r="155" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="C155" s="1"/>
       <c r="D155" s="1"/>
       <c r="F155" s="1"/>
     </row>
-    <row r="156" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="C156" s="1"/>
       <c r="D156" s="1"/>
       <c r="F156" s="1"/>
     </row>
-    <row r="157" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="C157" s="1"/>
       <c r="D157" s="1"/>
       <c r="F157" s="1"/>
     </row>
-    <row r="158" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="C158" s="1"/>
       <c r="D158" s="1"/>
       <c r="F158" s="1"/>
     </row>
-    <row r="159" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="C159" s="1"/>
       <c r="D159" s="1"/>
       <c r="F159" s="1"/>
     </row>
-    <row r="160" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="C160" s="1"/>
       <c r="D160" s="1"/>
@@ -10779,12 +10852,30 @@
       <c r="D1027" s="1"/>
       <c r="F1027" s="1"/>
     </row>
+    <row r="1028" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1028" s="1"/>
+      <c r="C1028" s="1"/>
+      <c r="D1028" s="1"/>
+      <c r="F1028" s="1"/>
+    </row>
+    <row r="1029" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1029" s="1"/>
+      <c r="C1029" s="1"/>
+      <c r="D1029" s="1"/>
+      <c r="F1029" s="1"/>
+    </row>
+    <row r="1030" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1030" s="1"/>
+      <c r="C1030" s="1"/>
+      <c r="D1030" s="1"/>
+      <c r="F1030" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H140">
-    <sortState ref="A2:H127">
-      <sortCondition ref="A2:A127"/>
-      <sortCondition ref="B2:B127"/>
-      <sortCondition ref="D2:D127"/>
+  <autoFilter ref="A1:H143">
+    <sortState ref="A2:H143">
+      <sortCondition ref="A2:A143"/>
+      <sortCondition ref="B2:B143"/>
+      <sortCondition ref="D2:D143"/>
     </sortState>
   </autoFilter>
   <sortState ref="A2:H140">
@@ -10814,7 +10905,7 @@
   <sheetData>
     <row r="1" spans="1:6" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="19" t="str">
@@ -10827,7 +10918,7 @@
     </row>
     <row r="2" spans="1:6" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="17"/>

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Consulta" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$143</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$147</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$135</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Base!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="341">
   <si>
     <t>Grupo</t>
   </si>
@@ -1027,6 +1027,27 @@
   </si>
   <si>
     <t>21740-530</t>
+  </si>
+  <si>
+    <t>LIMITES LADO HABIBS</t>
+  </si>
+  <si>
+    <t>BELARMINA</t>
+  </si>
+  <si>
+    <t>21745-110</t>
+  </si>
+  <si>
+    <t>ARQUIMEDES</t>
+  </si>
+  <si>
+    <t>21745-120</t>
+  </si>
+  <si>
+    <t>NEWTON</t>
+  </si>
+  <si>
+    <t>Vila Militar - Magalhães</t>
   </si>
 </sst>
 </file>
@@ -1555,7 +1576,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H1030"/>
+  <dimension ref="A1:H1034"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.453125" customWidth="1"/>
@@ -3050,7 +3071,7 @@
         <v>54</v>
       </c>
       <c r="G54" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F54),0)&gt;0), MAX($G$1:G53)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F54),0)&gt;0), MAX($G$1:G49)+1, ""))</f>
         <v/>
       </c>
       <c r="H54" s="21" t="b">
@@ -3443,56 +3464,50 @@
       </c>
     </row>
     <row r="69" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A69" s="32">
+      <c r="A69" s="38">
         <v>20</v>
       </c>
-      <c r="B69" s="33" t="s">
-        <v>140</v>
-      </c>
-      <c r="C69" s="34">
+      <c r="B69" s="39" t="s">
+        <v>337</v>
+      </c>
+      <c r="C69" s="40">
         <v>20</v>
       </c>
-      <c r="D69" s="32" t="s">
-        <v>226</v>
-      </c>
-      <c r="E69" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F69" s="32" t="s">
-        <v>141</v>
-      </c>
-      <c r="G69" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F69),0)&gt;0), MAX($G$1:G68)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D69" s="38">
+        <v>3.4</v>
+      </c>
+      <c r="E69" s="39" t="s">
+        <v>340</v>
+      </c>
+      <c r="F69" s="38" t="s">
+        <v>338</v>
+      </c>
+      <c r="G69" s="29"/>
       <c r="H69" s="21" t="b">
         <f>A69=C69</f>
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A70" s="32">
+      <c r="A70" s="38">
         <v>20</v>
       </c>
-      <c r="B70" s="33" t="s">
-        <v>259</v>
-      </c>
-      <c r="C70" s="34">
+      <c r="B70" s="39" t="s">
+        <v>335</v>
+      </c>
+      <c r="C70" s="40">
         <v>20</v>
       </c>
-      <c r="D70" s="32" t="s">
-        <v>228</v>
-      </c>
-      <c r="E70" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F70" s="32" t="s">
-        <v>260</v>
-      </c>
-      <c r="G70" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F70),0)&gt;0), MAX($G$1:G69)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D70" s="38">
+        <v>3.3</v>
+      </c>
+      <c r="E70" s="39" t="s">
+        <v>340</v>
+      </c>
+      <c r="F70" s="38" t="s">
+        <v>336</v>
+      </c>
+      <c r="G70" s="29"/>
       <c r="H70" s="21" t="b">
         <f>A70=C70</f>
         <v>1</v>
@@ -3503,19 +3518,19 @@
         <v>20</v>
       </c>
       <c r="B71" s="33" t="s">
-        <v>258</v>
+        <v>140</v>
       </c>
       <c r="C71" s="34">
         <v>20</v>
       </c>
-      <c r="D71" s="32">
-        <v>4.2</v>
+      <c r="D71" s="32" t="s">
+        <v>226</v>
       </c>
       <c r="E71" s="33" t="s">
-        <v>309</v>
-      </c>
-      <c r="F71" s="32">
-        <v>21765430</v>
+        <v>8</v>
+      </c>
+      <c r="F71" s="32" t="s">
+        <v>141</v>
       </c>
       <c r="G71" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F71),0)&gt;0), MAX($G$1:G70)+1, ""))</f>
@@ -3531,19 +3546,19 @@
         <v>20</v>
       </c>
       <c r="B72" s="33" t="s">
-        <v>138</v>
+        <v>259</v>
       </c>
       <c r="C72" s="34">
         <v>20</v>
       </c>
       <c r="D72" s="32" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="E72" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F72" s="32" t="s">
-        <v>139</v>
+        <v>260</v>
       </c>
       <c r="G72" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F72),0)&gt;0), MAX($G$1:G71)+1, ""))</f>
@@ -3559,19 +3574,19 @@
         <v>20</v>
       </c>
       <c r="B73" s="33" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="C73" s="34">
         <v>20</v>
       </c>
-      <c r="D73" s="32" t="s">
-        <v>225</v>
+      <c r="D73" s="32">
+        <v>4.2</v>
       </c>
       <c r="E73" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F73" s="32" t="s">
-        <v>137</v>
+        <v>309</v>
+      </c>
+      <c r="F73" s="32">
+        <v>21765430</v>
       </c>
       <c r="G73" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F73),0)&gt;0), MAX($G$1:G72)+1, ""))</f>
@@ -3587,19 +3602,19 @@
         <v>20</v>
       </c>
       <c r="B74" s="33" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C74" s="34">
         <v>20</v>
       </c>
       <c r="D74" s="32" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="E74" s="33" t="s">
-        <v>309</v>
+        <v>8</v>
       </c>
       <c r="F74" s="32" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G74" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F74),0)&gt;0), MAX($G$1:G73)+1, ""))</f>
@@ -3615,19 +3630,19 @@
         <v>20</v>
       </c>
       <c r="B75" s="33" t="s">
-        <v>132</v>
+        <v>269</v>
       </c>
       <c r="C75" s="34">
         <v>20</v>
       </c>
       <c r="D75" s="32" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="E75" s="33" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="F75" s="32" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G75" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F75),0)&gt;0), MAX($G$1:G74)+1, ""))</f>
@@ -3639,23 +3654,23 @@
       </c>
     </row>
     <row r="76" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A76" s="26">
+      <c r="A76" s="32">
         <v>20</v>
       </c>
-      <c r="B76" s="27" t="s">
-        <v>316</v>
-      </c>
-      <c r="C76" s="28">
+      <c r="B76" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="C76" s="34">
         <v>20</v>
       </c>
-      <c r="D76" s="26">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="E76" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="F76" s="26" t="s">
-        <v>322</v>
+      <c r="D76" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E76" s="33" t="s">
+        <v>309</v>
+      </c>
+      <c r="F76" s="32" t="s">
+        <v>136</v>
       </c>
       <c r="G76" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F76),0)&gt;0), MAX($G$1:G75)+1, ""))</f>
@@ -3671,19 +3686,19 @@
         <v>20</v>
       </c>
       <c r="B77" s="33" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C77" s="34">
         <v>20</v>
       </c>
       <c r="D77" s="32" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="E77" s="33" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="F77" s="32" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G77" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F77),0)&gt;0), MAX($G$1:G76)+1, ""))</f>
@@ -3695,23 +3710,23 @@
       </c>
     </row>
     <row r="78" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A78" s="32">
+      <c r="A78" s="26">
         <v>20</v>
       </c>
-      <c r="B78" s="33" t="s">
-        <v>128</v>
-      </c>
-      <c r="C78" s="34">
+      <c r="B78" s="27" t="s">
+        <v>316</v>
+      </c>
+      <c r="C78" s="28">
         <v>20</v>
       </c>
-      <c r="D78" s="32" t="s">
-        <v>237</v>
-      </c>
-      <c r="E78" s="33" t="s">
-        <v>309</v>
-      </c>
-      <c r="F78" s="32" t="s">
-        <v>129</v>
+      <c r="D78" s="26">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E78" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="F78" s="26" t="s">
+        <v>322</v>
       </c>
       <c r="G78" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F78),0)&gt;0), MAX($G$1:G77)+1, ""))</f>
@@ -3727,19 +3742,19 @@
         <v>20</v>
       </c>
       <c r="B79" s="33" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C79" s="34">
         <v>20</v>
       </c>
       <c r="D79" s="32" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="E79" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F79" s="32" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G79" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F79),0)&gt;0), MAX($G$1:G78)+1, ""))</f>
@@ -3755,19 +3770,19 @@
         <v>20</v>
       </c>
       <c r="B80" s="33" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C80" s="34">
         <v>20</v>
       </c>
       <c r="D80" s="32" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="E80" s="33" t="s">
-        <v>8</v>
+        <v>309</v>
       </c>
       <c r="F80" s="32" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G80" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F80),0)&gt;0), MAX($G$1:G79)+1, ""))</f>
@@ -3783,19 +3798,19 @@
         <v>20</v>
       </c>
       <c r="B81" s="33" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C81" s="34">
         <v>20</v>
       </c>
       <c r="D81" s="32" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="E81" s="33" t="s">
-        <v>309</v>
+        <v>8</v>
       </c>
       <c r="F81" s="32" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G81" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F81),0)&gt;0), MAX($G$1:G80)+1, ""))</f>
@@ -3811,19 +3826,19 @@
         <v>20</v>
       </c>
       <c r="B82" s="33" t="s">
-        <v>261</v>
+        <v>124</v>
       </c>
       <c r="C82" s="34">
         <v>20</v>
       </c>
       <c r="D82" s="32" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="E82" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F82" s="32" t="s">
-        <v>262</v>
+        <v>125</v>
       </c>
       <c r="G82" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F82),0)&gt;0), MAX($G$1:G81)+1, ""))</f>
@@ -3839,19 +3854,19 @@
         <v>20</v>
       </c>
       <c r="B83" s="33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C83" s="34">
         <v>20</v>
       </c>
       <c r="D83" s="32" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E83" s="33" t="s">
-        <v>8</v>
+        <v>309</v>
       </c>
       <c r="F83" s="32" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G83" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F83),0)&gt;0), MAX($G$1:G82)+1, ""))</f>
@@ -3867,19 +3882,19 @@
         <v>20</v>
       </c>
       <c r="B84" s="33" t="s">
-        <v>118</v>
+        <v>261</v>
       </c>
       <c r="C84" s="34">
         <v>20</v>
       </c>
       <c r="D84" s="32" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="E84" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F84" s="32" t="s">
-        <v>119</v>
+        <v>262</v>
       </c>
       <c r="G84" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F84),0)&gt;0), MAX($G$1:G83)+1, ""))</f>
@@ -3895,19 +3910,19 @@
         <v>20</v>
       </c>
       <c r="B85" s="33" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C85" s="34">
         <v>20</v>
       </c>
       <c r="D85" s="32" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="E85" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F85" s="32" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G85" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F85),0)&gt;0), MAX($G$1:G84)+1, ""))</f>
@@ -3919,23 +3934,23 @@
       </c>
     </row>
     <row r="86" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A86" s="26">
+      <c r="A86" s="32">
         <v>20</v>
       </c>
-      <c r="B86" s="27" t="s">
-        <v>301</v>
-      </c>
-      <c r="C86" s="28">
+      <c r="B86" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="C86" s="34">
         <v>20</v>
       </c>
-      <c r="D86" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E86" s="27" t="s">
-        <v>303</v>
-      </c>
-      <c r="F86" s="26" t="s">
-        <v>302</v>
+      <c r="D86" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="E86" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F86" s="32" t="s">
+        <v>119</v>
       </c>
       <c r="G86" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F86),0)&gt;0), MAX($G$1:G85)+1, ""))</f>
@@ -3951,19 +3966,19 @@
         <v>20</v>
       </c>
       <c r="B87" s="33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C87" s="34">
         <v>20</v>
       </c>
       <c r="D87" s="32" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="E87" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F87" s="32" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G87" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F87),0)&gt;0), MAX($G$1:G86)+1, ""))</f>
@@ -3975,23 +3990,23 @@
       </c>
     </row>
     <row r="88" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A88" s="32">
+      <c r="A88" s="26">
         <v>20</v>
       </c>
-      <c r="B88" s="33" t="s">
-        <v>112</v>
-      </c>
-      <c r="C88" s="34">
+      <c r="B88" s="27" t="s">
+        <v>301</v>
+      </c>
+      <c r="C88" s="28">
         <v>20</v>
       </c>
-      <c r="D88" s="32" t="s">
-        <v>225</v>
-      </c>
-      <c r="E88" s="33" t="s">
+      <c r="D88" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E88" s="27" t="s">
         <v>303</v>
       </c>
-      <c r="F88" s="32" t="s">
-        <v>113</v>
+      <c r="F88" s="26" t="s">
+        <v>302</v>
       </c>
       <c r="G88" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F88),0)&gt;0), MAX($G$1:G87)+1, ""))</f>
@@ -4007,19 +4022,19 @@
         <v>20</v>
       </c>
       <c r="B89" s="33" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C89" s="34">
         <v>20</v>
       </c>
       <c r="D89" s="32" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E89" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F89" s="32" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G89" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F89),0)&gt;0), MAX($G$1:G88)+1, ""))</f>
@@ -4031,23 +4046,23 @@
       </c>
     </row>
     <row r="90" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A90" s="26">
+      <c r="A90" s="32">
         <v>20</v>
       </c>
-      <c r="B90" s="27" t="s">
-        <v>306</v>
-      </c>
-      <c r="C90" s="28">
+      <c r="B90" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="C90" s="34">
         <v>20</v>
       </c>
-      <c r="D90" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E90" s="27" t="s">
+      <c r="D90" s="32" t="s">
+        <v>225</v>
+      </c>
+      <c r="E90" s="33" t="s">
         <v>303</v>
       </c>
-      <c r="F90" s="26" t="s">
-        <v>305</v>
+      <c r="F90" s="32" t="s">
+        <v>113</v>
       </c>
       <c r="G90" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F90),0)&gt;0), MAX($G$1:G89)+1, ""))</f>
@@ -4063,19 +4078,19 @@
         <v>20</v>
       </c>
       <c r="B91" s="33" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C91" s="34">
         <v>20</v>
       </c>
       <c r="D91" s="32" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E91" s="33" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="F91" s="32" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G91" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F91),0)&gt;0), MAX($G$1:G90)+1, ""))</f>
@@ -4087,51 +4102,48 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A92" s="32">
+      <c r="A92" s="38">
         <v>20</v>
       </c>
-      <c r="B92" s="33" t="s">
-        <v>103</v>
-      </c>
-      <c r="C92" s="34">
+      <c r="B92" s="39" t="s">
+        <v>334</v>
+      </c>
+      <c r="C92" s="40">
         <v>20</v>
       </c>
-      <c r="D92" s="32" t="s">
-        <v>210</v>
-      </c>
-      <c r="E92" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F92" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="G92" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F92),0)&gt;0), MAX($G$1:G91)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D92" s="38">
+        <v>3</v>
+      </c>
+      <c r="E92" s="39" t="s">
+        <v>308</v>
+      </c>
+      <c r="F92" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="G92" s="29"/>
       <c r="H92" s="21" t="b">
         <f>A92=C92</f>
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A93" s="32">
+      <c r="A93" s="26">
         <v>20</v>
       </c>
-      <c r="B93" s="33" t="s">
-        <v>267</v>
-      </c>
-      <c r="C93" s="34">
+      <c r="B93" s="27" t="s">
+        <v>306</v>
+      </c>
+      <c r="C93" s="28">
         <v>20</v>
       </c>
-      <c r="D93" s="32">
-        <v>6.2</v>
-      </c>
-      <c r="E93" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F93" s="32" t="s">
-        <v>268</v>
+      <c r="D93" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E93" s="27" t="s">
+        <v>303</v>
+      </c>
+      <c r="F93" s="26" t="s">
+        <v>305</v>
       </c>
       <c r="G93" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F93),0)&gt;0), MAX($G$1:G92)+1, ""))</f>
@@ -4147,19 +4159,19 @@
         <v>20</v>
       </c>
       <c r="B94" s="33" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C94" s="34">
         <v>20</v>
       </c>
       <c r="D94" s="32" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E94" s="33" t="s">
-        <v>303</v>
+        <v>61</v>
       </c>
       <c r="F94" s="32" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G94" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F94),0)&gt;0), MAX($G$1:G93)+1, ""))</f>
@@ -4171,28 +4183,25 @@
       </c>
     </row>
     <row r="95" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A95" s="26">
+      <c r="A95" s="38">
         <v>20</v>
       </c>
-      <c r="B95" s="27" t="s">
-        <v>304</v>
-      </c>
-      <c r="C95" s="28">
+      <c r="B95" s="39" t="s">
+        <v>339</v>
+      </c>
+      <c r="C95" s="40">
         <v>20</v>
       </c>
-      <c r="D95" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E95" s="27" t="s">
-        <v>303</v>
-      </c>
-      <c r="F95" s="26" t="s">
-        <v>305</v>
-      </c>
-      <c r="G95" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F95),0)&gt;0), MAX($G$1:G94)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D95" s="38">
+        <v>3.2</v>
+      </c>
+      <c r="E95" s="39" t="s">
+        <v>340</v>
+      </c>
+      <c r="F95" s="38" t="s">
+        <v>336</v>
+      </c>
+      <c r="G95" s="29"/>
       <c r="H95" s="21" t="b">
         <f>A95=C95</f>
         <v>1</v>
@@ -4203,19 +4212,19 @@
         <v>20</v>
       </c>
       <c r="B96" s="33" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C96" s="34">
         <v>20</v>
       </c>
       <c r="D96" s="32" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="E96" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F96" s="32" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G96" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F96),0)&gt;0), MAX($G$1:G95)+1, ""))</f>
@@ -4231,19 +4240,19 @@
         <v>20</v>
       </c>
       <c r="B97" s="33" t="s">
-        <v>93</v>
+        <v>267</v>
       </c>
       <c r="C97" s="34">
         <v>20</v>
       </c>
-      <c r="D97" s="32" t="s">
-        <v>221</v>
+      <c r="D97" s="32">
+        <v>6.2</v>
       </c>
       <c r="E97" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F97" s="32" t="s">
-        <v>94</v>
+        <v>268</v>
       </c>
       <c r="G97" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F97),0)&gt;0), MAX($G$1:G96)+1, ""))</f>
@@ -4259,19 +4268,19 @@
         <v>20</v>
       </c>
       <c r="B98" s="33" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="C98" s="34">
         <v>20</v>
       </c>
       <c r="D98" s="32" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E98" s="33" t="s">
-        <v>8</v>
+        <v>303</v>
       </c>
       <c r="F98" s="32" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="G98" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F98),0)&gt;0), MAX($G$1:G97)+1, ""))</f>
@@ -4283,23 +4292,23 @@
       </c>
     </row>
     <row r="99" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A99" s="32">
+      <c r="A99" s="26">
         <v>20</v>
       </c>
-      <c r="B99" s="33" t="s">
-        <v>294</v>
-      </c>
-      <c r="C99" s="34">
+      <c r="B99" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="C99" s="28">
         <v>20</v>
       </c>
-      <c r="D99" s="32">
-        <v>1.8</v>
-      </c>
-      <c r="E99" s="33" t="s">
-        <v>295</v>
-      </c>
-      <c r="F99" s="32" t="s">
-        <v>92</v>
+      <c r="D99" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E99" s="27" t="s">
+        <v>303</v>
+      </c>
+      <c r="F99" s="26" t="s">
+        <v>305</v>
       </c>
       <c r="G99" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F99),0)&gt;0), MAX($G$1:G98)+1, ""))</f>
@@ -4315,19 +4324,19 @@
         <v>20</v>
       </c>
       <c r="B100" s="33" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C100" s="34">
         <v>20</v>
       </c>
       <c r="D100" s="32" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="E100" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F100" s="32" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="G100" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F100),0)&gt;0), MAX($G$1:G99)+1, ""))</f>
@@ -4343,19 +4352,19 @@
         <v>20</v>
       </c>
       <c r="B101" s="33" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C101" s="34">
         <v>20</v>
       </c>
       <c r="D101" s="32" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E101" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F101" s="32" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G101" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F101),0)&gt;0), MAX($G$1:G100)+1, ""))</f>
@@ -4371,19 +4380,19 @@
         <v>20</v>
       </c>
       <c r="B102" s="33" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C102" s="34">
         <v>20</v>
       </c>
       <c r="D102" s="32" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="E102" s="33" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="F102" s="32" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G102" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F102),0)&gt;0), MAX($G$1:G101)+1, ""))</f>
@@ -4399,19 +4408,19 @@
         <v>20</v>
       </c>
       <c r="B103" s="33" t="s">
-        <v>80</v>
+        <v>294</v>
       </c>
       <c r="C103" s="34">
         <v>20</v>
       </c>
-      <c r="D103" s="32" t="s">
-        <v>220</v>
+      <c r="D103" s="32">
+        <v>1.8</v>
       </c>
       <c r="E103" s="33" t="s">
-        <v>8</v>
+        <v>295</v>
       </c>
       <c r="F103" s="32" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="G103" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F103),0)&gt;0), MAX($G$1:G102)+1, ""))</f>
@@ -4427,19 +4436,19 @@
         <v>20</v>
       </c>
       <c r="B104" s="33" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C104" s="34">
         <v>20</v>
       </c>
       <c r="D104" s="32" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="E104" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F104" s="32" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G104" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F104),0)&gt;0), MAX($G$1:G103)+1, ""))</f>
@@ -4451,23 +4460,23 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A105" s="26">
-        <v>25</v>
-      </c>
-      <c r="B105" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="C105" s="28">
-        <v>25</v>
-      </c>
-      <c r="D105" s="26" t="s">
-        <v>228</v>
-      </c>
-      <c r="E105" s="27" t="s">
+      <c r="A105" s="32">
+        <v>20</v>
+      </c>
+      <c r="B105" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="C105" s="34">
+        <v>20</v>
+      </c>
+      <c r="D105" s="32" t="s">
+        <v>223</v>
+      </c>
+      <c r="E105" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="F105" s="26" t="s">
-        <v>182</v>
+      <c r="F105" s="32" t="s">
+        <v>88</v>
       </c>
       <c r="G105" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F105),0)&gt;0), MAX($G$1:G104)+1, ""))</f>
@@ -4479,23 +4488,23 @@
       </c>
     </row>
     <row r="106" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A106" s="26">
-        <v>25</v>
-      </c>
-      <c r="B106" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="C106" s="28">
-        <v>25</v>
-      </c>
-      <c r="D106" s="26" t="s">
-        <v>241</v>
-      </c>
-      <c r="E106" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F106" s="26" t="s">
-        <v>180</v>
+      <c r="A106" s="32">
+        <v>20</v>
+      </c>
+      <c r="B106" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C106" s="34">
+        <v>20</v>
+      </c>
+      <c r="D106" s="32" t="s">
+        <v>221</v>
+      </c>
+      <c r="E106" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="F106" s="32" t="s">
+        <v>84</v>
       </c>
       <c r="G106" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F106),0)&gt;0), MAX($G$1:G105)+1, ""))</f>
@@ -4507,23 +4516,23 @@
       </c>
     </row>
     <row r="107" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A107" s="26">
-        <v>25</v>
-      </c>
-      <c r="B107" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="C107" s="28">
-        <v>25</v>
-      </c>
-      <c r="D107" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="E107" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F107" s="26" t="s">
-        <v>178</v>
+      <c r="A107" s="32">
+        <v>20</v>
+      </c>
+      <c r="B107" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C107" s="34">
+        <v>20</v>
+      </c>
+      <c r="D107" s="32" t="s">
+        <v>220</v>
+      </c>
+      <c r="E107" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F107" s="32" t="s">
+        <v>81</v>
       </c>
       <c r="G107" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F107),0)&gt;0), MAX($G$1:G106)+1, ""))</f>
@@ -4535,23 +4544,23 @@
       </c>
     </row>
     <row r="108" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A108" s="26">
-        <v>25</v>
-      </c>
-      <c r="B108" s="27" t="s">
-        <v>176</v>
-      </c>
-      <c r="C108" s="28">
-        <v>25</v>
-      </c>
-      <c r="D108" s="26" t="s">
-        <v>227</v>
-      </c>
-      <c r="E108" s="27" t="s">
+      <c r="A108" s="32">
+        <v>20</v>
+      </c>
+      <c r="B108" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="C108" s="34">
+        <v>20</v>
+      </c>
+      <c r="D108" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="E108" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="F108" s="26" t="s">
-        <v>328</v>
+      <c r="F108" s="32" t="s">
+        <v>79</v>
       </c>
       <c r="G108" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F108),0)&gt;0), MAX($G$1:G107)+1, ""))</f>
@@ -4567,19 +4576,19 @@
         <v>25</v>
       </c>
       <c r="B109" s="27" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="C109" s="28">
         <v>25</v>
       </c>
       <c r="D109" s="26" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="E109" s="27" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="F109" s="26" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="G109" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F109),0)&gt;0), MAX($G$1:G108)+1, ""))</f>
@@ -4591,23 +4600,23 @@
       </c>
     </row>
     <row r="110" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A110" s="32">
+      <c r="A110" s="26">
         <v>25</v>
       </c>
-      <c r="B110" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="C110" s="34">
+      <c r="B110" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="C110" s="28">
         <v>25</v>
       </c>
-      <c r="D110" s="32" t="s">
-        <v>210</v>
-      </c>
-      <c r="E110" s="33" t="s">
-        <v>287</v>
-      </c>
-      <c r="F110" s="32" t="s">
-        <v>104</v>
+      <c r="D110" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="E110" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="F110" s="26" t="s">
+        <v>180</v>
       </c>
       <c r="G110" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F110),0)&gt;0), MAX($G$1:G109)+1, ""))</f>
@@ -4619,23 +4628,23 @@
       </c>
     </row>
     <row r="111" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A111" s="32">
+      <c r="A111" s="26">
         <v>25</v>
       </c>
-      <c r="B111" s="33" t="s">
-        <v>286</v>
-      </c>
-      <c r="C111" s="34">
+      <c r="B111" s="27" t="s">
+        <v>177</v>
+      </c>
+      <c r="C111" s="28">
         <v>25</v>
       </c>
-      <c r="D111" s="32" t="s">
-        <v>210</v>
-      </c>
-      <c r="E111" s="33" t="s">
-        <v>287</v>
-      </c>
-      <c r="F111" s="32" t="s">
-        <v>104</v>
+      <c r="D111" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="E111" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="F111" s="26" t="s">
+        <v>178</v>
       </c>
       <c r="G111" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F111),0)&gt;0), MAX($G$1:G110)+1, ""))</f>
@@ -4651,19 +4660,19 @@
         <v>25</v>
       </c>
       <c r="B112" s="27" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C112" s="28">
         <v>25</v>
       </c>
       <c r="D112" s="26" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="E112" s="27" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="F112" s="26" t="s">
-        <v>173</v>
+        <v>328</v>
       </c>
       <c r="G112" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F112),0)&gt;0), MAX($G$1:G111)+1, ""))</f>
@@ -4679,19 +4688,19 @@
         <v>25</v>
       </c>
       <c r="B113" s="27" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C113" s="28">
         <v>25</v>
       </c>
       <c r="D113" s="26" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="E113" s="27" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="F113" s="26" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="G113" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F113),0)&gt;0), MAX($G$1:G112)+1, ""))</f>
@@ -4707,7 +4716,7 @@
         <v>25</v>
       </c>
       <c r="B114" s="33" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C114" s="34">
         <v>25</v>
@@ -4716,7 +4725,7 @@
         <v>210</v>
       </c>
       <c r="E114" s="33" t="s">
-        <v>8</v>
+        <v>287</v>
       </c>
       <c r="F114" s="32" t="s">
         <v>104</v>
@@ -4731,23 +4740,23 @@
       </c>
     </row>
     <row r="115" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A115" s="26">
+      <c r="A115" s="32">
         <v>25</v>
       </c>
-      <c r="B115" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="C115" s="28">
+      <c r="B115" s="33" t="s">
+        <v>286</v>
+      </c>
+      <c r="C115" s="34">
         <v>25</v>
       </c>
-      <c r="D115" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="E115" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F115" s="26" t="s">
-        <v>169</v>
+      <c r="D115" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="E115" s="33" t="s">
+        <v>287</v>
+      </c>
+      <c r="F115" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G115" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F115),0)&gt;0), MAX($G$1:G114)+1, ""))</f>
@@ -4763,19 +4772,19 @@
         <v>25</v>
       </c>
       <c r="B116" s="27" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="C116" s="28">
         <v>25</v>
       </c>
       <c r="D116" s="26" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="E116" s="27" t="s">
         <v>133</v>
       </c>
       <c r="F116" s="26" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="G116" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F116),0)&gt;0), MAX($G$1:G115)+1, ""))</f>
@@ -4791,19 +4800,19 @@
         <v>25</v>
       </c>
       <c r="B117" s="27" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C117" s="28">
         <v>25</v>
       </c>
       <c r="D117" s="26" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="E117" s="27" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="F117" s="26" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="G117" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F117),0)&gt;0), MAX($G$1:G116)+1, ""))</f>
@@ -4815,23 +4824,23 @@
       </c>
     </row>
     <row r="118" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A118" s="26">
+      <c r="A118" s="32">
         <v>25</v>
       </c>
-      <c r="B118" s="27" t="s">
-        <v>162</v>
-      </c>
-      <c r="C118" s="28">
+      <c r="B118" s="33" t="s">
+        <v>282</v>
+      </c>
+      <c r="C118" s="34">
         <v>25</v>
       </c>
-      <c r="D118" s="26" t="s">
-        <v>239</v>
-      </c>
-      <c r="E118" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="F118" s="26" t="s">
-        <v>163</v>
+      <c r="D118" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="E118" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F118" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G118" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F118),0)&gt;0), MAX($G$1:G117)+1, ""))</f>
@@ -4847,19 +4856,19 @@
         <v>25</v>
       </c>
       <c r="B119" s="27" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="C119" s="28">
         <v>25</v>
       </c>
       <c r="D119" s="26" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="E119" s="27" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="F119" s="26" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="G119" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F119),0)&gt;0), MAX($G$1:G118)+1, ""))</f>
@@ -4875,22 +4884,22 @@
         <v>25</v>
       </c>
       <c r="B120" s="27" t="s">
-        <v>314</v>
+        <v>166</v>
       </c>
       <c r="C120" s="28">
         <v>25</v>
       </c>
-      <c r="D120" s="26">
-        <v>3.9</v>
+      <c r="D120" s="26" t="s">
+        <v>232</v>
       </c>
       <c r="E120" s="27" t="s">
-        <v>313</v>
+        <v>133</v>
       </c>
       <c r="F120" s="26" t="s">
-        <v>315</v>
+        <v>167</v>
       </c>
       <c r="G120" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F120),0)&gt;0), MAX($G$1:G118)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F120),0)&gt;0), MAX($G$1:G119)+1, ""))</f>
         <v/>
       </c>
       <c r="H120" s="21" t="b">
@@ -4903,19 +4912,19 @@
         <v>25</v>
       </c>
       <c r="B121" s="27" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C121" s="28">
         <v>25</v>
       </c>
       <c r="D121" s="26" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="E121" s="27" t="s">
         <v>83</v>
       </c>
       <c r="F121" s="26" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="G121" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F121),0)&gt;0), MAX($G$1:G120)+1, ""))</f>
@@ -4931,19 +4940,19 @@
         <v>25</v>
       </c>
       <c r="B122" s="27" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C122" s="28">
         <v>25</v>
       </c>
       <c r="D122" s="26" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="E122" s="27" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="F122" s="26" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="G122" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F122),0)&gt;0), MAX($G$1:G121)+1, ""))</f>
@@ -4959,19 +4968,19 @@
         <v>25</v>
       </c>
       <c r="B123" s="27" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="C123" s="28">
         <v>25</v>
       </c>
       <c r="D123" s="26" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E123" s="27" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="F123" s="26" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="G123" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F123),0)&gt;0), MAX($G$1:G122)+1, ""))</f>
@@ -4987,22 +4996,22 @@
         <v>25</v>
       </c>
       <c r="B124" s="27" t="s">
-        <v>251</v>
+        <v>314</v>
       </c>
       <c r="C124" s="28">
         <v>25</v>
       </c>
-      <c r="D124" s="41" t="s">
-        <v>232</v>
+      <c r="D124" s="26">
+        <v>3.9</v>
       </c>
       <c r="E124" s="27" t="s">
-        <v>8</v>
+        <v>313</v>
       </c>
       <c r="F124" s="26" t="s">
-        <v>252</v>
+        <v>315</v>
       </c>
       <c r="G124" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F124),0)&gt;0), MAX($G$1:G123)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F124),0)&gt;0), MAX($G$1:G122)+1, ""))</f>
         <v/>
       </c>
       <c r="H124" s="21" t="b">
@@ -5015,19 +5024,19 @@
         <v>25</v>
       </c>
       <c r="B125" s="27" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C125" s="28">
         <v>25</v>
       </c>
       <c r="D125" s="26" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="E125" s="27" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="F125" s="26" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="G125" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F125),0)&gt;0), MAX($G$1:G124)+1, ""))</f>
@@ -5039,23 +5048,23 @@
       </c>
     </row>
     <row r="126" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A126" s="32">
+      <c r="A126" s="26">
         <v>25</v>
       </c>
-      <c r="B126" s="33" t="s">
-        <v>292</v>
-      </c>
-      <c r="C126" s="34">
+      <c r="B126" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="C126" s="28">
         <v>25</v>
       </c>
-      <c r="D126" s="32" t="s">
-        <v>210</v>
-      </c>
-      <c r="E126" s="33" t="s">
-        <v>287</v>
-      </c>
-      <c r="F126" s="32" t="s">
-        <v>104</v>
+      <c r="D126" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="E126" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F126" s="26" t="s">
+        <v>157</v>
       </c>
       <c r="G126" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F126),0)&gt;0), MAX($G$1:G125)+1, ""))</f>
@@ -5067,23 +5076,23 @@
       </c>
     </row>
     <row r="127" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A127" s="32">
+      <c r="A127" s="26">
         <v>25</v>
       </c>
-      <c r="B127" s="33" t="s">
-        <v>290</v>
-      </c>
-      <c r="C127" s="34">
+      <c r="B127" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="C127" s="28">
         <v>25</v>
       </c>
-      <c r="D127" s="32" t="s">
-        <v>210</v>
-      </c>
-      <c r="E127" s="33" t="s">
-        <v>287</v>
-      </c>
-      <c r="F127" s="32" t="s">
-        <v>104</v>
+      <c r="D127" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="E127" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="F127" s="26" t="s">
+        <v>155</v>
       </c>
       <c r="G127" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F127),0)&gt;0), MAX($G$1:G126)+1, ""))</f>
@@ -5095,23 +5104,23 @@
       </c>
     </row>
     <row r="128" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A128" s="32">
+      <c r="A128" s="26">
         <v>25</v>
       </c>
-      <c r="B128" s="33" t="s">
-        <v>291</v>
-      </c>
-      <c r="C128" s="34">
+      <c r="B128" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="C128" s="28">
         <v>25</v>
       </c>
-      <c r="D128" s="32" t="s">
-        <v>210</v>
-      </c>
-      <c r="E128" s="33" t="s">
-        <v>287</v>
-      </c>
-      <c r="F128" s="32" t="s">
-        <v>104</v>
+      <c r="D128" s="41" t="s">
+        <v>232</v>
+      </c>
+      <c r="E128" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F128" s="26" t="s">
+        <v>252</v>
       </c>
       <c r="G128" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F128),0)&gt;0), MAX($G$1:G127)+1, ""))</f>
@@ -5127,19 +5136,19 @@
         <v>25</v>
       </c>
       <c r="B129" s="27" t="s">
-        <v>256</v>
+        <v>152</v>
       </c>
       <c r="C129" s="28">
         <v>25</v>
       </c>
-      <c r="D129" s="26">
-        <v>2.5</v>
+      <c r="D129" s="26" t="s">
+        <v>238</v>
       </c>
       <c r="E129" s="27" t="s">
         <v>133</v>
       </c>
       <c r="F129" s="26" t="s">
-        <v>257</v>
+        <v>153</v>
       </c>
       <c r="G129" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F129),0)&gt;0), MAX($G$1:G128)+1, ""))</f>
@@ -5155,7 +5164,7 @@
         <v>25</v>
       </c>
       <c r="B130" s="33" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C130" s="34">
         <v>25</v>
@@ -5179,26 +5188,26 @@
       </c>
     </row>
     <row r="131" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A131" s="26">
+      <c r="A131" s="32">
         <v>25</v>
       </c>
-      <c r="B131" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="C131" s="28">
+      <c r="B131" s="33" t="s">
+        <v>290</v>
+      </c>
+      <c r="C131" s="34">
         <v>25</v>
       </c>
-      <c r="D131" s="26" t="s">
-        <v>229</v>
-      </c>
-      <c r="E131" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="F131" s="26" t="s">
-        <v>151</v>
+      <c r="D131" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="E131" s="33" t="s">
+        <v>287</v>
+      </c>
+      <c r="F131" s="32" t="s">
+        <v>104</v>
       </c>
       <c r="G131" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F131),0)&gt;0), MAX($G$1:G129)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F131),0)&gt;0), MAX($G$1:G130)+1, ""))</f>
         <v/>
       </c>
       <c r="H131" s="21" t="b">
@@ -5208,22 +5217,22 @@
     </row>
     <row r="132" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A132" s="32">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B132" s="33" t="s">
-        <v>195</v>
+        <v>291</v>
       </c>
       <c r="C132" s="34">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D132" s="32" t="s">
-        <v>235</v>
+        <v>210</v>
       </c>
       <c r="E132" s="33" t="s">
-        <v>133</v>
+        <v>287</v>
       </c>
       <c r="F132" s="32" t="s">
-        <v>196</v>
+        <v>104</v>
       </c>
       <c r="G132" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B132),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E132),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F132),0)&gt;0), MAX($G$1:G131)+1, ""))</f>
@@ -5235,23 +5244,23 @@
       </c>
     </row>
     <row r="133" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A133" s="32">
-        <v>30</v>
-      </c>
-      <c r="B133" s="33" t="s">
-        <v>194</v>
-      </c>
-      <c r="C133" s="34">
-        <v>30</v>
-      </c>
-      <c r="D133" s="32" t="s">
-        <v>245</v>
-      </c>
-      <c r="E133" s="33" t="s">
+      <c r="A133" s="26">
+        <v>25</v>
+      </c>
+      <c r="B133" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="C133" s="28">
+        <v>25</v>
+      </c>
+      <c r="D133" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E133" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="F133" s="32" t="s">
-        <v>193</v>
+      <c r="F133" s="26" t="s">
+        <v>257</v>
       </c>
       <c r="G133" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F133),0)&gt;0), MAX($G$1:G132)+1, ""))</f>
@@ -5264,22 +5273,22 @@
     </row>
     <row r="134" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A134" s="32">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B134" s="33" t="s">
-        <v>192</v>
+        <v>289</v>
       </c>
       <c r="C134" s="34">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D134" s="32" t="s">
-        <v>244</v>
+        <v>210</v>
       </c>
       <c r="E134" s="33" t="s">
-        <v>133</v>
+        <v>287</v>
       </c>
       <c r="F134" s="32" t="s">
-        <v>193</v>
+        <v>104</v>
       </c>
       <c r="G134" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F134),0)&gt;0), MAX($G$1:G133)+1, ""))</f>
@@ -5291,26 +5300,26 @@
       </c>
     </row>
     <row r="135" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A135" s="32">
-        <v>30</v>
-      </c>
-      <c r="B135" s="33" t="s">
-        <v>250</v>
-      </c>
-      <c r="C135" s="34">
-        <v>30</v>
-      </c>
-      <c r="D135" s="32" t="s">
-        <v>220</v>
-      </c>
-      <c r="E135" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F135" s="32" t="s">
-        <v>191</v>
+      <c r="A135" s="26">
+        <v>25</v>
+      </c>
+      <c r="B135" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C135" s="28">
+        <v>25</v>
+      </c>
+      <c r="D135" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="E135" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="F135" s="26" t="s">
+        <v>151</v>
       </c>
       <c r="G135" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F135),0)&gt;0), MAX($G$1:G134)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F135),0)&gt;0), MAX($G$1:G133)+1, ""))</f>
         <v/>
       </c>
       <c r="H135" s="21" t="b">
@@ -5323,19 +5332,19 @@
         <v>30</v>
       </c>
       <c r="B136" s="33" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="C136" s="34">
         <v>30</v>
       </c>
       <c r="D136" s="32" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E136" s="33" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="F136" s="32" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="G136" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F136),0)&gt;0), MAX($G$1:G135)+1, ""))</f>
@@ -5351,19 +5360,19 @@
         <v>30</v>
       </c>
       <c r="B137" s="33" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C137" s="34">
         <v>30</v>
       </c>
       <c r="D137" s="32" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="E137" s="33" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="F137" s="32" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="G137" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F137),0)&gt;0), MAX($G$1:G136)+1, ""))</f>
@@ -5379,19 +5388,19 @@
         <v>30</v>
       </c>
       <c r="B138" s="33" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="C138" s="34">
         <v>30</v>
       </c>
       <c r="D138" s="32" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E138" s="33" t="s">
         <v>133</v>
       </c>
       <c r="F138" s="32" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="G138" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F138),0)&gt;0), MAX($G$1:G137)+1, ""))</f>
@@ -5407,19 +5416,19 @@
         <v>30</v>
       </c>
       <c r="B139" s="33" t="s">
-        <v>183</v>
+        <v>250</v>
       </c>
       <c r="C139" s="34">
         <v>30</v>
       </c>
       <c r="D139" s="32" t="s">
-        <v>242</v>
+        <v>220</v>
       </c>
       <c r="E139" s="33" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="F139" s="32" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="G139" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F139),0)&gt;0), MAX($G$1:G138)+1, ""))</f>
@@ -5431,23 +5440,23 @@
       </c>
     </row>
     <row r="140" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A140" s="26">
-        <v>40</v>
-      </c>
-      <c r="B140" s="27" t="s">
-        <v>200</v>
-      </c>
-      <c r="C140" s="28">
-        <v>40</v>
-      </c>
-      <c r="D140" s="26" t="s">
-        <v>247</v>
-      </c>
-      <c r="E140" s="27" t="s">
-        <v>201</v>
-      </c>
-      <c r="F140" s="26" t="s">
-        <v>202</v>
+      <c r="A140" s="32">
+        <v>30</v>
+      </c>
+      <c r="B140" s="33" t="s">
+        <v>189</v>
+      </c>
+      <c r="C140" s="34">
+        <v>30</v>
+      </c>
+      <c r="D140" s="32" t="s">
+        <v>232</v>
+      </c>
+      <c r="E140" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F140" s="32" t="s">
+        <v>190</v>
       </c>
       <c r="G140" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F140),0)&gt;0), MAX($G$1:G139)+1, ""))</f>
@@ -5459,23 +5468,23 @@
       </c>
     </row>
     <row r="141" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A141" s="26">
-        <v>40</v>
-      </c>
-      <c r="B141" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="C141" s="28">
-        <v>40</v>
-      </c>
-      <c r="D141" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="E141" s="27" t="s">
-        <v>198</v>
-      </c>
-      <c r="F141" s="26" t="s">
-        <v>199</v>
+      <c r="A141" s="32">
+        <v>30</v>
+      </c>
+      <c r="B141" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="C141" s="34">
+        <v>30</v>
+      </c>
+      <c r="D141" s="32" t="s">
+        <v>231</v>
+      </c>
+      <c r="E141" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="F141" s="32" t="s">
+        <v>188</v>
       </c>
       <c r="G141" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F141),0)&gt;0), MAX($G$1:G140)+1, ""))</f>
@@ -5487,23 +5496,23 @@
       </c>
     </row>
     <row r="142" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A142" s="26">
-        <v>40</v>
-      </c>
-      <c r="B142" s="27" t="s">
-        <v>253</v>
-      </c>
-      <c r="C142" s="28">
-        <v>40</v>
-      </c>
-      <c r="D142" s="26">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="E142" s="27" t="s">
-        <v>254</v>
-      </c>
-      <c r="F142" s="26" t="s">
-        <v>255</v>
+      <c r="A142" s="32">
+        <v>30</v>
+      </c>
+      <c r="B142" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="C142" s="34">
+        <v>30</v>
+      </c>
+      <c r="D142" s="32" t="s">
+        <v>243</v>
+      </c>
+      <c r="E142" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="F142" s="32" t="s">
+        <v>186</v>
       </c>
       <c r="G142" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F142),0)&gt;0), MAX($G$1:G141)+1, ""))</f>
@@ -5515,23 +5524,23 @@
       </c>
     </row>
     <row r="143" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A143" s="26">
-        <v>45</v>
-      </c>
-      <c r="B143" s="27" t="s">
-        <v>298</v>
-      </c>
-      <c r="C143" s="28">
-        <v>45</v>
-      </c>
-      <c r="D143" s="26">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="E143" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="F143" s="26" t="s">
-        <v>300</v>
+      <c r="A143" s="32">
+        <v>30</v>
+      </c>
+      <c r="B143" s="33" t="s">
+        <v>183</v>
+      </c>
+      <c r="C143" s="34">
+        <v>30</v>
+      </c>
+      <c r="D143" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="E143" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="F143" s="32" t="s">
+        <v>184</v>
       </c>
       <c r="G143" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F143),0)&gt;0), MAX($G$1:G142)+1, ""))</f>
@@ -5543,108 +5552,196 @@
       </c>
     </row>
     <row r="144" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A144" s="30"/>
-      <c r="B144" s="31"/>
-      <c r="C144" s="30"/>
-      <c r="D144" s="30"/>
-      <c r="E144" s="31"/>
-      <c r="F144" s="30"/>
-      <c r="G144" s="31"/>
-    </row>
-    <row r="145" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A145" s="30"/>
-      <c r="B145" s="31"/>
-      <c r="C145" s="30"/>
-      <c r="D145" s="30"/>
-      <c r="E145" s="31"/>
-      <c r="F145" s="30"/>
-      <c r="G145" s="31"/>
-    </row>
-    <row r="146" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A146" s="1"/>
-      <c r="C146" s="1"/>
-      <c r="D146" s="1"/>
-      <c r="F146" s="1"/>
-    </row>
-    <row r="147" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A147" s="1"/>
-      <c r="C147" s="1"/>
-      <c r="D147" s="1"/>
-      <c r="F147" s="1"/>
-    </row>
-    <row r="148" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A148" s="1"/>
-      <c r="C148" s="1"/>
-      <c r="D148" s="1"/>
-      <c r="F148" s="1"/>
-    </row>
-    <row r="149" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A149" s="1"/>
-      <c r="C149" s="1"/>
-      <c r="D149" s="1"/>
-      <c r="F149" s="1"/>
-    </row>
-    <row r="150" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A144" s="26">
+        <v>40</v>
+      </c>
+      <c r="B144" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="C144" s="28">
+        <v>40</v>
+      </c>
+      <c r="D144" s="26" t="s">
+        <v>247</v>
+      </c>
+      <c r="E144" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="F144" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="G144" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F144),0)&gt;0), MAX($G$1:G143)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H144" s="21" t="b">
+        <f>A144=C144</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A145" s="26">
+        <v>40</v>
+      </c>
+      <c r="B145" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="C145" s="28">
+        <v>40</v>
+      </c>
+      <c r="D145" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="E145" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="F145" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="G145" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B145),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E145),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F145),0)&gt;0), MAX($G$1:G144)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H145" s="21" t="b">
+        <f>A145=C145</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A146" s="26">
+        <v>40</v>
+      </c>
+      <c r="B146" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="C146" s="28">
+        <v>40</v>
+      </c>
+      <c r="D146" s="26">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E146" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="F146" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="G146" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F146),0)&gt;0), MAX($G$1:G145)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H146" s="21" t="b">
+        <f>A146=C146</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A147" s="26">
+        <v>45</v>
+      </c>
+      <c r="B147" s="27" t="s">
+        <v>298</v>
+      </c>
+      <c r="C147" s="28">
+        <v>45</v>
+      </c>
+      <c r="D147" s="26">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E147" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="F147" s="26" t="s">
+        <v>300</v>
+      </c>
+      <c r="G147" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F147),0)&gt;0), MAX($G$1:G146)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H147" s="21" t="b">
+        <f>A147=C147</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A148" s="30"/>
+      <c r="B148" s="31"/>
+      <c r="C148" s="30"/>
+      <c r="D148" s="30"/>
+      <c r="E148" s="31"/>
+      <c r="F148" s="30"/>
+      <c r="G148" s="31"/>
+    </row>
+    <row r="149" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A149" s="30"/>
+      <c r="B149" s="31"/>
+      <c r="C149" s="30"/>
+      <c r="D149" s="30"/>
+      <c r="E149" s="31"/>
+      <c r="F149" s="30"/>
+      <c r="G149" s="31"/>
+    </row>
+    <row r="150" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="C150" s="1"/>
       <c r="D150" s="1"/>
       <c r="F150" s="1"/>
     </row>
-    <row r="151" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="C151" s="1"/>
       <c r="D151" s="1"/>
       <c r="F151" s="1"/>
     </row>
-    <row r="152" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="C152" s="1"/>
       <c r="D152" s="1"/>
       <c r="F152" s="1"/>
     </row>
-    <row r="153" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="C153" s="1"/>
       <c r="D153" s="1"/>
       <c r="F153" s="1"/>
     </row>
-    <row r="154" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="C154" s="1"/>
       <c r="D154" s="1"/>
       <c r="F154" s="1"/>
     </row>
-    <row r="155" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="C155" s="1"/>
       <c r="D155" s="1"/>
       <c r="F155" s="1"/>
     </row>
-    <row r="156" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="C156" s="1"/>
       <c r="D156" s="1"/>
       <c r="F156" s="1"/>
     </row>
-    <row r="157" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="C157" s="1"/>
       <c r="D157" s="1"/>
       <c r="F157" s="1"/>
     </row>
-    <row r="158" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="C158" s="1"/>
       <c r="D158" s="1"/>
       <c r="F158" s="1"/>
     </row>
-    <row r="159" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="C159" s="1"/>
       <c r="D159" s="1"/>
       <c r="F159" s="1"/>
     </row>
-    <row r="160" spans="1:7" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="C160" s="1"/>
       <c r="D160" s="1"/>
@@ -10870,12 +10967,36 @@
       <c r="D1030" s="1"/>
       <c r="F1030" s="1"/>
     </row>
+    <row r="1031" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1031" s="1"/>
+      <c r="C1031" s="1"/>
+      <c r="D1031" s="1"/>
+      <c r="F1031" s="1"/>
+    </row>
+    <row r="1032" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1032" s="1"/>
+      <c r="C1032" s="1"/>
+      <c r="D1032" s="1"/>
+      <c r="F1032" s="1"/>
+    </row>
+    <row r="1033" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1033" s="1"/>
+      <c r="C1033" s="1"/>
+      <c r="D1033" s="1"/>
+      <c r="F1033" s="1"/>
+    </row>
+    <row r="1034" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1034" s="1"/>
+      <c r="C1034" s="1"/>
+      <c r="D1034" s="1"/>
+      <c r="F1034" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H143">
-    <sortState ref="A2:H143">
-      <sortCondition ref="A2:A143"/>
-      <sortCondition ref="B2:B143"/>
-      <sortCondition ref="D2:D143"/>
+  <autoFilter ref="A1:H147">
+    <sortState ref="A2:H147">
+      <sortCondition ref="A2:A147"/>
+      <sortCondition ref="B2:B147"/>
+      <sortCondition ref="D2:D147"/>
     </sortState>
   </autoFilter>
   <sortState ref="A2:H140">

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Consulta" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$148</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$135</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Base!$1:$1</definedName>
   </definedNames>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="343">
   <si>
     <t>Grupo</t>
   </si>
@@ -1048,6 +1048,12 @@
   </si>
   <si>
     <t>Vila Militar - Magalhães</t>
+  </si>
+  <si>
+    <t>TRAVESSA HUMBERTO TEIXEIRA</t>
+  </si>
+  <si>
+    <t>21775-375</t>
   </si>
 </sst>
 </file>
@@ -1576,7 +1582,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H1034"/>
+  <dimension ref="A1:H1035"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.453125" customWidth="1"/>
@@ -5528,19 +5534,19 @@
         <v>30</v>
       </c>
       <c r="B143" s="33" t="s">
-        <v>183</v>
+        <v>341</v>
       </c>
       <c r="C143" s="34">
         <v>30</v>
       </c>
-      <c r="D143" s="32" t="s">
-        <v>242</v>
+      <c r="D143" s="32">
+        <v>2.9</v>
       </c>
       <c r="E143" s="33" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="F143" s="32" t="s">
-        <v>184</v>
+        <v>342</v>
       </c>
       <c r="G143" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F143),0)&gt;0), MAX($G$1:G142)+1, ""))</f>
@@ -5552,26 +5558,26 @@
       </c>
     </row>
     <row r="144" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A144" s="26">
-        <v>40</v>
-      </c>
-      <c r="B144" s="27" t="s">
-        <v>200</v>
-      </c>
-      <c r="C144" s="28">
-        <v>40</v>
-      </c>
-      <c r="D144" s="26" t="s">
-        <v>247</v>
-      </c>
-      <c r="E144" s="27" t="s">
-        <v>201</v>
-      </c>
-      <c r="F144" s="26" t="s">
-        <v>202</v>
+      <c r="A144" s="32">
+        <v>30</v>
+      </c>
+      <c r="B144" s="33" t="s">
+        <v>183</v>
+      </c>
+      <c r="C144" s="34">
+        <v>30</v>
+      </c>
+      <c r="D144" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="E144" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="F144" s="32" t="s">
+        <v>184</v>
       </c>
       <c r="G144" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F144),0)&gt;0), MAX($G$1:G143)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F144),0)&gt;0), MAX($G$1:G142)+1, ""))</f>
         <v/>
       </c>
       <c r="H144" s="21" t="b">
@@ -5584,19 +5590,19 @@
         <v>40</v>
       </c>
       <c r="B145" s="27" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C145" s="28">
         <v>40</v>
       </c>
       <c r="D145" s="26" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E145" s="27" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F145" s="26" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="G145" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B145),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E145),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F145),0)&gt;0), MAX($G$1:G144)+1, ""))</f>
@@ -5612,19 +5618,19 @@
         <v>40</v>
       </c>
       <c r="B146" s="27" t="s">
-        <v>253</v>
+        <v>197</v>
       </c>
       <c r="C146" s="28">
         <v>40</v>
       </c>
-      <c r="D146" s="26">
-        <v>8.3000000000000007</v>
+      <c r="D146" s="26" t="s">
+        <v>246</v>
       </c>
       <c r="E146" s="27" t="s">
-        <v>254</v>
+        <v>198</v>
       </c>
       <c r="F146" s="26" t="s">
-        <v>255</v>
+        <v>199</v>
       </c>
       <c r="G146" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F146),0)&gt;0), MAX($G$1:G145)+1, ""))</f>
@@ -5637,22 +5643,22 @@
     </row>
     <row r="147" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A147" s="26">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B147" s="27" t="s">
-        <v>298</v>
+        <v>253</v>
       </c>
       <c r="C147" s="28">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D147" s="26">
-        <v>10.199999999999999</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="E147" s="27" t="s">
-        <v>299</v>
+        <v>254</v>
       </c>
       <c r="F147" s="26" t="s">
-        <v>300</v>
+        <v>255</v>
       </c>
       <c r="G147" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F147),0)&gt;0), MAX($G$1:G146)+1, ""))</f>
@@ -5664,13 +5670,32 @@
       </c>
     </row>
     <row r="148" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A148" s="30"/>
-      <c r="B148" s="31"/>
-      <c r="C148" s="30"/>
-      <c r="D148" s="30"/>
-      <c r="E148" s="31"/>
-      <c r="F148" s="30"/>
-      <c r="G148" s="31"/>
+      <c r="A148" s="26">
+        <v>45</v>
+      </c>
+      <c r="B148" s="27" t="s">
+        <v>298</v>
+      </c>
+      <c r="C148" s="28">
+        <v>45</v>
+      </c>
+      <c r="D148" s="26">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E148" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="F148" s="26" t="s">
+        <v>300</v>
+      </c>
+      <c r="G148" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F148),0)&gt;0), MAX($G$1:G147)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H148" s="21" t="b">
+        <f>A148=C148</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="149" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A149" s="30"/>
@@ -5682,10 +5707,13 @@
       <c r="G149" s="31"/>
     </row>
     <row r="150" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A150" s="1"/>
-      <c r="C150" s="1"/>
-      <c r="D150" s="1"/>
-      <c r="F150" s="1"/>
+      <c r="A150" s="30"/>
+      <c r="B150" s="31"/>
+      <c r="C150" s="30"/>
+      <c r="D150" s="30"/>
+      <c r="E150" s="31"/>
+      <c r="F150" s="30"/>
+      <c r="G150" s="31"/>
     </row>
     <row r="151" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
@@ -10991,8 +11019,14 @@
       <c r="D1034" s="1"/>
       <c r="F1034" s="1"/>
     </row>
+    <row r="1035" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1035" s="1"/>
+      <c r="C1035" s="1"/>
+      <c r="D1035" s="1"/>
+      <c r="F1035" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H147">
+  <autoFilter ref="A1:H148">
     <sortState ref="A2:H147">
       <sortCondition ref="A2:A147"/>
       <sortCondition ref="B2:B147"/>

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="341">
   <si>
     <t>Grupo</t>
   </si>
@@ -552,9 +552,6 @@
     <t>HUMBERTO TEIXEIRA</t>
   </si>
   <si>
-    <t>21815-040</t>
-  </si>
-  <si>
     <t>EUCLIDES ROXO</t>
   </si>
   <si>
@@ -747,9 +744,6 @@
     <t>3,4</t>
   </si>
   <si>
-    <t>3,3</t>
-  </si>
-  <si>
     <t>3,7</t>
   </si>
   <si>
@@ -1053,7 +1047,7 @@
     <t>TRAVESSA HUMBERTO TEIXEIRA</t>
   </si>
   <si>
-    <t>21775-375</t>
+    <t>21775-370</t>
   </si>
 </sst>
 </file>
@@ -1613,7 +1607,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="25" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
@@ -1621,7 +1615,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C2" s="34">
         <v>13</v>
@@ -1630,7 +1624,7 @@
         <v>22</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F2" s="32" t="s">
         <v>26</v>
@@ -1677,7 +1671,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C4" s="34">
         <v>13</v>
@@ -1686,7 +1680,7 @@
         <v>22</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F4" s="32" t="s">
         <v>26</v>
@@ -1705,7 +1699,7 @@
         <v>13</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C5" s="34">
         <v>13</v>
@@ -1714,7 +1708,7 @@
         <v>22</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F5" s="32" t="s">
         <v>26</v>
@@ -1761,7 +1755,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C7" s="34">
         <v>13</v>
@@ -1770,7 +1764,7 @@
         <v>22</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F7" s="32" t="s">
         <v>26</v>
@@ -1789,7 +1783,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C8" s="34">
         <v>13</v>
@@ -1798,7 +1792,7 @@
         <v>22</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F8" s="32" t="s">
         <v>26</v>
@@ -1845,7 +1839,7 @@
         <v>13</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C10" s="34">
         <v>13</v>
@@ -1854,7 +1848,7 @@
         <v>22</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F10" s="32" t="s">
         <v>26</v>
@@ -1879,7 +1873,7 @@
         <v>13</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E11" s="33" t="s">
         <v>8</v>
@@ -1901,7 +1895,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C12" s="34">
         <v>13</v>
@@ -1910,7 +1904,7 @@
         <v>22</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F12" s="32" t="s">
         <v>26</v>
@@ -1957,7 +1951,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C14" s="34">
         <v>13</v>
@@ -1966,7 +1960,7 @@
         <v>22</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F14" s="32" t="s">
         <v>26</v>
@@ -2075,10 +2069,10 @@
         <v>15</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F18" s="26" t="s">
         <v>77</v>
@@ -2103,7 +2097,7 @@
         <v>15</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E19" s="27" t="s">
         <v>8</v>
@@ -2131,7 +2125,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E20" s="27" t="s">
         <v>8</v>
@@ -2159,7 +2153,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E21" s="27" t="s">
         <v>8</v>
@@ -2187,7 +2181,7 @@
         <v>15</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E22" s="27" t="s">
         <v>8</v>
@@ -2209,16 +2203,16 @@
         <v>15</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C23" s="28">
         <v>15</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F23" s="26" t="s">
         <v>66</v>
@@ -2237,7 +2231,7 @@
         <v>15</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C24" s="28">
         <v>15</v>
@@ -2249,7 +2243,7 @@
         <v>8</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G24" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B24),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E24),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F24),0)&gt;0), MAX($G$1:G23)+1, ""))</f>
@@ -2271,7 +2265,7 @@
         <v>15</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E25" s="27" t="s">
         <v>8</v>
@@ -2293,13 +2287,13 @@
         <v>15</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C26" s="28">
         <v>15</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E26" s="27" t="s">
         <v>8</v>
@@ -2321,7 +2315,7 @@
         <v>15</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C27" s="28">
         <v>15</v>
@@ -2330,10 +2324,10 @@
         <v>2.1</v>
       </c>
       <c r="E27" s="27" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G27" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B27),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E27),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F27),0)&gt;0), MAX($G$1:G26)+1, ""))</f>
@@ -2355,7 +2349,7 @@
         <v>15</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E28" s="27" t="s">
         <v>8</v>
@@ -2377,13 +2371,13 @@
         <v>15</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C29" s="28">
         <v>15</v>
       </c>
       <c r="D29" s="26" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E29" s="27" t="s">
         <v>8</v>
@@ -2405,7 +2399,7 @@
         <v>15</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C30" s="28">
         <v>15</v>
@@ -2417,7 +2411,7 @@
         <v>8</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G30" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B30),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E30),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F30),0)&gt;0), MAX($G$1:G29)+1, ""))</f>
@@ -2433,7 +2427,7 @@
         <v>15</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C31" s="28">
         <v>15</v>
@@ -2445,7 +2439,7 @@
         <v>8</v>
       </c>
       <c r="F31" s="26" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G31" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B31),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E31),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F31),0)&gt;0), MAX($G$1:G30)+1, ""))</f>
@@ -2467,7 +2461,7 @@
         <v>15</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E32" s="27" t="s">
         <v>8</v>
@@ -2495,7 +2489,7 @@
         <v>15</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E33" s="27" t="s">
         <v>8</v>
@@ -2523,7 +2517,7 @@
         <v>15</v>
       </c>
       <c r="D34" s="26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E34" s="27" t="s">
         <v>8</v>
@@ -2551,7 +2545,7 @@
         <v>15</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E35" s="27" t="s">
         <v>8</v>
@@ -2579,7 +2573,7 @@
         <v>15</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E36" s="27" t="s">
         <v>8</v>
@@ -2601,7 +2595,7 @@
         <v>15</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C37" s="28">
         <v>15</v>
@@ -2613,7 +2607,7 @@
         <v>8</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G37" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F37),0)&gt;0), MAX($G$1:G36)+1, ""))</f>
@@ -2629,7 +2623,7 @@
         <v>15</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C38" s="28">
         <v>15</v>
@@ -2638,10 +2632,10 @@
         <v>2.1</v>
       </c>
       <c r="E38" s="27" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F38" s="26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G38" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F38),0)&gt;0), MAX($G$1:G37)+1, ""))</f>
@@ -2663,7 +2657,7 @@
         <v>15</v>
       </c>
       <c r="D39" s="26" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E39" s="27" t="s">
         <v>8</v>
@@ -2691,7 +2685,7 @@
         <v>15</v>
       </c>
       <c r="D40" s="26" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E40" s="27" t="s">
         <v>8</v>
@@ -2713,16 +2707,16 @@
         <v>15</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C41" s="28">
         <v>15</v>
       </c>
       <c r="D41" s="26" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E41" s="27" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F41" s="26" t="s">
         <v>34</v>
@@ -2747,7 +2741,7 @@
         <v>17</v>
       </c>
       <c r="D42" s="35" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E42" s="36" t="s">
         <v>8</v>
@@ -2769,13 +2763,13 @@
         <v>17</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C43" s="37">
         <v>17</v>
       </c>
       <c r="D43" s="35" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E43" s="36" t="s">
         <v>61</v>
@@ -2797,7 +2791,7 @@
         <v>17</v>
       </c>
       <c r="B44" s="27" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C44" s="28">
         <v>17</v>
@@ -2809,7 +2803,7 @@
         <v>61</v>
       </c>
       <c r="F44" s="26" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G44" s="29"/>
       <c r="H44" s="21" t="b">
@@ -2828,7 +2822,7 @@
         <v>17</v>
       </c>
       <c r="D45" s="35" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E45" s="36" t="s">
         <v>8</v>
@@ -2856,7 +2850,7 @@
         <v>17</v>
       </c>
       <c r="D46" s="35" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E46" s="36" t="s">
         <v>61</v>
@@ -2878,7 +2872,7 @@
         <v>17</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C47" s="28">
         <v>17</v>
@@ -2890,7 +2884,7 @@
         <v>61</v>
       </c>
       <c r="F47" s="26" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G47" s="29"/>
       <c r="H47" s="21" t="b">
@@ -2903,7 +2897,7 @@
         <v>17</v>
       </c>
       <c r="B48" s="27" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C48" s="28">
         <v>17</v>
@@ -2915,7 +2909,7 @@
         <v>61</v>
       </c>
       <c r="F48" s="26" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G48" s="29"/>
       <c r="H48" s="21" t="b">
@@ -2928,13 +2922,13 @@
         <v>17</v>
       </c>
       <c r="B49" s="39" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C49" s="40">
         <v>17</v>
       </c>
       <c r="D49" s="38" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E49" s="39" t="s">
         <v>61</v>
@@ -2956,7 +2950,7 @@
         <v>17</v>
       </c>
       <c r="B50" s="27" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C50" s="28">
         <v>17</v>
@@ -2968,7 +2962,7 @@
         <v>61</v>
       </c>
       <c r="F50" s="26" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G50" s="29"/>
       <c r="H50" s="21" t="b">
@@ -2981,7 +2975,7 @@
         <v>17</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C51" s="28">
         <v>17</v>
@@ -2993,7 +2987,7 @@
         <v>61</v>
       </c>
       <c r="F51" s="26" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G51" s="29"/>
       <c r="H51" s="21" t="b">
@@ -3012,7 +3006,7 @@
         <v>17</v>
       </c>
       <c r="D52" s="38" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E52" s="39" t="s">
         <v>8</v>
@@ -3034,16 +3028,16 @@
         <v>17</v>
       </c>
       <c r="B53" s="39" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C53" s="40">
         <v>17</v>
       </c>
       <c r="D53" s="38" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E53" s="39" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F53" s="38" t="s">
         <v>107</v>
@@ -3068,7 +3062,7 @@
         <v>17</v>
       </c>
       <c r="D54" s="35" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E54" s="36" t="s">
         <v>8</v>
@@ -3096,7 +3090,7 @@
         <v>17</v>
       </c>
       <c r="D55" s="35" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E55" s="36" t="s">
         <v>8</v>
@@ -3124,7 +3118,7 @@
         <v>17</v>
       </c>
       <c r="D56" s="38" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E56" s="39" t="s">
         <v>8</v>
@@ -3152,7 +3146,7 @@
         <v>17</v>
       </c>
       <c r="D57" s="38" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E57" s="39" t="s">
         <v>8</v>
@@ -3174,7 +3168,7 @@
         <v>17</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C58" s="37">
         <v>17</v>
@@ -3186,10 +3180,10 @@
         <v>61</v>
       </c>
       <c r="F58" s="35" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G58" s="29" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="H58" s="21" t="b">
         <v>1</v>
@@ -3200,7 +3194,7 @@
         <v>17</v>
       </c>
       <c r="B59" s="36" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C59" s="37">
         <v>17</v>
@@ -3212,10 +3206,10 @@
         <v>61</v>
       </c>
       <c r="F59" s="35" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G59" s="29" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="H59" s="21" t="b">
         <v>1</v>
@@ -3226,7 +3220,7 @@
         <v>17</v>
       </c>
       <c r="B60" s="36" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C60" s="37">
         <v>17</v>
@@ -3238,10 +3232,10 @@
         <v>61</v>
       </c>
       <c r="F60" s="35" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G60" s="29" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="H60" s="21" t="b">
         <v>1</v>
@@ -3258,7 +3252,7 @@
         <v>17</v>
       </c>
       <c r="D61" s="35" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E61" s="36" t="s">
         <v>8</v>
@@ -3286,7 +3280,7 @@
         <v>17</v>
       </c>
       <c r="D62" s="38" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E62" s="39" t="s">
         <v>8</v>
@@ -3314,7 +3308,7 @@
         <v>17</v>
       </c>
       <c r="D63" s="35" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E63" s="36" t="s">
         <v>8</v>
@@ -3342,7 +3336,7 @@
         <v>17</v>
       </c>
       <c r="D64" s="35" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E64" s="36" t="s">
         <v>8</v>
@@ -3351,7 +3345,7 @@
         <v>31</v>
       </c>
       <c r="G64" s="29" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="H64" s="21" t="b">
         <v>1</v>
@@ -3368,7 +3362,7 @@
         <v>20</v>
       </c>
       <c r="D65" s="32" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E65" s="33" t="s">
         <v>8</v>
@@ -3396,7 +3390,7 @@
         <v>20</v>
       </c>
       <c r="D66" s="32" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E66" s="33" t="s">
         <v>8</v>
@@ -3424,7 +3418,7 @@
         <v>20</v>
       </c>
       <c r="D67" s="32" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E67" s="33" t="s">
         <v>8</v>
@@ -3452,10 +3446,10 @@
         <v>20</v>
       </c>
       <c r="D68" s="32" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E68" s="33" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F68" s="32" t="s">
         <v>143</v>
@@ -3474,7 +3468,7 @@
         <v>20</v>
       </c>
       <c r="B69" s="39" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C69" s="40">
         <v>20</v>
@@ -3483,10 +3477,10 @@
         <v>3.4</v>
       </c>
       <c r="E69" s="39" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F69" s="38" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G69" s="29"/>
       <c r="H69" s="21" t="b">
@@ -3499,7 +3493,7 @@
         <v>20</v>
       </c>
       <c r="B70" s="39" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C70" s="40">
         <v>20</v>
@@ -3508,10 +3502,10 @@
         <v>3.3</v>
       </c>
       <c r="E70" s="39" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F70" s="38" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G70" s="29"/>
       <c r="H70" s="21" t="b">
@@ -3530,7 +3524,7 @@
         <v>20</v>
       </c>
       <c r="D71" s="32" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E71" s="33" t="s">
         <v>8</v>
@@ -3552,19 +3546,19 @@
         <v>20</v>
       </c>
       <c r="B72" s="33" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C72" s="34">
         <v>20</v>
       </c>
       <c r="D72" s="32" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E72" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F72" s="32" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G72" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F72),0)&gt;0), MAX($G$1:G71)+1, ""))</f>
@@ -3580,7 +3574,7 @@
         <v>20</v>
       </c>
       <c r="B73" s="33" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C73" s="34">
         <v>20</v>
@@ -3589,7 +3583,7 @@
         <v>4.2</v>
       </c>
       <c r="E73" s="33" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F73" s="32">
         <v>21765430</v>
@@ -3614,7 +3608,7 @@
         <v>20</v>
       </c>
       <c r="D74" s="32" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E74" s="33" t="s">
         <v>8</v>
@@ -3636,13 +3630,13 @@
         <v>20</v>
       </c>
       <c r="B75" s="33" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C75" s="34">
         <v>20</v>
       </c>
       <c r="D75" s="32" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E75" s="33" t="s">
         <v>8</v>
@@ -3670,10 +3664,10 @@
         <v>20</v>
       </c>
       <c r="D76" s="32" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E76" s="33" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F76" s="32" t="s">
         <v>136</v>
@@ -3698,7 +3692,7 @@
         <v>20</v>
       </c>
       <c r="D77" s="32" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E77" s="33" t="s">
         <v>133</v>
@@ -3720,7 +3714,7 @@
         <v>20</v>
       </c>
       <c r="B78" s="27" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C78" s="28">
         <v>20</v>
@@ -3732,7 +3726,7 @@
         <v>61</v>
       </c>
       <c r="F78" s="26" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G78" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F78),0)&gt;0), MAX($G$1:G77)+1, ""))</f>
@@ -3754,7 +3748,7 @@
         <v>20</v>
       </c>
       <c r="D79" s="32" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E79" s="33" t="s">
         <v>8</v>
@@ -3782,10 +3776,10 @@
         <v>20</v>
       </c>
       <c r="D80" s="32" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E80" s="33" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F80" s="32" t="s">
         <v>129</v>
@@ -3810,7 +3804,7 @@
         <v>20</v>
       </c>
       <c r="D81" s="32" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E81" s="33" t="s">
         <v>8</v>
@@ -3838,7 +3832,7 @@
         <v>20</v>
       </c>
       <c r="D82" s="32" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E82" s="33" t="s">
         <v>8</v>
@@ -3866,10 +3860,10 @@
         <v>20</v>
       </c>
       <c r="D83" s="32" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E83" s="33" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F83" s="32" t="s">
         <v>123</v>
@@ -3888,19 +3882,19 @@
         <v>20</v>
       </c>
       <c r="B84" s="33" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C84" s="34">
         <v>20</v>
       </c>
       <c r="D84" s="32" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E84" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F84" s="32" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G84" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F84),0)&gt;0), MAX($G$1:G83)+1, ""))</f>
@@ -3922,7 +3916,7 @@
         <v>20</v>
       </c>
       <c r="D85" s="32" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E85" s="33" t="s">
         <v>8</v>
@@ -3950,7 +3944,7 @@
         <v>20</v>
       </c>
       <c r="D86" s="32" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E86" s="33" t="s">
         <v>8</v>
@@ -3978,7 +3972,7 @@
         <v>20</v>
       </c>
       <c r="D87" s="32" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E87" s="33" t="s">
         <v>8</v>
@@ -4000,7 +3994,7 @@
         <v>20</v>
       </c>
       <c r="B88" s="27" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C88" s="28">
         <v>20</v>
@@ -4009,10 +4003,10 @@
         <v>2.4</v>
       </c>
       <c r="E88" s="27" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F88" s="26" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G88" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F88),0)&gt;0), MAX($G$1:G87)+1, ""))</f>
@@ -4034,7 +4028,7 @@
         <v>20</v>
       </c>
       <c r="D89" s="32" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E89" s="33" t="s">
         <v>8</v>
@@ -4062,10 +4056,10 @@
         <v>20</v>
       </c>
       <c r="D90" s="32" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E90" s="33" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F90" s="32" t="s">
         <v>113</v>
@@ -4090,7 +4084,7 @@
         <v>20</v>
       </c>
       <c r="D91" s="32" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E91" s="33" t="s">
         <v>8</v>
@@ -4112,7 +4106,7 @@
         <v>20</v>
       </c>
       <c r="B92" s="39" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C92" s="40">
         <v>20</v>
@@ -4121,7 +4115,7 @@
         <v>3</v>
       </c>
       <c r="E92" s="39" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F92" s="38" t="s">
         <v>107</v>
@@ -4137,7 +4131,7 @@
         <v>20</v>
       </c>
       <c r="B93" s="27" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C93" s="28">
         <v>20</v>
@@ -4146,10 +4140,10 @@
         <v>2.4</v>
       </c>
       <c r="E93" s="27" t="s">
+        <v>301</v>
+      </c>
+      <c r="F93" s="26" t="s">
         <v>303</v>
-      </c>
-      <c r="F93" s="26" t="s">
-        <v>305</v>
       </c>
       <c r="G93" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F93),0)&gt;0), MAX($G$1:G92)+1, ""))</f>
@@ -4171,7 +4165,7 @@
         <v>20</v>
       </c>
       <c r="D94" s="32" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E94" s="33" t="s">
         <v>61</v>
@@ -4193,7 +4187,7 @@
         <v>20</v>
       </c>
       <c r="B95" s="39" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C95" s="40">
         <v>20</v>
@@ -4202,10 +4196,10 @@
         <v>3.2</v>
       </c>
       <c r="E95" s="39" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F95" s="38" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G95" s="29"/>
       <c r="H95" s="21" t="b">
@@ -4224,7 +4218,7 @@
         <v>20</v>
       </c>
       <c r="D96" s="32" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E96" s="33" t="s">
         <v>8</v>
@@ -4246,7 +4240,7 @@
         <v>20</v>
       </c>
       <c r="B97" s="33" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C97" s="34">
         <v>20</v>
@@ -4258,7 +4252,7 @@
         <v>8</v>
       </c>
       <c r="F97" s="32" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G97" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F97),0)&gt;0), MAX($G$1:G96)+1, ""))</f>
@@ -4280,10 +4274,10 @@
         <v>20</v>
       </c>
       <c r="D98" s="32" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E98" s="33" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F98" s="32" t="s">
         <v>102</v>
@@ -4302,7 +4296,7 @@
         <v>20</v>
       </c>
       <c r="B99" s="27" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C99" s="28">
         <v>20</v>
@@ -4311,10 +4305,10 @@
         <v>2.4</v>
       </c>
       <c r="E99" s="27" t="s">
+        <v>301</v>
+      </c>
+      <c r="F99" s="26" t="s">
         <v>303</v>
-      </c>
-      <c r="F99" s="26" t="s">
-        <v>305</v>
       </c>
       <c r="G99" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F99),0)&gt;0), MAX($G$1:G98)+1, ""))</f>
@@ -4336,7 +4330,7 @@
         <v>20</v>
       </c>
       <c r="D100" s="32" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E100" s="33" t="s">
         <v>8</v>
@@ -4364,7 +4358,7 @@
         <v>20</v>
       </c>
       <c r="D101" s="32" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E101" s="33" t="s">
         <v>8</v>
@@ -4392,7 +4386,7 @@
         <v>20</v>
       </c>
       <c r="D102" s="32" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E102" s="33" t="s">
         <v>8</v>
@@ -4414,7 +4408,7 @@
         <v>20</v>
       </c>
       <c r="B103" s="33" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C103" s="34">
         <v>20</v>
@@ -4423,7 +4417,7 @@
         <v>1.8</v>
       </c>
       <c r="E103" s="33" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F103" s="32" t="s">
         <v>92</v>
@@ -4448,7 +4442,7 @@
         <v>20</v>
       </c>
       <c r="D104" s="32" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E104" s="33" t="s">
         <v>8</v>
@@ -4476,7 +4470,7 @@
         <v>20</v>
       </c>
       <c r="D105" s="32" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E105" s="33" t="s">
         <v>8</v>
@@ -4504,7 +4498,7 @@
         <v>20</v>
       </c>
       <c r="D106" s="32" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E106" s="33" t="s">
         <v>83</v>
@@ -4532,7 +4526,7 @@
         <v>20</v>
       </c>
       <c r="D107" s="32" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E107" s="33" t="s">
         <v>8</v>
@@ -4560,7 +4554,7 @@
         <v>20</v>
       </c>
       <c r="D108" s="32" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E108" s="33" t="s">
         <v>8</v>
@@ -4582,19 +4576,19 @@
         <v>25</v>
       </c>
       <c r="B109" s="27" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C109" s="28">
         <v>25</v>
       </c>
       <c r="D109" s="26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E109" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F109" s="26" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G109" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F109),0)&gt;0), MAX($G$1:G108)+1, ""))</f>
@@ -4610,19 +4604,19 @@
         <v>25</v>
       </c>
       <c r="B110" s="27" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C110" s="28">
         <v>25</v>
       </c>
       <c r="D110" s="26" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E110" s="27" t="s">
         <v>133</v>
       </c>
       <c r="F110" s="26" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G110" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F110),0)&gt;0), MAX($G$1:G109)+1, ""))</f>
@@ -4638,19 +4632,19 @@
         <v>25</v>
       </c>
       <c r="B111" s="27" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C111" s="28">
         <v>25</v>
       </c>
       <c r="D111" s="26" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E111" s="27" t="s">
         <v>133</v>
       </c>
       <c r="F111" s="26" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G111" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F111),0)&gt;0), MAX($G$1:G110)+1, ""))</f>
@@ -4666,19 +4660,19 @@
         <v>25</v>
       </c>
       <c r="B112" s="27" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C112" s="28">
         <v>25</v>
       </c>
       <c r="D112" s="26" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E112" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F112" s="26" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G112" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F112),0)&gt;0), MAX($G$1:G111)+1, ""))</f>
@@ -4699,14 +4693,14 @@
       <c r="C113" s="28">
         <v>25</v>
       </c>
-      <c r="D113" s="26" t="s">
-        <v>240</v>
+      <c r="D113" s="26">
+        <v>2.7</v>
       </c>
       <c r="E113" s="27" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="F113" s="26" t="s">
-        <v>175</v>
+        <v>340</v>
       </c>
       <c r="G113" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F113),0)&gt;0), MAX($G$1:G112)+1, ""))</f>
@@ -4722,16 +4716,16 @@
         <v>25</v>
       </c>
       <c r="B114" s="33" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C114" s="34">
         <v>25</v>
       </c>
       <c r="D114" s="32" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E114" s="33" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F114" s="32" t="s">
         <v>104</v>
@@ -4750,16 +4744,16 @@
         <v>25</v>
       </c>
       <c r="B115" s="33" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C115" s="34">
         <v>25</v>
       </c>
       <c r="D115" s="32" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E115" s="33" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F115" s="32" t="s">
         <v>104</v>
@@ -4784,7 +4778,7 @@
         <v>25</v>
       </c>
       <c r="D116" s="26" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E116" s="27" t="s">
         <v>133</v>
@@ -4812,7 +4806,7 @@
         <v>25</v>
       </c>
       <c r="D117" s="26" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E117" s="27" t="s">
         <v>8</v>
@@ -4834,13 +4828,13 @@
         <v>25</v>
       </c>
       <c r="B118" s="33" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C118" s="34">
         <v>25</v>
       </c>
       <c r="D118" s="32" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E118" s="33" t="s">
         <v>8</v>
@@ -4868,7 +4862,7 @@
         <v>25</v>
       </c>
       <c r="D119" s="26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E119" s="27" t="s">
         <v>133</v>
@@ -4896,7 +4890,7 @@
         <v>25</v>
       </c>
       <c r="D120" s="26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E120" s="27" t="s">
         <v>133</v>
@@ -4924,7 +4918,7 @@
         <v>25</v>
       </c>
       <c r="D121" s="26" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E121" s="27" t="s">
         <v>83</v>
@@ -4952,7 +4946,7 @@
         <v>25</v>
       </c>
       <c r="D122" s="26" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E122" s="27" t="s">
         <v>83</v>
@@ -4980,7 +4974,7 @@
         <v>25</v>
       </c>
       <c r="D123" s="26" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E123" s="27" t="s">
         <v>83</v>
@@ -5002,7 +4996,7 @@
         <v>25</v>
       </c>
       <c r="B124" s="27" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C124" s="28">
         <v>25</v>
@@ -5011,10 +5005,10 @@
         <v>3.9</v>
       </c>
       <c r="E124" s="27" t="s">
+        <v>311</v>
+      </c>
+      <c r="F124" s="26" t="s">
         <v>313</v>
-      </c>
-      <c r="F124" s="26" t="s">
-        <v>315</v>
       </c>
       <c r="G124" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F124),0)&gt;0), MAX($G$1:G122)+1, ""))</f>
@@ -5036,7 +5030,7 @@
         <v>25</v>
       </c>
       <c r="D125" s="26" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E125" s="27" t="s">
         <v>83</v>
@@ -5064,7 +5058,7 @@
         <v>25</v>
       </c>
       <c r="D126" s="26" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E126" s="27" t="s">
         <v>8</v>
@@ -5092,7 +5086,7 @@
         <v>25</v>
       </c>
       <c r="D127" s="26" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E127" s="27" t="s">
         <v>133</v>
@@ -5114,19 +5108,19 @@
         <v>25</v>
       </c>
       <c r="B128" s="27" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C128" s="28">
         <v>25</v>
       </c>
       <c r="D128" s="41" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E128" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F128" s="26" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G128" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F128),0)&gt;0), MAX($G$1:G127)+1, ""))</f>
@@ -5148,7 +5142,7 @@
         <v>25</v>
       </c>
       <c r="D129" s="26" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E129" s="27" t="s">
         <v>133</v>
@@ -5170,16 +5164,16 @@
         <v>25</v>
       </c>
       <c r="B130" s="33" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C130" s="34">
         <v>25</v>
       </c>
       <c r="D130" s="32" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E130" s="33" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F130" s="32" t="s">
         <v>104</v>
@@ -5198,16 +5192,16 @@
         <v>25</v>
       </c>
       <c r="B131" s="33" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C131" s="34">
         <v>25</v>
       </c>
       <c r="D131" s="32" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E131" s="33" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F131" s="32" t="s">
         <v>104</v>
@@ -5226,16 +5220,16 @@
         <v>25</v>
       </c>
       <c r="B132" s="33" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C132" s="34">
         <v>25</v>
       </c>
       <c r="D132" s="32" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E132" s="33" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F132" s="32" t="s">
         <v>104</v>
@@ -5254,7 +5248,7 @@
         <v>25</v>
       </c>
       <c r="B133" s="27" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C133" s="28">
         <v>25</v>
@@ -5266,7 +5260,7 @@
         <v>133</v>
       </c>
       <c r="F133" s="26" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G133" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F133),0)&gt;0), MAX($G$1:G132)+1, ""))</f>
@@ -5282,16 +5276,16 @@
         <v>25</v>
       </c>
       <c r="B134" s="33" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C134" s="34">
         <v>25</v>
       </c>
       <c r="D134" s="32" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E134" s="33" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F134" s="32" t="s">
         <v>104</v>
@@ -5316,7 +5310,7 @@
         <v>25</v>
       </c>
       <c r="D135" s="26" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E135" s="27" t="s">
         <v>83</v>
@@ -5338,19 +5332,19 @@
         <v>30</v>
       </c>
       <c r="B136" s="33" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C136" s="34">
         <v>30</v>
       </c>
       <c r="D136" s="32" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E136" s="33" t="s">
         <v>133</v>
       </c>
       <c r="F136" s="32" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G136" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F136),0)&gt;0), MAX($G$1:G135)+1, ""))</f>
@@ -5366,19 +5360,19 @@
         <v>30</v>
       </c>
       <c r="B137" s="33" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C137" s="34">
         <v>30</v>
       </c>
       <c r="D137" s="32" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E137" s="33" t="s">
         <v>133</v>
       </c>
       <c r="F137" s="32" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G137" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F137),0)&gt;0), MAX($G$1:G136)+1, ""))</f>
@@ -5394,19 +5388,19 @@
         <v>30</v>
       </c>
       <c r="B138" s="33" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C138" s="34">
         <v>30</v>
       </c>
       <c r="D138" s="32" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E138" s="33" t="s">
         <v>133</v>
       </c>
       <c r="F138" s="32" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G138" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F138),0)&gt;0), MAX($G$1:G137)+1, ""))</f>
@@ -5422,19 +5416,19 @@
         <v>30</v>
       </c>
       <c r="B139" s="33" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C139" s="34">
         <v>30</v>
       </c>
       <c r="D139" s="32" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E139" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F139" s="32" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G139" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F139),0)&gt;0), MAX($G$1:G138)+1, ""))</f>
@@ -5450,19 +5444,19 @@
         <v>30</v>
       </c>
       <c r="B140" s="33" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C140" s="34">
         <v>30</v>
       </c>
       <c r="D140" s="32" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E140" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F140" s="32" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G140" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F140),0)&gt;0), MAX($G$1:G139)+1, ""))</f>
@@ -5478,19 +5472,19 @@
         <v>30</v>
       </c>
       <c r="B141" s="33" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C141" s="34">
         <v>30</v>
       </c>
       <c r="D141" s="32" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E141" s="33" t="s">
         <v>83</v>
       </c>
       <c r="F141" s="32" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G141" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F141),0)&gt;0), MAX($G$1:G140)+1, ""))</f>
@@ -5506,19 +5500,19 @@
         <v>30</v>
       </c>
       <c r="B142" s="33" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C142" s="34">
         <v>30</v>
       </c>
       <c r="D142" s="32" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E142" s="33" t="s">
         <v>133</v>
       </c>
       <c r="F142" s="32" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G142" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F142),0)&gt;0), MAX($G$1:G141)+1, ""))</f>
@@ -5534,7 +5528,7 @@
         <v>30</v>
       </c>
       <c r="B143" s="33" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C143" s="34">
         <v>30</v>
@@ -5546,7 +5540,7 @@
         <v>83</v>
       </c>
       <c r="F143" s="32" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G143" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F143),0)&gt;0), MAX($G$1:G142)+1, ""))</f>
@@ -5562,19 +5556,19 @@
         <v>30</v>
       </c>
       <c r="B144" s="33" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C144" s="34">
         <v>30</v>
       </c>
       <c r="D144" s="32" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E144" s="33" t="s">
         <v>133</v>
       </c>
       <c r="F144" s="32" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G144" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F144),0)&gt;0), MAX($G$1:G142)+1, ""))</f>
@@ -5590,19 +5584,19 @@
         <v>40</v>
       </c>
       <c r="B145" s="27" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C145" s="28">
         <v>40</v>
       </c>
       <c r="D145" s="26" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E145" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="F145" s="26" t="s">
         <v>201</v>
-      </c>
-      <c r="F145" s="26" t="s">
-        <v>202</v>
       </c>
       <c r="G145" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B145),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E145),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F145),0)&gt;0), MAX($G$1:G144)+1, ""))</f>
@@ -5618,19 +5612,19 @@
         <v>40</v>
       </c>
       <c r="B146" s="27" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C146" s="28">
         <v>40</v>
       </c>
       <c r="D146" s="26" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E146" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="F146" s="26" t="s">
         <v>198</v>
-      </c>
-      <c r="F146" s="26" t="s">
-        <v>199</v>
       </c>
       <c r="G146" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F146),0)&gt;0), MAX($G$1:G145)+1, ""))</f>
@@ -5646,7 +5640,7 @@
         <v>40</v>
       </c>
       <c r="B147" s="27" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C147" s="28">
         <v>40</v>
@@ -5655,10 +5649,10 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="E147" s="27" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F147" s="26" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G147" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F147),0)&gt;0), MAX($G$1:G146)+1, ""))</f>
@@ -5674,7 +5668,7 @@
         <v>45</v>
       </c>
       <c r="B148" s="27" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C148" s="28">
         <v>45</v>
@@ -5683,10 +5677,10 @@
         <v>10.199999999999999</v>
       </c>
       <c r="E148" s="27" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F148" s="26" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G148" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F148),0)&gt;0), MAX($G$1:G147)+1, ""))</f>
@@ -11060,7 +11054,7 @@
   <sheetData>
     <row r="1" spans="1:6" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="19" t="str">
@@ -11073,7 +11067,7 @@
     </row>
     <row r="2" spans="1:6" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="17"/>

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="356">
   <si>
     <t>Grupo</t>
   </si>
@@ -1048,13 +1048,58 @@
   </si>
   <si>
     <t>21775-370</t>
+  </si>
+  <si>
+    <t>MURUNDU</t>
+  </si>
+  <si>
+    <t>DEMETRIO TOURINHO</t>
+  </si>
+  <si>
+    <t>SANTO INACIO</t>
+  </si>
+  <si>
+    <t>PROFESSOR HELIO VIANA</t>
+  </si>
+  <si>
+    <t>21775-190</t>
+  </si>
+  <si>
+    <t>21715-410</t>
+  </si>
+  <si>
+    <t>COSTA RUBIM</t>
+  </si>
+  <si>
+    <t>21710-000</t>
+  </si>
+  <si>
+    <t>21775-120</t>
+  </si>
+  <si>
+    <t>21760-240</t>
+  </si>
+  <si>
+    <t>21765-080</t>
+  </si>
+  <si>
+    <t>FREDERICO FAULHABER APÓS PIRPIRITUBA</t>
+  </si>
+  <si>
+    <t>FREDERICO FAULHABER ANTES PIRPIRITUBA</t>
+  </si>
+  <si>
+    <t>Piraquara</t>
+  </si>
+  <si>
+    <t>21760-001</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1114,13 +1159,6 @@
       <color theme="4" tint="-0.499984740745262"/>
       <name val="Courier New"/>
       <family val="3"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="4" tint="-0.499984740745262"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1200,7 +1238,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1301,10 +1339,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1312,18 +1346,18 @@
     <xf numFmtId="2" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1576,7 +1610,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H1035"/>
+  <dimension ref="A1:H1036"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.453125" customWidth="1"/>
@@ -1611,22 +1645,22 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="32">
+      <c r="A2" s="30">
         <v>13</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="C2" s="34">
+      <c r="C2" s="32">
         <v>13</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="33" t="s">
+      <c r="E2" s="31" t="s">
         <v>272</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="30" t="s">
         <v>26</v>
       </c>
       <c r="G2" s="29" t="str">
@@ -1639,22 +1673,22 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="32">
+      <c r="A3" s="30">
         <v>13</v>
       </c>
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="34">
+      <c r="C3" s="32">
         <v>13</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="E3" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="32" t="s">
+      <c r="F3" s="30" t="s">
         <v>29</v>
       </c>
       <c r="G3" s="29" t="str">
@@ -1667,22 +1701,22 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="32">
+      <c r="A4" s="30">
         <v>13</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="C4" s="34">
+      <c r="C4" s="32">
         <v>13</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="E4" s="31" t="s">
         <v>272</v>
       </c>
-      <c r="F4" s="32" t="s">
+      <c r="F4" s="30" t="s">
         <v>26</v>
       </c>
       <c r="G4" s="29" t="str">
@@ -1695,22 +1729,22 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="32">
+      <c r="A5" s="30">
         <v>13</v>
       </c>
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="31" t="s">
         <v>278</v>
       </c>
-      <c r="C5" s="34">
+      <c r="C5" s="32">
         <v>13</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="E5" s="31" t="s">
         <v>272</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="F5" s="30" t="s">
         <v>26</v>
       </c>
       <c r="G5" s="29" t="str">
@@ -1723,22 +1757,22 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="32">
+      <c r="A6" s="30">
         <v>13</v>
       </c>
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="34">
+      <c r="C6" s="32">
         <v>13</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="33" t="s">
+      <c r="E6" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="32" t="s">
+      <c r="F6" s="30" t="s">
         <v>26</v>
       </c>
       <c r="G6" s="29" t="str">
@@ -1751,22 +1785,22 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="32">
+      <c r="A7" s="30">
         <v>13</v>
       </c>
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="C7" s="34">
+      <c r="C7" s="32">
         <v>13</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="D7" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="33" t="s">
+      <c r="E7" s="31" t="s">
         <v>272</v>
       </c>
-      <c r="F7" s="32" t="s">
+      <c r="F7" s="30" t="s">
         <v>26</v>
       </c>
       <c r="G7" s="29" t="str">
@@ -1779,22 +1813,22 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="32">
+      <c r="A8" s="30">
         <v>13</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="31" t="s">
         <v>281</v>
       </c>
-      <c r="C8" s="34">
+      <c r="C8" s="32">
         <v>13</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="33" t="s">
+      <c r="E8" s="31" t="s">
         <v>272</v>
       </c>
-      <c r="F8" s="32" t="s">
+      <c r="F8" s="30" t="s">
         <v>26</v>
       </c>
       <c r="G8" s="29" t="str">
@@ -1807,22 +1841,22 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="32">
+      <c r="A9" s="30">
         <v>13</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="32">
         <v>13</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="D9" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="E9" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="32" t="s">
+      <c r="F9" s="30" t="s">
         <v>23</v>
       </c>
       <c r="G9" s="29" t="str">
@@ -1835,22 +1869,22 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="32">
+      <c r="A10" s="30">
         <v>13</v>
       </c>
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="31" t="s">
         <v>271</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="32">
         <v>13</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="33" t="s">
+      <c r="E10" s="31" t="s">
         <v>272</v>
       </c>
-      <c r="F10" s="32" t="s">
+      <c r="F10" s="30" t="s">
         <v>26</v>
       </c>
       <c r="G10" s="29" t="str">
@@ -1863,22 +1897,22 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="32">
+      <c r="A11" s="30">
         <v>13</v>
       </c>
-      <c r="B11" s="33" t="s">
+      <c r="B11" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="34">
+      <c r="C11" s="32">
         <v>13</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D11" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="E11" s="33" t="s">
+      <c r="E11" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="32" t="s">
+      <c r="F11" s="30" t="s">
         <v>20</v>
       </c>
       <c r="G11" s="29" t="str">
@@ -1891,22 +1925,22 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="32">
+      <c r="A12" s="30">
         <v>13</v>
       </c>
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="31" t="s">
         <v>274</v>
       </c>
-      <c r="C12" s="34">
+      <c r="C12" s="32">
         <v>13</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="33" t="s">
+      <c r="E12" s="31" t="s">
         <v>272</v>
       </c>
-      <c r="F12" s="32" t="s">
+      <c r="F12" s="30" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="29" t="str">
@@ -1919,22 +1953,22 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="32">
+      <c r="A13" s="30">
         <v>13</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="34">
+      <c r="C13" s="32">
         <v>13</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="D13" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="33" t="s">
+      <c r="E13" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="32" t="s">
+      <c r="F13" s="30" t="s">
         <v>18</v>
       </c>
       <c r="G13" s="29" t="str">
@@ -1947,22 +1981,22 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="32">
+      <c r="A14" s="30">
         <v>13</v>
       </c>
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="31" t="s">
         <v>273</v>
       </c>
-      <c r="C14" s="34">
+      <c r="C14" s="32">
         <v>13</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="33" t="s">
+      <c r="E14" s="31" t="s">
         <v>272</v>
       </c>
-      <c r="F14" s="32" t="s">
+      <c r="F14" s="30" t="s">
         <v>26</v>
       </c>
       <c r="G14" s="29" t="str">
@@ -1975,22 +2009,22 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="32">
+      <c r="A15" s="30">
         <v>13</v>
       </c>
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="32">
         <v>13</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="33" t="s">
+      <c r="E15" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="32" t="s">
+      <c r="F15" s="30" t="s">
         <v>15</v>
       </c>
       <c r="G15" s="29" t="str">
@@ -2003,22 +2037,22 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="32">
+      <c r="A16" s="30">
         <v>13</v>
       </c>
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="32">
         <v>13</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="33" t="s">
+      <c r="E16" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="32" t="s">
+      <c r="F16" s="30" t="s">
         <v>12</v>
       </c>
       <c r="G16" s="29" t="str">
@@ -2031,22 +2065,22 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="32">
+      <c r="A17" s="30">
         <v>13</v>
       </c>
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="34">
+      <c r="C17" s="32">
         <v>13</v>
       </c>
-      <c r="D17" s="32" t="s">
+      <c r="D17" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="33" t="s">
+      <c r="E17" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="32" t="s">
+      <c r="F17" s="30" t="s">
         <v>9</v>
       </c>
       <c r="G17" s="29" t="str">
@@ -2231,19 +2265,19 @@
         <v>15</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>261</v>
+        <v>347</v>
       </c>
       <c r="C24" s="28">
         <v>15</v>
       </c>
-      <c r="D24" s="26" t="s">
-        <v>7</v>
+      <c r="D24" s="26">
+        <v>2.5</v>
       </c>
       <c r="E24" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>263</v>
+        <v>348</v>
       </c>
       <c r="G24" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B24),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E24),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F24),0)&gt;0), MAX($G$1:G23)+1, ""))</f>
@@ -2259,19 +2293,19 @@
         <v>15</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>58</v>
+        <v>261</v>
       </c>
       <c r="C25" s="28">
         <v>15</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>225</v>
+        <v>7</v>
       </c>
       <c r="E25" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>59</v>
+        <v>263</v>
       </c>
       <c r="G25" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B25),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E25),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F25),0)&gt;0), MAX($G$1:G24)+1, ""))</f>
@@ -2287,19 +2321,19 @@
         <v>15</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>270</v>
+        <v>353</v>
       </c>
       <c r="C26" s="28">
         <v>15</v>
       </c>
-      <c r="D26" s="26" t="s">
-        <v>207</v>
+      <c r="D26" s="26">
+        <v>2</v>
       </c>
       <c r="E26" s="27" t="s">
-        <v>8</v>
+        <v>354</v>
       </c>
       <c r="F26" s="26" t="s">
-        <v>57</v>
+        <v>350</v>
       </c>
       <c r="G26" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B26),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E26),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F26),0)&gt;0), MAX($G$1:G25)+1, ""))</f>
@@ -2315,19 +2349,19 @@
         <v>15</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>308</v>
+        <v>58</v>
       </c>
       <c r="C27" s="28">
         <v>15</v>
       </c>
-      <c r="D27" s="26">
-        <v>2.1</v>
+      <c r="D27" s="26" t="s">
+        <v>225</v>
       </c>
       <c r="E27" s="27" t="s">
-        <v>297</v>
+        <v>8</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>309</v>
+        <v>59</v>
       </c>
       <c r="G27" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B27),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E27),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F27),0)&gt;0), MAX($G$1:G26)+1, ""))</f>
@@ -2343,19 +2377,19 @@
         <v>15</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>55</v>
+        <v>270</v>
       </c>
       <c r="C28" s="28">
         <v>15</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E28" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G28" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B28),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E28),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F28),0)&gt;0), MAX($G$1:G27)+1, ""))</f>
@@ -2371,19 +2405,19 @@
         <v>15</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>279</v>
+        <v>308</v>
       </c>
       <c r="C29" s="28">
         <v>15</v>
       </c>
-      <c r="D29" s="26" t="s">
-        <v>212</v>
+      <c r="D29" s="26">
+        <v>2.1</v>
       </c>
       <c r="E29" s="27" t="s">
-        <v>8</v>
+        <v>297</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>77</v>
+        <v>309</v>
       </c>
       <c r="G29" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B29),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E29),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F29),0)&gt;0), MAX($G$1:G28)+1, ""))</f>
@@ -2399,19 +2433,19 @@
         <v>15</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>262</v>
+        <v>55</v>
       </c>
       <c r="C30" s="28">
         <v>15</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>22</v>
+        <v>206</v>
       </c>
       <c r="E30" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>264</v>
+        <v>56</v>
       </c>
       <c r="G30" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B30),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E30),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F30),0)&gt;0), MAX($G$1:G29)+1, ""))</f>
@@ -2427,19 +2461,19 @@
         <v>15</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="C31" s="28">
         <v>15</v>
       </c>
-      <c r="D31" s="26">
-        <v>2.2000000000000002</v>
+      <c r="D31" s="26" t="s">
+        <v>212</v>
       </c>
       <c r="E31" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F31" s="26" t="s">
-        <v>295</v>
+        <v>77</v>
       </c>
       <c r="G31" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B31),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E31),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F31),0)&gt;0), MAX($G$1:G30)+1, ""))</f>
@@ -2455,19 +2489,19 @@
         <v>15</v>
       </c>
       <c r="B32" s="27" t="s">
-        <v>51</v>
+        <v>262</v>
       </c>
       <c r="C32" s="28">
         <v>15</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>215</v>
+        <v>22</v>
       </c>
       <c r="E32" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F32" s="26" t="s">
-        <v>52</v>
+        <v>264</v>
       </c>
       <c r="G32" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B32),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E32),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F32),0)&gt;0), MAX($G$1:G31)+1, ""))</f>
@@ -2483,19 +2517,19 @@
         <v>15</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>47</v>
+        <v>294</v>
       </c>
       <c r="C33" s="28">
         <v>15</v>
       </c>
-      <c r="D33" s="26" t="s">
-        <v>235</v>
+      <c r="D33" s="26">
+        <v>2.2000000000000002</v>
       </c>
       <c r="E33" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F33" s="26" t="s">
-        <v>48</v>
+        <v>295</v>
       </c>
       <c r="G33" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B33),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E33),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F33),0)&gt;0), MAX($G$1:G32)+1, ""))</f>
@@ -2511,19 +2545,19 @@
         <v>15</v>
       </c>
       <c r="B34" s="27" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C34" s="28">
         <v>15</v>
       </c>
       <c r="D34" s="26" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="E34" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F34" s="26" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G34" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B34),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E34),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F34),0)&gt;0), MAX($G$1:G33)+1, ""))</f>
@@ -2539,19 +2573,19 @@
         <v>15</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C35" s="28">
         <v>15</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>208</v>
+        <v>235</v>
       </c>
       <c r="E35" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G35" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F35),0)&gt;0), MAX($G$1:G34)+1, ""))</f>
@@ -2567,19 +2601,19 @@
         <v>15</v>
       </c>
       <c r="B36" s="27" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C36" s="28">
         <v>15</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="E36" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F36" s="26" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G36" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B36),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E36),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F36),0)&gt;0), MAX($G$1:G35)+1, ""))</f>
@@ -2595,19 +2629,19 @@
         <v>15</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>310</v>
+        <v>43</v>
       </c>
       <c r="C37" s="28">
         <v>15</v>
       </c>
-      <c r="D37" s="26">
-        <v>2.2000000000000002</v>
+      <c r="D37" s="26" t="s">
+        <v>208</v>
       </c>
       <c r="E37" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>295</v>
+        <v>44</v>
       </c>
       <c r="G37" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F37),0)&gt;0), MAX($G$1:G36)+1, ""))</f>
@@ -2623,19 +2657,19 @@
         <v>15</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>246</v>
+        <v>41</v>
       </c>
       <c r="C38" s="28">
         <v>15</v>
       </c>
-      <c r="D38" s="26">
-        <v>2.1</v>
+      <c r="D38" s="26" t="s">
+        <v>214</v>
       </c>
       <c r="E38" s="27" t="s">
-        <v>247</v>
+        <v>8</v>
       </c>
       <c r="F38" s="26" t="s">
-        <v>204</v>
+        <v>42</v>
       </c>
       <c r="G38" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F38),0)&gt;0), MAX($G$1:G37)+1, ""))</f>
@@ -2651,19 +2685,19 @@
         <v>15</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>39</v>
+        <v>310</v>
       </c>
       <c r="C39" s="28">
         <v>15</v>
       </c>
-      <c r="D39" s="26" t="s">
-        <v>213</v>
+      <c r="D39" s="26">
+        <v>2.2000000000000002</v>
       </c>
       <c r="E39" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F39" s="26" t="s">
-        <v>40</v>
+        <v>295</v>
       </c>
       <c r="G39" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B39),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E39),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F39),0)&gt;0), MAX($G$1:G38)+1, ""))</f>
@@ -2679,19 +2713,19 @@
         <v>15</v>
       </c>
       <c r="B40" s="27" t="s">
-        <v>35</v>
+        <v>246</v>
       </c>
       <c r="C40" s="28">
         <v>15</v>
       </c>
-      <c r="D40" s="26" t="s">
-        <v>212</v>
+      <c r="D40" s="26">
+        <v>2.1</v>
       </c>
       <c r="E40" s="27" t="s">
-        <v>8</v>
+        <v>247</v>
       </c>
       <c r="F40" s="26" t="s">
-        <v>36</v>
+        <v>204</v>
       </c>
       <c r="G40" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B40),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E40),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F40),0)&gt;0), MAX($G$1:G39)+1, ""))</f>
@@ -2707,19 +2741,19 @@
         <v>15</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>282</v>
+        <v>39</v>
       </c>
       <c r="C41" s="28">
         <v>15</v>
       </c>
       <c r="D41" s="26" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E41" s="27" t="s">
-        <v>269</v>
+        <v>8</v>
       </c>
       <c r="F41" s="26" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G41" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B41),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E41),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F41),0)&gt;0), MAX($G$1:G40)+1, ""))</f>
@@ -2731,23 +2765,23 @@
       </c>
     </row>
     <row r="42" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A42" s="35">
-        <v>17</v>
-      </c>
-      <c r="B42" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="C42" s="37">
-        <v>17</v>
-      </c>
-      <c r="D42" s="35" t="s">
-        <v>216</v>
-      </c>
-      <c r="E42" s="36" t="s">
+      <c r="A42" s="26">
+        <v>15</v>
+      </c>
+      <c r="B42" s="27" t="s">
+        <v>343</v>
+      </c>
+      <c r="C42" s="28">
+        <v>15</v>
+      </c>
+      <c r="D42" s="26">
+        <v>1.4</v>
+      </c>
+      <c r="E42" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F42" s="35" t="s">
-        <v>73</v>
+      <c r="F42" s="26" t="s">
+        <v>349</v>
       </c>
       <c r="G42" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B42),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E42),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F42),0)&gt;0), MAX($G$1:G41)+1, ""))</f>
@@ -2759,23 +2793,23 @@
       </c>
     </row>
     <row r="43" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A43" s="35">
-        <v>17</v>
-      </c>
-      <c r="B43" s="36" t="s">
-        <v>283</v>
-      </c>
-      <c r="C43" s="37">
-        <v>17</v>
-      </c>
-      <c r="D43" s="35" t="s">
-        <v>224</v>
-      </c>
-      <c r="E43" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="F43" s="35" t="s">
-        <v>69</v>
+      <c r="A43" s="26">
+        <v>15</v>
+      </c>
+      <c r="B43" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C43" s="28">
+        <v>15</v>
+      </c>
+      <c r="D43" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="E43" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="26" t="s">
+        <v>36</v>
       </c>
       <c r="G43" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F43),0)&gt;0), MAX($G$1:G42)+1, ""))</f>
@@ -2788,47 +2822,50 @@
     </row>
     <row r="44" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A44" s="26">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B44" s="27" t="s">
-        <v>315</v>
+        <v>282</v>
       </c>
       <c r="C44" s="28">
-        <v>17</v>
-      </c>
-      <c r="D44" s="26">
-        <v>1.7</v>
+        <v>15</v>
+      </c>
+      <c r="D44" s="26" t="s">
+        <v>211</v>
       </c>
       <c r="E44" s="27" t="s">
-        <v>61</v>
+        <v>269</v>
       </c>
       <c r="F44" s="26" t="s">
-        <v>321</v>
-      </c>
-      <c r="G44" s="29"/>
+        <v>34</v>
+      </c>
+      <c r="G44" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F44),0)&gt;0), MAX($G$1:G43)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H44" s="21" t="b">
         <f>A44=C44</f>
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A45" s="35">
+      <c r="A45" s="33">
         <v>17</v>
       </c>
-      <c r="B45" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="C45" s="37">
+      <c r="B45" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="C45" s="35">
         <v>17</v>
       </c>
-      <c r="D45" s="35" t="s">
-        <v>217</v>
-      </c>
-      <c r="E45" s="36" t="s">
+      <c r="D45" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="E45" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F45" s="35" t="s">
-        <v>64</v>
+      <c r="F45" s="33" t="s">
+        <v>73</v>
       </c>
       <c r="G45" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F45),0)&gt;0), MAX($G$1:G44)+1, ""))</f>
@@ -2840,23 +2877,23 @@
       </c>
     </row>
     <row r="46" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A46" s="35">
+      <c r="A46" s="33">
         <v>17</v>
       </c>
-      <c r="B46" s="36" t="s">
-        <v>60</v>
-      </c>
-      <c r="C46" s="37">
+      <c r="B46" s="34" t="s">
+        <v>283</v>
+      </c>
+      <c r="C46" s="35">
         <v>17</v>
       </c>
-      <c r="D46" s="35" t="s">
-        <v>218</v>
-      </c>
-      <c r="E46" s="36" t="s">
+      <c r="D46" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="E46" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="F46" s="35" t="s">
-        <v>62</v>
+      <c r="F46" s="33" t="s">
+        <v>69</v>
       </c>
       <c r="G46" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F46),0)&gt;0), MAX($G$1:G45)+1, ""))</f>
@@ -2872,19 +2909,19 @@
         <v>17</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C47" s="28">
         <v>17</v>
       </c>
       <c r="D47" s="26">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="E47" s="27" t="s">
         <v>61</v>
       </c>
       <c r="F47" s="26" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G47" s="29"/>
       <c r="H47" s="21" t="b">
@@ -2893,48 +2930,51 @@
       </c>
     </row>
     <row r="48" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A48" s="26">
+      <c r="A48" s="33">
         <v>17</v>
       </c>
-      <c r="B48" s="27" t="s">
-        <v>318</v>
-      </c>
-      <c r="C48" s="28">
+      <c r="B48" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="C48" s="35">
         <v>17</v>
       </c>
-      <c r="D48" s="26">
-        <v>1.9</v>
-      </c>
-      <c r="E48" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="F48" s="26" t="s">
-        <v>324</v>
-      </c>
-      <c r="G48" s="29"/>
+      <c r="D48" s="33" t="s">
+        <v>217</v>
+      </c>
+      <c r="E48" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="G48" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F48),0)&gt;0), MAX($G$1:G47)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H48" s="21" t="b">
         <f>A48=C48</f>
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="38">
+      <c r="A49" s="33">
         <v>17</v>
       </c>
-      <c r="B49" s="39" t="s">
-        <v>291</v>
-      </c>
-      <c r="C49" s="40">
+      <c r="B49" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="C49" s="35">
         <v>17</v>
       </c>
-      <c r="D49" s="38" t="s">
-        <v>221</v>
-      </c>
-      <c r="E49" s="39" t="s">
+      <c r="D49" s="33" t="s">
+        <v>218</v>
+      </c>
+      <c r="E49" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="F49" s="38" t="s">
-        <v>113</v>
+      <c r="F49" s="33" t="s">
+        <v>62</v>
       </c>
       <c r="G49" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F49),0)&gt;0), MAX($G$1:G48)+1, ""))</f>
@@ -2950,19 +2990,19 @@
         <v>17</v>
       </c>
       <c r="B50" s="27" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C50" s="28">
         <v>17</v>
       </c>
       <c r="D50" s="26">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E50" s="27" t="s">
         <v>61</v>
       </c>
       <c r="F50" s="26" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G50" s="29"/>
       <c r="H50" s="21" t="b">
@@ -2975,72 +3015,72 @@
         <v>17</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>319</v>
+        <v>342</v>
       </c>
       <c r="C51" s="28">
         <v>17</v>
       </c>
       <c r="D51" s="26">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="E51" s="27" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="F51" s="26" t="s">
-        <v>325</v>
-      </c>
-      <c r="G51" s="29"/>
+        <v>351</v>
+      </c>
+      <c r="G51" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F51),0)&gt;0), MAX($G$1:G49)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H51" s="21" t="b">
         <f>A51=C51</f>
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="38">
+      <c r="A52" s="26">
         <v>17</v>
       </c>
-      <c r="B52" s="39" t="s">
-        <v>108</v>
-      </c>
-      <c r="C52" s="40">
+      <c r="B52" s="27" t="s">
+        <v>318</v>
+      </c>
+      <c r="C52" s="28">
         <v>17</v>
       </c>
-      <c r="D52" s="38" t="s">
-        <v>222</v>
-      </c>
-      <c r="E52" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F52" s="38" t="s">
-        <v>109</v>
-      </c>
-      <c r="G52" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F52),0)&gt;0), MAX($G$1:G51)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D52" s="26">
+        <v>1.9</v>
+      </c>
+      <c r="E52" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="F52" s="26" t="s">
+        <v>324</v>
+      </c>
+      <c r="G52" s="29"/>
       <c r="H52" s="21" t="b">
         <f>A52=C52</f>
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="38">
+      <c r="A53" s="36">
         <v>17</v>
       </c>
-      <c r="B53" s="39" t="s">
-        <v>305</v>
-      </c>
-      <c r="C53" s="40">
+      <c r="B53" s="37" t="s">
+        <v>291</v>
+      </c>
+      <c r="C53" s="38">
         <v>17</v>
       </c>
-      <c r="D53" s="38" t="s">
-        <v>231</v>
-      </c>
-      <c r="E53" s="39" t="s">
-        <v>306</v>
-      </c>
-      <c r="F53" s="38" t="s">
-        <v>107</v>
+      <c r="D53" s="36" t="s">
+        <v>221</v>
+      </c>
+      <c r="E53" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="F53" s="36" t="s">
+        <v>113</v>
       </c>
       <c r="G53" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F53),0)&gt;0), MAX($G$1:G52)+1, ""))</f>
@@ -3052,79 +3092,73 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A54" s="35">
+      <c r="A54" s="26">
         <v>17</v>
       </c>
-      <c r="B54" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="C54" s="37">
+      <c r="B54" s="27" t="s">
+        <v>316</v>
+      </c>
+      <c r="C54" s="28">
         <v>17</v>
       </c>
-      <c r="D54" s="35" t="s">
-        <v>209</v>
-      </c>
-      <c r="E54" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F54" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="G54" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F54),0)&gt;0), MAX($G$1:G49)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D54" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E54" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="F54" s="26" t="s">
+        <v>322</v>
+      </c>
+      <c r="G54" s="29"/>
       <c r="H54" s="21" t="b">
         <f>A54=C54</f>
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="35">
+      <c r="A55" s="26">
         <v>17</v>
       </c>
-      <c r="B55" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="C55" s="37">
+      <c r="B55" s="27" t="s">
+        <v>319</v>
+      </c>
+      <c r="C55" s="28">
         <v>17</v>
       </c>
-      <c r="D55" s="35" t="s">
-        <v>213</v>
-      </c>
-      <c r="E55" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F55" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="G55" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F55),0)&gt;0), MAX($G$1:G54)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D55" s="26">
+        <v>2</v>
+      </c>
+      <c r="E55" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="F55" s="26" t="s">
+        <v>325</v>
+      </c>
+      <c r="G55" s="29"/>
       <c r="H55" s="21" t="b">
         <f>A55=C55</f>
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A56" s="38">
+      <c r="A56" s="36">
         <v>17</v>
       </c>
-      <c r="B56" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="C56" s="40">
+      <c r="B56" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="C56" s="38">
         <v>17</v>
       </c>
-      <c r="D56" s="38" t="s">
-        <v>221</v>
-      </c>
-      <c r="E56" s="39" t="s">
+      <c r="D56" s="36" t="s">
+        <v>222</v>
+      </c>
+      <c r="E56" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F56" s="38" t="s">
-        <v>100</v>
+      <c r="F56" s="36" t="s">
+        <v>109</v>
       </c>
       <c r="G56" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F56),0)&gt;0), MAX($G$1:G55)+1, ""))</f>
@@ -3136,23 +3170,23 @@
       </c>
     </row>
     <row r="57" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A57" s="38">
+      <c r="A57" s="36">
         <v>17</v>
       </c>
-      <c r="B57" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="C57" s="40">
+      <c r="B57" s="37" t="s">
+        <v>305</v>
+      </c>
+      <c r="C57" s="38">
         <v>17</v>
       </c>
-      <c r="D57" s="38" t="s">
-        <v>219</v>
-      </c>
-      <c r="E57" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" s="38" t="s">
-        <v>96</v>
+      <c r="D57" s="36" t="s">
+        <v>231</v>
+      </c>
+      <c r="E57" s="37" t="s">
+        <v>306</v>
+      </c>
+      <c r="F57" s="36" t="s">
+        <v>107</v>
       </c>
       <c r="G57" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F57),0)&gt;0), MAX($G$1:G56)+1, ""))</f>
@@ -3164,101 +3198,107 @@
       </c>
     </row>
     <row r="58" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A58" s="35">
+      <c r="A58" s="33">
         <v>17</v>
       </c>
-      <c r="B58" s="36" t="s">
-        <v>329</v>
-      </c>
-      <c r="C58" s="37">
+      <c r="B58" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="C58" s="35">
         <v>17</v>
       </c>
-      <c r="D58" s="35">
-        <v>1.9</v>
-      </c>
-      <c r="E58" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="F58" s="35" t="s">
-        <v>331</v>
-      </c>
-      <c r="G58" s="29" t="s">
-        <v>328</v>
+      <c r="D58" s="33" t="s">
+        <v>209</v>
+      </c>
+      <c r="E58" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="G58" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F58),0)&gt;0), MAX($G$1:G53)+1, ""))</f>
+        <v/>
       </c>
       <c r="H58" s="21" t="b">
+        <f>A58=C58</f>
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A59" s="35">
+      <c r="A59" s="33">
         <v>17</v>
       </c>
-      <c r="B59" s="36" t="s">
-        <v>327</v>
-      </c>
-      <c r="C59" s="37">
+      <c r="B59" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="C59" s="35">
         <v>17</v>
       </c>
-      <c r="D59" s="35">
-        <v>1.9</v>
-      </c>
-      <c r="E59" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="F59" s="35" t="s">
-        <v>331</v>
-      </c>
-      <c r="G59" s="29" t="s">
-        <v>328</v>
+      <c r="D59" s="33" t="s">
+        <v>213</v>
+      </c>
+      <c r="E59" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="G59" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F59),0)&gt;0), MAX($G$1:G58)+1, ""))</f>
+        <v/>
       </c>
       <c r="H59" s="21" t="b">
+        <f>A59=C59</f>
         <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A60" s="35">
+      <c r="A60" s="36">
         <v>17</v>
       </c>
-      <c r="B60" s="36" t="s">
-        <v>330</v>
-      </c>
-      <c r="C60" s="37">
+      <c r="B60" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="C60" s="38">
         <v>17</v>
       </c>
-      <c r="D60" s="35">
-        <v>1.9</v>
-      </c>
-      <c r="E60" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="F60" s="35" t="s">
-        <v>331</v>
-      </c>
-      <c r="G60" s="29" t="s">
-        <v>328</v>
+      <c r="D60" s="36" t="s">
+        <v>221</v>
+      </c>
+      <c r="E60" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F60" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="G60" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F60),0)&gt;0), MAX($G$1:G59)+1, ""))</f>
+        <v/>
       </c>
       <c r="H60" s="21" t="b">
+        <f>A60=C60</f>
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A61" s="35">
+      <c r="A61" s="36">
         <v>17</v>
       </c>
-      <c r="B61" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="C61" s="37">
+      <c r="B61" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="C61" s="38">
         <v>17</v>
       </c>
-      <c r="D61" s="35" t="s">
-        <v>216</v>
-      </c>
-      <c r="E61" s="36" t="s">
+      <c r="D61" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E61" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F61" s="35" t="s">
-        <v>38</v>
+      <c r="F61" s="36" t="s">
+        <v>96</v>
       </c>
       <c r="G61" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F61),0)&gt;0), MAX($G$1:G60)+1, ""))</f>
@@ -3270,79 +3310,75 @@
       </c>
     </row>
     <row r="62" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A62" s="38">
+      <c r="A62" s="33">
         <v>17</v>
       </c>
-      <c r="B62" s="39" t="s">
-        <v>85</v>
-      </c>
-      <c r="C62" s="40">
+      <c r="B62" s="34" t="s">
+        <v>329</v>
+      </c>
+      <c r="C62" s="35">
         <v>17</v>
       </c>
-      <c r="D62" s="38" t="s">
-        <v>221</v>
-      </c>
-      <c r="E62" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F62" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="G62" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F62),0)&gt;0), MAX($G$1:G61)+1, ""))</f>
-        <v/>
+      <c r="D62" s="33">
+        <v>1.9</v>
+      </c>
+      <c r="E62" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="F62" s="33" t="s">
+        <v>331</v>
+      </c>
+      <c r="G62" s="29" t="s">
+        <v>328</v>
       </c>
       <c r="H62" s="21" t="b">
-        <f>A62=C62</f>
         <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A63" s="35">
+      <c r="A63" s="33">
         <v>17</v>
       </c>
-      <c r="B63" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="C63" s="37">
+      <c r="B63" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="C63" s="35">
         <v>17</v>
       </c>
-      <c r="D63" s="35" t="s">
-        <v>210</v>
-      </c>
-      <c r="E63" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F63" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="G63" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F63),0)&gt;0), MAX($G$1:G62)+1, ""))</f>
-        <v/>
+      <c r="D63" s="33">
+        <v>1.9</v>
+      </c>
+      <c r="E63" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="F63" s="33" t="s">
+        <v>331</v>
+      </c>
+      <c r="G63" s="29" t="s">
+        <v>328</v>
       </c>
       <c r="H63" s="21" t="b">
-        <f>A63=C63</f>
         <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A64" s="35">
+      <c r="A64" s="33">
         <v>17</v>
       </c>
-      <c r="B64" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="C64" s="37">
+      <c r="B64" s="34" t="s">
+        <v>330</v>
+      </c>
+      <c r="C64" s="35">
         <v>17</v>
       </c>
-      <c r="D64" s="35" t="s">
-        <v>209</v>
-      </c>
-      <c r="E64" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F64" s="35" t="s">
-        <v>31</v>
+      <c r="D64" s="33">
+        <v>1.9</v>
+      </c>
+      <c r="E64" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="F64" s="33" t="s">
+        <v>331</v>
       </c>
       <c r="G64" s="29" t="s">
         <v>328</v>
@@ -3352,26 +3388,26 @@
       </c>
     </row>
     <row r="65" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A65" s="32">
-        <v>20</v>
-      </c>
-      <c r="B65" s="33" t="s">
-        <v>148</v>
-      </c>
-      <c r="C65" s="34">
-        <v>20</v>
-      </c>
-      <c r="D65" s="32" t="s">
-        <v>208</v>
-      </c>
-      <c r="E65" s="33" t="s">
+      <c r="A65" s="33">
+        <v>17</v>
+      </c>
+      <c r="B65" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="C65" s="35">
+        <v>17</v>
+      </c>
+      <c r="D65" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="E65" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F65" s="32" t="s">
-        <v>149</v>
+      <c r="F65" s="33" t="s">
+        <v>38</v>
       </c>
       <c r="G65" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F65),0)&gt;0), MAX($G$1:G61)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F65),0)&gt;0), MAX($G$1:G64)+1, ""))</f>
         <v/>
       </c>
       <c r="H65" s="21" t="b">
@@ -3380,23 +3416,23 @@
       </c>
     </row>
     <row r="66" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A66" s="32">
-        <v>20</v>
-      </c>
-      <c r="B66" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="C66" s="34">
-        <v>20</v>
-      </c>
-      <c r="D66" s="32" t="s">
-        <v>211</v>
-      </c>
-      <c r="E66" s="33" t="s">
+      <c r="A66" s="36">
+        <v>17</v>
+      </c>
+      <c r="B66" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="C66" s="38">
+        <v>17</v>
+      </c>
+      <c r="D66" s="36" t="s">
+        <v>221</v>
+      </c>
+      <c r="E66" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F66" s="32" t="s">
-        <v>147</v>
+      <c r="F66" s="36" t="s">
+        <v>86</v>
       </c>
       <c r="G66" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F66),0)&gt;0), MAX($G$1:G65)+1, ""))</f>
@@ -3408,23 +3444,23 @@
       </c>
     </row>
     <row r="67" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A67" s="32">
-        <v>20</v>
-      </c>
-      <c r="B67" s="33" t="s">
-        <v>144</v>
-      </c>
-      <c r="C67" s="34">
-        <v>20</v>
-      </c>
-      <c r="D67" s="32" t="s">
-        <v>213</v>
-      </c>
-      <c r="E67" s="33" t="s">
+      <c r="A67" s="33">
+        <v>17</v>
+      </c>
+      <c r="B67" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="C67" s="35">
+        <v>17</v>
+      </c>
+      <c r="D67" s="33" t="s">
+        <v>210</v>
+      </c>
+      <c r="E67" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F67" s="32" t="s">
-        <v>145</v>
+      <c r="F67" s="33" t="s">
+        <v>33</v>
       </c>
       <c r="G67" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F67),0)&gt;0), MAX($G$1:G66)+1, ""))</f>
@@ -3436,101 +3472,105 @@
       </c>
     </row>
     <row r="68" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A68" s="32">
+      <c r="A68" s="33">
+        <v>17</v>
+      </c>
+      <c r="B68" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="C68" s="35">
+        <v>17</v>
+      </c>
+      <c r="D68" s="33" t="s">
+        <v>209</v>
+      </c>
+      <c r="E68" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F68" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="G68" s="29" t="s">
+        <v>328</v>
+      </c>
+      <c r="H68" s="21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A69" s="30">
         <v>20</v>
       </c>
-      <c r="B68" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="C68" s="34">
+      <c r="B69" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="C69" s="32">
         <v>20</v>
       </c>
-      <c r="D68" s="32" t="s">
-        <v>218</v>
-      </c>
-      <c r="E68" s="33" t="s">
-        <v>307</v>
-      </c>
-      <c r="F68" s="32" t="s">
-        <v>143</v>
-      </c>
-      <c r="G68" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F68),0)&gt;0), MAX($G$1:G67)+1, ""))</f>
-        <v/>
-      </c>
-      <c r="H68" s="21" t="b">
-        <f>A68=C68</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A69" s="38">
-        <v>20</v>
-      </c>
-      <c r="B69" s="39" t="s">
-        <v>335</v>
-      </c>
-      <c r="C69" s="40">
-        <v>20</v>
-      </c>
-      <c r="D69" s="38">
-        <v>3.4</v>
-      </c>
-      <c r="E69" s="39" t="s">
-        <v>338</v>
-      </c>
-      <c r="F69" s="38" t="s">
-        <v>336</v>
-      </c>
-      <c r="G69" s="29"/>
+      <c r="D69" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="E69" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F69" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="G69" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F69),0)&gt;0), MAX($G$1:G65)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H69" s="21" t="b">
         <f>A69=C69</f>
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A70" s="38">
+      <c r="A70" s="30">
         <v>20</v>
       </c>
-      <c r="B70" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="C70" s="40">
+      <c r="B70" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="C70" s="32">
         <v>20</v>
       </c>
-      <c r="D70" s="38">
-        <v>3.3</v>
-      </c>
-      <c r="E70" s="39" t="s">
-        <v>338</v>
-      </c>
-      <c r="F70" s="38" t="s">
-        <v>334</v>
-      </c>
-      <c r="G70" s="29"/>
+      <c r="D70" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="E70" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F70" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="G70" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F70),0)&gt;0), MAX($G$1:G69)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H70" s="21" t="b">
         <f>A70=C70</f>
         <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A71" s="32">
+      <c r="A71" s="30">
         <v>20</v>
       </c>
-      <c r="B71" s="33" t="s">
-        <v>140</v>
-      </c>
-      <c r="C71" s="34">
+      <c r="B71" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="C71" s="32">
         <v>20</v>
       </c>
-      <c r="D71" s="32" t="s">
-        <v>225</v>
-      </c>
-      <c r="E71" s="33" t="s">
+      <c r="D71" s="30" t="s">
+        <v>213</v>
+      </c>
+      <c r="E71" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F71" s="32" t="s">
-        <v>141</v>
+      <c r="F71" s="30" t="s">
+        <v>145</v>
       </c>
       <c r="G71" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F71),0)&gt;0), MAX($G$1:G70)+1, ""))</f>
@@ -3542,23 +3582,23 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A72" s="32">
+      <c r="A72" s="30">
         <v>20</v>
       </c>
-      <c r="B72" s="33" t="s">
-        <v>257</v>
-      </c>
-      <c r="C72" s="34">
+      <c r="B72" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="C72" s="32">
         <v>20</v>
       </c>
-      <c r="D72" s="32" t="s">
-        <v>227</v>
-      </c>
-      <c r="E72" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F72" s="32" t="s">
-        <v>258</v>
+      <c r="D72" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="E72" s="31" t="s">
+        <v>307</v>
+      </c>
+      <c r="F72" s="30" t="s">
+        <v>143</v>
       </c>
       <c r="G72" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F72),0)&gt;0), MAX($G$1:G71)+1, ""))</f>
@@ -3570,79 +3610,73 @@
       </c>
     </row>
     <row r="73" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A73" s="32">
+      <c r="A73" s="36">
         <v>20</v>
       </c>
-      <c r="B73" s="33" t="s">
-        <v>256</v>
-      </c>
-      <c r="C73" s="34">
+      <c r="B73" s="37" t="s">
+        <v>335</v>
+      </c>
+      <c r="C73" s="38">
         <v>20</v>
       </c>
-      <c r="D73" s="32">
-        <v>4.2</v>
-      </c>
-      <c r="E73" s="33" t="s">
-        <v>307</v>
-      </c>
-      <c r="F73" s="32">
-        <v>21765430</v>
-      </c>
-      <c r="G73" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F73),0)&gt;0), MAX($G$1:G72)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D73" s="36">
+        <v>3.4</v>
+      </c>
+      <c r="E73" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="F73" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="G73" s="29"/>
       <c r="H73" s="21" t="b">
         <f>A73=C73</f>
         <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A74" s="32">
+      <c r="A74" s="36">
         <v>20</v>
       </c>
-      <c r="B74" s="33" t="s">
-        <v>138</v>
-      </c>
-      <c r="C74" s="34">
+      <c r="B74" s="37" t="s">
+        <v>333</v>
+      </c>
+      <c r="C74" s="38">
         <v>20</v>
       </c>
-      <c r="D74" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="E74" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F74" s="32" t="s">
-        <v>139</v>
-      </c>
-      <c r="G74" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F74),0)&gt;0), MAX($G$1:G73)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D74" s="36">
+        <v>3.3</v>
+      </c>
+      <c r="E74" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="F74" s="36" t="s">
+        <v>334</v>
+      </c>
+      <c r="G74" s="29"/>
       <c r="H74" s="21" t="b">
         <f>A74=C74</f>
         <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A75" s="32">
+      <c r="A75" s="30">
         <v>20</v>
       </c>
-      <c r="B75" s="33" t="s">
-        <v>267</v>
-      </c>
-      <c r="C75" s="34">
+      <c r="B75" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="C75" s="32">
         <v>20</v>
       </c>
-      <c r="D75" s="32" t="s">
-        <v>224</v>
-      </c>
-      <c r="E75" s="33" t="s">
+      <c r="D75" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="E75" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F75" s="32" t="s">
-        <v>137</v>
+      <c r="F75" s="30" t="s">
+        <v>141</v>
       </c>
       <c r="G75" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F75),0)&gt;0), MAX($G$1:G74)+1, ""))</f>
@@ -3654,23 +3688,23 @@
       </c>
     </row>
     <row r="76" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A76" s="32">
+      <c r="A76" s="30">
         <v>20</v>
       </c>
-      <c r="B76" s="33" t="s">
-        <v>135</v>
-      </c>
-      <c r="C76" s="34">
+      <c r="B76" s="31" t="s">
+        <v>257</v>
+      </c>
+      <c r="C76" s="32">
         <v>20</v>
       </c>
-      <c r="D76" s="32" t="s">
-        <v>221</v>
-      </c>
-      <c r="E76" s="33" t="s">
-        <v>307</v>
-      </c>
-      <c r="F76" s="32" t="s">
-        <v>136</v>
+      <c r="D76" s="30" t="s">
+        <v>227</v>
+      </c>
+      <c r="E76" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F76" s="30" t="s">
+        <v>258</v>
       </c>
       <c r="G76" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F76),0)&gt;0), MAX($G$1:G75)+1, ""))</f>
@@ -3682,23 +3716,23 @@
       </c>
     </row>
     <row r="77" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A77" s="32">
+      <c r="A77" s="30">
         <v>20</v>
       </c>
-      <c r="B77" s="33" t="s">
-        <v>132</v>
-      </c>
-      <c r="C77" s="34">
+      <c r="B77" s="31" t="s">
+        <v>256</v>
+      </c>
+      <c r="C77" s="32">
         <v>20</v>
       </c>
-      <c r="D77" s="32" t="s">
-        <v>216</v>
-      </c>
-      <c r="E77" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="F77" s="32" t="s">
-        <v>134</v>
+      <c r="D77" s="30">
+        <v>4.2</v>
+      </c>
+      <c r="E77" s="31" t="s">
+        <v>307</v>
+      </c>
+      <c r="F77" s="30">
+        <v>21765430</v>
       </c>
       <c r="G77" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F77),0)&gt;0), MAX($G$1:G76)+1, ""))</f>
@@ -3710,23 +3744,23 @@
       </c>
     </row>
     <row r="78" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A78" s="26">
+      <c r="A78" s="30">
         <v>20</v>
       </c>
-      <c r="B78" s="27" t="s">
-        <v>314</v>
-      </c>
-      <c r="C78" s="28">
+      <c r="B78" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="C78" s="32">
         <v>20</v>
       </c>
-      <c r="D78" s="26">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="E78" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="F78" s="26" t="s">
-        <v>320</v>
+      <c r="D78" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="E78" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F78" s="30" t="s">
+        <v>139</v>
       </c>
       <c r="G78" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F78),0)&gt;0), MAX($G$1:G77)+1, ""))</f>
@@ -3738,23 +3772,23 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A79" s="32">
+      <c r="A79" s="30">
         <v>20</v>
       </c>
-      <c r="B79" s="33" t="s">
-        <v>130</v>
-      </c>
-      <c r="C79" s="34">
+      <c r="B79" s="31" t="s">
+        <v>267</v>
+      </c>
+      <c r="C79" s="32">
         <v>20</v>
       </c>
-      <c r="D79" s="32" t="s">
-        <v>222</v>
-      </c>
-      <c r="E79" s="33" t="s">
+      <c r="D79" s="30" t="s">
+        <v>224</v>
+      </c>
+      <c r="E79" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F79" s="32" t="s">
-        <v>131</v>
+      <c r="F79" s="30" t="s">
+        <v>137</v>
       </c>
       <c r="G79" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F79),0)&gt;0), MAX($G$1:G78)+1, ""))</f>
@@ -3766,23 +3800,23 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A80" s="32">
+      <c r="A80" s="30">
         <v>20</v>
       </c>
-      <c r="B80" s="33" t="s">
-        <v>128</v>
-      </c>
-      <c r="C80" s="34">
+      <c r="B80" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="C80" s="32">
         <v>20</v>
       </c>
-      <c r="D80" s="32" t="s">
-        <v>236</v>
-      </c>
-      <c r="E80" s="33" t="s">
+      <c r="D80" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="E80" s="31" t="s">
         <v>307</v>
       </c>
-      <c r="F80" s="32" t="s">
-        <v>129</v>
+      <c r="F80" s="30" t="s">
+        <v>136</v>
       </c>
       <c r="G80" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F80),0)&gt;0), MAX($G$1:G79)+1, ""))</f>
@@ -3794,23 +3828,23 @@
       </c>
     </row>
     <row r="81" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A81" s="32">
+      <c r="A81" s="30">
         <v>20</v>
       </c>
-      <c r="B81" s="33" t="s">
-        <v>126</v>
-      </c>
-      <c r="C81" s="34">
+      <c r="B81" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="C81" s="32">
         <v>20</v>
       </c>
-      <c r="D81" s="32" t="s">
-        <v>232</v>
-      </c>
-      <c r="E81" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F81" s="32" t="s">
-        <v>127</v>
+      <c r="D81" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="E81" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="F81" s="30" t="s">
+        <v>134</v>
       </c>
       <c r="G81" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F81),0)&gt;0), MAX($G$1:G80)+1, ""))</f>
@@ -3822,23 +3856,23 @@
       </c>
     </row>
     <row r="82" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A82" s="32">
+      <c r="A82" s="26">
         <v>20</v>
       </c>
-      <c r="B82" s="33" t="s">
-        <v>124</v>
-      </c>
-      <c r="C82" s="34">
+      <c r="B82" s="27" t="s">
+        <v>314</v>
+      </c>
+      <c r="C82" s="28">
         <v>20</v>
       </c>
-      <c r="D82" s="32" t="s">
-        <v>217</v>
-      </c>
-      <c r="E82" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F82" s="32" t="s">
-        <v>125</v>
+      <c r="D82" s="26">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E82" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="F82" s="26" t="s">
+        <v>320</v>
       </c>
       <c r="G82" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F82),0)&gt;0), MAX($G$1:G81)+1, ""))</f>
@@ -3850,23 +3884,23 @@
       </c>
     </row>
     <row r="83" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A83" s="32">
+      <c r="A83" s="30">
         <v>20</v>
       </c>
-      <c r="B83" s="33" t="s">
-        <v>122</v>
-      </c>
-      <c r="C83" s="34">
+      <c r="B83" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="C83" s="32">
         <v>20</v>
       </c>
-      <c r="D83" s="32" t="s">
-        <v>225</v>
-      </c>
-      <c r="E83" s="33" t="s">
-        <v>307</v>
-      </c>
-      <c r="F83" s="32" t="s">
-        <v>123</v>
+      <c r="D83" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="E83" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" s="30" t="s">
+        <v>131</v>
       </c>
       <c r="G83" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F83),0)&gt;0), MAX($G$1:G82)+1, ""))</f>
@@ -3878,23 +3912,23 @@
       </c>
     </row>
     <row r="84" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A84" s="32">
+      <c r="A84" s="30">
         <v>20</v>
       </c>
-      <c r="B84" s="33" t="s">
-        <v>259</v>
-      </c>
-      <c r="C84" s="34">
+      <c r="B84" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="C84" s="32">
         <v>20</v>
       </c>
-      <c r="D84" s="32" t="s">
-        <v>227</v>
-      </c>
-      <c r="E84" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F84" s="32" t="s">
-        <v>260</v>
+      <c r="D84" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="E84" s="31" t="s">
+        <v>307</v>
+      </c>
+      <c r="F84" s="30" t="s">
+        <v>129</v>
       </c>
       <c r="G84" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F84),0)&gt;0), MAX($G$1:G83)+1, ""))</f>
@@ -3906,23 +3940,23 @@
       </c>
     </row>
     <row r="85" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A85" s="32">
+      <c r="A85" s="26">
         <v>20</v>
       </c>
-      <c r="B85" s="33" t="s">
-        <v>120</v>
-      </c>
-      <c r="C85" s="34">
+      <c r="B85" s="27" t="s">
+        <v>352</v>
+      </c>
+      <c r="C85" s="28">
         <v>20</v>
       </c>
-      <c r="D85" s="32" t="s">
-        <v>229</v>
-      </c>
-      <c r="E85" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F85" s="32" t="s">
-        <v>121</v>
+      <c r="D85" s="26">
+        <v>2.7</v>
+      </c>
+      <c r="E85" s="27" t="s">
+        <v>247</v>
+      </c>
+      <c r="F85" s="26" t="s">
+        <v>355</v>
       </c>
       <c r="G85" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F85),0)&gt;0), MAX($G$1:G84)+1, ""))</f>
@@ -3934,23 +3968,23 @@
       </c>
     </row>
     <row r="86" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A86" s="32">
+      <c r="A86" s="30">
         <v>20</v>
       </c>
-      <c r="B86" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="C86" s="34">
+      <c r="B86" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="C86" s="32">
         <v>20</v>
       </c>
-      <c r="D86" s="32" t="s">
-        <v>210</v>
-      </c>
-      <c r="E86" s="33" t="s">
+      <c r="D86" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="E86" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F86" s="32" t="s">
-        <v>119</v>
+      <c r="F86" s="30" t="s">
+        <v>127</v>
       </c>
       <c r="G86" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F86),0)&gt;0), MAX($G$1:G85)+1, ""))</f>
@@ -3962,23 +3996,23 @@
       </c>
     </row>
     <row r="87" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A87" s="32">
+      <c r="A87" s="30">
         <v>20</v>
       </c>
-      <c r="B87" s="33" t="s">
-        <v>116</v>
-      </c>
-      <c r="C87" s="34">
+      <c r="B87" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="C87" s="32">
         <v>20</v>
       </c>
-      <c r="D87" s="32" t="s">
-        <v>214</v>
-      </c>
-      <c r="E87" s="33" t="s">
+      <c r="D87" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="E87" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F87" s="32" t="s">
-        <v>117</v>
+      <c r="F87" s="30" t="s">
+        <v>125</v>
       </c>
       <c r="G87" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F87),0)&gt;0), MAX($G$1:G86)+1, ""))</f>
@@ -3990,23 +4024,23 @@
       </c>
     </row>
     <row r="88" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A88" s="26">
+      <c r="A88" s="30">
         <v>20</v>
       </c>
-      <c r="B88" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="C88" s="28">
+      <c r="B88" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="C88" s="32">
         <v>20</v>
       </c>
-      <c r="D88" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E88" s="27" t="s">
-        <v>301</v>
-      </c>
-      <c r="F88" s="26" t="s">
-        <v>300</v>
+      <c r="D88" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="E88" s="31" t="s">
+        <v>307</v>
+      </c>
+      <c r="F88" s="30" t="s">
+        <v>123</v>
       </c>
       <c r="G88" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F88),0)&gt;0), MAX($G$1:G87)+1, ""))</f>
@@ -4018,23 +4052,23 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A89" s="32">
+      <c r="A89" s="30">
         <v>20</v>
       </c>
-      <c r="B89" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="C89" s="34">
+      <c r="B89" s="31" t="s">
+        <v>259</v>
+      </c>
+      <c r="C89" s="32">
         <v>20</v>
       </c>
-      <c r="D89" s="32" t="s">
-        <v>221</v>
-      </c>
-      <c r="E89" s="33" t="s">
+      <c r="D89" s="30" t="s">
+        <v>227</v>
+      </c>
+      <c r="E89" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F89" s="32" t="s">
-        <v>115</v>
+      <c r="F89" s="30" t="s">
+        <v>260</v>
       </c>
       <c r="G89" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F89),0)&gt;0), MAX($G$1:G88)+1, ""))</f>
@@ -4046,23 +4080,23 @@
       </c>
     </row>
     <row r="90" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A90" s="32">
+      <c r="A90" s="30">
         <v>20</v>
       </c>
-      <c r="B90" s="33" t="s">
-        <v>112</v>
-      </c>
-      <c r="C90" s="34">
+      <c r="B90" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="C90" s="32">
         <v>20</v>
       </c>
-      <c r="D90" s="32" t="s">
-        <v>224</v>
-      </c>
-      <c r="E90" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="F90" s="32" t="s">
-        <v>113</v>
+      <c r="D90" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="E90" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F90" s="30" t="s">
+        <v>121</v>
       </c>
       <c r="G90" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F90),0)&gt;0), MAX($G$1:G89)+1, ""))</f>
@@ -4074,23 +4108,23 @@
       </c>
     </row>
     <row r="91" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A91" s="32">
+      <c r="A91" s="30">
         <v>20</v>
       </c>
-      <c r="B91" s="33" t="s">
-        <v>110</v>
-      </c>
-      <c r="C91" s="34">
+      <c r="B91" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C91" s="32">
         <v>20</v>
       </c>
-      <c r="D91" s="32" t="s">
-        <v>220</v>
-      </c>
-      <c r="E91" s="33" t="s">
+      <c r="D91" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="E91" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F91" s="32" t="s">
-        <v>111</v>
+      <c r="F91" s="30" t="s">
+        <v>119</v>
       </c>
       <c r="G91" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F91),0)&gt;0), MAX($G$1:G90)+1, ""))</f>
@@ -4102,25 +4136,28 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A92" s="38">
+      <c r="A92" s="30">
         <v>20</v>
       </c>
-      <c r="B92" s="39" t="s">
-        <v>332</v>
-      </c>
-      <c r="C92" s="40">
+      <c r="B92" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="C92" s="32">
         <v>20</v>
       </c>
-      <c r="D92" s="38">
-        <v>3</v>
-      </c>
-      <c r="E92" s="39" t="s">
-        <v>306</v>
-      </c>
-      <c r="F92" s="38" t="s">
-        <v>107</v>
-      </c>
-      <c r="G92" s="29"/>
+      <c r="D92" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="E92" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F92" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="G92" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F92),0)&gt;0), MAX($G$1:G91)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H92" s="21" t="b">
         <f>A92=C92</f>
         <v>1</v>
@@ -4131,7 +4168,7 @@
         <v>20</v>
       </c>
       <c r="B93" s="27" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="C93" s="28">
         <v>20</v>
@@ -4143,7 +4180,7 @@
         <v>301</v>
       </c>
       <c r="F93" s="26" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G93" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F93),0)&gt;0), MAX($G$1:G92)+1, ""))</f>
@@ -4155,23 +4192,23 @@
       </c>
     </row>
     <row r="94" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A94" s="32">
+      <c r="A94" s="30">
         <v>20</v>
       </c>
-      <c r="B94" s="33" t="s">
-        <v>105</v>
-      </c>
-      <c r="C94" s="34">
+      <c r="B94" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="C94" s="32">
         <v>20</v>
       </c>
-      <c r="D94" s="32" t="s">
-        <v>216</v>
-      </c>
-      <c r="E94" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F94" s="32" t="s">
-        <v>106</v>
+      <c r="D94" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="E94" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" s="30" t="s">
+        <v>115</v>
       </c>
       <c r="G94" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F94),0)&gt;0), MAX($G$1:G93)+1, ""))</f>
@@ -4183,48 +4220,51 @@
       </c>
     </row>
     <row r="95" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A95" s="38">
+      <c r="A95" s="30">
         <v>20</v>
       </c>
-      <c r="B95" s="39" t="s">
-        <v>337</v>
-      </c>
-      <c r="C95" s="40">
+      <c r="B95" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="C95" s="32">
         <v>20</v>
       </c>
-      <c r="D95" s="38">
-        <v>3.2</v>
-      </c>
-      <c r="E95" s="39" t="s">
-        <v>338</v>
-      </c>
-      <c r="F95" s="38" t="s">
-        <v>334</v>
-      </c>
-      <c r="G95" s="29"/>
+      <c r="D95" s="30" t="s">
+        <v>224</v>
+      </c>
+      <c r="E95" s="31" t="s">
+        <v>301</v>
+      </c>
+      <c r="F95" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="G95" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F95),0)&gt;0), MAX($G$1:G94)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H95" s="21" t="b">
         <f>A95=C95</f>
         <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A96" s="32">
+      <c r="A96" s="30">
         <v>20</v>
       </c>
-      <c r="B96" s="33" t="s">
-        <v>103</v>
-      </c>
-      <c r="C96" s="34">
+      <c r="B96" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="C96" s="32">
         <v>20</v>
       </c>
-      <c r="D96" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="E96" s="33" t="s">
+      <c r="D96" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="E96" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F96" s="32" t="s">
-        <v>104</v>
+      <c r="F96" s="30" t="s">
+        <v>111</v>
       </c>
       <c r="G96" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F96),0)&gt;0), MAX($G$1:G95)+1, ""))</f>
@@ -4236,51 +4276,48 @@
       </c>
     </row>
     <row r="97" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A97" s="32">
+      <c r="A97" s="36">
         <v>20</v>
       </c>
-      <c r="B97" s="33" t="s">
-        <v>265</v>
-      </c>
-      <c r="C97" s="34">
+      <c r="B97" s="37" t="s">
+        <v>332</v>
+      </c>
+      <c r="C97" s="38">
         <v>20</v>
       </c>
-      <c r="D97" s="32">
-        <v>6.2</v>
-      </c>
-      <c r="E97" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F97" s="32" t="s">
-        <v>266</v>
-      </c>
-      <c r="G97" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F97),0)&gt;0), MAX($G$1:G96)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D97" s="36">
+        <v>3</v>
+      </c>
+      <c r="E97" s="37" t="s">
+        <v>306</v>
+      </c>
+      <c r="F97" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="G97" s="29"/>
       <c r="H97" s="21" t="b">
         <f>A97=C97</f>
         <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A98" s="32">
+      <c r="A98" s="26">
         <v>20</v>
       </c>
-      <c r="B98" s="33" t="s">
-        <v>101</v>
-      </c>
-      <c r="C98" s="34">
+      <c r="B98" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="C98" s="28">
         <v>20</v>
       </c>
-      <c r="D98" s="32" t="s">
-        <v>217</v>
-      </c>
-      <c r="E98" s="33" t="s">
+      <c r="D98" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E98" s="27" t="s">
         <v>301</v>
       </c>
-      <c r="F98" s="32" t="s">
-        <v>102</v>
+      <c r="F98" s="26" t="s">
+        <v>303</v>
       </c>
       <c r="G98" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F98),0)&gt;0), MAX($G$1:G97)+1, ""))</f>
@@ -4292,23 +4329,23 @@
       </c>
     </row>
     <row r="99" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A99" s="26">
+      <c r="A99" s="30">
         <v>20</v>
       </c>
-      <c r="B99" s="27" t="s">
-        <v>302</v>
-      </c>
-      <c r="C99" s="28">
+      <c r="B99" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="C99" s="32">
         <v>20</v>
       </c>
-      <c r="D99" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E99" s="27" t="s">
-        <v>301</v>
-      </c>
-      <c r="F99" s="26" t="s">
-        <v>303</v>
+      <c r="D99" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="E99" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="F99" s="30" t="s">
+        <v>106</v>
       </c>
       <c r="G99" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F99),0)&gt;0), MAX($G$1:G98)+1, ""))</f>
@@ -4320,23 +4357,23 @@
       </c>
     </row>
     <row r="100" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A100" s="32">
+      <c r="A100" s="26">
         <v>20</v>
       </c>
-      <c r="B100" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="C100" s="34">
+      <c r="B100" s="27" t="s">
+        <v>341</v>
+      </c>
+      <c r="C100" s="28">
         <v>20</v>
       </c>
-      <c r="D100" s="32" t="s">
-        <v>218</v>
-      </c>
-      <c r="E100" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F100" s="32" t="s">
-        <v>98</v>
+      <c r="D100" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E100" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="F100" s="26" t="s">
+        <v>346</v>
       </c>
       <c r="G100" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F100),0)&gt;0), MAX($G$1:G99)+1, ""))</f>
@@ -4348,51 +4385,48 @@
       </c>
     </row>
     <row r="101" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A101" s="32">
+      <c r="A101" s="36">
         <v>20</v>
       </c>
-      <c r="B101" s="33" t="s">
-        <v>93</v>
-      </c>
-      <c r="C101" s="34">
+      <c r="B101" s="37" t="s">
+        <v>337</v>
+      </c>
+      <c r="C101" s="38">
         <v>20</v>
       </c>
-      <c r="D101" s="32" t="s">
-        <v>220</v>
-      </c>
-      <c r="E101" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F101" s="32" t="s">
-        <v>94</v>
-      </c>
-      <c r="G101" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F101),0)&gt;0), MAX($G$1:G100)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D101" s="36">
+        <v>3.2</v>
+      </c>
+      <c r="E101" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="F101" s="36" t="s">
+        <v>334</v>
+      </c>
+      <c r="G101" s="29"/>
       <c r="H101" s="21" t="b">
         <f>A101=C101</f>
         <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A102" s="32">
+      <c r="A102" s="30">
         <v>20</v>
       </c>
-      <c r="B102" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="C102" s="34">
+      <c r="B102" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="C102" s="32">
         <v>20</v>
       </c>
-      <c r="D102" s="32" t="s">
-        <v>225</v>
-      </c>
-      <c r="E102" s="33" t="s">
+      <c r="D102" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="E102" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F102" s="32" t="s">
-        <v>92</v>
+      <c r="F102" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G102" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F102),0)&gt;0), MAX($G$1:G101)+1, ""))</f>
@@ -4404,23 +4438,23 @@
       </c>
     </row>
     <row r="103" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A103" s="32">
+      <c r="A103" s="30">
         <v>20</v>
       </c>
-      <c r="B103" s="33" t="s">
-        <v>292</v>
-      </c>
-      <c r="C103" s="34">
+      <c r="B103" s="31" t="s">
+        <v>265</v>
+      </c>
+      <c r="C103" s="32">
         <v>20</v>
       </c>
-      <c r="D103" s="32">
-        <v>1.8</v>
-      </c>
-      <c r="E103" s="33" t="s">
-        <v>293</v>
-      </c>
-      <c r="F103" s="32" t="s">
-        <v>92</v>
+      <c r="D103" s="30">
+        <v>6.2</v>
+      </c>
+      <c r="E103" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F103" s="30" t="s">
+        <v>266</v>
       </c>
       <c r="G103" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F103),0)&gt;0), MAX($G$1:G102)+1, ""))</f>
@@ -4432,23 +4466,23 @@
       </c>
     </row>
     <row r="104" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A104" s="32">
+      <c r="A104" s="30">
         <v>20</v>
       </c>
-      <c r="B104" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="C104" s="34">
+      <c r="B104" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="C104" s="32">
         <v>20</v>
       </c>
-      <c r="D104" s="32" t="s">
-        <v>224</v>
-      </c>
-      <c r="E104" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F104" s="32" t="s">
-        <v>90</v>
+      <c r="D104" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="E104" s="31" t="s">
+        <v>301</v>
+      </c>
+      <c r="F104" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G104" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F104),0)&gt;0), MAX($G$1:G103)+1, ""))</f>
@@ -4460,23 +4494,23 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A105" s="32">
+      <c r="A105" s="26">
         <v>20</v>
       </c>
-      <c r="B105" s="33" t="s">
-        <v>87</v>
-      </c>
-      <c r="C105" s="34">
+      <c r="B105" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C105" s="28">
         <v>20</v>
       </c>
-      <c r="D105" s="32" t="s">
-        <v>222</v>
-      </c>
-      <c r="E105" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F105" s="32" t="s">
-        <v>88</v>
+      <c r="D105" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E105" s="27" t="s">
+        <v>301</v>
+      </c>
+      <c r="F105" s="26" t="s">
+        <v>303</v>
       </c>
       <c r="G105" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F105),0)&gt;0), MAX($G$1:G104)+1, ""))</f>
@@ -4488,23 +4522,23 @@
       </c>
     </row>
     <row r="106" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A106" s="32">
+      <c r="A106" s="30">
         <v>20</v>
       </c>
-      <c r="B106" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="C106" s="34">
+      <c r="B106" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="C106" s="32">
         <v>20</v>
       </c>
-      <c r="D106" s="32" t="s">
-        <v>220</v>
-      </c>
-      <c r="E106" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="F106" s="32" t="s">
-        <v>84</v>
+      <c r="D106" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="E106" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F106" s="30" t="s">
+        <v>98</v>
       </c>
       <c r="G106" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F106),0)&gt;0), MAX($G$1:G105)+1, ""))</f>
@@ -4516,23 +4550,23 @@
       </c>
     </row>
     <row r="107" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A107" s="32">
+      <c r="A107" s="30">
         <v>20</v>
       </c>
-      <c r="B107" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="C107" s="34">
+      <c r="B107" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="C107" s="32">
         <v>20</v>
       </c>
-      <c r="D107" s="32" t="s">
-        <v>219</v>
-      </c>
-      <c r="E107" s="33" t="s">
+      <c r="D107" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="E107" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F107" s="32" t="s">
-        <v>81</v>
+      <c r="F107" s="30" t="s">
+        <v>94</v>
       </c>
       <c r="G107" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F107),0)&gt;0), MAX($G$1:G106)+1, ""))</f>
@@ -4544,23 +4578,23 @@
       </c>
     </row>
     <row r="108" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A108" s="32">
+      <c r="A108" s="30">
         <v>20</v>
       </c>
-      <c r="B108" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="C108" s="34">
+      <c r="B108" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="C108" s="32">
         <v>20</v>
       </c>
-      <c r="D108" s="32" t="s">
-        <v>218</v>
-      </c>
-      <c r="E108" s="33" t="s">
+      <c r="D108" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="E108" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F108" s="32" t="s">
-        <v>79</v>
+      <c r="F108" s="30" t="s">
+        <v>92</v>
       </c>
       <c r="G108" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F108),0)&gt;0), MAX($G$1:G107)+1, ""))</f>
@@ -4572,23 +4606,23 @@
       </c>
     </row>
     <row r="109" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A109" s="26">
-        <v>25</v>
-      </c>
-      <c r="B109" s="27" t="s">
-        <v>180</v>
-      </c>
-      <c r="C109" s="28">
-        <v>25</v>
-      </c>
-      <c r="D109" s="26" t="s">
-        <v>227</v>
-      </c>
-      <c r="E109" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F109" s="26" t="s">
-        <v>181</v>
+      <c r="A109" s="30">
+        <v>20</v>
+      </c>
+      <c r="B109" s="31" t="s">
+        <v>292</v>
+      </c>
+      <c r="C109" s="32">
+        <v>20</v>
+      </c>
+      <c r="D109" s="30">
+        <v>1.8</v>
+      </c>
+      <c r="E109" s="31" t="s">
+        <v>293</v>
+      </c>
+      <c r="F109" s="30" t="s">
+        <v>92</v>
       </c>
       <c r="G109" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F109),0)&gt;0), MAX($G$1:G108)+1, ""))</f>
@@ -4600,23 +4634,23 @@
       </c>
     </row>
     <row r="110" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A110" s="26">
-        <v>25</v>
-      </c>
-      <c r="B110" s="27" t="s">
-        <v>178</v>
-      </c>
-      <c r="C110" s="28">
-        <v>25</v>
-      </c>
-      <c r="D110" s="26" t="s">
-        <v>239</v>
-      </c>
-      <c r="E110" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F110" s="26" t="s">
-        <v>179</v>
+      <c r="A110" s="30">
+        <v>20</v>
+      </c>
+      <c r="B110" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="C110" s="32">
+        <v>20</v>
+      </c>
+      <c r="D110" s="30" t="s">
+        <v>224</v>
+      </c>
+      <c r="E110" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F110" s="30" t="s">
+        <v>90</v>
       </c>
       <c r="G110" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F110),0)&gt;0), MAX($G$1:G109)+1, ""))</f>
@@ -4628,23 +4662,23 @@
       </c>
     </row>
     <row r="111" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A111" s="26">
-        <v>25</v>
-      </c>
-      <c r="B111" s="27" t="s">
-        <v>176</v>
-      </c>
-      <c r="C111" s="28">
-        <v>25</v>
-      </c>
-      <c r="D111" s="26" t="s">
-        <v>233</v>
-      </c>
-      <c r="E111" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F111" s="26" t="s">
-        <v>177</v>
+      <c r="A111" s="30">
+        <v>20</v>
+      </c>
+      <c r="B111" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="C111" s="32">
+        <v>20</v>
+      </c>
+      <c r="D111" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="E111" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F111" s="30" t="s">
+        <v>88</v>
       </c>
       <c r="G111" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F111),0)&gt;0), MAX($G$1:G110)+1, ""))</f>
@@ -4656,23 +4690,23 @@
       </c>
     </row>
     <row r="112" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A112" s="26">
-        <v>25</v>
-      </c>
-      <c r="B112" s="27" t="s">
-        <v>175</v>
-      </c>
-      <c r="C112" s="28">
-        <v>25</v>
-      </c>
-      <c r="D112" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="E112" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F112" s="26" t="s">
-        <v>326</v>
+      <c r="A112" s="30">
+        <v>20</v>
+      </c>
+      <c r="B112" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="C112" s="32">
+        <v>20</v>
+      </c>
+      <c r="D112" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="E112" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="F112" s="30" t="s">
+        <v>84</v>
       </c>
       <c r="G112" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F112),0)&gt;0), MAX($G$1:G111)+1, ""))</f>
@@ -4684,23 +4718,23 @@
       </c>
     </row>
     <row r="113" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A113" s="26">
-        <v>25</v>
-      </c>
-      <c r="B113" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="C113" s="28">
-        <v>25</v>
-      </c>
-      <c r="D113" s="26">
-        <v>2.7</v>
-      </c>
-      <c r="E113" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="F113" s="26" t="s">
-        <v>340</v>
+      <c r="A113" s="30">
+        <v>20</v>
+      </c>
+      <c r="B113" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="C113" s="32">
+        <v>20</v>
+      </c>
+      <c r="D113" s="30" t="s">
+        <v>219</v>
+      </c>
+      <c r="E113" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F113" s="30" t="s">
+        <v>81</v>
       </c>
       <c r="G113" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F113),0)&gt;0), MAX($G$1:G112)+1, ""))</f>
@@ -4712,23 +4746,23 @@
       </c>
     </row>
     <row r="114" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A114" s="32">
-        <v>25</v>
-      </c>
-      <c r="B114" s="33" t="s">
-        <v>286</v>
-      </c>
-      <c r="C114" s="34">
-        <v>25</v>
-      </c>
-      <c r="D114" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="E114" s="33" t="s">
-        <v>285</v>
-      </c>
-      <c r="F114" s="32" t="s">
-        <v>104</v>
+      <c r="A114" s="30">
+        <v>20</v>
+      </c>
+      <c r="B114" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="C114" s="32">
+        <v>20</v>
+      </c>
+      <c r="D114" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="E114" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F114" s="30" t="s">
+        <v>79</v>
       </c>
       <c r="G114" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F114),0)&gt;0), MAX($G$1:G113)+1, ""))</f>
@@ -4740,23 +4774,23 @@
       </c>
     </row>
     <row r="115" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A115" s="32">
+      <c r="A115" s="26">
         <v>25</v>
       </c>
-      <c r="B115" s="33" t="s">
-        <v>284</v>
-      </c>
-      <c r="C115" s="34">
+      <c r="B115" s="27" t="s">
+        <v>180</v>
+      </c>
+      <c r="C115" s="28">
         <v>25</v>
       </c>
-      <c r="D115" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="E115" s="33" t="s">
-        <v>285</v>
-      </c>
-      <c r="F115" s="32" t="s">
-        <v>104</v>
+      <c r="D115" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="E115" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F115" s="26" t="s">
+        <v>181</v>
       </c>
       <c r="G115" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F115),0)&gt;0), MAX($G$1:G114)+1, ""))</f>
@@ -4772,19 +4806,19 @@
         <v>25</v>
       </c>
       <c r="B116" s="27" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C116" s="28">
         <v>25</v>
       </c>
       <c r="D116" s="26" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E116" s="27" t="s">
         <v>133</v>
       </c>
       <c r="F116" s="26" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="G116" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F116),0)&gt;0), MAX($G$1:G115)+1, ""))</f>
@@ -4800,19 +4834,19 @@
         <v>25</v>
       </c>
       <c r="B117" s="27" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C117" s="28">
         <v>25</v>
       </c>
       <c r="D117" s="26" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="E117" s="27" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="F117" s="26" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="G117" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F117),0)&gt;0), MAX($G$1:G116)+1, ""))</f>
@@ -4824,23 +4858,23 @@
       </c>
     </row>
     <row r="118" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A118" s="32">
+      <c r="A118" s="26">
         <v>25</v>
       </c>
-      <c r="B118" s="33" t="s">
-        <v>280</v>
-      </c>
-      <c r="C118" s="34">
+      <c r="B118" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="C118" s="28">
         <v>25</v>
       </c>
-      <c r="D118" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="E118" s="33" t="s">
+      <c r="D118" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="E118" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F118" s="32" t="s">
-        <v>104</v>
+      <c r="F118" s="26" t="s">
+        <v>326</v>
       </c>
       <c r="G118" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F118),0)&gt;0), MAX($G$1:G117)+1, ""))</f>
@@ -4856,19 +4890,19 @@
         <v>25</v>
       </c>
       <c r="B119" s="27" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C119" s="28">
         <v>25</v>
       </c>
-      <c r="D119" s="26" t="s">
-        <v>223</v>
+      <c r="D119" s="26">
+        <v>2.7</v>
       </c>
       <c r="E119" s="27" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="F119" s="26" t="s">
-        <v>169</v>
+        <v>340</v>
       </c>
       <c r="G119" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F119),0)&gt;0), MAX($G$1:G118)+1, ""))</f>
@@ -4880,23 +4914,23 @@
       </c>
     </row>
     <row r="120" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A120" s="26">
+      <c r="A120" s="30">
         <v>25</v>
       </c>
-      <c r="B120" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="C120" s="28">
+      <c r="B120" s="31" t="s">
+        <v>286</v>
+      </c>
+      <c r="C120" s="32">
         <v>25</v>
       </c>
-      <c r="D120" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="E120" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F120" s="26" t="s">
-        <v>167</v>
+      <c r="D120" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="E120" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="F120" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G120" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F120),0)&gt;0), MAX($G$1:G119)+1, ""))</f>
@@ -4908,23 +4942,23 @@
       </c>
     </row>
     <row r="121" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A121" s="26">
+      <c r="A121" s="30">
         <v>25</v>
       </c>
-      <c r="B121" s="27" t="s">
-        <v>164</v>
-      </c>
-      <c r="C121" s="28">
+      <c r="B121" s="31" t="s">
+        <v>284</v>
+      </c>
+      <c r="C121" s="32">
         <v>25</v>
       </c>
-      <c r="D121" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="E121" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="F121" s="26" t="s">
-        <v>165</v>
+      <c r="D121" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="E121" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="F121" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G121" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F121),0)&gt;0), MAX($G$1:G120)+1, ""))</f>
@@ -4940,19 +4974,19 @@
         <v>25</v>
       </c>
       <c r="B122" s="27" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="C122" s="28">
         <v>25</v>
       </c>
       <c r="D122" s="26" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E122" s="27" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="F122" s="26" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="G122" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F122),0)&gt;0), MAX($G$1:G121)+1, ""))</f>
@@ -4968,19 +5002,19 @@
         <v>25</v>
       </c>
       <c r="B123" s="27" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="C123" s="28">
         <v>25</v>
       </c>
       <c r="D123" s="26" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="E123" s="27" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="F123" s="26" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="G123" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F123),0)&gt;0), MAX($G$1:G122)+1, ""))</f>
@@ -4992,26 +5026,26 @@
       </c>
     </row>
     <row r="124" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A124" s="26">
+      <c r="A124" s="30">
         <v>25</v>
       </c>
-      <c r="B124" s="27" t="s">
-        <v>312</v>
-      </c>
-      <c r="C124" s="28">
+      <c r="B124" s="31" t="s">
+        <v>280</v>
+      </c>
+      <c r="C124" s="32">
         <v>25</v>
       </c>
-      <c r="D124" s="26">
-        <v>3.9</v>
-      </c>
-      <c r="E124" s="27" t="s">
-        <v>311</v>
-      </c>
-      <c r="F124" s="26" t="s">
-        <v>313</v>
+      <c r="D124" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="E124" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F124" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G124" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F124),0)&gt;0), MAX($G$1:G122)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F124),0)&gt;0), MAX($G$1:G123)+1, ""))</f>
         <v/>
       </c>
       <c r="H124" s="21" t="b">
@@ -5024,19 +5058,19 @@
         <v>25</v>
       </c>
       <c r="B125" s="27" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="C125" s="28">
         <v>25</v>
       </c>
       <c r="D125" s="26" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="E125" s="27" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="F125" s="26" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="G125" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F125),0)&gt;0), MAX($G$1:G124)+1, ""))</f>
@@ -5052,19 +5086,19 @@
         <v>25</v>
       </c>
       <c r="B126" s="27" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="C126" s="28">
         <v>25</v>
       </c>
       <c r="D126" s="26" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="E126" s="27" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="F126" s="26" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="G126" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F126),0)&gt;0), MAX($G$1:G125)+1, ""))</f>
@@ -5080,19 +5114,19 @@
         <v>25</v>
       </c>
       <c r="B127" s="27" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C127" s="28">
         <v>25</v>
       </c>
       <c r="D127" s="26" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E127" s="27" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="F127" s="26" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="G127" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F127),0)&gt;0), MAX($G$1:G126)+1, ""))</f>
@@ -5108,19 +5142,19 @@
         <v>25</v>
       </c>
       <c r="B128" s="27" t="s">
-        <v>249</v>
+        <v>162</v>
       </c>
       <c r="C128" s="28">
         <v>25</v>
       </c>
-      <c r="D128" s="41" t="s">
-        <v>231</v>
+      <c r="D128" s="26" t="s">
+        <v>238</v>
       </c>
       <c r="E128" s="27" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="F128" s="26" t="s">
-        <v>250</v>
+        <v>163</v>
       </c>
       <c r="G128" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F128),0)&gt;0), MAX($G$1:G127)+1, ""))</f>
@@ -5136,19 +5170,19 @@
         <v>25</v>
       </c>
       <c r="B129" s="27" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="C129" s="28">
         <v>25</v>
       </c>
       <c r="D129" s="26" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E129" s="27" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="F129" s="26" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="G129" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F129),0)&gt;0), MAX($G$1:G128)+1, ""))</f>
@@ -5160,23 +5194,23 @@
       </c>
     </row>
     <row r="130" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A130" s="32">
+      <c r="A130" s="26">
         <v>25</v>
       </c>
-      <c r="B130" s="33" t="s">
-        <v>290</v>
-      </c>
-      <c r="C130" s="34">
+      <c r="B130" s="27" t="s">
+        <v>344</v>
+      </c>
+      <c r="C130" s="28">
         <v>25</v>
       </c>
-      <c r="D130" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="E130" s="33" t="s">
-        <v>285</v>
-      </c>
-      <c r="F130" s="32" t="s">
-        <v>104</v>
+      <c r="D130" s="26">
+        <v>3.4</v>
+      </c>
+      <c r="E130" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="F130" s="26" t="s">
+        <v>345</v>
       </c>
       <c r="G130" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F130),0)&gt;0), MAX($G$1:G129)+1, ""))</f>
@@ -5188,26 +5222,26 @@
       </c>
     </row>
     <row r="131" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A131" s="32">
+      <c r="A131" s="26">
         <v>25</v>
       </c>
-      <c r="B131" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="C131" s="34">
+      <c r="B131" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="C131" s="28">
         <v>25</v>
       </c>
-      <c r="D131" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="E131" s="33" t="s">
-        <v>285</v>
-      </c>
-      <c r="F131" s="32" t="s">
-        <v>104</v>
+      <c r="D131" s="26">
+        <v>3.9</v>
+      </c>
+      <c r="E131" s="27" t="s">
+        <v>311</v>
+      </c>
+      <c r="F131" s="26" t="s">
+        <v>313</v>
       </c>
       <c r="G131" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F131),0)&gt;0), MAX($G$1:G130)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F131),0)&gt;0), MAX($G$1:G129)+1, ""))</f>
         <v/>
       </c>
       <c r="H131" s="21" t="b">
@@ -5216,23 +5250,23 @@
       </c>
     </row>
     <row r="132" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A132" s="32">
+      <c r="A132" s="26">
         <v>25</v>
       </c>
-      <c r="B132" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="C132" s="34">
+      <c r="B132" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="C132" s="28">
         <v>25</v>
       </c>
-      <c r="D132" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="E132" s="33" t="s">
-        <v>285</v>
-      </c>
-      <c r="F132" s="32" t="s">
-        <v>104</v>
+      <c r="D132" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="E132" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="F132" s="26" t="s">
+        <v>159</v>
       </c>
       <c r="G132" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B132),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E132),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F132),0)&gt;0), MAX($G$1:G131)+1, ""))</f>
@@ -5248,19 +5282,19 @@
         <v>25</v>
       </c>
       <c r="B133" s="27" t="s">
-        <v>254</v>
+        <v>156</v>
       </c>
       <c r="C133" s="28">
         <v>25</v>
       </c>
-      <c r="D133" s="26">
-        <v>2.5</v>
+      <c r="D133" s="26" t="s">
+        <v>226</v>
       </c>
       <c r="E133" s="27" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="F133" s="26" t="s">
-        <v>255</v>
+        <v>157</v>
       </c>
       <c r="G133" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F133),0)&gt;0), MAX($G$1:G132)+1, ""))</f>
@@ -5272,23 +5306,23 @@
       </c>
     </row>
     <row r="134" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A134" s="32">
+      <c r="A134" s="26">
         <v>25</v>
       </c>
-      <c r="B134" s="33" t="s">
-        <v>287</v>
-      </c>
-      <c r="C134" s="34">
+      <c r="B134" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="C134" s="28">
         <v>25</v>
       </c>
-      <c r="D134" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="E134" s="33" t="s">
-        <v>285</v>
-      </c>
-      <c r="F134" s="32" t="s">
-        <v>104</v>
+      <c r="D134" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="E134" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="F134" s="26" t="s">
+        <v>155</v>
       </c>
       <c r="G134" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F134),0)&gt;0), MAX($G$1:G133)+1, ""))</f>
@@ -5304,22 +5338,22 @@
         <v>25</v>
       </c>
       <c r="B135" s="27" t="s">
-        <v>150</v>
+        <v>249</v>
       </c>
       <c r="C135" s="28">
         <v>25</v>
       </c>
-      <c r="D135" s="26" t="s">
-        <v>228</v>
+      <c r="D135" s="39" t="s">
+        <v>231</v>
       </c>
       <c r="E135" s="27" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="F135" s="26" t="s">
-        <v>151</v>
+        <v>250</v>
       </c>
       <c r="G135" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F135),0)&gt;0), MAX($G$1:G133)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F135),0)&gt;0), MAX($G$1:G134)+1, ""))</f>
         <v/>
       </c>
       <c r="H135" s="21" t="b">
@@ -5328,23 +5362,23 @@
       </c>
     </row>
     <row r="136" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A136" s="32">
-        <v>30</v>
-      </c>
-      <c r="B136" s="33" t="s">
-        <v>194</v>
-      </c>
-      <c r="C136" s="34">
-        <v>30</v>
-      </c>
-      <c r="D136" s="32" t="s">
-        <v>234</v>
-      </c>
-      <c r="E136" s="33" t="s">
+      <c r="A136" s="26">
+        <v>25</v>
+      </c>
+      <c r="B136" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="C136" s="28">
+        <v>25</v>
+      </c>
+      <c r="D136" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="E136" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="F136" s="32" t="s">
-        <v>195</v>
+      <c r="F136" s="26" t="s">
+        <v>153</v>
       </c>
       <c r="G136" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F136),0)&gt;0), MAX($G$1:G135)+1, ""))</f>
@@ -5356,23 +5390,23 @@
       </c>
     </row>
     <row r="137" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A137" s="32">
-        <v>30</v>
-      </c>
-      <c r="B137" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="C137" s="34">
-        <v>30</v>
-      </c>
-      <c r="D137" s="32" t="s">
-        <v>243</v>
-      </c>
-      <c r="E137" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="F137" s="32" t="s">
-        <v>192</v>
+      <c r="A137" s="30">
+        <v>25</v>
+      </c>
+      <c r="B137" s="31" t="s">
+        <v>290</v>
+      </c>
+      <c r="C137" s="32">
+        <v>25</v>
+      </c>
+      <c r="D137" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="E137" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="F137" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G137" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F137),0)&gt;0), MAX($G$1:G136)+1, ""))</f>
@@ -5384,23 +5418,23 @@
       </c>
     </row>
     <row r="138" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A138" s="32">
-        <v>30</v>
-      </c>
-      <c r="B138" s="33" t="s">
-        <v>191</v>
-      </c>
-      <c r="C138" s="34">
-        <v>30</v>
-      </c>
-      <c r="D138" s="32" t="s">
-        <v>242</v>
-      </c>
-      <c r="E138" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="F138" s="32" t="s">
-        <v>192</v>
+      <c r="A138" s="30">
+        <v>25</v>
+      </c>
+      <c r="B138" s="31" t="s">
+        <v>288</v>
+      </c>
+      <c r="C138" s="32">
+        <v>25</v>
+      </c>
+      <c r="D138" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="E138" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="F138" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G138" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F138),0)&gt;0), MAX($G$1:G137)+1, ""))</f>
@@ -5412,23 +5446,23 @@
       </c>
     </row>
     <row r="139" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A139" s="32">
-        <v>30</v>
-      </c>
-      <c r="B139" s="33" t="s">
-        <v>248</v>
-      </c>
-      <c r="C139" s="34">
-        <v>30</v>
-      </c>
-      <c r="D139" s="32" t="s">
-        <v>219</v>
-      </c>
-      <c r="E139" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F139" s="32" t="s">
-        <v>190</v>
+      <c r="A139" s="30">
+        <v>25</v>
+      </c>
+      <c r="B139" s="31" t="s">
+        <v>289</v>
+      </c>
+      <c r="C139" s="32">
+        <v>25</v>
+      </c>
+      <c r="D139" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="E139" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="F139" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G139" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F139),0)&gt;0), MAX($G$1:G138)+1, ""))</f>
@@ -5440,23 +5474,23 @@
       </c>
     </row>
     <row r="140" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A140" s="32">
-        <v>30</v>
-      </c>
-      <c r="B140" s="33" t="s">
-        <v>188</v>
-      </c>
-      <c r="C140" s="34">
-        <v>30</v>
-      </c>
-      <c r="D140" s="32" t="s">
-        <v>231</v>
-      </c>
-      <c r="E140" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F140" s="32" t="s">
-        <v>189</v>
+      <c r="A140" s="26">
+        <v>25</v>
+      </c>
+      <c r="B140" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="C140" s="28">
+        <v>25</v>
+      </c>
+      <c r="D140" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E140" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="F140" s="26" t="s">
+        <v>255</v>
       </c>
       <c r="G140" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F140),0)&gt;0), MAX($G$1:G139)+1, ""))</f>
@@ -5468,23 +5502,23 @@
       </c>
     </row>
     <row r="141" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A141" s="32">
-        <v>30</v>
-      </c>
-      <c r="B141" s="33" t="s">
-        <v>186</v>
-      </c>
-      <c r="C141" s="34">
-        <v>30</v>
-      </c>
-      <c r="D141" s="32" t="s">
-        <v>230</v>
-      </c>
-      <c r="E141" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="F141" s="32" t="s">
-        <v>187</v>
+      <c r="A141" s="30">
+        <v>25</v>
+      </c>
+      <c r="B141" s="31" t="s">
+        <v>287</v>
+      </c>
+      <c r="C141" s="32">
+        <v>25</v>
+      </c>
+      <c r="D141" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="E141" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="F141" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G141" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F141),0)&gt;0), MAX($G$1:G140)+1, ""))</f>
@@ -5496,26 +5530,26 @@
       </c>
     </row>
     <row r="142" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A142" s="32">
-        <v>30</v>
-      </c>
-      <c r="B142" s="33" t="s">
-        <v>184</v>
-      </c>
-      <c r="C142" s="34">
-        <v>30</v>
-      </c>
-      <c r="D142" s="32" t="s">
-        <v>241</v>
-      </c>
-      <c r="E142" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="F142" s="32" t="s">
-        <v>185</v>
+      <c r="A142" s="26">
+        <v>25</v>
+      </c>
+      <c r="B142" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C142" s="28">
+        <v>25</v>
+      </c>
+      <c r="D142" s="26" t="s">
+        <v>228</v>
+      </c>
+      <c r="E142" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="F142" s="26" t="s">
+        <v>151</v>
       </c>
       <c r="G142" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F142),0)&gt;0), MAX($G$1:G141)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F142),0)&gt;0), MAX($G$1:G140)+1, ""))</f>
         <v/>
       </c>
       <c r="H142" s="21" t="b">
@@ -5524,23 +5558,23 @@
       </c>
     </row>
     <row r="143" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A143" s="32">
+      <c r="A143" s="30">
         <v>30</v>
       </c>
-      <c r="B143" s="33" t="s">
-        <v>339</v>
-      </c>
-      <c r="C143" s="34">
+      <c r="B143" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="C143" s="32">
         <v>30</v>
       </c>
-      <c r="D143" s="32">
-        <v>2.9</v>
-      </c>
-      <c r="E143" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="F143" s="32" t="s">
-        <v>340</v>
+      <c r="D143" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="E143" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="F143" s="30" t="s">
+        <v>195</v>
       </c>
       <c r="G143" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F143),0)&gt;0), MAX($G$1:G142)+1, ""))</f>
@@ -5552,26 +5586,26 @@
       </c>
     </row>
     <row r="144" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A144" s="32">
+      <c r="A144" s="30">
         <v>30</v>
       </c>
-      <c r="B144" s="33" t="s">
-        <v>182</v>
-      </c>
-      <c r="C144" s="34">
+      <c r="B144" s="31" t="s">
+        <v>193</v>
+      </c>
+      <c r="C144" s="32">
         <v>30</v>
       </c>
-      <c r="D144" s="32" t="s">
-        <v>240</v>
-      </c>
-      <c r="E144" s="33" t="s">
+      <c r="D144" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="E144" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="F144" s="32" t="s">
-        <v>183</v>
+      <c r="F144" s="30" t="s">
+        <v>192</v>
       </c>
       <c r="G144" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F144),0)&gt;0), MAX($G$1:G142)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F144),0)&gt;0), MAX($G$1:G143)+1, ""))</f>
         <v/>
       </c>
       <c r="H144" s="21" t="b">
@@ -5580,23 +5614,23 @@
       </c>
     </row>
     <row r="145" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A145" s="26">
-        <v>40</v>
-      </c>
-      <c r="B145" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="C145" s="28">
-        <v>40</v>
-      </c>
-      <c r="D145" s="26" t="s">
-        <v>245</v>
-      </c>
-      <c r="E145" s="27" t="s">
-        <v>200</v>
-      </c>
-      <c r="F145" s="26" t="s">
-        <v>201</v>
+      <c r="A145" s="30">
+        <v>30</v>
+      </c>
+      <c r="B145" s="31" t="s">
+        <v>191</v>
+      </c>
+      <c r="C145" s="32">
+        <v>30</v>
+      </c>
+      <c r="D145" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="E145" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="F145" s="30" t="s">
+        <v>192</v>
       </c>
       <c r="G145" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B145),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E145),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F145),0)&gt;0), MAX($G$1:G144)+1, ""))</f>
@@ -5608,23 +5642,23 @@
       </c>
     </row>
     <row r="146" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A146" s="26">
-        <v>40</v>
-      </c>
-      <c r="B146" s="27" t="s">
-        <v>196</v>
-      </c>
-      <c r="C146" s="28">
-        <v>40</v>
-      </c>
-      <c r="D146" s="26" t="s">
-        <v>244</v>
-      </c>
-      <c r="E146" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="F146" s="26" t="s">
-        <v>198</v>
+      <c r="A146" s="30">
+        <v>30</v>
+      </c>
+      <c r="B146" s="31" t="s">
+        <v>248</v>
+      </c>
+      <c r="C146" s="32">
+        <v>30</v>
+      </c>
+      <c r="D146" s="30" t="s">
+        <v>219</v>
+      </c>
+      <c r="E146" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F146" s="30" t="s">
+        <v>190</v>
       </c>
       <c r="G146" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F146),0)&gt;0), MAX($G$1:G145)+1, ""))</f>
@@ -5636,23 +5670,23 @@
       </c>
     </row>
     <row r="147" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A147" s="26">
-        <v>40</v>
-      </c>
-      <c r="B147" s="27" t="s">
-        <v>251</v>
-      </c>
-      <c r="C147" s="28">
-        <v>40</v>
-      </c>
-      <c r="D147" s="26">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="E147" s="27" t="s">
-        <v>252</v>
-      </c>
-      <c r="F147" s="26" t="s">
-        <v>253</v>
+      <c r="A147" s="30">
+        <v>30</v>
+      </c>
+      <c r="B147" s="31" t="s">
+        <v>188</v>
+      </c>
+      <c r="C147" s="32">
+        <v>30</v>
+      </c>
+      <c r="D147" s="30" t="s">
+        <v>231</v>
+      </c>
+      <c r="E147" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F147" s="30" t="s">
+        <v>189</v>
       </c>
       <c r="G147" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F147),0)&gt;0), MAX($G$1:G146)+1, ""))</f>
@@ -5664,23 +5698,23 @@
       </c>
     </row>
     <row r="148" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A148" s="26">
-        <v>45</v>
-      </c>
-      <c r="B148" s="27" t="s">
-        <v>296</v>
-      </c>
-      <c r="C148" s="28">
-        <v>45</v>
-      </c>
-      <c r="D148" s="26">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="E148" s="27" t="s">
-        <v>297</v>
-      </c>
-      <c r="F148" s="26" t="s">
-        <v>298</v>
+      <c r="A148" s="30">
+        <v>30</v>
+      </c>
+      <c r="B148" s="31" t="s">
+        <v>186</v>
+      </c>
+      <c r="C148" s="32">
+        <v>30</v>
+      </c>
+      <c r="D148" s="30" t="s">
+        <v>230</v>
+      </c>
+      <c r="E148" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="F148" s="30" t="s">
+        <v>187</v>
       </c>
       <c r="G148" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F148),0)&gt;0), MAX($G$1:G147)+1, ""))</f>
@@ -5692,52 +5726,200 @@
       </c>
     </row>
     <row r="149" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A149" s="30"/>
-      <c r="B149" s="31"/>
-      <c r="C149" s="30"/>
-      <c r="D149" s="30"/>
-      <c r="E149" s="31"/>
-      <c r="F149" s="30"/>
-      <c r="G149" s="31"/>
+      <c r="A149" s="30">
+        <v>30</v>
+      </c>
+      <c r="B149" s="31" t="s">
+        <v>184</v>
+      </c>
+      <c r="C149" s="32">
+        <v>30</v>
+      </c>
+      <c r="D149" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="E149" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="F149" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="G149" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B149),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E149),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F149),0)&gt;0), MAX($G$1:G148)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H149" s="21" t="b">
+        <f>A149=C149</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="150" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A150" s="30"/>
-      <c r="B150" s="31"/>
-      <c r="C150" s="30"/>
-      <c r="D150" s="30"/>
-      <c r="E150" s="31"/>
-      <c r="F150" s="30"/>
-      <c r="G150" s="31"/>
+      <c r="A150" s="30">
+        <v>30</v>
+      </c>
+      <c r="B150" s="31" t="s">
+        <v>339</v>
+      </c>
+      <c r="C150" s="32">
+        <v>30</v>
+      </c>
+      <c r="D150" s="30">
+        <v>2.9</v>
+      </c>
+      <c r="E150" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="F150" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="G150" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B150),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E150),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F150),0)&gt;0), MAX($G$1:G149)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H150" s="21" t="b">
+        <f>A150=C150</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="151" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A151" s="1"/>
-      <c r="C151" s="1"/>
-      <c r="D151" s="1"/>
-      <c r="F151" s="1"/>
+      <c r="A151" s="30">
+        <v>30</v>
+      </c>
+      <c r="B151" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="C151" s="32">
+        <v>30</v>
+      </c>
+      <c r="D151" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="E151" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="F151" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="G151" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B151),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E151),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F151),0)&gt;0), MAX($G$1:G149)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H151" s="21" t="b">
+        <f>A151=C151</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="152" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A152" s="1"/>
-      <c r="C152" s="1"/>
-      <c r="D152" s="1"/>
-      <c r="F152" s="1"/>
+      <c r="A152" s="26">
+        <v>40</v>
+      </c>
+      <c r="B152" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="C152" s="28">
+        <v>40</v>
+      </c>
+      <c r="D152" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="E152" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="F152" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="G152" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B152),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E152),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F152),0)&gt;0), MAX($G$1:G151)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H152" s="21" t="b">
+        <f>A152=C152</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="153" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A153" s="1"/>
-      <c r="C153" s="1"/>
-      <c r="D153" s="1"/>
-      <c r="F153" s="1"/>
+      <c r="A153" s="26">
+        <v>40</v>
+      </c>
+      <c r="B153" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="C153" s="28">
+        <v>40</v>
+      </c>
+      <c r="D153" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="E153" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="F153" s="26" t="s">
+        <v>198</v>
+      </c>
+      <c r="G153" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B153),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E153),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F153),0)&gt;0), MAX($G$1:G152)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H153" s="21" t="b">
+        <f>A153=C153</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="154" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A154" s="1"/>
-      <c r="C154" s="1"/>
-      <c r="D154" s="1"/>
-      <c r="F154" s="1"/>
+      <c r="A154" s="26">
+        <v>40</v>
+      </c>
+      <c r="B154" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="C154" s="28">
+        <v>40</v>
+      </c>
+      <c r="D154" s="26">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E154" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="F154" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="G154" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B154),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E154),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F154),0)&gt;0), MAX($G$1:G153)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H154" s="21" t="b">
+        <f>A154=C154</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="155" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A155" s="1"/>
-      <c r="C155" s="1"/>
-      <c r="D155" s="1"/>
-      <c r="F155" s="1"/>
+      <c r="A155" s="26">
+        <v>45</v>
+      </c>
+      <c r="B155" s="27" t="s">
+        <v>296</v>
+      </c>
+      <c r="C155" s="28">
+        <v>45</v>
+      </c>
+      <c r="D155" s="26">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E155" s="27" t="s">
+        <v>297</v>
+      </c>
+      <c r="F155" s="26" t="s">
+        <v>298</v>
+      </c>
+      <c r="G155" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F155),0)&gt;0), MAX($G$1:G154)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H155" s="21" t="b">
+        <f>A155=C155</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="156" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
@@ -11018,6 +11200,12 @@
       <c r="C1035" s="1"/>
       <c r="D1035" s="1"/>
       <c r="F1035" s="1"/>
+    </row>
+    <row r="1036" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1036" s="1"/>
+      <c r="C1036" s="1"/>
+      <c r="D1036" s="1"/>
+      <c r="F1036" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H148">
@@ -11027,10 +11215,10 @@
       <sortCondition ref="D2:D147"/>
     </sortState>
   </autoFilter>
-  <sortState ref="A2:H140">
-    <sortCondition ref="A2:A140"/>
-    <sortCondition ref="B2:B140"/>
-    <sortCondition ref="D2:D140"/>
+  <sortState ref="A2:H155">
+    <sortCondition ref="A2:A155"/>
+    <sortCondition ref="B2:B155"/>
+    <sortCondition ref="D2:D155"/>
   </sortState>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="360">
   <si>
     <t>Grupo</t>
   </si>
@@ -1093,6 +1093,18 @@
   </si>
   <si>
     <t>21760-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOMAS VALENTINA </t>
+  </si>
+  <si>
+    <t>21721-280</t>
+  </si>
+  <si>
+    <t>MOEMA</t>
+  </si>
+  <si>
+    <t>21710-370</t>
   </si>
 </sst>
 </file>
@@ -2545,19 +2557,19 @@
         <v>15</v>
       </c>
       <c r="B34" s="27" t="s">
-        <v>51</v>
+        <v>356</v>
       </c>
       <c r="C34" s="28">
         <v>15</v>
       </c>
-      <c r="D34" s="26" t="s">
-        <v>215</v>
+      <c r="D34" s="26">
+        <v>1.5</v>
       </c>
       <c r="E34" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F34" s="26" t="s">
-        <v>52</v>
+        <v>357</v>
       </c>
       <c r="G34" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B34),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E34),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F34),0)&gt;0), MAX($G$1:G33)+1, ""))</f>
@@ -2573,19 +2585,19 @@
         <v>15</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C35" s="28">
         <v>15</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="E35" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G35" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F35),0)&gt;0), MAX($G$1:G34)+1, ""))</f>
@@ -2601,19 +2613,19 @@
         <v>15</v>
       </c>
       <c r="B36" s="27" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C36" s="28">
         <v>15</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="E36" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F36" s="26" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G36" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B36),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E36),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F36),0)&gt;0), MAX($G$1:G35)+1, ""))</f>
@@ -2629,19 +2641,19 @@
         <v>15</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C37" s="28">
         <v>15</v>
       </c>
       <c r="D37" s="26" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="E37" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G37" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F37),0)&gt;0), MAX($G$1:G36)+1, ""))</f>
@@ -2657,19 +2669,19 @@
         <v>15</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C38" s="28">
         <v>15</v>
       </c>
       <c r="D38" s="26" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="E38" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F38" s="26" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G38" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F38),0)&gt;0), MAX($G$1:G37)+1, ""))</f>
@@ -2685,19 +2697,19 @@
         <v>15</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>310</v>
+        <v>41</v>
       </c>
       <c r="C39" s="28">
         <v>15</v>
       </c>
-      <c r="D39" s="26">
-        <v>2.2000000000000002</v>
+      <c r="D39" s="26" t="s">
+        <v>214</v>
       </c>
       <c r="E39" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F39" s="26" t="s">
-        <v>295</v>
+        <v>42</v>
       </c>
       <c r="G39" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B39),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E39),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F39),0)&gt;0), MAX($G$1:G38)+1, ""))</f>
@@ -2713,19 +2725,19 @@
         <v>15</v>
       </c>
       <c r="B40" s="27" t="s">
-        <v>246</v>
+        <v>310</v>
       </c>
       <c r="C40" s="28">
         <v>15</v>
       </c>
       <c r="D40" s="26">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E40" s="27" t="s">
-        <v>247</v>
+        <v>8</v>
       </c>
       <c r="F40" s="26" t="s">
-        <v>204</v>
+        <v>295</v>
       </c>
       <c r="G40" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B40),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E40),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F40),0)&gt;0), MAX($G$1:G39)+1, ""))</f>
@@ -2741,19 +2753,19 @@
         <v>15</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>39</v>
+        <v>246</v>
       </c>
       <c r="C41" s="28">
         <v>15</v>
       </c>
-      <c r="D41" s="26" t="s">
-        <v>213</v>
+      <c r="D41" s="26">
+        <v>2.1</v>
       </c>
       <c r="E41" s="27" t="s">
-        <v>8</v>
+        <v>247</v>
       </c>
       <c r="F41" s="26" t="s">
-        <v>40</v>
+        <v>204</v>
       </c>
       <c r="G41" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B41),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E41),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F41),0)&gt;0), MAX($G$1:G40)+1, ""))</f>
@@ -2769,19 +2781,19 @@
         <v>15</v>
       </c>
       <c r="B42" s="27" t="s">
-        <v>343</v>
+        <v>39</v>
       </c>
       <c r="C42" s="28">
         <v>15</v>
       </c>
-      <c r="D42" s="26">
-        <v>1.4</v>
+      <c r="D42" s="26" t="s">
+        <v>213</v>
       </c>
       <c r="E42" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F42" s="26" t="s">
-        <v>349</v>
+        <v>40</v>
       </c>
       <c r="G42" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B42),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E42),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F42),0)&gt;0), MAX($G$1:G41)+1, ""))</f>
@@ -2797,19 +2809,19 @@
         <v>15</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>35</v>
+        <v>343</v>
       </c>
       <c r="C43" s="28">
         <v>15</v>
       </c>
-      <c r="D43" s="26" t="s">
-        <v>212</v>
+      <c r="D43" s="26">
+        <v>1.4</v>
       </c>
       <c r="E43" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F43" s="26" t="s">
-        <v>36</v>
+        <v>349</v>
       </c>
       <c r="G43" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F43),0)&gt;0), MAX($G$1:G42)+1, ""))</f>
@@ -2825,19 +2837,19 @@
         <v>15</v>
       </c>
       <c r="B44" s="27" t="s">
-        <v>282</v>
+        <v>35</v>
       </c>
       <c r="C44" s="28">
         <v>15</v>
       </c>
       <c r="D44" s="26" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E44" s="27" t="s">
-        <v>269</v>
+        <v>8</v>
       </c>
       <c r="F44" s="26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G44" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F44),0)&gt;0), MAX($G$1:G43)+1, ""))</f>
@@ -2849,23 +2861,23 @@
       </c>
     </row>
     <row r="45" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A45" s="33">
-        <v>17</v>
-      </c>
-      <c r="B45" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="C45" s="35">
-        <v>17</v>
-      </c>
-      <c r="D45" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="E45" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" s="33" t="s">
-        <v>73</v>
+      <c r="A45" s="26">
+        <v>15</v>
+      </c>
+      <c r="B45" s="27" t="s">
+        <v>282</v>
+      </c>
+      <c r="C45" s="28">
+        <v>15</v>
+      </c>
+      <c r="D45" s="26" t="s">
+        <v>211</v>
+      </c>
+      <c r="E45" s="27" t="s">
+        <v>269</v>
+      </c>
+      <c r="F45" s="26" t="s">
+        <v>34</v>
       </c>
       <c r="G45" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F45),0)&gt;0), MAX($G$1:G44)+1, ""))</f>
@@ -2881,19 +2893,19 @@
         <v>17</v>
       </c>
       <c r="B46" s="34" t="s">
-        <v>283</v>
+        <v>72</v>
       </c>
       <c r="C46" s="35">
         <v>17</v>
       </c>
       <c r="D46" s="33" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="E46" s="34" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="F46" s="33" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G46" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F46),0)&gt;0), MAX($G$1:G45)+1, ""))</f>
@@ -2905,53 +2917,53 @@
       </c>
     </row>
     <row r="47" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A47" s="26">
+      <c r="A47" s="33">
         <v>17</v>
       </c>
-      <c r="B47" s="27" t="s">
-        <v>315</v>
-      </c>
-      <c r="C47" s="28">
+      <c r="B47" s="34" t="s">
+        <v>283</v>
+      </c>
+      <c r="C47" s="35">
         <v>17</v>
       </c>
-      <c r="D47" s="26">
-        <v>1.7</v>
-      </c>
-      <c r="E47" s="27" t="s">
+      <c r="D47" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="E47" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="F47" s="26" t="s">
-        <v>321</v>
-      </c>
-      <c r="G47" s="29"/>
+      <c r="F47" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="G47" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F47),0)&gt;0), MAX($G$1:G46)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H47" s="21" t="b">
         <f>A47=C47</f>
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A48" s="33">
+      <c r="A48" s="26">
         <v>17</v>
       </c>
-      <c r="B48" s="34" t="s">
-        <v>63</v>
-      </c>
-      <c r="C48" s="35">
+      <c r="B48" s="27" t="s">
+        <v>315</v>
+      </c>
+      <c r="C48" s="28">
         <v>17</v>
       </c>
-      <c r="D48" s="33" t="s">
-        <v>217</v>
-      </c>
-      <c r="E48" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F48" s="33" t="s">
-        <v>64</v>
-      </c>
-      <c r="G48" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F48),0)&gt;0), MAX($G$1:G47)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D48" s="26">
+        <v>1.7</v>
+      </c>
+      <c r="E48" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="F48" s="26" t="s">
+        <v>321</v>
+      </c>
+      <c r="G48" s="29"/>
       <c r="H48" s="21" t="b">
         <f>A48=C48</f>
         <v>1</v>
@@ -2962,19 +2974,19 @@
         <v>17</v>
       </c>
       <c r="B49" s="34" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C49" s="35">
         <v>17</v>
       </c>
       <c r="D49" s="33" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E49" s="34" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="F49" s="33" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G49" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F49),0)&gt;0), MAX($G$1:G48)+1, ""))</f>
@@ -2986,25 +2998,28 @@
       </c>
     </row>
     <row r="50" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A50" s="26">
+      <c r="A50" s="33">
         <v>17</v>
       </c>
-      <c r="B50" s="27" t="s">
-        <v>317</v>
-      </c>
-      <c r="C50" s="28">
+      <c r="B50" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="C50" s="35">
         <v>17</v>
       </c>
-      <c r="D50" s="26">
-        <v>3</v>
-      </c>
-      <c r="E50" s="27" t="s">
+      <c r="D50" s="33" t="s">
+        <v>218</v>
+      </c>
+      <c r="E50" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="F50" s="26" t="s">
-        <v>323</v>
-      </c>
-      <c r="G50" s="29"/>
+      <c r="F50" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="G50" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F50),0)&gt;0), MAX($G$1:G49)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H50" s="21" t="b">
         <f>A50=C50</f>
         <v>1</v>
@@ -3015,24 +3030,21 @@
         <v>17</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>342</v>
+        <v>317</v>
       </c>
       <c r="C51" s="28">
         <v>17</v>
       </c>
       <c r="D51" s="26">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="E51" s="27" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="F51" s="26" t="s">
-        <v>351</v>
-      </c>
-      <c r="G51" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F51),0)&gt;0), MAX($G$1:G49)+1, ""))</f>
-        <v/>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="G51" s="29"/>
       <c r="H51" s="21" t="b">
         <f>A51=C51</f>
         <v>1</v>
@@ -3043,74 +3055,77 @@
         <v>17</v>
       </c>
       <c r="B52" s="27" t="s">
-        <v>318</v>
+        <v>342</v>
       </c>
       <c r="C52" s="28">
         <v>17</v>
       </c>
       <c r="D52" s="26">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="E52" s="27" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="F52" s="26" t="s">
-        <v>324</v>
-      </c>
-      <c r="G52" s="29"/>
+        <v>351</v>
+      </c>
+      <c r="G52" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F52),0)&gt;0), MAX($G$1:G50)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H52" s="21" t="b">
         <f>A52=C52</f>
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="36">
+      <c r="A53" s="26">
         <v>17</v>
       </c>
-      <c r="B53" s="37" t="s">
-        <v>291</v>
-      </c>
-      <c r="C53" s="38">
+      <c r="B53" s="27" t="s">
+        <v>318</v>
+      </c>
+      <c r="C53" s="28">
         <v>17</v>
       </c>
-      <c r="D53" s="36" t="s">
-        <v>221</v>
-      </c>
-      <c r="E53" s="37" t="s">
+      <c r="D53" s="26">
+        <v>1.9</v>
+      </c>
+      <c r="E53" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="F53" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="G53" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F53),0)&gt;0), MAX($G$1:G52)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="F53" s="26" t="s">
+        <v>324</v>
+      </c>
+      <c r="G53" s="29"/>
       <c r="H53" s="21" t="b">
         <f>A53=C53</f>
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A54" s="26">
+      <c r="A54" s="36">
         <v>17</v>
       </c>
-      <c r="B54" s="27" t="s">
-        <v>316</v>
-      </c>
-      <c r="C54" s="28">
+      <c r="B54" s="37" t="s">
+        <v>291</v>
+      </c>
+      <c r="C54" s="38">
         <v>17</v>
       </c>
-      <c r="D54" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E54" s="27" t="s">
+      <c r="D54" s="36" t="s">
+        <v>221</v>
+      </c>
+      <c r="E54" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="F54" s="26" t="s">
-        <v>322</v>
-      </c>
-      <c r="G54" s="29"/>
+      <c r="F54" s="36" t="s">
+        <v>113</v>
+      </c>
+      <c r="G54" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F54),0)&gt;0), MAX($G$1:G53)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H54" s="21" t="b">
         <f>A54=C54</f>
         <v>1</v>
@@ -3121,19 +3136,19 @@
         <v>17</v>
       </c>
       <c r="B55" s="27" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C55" s="28">
         <v>17</v>
       </c>
       <c r="D55" s="26">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E55" s="27" t="s">
         <v>61</v>
       </c>
       <c r="F55" s="26" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="G55" s="29"/>
       <c r="H55" s="21" t="b">
@@ -3142,28 +3157,25 @@
       </c>
     </row>
     <row r="56" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A56" s="36">
+      <c r="A56" s="26">
         <v>17</v>
       </c>
-      <c r="B56" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="C56" s="38">
+      <c r="B56" s="27" t="s">
+        <v>319</v>
+      </c>
+      <c r="C56" s="28">
         <v>17</v>
       </c>
-      <c r="D56" s="36" t="s">
-        <v>222</v>
-      </c>
-      <c r="E56" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F56" s="36" t="s">
-        <v>109</v>
-      </c>
-      <c r="G56" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F56),0)&gt;0), MAX($G$1:G55)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D56" s="26">
+        <v>2</v>
+      </c>
+      <c r="E56" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="F56" s="26" t="s">
+        <v>325</v>
+      </c>
+      <c r="G56" s="29"/>
       <c r="H56" s="21" t="b">
         <f>A56=C56</f>
         <v>1</v>
@@ -3174,19 +3186,19 @@
         <v>17</v>
       </c>
       <c r="B57" s="37" t="s">
-        <v>305</v>
+        <v>108</v>
       </c>
       <c r="C57" s="38">
         <v>17</v>
       </c>
       <c r="D57" s="36" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="E57" s="37" t="s">
-        <v>306</v>
+        <v>8</v>
       </c>
       <c r="F57" s="36" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G57" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F57),0)&gt;0), MAX($G$1:G56)+1, ""))</f>
@@ -3198,26 +3210,26 @@
       </c>
     </row>
     <row r="58" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A58" s="33">
+      <c r="A58" s="36">
         <v>17</v>
       </c>
-      <c r="B58" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="C58" s="35">
+      <c r="B58" s="37" t="s">
+        <v>305</v>
+      </c>
+      <c r="C58" s="38">
         <v>17</v>
       </c>
-      <c r="D58" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="E58" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" s="33" t="s">
-        <v>54</v>
+      <c r="D58" s="36" t="s">
+        <v>231</v>
+      </c>
+      <c r="E58" s="37" t="s">
+        <v>306</v>
+      </c>
+      <c r="F58" s="36" t="s">
+        <v>107</v>
       </c>
       <c r="G58" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F58),0)&gt;0), MAX($G$1:G53)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F58),0)&gt;0), MAX($G$1:G57)+1, ""))</f>
         <v/>
       </c>
       <c r="H58" s="21" t="b">
@@ -3230,22 +3242,22 @@
         <v>17</v>
       </c>
       <c r="B59" s="34" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C59" s="35">
         <v>17</v>
       </c>
       <c r="D59" s="33" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E59" s="34" t="s">
         <v>8</v>
       </c>
       <c r="F59" s="33" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G59" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F59),0)&gt;0), MAX($G$1:G58)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F59),0)&gt;0), MAX($G$1:G54)+1, ""))</f>
         <v/>
       </c>
       <c r="H59" s="21" t="b">
@@ -3254,23 +3266,23 @@
       </c>
     </row>
     <row r="60" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A60" s="36">
+      <c r="A60" s="26">
         <v>17</v>
       </c>
-      <c r="B60" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="C60" s="38">
+      <c r="B60" s="27" t="s">
+        <v>358</v>
+      </c>
+      <c r="C60" s="28">
         <v>17</v>
       </c>
-      <c r="D60" s="36" t="s">
-        <v>221</v>
-      </c>
-      <c r="E60" s="37" t="s">
+      <c r="D60" s="26">
+        <v>1.8</v>
+      </c>
+      <c r="E60" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F60" s="36" t="s">
-        <v>100</v>
+      <c r="F60" s="26" t="s">
+        <v>359</v>
       </c>
       <c r="G60" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F60),0)&gt;0), MAX($G$1:G59)+1, ""))</f>
@@ -3282,23 +3294,23 @@
       </c>
     </row>
     <row r="61" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A61" s="36">
+      <c r="A61" s="33">
         <v>17</v>
       </c>
-      <c r="B61" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="C61" s="38">
+      <c r="B61" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="C61" s="35">
         <v>17</v>
       </c>
-      <c r="D61" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="E61" s="37" t="s">
+      <c r="D61" s="33" t="s">
+        <v>213</v>
+      </c>
+      <c r="E61" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F61" s="36" t="s">
-        <v>96</v>
+      <c r="F61" s="33" t="s">
+        <v>50</v>
       </c>
       <c r="G61" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F61),0)&gt;0), MAX($G$1:G60)+1, ""))</f>
@@ -3310,54 +3322,58 @@
       </c>
     </row>
     <row r="62" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A62" s="33">
+      <c r="A62" s="36">
         <v>17</v>
       </c>
-      <c r="B62" s="34" t="s">
-        <v>329</v>
-      </c>
-      <c r="C62" s="35">
+      <c r="B62" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="C62" s="38">
         <v>17</v>
       </c>
-      <c r="D62" s="33">
-        <v>1.9</v>
-      </c>
-      <c r="E62" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="F62" s="33" t="s">
-        <v>331</v>
-      </c>
-      <c r="G62" s="29" t="s">
-        <v>328</v>
+      <c r="D62" s="36" t="s">
+        <v>221</v>
+      </c>
+      <c r="E62" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="G62" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F62),0)&gt;0), MAX($G$1:G61)+1, ""))</f>
+        <v/>
       </c>
       <c r="H62" s="21" t="b">
+        <f>A62=C62</f>
         <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A63" s="33">
+      <c r="A63" s="36">
         <v>17</v>
       </c>
-      <c r="B63" s="34" t="s">
-        <v>327</v>
-      </c>
-      <c r="C63" s="35">
+      <c r="B63" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="C63" s="38">
         <v>17</v>
       </c>
-      <c r="D63" s="33">
-        <v>1.9</v>
-      </c>
-      <c r="E63" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="F63" s="33" t="s">
-        <v>331</v>
-      </c>
-      <c r="G63" s="29" t="s">
-        <v>328</v>
+      <c r="D63" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E63" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F63" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="G63" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F63),0)&gt;0), MAX($G$1:G62)+1, ""))</f>
+        <v/>
       </c>
       <c r="H63" s="21" t="b">
+        <f>A63=C63</f>
         <v>1</v>
       </c>
     </row>
@@ -3366,7 +3382,7 @@
         <v>17</v>
       </c>
       <c r="B64" s="34" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C64" s="35">
         <v>17</v>
@@ -3392,54 +3408,50 @@
         <v>17</v>
       </c>
       <c r="B65" s="34" t="s">
-        <v>37</v>
+        <v>327</v>
       </c>
       <c r="C65" s="35">
         <v>17</v>
       </c>
-      <c r="D65" s="33" t="s">
-        <v>216</v>
+      <c r="D65" s="33">
+        <v>1.9</v>
       </c>
       <c r="E65" s="34" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="F65" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="G65" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F65),0)&gt;0), MAX($G$1:G64)+1, ""))</f>
-        <v/>
+        <v>331</v>
+      </c>
+      <c r="G65" s="29" t="s">
+        <v>328</v>
       </c>
       <c r="H65" s="21" t="b">
-        <f>A65=C65</f>
         <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A66" s="36">
+      <c r="A66" s="33">
         <v>17</v>
       </c>
-      <c r="B66" s="37" t="s">
-        <v>85</v>
-      </c>
-      <c r="C66" s="38">
+      <c r="B66" s="34" t="s">
+        <v>330</v>
+      </c>
+      <c r="C66" s="35">
         <v>17</v>
       </c>
-      <c r="D66" s="36" t="s">
-        <v>221</v>
-      </c>
-      <c r="E66" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F66" s="36" t="s">
-        <v>86</v>
-      </c>
-      <c r="G66" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F66),0)&gt;0), MAX($G$1:G65)+1, ""))</f>
-        <v/>
+      <c r="D66" s="33">
+        <v>1.9</v>
+      </c>
+      <c r="E66" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="F66" s="33" t="s">
+        <v>331</v>
+      </c>
+      <c r="G66" s="29" t="s">
+        <v>328</v>
       </c>
       <c r="H66" s="21" t="b">
-        <f>A66=C66</f>
         <v>1</v>
       </c>
     </row>
@@ -3448,19 +3460,19 @@
         <v>17</v>
       </c>
       <c r="B67" s="34" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C67" s="35">
         <v>17</v>
       </c>
       <c r="D67" s="33" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E67" s="34" t="s">
         <v>8</v>
       </c>
       <c r="F67" s="33" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G67" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F67),0)&gt;0), MAX($G$1:G66)+1, ""))</f>
@@ -3472,52 +3484,54 @@
       </c>
     </row>
     <row r="68" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A68" s="33">
+      <c r="A68" s="36">
         <v>17</v>
       </c>
-      <c r="B68" s="34" t="s">
-        <v>30</v>
-      </c>
-      <c r="C68" s="35">
+      <c r="B68" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="C68" s="38">
         <v>17</v>
       </c>
-      <c r="D68" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="E68" s="34" t="s">
+      <c r="D68" s="36" t="s">
+        <v>221</v>
+      </c>
+      <c r="E68" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F68" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="G68" s="29" t="s">
-        <v>328</v>
+      <c r="F68" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="G68" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F68),0)&gt;0), MAX($G$1:G67)+1, ""))</f>
+        <v/>
       </c>
       <c r="H68" s="21" t="b">
+        <f>A68=C68</f>
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A69" s="30">
-        <v>20</v>
-      </c>
-      <c r="B69" s="31" t="s">
-        <v>148</v>
-      </c>
-      <c r="C69" s="32">
-        <v>20</v>
-      </c>
-      <c r="D69" s="30" t="s">
-        <v>208</v>
-      </c>
-      <c r="E69" s="31" t="s">
+      <c r="A69" s="33">
+        <v>17</v>
+      </c>
+      <c r="B69" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="C69" s="35">
+        <v>17</v>
+      </c>
+      <c r="D69" s="33" t="s">
+        <v>210</v>
+      </c>
+      <c r="E69" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F69" s="30" t="s">
-        <v>149</v>
+      <c r="F69" s="33" t="s">
+        <v>33</v>
       </c>
       <c r="G69" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F69),0)&gt;0), MAX($G$1:G65)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F69),0)&gt;0), MAX($G$1:G68)+1, ""))</f>
         <v/>
       </c>
       <c r="H69" s="21" t="b">
@@ -3526,30 +3540,28 @@
       </c>
     </row>
     <row r="70" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A70" s="30">
-        <v>20</v>
-      </c>
-      <c r="B70" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="C70" s="32">
-        <v>20</v>
-      </c>
-      <c r="D70" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="E70" s="31" t="s">
+      <c r="A70" s="33">
+        <v>17</v>
+      </c>
+      <c r="B70" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="C70" s="35">
+        <v>17</v>
+      </c>
+      <c r="D70" s="33" t="s">
+        <v>209</v>
+      </c>
+      <c r="E70" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F70" s="30" t="s">
-        <v>147</v>
-      </c>
-      <c r="G70" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F70),0)&gt;0), MAX($G$1:G69)+1, ""))</f>
-        <v/>
+      <c r="F70" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="G70" s="29" t="s">
+        <v>328</v>
       </c>
       <c r="H70" s="21" t="b">
-        <f>A70=C70</f>
         <v>1</v>
       </c>
     </row>
@@ -3558,22 +3570,22 @@
         <v>20</v>
       </c>
       <c r="B71" s="31" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C71" s="32">
         <v>20</v>
       </c>
       <c r="D71" s="30" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="E71" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F71" s="30" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G71" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F71),0)&gt;0), MAX($G$1:G70)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F71),0)&gt;0), MAX($G$1:G67)+1, ""))</f>
         <v/>
       </c>
       <c r="H71" s="21" t="b">
@@ -3586,19 +3598,19 @@
         <v>20</v>
       </c>
       <c r="B72" s="31" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C72" s="32">
         <v>20</v>
       </c>
       <c r="D72" s="30" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="E72" s="31" t="s">
-        <v>307</v>
+        <v>8</v>
       </c>
       <c r="F72" s="30" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G72" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F72),0)&gt;0), MAX($G$1:G71)+1, ""))</f>
@@ -3610,106 +3622,106 @@
       </c>
     </row>
     <row r="73" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A73" s="36">
+      <c r="A73" s="30">
         <v>20</v>
       </c>
-      <c r="B73" s="37" t="s">
-        <v>335</v>
-      </c>
-      <c r="C73" s="38">
+      <c r="B73" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="C73" s="32">
         <v>20</v>
       </c>
-      <c r="D73" s="36">
-        <v>3.4</v>
-      </c>
-      <c r="E73" s="37" t="s">
-        <v>338</v>
-      </c>
-      <c r="F73" s="36" t="s">
-        <v>336</v>
-      </c>
-      <c r="G73" s="29"/>
+      <c r="D73" s="30" t="s">
+        <v>213</v>
+      </c>
+      <c r="E73" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F73" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="G73" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F73),0)&gt;0), MAX($G$1:G72)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H73" s="21" t="b">
         <f>A73=C73</f>
         <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A74" s="36">
+      <c r="A74" s="30">
         <v>20</v>
       </c>
-      <c r="B74" s="37" t="s">
-        <v>333</v>
-      </c>
-      <c r="C74" s="38">
+      <c r="B74" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="C74" s="32">
         <v>20</v>
       </c>
-      <c r="D74" s="36">
-        <v>3.3</v>
-      </c>
-      <c r="E74" s="37" t="s">
-        <v>338</v>
-      </c>
-      <c r="F74" s="36" t="s">
-        <v>334</v>
-      </c>
-      <c r="G74" s="29"/>
+      <c r="D74" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="E74" s="31" t="s">
+        <v>307</v>
+      </c>
+      <c r="F74" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="G74" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F74),0)&gt;0), MAX($G$1:G73)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H74" s="21" t="b">
         <f>A74=C74</f>
         <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A75" s="30">
+      <c r="A75" s="36">
         <v>20</v>
       </c>
-      <c r="B75" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="C75" s="32">
+      <c r="B75" s="37" t="s">
+        <v>335</v>
+      </c>
+      <c r="C75" s="38">
         <v>20</v>
       </c>
-      <c r="D75" s="30" t="s">
-        <v>225</v>
-      </c>
-      <c r="E75" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F75" s="30" t="s">
-        <v>141</v>
-      </c>
-      <c r="G75" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F75),0)&gt;0), MAX($G$1:G74)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D75" s="36">
+        <v>3.4</v>
+      </c>
+      <c r="E75" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="F75" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="G75" s="29"/>
       <c r="H75" s="21" t="b">
         <f>A75=C75</f>
         <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A76" s="30">
+      <c r="A76" s="36">
         <v>20</v>
       </c>
-      <c r="B76" s="31" t="s">
-        <v>257</v>
-      </c>
-      <c r="C76" s="32">
+      <c r="B76" s="37" t="s">
+        <v>333</v>
+      </c>
+      <c r="C76" s="38">
         <v>20</v>
       </c>
-      <c r="D76" s="30" t="s">
-        <v>227</v>
-      </c>
-      <c r="E76" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F76" s="30" t="s">
-        <v>258</v>
-      </c>
-      <c r="G76" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F76),0)&gt;0), MAX($G$1:G75)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D76" s="36">
+        <v>3.3</v>
+      </c>
+      <c r="E76" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="F76" s="36" t="s">
+        <v>334</v>
+      </c>
+      <c r="G76" s="29"/>
       <c r="H76" s="21" t="b">
         <f>A76=C76</f>
         <v>1</v>
@@ -3720,19 +3732,19 @@
         <v>20</v>
       </c>
       <c r="B77" s="31" t="s">
-        <v>256</v>
+        <v>140</v>
       </c>
       <c r="C77" s="32">
         <v>20</v>
       </c>
-      <c r="D77" s="30">
-        <v>4.2</v>
+      <c r="D77" s="30" t="s">
+        <v>225</v>
       </c>
       <c r="E77" s="31" t="s">
-        <v>307</v>
-      </c>
-      <c r="F77" s="30">
-        <v>21765430</v>
+        <v>8</v>
+      </c>
+      <c r="F77" s="30" t="s">
+        <v>141</v>
       </c>
       <c r="G77" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F77),0)&gt;0), MAX($G$1:G76)+1, ""))</f>
@@ -3748,19 +3760,19 @@
         <v>20</v>
       </c>
       <c r="B78" s="31" t="s">
-        <v>138</v>
+        <v>257</v>
       </c>
       <c r="C78" s="32">
         <v>20</v>
       </c>
       <c r="D78" s="30" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="E78" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F78" s="30" t="s">
-        <v>139</v>
+        <v>258</v>
       </c>
       <c r="G78" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F78),0)&gt;0), MAX($G$1:G77)+1, ""))</f>
@@ -3776,19 +3788,19 @@
         <v>20</v>
       </c>
       <c r="B79" s="31" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="C79" s="32">
         <v>20</v>
       </c>
-      <c r="D79" s="30" t="s">
-        <v>224</v>
+      <c r="D79" s="30">
+        <v>4.2</v>
       </c>
       <c r="E79" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F79" s="30" t="s">
-        <v>137</v>
+        <v>307</v>
+      </c>
+      <c r="F79" s="30">
+        <v>21765430</v>
       </c>
       <c r="G79" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F79),0)&gt;0), MAX($G$1:G78)+1, ""))</f>
@@ -3804,19 +3816,19 @@
         <v>20</v>
       </c>
       <c r="B80" s="31" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C80" s="32">
         <v>20</v>
       </c>
       <c r="D80" s="30" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="E80" s="31" t="s">
-        <v>307</v>
+        <v>8</v>
       </c>
       <c r="F80" s="30" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G80" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F80),0)&gt;0), MAX($G$1:G79)+1, ""))</f>
@@ -3832,19 +3844,19 @@
         <v>20</v>
       </c>
       <c r="B81" s="31" t="s">
-        <v>132</v>
+        <v>267</v>
       </c>
       <c r="C81" s="32">
         <v>20</v>
       </c>
       <c r="D81" s="30" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="E81" s="31" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="F81" s="30" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G81" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F81),0)&gt;0), MAX($G$1:G80)+1, ""))</f>
@@ -3856,23 +3868,23 @@
       </c>
     </row>
     <row r="82" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A82" s="26">
+      <c r="A82" s="30">
         <v>20</v>
       </c>
-      <c r="B82" s="27" t="s">
-        <v>314</v>
-      </c>
-      <c r="C82" s="28">
+      <c r="B82" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="C82" s="32">
         <v>20</v>
       </c>
-      <c r="D82" s="26">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="E82" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="F82" s="26" t="s">
-        <v>320</v>
+      <c r="D82" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="E82" s="31" t="s">
+        <v>307</v>
+      </c>
+      <c r="F82" s="30" t="s">
+        <v>136</v>
       </c>
       <c r="G82" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F82),0)&gt;0), MAX($G$1:G81)+1, ""))</f>
@@ -3888,19 +3900,19 @@
         <v>20</v>
       </c>
       <c r="B83" s="31" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C83" s="32">
         <v>20</v>
       </c>
       <c r="D83" s="30" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="E83" s="31" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="F83" s="30" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G83" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F83),0)&gt;0), MAX($G$1:G82)+1, ""))</f>
@@ -3912,23 +3924,23 @@
       </c>
     </row>
     <row r="84" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A84" s="30">
+      <c r="A84" s="26">
         <v>20</v>
       </c>
-      <c r="B84" s="31" t="s">
-        <v>128</v>
-      </c>
-      <c r="C84" s="32">
+      <c r="B84" s="27" t="s">
+        <v>314</v>
+      </c>
+      <c r="C84" s="28">
         <v>20</v>
       </c>
-      <c r="D84" s="30" t="s">
-        <v>236</v>
-      </c>
-      <c r="E84" s="31" t="s">
-        <v>307</v>
-      </c>
-      <c r="F84" s="30" t="s">
-        <v>129</v>
+      <c r="D84" s="26">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E84" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="F84" s="26" t="s">
+        <v>320</v>
       </c>
       <c r="G84" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F84),0)&gt;0), MAX($G$1:G83)+1, ""))</f>
@@ -3940,23 +3952,23 @@
       </c>
     </row>
     <row r="85" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A85" s="26">
+      <c r="A85" s="30">
         <v>20</v>
       </c>
-      <c r="B85" s="27" t="s">
-        <v>352</v>
-      </c>
-      <c r="C85" s="28">
+      <c r="B85" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="C85" s="32">
         <v>20</v>
       </c>
-      <c r="D85" s="26">
-        <v>2.7</v>
-      </c>
-      <c r="E85" s="27" t="s">
-        <v>247</v>
-      </c>
-      <c r="F85" s="26" t="s">
-        <v>355</v>
+      <c r="D85" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="E85" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F85" s="30" t="s">
+        <v>131</v>
       </c>
       <c r="G85" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F85),0)&gt;0), MAX($G$1:G84)+1, ""))</f>
@@ -3972,19 +3984,19 @@
         <v>20</v>
       </c>
       <c r="B86" s="31" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C86" s="32">
         <v>20</v>
       </c>
       <c r="D86" s="30" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="E86" s="31" t="s">
-        <v>8</v>
+        <v>307</v>
       </c>
       <c r="F86" s="30" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G86" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F86),0)&gt;0), MAX($G$1:G85)+1, ""))</f>
@@ -3996,23 +4008,23 @@
       </c>
     </row>
     <row r="87" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A87" s="30">
+      <c r="A87" s="26">
         <v>20</v>
       </c>
-      <c r="B87" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="C87" s="32">
+      <c r="B87" s="27" t="s">
+        <v>352</v>
+      </c>
+      <c r="C87" s="28">
         <v>20</v>
       </c>
-      <c r="D87" s="30" t="s">
-        <v>217</v>
-      </c>
-      <c r="E87" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F87" s="30" t="s">
-        <v>125</v>
+      <c r="D87" s="26">
+        <v>2.7</v>
+      </c>
+      <c r="E87" s="27" t="s">
+        <v>247</v>
+      </c>
+      <c r="F87" s="26" t="s">
+        <v>355</v>
       </c>
       <c r="G87" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F87),0)&gt;0), MAX($G$1:G86)+1, ""))</f>
@@ -4028,19 +4040,19 @@
         <v>20</v>
       </c>
       <c r="B88" s="31" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C88" s="32">
         <v>20</v>
       </c>
       <c r="D88" s="30" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="E88" s="31" t="s">
-        <v>307</v>
+        <v>8</v>
       </c>
       <c r="F88" s="30" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G88" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F88),0)&gt;0), MAX($G$1:G87)+1, ""))</f>
@@ -4056,19 +4068,19 @@
         <v>20</v>
       </c>
       <c r="B89" s="31" t="s">
-        <v>259</v>
+        <v>124</v>
       </c>
       <c r="C89" s="32">
         <v>20</v>
       </c>
       <c r="D89" s="30" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="E89" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F89" s="30" t="s">
-        <v>260</v>
+        <v>125</v>
       </c>
       <c r="G89" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F89),0)&gt;0), MAX($G$1:G88)+1, ""))</f>
@@ -4084,19 +4096,19 @@
         <v>20</v>
       </c>
       <c r="B90" s="31" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C90" s="32">
         <v>20</v>
       </c>
       <c r="D90" s="30" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E90" s="31" t="s">
-        <v>8</v>
+        <v>307</v>
       </c>
       <c r="F90" s="30" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G90" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F90),0)&gt;0), MAX($G$1:G89)+1, ""))</f>
@@ -4112,19 +4124,19 @@
         <v>20</v>
       </c>
       <c r="B91" s="31" t="s">
-        <v>118</v>
+        <v>259</v>
       </c>
       <c r="C91" s="32">
         <v>20</v>
       </c>
       <c r="D91" s="30" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="E91" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F91" s="30" t="s">
-        <v>119</v>
+        <v>260</v>
       </c>
       <c r="G91" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F91),0)&gt;0), MAX($G$1:G90)+1, ""))</f>
@@ -4140,19 +4152,19 @@
         <v>20</v>
       </c>
       <c r="B92" s="31" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C92" s="32">
         <v>20</v>
       </c>
       <c r="D92" s="30" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="E92" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F92" s="30" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G92" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F92),0)&gt;0), MAX($G$1:G91)+1, ""))</f>
@@ -4164,23 +4176,23 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A93" s="26">
+      <c r="A93" s="30">
         <v>20</v>
       </c>
-      <c r="B93" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="C93" s="28">
+      <c r="B93" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C93" s="32">
         <v>20</v>
       </c>
-      <c r="D93" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E93" s="27" t="s">
-        <v>301</v>
-      </c>
-      <c r="F93" s="26" t="s">
-        <v>300</v>
+      <c r="D93" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="E93" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F93" s="30" t="s">
+        <v>119</v>
       </c>
       <c r="G93" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F93),0)&gt;0), MAX($G$1:G92)+1, ""))</f>
@@ -4196,19 +4208,19 @@
         <v>20</v>
       </c>
       <c r="B94" s="31" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C94" s="32">
         <v>20</v>
       </c>
       <c r="D94" s="30" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="E94" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F94" s="30" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G94" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F94),0)&gt;0), MAX($G$1:G93)+1, ""))</f>
@@ -4220,23 +4232,23 @@
       </c>
     </row>
     <row r="95" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A95" s="30">
+      <c r="A95" s="26">
         <v>20</v>
       </c>
-      <c r="B95" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="C95" s="32">
+      <c r="B95" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="C95" s="28">
         <v>20</v>
       </c>
-      <c r="D95" s="30" t="s">
-        <v>224</v>
-      </c>
-      <c r="E95" s="31" t="s">
+      <c r="D95" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E95" s="27" t="s">
         <v>301</v>
       </c>
-      <c r="F95" s="30" t="s">
-        <v>113</v>
+      <c r="F95" s="26" t="s">
+        <v>300</v>
       </c>
       <c r="G95" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F95),0)&gt;0), MAX($G$1:G94)+1, ""))</f>
@@ -4252,19 +4264,19 @@
         <v>20</v>
       </c>
       <c r="B96" s="31" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C96" s="32">
         <v>20</v>
       </c>
       <c r="D96" s="30" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E96" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F96" s="30" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G96" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F96),0)&gt;0), MAX($G$1:G95)+1, ""))</f>
@@ -4276,48 +4288,51 @@
       </c>
     </row>
     <row r="97" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A97" s="36">
+      <c r="A97" s="30">
         <v>20</v>
       </c>
-      <c r="B97" s="37" t="s">
-        <v>332</v>
-      </c>
-      <c r="C97" s="38">
+      <c r="B97" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="C97" s="32">
         <v>20</v>
       </c>
-      <c r="D97" s="36">
-        <v>3</v>
-      </c>
-      <c r="E97" s="37" t="s">
-        <v>306</v>
-      </c>
-      <c r="F97" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="G97" s="29"/>
+      <c r="D97" s="30" t="s">
+        <v>224</v>
+      </c>
+      <c r="E97" s="31" t="s">
+        <v>301</v>
+      </c>
+      <c r="F97" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="G97" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F97),0)&gt;0), MAX($G$1:G96)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H97" s="21" t="b">
         <f>A97=C97</f>
         <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A98" s="26">
+      <c r="A98" s="30">
         <v>20</v>
       </c>
-      <c r="B98" s="27" t="s">
-        <v>304</v>
-      </c>
-      <c r="C98" s="28">
+      <c r="B98" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="C98" s="32">
         <v>20</v>
       </c>
-      <c r="D98" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E98" s="27" t="s">
-        <v>301</v>
-      </c>
-      <c r="F98" s="26" t="s">
-        <v>303</v>
+      <c r="D98" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="E98" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F98" s="30" t="s">
+        <v>111</v>
       </c>
       <c r="G98" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F98),0)&gt;0), MAX($G$1:G97)+1, ""))</f>
@@ -4329,28 +4344,25 @@
       </c>
     </row>
     <row r="99" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A99" s="30">
+      <c r="A99" s="36">
         <v>20</v>
       </c>
-      <c r="B99" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="C99" s="32">
+      <c r="B99" s="37" t="s">
+        <v>332</v>
+      </c>
+      <c r="C99" s="38">
         <v>20</v>
       </c>
-      <c r="D99" s="30" t="s">
-        <v>216</v>
-      </c>
-      <c r="E99" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="F99" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="G99" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F99),0)&gt;0), MAX($G$1:G98)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D99" s="36">
+        <v>3</v>
+      </c>
+      <c r="E99" s="37" t="s">
+        <v>306</v>
+      </c>
+      <c r="F99" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="G99" s="29"/>
       <c r="H99" s="21" t="b">
         <f>A99=C99</f>
         <v>1</v>
@@ -4361,19 +4373,19 @@
         <v>20</v>
       </c>
       <c r="B100" s="27" t="s">
-        <v>341</v>
+        <v>304</v>
       </c>
       <c r="C100" s="28">
         <v>20</v>
       </c>
       <c r="D100" s="26">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="E100" s="27" t="s">
-        <v>83</v>
+        <v>301</v>
       </c>
       <c r="F100" s="26" t="s">
-        <v>346</v>
+        <v>303</v>
       </c>
       <c r="G100" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F100),0)&gt;0), MAX($G$1:G99)+1, ""))</f>
@@ -4385,48 +4397,51 @@
       </c>
     </row>
     <row r="101" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A101" s="36">
+      <c r="A101" s="30">
         <v>20</v>
       </c>
-      <c r="B101" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="C101" s="38">
+      <c r="B101" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="C101" s="32">
         <v>20</v>
       </c>
-      <c r="D101" s="36">
-        <v>3.2</v>
-      </c>
-      <c r="E101" s="37" t="s">
-        <v>338</v>
-      </c>
-      <c r="F101" s="36" t="s">
-        <v>334</v>
-      </c>
-      <c r="G101" s="29"/>
+      <c r="D101" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="E101" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="F101" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="G101" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F101),0)&gt;0), MAX($G$1:G100)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H101" s="21" t="b">
         <f>A101=C101</f>
         <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A102" s="30">
+      <c r="A102" s="26">
         <v>20</v>
       </c>
-      <c r="B102" s="31" t="s">
-        <v>103</v>
-      </c>
-      <c r="C102" s="32">
+      <c r="B102" s="27" t="s">
+        <v>341</v>
+      </c>
+      <c r="C102" s="28">
         <v>20</v>
       </c>
-      <c r="D102" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="E102" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F102" s="30" t="s">
-        <v>104</v>
+      <c r="D102" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E102" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="F102" s="26" t="s">
+        <v>346</v>
       </c>
       <c r="G102" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F102),0)&gt;0), MAX($G$1:G101)+1, ""))</f>
@@ -4438,28 +4453,25 @@
       </c>
     </row>
     <row r="103" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A103" s="30">
+      <c r="A103" s="36">
         <v>20</v>
       </c>
-      <c r="B103" s="31" t="s">
-        <v>265</v>
-      </c>
-      <c r="C103" s="32">
+      <c r="B103" s="37" t="s">
+        <v>337</v>
+      </c>
+      <c r="C103" s="38">
         <v>20</v>
       </c>
-      <c r="D103" s="30">
-        <v>6.2</v>
-      </c>
-      <c r="E103" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F103" s="30" t="s">
-        <v>266</v>
-      </c>
-      <c r="G103" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F103),0)&gt;0), MAX($G$1:G102)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D103" s="36">
+        <v>3.2</v>
+      </c>
+      <c r="E103" s="37" t="s">
+        <v>338</v>
+      </c>
+      <c r="F103" s="36" t="s">
+        <v>334</v>
+      </c>
+      <c r="G103" s="29"/>
       <c r="H103" s="21" t="b">
         <f>A103=C103</f>
         <v>1</v>
@@ -4470,19 +4482,19 @@
         <v>20</v>
       </c>
       <c r="B104" s="31" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C104" s="32">
         <v>20</v>
       </c>
       <c r="D104" s="30" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="E104" s="31" t="s">
-        <v>301</v>
+        <v>8</v>
       </c>
       <c r="F104" s="30" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G104" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F104),0)&gt;0), MAX($G$1:G103)+1, ""))</f>
@@ -4494,23 +4506,23 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A105" s="26">
+      <c r="A105" s="30">
         <v>20</v>
       </c>
-      <c r="B105" s="27" t="s">
-        <v>302</v>
-      </c>
-      <c r="C105" s="28">
+      <c r="B105" s="31" t="s">
+        <v>265</v>
+      </c>
+      <c r="C105" s="32">
         <v>20</v>
       </c>
-      <c r="D105" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E105" s="27" t="s">
-        <v>301</v>
-      </c>
-      <c r="F105" s="26" t="s">
-        <v>303</v>
+      <c r="D105" s="30">
+        <v>6.2</v>
+      </c>
+      <c r="E105" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F105" s="30" t="s">
+        <v>266</v>
       </c>
       <c r="G105" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F105),0)&gt;0), MAX($G$1:G104)+1, ""))</f>
@@ -4526,19 +4538,19 @@
         <v>20</v>
       </c>
       <c r="B106" s="31" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C106" s="32">
         <v>20</v>
       </c>
       <c r="D106" s="30" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E106" s="31" t="s">
-        <v>8</v>
+        <v>301</v>
       </c>
       <c r="F106" s="30" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G106" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F106),0)&gt;0), MAX($G$1:G105)+1, ""))</f>
@@ -4550,23 +4562,23 @@
       </c>
     </row>
     <row r="107" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A107" s="30">
+      <c r="A107" s="26">
         <v>20</v>
       </c>
-      <c r="B107" s="31" t="s">
-        <v>93</v>
-      </c>
-      <c r="C107" s="32">
+      <c r="B107" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C107" s="28">
         <v>20</v>
       </c>
-      <c r="D107" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="E107" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F107" s="30" t="s">
-        <v>94</v>
+      <c r="D107" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E107" s="27" t="s">
+        <v>301</v>
+      </c>
+      <c r="F107" s="26" t="s">
+        <v>303</v>
       </c>
       <c r="G107" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F107),0)&gt;0), MAX($G$1:G106)+1, ""))</f>
@@ -4582,19 +4594,19 @@
         <v>20</v>
       </c>
       <c r="B108" s="31" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C108" s="32">
         <v>20</v>
       </c>
       <c r="D108" s="30" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="E108" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F108" s="30" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G108" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F108),0)&gt;0), MAX($G$1:G107)+1, ""))</f>
@@ -4610,19 +4622,19 @@
         <v>20</v>
       </c>
       <c r="B109" s="31" t="s">
-        <v>292</v>
+        <v>93</v>
       </c>
       <c r="C109" s="32">
         <v>20</v>
       </c>
-      <c r="D109" s="30">
-        <v>1.8</v>
+      <c r="D109" s="30" t="s">
+        <v>220</v>
       </c>
       <c r="E109" s="31" t="s">
-        <v>293</v>
+        <v>8</v>
       </c>
       <c r="F109" s="30" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G109" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F109),0)&gt;0), MAX($G$1:G108)+1, ""))</f>
@@ -4638,19 +4650,19 @@
         <v>20</v>
       </c>
       <c r="B110" s="31" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C110" s="32">
         <v>20</v>
       </c>
       <c r="D110" s="30" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E110" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F110" s="30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G110" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F110),0)&gt;0), MAX($G$1:G109)+1, ""))</f>
@@ -4666,19 +4678,19 @@
         <v>20</v>
       </c>
       <c r="B111" s="31" t="s">
-        <v>87</v>
+        <v>292</v>
       </c>
       <c r="C111" s="32">
         <v>20</v>
       </c>
-      <c r="D111" s="30" t="s">
-        <v>222</v>
+      <c r="D111" s="30">
+        <v>1.8</v>
       </c>
       <c r="E111" s="31" t="s">
-        <v>8</v>
+        <v>293</v>
       </c>
       <c r="F111" s="30" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G111" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F111),0)&gt;0), MAX($G$1:G110)+1, ""))</f>
@@ -4694,19 +4706,19 @@
         <v>20</v>
       </c>
       <c r="B112" s="31" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C112" s="32">
         <v>20</v>
       </c>
       <c r="D112" s="30" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E112" s="31" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="F112" s="30" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G112" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F112),0)&gt;0), MAX($G$1:G111)+1, ""))</f>
@@ -4722,19 +4734,19 @@
         <v>20</v>
       </c>
       <c r="B113" s="31" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C113" s="32">
         <v>20</v>
       </c>
       <c r="D113" s="30" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E113" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F113" s="30" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="G113" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F113),0)&gt;0), MAX($G$1:G112)+1, ""))</f>
@@ -4750,19 +4762,19 @@
         <v>20</v>
       </c>
       <c r="B114" s="31" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C114" s="32">
         <v>20</v>
       </c>
       <c r="D114" s="30" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E114" s="31" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="F114" s="30" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G114" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F114),0)&gt;0), MAX($G$1:G113)+1, ""))</f>
@@ -4774,23 +4786,23 @@
       </c>
     </row>
     <row r="115" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A115" s="26">
-        <v>25</v>
-      </c>
-      <c r="B115" s="27" t="s">
-        <v>180</v>
-      </c>
-      <c r="C115" s="28">
-        <v>25</v>
-      </c>
-      <c r="D115" s="26" t="s">
-        <v>227</v>
-      </c>
-      <c r="E115" s="27" t="s">
+      <c r="A115" s="30">
+        <v>20</v>
+      </c>
+      <c r="B115" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="C115" s="32">
+        <v>20</v>
+      </c>
+      <c r="D115" s="30" t="s">
+        <v>219</v>
+      </c>
+      <c r="E115" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F115" s="26" t="s">
-        <v>181</v>
+      <c r="F115" s="30" t="s">
+        <v>81</v>
       </c>
       <c r="G115" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F115),0)&gt;0), MAX($G$1:G114)+1, ""))</f>
@@ -4802,23 +4814,23 @@
       </c>
     </row>
     <row r="116" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A116" s="26">
-        <v>25</v>
-      </c>
-      <c r="B116" s="27" t="s">
-        <v>178</v>
-      </c>
-      <c r="C116" s="28">
-        <v>25</v>
-      </c>
-      <c r="D116" s="26" t="s">
-        <v>239</v>
-      </c>
-      <c r="E116" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F116" s="26" t="s">
-        <v>179</v>
+      <c r="A116" s="30">
+        <v>20</v>
+      </c>
+      <c r="B116" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="C116" s="32">
+        <v>20</v>
+      </c>
+      <c r="D116" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="E116" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F116" s="30" t="s">
+        <v>79</v>
       </c>
       <c r="G116" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F116),0)&gt;0), MAX($G$1:G115)+1, ""))</f>
@@ -4834,19 +4846,19 @@
         <v>25</v>
       </c>
       <c r="B117" s="27" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C117" s="28">
         <v>25</v>
       </c>
       <c r="D117" s="26" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="E117" s="27" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="F117" s="26" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G117" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F117),0)&gt;0), MAX($G$1:G116)+1, ""))</f>
@@ -4862,19 +4874,19 @@
         <v>25</v>
       </c>
       <c r="B118" s="27" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C118" s="28">
         <v>25</v>
       </c>
       <c r="D118" s="26" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="E118" s="27" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="F118" s="26" t="s">
-        <v>326</v>
+        <v>179</v>
       </c>
       <c r="G118" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F118),0)&gt;0), MAX($G$1:G117)+1, ""))</f>
@@ -4890,19 +4902,19 @@
         <v>25</v>
       </c>
       <c r="B119" s="27" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C119" s="28">
         <v>25</v>
       </c>
-      <c r="D119" s="26">
-        <v>2.7</v>
+      <c r="D119" s="26" t="s">
+        <v>233</v>
       </c>
       <c r="E119" s="27" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="F119" s="26" t="s">
-        <v>340</v>
+        <v>177</v>
       </c>
       <c r="G119" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F119),0)&gt;0), MAX($G$1:G118)+1, ""))</f>
@@ -4914,23 +4926,23 @@
       </c>
     </row>
     <row r="120" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A120" s="30">
+      <c r="A120" s="26">
         <v>25</v>
       </c>
-      <c r="B120" s="31" t="s">
-        <v>286</v>
-      </c>
-      <c r="C120" s="32">
+      <c r="B120" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="C120" s="28">
         <v>25</v>
       </c>
-      <c r="D120" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="E120" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="F120" s="30" t="s">
-        <v>104</v>
+      <c r="D120" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="E120" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F120" s="26" t="s">
+        <v>326</v>
       </c>
       <c r="G120" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F120),0)&gt;0), MAX($G$1:G119)+1, ""))</f>
@@ -4942,23 +4954,23 @@
       </c>
     </row>
     <row r="121" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A121" s="30">
+      <c r="A121" s="26">
         <v>25</v>
       </c>
-      <c r="B121" s="31" t="s">
-        <v>284</v>
-      </c>
-      <c r="C121" s="32">
+      <c r="B121" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="C121" s="28">
         <v>25</v>
       </c>
-      <c r="D121" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="E121" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="F121" s="30" t="s">
-        <v>104</v>
+      <c r="D121" s="26">
+        <v>2.7</v>
+      </c>
+      <c r="E121" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="F121" s="26" t="s">
+        <v>340</v>
       </c>
       <c r="G121" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F121),0)&gt;0), MAX($G$1:G120)+1, ""))</f>
@@ -4970,23 +4982,23 @@
       </c>
     </row>
     <row r="122" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A122" s="26">
+      <c r="A122" s="30">
         <v>25</v>
       </c>
-      <c r="B122" s="27" t="s">
-        <v>172</v>
-      </c>
-      <c r="C122" s="28">
+      <c r="B122" s="31" t="s">
+        <v>286</v>
+      </c>
+      <c r="C122" s="32">
         <v>25</v>
       </c>
-      <c r="D122" s="26" t="s">
-        <v>236</v>
-      </c>
-      <c r="E122" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F122" s="26" t="s">
-        <v>173</v>
+      <c r="D122" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="E122" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="F122" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G122" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F122),0)&gt;0), MAX($G$1:G121)+1, ""))</f>
@@ -4998,23 +5010,23 @@
       </c>
     </row>
     <row r="123" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A123" s="26">
+      <c r="A123" s="30">
         <v>25</v>
       </c>
-      <c r="B123" s="27" t="s">
-        <v>170</v>
-      </c>
-      <c r="C123" s="28">
+      <c r="B123" s="31" t="s">
+        <v>284</v>
+      </c>
+      <c r="C123" s="32">
         <v>25</v>
       </c>
-      <c r="D123" s="26" t="s">
-        <v>219</v>
-      </c>
-      <c r="E123" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F123" s="26" t="s">
-        <v>171</v>
+      <c r="D123" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="E123" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="F123" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G123" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F123),0)&gt;0), MAX($G$1:G122)+1, ""))</f>
@@ -5026,23 +5038,23 @@
       </c>
     </row>
     <row r="124" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A124" s="30">
+      <c r="A124" s="26">
         <v>25</v>
       </c>
-      <c r="B124" s="31" t="s">
-        <v>280</v>
-      </c>
-      <c r="C124" s="32">
+      <c r="B124" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="C124" s="28">
         <v>25</v>
       </c>
-      <c r="D124" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="E124" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F124" s="30" t="s">
-        <v>104</v>
+      <c r="D124" s="26" t="s">
+        <v>236</v>
+      </c>
+      <c r="E124" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="F124" s="26" t="s">
+        <v>173</v>
       </c>
       <c r="G124" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F124),0)&gt;0), MAX($G$1:G123)+1, ""))</f>
@@ -5058,19 +5070,19 @@
         <v>25</v>
       </c>
       <c r="B125" s="27" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C125" s="28">
         <v>25</v>
       </c>
       <c r="D125" s="26" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E125" s="27" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="F125" s="26" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G125" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F125),0)&gt;0), MAX($G$1:G124)+1, ""))</f>
@@ -5082,23 +5094,23 @@
       </c>
     </row>
     <row r="126" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A126" s="26">
+      <c r="A126" s="30">
         <v>25</v>
       </c>
-      <c r="B126" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="C126" s="28">
+      <c r="B126" s="31" t="s">
+        <v>280</v>
+      </c>
+      <c r="C126" s="32">
         <v>25</v>
       </c>
-      <c r="D126" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="E126" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F126" s="26" t="s">
-        <v>167</v>
+      <c r="D126" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="E126" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F126" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G126" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F126),0)&gt;0), MAX($G$1:G125)+1, ""))</f>
@@ -5114,19 +5126,19 @@
         <v>25</v>
       </c>
       <c r="B127" s="27" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C127" s="28">
         <v>25</v>
       </c>
       <c r="D127" s="26" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="E127" s="27" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="F127" s="26" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G127" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F127),0)&gt;0), MAX($G$1:G126)+1, ""))</f>
@@ -5142,19 +5154,19 @@
         <v>25</v>
       </c>
       <c r="B128" s="27" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C128" s="28">
         <v>25</v>
       </c>
       <c r="D128" s="26" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="E128" s="27" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="F128" s="26" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="G128" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F128),0)&gt;0), MAX($G$1:G127)+1, ""))</f>
@@ -5170,19 +5182,19 @@
         <v>25</v>
       </c>
       <c r="B129" s="27" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C129" s="28">
         <v>25</v>
       </c>
       <c r="D129" s="26" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="E129" s="27" t="s">
         <v>83</v>
       </c>
       <c r="F129" s="26" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G129" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F129),0)&gt;0), MAX($G$1:G128)+1, ""))</f>
@@ -5198,19 +5210,19 @@
         <v>25</v>
       </c>
       <c r="B130" s="27" t="s">
-        <v>344</v>
+        <v>162</v>
       </c>
       <c r="C130" s="28">
         <v>25</v>
       </c>
-      <c r="D130" s="26">
-        <v>3.4</v>
+      <c r="D130" s="26" t="s">
+        <v>238</v>
       </c>
       <c r="E130" s="27" t="s">
         <v>83</v>
       </c>
       <c r="F130" s="26" t="s">
-        <v>345</v>
+        <v>163</v>
       </c>
       <c r="G130" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F130),0)&gt;0), MAX($G$1:G129)+1, ""))</f>
@@ -5226,22 +5238,22 @@
         <v>25</v>
       </c>
       <c r="B131" s="27" t="s">
-        <v>312</v>
+        <v>160</v>
       </c>
       <c r="C131" s="28">
         <v>25</v>
       </c>
-      <c r="D131" s="26">
-        <v>3.9</v>
+      <c r="D131" s="26" t="s">
+        <v>230</v>
       </c>
       <c r="E131" s="27" t="s">
-        <v>311</v>
+        <v>83</v>
       </c>
       <c r="F131" s="26" t="s">
-        <v>313</v>
+        <v>161</v>
       </c>
       <c r="G131" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F131),0)&gt;0), MAX($G$1:G129)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F131),0)&gt;0), MAX($G$1:G130)+1, ""))</f>
         <v/>
       </c>
       <c r="H131" s="21" t="b">
@@ -5254,19 +5266,19 @@
         <v>25</v>
       </c>
       <c r="B132" s="27" t="s">
-        <v>158</v>
+        <v>344</v>
       </c>
       <c r="C132" s="28">
         <v>25</v>
       </c>
-      <c r="D132" s="26" t="s">
-        <v>229</v>
+      <c r="D132" s="26">
+        <v>3.4</v>
       </c>
       <c r="E132" s="27" t="s">
         <v>83</v>
       </c>
       <c r="F132" s="26" t="s">
-        <v>159</v>
+        <v>345</v>
       </c>
       <c r="G132" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B132),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E132),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F132),0)&gt;0), MAX($G$1:G131)+1, ""))</f>
@@ -5282,22 +5294,22 @@
         <v>25</v>
       </c>
       <c r="B133" s="27" t="s">
-        <v>156</v>
+        <v>312</v>
       </c>
       <c r="C133" s="28">
         <v>25</v>
       </c>
-      <c r="D133" s="26" t="s">
-        <v>226</v>
+      <c r="D133" s="26">
+        <v>3.9</v>
       </c>
       <c r="E133" s="27" t="s">
-        <v>8</v>
+        <v>311</v>
       </c>
       <c r="F133" s="26" t="s">
-        <v>157</v>
+        <v>313</v>
       </c>
       <c r="G133" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F133),0)&gt;0), MAX($G$1:G132)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F133),0)&gt;0), MAX($G$1:G131)+1, ""))</f>
         <v/>
       </c>
       <c r="H133" s="21" t="b">
@@ -5310,19 +5322,19 @@
         <v>25</v>
       </c>
       <c r="B134" s="27" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C134" s="28">
         <v>25</v>
       </c>
       <c r="D134" s="26" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E134" s="27" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="F134" s="26" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="G134" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F134),0)&gt;0), MAX($G$1:G133)+1, ""))</f>
@@ -5338,19 +5350,19 @@
         <v>25</v>
       </c>
       <c r="B135" s="27" t="s">
-        <v>249</v>
+        <v>156</v>
       </c>
       <c r="C135" s="28">
         <v>25</v>
       </c>
-      <c r="D135" s="39" t="s">
-        <v>231</v>
+      <c r="D135" s="26" t="s">
+        <v>226</v>
       </c>
       <c r="E135" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F135" s="26" t="s">
-        <v>250</v>
+        <v>157</v>
       </c>
       <c r="G135" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F135),0)&gt;0), MAX($G$1:G134)+1, ""))</f>
@@ -5366,19 +5378,19 @@
         <v>25</v>
       </c>
       <c r="B136" s="27" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C136" s="28">
         <v>25</v>
       </c>
       <c r="D136" s="26" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E136" s="27" t="s">
         <v>133</v>
       </c>
       <c r="F136" s="26" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G136" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F136),0)&gt;0), MAX($G$1:G135)+1, ""))</f>
@@ -5390,23 +5402,23 @@
       </c>
     </row>
     <row r="137" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A137" s="30">
+      <c r="A137" s="26">
         <v>25</v>
       </c>
-      <c r="B137" s="31" t="s">
-        <v>290</v>
-      </c>
-      <c r="C137" s="32">
+      <c r="B137" s="27" t="s">
+        <v>249</v>
+      </c>
+      <c r="C137" s="28">
         <v>25</v>
       </c>
-      <c r="D137" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="E137" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="F137" s="30" t="s">
-        <v>104</v>
+      <c r="D137" s="39" t="s">
+        <v>231</v>
+      </c>
+      <c r="E137" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F137" s="26" t="s">
+        <v>250</v>
       </c>
       <c r="G137" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F137),0)&gt;0), MAX($G$1:G136)+1, ""))</f>
@@ -5418,23 +5430,23 @@
       </c>
     </row>
     <row r="138" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A138" s="30">
+      <c r="A138" s="26">
         <v>25</v>
       </c>
-      <c r="B138" s="31" t="s">
-        <v>288</v>
-      </c>
-      <c r="C138" s="32">
+      <c r="B138" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="C138" s="28">
         <v>25</v>
       </c>
-      <c r="D138" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="E138" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="F138" s="30" t="s">
-        <v>104</v>
+      <c r="D138" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="E138" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="F138" s="26" t="s">
+        <v>153</v>
       </c>
       <c r="G138" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F138),0)&gt;0), MAX($G$1:G137)+1, ""))</f>
@@ -5450,7 +5462,7 @@
         <v>25</v>
       </c>
       <c r="B139" s="31" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C139" s="32">
         <v>25</v>
@@ -5474,23 +5486,23 @@
       </c>
     </row>
     <row r="140" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A140" s="26">
+      <c r="A140" s="30">
         <v>25</v>
       </c>
-      <c r="B140" s="27" t="s">
-        <v>254</v>
-      </c>
-      <c r="C140" s="28">
+      <c r="B140" s="31" t="s">
+        <v>288</v>
+      </c>
+      <c r="C140" s="32">
         <v>25</v>
       </c>
-      <c r="D140" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E140" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F140" s="26" t="s">
-        <v>255</v>
+      <c r="D140" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="E140" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="F140" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G140" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F140),0)&gt;0), MAX($G$1:G139)+1, ""))</f>
@@ -5506,7 +5518,7 @@
         <v>25</v>
       </c>
       <c r="B141" s="31" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C141" s="32">
         <v>25</v>
@@ -5534,22 +5546,22 @@
         <v>25</v>
       </c>
       <c r="B142" s="27" t="s">
-        <v>150</v>
+        <v>254</v>
       </c>
       <c r="C142" s="28">
         <v>25</v>
       </c>
-      <c r="D142" s="26" t="s">
-        <v>228</v>
+      <c r="D142" s="26">
+        <v>2.5</v>
       </c>
       <c r="E142" s="27" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="F142" s="26" t="s">
-        <v>151</v>
+        <v>255</v>
       </c>
       <c r="G142" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F142),0)&gt;0), MAX($G$1:G140)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F142),0)&gt;0), MAX($G$1:G141)+1, ""))</f>
         <v/>
       </c>
       <c r="H142" s="21" t="b">
@@ -5559,22 +5571,22 @@
     </row>
     <row r="143" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A143" s="30">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B143" s="31" t="s">
-        <v>194</v>
+        <v>287</v>
       </c>
       <c r="C143" s="32">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D143" s="30" t="s">
-        <v>234</v>
+        <v>209</v>
       </c>
       <c r="E143" s="31" t="s">
-        <v>133</v>
+        <v>285</v>
       </c>
       <c r="F143" s="30" t="s">
-        <v>195</v>
+        <v>104</v>
       </c>
       <c r="G143" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F143),0)&gt;0), MAX($G$1:G142)+1, ""))</f>
@@ -5586,26 +5598,26 @@
       </c>
     </row>
     <row r="144" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A144" s="30">
-        <v>30</v>
-      </c>
-      <c r="B144" s="31" t="s">
-        <v>193</v>
-      </c>
-      <c r="C144" s="32">
-        <v>30</v>
-      </c>
-      <c r="D144" s="30" t="s">
-        <v>243</v>
-      </c>
-      <c r="E144" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="F144" s="30" t="s">
-        <v>192</v>
+      <c r="A144" s="26">
+        <v>25</v>
+      </c>
+      <c r="B144" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C144" s="28">
+        <v>25</v>
+      </c>
+      <c r="D144" s="26" t="s">
+        <v>228</v>
+      </c>
+      <c r="E144" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="F144" s="26" t="s">
+        <v>151</v>
       </c>
       <c r="G144" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F144),0)&gt;0), MAX($G$1:G143)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F144),0)&gt;0), MAX($G$1:G142)+1, ""))</f>
         <v/>
       </c>
       <c r="H144" s="21" t="b">
@@ -5618,19 +5630,19 @@
         <v>30</v>
       </c>
       <c r="B145" s="31" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C145" s="32">
         <v>30</v>
       </c>
       <c r="D145" s="30" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="E145" s="31" t="s">
         <v>133</v>
       </c>
       <c r="F145" s="30" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G145" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B145),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E145),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F145),0)&gt;0), MAX($G$1:G144)+1, ""))</f>
@@ -5646,19 +5658,19 @@
         <v>30</v>
       </c>
       <c r="B146" s="31" t="s">
-        <v>248</v>
+        <v>193</v>
       </c>
       <c r="C146" s="32">
         <v>30</v>
       </c>
       <c r="D146" s="30" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="E146" s="31" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="F146" s="30" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G146" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F146),0)&gt;0), MAX($G$1:G145)+1, ""))</f>
@@ -5674,19 +5686,19 @@
         <v>30</v>
       </c>
       <c r="B147" s="31" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C147" s="32">
         <v>30</v>
       </c>
       <c r="D147" s="30" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E147" s="31" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="F147" s="30" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="G147" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F147),0)&gt;0), MAX($G$1:G146)+1, ""))</f>
@@ -5702,19 +5714,19 @@
         <v>30</v>
       </c>
       <c r="B148" s="31" t="s">
-        <v>186</v>
+        <v>248</v>
       </c>
       <c r="C148" s="32">
         <v>30</v>
       </c>
       <c r="D148" s="30" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="E148" s="31" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="F148" s="30" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G148" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F148),0)&gt;0), MAX($G$1:G147)+1, ""))</f>
@@ -5730,19 +5742,19 @@
         <v>30</v>
       </c>
       <c r="B149" s="31" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C149" s="32">
         <v>30</v>
       </c>
       <c r="D149" s="30" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="E149" s="31" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="F149" s="30" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="G149" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B149),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E149),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F149),0)&gt;0), MAX($G$1:G148)+1, ""))</f>
@@ -5758,19 +5770,19 @@
         <v>30</v>
       </c>
       <c r="B150" s="31" t="s">
-        <v>339</v>
+        <v>186</v>
       </c>
       <c r="C150" s="32">
         <v>30</v>
       </c>
-      <c r="D150" s="30">
-        <v>2.9</v>
+      <c r="D150" s="30" t="s">
+        <v>230</v>
       </c>
       <c r="E150" s="31" t="s">
         <v>83</v>
       </c>
       <c r="F150" s="30" t="s">
-        <v>340</v>
+        <v>187</v>
       </c>
       <c r="G150" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B150),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E150),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F150),0)&gt;0), MAX($G$1:G149)+1, ""))</f>
@@ -5786,22 +5798,22 @@
         <v>30</v>
       </c>
       <c r="B151" s="31" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C151" s="32">
         <v>30</v>
       </c>
       <c r="D151" s="30" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E151" s="31" t="s">
         <v>133</v>
       </c>
       <c r="F151" s="30" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G151" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B151),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E151),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F151),0)&gt;0), MAX($G$1:G149)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B151),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E151),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F151),0)&gt;0), MAX($G$1:G150)+1, ""))</f>
         <v/>
       </c>
       <c r="H151" s="21" t="b">
@@ -5810,23 +5822,23 @@
       </c>
     </row>
     <row r="152" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A152" s="26">
-        <v>40</v>
-      </c>
-      <c r="B152" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="C152" s="28">
-        <v>40</v>
-      </c>
-      <c r="D152" s="26" t="s">
-        <v>245</v>
-      </c>
-      <c r="E152" s="27" t="s">
-        <v>200</v>
-      </c>
-      <c r="F152" s="26" t="s">
-        <v>201</v>
+      <c r="A152" s="30">
+        <v>30</v>
+      </c>
+      <c r="B152" s="31" t="s">
+        <v>339</v>
+      </c>
+      <c r="C152" s="32">
+        <v>30</v>
+      </c>
+      <c r="D152" s="30">
+        <v>2.9</v>
+      </c>
+      <c r="E152" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="F152" s="30" t="s">
+        <v>340</v>
       </c>
       <c r="G152" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B152),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E152),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F152),0)&gt;0), MAX($G$1:G151)+1, ""))</f>
@@ -5838,26 +5850,26 @@
       </c>
     </row>
     <row r="153" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A153" s="26">
-        <v>40</v>
-      </c>
-      <c r="B153" s="27" t="s">
-        <v>196</v>
-      </c>
-      <c r="C153" s="28">
-        <v>40</v>
-      </c>
-      <c r="D153" s="26" t="s">
-        <v>244</v>
-      </c>
-      <c r="E153" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="F153" s="26" t="s">
-        <v>198</v>
+      <c r="A153" s="30">
+        <v>30</v>
+      </c>
+      <c r="B153" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="C153" s="32">
+        <v>30</v>
+      </c>
+      <c r="D153" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="E153" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="F153" s="30" t="s">
+        <v>183</v>
       </c>
       <c r="G153" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B153),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E153),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F153),0)&gt;0), MAX($G$1:G152)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B153),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E153),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F153),0)&gt;0), MAX($G$1:G151)+1, ""))</f>
         <v/>
       </c>
       <c r="H153" s="21" t="b">
@@ -5870,19 +5882,19 @@
         <v>40</v>
       </c>
       <c r="B154" s="27" t="s">
-        <v>251</v>
+        <v>199</v>
       </c>
       <c r="C154" s="28">
         <v>40</v>
       </c>
-      <c r="D154" s="26">
-        <v>8.3000000000000007</v>
+      <c r="D154" s="26" t="s">
+        <v>245</v>
       </c>
       <c r="E154" s="27" t="s">
-        <v>252</v>
+        <v>200</v>
       </c>
       <c r="F154" s="26" t="s">
-        <v>253</v>
+        <v>201</v>
       </c>
       <c r="G154" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B154),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E154),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F154),0)&gt;0), MAX($G$1:G153)+1, ""))</f>
@@ -5895,22 +5907,22 @@
     </row>
     <row r="155" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A155" s="26">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B155" s="27" t="s">
-        <v>296</v>
+        <v>196</v>
       </c>
       <c r="C155" s="28">
-        <v>45</v>
-      </c>
-      <c r="D155" s="26">
-        <v>10.199999999999999</v>
+        <v>40</v>
+      </c>
+      <c r="D155" s="26" t="s">
+        <v>244</v>
       </c>
       <c r="E155" s="27" t="s">
-        <v>297</v>
+        <v>197</v>
       </c>
       <c r="F155" s="26" t="s">
-        <v>298</v>
+        <v>198</v>
       </c>
       <c r="G155" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F155),0)&gt;0), MAX($G$1:G154)+1, ""))</f>
@@ -5922,16 +5934,60 @@
       </c>
     </row>
     <row r="156" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A156" s="1"/>
-      <c r="C156" s="1"/>
-      <c r="D156" s="1"/>
-      <c r="F156" s="1"/>
+      <c r="A156" s="26">
+        <v>40</v>
+      </c>
+      <c r="B156" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="C156" s="28">
+        <v>40</v>
+      </c>
+      <c r="D156" s="26">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E156" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="F156" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="G156" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B156),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E156),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F156),0)&gt;0), MAX($G$1:G155)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H156" s="21" t="b">
+        <f>A156=C156</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="157" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A157" s="1"/>
-      <c r="C157" s="1"/>
-      <c r="D157" s="1"/>
-      <c r="F157" s="1"/>
+      <c r="A157" s="26">
+        <v>45</v>
+      </c>
+      <c r="B157" s="27" t="s">
+        <v>296</v>
+      </c>
+      <c r="C157" s="28">
+        <v>45</v>
+      </c>
+      <c r="D157" s="26">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E157" s="27" t="s">
+        <v>297</v>
+      </c>
+      <c r="F157" s="26" t="s">
+        <v>298</v>
+      </c>
+      <c r="G157" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F157),0)&gt;0), MAX($G$1:G156)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H157" s="21" t="b">
+        <f>A157=C157</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="158" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
@@ -11215,10 +11271,10 @@
       <sortCondition ref="D2:D147"/>
     </sortState>
   </autoFilter>
-  <sortState ref="A2:H155">
-    <sortCondition ref="A2:A155"/>
-    <sortCondition ref="B2:B155"/>
-    <sortCondition ref="D2:D155"/>
+  <sortState ref="A2:H157">
+    <sortCondition ref="A2:A157"/>
+    <sortCondition ref="B2:B157"/>
+    <sortCondition ref="D2:D157"/>
   </sortState>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="364">
   <si>
     <t>Grupo</t>
   </si>
@@ -1105,6 +1105,18 @@
   </si>
   <si>
     <t>21710-370</t>
+  </si>
+  <si>
+    <t>ROSA DE ALMEIDA</t>
+  </si>
+  <si>
+    <t>21775-480</t>
+  </si>
+  <si>
+    <t>LUTECIA</t>
+  </si>
+  <si>
+    <t>21720-070</t>
   </si>
 </sst>
 </file>
@@ -4618,23 +4630,23 @@
       </c>
     </row>
     <row r="109" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A109" s="30">
+      <c r="A109" s="26">
         <v>20</v>
       </c>
-      <c r="B109" s="31" t="s">
-        <v>93</v>
-      </c>
-      <c r="C109" s="32">
+      <c r="B109" s="27" t="s">
+        <v>360</v>
+      </c>
+      <c r="C109" s="28">
         <v>20</v>
       </c>
-      <c r="D109" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="E109" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F109" s="30" t="s">
-        <v>94</v>
+      <c r="D109" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E109" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="F109" s="26" t="s">
+        <v>361</v>
       </c>
       <c r="G109" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F109),0)&gt;0), MAX($G$1:G108)+1, ""))</f>
@@ -4650,19 +4662,19 @@
         <v>20</v>
       </c>
       <c r="B110" s="31" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C110" s="32">
         <v>20</v>
       </c>
       <c r="D110" s="30" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E110" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F110" s="30" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G110" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F110),0)&gt;0), MAX($G$1:G109)+1, ""))</f>
@@ -4678,16 +4690,16 @@
         <v>20</v>
       </c>
       <c r="B111" s="31" t="s">
-        <v>292</v>
+        <v>91</v>
       </c>
       <c r="C111" s="32">
         <v>20</v>
       </c>
-      <c r="D111" s="30">
-        <v>1.8</v>
+      <c r="D111" s="30" t="s">
+        <v>225</v>
       </c>
       <c r="E111" s="31" t="s">
-        <v>293</v>
+        <v>8</v>
       </c>
       <c r="F111" s="30" t="s">
         <v>92</v>
@@ -4706,19 +4718,19 @@
         <v>20</v>
       </c>
       <c r="B112" s="31" t="s">
-        <v>89</v>
+        <v>292</v>
       </c>
       <c r="C112" s="32">
         <v>20</v>
       </c>
-      <c r="D112" s="30" t="s">
-        <v>224</v>
+      <c r="D112" s="30">
+        <v>1.8</v>
       </c>
       <c r="E112" s="31" t="s">
-        <v>8</v>
+        <v>293</v>
       </c>
       <c r="F112" s="30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G112" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F112),0)&gt;0), MAX($G$1:G111)+1, ""))</f>
@@ -4734,19 +4746,19 @@
         <v>20</v>
       </c>
       <c r="B113" s="31" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C113" s="32">
         <v>20</v>
       </c>
       <c r="D113" s="30" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E113" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F113" s="30" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G113" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F113),0)&gt;0), MAX($G$1:G112)+1, ""))</f>
@@ -4762,19 +4774,19 @@
         <v>20</v>
       </c>
       <c r="B114" s="31" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C114" s="32">
         <v>20</v>
       </c>
       <c r="D114" s="30" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E114" s="31" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="F114" s="30" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G114" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F114),0)&gt;0), MAX($G$1:G113)+1, ""))</f>
@@ -4790,19 +4802,19 @@
         <v>20</v>
       </c>
       <c r="B115" s="31" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C115" s="32">
         <v>20</v>
       </c>
       <c r="D115" s="30" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E115" s="31" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="F115" s="30" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G115" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F115),0)&gt;0), MAX($G$1:G114)+1, ""))</f>
@@ -4818,19 +4830,19 @@
         <v>20</v>
       </c>
       <c r="B116" s="31" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C116" s="32">
         <v>20</v>
       </c>
       <c r="D116" s="30" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E116" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F116" s="30" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G116" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F116),0)&gt;0), MAX($G$1:G115)+1, ""))</f>
@@ -4842,23 +4854,23 @@
       </c>
     </row>
     <row r="117" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A117" s="26">
-        <v>25</v>
-      </c>
-      <c r="B117" s="27" t="s">
-        <v>180</v>
-      </c>
-      <c r="C117" s="28">
-        <v>25</v>
-      </c>
-      <c r="D117" s="26" t="s">
-        <v>227</v>
-      </c>
-      <c r="E117" s="27" t="s">
+      <c r="A117" s="30">
+        <v>20</v>
+      </c>
+      <c r="B117" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="C117" s="32">
+        <v>20</v>
+      </c>
+      <c r="D117" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="E117" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F117" s="26" t="s">
-        <v>181</v>
+      <c r="F117" s="30" t="s">
+        <v>79</v>
       </c>
       <c r="G117" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F117),0)&gt;0), MAX($G$1:G116)+1, ""))</f>
@@ -4874,19 +4886,19 @@
         <v>25</v>
       </c>
       <c r="B118" s="27" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C118" s="28">
         <v>25</v>
       </c>
       <c r="D118" s="26" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="E118" s="27" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="F118" s="26" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G118" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F118),0)&gt;0), MAX($G$1:G117)+1, ""))</f>
@@ -4902,19 +4914,19 @@
         <v>25</v>
       </c>
       <c r="B119" s="27" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C119" s="28">
         <v>25</v>
       </c>
       <c r="D119" s="26" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="E119" s="27" t="s">
         <v>133</v>
       </c>
       <c r="F119" s="26" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G119" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F119),0)&gt;0), MAX($G$1:G118)+1, ""))</f>
@@ -4930,19 +4942,19 @@
         <v>25</v>
       </c>
       <c r="B120" s="27" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C120" s="28">
         <v>25</v>
       </c>
       <c r="D120" s="26" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="E120" s="27" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="F120" s="26" t="s">
-        <v>326</v>
+        <v>177</v>
       </c>
       <c r="G120" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F120),0)&gt;0), MAX($G$1:G119)+1, ""))</f>
@@ -4958,19 +4970,19 @@
         <v>25</v>
       </c>
       <c r="B121" s="27" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C121" s="28">
         <v>25</v>
       </c>
-      <c r="D121" s="26">
-        <v>2.7</v>
+      <c r="D121" s="26" t="s">
+        <v>226</v>
       </c>
       <c r="E121" s="27" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="F121" s="26" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="G121" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F121),0)&gt;0), MAX($G$1:G120)+1, ""))</f>
@@ -4982,23 +4994,23 @@
       </c>
     </row>
     <row r="122" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A122" s="30">
+      <c r="A122" s="26">
         <v>25</v>
       </c>
-      <c r="B122" s="31" t="s">
-        <v>286</v>
-      </c>
-      <c r="C122" s="32">
+      <c r="B122" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="C122" s="28">
         <v>25</v>
       </c>
-      <c r="D122" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="E122" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="F122" s="30" t="s">
-        <v>104</v>
+      <c r="D122" s="26">
+        <v>2.7</v>
+      </c>
+      <c r="E122" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="F122" s="26" t="s">
+        <v>340</v>
       </c>
       <c r="G122" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F122),0)&gt;0), MAX($G$1:G121)+1, ""))</f>
@@ -5014,7 +5026,7 @@
         <v>25</v>
       </c>
       <c r="B123" s="31" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C123" s="32">
         <v>25</v>
@@ -5038,23 +5050,23 @@
       </c>
     </row>
     <row r="124" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A124" s="26">
+      <c r="A124" s="30">
         <v>25</v>
       </c>
-      <c r="B124" s="27" t="s">
-        <v>172</v>
-      </c>
-      <c r="C124" s="28">
+      <c r="B124" s="31" t="s">
+        <v>284</v>
+      </c>
+      <c r="C124" s="32">
         <v>25</v>
       </c>
-      <c r="D124" s="26" t="s">
-        <v>236</v>
-      </c>
-      <c r="E124" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F124" s="26" t="s">
-        <v>173</v>
+      <c r="D124" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="E124" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="F124" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G124" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F124),0)&gt;0), MAX($G$1:G123)+1, ""))</f>
@@ -5070,19 +5082,19 @@
         <v>25</v>
       </c>
       <c r="B125" s="27" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C125" s="28">
         <v>25</v>
       </c>
       <c r="D125" s="26" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="E125" s="27" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="F125" s="26" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G125" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F125),0)&gt;0), MAX($G$1:G124)+1, ""))</f>
@@ -5094,23 +5106,23 @@
       </c>
     </row>
     <row r="126" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A126" s="30">
+      <c r="A126" s="26">
         <v>25</v>
       </c>
-      <c r="B126" s="31" t="s">
-        <v>280</v>
-      </c>
-      <c r="C126" s="32">
+      <c r="B126" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="C126" s="28">
         <v>25</v>
       </c>
-      <c r="D126" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="E126" s="31" t="s">
+      <c r="D126" s="26" t="s">
+        <v>219</v>
+      </c>
+      <c r="E126" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F126" s="30" t="s">
-        <v>104</v>
+      <c r="F126" s="26" t="s">
+        <v>171</v>
       </c>
       <c r="G126" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F126),0)&gt;0), MAX($G$1:G125)+1, ""))</f>
@@ -5126,19 +5138,19 @@
         <v>25</v>
       </c>
       <c r="B127" s="27" t="s">
-        <v>168</v>
+        <v>362</v>
       </c>
       <c r="C127" s="28">
         <v>25</v>
       </c>
-      <c r="D127" s="26" t="s">
-        <v>223</v>
+      <c r="D127" s="26">
+        <v>3.4</v>
       </c>
       <c r="E127" s="27" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="F127" s="26" t="s">
-        <v>169</v>
+        <v>363</v>
       </c>
       <c r="G127" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F127),0)&gt;0), MAX($G$1:G126)+1, ""))</f>
@@ -5150,23 +5162,23 @@
       </c>
     </row>
     <row r="128" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A128" s="26">
+      <c r="A128" s="30">
         <v>25</v>
       </c>
-      <c r="B128" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="C128" s="28">
+      <c r="B128" s="31" t="s">
+        <v>280</v>
+      </c>
+      <c r="C128" s="32">
         <v>25</v>
       </c>
-      <c r="D128" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="E128" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F128" s="26" t="s">
-        <v>167</v>
+      <c r="D128" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="E128" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F128" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G128" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F128),0)&gt;0), MAX($G$1:G127)+1, ""))</f>
@@ -5182,19 +5194,19 @@
         <v>25</v>
       </c>
       <c r="B129" s="27" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C129" s="28">
         <v>25</v>
       </c>
       <c r="D129" s="26" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="E129" s="27" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="F129" s="26" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G129" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F129),0)&gt;0), MAX($G$1:G128)+1, ""))</f>
@@ -5210,19 +5222,19 @@
         <v>25</v>
       </c>
       <c r="B130" s="27" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C130" s="28">
         <v>25</v>
       </c>
       <c r="D130" s="26" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="E130" s="27" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="F130" s="26" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="G130" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F130),0)&gt;0), MAX($G$1:G129)+1, ""))</f>
@@ -5238,19 +5250,19 @@
         <v>25</v>
       </c>
       <c r="B131" s="27" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C131" s="28">
         <v>25</v>
       </c>
       <c r="D131" s="26" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="E131" s="27" t="s">
         <v>83</v>
       </c>
       <c r="F131" s="26" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G131" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F131),0)&gt;0), MAX($G$1:G130)+1, ""))</f>
@@ -5266,19 +5278,19 @@
         <v>25</v>
       </c>
       <c r="B132" s="27" t="s">
-        <v>344</v>
+        <v>162</v>
       </c>
       <c r="C132" s="28">
         <v>25</v>
       </c>
-      <c r="D132" s="26">
-        <v>3.4</v>
+      <c r="D132" s="26" t="s">
+        <v>238</v>
       </c>
       <c r="E132" s="27" t="s">
         <v>83</v>
       </c>
       <c r="F132" s="26" t="s">
-        <v>345</v>
+        <v>163</v>
       </c>
       <c r="G132" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B132),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E132),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F132),0)&gt;0), MAX($G$1:G131)+1, ""))</f>
@@ -5294,22 +5306,22 @@
         <v>25</v>
       </c>
       <c r="B133" s="27" t="s">
-        <v>312</v>
+        <v>160</v>
       </c>
       <c r="C133" s="28">
         <v>25</v>
       </c>
-      <c r="D133" s="26">
-        <v>3.9</v>
+      <c r="D133" s="26" t="s">
+        <v>230</v>
       </c>
       <c r="E133" s="27" t="s">
-        <v>311</v>
+        <v>83</v>
       </c>
       <c r="F133" s="26" t="s">
-        <v>313</v>
+        <v>161</v>
       </c>
       <c r="G133" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F133),0)&gt;0), MAX($G$1:G131)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F133),0)&gt;0), MAX($G$1:G132)+1, ""))</f>
         <v/>
       </c>
       <c r="H133" s="21" t="b">
@@ -5322,19 +5334,19 @@
         <v>25</v>
       </c>
       <c r="B134" s="27" t="s">
-        <v>158</v>
+        <v>344</v>
       </c>
       <c r="C134" s="28">
         <v>25</v>
       </c>
-      <c r="D134" s="26" t="s">
-        <v>229</v>
+      <c r="D134" s="26">
+        <v>3.4</v>
       </c>
       <c r="E134" s="27" t="s">
         <v>83</v>
       </c>
       <c r="F134" s="26" t="s">
-        <v>159</v>
+        <v>345</v>
       </c>
       <c r="G134" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F134),0)&gt;0), MAX($G$1:G133)+1, ""))</f>
@@ -5350,22 +5362,22 @@
         <v>25</v>
       </c>
       <c r="B135" s="27" t="s">
-        <v>156</v>
+        <v>312</v>
       </c>
       <c r="C135" s="28">
         <v>25</v>
       </c>
-      <c r="D135" s="26" t="s">
-        <v>226</v>
+      <c r="D135" s="26">
+        <v>3.9</v>
       </c>
       <c r="E135" s="27" t="s">
-        <v>8</v>
+        <v>311</v>
       </c>
       <c r="F135" s="26" t="s">
-        <v>157</v>
+        <v>313</v>
       </c>
       <c r="G135" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F135),0)&gt;0), MAX($G$1:G134)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F135),0)&gt;0), MAX($G$1:G133)+1, ""))</f>
         <v/>
       </c>
       <c r="H135" s="21" t="b">
@@ -5378,19 +5390,19 @@
         <v>25</v>
       </c>
       <c r="B136" s="27" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C136" s="28">
         <v>25</v>
       </c>
       <c r="D136" s="26" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E136" s="27" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="F136" s="26" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="G136" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F136),0)&gt;0), MAX($G$1:G135)+1, ""))</f>
@@ -5406,19 +5418,19 @@
         <v>25</v>
       </c>
       <c r="B137" s="27" t="s">
-        <v>249</v>
+        <v>156</v>
       </c>
       <c r="C137" s="28">
         <v>25</v>
       </c>
-      <c r="D137" s="39" t="s">
-        <v>231</v>
+      <c r="D137" s="26" t="s">
+        <v>226</v>
       </c>
       <c r="E137" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F137" s="26" t="s">
-        <v>250</v>
+        <v>157</v>
       </c>
       <c r="G137" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F137),0)&gt;0), MAX($G$1:G136)+1, ""))</f>
@@ -5434,19 +5446,19 @@
         <v>25</v>
       </c>
       <c r="B138" s="27" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C138" s="28">
         <v>25</v>
       </c>
       <c r="D138" s="26" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E138" s="27" t="s">
         <v>133</v>
       </c>
       <c r="F138" s="26" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G138" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F138),0)&gt;0), MAX($G$1:G137)+1, ""))</f>
@@ -5458,23 +5470,23 @@
       </c>
     </row>
     <row r="139" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A139" s="30">
+      <c r="A139" s="26">
         <v>25</v>
       </c>
-      <c r="B139" s="31" t="s">
-        <v>290</v>
-      </c>
-      <c r="C139" s="32">
+      <c r="B139" s="27" t="s">
+        <v>249</v>
+      </c>
+      <c r="C139" s="28">
         <v>25</v>
       </c>
-      <c r="D139" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="E139" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="F139" s="30" t="s">
-        <v>104</v>
+      <c r="D139" s="39" t="s">
+        <v>231</v>
+      </c>
+      <c r="E139" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F139" s="26" t="s">
+        <v>250</v>
       </c>
       <c r="G139" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F139),0)&gt;0), MAX($G$1:G138)+1, ""))</f>
@@ -5486,23 +5498,23 @@
       </c>
     </row>
     <row r="140" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A140" s="30">
+      <c r="A140" s="26">
         <v>25</v>
       </c>
-      <c r="B140" s="31" t="s">
-        <v>288</v>
-      </c>
-      <c r="C140" s="32">
+      <c r="B140" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="C140" s="28">
         <v>25</v>
       </c>
-      <c r="D140" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="E140" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="F140" s="30" t="s">
-        <v>104</v>
+      <c r="D140" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="E140" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="F140" s="26" t="s">
+        <v>153</v>
       </c>
       <c r="G140" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F140),0)&gt;0), MAX($G$1:G139)+1, ""))</f>
@@ -5518,7 +5530,7 @@
         <v>25</v>
       </c>
       <c r="B141" s="31" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C141" s="32">
         <v>25</v>
@@ -5542,23 +5554,23 @@
       </c>
     </row>
     <row r="142" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A142" s="26">
+      <c r="A142" s="30">
         <v>25</v>
       </c>
-      <c r="B142" s="27" t="s">
-        <v>254</v>
-      </c>
-      <c r="C142" s="28">
+      <c r="B142" s="31" t="s">
+        <v>288</v>
+      </c>
+      <c r="C142" s="32">
         <v>25</v>
       </c>
-      <c r="D142" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E142" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F142" s="26" t="s">
-        <v>255</v>
+      <c r="D142" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="E142" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="F142" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G142" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F142),0)&gt;0), MAX($G$1:G141)+1, ""))</f>
@@ -5574,7 +5586,7 @@
         <v>25</v>
       </c>
       <c r="B143" s="31" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C143" s="32">
         <v>25</v>
@@ -5602,22 +5614,22 @@
         <v>25</v>
       </c>
       <c r="B144" s="27" t="s">
-        <v>150</v>
+        <v>254</v>
       </c>
       <c r="C144" s="28">
         <v>25</v>
       </c>
-      <c r="D144" s="26" t="s">
-        <v>228</v>
+      <c r="D144" s="26">
+        <v>2.5</v>
       </c>
       <c r="E144" s="27" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="F144" s="26" t="s">
-        <v>151</v>
+        <v>255</v>
       </c>
       <c r="G144" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F144),0)&gt;0), MAX($G$1:G142)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F144),0)&gt;0), MAX($G$1:G143)+1, ""))</f>
         <v/>
       </c>
       <c r="H144" s="21" t="b">
@@ -5627,22 +5639,22 @@
     </row>
     <row r="145" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A145" s="30">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B145" s="31" t="s">
-        <v>194</v>
+        <v>287</v>
       </c>
       <c r="C145" s="32">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D145" s="30" t="s">
-        <v>234</v>
+        <v>209</v>
       </c>
       <c r="E145" s="31" t="s">
-        <v>133</v>
+        <v>285</v>
       </c>
       <c r="F145" s="30" t="s">
-        <v>195</v>
+        <v>104</v>
       </c>
       <c r="G145" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B145),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E145),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F145),0)&gt;0), MAX($G$1:G144)+1, ""))</f>
@@ -5654,26 +5666,26 @@
       </c>
     </row>
     <row r="146" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A146" s="30">
-        <v>30</v>
-      </c>
-      <c r="B146" s="31" t="s">
-        <v>193</v>
-      </c>
-      <c r="C146" s="32">
-        <v>30</v>
-      </c>
-      <c r="D146" s="30" t="s">
-        <v>243</v>
-      </c>
-      <c r="E146" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="F146" s="30" t="s">
-        <v>192</v>
+      <c r="A146" s="26">
+        <v>25</v>
+      </c>
+      <c r="B146" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C146" s="28">
+        <v>25</v>
+      </c>
+      <c r="D146" s="26" t="s">
+        <v>228</v>
+      </c>
+      <c r="E146" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="F146" s="26" t="s">
+        <v>151</v>
       </c>
       <c r="G146" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F146),0)&gt;0), MAX($G$1:G145)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F146),0)&gt;0), MAX($G$1:G144)+1, ""))</f>
         <v/>
       </c>
       <c r="H146" s="21" t="b">
@@ -5686,19 +5698,19 @@
         <v>30</v>
       </c>
       <c r="B147" s="31" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C147" s="32">
         <v>30</v>
       </c>
       <c r="D147" s="30" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="E147" s="31" t="s">
         <v>133</v>
       </c>
       <c r="F147" s="30" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G147" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F147),0)&gt;0), MAX($G$1:G146)+1, ""))</f>
@@ -5714,19 +5726,19 @@
         <v>30</v>
       </c>
       <c r="B148" s="31" t="s">
-        <v>248</v>
+        <v>193</v>
       </c>
       <c r="C148" s="32">
         <v>30</v>
       </c>
       <c r="D148" s="30" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="E148" s="31" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="F148" s="30" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G148" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F148),0)&gt;0), MAX($G$1:G147)+1, ""))</f>
@@ -5742,19 +5754,19 @@
         <v>30</v>
       </c>
       <c r="B149" s="31" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C149" s="32">
         <v>30</v>
       </c>
       <c r="D149" s="30" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E149" s="31" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="F149" s="30" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="G149" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B149),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E149),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F149),0)&gt;0), MAX($G$1:G148)+1, ""))</f>
@@ -5770,19 +5782,19 @@
         <v>30</v>
       </c>
       <c r="B150" s="31" t="s">
-        <v>186</v>
+        <v>248</v>
       </c>
       <c r="C150" s="32">
         <v>30</v>
       </c>
       <c r="D150" s="30" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="E150" s="31" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="F150" s="30" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G150" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B150),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E150),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F150),0)&gt;0), MAX($G$1:G149)+1, ""))</f>
@@ -5798,19 +5810,19 @@
         <v>30</v>
       </c>
       <c r="B151" s="31" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C151" s="32">
         <v>30</v>
       </c>
       <c r="D151" s="30" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="E151" s="31" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="F151" s="30" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="G151" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B151),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E151),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F151),0)&gt;0), MAX($G$1:G150)+1, ""))</f>
@@ -5826,19 +5838,19 @@
         <v>30</v>
       </c>
       <c r="B152" s="31" t="s">
-        <v>339</v>
+        <v>186</v>
       </c>
       <c r="C152" s="32">
         <v>30</v>
       </c>
-      <c r="D152" s="30">
-        <v>2.9</v>
+      <c r="D152" s="30" t="s">
+        <v>230</v>
       </c>
       <c r="E152" s="31" t="s">
         <v>83</v>
       </c>
       <c r="F152" s="30" t="s">
-        <v>340</v>
+        <v>187</v>
       </c>
       <c r="G152" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B152),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E152),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F152),0)&gt;0), MAX($G$1:G151)+1, ""))</f>
@@ -5854,22 +5866,22 @@
         <v>30</v>
       </c>
       <c r="B153" s="31" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C153" s="32">
         <v>30</v>
       </c>
       <c r="D153" s="30" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E153" s="31" t="s">
         <v>133</v>
       </c>
       <c r="F153" s="30" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G153" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B153),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E153),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F153),0)&gt;0), MAX($G$1:G151)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B153),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E153),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F153),0)&gt;0), MAX($G$1:G152)+1, ""))</f>
         <v/>
       </c>
       <c r="H153" s="21" t="b">
@@ -5878,23 +5890,23 @@
       </c>
     </row>
     <row r="154" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A154" s="26">
-        <v>40</v>
-      </c>
-      <c r="B154" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="C154" s="28">
-        <v>40</v>
-      </c>
-      <c r="D154" s="26" t="s">
-        <v>245</v>
-      </c>
-      <c r="E154" s="27" t="s">
-        <v>200</v>
-      </c>
-      <c r="F154" s="26" t="s">
-        <v>201</v>
+      <c r="A154" s="30">
+        <v>30</v>
+      </c>
+      <c r="B154" s="31" t="s">
+        <v>339</v>
+      </c>
+      <c r="C154" s="32">
+        <v>30</v>
+      </c>
+      <c r="D154" s="30">
+        <v>2.9</v>
+      </c>
+      <c r="E154" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="F154" s="30" t="s">
+        <v>340</v>
       </c>
       <c r="G154" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B154),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E154),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F154),0)&gt;0), MAX($G$1:G153)+1, ""))</f>
@@ -5906,26 +5918,26 @@
       </c>
     </row>
     <row r="155" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A155" s="26">
-        <v>40</v>
-      </c>
-      <c r="B155" s="27" t="s">
-        <v>196</v>
-      </c>
-      <c r="C155" s="28">
-        <v>40</v>
-      </c>
-      <c r="D155" s="26" t="s">
-        <v>244</v>
-      </c>
-      <c r="E155" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="F155" s="26" t="s">
-        <v>198</v>
+      <c r="A155" s="30">
+        <v>30</v>
+      </c>
+      <c r="B155" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="C155" s="32">
+        <v>30</v>
+      </c>
+      <c r="D155" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="E155" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="F155" s="30" t="s">
+        <v>183</v>
       </c>
       <c r="G155" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F155),0)&gt;0), MAX($G$1:G154)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F155),0)&gt;0), MAX($G$1:G153)+1, ""))</f>
         <v/>
       </c>
       <c r="H155" s="21" t="b">
@@ -5938,19 +5950,19 @@
         <v>40</v>
       </c>
       <c r="B156" s="27" t="s">
-        <v>251</v>
+        <v>199</v>
       </c>
       <c r="C156" s="28">
         <v>40</v>
       </c>
-      <c r="D156" s="26">
-        <v>8.3000000000000007</v>
+      <c r="D156" s="26" t="s">
+        <v>245</v>
       </c>
       <c r="E156" s="27" t="s">
-        <v>252</v>
+        <v>200</v>
       </c>
       <c r="F156" s="26" t="s">
-        <v>253</v>
+        <v>201</v>
       </c>
       <c r="G156" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B156),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E156),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F156),0)&gt;0), MAX($G$1:G155)+1, ""))</f>
@@ -5963,22 +5975,22 @@
     </row>
     <row r="157" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A157" s="26">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B157" s="27" t="s">
-        <v>296</v>
+        <v>196</v>
       </c>
       <c r="C157" s="28">
-        <v>45</v>
-      </c>
-      <c r="D157" s="26">
-        <v>10.199999999999999</v>
+        <v>40</v>
+      </c>
+      <c r="D157" s="26" t="s">
+        <v>244</v>
       </c>
       <c r="E157" s="27" t="s">
-        <v>297</v>
+        <v>197</v>
       </c>
       <c r="F157" s="26" t="s">
-        <v>298</v>
+        <v>198</v>
       </c>
       <c r="G157" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F157),0)&gt;0), MAX($G$1:G156)+1, ""))</f>
@@ -5990,16 +6002,60 @@
       </c>
     </row>
     <row r="158" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A158" s="1"/>
-      <c r="C158" s="1"/>
-      <c r="D158" s="1"/>
-      <c r="F158" s="1"/>
+      <c r="A158" s="26">
+        <v>40</v>
+      </c>
+      <c r="B158" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="C158" s="28">
+        <v>40</v>
+      </c>
+      <c r="D158" s="26">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E158" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="F158" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="G158" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B158),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E158),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F158),0)&gt;0), MAX($G$1:G157)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H158" s="21" t="b">
+        <f>A158=C158</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="159" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A159" s="1"/>
-      <c r="C159" s="1"/>
-      <c r="D159" s="1"/>
-      <c r="F159" s="1"/>
+      <c r="A159" s="26">
+        <v>45</v>
+      </c>
+      <c r="B159" s="27" t="s">
+        <v>296</v>
+      </c>
+      <c r="C159" s="28">
+        <v>45</v>
+      </c>
+      <c r="D159" s="26">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E159" s="27" t="s">
+        <v>297</v>
+      </c>
+      <c r="F159" s="26" t="s">
+        <v>298</v>
+      </c>
+      <c r="G159" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F159),0)&gt;0), MAX($G$1:G158)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H159" s="21" t="b">
+        <f>A159=C159</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="160" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
@@ -11271,10 +11327,10 @@
       <sortCondition ref="D2:D147"/>
     </sortState>
   </autoFilter>
-  <sortState ref="A2:H157">
-    <sortCondition ref="A2:A157"/>
-    <sortCondition ref="B2:B157"/>
-    <sortCondition ref="D2:D157"/>
+  <sortState ref="A2:H159">
+    <sortCondition ref="A2:A159"/>
+    <sortCondition ref="B2:B159"/>
+    <sortCondition ref="D2:D159"/>
   </sortState>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="366">
   <si>
     <t>Grupo</t>
   </si>
@@ -1117,6 +1117,12 @@
   </si>
   <si>
     <t>21720-070</t>
+  </si>
+  <si>
+    <t>HOSPITAL ALBERT SCHWEITZER</t>
+  </si>
+  <si>
+    <t>21720-040</t>
   </si>
 </sst>
 </file>
@@ -1638,7 +1644,7 @@
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.453125" customWidth="1"/>
-    <col min="2" max="2" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.90625" customWidth="1"/>
     <col min="4" max="4" width="7.81640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.6328125" bestFit="1" customWidth="1"/>
@@ -4998,19 +5004,19 @@
         <v>25</v>
       </c>
       <c r="B122" s="27" t="s">
-        <v>174</v>
+        <v>364</v>
       </c>
       <c r="C122" s="28">
         <v>25</v>
       </c>
       <c r="D122" s="26">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="E122" s="27" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="F122" s="26" t="s">
-        <v>340</v>
+        <v>365</v>
       </c>
       <c r="G122" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F122),0)&gt;0), MAX($G$1:G121)+1, ""))</f>
@@ -5022,23 +5028,23 @@
       </c>
     </row>
     <row r="123" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A123" s="30">
+      <c r="A123" s="26">
         <v>25</v>
       </c>
-      <c r="B123" s="31" t="s">
-        <v>286</v>
-      </c>
-      <c r="C123" s="32">
+      <c r="B123" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="C123" s="28">
         <v>25</v>
       </c>
-      <c r="D123" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="E123" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="F123" s="30" t="s">
-        <v>104</v>
+      <c r="D123" s="26">
+        <v>2.7</v>
+      </c>
+      <c r="E123" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="F123" s="26" t="s">
+        <v>340</v>
       </c>
       <c r="G123" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F123),0)&gt;0), MAX($G$1:G122)+1, ""))</f>
@@ -5054,7 +5060,7 @@
         <v>25</v>
       </c>
       <c r="B124" s="31" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C124" s="32">
         <v>25</v>
@@ -5078,23 +5084,23 @@
       </c>
     </row>
     <row r="125" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A125" s="26">
+      <c r="A125" s="30">
         <v>25</v>
       </c>
-      <c r="B125" s="27" t="s">
-        <v>172</v>
-      </c>
-      <c r="C125" s="28">
+      <c r="B125" s="31" t="s">
+        <v>284</v>
+      </c>
+      <c r="C125" s="32">
         <v>25</v>
       </c>
-      <c r="D125" s="26" t="s">
-        <v>236</v>
-      </c>
-      <c r="E125" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F125" s="26" t="s">
-        <v>173</v>
+      <c r="D125" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="E125" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="F125" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G125" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F125),0)&gt;0), MAX($G$1:G124)+1, ""))</f>
@@ -5110,19 +5116,19 @@
         <v>25</v>
       </c>
       <c r="B126" s="27" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C126" s="28">
         <v>25</v>
       </c>
       <c r="D126" s="26" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="E126" s="27" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="F126" s="26" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G126" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F126),0)&gt;0), MAX($G$1:G125)+1, ""))</f>
@@ -5138,19 +5144,19 @@
         <v>25</v>
       </c>
       <c r="B127" s="27" t="s">
-        <v>362</v>
+        <v>170</v>
       </c>
       <c r="C127" s="28">
         <v>25</v>
       </c>
-      <c r="D127" s="26">
-        <v>3.4</v>
+      <c r="D127" s="26" t="s">
+        <v>219</v>
       </c>
       <c r="E127" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F127" s="26" t="s">
-        <v>363</v>
+        <v>171</v>
       </c>
       <c r="G127" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F127),0)&gt;0), MAX($G$1:G126)+1, ""))</f>
@@ -5162,23 +5168,23 @@
       </c>
     </row>
     <row r="128" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A128" s="30">
+      <c r="A128" s="26">
         <v>25</v>
       </c>
-      <c r="B128" s="31" t="s">
-        <v>280</v>
-      </c>
-      <c r="C128" s="32">
+      <c r="B128" s="27" t="s">
+        <v>362</v>
+      </c>
+      <c r="C128" s="28">
         <v>25</v>
       </c>
-      <c r="D128" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="E128" s="31" t="s">
+      <c r="D128" s="26">
+        <v>3.4</v>
+      </c>
+      <c r="E128" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F128" s="30" t="s">
-        <v>104</v>
+      <c r="F128" s="26" t="s">
+        <v>363</v>
       </c>
       <c r="G128" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F128),0)&gt;0), MAX($G$1:G127)+1, ""))</f>
@@ -5190,23 +5196,23 @@
       </c>
     </row>
     <row r="129" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A129" s="26">
+      <c r="A129" s="30">
         <v>25</v>
       </c>
-      <c r="B129" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="C129" s="28">
+      <c r="B129" s="31" t="s">
+        <v>280</v>
+      </c>
+      <c r="C129" s="32">
         <v>25</v>
       </c>
-      <c r="D129" s="26" t="s">
-        <v>223</v>
-      </c>
-      <c r="E129" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F129" s="26" t="s">
-        <v>169</v>
+      <c r="D129" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="E129" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F129" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G129" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F129),0)&gt;0), MAX($G$1:G128)+1, ""))</f>
@@ -5222,19 +5228,19 @@
         <v>25</v>
       </c>
       <c r="B130" s="27" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C130" s="28">
         <v>25</v>
       </c>
       <c r="D130" s="26" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="E130" s="27" t="s">
         <v>133</v>
       </c>
       <c r="F130" s="26" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G130" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F130),0)&gt;0), MAX($G$1:G129)+1, ""))</f>
@@ -5250,19 +5256,19 @@
         <v>25</v>
       </c>
       <c r="B131" s="27" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C131" s="28">
         <v>25</v>
       </c>
       <c r="D131" s="26" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E131" s="27" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="F131" s="26" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G131" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F131),0)&gt;0), MAX($G$1:G130)+1, ""))</f>
@@ -5278,19 +5284,19 @@
         <v>25</v>
       </c>
       <c r="B132" s="27" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C132" s="28">
         <v>25</v>
       </c>
       <c r="D132" s="26" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="E132" s="27" t="s">
         <v>83</v>
       </c>
       <c r="F132" s="26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G132" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B132),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E132),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F132),0)&gt;0), MAX($G$1:G131)+1, ""))</f>
@@ -5306,19 +5312,19 @@
         <v>25</v>
       </c>
       <c r="B133" s="27" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C133" s="28">
         <v>25</v>
       </c>
       <c r="D133" s="26" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="E133" s="27" t="s">
         <v>83</v>
       </c>
       <c r="F133" s="26" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G133" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F133),0)&gt;0), MAX($G$1:G132)+1, ""))</f>
@@ -5334,19 +5340,19 @@
         <v>25</v>
       </c>
       <c r="B134" s="27" t="s">
-        <v>344</v>
+        <v>160</v>
       </c>
       <c r="C134" s="28">
         <v>25</v>
       </c>
-      <c r="D134" s="26">
-        <v>3.4</v>
+      <c r="D134" s="26" t="s">
+        <v>230</v>
       </c>
       <c r="E134" s="27" t="s">
         <v>83</v>
       </c>
       <c r="F134" s="26" t="s">
-        <v>345</v>
+        <v>161</v>
       </c>
       <c r="G134" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F134),0)&gt;0), MAX($G$1:G133)+1, ""))</f>
@@ -5362,22 +5368,22 @@
         <v>25</v>
       </c>
       <c r="B135" s="27" t="s">
-        <v>312</v>
+        <v>344</v>
       </c>
       <c r="C135" s="28">
         <v>25</v>
       </c>
       <c r="D135" s="26">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="E135" s="27" t="s">
-        <v>311</v>
+        <v>83</v>
       </c>
       <c r="F135" s="26" t="s">
-        <v>313</v>
+        <v>345</v>
       </c>
       <c r="G135" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F135),0)&gt;0), MAX($G$1:G133)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F135),0)&gt;0), MAX($G$1:G134)+1, ""))</f>
         <v/>
       </c>
       <c r="H135" s="21" t="b">
@@ -5390,22 +5396,22 @@
         <v>25</v>
       </c>
       <c r="B136" s="27" t="s">
-        <v>158</v>
+        <v>312</v>
       </c>
       <c r="C136" s="28">
         <v>25</v>
       </c>
-      <c r="D136" s="26" t="s">
-        <v>229</v>
+      <c r="D136" s="26">
+        <v>3.9</v>
       </c>
       <c r="E136" s="27" t="s">
-        <v>83</v>
+        <v>311</v>
       </c>
       <c r="F136" s="26" t="s">
-        <v>159</v>
+        <v>313</v>
       </c>
       <c r="G136" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F136),0)&gt;0), MAX($G$1:G135)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F136),0)&gt;0), MAX($G$1:G134)+1, ""))</f>
         <v/>
       </c>
       <c r="H136" s="21" t="b">
@@ -5418,19 +5424,19 @@
         <v>25</v>
       </c>
       <c r="B137" s="27" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C137" s="28">
         <v>25</v>
       </c>
       <c r="D137" s="26" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E137" s="27" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="F137" s="26" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G137" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F137),0)&gt;0), MAX($G$1:G136)+1, ""))</f>
@@ -5446,19 +5452,19 @@
         <v>25</v>
       </c>
       <c r="B138" s="27" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C138" s="28">
         <v>25</v>
       </c>
       <c r="D138" s="26" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="E138" s="27" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="F138" s="26" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G138" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F138),0)&gt;0), MAX($G$1:G137)+1, ""))</f>
@@ -5474,19 +5480,19 @@
         <v>25</v>
       </c>
       <c r="B139" s="27" t="s">
-        <v>249</v>
+        <v>154</v>
       </c>
       <c r="C139" s="28">
         <v>25</v>
       </c>
-      <c r="D139" s="39" t="s">
-        <v>231</v>
+      <c r="D139" s="26" t="s">
+        <v>232</v>
       </c>
       <c r="E139" s="27" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="F139" s="26" t="s">
-        <v>250</v>
+        <v>155</v>
       </c>
       <c r="G139" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F139),0)&gt;0), MAX($G$1:G138)+1, ""))</f>
@@ -5502,19 +5508,19 @@
         <v>25</v>
       </c>
       <c r="B140" s="27" t="s">
-        <v>152</v>
+        <v>249</v>
       </c>
       <c r="C140" s="28">
         <v>25</v>
       </c>
-      <c r="D140" s="26" t="s">
-        <v>237</v>
+      <c r="D140" s="39" t="s">
+        <v>231</v>
       </c>
       <c r="E140" s="27" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="F140" s="26" t="s">
-        <v>153</v>
+        <v>250</v>
       </c>
       <c r="G140" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F140),0)&gt;0), MAX($G$1:G139)+1, ""))</f>
@@ -5526,23 +5532,23 @@
       </c>
     </row>
     <row r="141" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A141" s="30">
+      <c r="A141" s="26">
         <v>25</v>
       </c>
-      <c r="B141" s="31" t="s">
-        <v>290</v>
-      </c>
-      <c r="C141" s="32">
+      <c r="B141" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="C141" s="28">
         <v>25</v>
       </c>
-      <c r="D141" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="E141" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="F141" s="30" t="s">
-        <v>104</v>
+      <c r="D141" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="E141" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="F141" s="26" t="s">
+        <v>153</v>
       </c>
       <c r="G141" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F141),0)&gt;0), MAX($G$1:G140)+1, ""))</f>
@@ -5558,7 +5564,7 @@
         <v>25</v>
       </c>
       <c r="B142" s="31" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C142" s="32">
         <v>25</v>
@@ -5586,7 +5592,7 @@
         <v>25</v>
       </c>
       <c r="B143" s="31" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C143" s="32">
         <v>25</v>
@@ -5610,23 +5616,23 @@
       </c>
     </row>
     <row r="144" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A144" s="26">
+      <c r="A144" s="30">
         <v>25</v>
       </c>
-      <c r="B144" s="27" t="s">
-        <v>254</v>
-      </c>
-      <c r="C144" s="28">
+      <c r="B144" s="31" t="s">
+        <v>289</v>
+      </c>
+      <c r="C144" s="32">
         <v>25</v>
       </c>
-      <c r="D144" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E144" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F144" s="26" t="s">
-        <v>255</v>
+      <c r="D144" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="E144" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="F144" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G144" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F144),0)&gt;0), MAX($G$1:G143)+1, ""))</f>
@@ -5638,23 +5644,23 @@
       </c>
     </row>
     <row r="145" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A145" s="30">
+      <c r="A145" s="26">
         <v>25</v>
       </c>
-      <c r="B145" s="31" t="s">
-        <v>287</v>
-      </c>
-      <c r="C145" s="32">
+      <c r="B145" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="C145" s="28">
         <v>25</v>
       </c>
-      <c r="D145" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="E145" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="F145" s="30" t="s">
-        <v>104</v>
+      <c r="D145" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E145" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="F145" s="26" t="s">
+        <v>255</v>
       </c>
       <c r="G145" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B145),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E145),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F145),0)&gt;0), MAX($G$1:G144)+1, ""))</f>
@@ -5666,26 +5672,26 @@
       </c>
     </row>
     <row r="146" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A146" s="26">
+      <c r="A146" s="30">
         <v>25</v>
       </c>
-      <c r="B146" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="C146" s="28">
+      <c r="B146" s="31" t="s">
+        <v>287</v>
+      </c>
+      <c r="C146" s="32">
         <v>25</v>
       </c>
-      <c r="D146" s="26" t="s">
-        <v>228</v>
-      </c>
-      <c r="E146" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="F146" s="26" t="s">
-        <v>151</v>
+      <c r="D146" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="E146" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="F146" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G146" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F146),0)&gt;0), MAX($G$1:G144)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F146),0)&gt;0), MAX($G$1:G145)+1, ""))</f>
         <v/>
       </c>
       <c r="H146" s="21" t="b">
@@ -5694,26 +5700,26 @@
       </c>
     </row>
     <row r="147" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A147" s="30">
-        <v>30</v>
-      </c>
-      <c r="B147" s="31" t="s">
-        <v>194</v>
-      </c>
-      <c r="C147" s="32">
-        <v>30</v>
-      </c>
-      <c r="D147" s="30" t="s">
-        <v>234</v>
-      </c>
-      <c r="E147" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="F147" s="30" t="s">
-        <v>195</v>
+      <c r="A147" s="26">
+        <v>25</v>
+      </c>
+      <c r="B147" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C147" s="28">
+        <v>25</v>
+      </c>
+      <c r="D147" s="26" t="s">
+        <v>228</v>
+      </c>
+      <c r="E147" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="F147" s="26" t="s">
+        <v>151</v>
       </c>
       <c r="G147" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F147),0)&gt;0), MAX($G$1:G146)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F147),0)&gt;0), MAX($G$1:G145)+1, ""))</f>
         <v/>
       </c>
       <c r="H147" s="21" t="b">
@@ -5726,19 +5732,19 @@
         <v>30</v>
       </c>
       <c r="B148" s="31" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C148" s="32">
         <v>30</v>
       </c>
       <c r="D148" s="30" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="E148" s="31" t="s">
         <v>133</v>
       </c>
       <c r="F148" s="30" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G148" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F148),0)&gt;0), MAX($G$1:G147)+1, ""))</f>
@@ -5754,13 +5760,13 @@
         <v>30</v>
       </c>
       <c r="B149" s="31" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C149" s="32">
         <v>30</v>
       </c>
       <c r="D149" s="30" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E149" s="31" t="s">
         <v>133</v>
@@ -5782,19 +5788,19 @@
         <v>30</v>
       </c>
       <c r="B150" s="31" t="s">
-        <v>248</v>
+        <v>191</v>
       </c>
       <c r="C150" s="32">
         <v>30</v>
       </c>
       <c r="D150" s="30" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="E150" s="31" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="F150" s="30" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G150" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B150),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E150),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F150),0)&gt;0), MAX($G$1:G149)+1, ""))</f>
@@ -5810,19 +5816,19 @@
         <v>30</v>
       </c>
       <c r="B151" s="31" t="s">
-        <v>188</v>
+        <v>248</v>
       </c>
       <c r="C151" s="32">
         <v>30</v>
       </c>
       <c r="D151" s="30" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="E151" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F151" s="30" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G151" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B151),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E151),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F151),0)&gt;0), MAX($G$1:G150)+1, ""))</f>
@@ -5838,19 +5844,19 @@
         <v>30</v>
       </c>
       <c r="B152" s="31" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C152" s="32">
         <v>30</v>
       </c>
       <c r="D152" s="30" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E152" s="31" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="F152" s="30" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="G152" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B152),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E152),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F152),0)&gt;0), MAX($G$1:G151)+1, ""))</f>
@@ -5866,19 +5872,19 @@
         <v>30</v>
       </c>
       <c r="B153" s="31" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C153" s="32">
         <v>30</v>
       </c>
       <c r="D153" s="30" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="E153" s="31" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="F153" s="30" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G153" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B153),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E153),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F153),0)&gt;0), MAX($G$1:G152)+1, ""))</f>
@@ -5894,19 +5900,19 @@
         <v>30</v>
       </c>
       <c r="B154" s="31" t="s">
-        <v>339</v>
+        <v>184</v>
       </c>
       <c r="C154" s="32">
         <v>30</v>
       </c>
-      <c r="D154" s="30">
-        <v>2.9</v>
+      <c r="D154" s="30" t="s">
+        <v>241</v>
       </c>
       <c r="E154" s="31" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="F154" s="30" t="s">
-        <v>340</v>
+        <v>185</v>
       </c>
       <c r="G154" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B154),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E154),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F154),0)&gt;0), MAX($G$1:G153)+1, ""))</f>
@@ -5922,22 +5928,22 @@
         <v>30</v>
       </c>
       <c r="B155" s="31" t="s">
-        <v>182</v>
+        <v>339</v>
       </c>
       <c r="C155" s="32">
         <v>30</v>
       </c>
-      <c r="D155" s="30" t="s">
-        <v>240</v>
+      <c r="D155" s="30">
+        <v>2.9</v>
       </c>
       <c r="E155" s="31" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="F155" s="30" t="s">
-        <v>183</v>
+        <v>340</v>
       </c>
       <c r="G155" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F155),0)&gt;0), MAX($G$1:G153)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F155),0)&gt;0), MAX($G$1:G154)+1, ""))</f>
         <v/>
       </c>
       <c r="H155" s="21" t="b">
@@ -5946,26 +5952,26 @@
       </c>
     </row>
     <row r="156" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A156" s="26">
-        <v>40</v>
-      </c>
-      <c r="B156" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="C156" s="28">
-        <v>40</v>
-      </c>
-      <c r="D156" s="26" t="s">
-        <v>245</v>
-      </c>
-      <c r="E156" s="27" t="s">
-        <v>200</v>
-      </c>
-      <c r="F156" s="26" t="s">
-        <v>201</v>
+      <c r="A156" s="30">
+        <v>30</v>
+      </c>
+      <c r="B156" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="C156" s="32">
+        <v>30</v>
+      </c>
+      <c r="D156" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="E156" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="F156" s="30" t="s">
+        <v>183</v>
       </c>
       <c r="G156" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B156),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E156),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F156),0)&gt;0), MAX($G$1:G155)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B156),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E156),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F156),0)&gt;0), MAX($G$1:G154)+1, ""))</f>
         <v/>
       </c>
       <c r="H156" s="21" t="b">
@@ -5978,19 +5984,19 @@
         <v>40</v>
       </c>
       <c r="B157" s="27" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C157" s="28">
         <v>40</v>
       </c>
       <c r="D157" s="26" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E157" s="27" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F157" s="26" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="G157" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F157),0)&gt;0), MAX($G$1:G156)+1, ""))</f>
@@ -6006,19 +6012,19 @@
         <v>40</v>
       </c>
       <c r="B158" s="27" t="s">
-        <v>251</v>
+        <v>196</v>
       </c>
       <c r="C158" s="28">
         <v>40</v>
       </c>
-      <c r="D158" s="26">
-        <v>8.3000000000000007</v>
+      <c r="D158" s="26" t="s">
+        <v>244</v>
       </c>
       <c r="E158" s="27" t="s">
-        <v>252</v>
+        <v>197</v>
       </c>
       <c r="F158" s="26" t="s">
-        <v>253</v>
+        <v>198</v>
       </c>
       <c r="G158" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B158),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E158),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F158),0)&gt;0), MAX($G$1:G157)+1, ""))</f>
@@ -6031,22 +6037,22 @@
     </row>
     <row r="159" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A159" s="26">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B159" s="27" t="s">
-        <v>296</v>
+        <v>251</v>
       </c>
       <c r="C159" s="28">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D159" s="26">
-        <v>10.199999999999999</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="E159" s="27" t="s">
-        <v>297</v>
+        <v>252</v>
       </c>
       <c r="F159" s="26" t="s">
-        <v>298</v>
+        <v>253</v>
       </c>
       <c r="G159" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F159),0)&gt;0), MAX($G$1:G158)+1, ""))</f>
@@ -6058,10 +6064,32 @@
       </c>
     </row>
     <row r="160" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A160" s="1"/>
-      <c r="C160" s="1"/>
-      <c r="D160" s="1"/>
-      <c r="F160" s="1"/>
+      <c r="A160" s="26">
+        <v>45</v>
+      </c>
+      <c r="B160" s="27" t="s">
+        <v>296</v>
+      </c>
+      <c r="C160" s="28">
+        <v>45</v>
+      </c>
+      <c r="D160" s="26">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E160" s="27" t="s">
+        <v>297</v>
+      </c>
+      <c r="F160" s="26" t="s">
+        <v>298</v>
+      </c>
+      <c r="G160" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B160),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E160),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F160),0)&gt;0), MAX($G$1:G159)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H160" s="21" t="b">
+        <f>A160=C160</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="161" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
@@ -11327,10 +11355,10 @@
       <sortCondition ref="D2:D147"/>
     </sortState>
   </autoFilter>
-  <sortState ref="A2:H159">
-    <sortCondition ref="A2:A159"/>
-    <sortCondition ref="B2:B159"/>
-    <sortCondition ref="D2:D159"/>
+  <sortState ref="A2:H160">
+    <sortCondition ref="A2:A160"/>
+    <sortCondition ref="B2:B160"/>
+    <sortCondition ref="D2:D160"/>
   </sortState>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Consulta" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$148</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$149</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$136</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Base!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="367">
   <si>
     <t>Grupo</t>
   </si>
@@ -84,9 +84,6 @@
     <t>21710-250</t>
   </si>
   <si>
-    <t>GAL RAPOSA</t>
-  </si>
-  <si>
     <t>21710-260</t>
   </si>
   <si>
@@ -237,9 +234,6 @@
     <t>21740-220</t>
   </si>
   <si>
-    <t>CARLOS WENCESLEU</t>
-  </si>
-  <si>
     <t>21715-320</t>
   </si>
   <si>
@@ -1123,6 +1117,15 @@
   </si>
   <si>
     <t>21720-040</t>
+  </si>
+  <si>
+    <t>GENERAL RAPOSO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOS WENCESLEU </t>
+  </si>
+  <si>
+    <t>CARLOS WENCESLEU ATÉ O PARQUE</t>
   </si>
 </sst>
 </file>
@@ -1640,7 +1643,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H1036"/>
+  <dimension ref="A1:H1037"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.453125" customWidth="1"/>
@@ -1671,7 +1674,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="25" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
@@ -1679,19 +1682,19 @@
         <v>13</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C2" s="32">
         <v>13</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F2" s="30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B2),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E2),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F2),0)&gt;0), MAX($G$1:G1)+1, ""))</f>
@@ -1703,26 +1706,26 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="30">
+      <c r="A3" s="26">
         <v>13</v>
       </c>
-      <c r="B3" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="32">
+      <c r="B3" s="27" t="s">
+        <v>366</v>
+      </c>
+      <c r="C3" s="28">
         <v>13</v>
       </c>
-      <c r="D3" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="31" t="s">
+      <c r="D3" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="E3" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="30" t="s">
-        <v>29</v>
+      <c r="F3" s="26" t="s">
+        <v>69</v>
       </c>
       <c r="G3" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B3),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E3),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F3),0)&gt;0), MAX($G$1:G2)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B3),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E3),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F3),0)&gt;0), MAX($G$1:G1)+1, ""))</f>
         <v/>
       </c>
       <c r="H3" s="21" t="b">
@@ -1735,19 +1738,19 @@
         <v>13</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>277</v>
+        <v>26</v>
       </c>
       <c r="C4" s="32">
         <v>13</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>272</v>
+        <v>8</v>
       </c>
       <c r="F4" s="30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G4" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B4),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E4),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F4),0)&gt;0), MAX($G$1:G3)+1, ""))</f>
@@ -1763,19 +1766,19 @@
         <v>13</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C5" s="32">
         <v>13</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F5" s="30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G5" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B5),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E5),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F5),0)&gt;0), MAX($G$1:G4)+1, ""))</f>
@@ -1791,19 +1794,19 @@
         <v>13</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>24</v>
+        <v>276</v>
       </c>
       <c r="C6" s="32">
         <v>13</v>
       </c>
       <c r="D6" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="31" t="s">
+        <v>270</v>
+      </c>
+      <c r="F6" s="30" t="s">
         <v>25</v>
-      </c>
-      <c r="E6" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="30" t="s">
-        <v>26</v>
       </c>
       <c r="G6" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B6),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E6),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F6),0)&gt;0), MAX($G$1:G5)+1, ""))</f>
@@ -1819,19 +1822,19 @@
         <v>13</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>276</v>
+        <v>23</v>
       </c>
       <c r="C7" s="32">
         <v>13</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>272</v>
+        <v>8</v>
       </c>
       <c r="F7" s="30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G7" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B7),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E7),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F7),0)&gt;0), MAX($G$1:G6)+1, ""))</f>
@@ -1847,19 +1850,19 @@
         <v>13</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="C8" s="32">
         <v>13</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F8" s="30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G8" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B8),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E8),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F8),0)&gt;0), MAX($G$1:G7)+1, ""))</f>
@@ -1875,19 +1878,19 @@
         <v>13</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>21</v>
+        <v>279</v>
       </c>
       <c r="C9" s="32">
         <v>13</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>8</v>
+        <v>270</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G9" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B9),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E9),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F9),0)&gt;0), MAX($G$1:G8)+1, ""))</f>
@@ -1903,19 +1906,19 @@
         <v>13</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>271</v>
+        <v>20</v>
       </c>
       <c r="C10" s="32">
         <v>13</v>
       </c>
       <c r="D10" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="30" t="s">
         <v>22</v>
-      </c>
-      <c r="E10" s="31" t="s">
-        <v>272</v>
-      </c>
-      <c r="F10" s="30" t="s">
-        <v>26</v>
       </c>
       <c r="G10" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B10),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E10),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F10),0)&gt;0), MAX($G$1:G9)+1, ""))</f>
@@ -1931,19 +1934,19 @@
         <v>13</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>19</v>
+        <v>269</v>
       </c>
       <c r="C11" s="32">
         <v>13</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>208</v>
+        <v>21</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>8</v>
+        <v>270</v>
       </c>
       <c r="F11" s="30" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G11" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B11),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E11),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F11),0)&gt;0), MAX($G$1:G10)+1, ""))</f>
@@ -1959,19 +1962,19 @@
         <v>13</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C12" s="32">
         <v>13</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F12" s="30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G12" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B12),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E12),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F12),0)&gt;0), MAX($G$1:G11)+1, ""))</f>
@@ -1987,19 +1990,19 @@
         <v>13</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>16</v>
+        <v>364</v>
       </c>
       <c r="C13" s="32">
         <v>13</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>17</v>
+        <v>206</v>
       </c>
       <c r="E13" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F13" s="30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G13" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B13),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E13),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F13),0)&gt;0), MAX($G$1:G12)+1, ""))</f>
@@ -2015,19 +2018,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>273</v>
+        <v>16</v>
       </c>
       <c r="C14" s="32">
         <v>13</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>272</v>
+        <v>8</v>
       </c>
       <c r="F14" s="30" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G14" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B14),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E14),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F14),0)&gt;0), MAX($G$1:G13)+1, ""))</f>
@@ -2043,19 +2046,19 @@
         <v>13</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>13</v>
+        <v>271</v>
       </c>
       <c r="C15" s="32">
         <v>13</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>8</v>
+        <v>270</v>
       </c>
       <c r="F15" s="30" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G15" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B15),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E15),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F15),0)&gt;0), MAX($G$1:G14)+1, ""))</f>
@@ -2071,19 +2074,19 @@
         <v>13</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C16" s="32">
         <v>13</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E16" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F16" s="30" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G16" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B16),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E16),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F16),0)&gt;0), MAX($G$1:G15)+1, ""))</f>
@@ -2099,19 +2102,19 @@
         <v>13</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C17" s="32">
         <v>13</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E17" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F17" s="30" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G17" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B17),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E17),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F17),0)&gt;0), MAX($G$1:G16)+1, ""))</f>
@@ -2123,23 +2126,23 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="26">
-        <v>15</v>
-      </c>
-      <c r="B18" s="27" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" s="28">
-        <v>15</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="E18" s="27" t="s">
-        <v>307</v>
-      </c>
-      <c r="F18" s="26" t="s">
-        <v>77</v>
+      <c r="A18" s="30">
+        <v>13</v>
+      </c>
+      <c r="B18" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="32">
+        <v>13</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="30" t="s">
+        <v>9</v>
       </c>
       <c r="G18" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B18),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E18),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F18),0)&gt;0), MAX($G$1:G17)+1, ""))</f>
@@ -2161,10 +2164,10 @@
         <v>15</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>8</v>
+        <v>305</v>
       </c>
       <c r="F19" s="26" t="s">
         <v>75</v>
@@ -2183,22 +2186,22 @@
         <v>15</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C20" s="28">
         <v>15</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E20" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G20" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B20),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E20),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F20),0)&gt;0), MAX($G$1:G18)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B20),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E20),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F20),0)&gt;0), MAX($G$1:G19)+1, ""))</f>
         <v/>
       </c>
       <c r="H20" s="21" t="b">
@@ -2211,22 +2214,22 @@
         <v>15</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>67</v>
+        <v>365</v>
       </c>
       <c r="C21" s="28">
         <v>15</v>
       </c>
-      <c r="D21" s="26" t="s">
-        <v>221</v>
+      <c r="D21" s="26">
+        <v>1</v>
       </c>
       <c r="E21" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G21" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F21),0)&gt;0), MAX($G$1:G20)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F21),0)&gt;0), MAX($G$1:G18)+1, ""))</f>
         <v/>
       </c>
       <c r="H21" s="21" t="b">
@@ -2239,19 +2242,19 @@
         <v>15</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C22" s="28">
         <v>15</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="E22" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G22" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B22),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E22),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F22),0)&gt;0), MAX($G$1:G21)+1, ""))</f>
@@ -2267,19 +2270,19 @@
         <v>15</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>268</v>
+        <v>64</v>
       </c>
       <c r="C23" s="28">
         <v>15</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>269</v>
+        <v>8</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G23" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B23),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E23),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F23),0)&gt;0), MAX($G$1:G22)+1, ""))</f>
@@ -2295,19 +2298,19 @@
         <v>15</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>347</v>
+        <v>266</v>
       </c>
       <c r="C24" s="28">
         <v>15</v>
       </c>
-      <c r="D24" s="26">
-        <v>2.5</v>
+      <c r="D24" s="26" t="s">
+        <v>206</v>
       </c>
       <c r="E24" s="27" t="s">
-        <v>8</v>
+        <v>267</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>348</v>
+        <v>65</v>
       </c>
       <c r="G24" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B24),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E24),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F24),0)&gt;0), MAX($G$1:G23)+1, ""))</f>
@@ -2323,19 +2326,19 @@
         <v>15</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>261</v>
+        <v>345</v>
       </c>
       <c r="C25" s="28">
         <v>15</v>
       </c>
-      <c r="D25" s="26" t="s">
-        <v>7</v>
+      <c r="D25" s="26">
+        <v>2.5</v>
       </c>
       <c r="E25" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>263</v>
+        <v>346</v>
       </c>
       <c r="G25" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B25),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E25),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F25),0)&gt;0), MAX($G$1:G24)+1, ""))</f>
@@ -2351,19 +2354,19 @@
         <v>15</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>353</v>
+        <v>259</v>
       </c>
       <c r="C26" s="28">
         <v>15</v>
       </c>
-      <c r="D26" s="26">
-        <v>2</v>
+      <c r="D26" s="26" t="s">
+        <v>7</v>
       </c>
       <c r="E26" s="27" t="s">
-        <v>354</v>
+        <v>8</v>
       </c>
       <c r="F26" s="26" t="s">
-        <v>350</v>
+        <v>261</v>
       </c>
       <c r="G26" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B26),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E26),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F26),0)&gt;0), MAX($G$1:G25)+1, ""))</f>
@@ -2379,19 +2382,19 @@
         <v>15</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>58</v>
+        <v>351</v>
       </c>
       <c r="C27" s="28">
         <v>15</v>
       </c>
-      <c r="D27" s="26" t="s">
-        <v>225</v>
+      <c r="D27" s="26">
+        <v>2</v>
       </c>
       <c r="E27" s="27" t="s">
-        <v>8</v>
+        <v>352</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>59</v>
+        <v>348</v>
       </c>
       <c r="G27" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B27),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E27),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F27),0)&gt;0), MAX($G$1:G26)+1, ""))</f>
@@ -2407,19 +2410,19 @@
         <v>15</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>270</v>
+        <v>57</v>
       </c>
       <c r="C28" s="28">
         <v>15</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="E28" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G28" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B28),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E28),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F28),0)&gt;0), MAX($G$1:G27)+1, ""))</f>
@@ -2435,19 +2438,19 @@
         <v>15</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>308</v>
+        <v>268</v>
       </c>
       <c r="C29" s="28">
         <v>15</v>
       </c>
-      <c r="D29" s="26">
-        <v>2.1</v>
+      <c r="D29" s="26" t="s">
+        <v>205</v>
       </c>
       <c r="E29" s="27" t="s">
-        <v>297</v>
+        <v>8</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>309</v>
+        <v>56</v>
       </c>
       <c r="G29" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B29),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E29),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F29),0)&gt;0), MAX($G$1:G28)+1, ""))</f>
@@ -2463,19 +2466,19 @@
         <v>15</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>55</v>
+        <v>306</v>
       </c>
       <c r="C30" s="28">
         <v>15</v>
       </c>
-      <c r="D30" s="26" t="s">
-        <v>206</v>
+      <c r="D30" s="26">
+        <v>2.1</v>
       </c>
       <c r="E30" s="27" t="s">
-        <v>8</v>
+        <v>295</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>56</v>
+        <v>307</v>
       </c>
       <c r="G30" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B30),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E30),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F30),0)&gt;0), MAX($G$1:G29)+1, ""))</f>
@@ -2491,19 +2494,19 @@
         <v>15</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>279</v>
+        <v>54</v>
       </c>
       <c r="C31" s="28">
         <v>15</v>
       </c>
       <c r="D31" s="26" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="E31" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F31" s="26" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="G31" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B31),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E31),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F31),0)&gt;0), MAX($G$1:G30)+1, ""))</f>
@@ -2519,19 +2522,19 @@
         <v>15</v>
       </c>
       <c r="B32" s="27" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="C32" s="28">
         <v>15</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>22</v>
+        <v>210</v>
       </c>
       <c r="E32" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F32" s="26" t="s">
-        <v>264</v>
+        <v>75</v>
       </c>
       <c r="G32" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B32),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E32),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F32),0)&gt;0), MAX($G$1:G31)+1, ""))</f>
@@ -2547,19 +2550,19 @@
         <v>15</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>294</v>
+        <v>260</v>
       </c>
       <c r="C33" s="28">
         <v>15</v>
       </c>
-      <c r="D33" s="26">
-        <v>2.2000000000000002</v>
+      <c r="D33" s="26" t="s">
+        <v>21</v>
       </c>
       <c r="E33" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F33" s="26" t="s">
-        <v>295</v>
+        <v>262</v>
       </c>
       <c r="G33" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B33),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E33),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F33),0)&gt;0), MAX($G$1:G32)+1, ""))</f>
@@ -2575,19 +2578,19 @@
         <v>15</v>
       </c>
       <c r="B34" s="27" t="s">
-        <v>356</v>
+        <v>292</v>
       </c>
       <c r="C34" s="28">
         <v>15</v>
       </c>
       <c r="D34" s="26">
-        <v>1.5</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E34" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F34" s="26" t="s">
-        <v>357</v>
+        <v>293</v>
       </c>
       <c r="G34" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B34),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E34),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F34),0)&gt;0), MAX($G$1:G33)+1, ""))</f>
@@ -2603,19 +2606,19 @@
         <v>15</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>51</v>
+        <v>354</v>
       </c>
       <c r="C35" s="28">
         <v>15</v>
       </c>
-      <c r="D35" s="26" t="s">
-        <v>215</v>
+      <c r="D35" s="26">
+        <v>1.5</v>
       </c>
       <c r="E35" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>52</v>
+        <v>355</v>
       </c>
       <c r="G35" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F35),0)&gt;0), MAX($G$1:G34)+1, ""))</f>
@@ -2631,19 +2634,19 @@
         <v>15</v>
       </c>
       <c r="B36" s="27" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C36" s="28">
         <v>15</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="E36" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F36" s="26" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G36" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B36),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E36),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F36),0)&gt;0), MAX($G$1:G35)+1, ""))</f>
@@ -2659,19 +2662,19 @@
         <v>15</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C37" s="28">
         <v>15</v>
       </c>
       <c r="D37" s="26" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="E37" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G37" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F37),0)&gt;0), MAX($G$1:G36)+1, ""))</f>
@@ -2687,19 +2690,19 @@
         <v>15</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C38" s="28">
         <v>15</v>
       </c>
       <c r="D38" s="26" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="E38" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F38" s="26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G38" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F38),0)&gt;0), MAX($G$1:G37)+1, ""))</f>
@@ -2715,19 +2718,19 @@
         <v>15</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C39" s="28">
         <v>15</v>
       </c>
       <c r="D39" s="26" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E39" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F39" s="26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G39" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B39),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E39),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F39),0)&gt;0), MAX($G$1:G38)+1, ""))</f>
@@ -2743,19 +2746,19 @@
         <v>15</v>
       </c>
       <c r="B40" s="27" t="s">
-        <v>310</v>
+        <v>40</v>
       </c>
       <c r="C40" s="28">
         <v>15</v>
       </c>
-      <c r="D40" s="26">
-        <v>2.2000000000000002</v>
+      <c r="D40" s="26" t="s">
+        <v>212</v>
       </c>
       <c r="E40" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F40" s="26" t="s">
-        <v>295</v>
+        <v>41</v>
       </c>
       <c r="G40" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B40),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E40),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F40),0)&gt;0), MAX($G$1:G39)+1, ""))</f>
@@ -2771,19 +2774,19 @@
         <v>15</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>246</v>
+        <v>308</v>
       </c>
       <c r="C41" s="28">
         <v>15</v>
       </c>
       <c r="D41" s="26">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E41" s="27" t="s">
-        <v>247</v>
+        <v>8</v>
       </c>
       <c r="F41" s="26" t="s">
-        <v>204</v>
+        <v>293</v>
       </c>
       <c r="G41" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B41),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E41),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F41),0)&gt;0), MAX($G$1:G40)+1, ""))</f>
@@ -2799,19 +2802,19 @@
         <v>15</v>
       </c>
       <c r="B42" s="27" t="s">
-        <v>39</v>
+        <v>244</v>
       </c>
       <c r="C42" s="28">
         <v>15</v>
       </c>
-      <c r="D42" s="26" t="s">
-        <v>213</v>
+      <c r="D42" s="26">
+        <v>2.1</v>
       </c>
       <c r="E42" s="27" t="s">
-        <v>8</v>
+        <v>245</v>
       </c>
       <c r="F42" s="26" t="s">
-        <v>40</v>
+        <v>202</v>
       </c>
       <c r="G42" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B42),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E42),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F42),0)&gt;0), MAX($G$1:G41)+1, ""))</f>
@@ -2827,19 +2830,19 @@
         <v>15</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>343</v>
+        <v>38</v>
       </c>
       <c r="C43" s="28">
         <v>15</v>
       </c>
-      <c r="D43" s="26">
-        <v>1.4</v>
+      <c r="D43" s="26" t="s">
+        <v>211</v>
       </c>
       <c r="E43" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F43" s="26" t="s">
-        <v>349</v>
+        <v>39</v>
       </c>
       <c r="G43" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F43),0)&gt;0), MAX($G$1:G42)+1, ""))</f>
@@ -2855,19 +2858,19 @@
         <v>15</v>
       </c>
       <c r="B44" s="27" t="s">
-        <v>35</v>
+        <v>341</v>
       </c>
       <c r="C44" s="28">
         <v>15</v>
       </c>
-      <c r="D44" s="26" t="s">
-        <v>212</v>
+      <c r="D44" s="26">
+        <v>1.4</v>
       </c>
       <c r="E44" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F44" s="26" t="s">
-        <v>36</v>
+        <v>347</v>
       </c>
       <c r="G44" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F44),0)&gt;0), MAX($G$1:G43)+1, ""))</f>
@@ -2883,19 +2886,19 @@
         <v>15</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>282</v>
+        <v>34</v>
       </c>
       <c r="C45" s="28">
         <v>15</v>
       </c>
       <c r="D45" s="26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E45" s="27" t="s">
-        <v>269</v>
+        <v>8</v>
       </c>
       <c r="F45" s="26" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G45" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F45),0)&gt;0), MAX($G$1:G44)+1, ""))</f>
@@ -2907,23 +2910,23 @@
       </c>
     </row>
     <row r="46" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A46" s="33">
-        <v>17</v>
-      </c>
-      <c r="B46" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="C46" s="35">
-        <v>17</v>
-      </c>
-      <c r="D46" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="E46" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F46" s="33" t="s">
-        <v>73</v>
+      <c r="A46" s="26">
+        <v>15</v>
+      </c>
+      <c r="B46" s="27" t="s">
+        <v>280</v>
+      </c>
+      <c r="C46" s="28">
+        <v>15</v>
+      </c>
+      <c r="D46" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="E46" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="F46" s="26" t="s">
+        <v>33</v>
       </c>
       <c r="G46" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F46),0)&gt;0), MAX($G$1:G45)+1, ""))</f>
@@ -2939,19 +2942,19 @@
         <v>17</v>
       </c>
       <c r="B47" s="34" t="s">
-        <v>283</v>
+        <v>70</v>
       </c>
       <c r="C47" s="35">
         <v>17</v>
       </c>
       <c r="D47" s="33" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="E47" s="34" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="F47" s="33" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G47" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F47),0)&gt;0), MAX($G$1:G46)+1, ""))</f>
@@ -2963,53 +2966,53 @@
       </c>
     </row>
     <row r="48" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A48" s="26">
+      <c r="A48" s="33">
         <v>17</v>
       </c>
-      <c r="B48" s="27" t="s">
-        <v>315</v>
-      </c>
-      <c r="C48" s="28">
+      <c r="B48" s="34" t="s">
+        <v>281</v>
+      </c>
+      <c r="C48" s="35">
         <v>17</v>
       </c>
-      <c r="D48" s="26">
-        <v>1.7</v>
-      </c>
-      <c r="E48" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="F48" s="26" t="s">
-        <v>321</v>
-      </c>
-      <c r="G48" s="29"/>
+      <c r="D48" s="33" t="s">
+        <v>222</v>
+      </c>
+      <c r="E48" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="F48" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="G48" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F48),0)&gt;0), MAX($G$1:G47)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H48" s="21" t="b">
         <f>A48=C48</f>
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="33">
+      <c r="A49" s="26">
         <v>17</v>
       </c>
-      <c r="B49" s="34" t="s">
-        <v>63</v>
-      </c>
-      <c r="C49" s="35">
+      <c r="B49" s="27" t="s">
+        <v>313</v>
+      </c>
+      <c r="C49" s="28">
         <v>17</v>
       </c>
-      <c r="D49" s="33" t="s">
-        <v>217</v>
-      </c>
-      <c r="E49" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F49" s="33" t="s">
-        <v>64</v>
-      </c>
-      <c r="G49" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F49),0)&gt;0), MAX($G$1:G48)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D49" s="26">
+        <v>1.7</v>
+      </c>
+      <c r="E49" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F49" s="26" t="s">
+        <v>319</v>
+      </c>
+      <c r="G49" s="29"/>
       <c r="H49" s="21" t="b">
         <f>A49=C49</f>
         <v>1</v>
@@ -3020,19 +3023,19 @@
         <v>17</v>
       </c>
       <c r="B50" s="34" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C50" s="35">
         <v>17</v>
       </c>
       <c r="D50" s="33" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E50" s="34" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="F50" s="33" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G50" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F50),0)&gt;0), MAX($G$1:G49)+1, ""))</f>
@@ -3044,25 +3047,28 @@
       </c>
     </row>
     <row r="51" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="26">
+      <c r="A51" s="33">
         <v>17</v>
       </c>
-      <c r="B51" s="27" t="s">
-        <v>317</v>
-      </c>
-      <c r="C51" s="28">
+      <c r="B51" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="C51" s="35">
         <v>17</v>
       </c>
-      <c r="D51" s="26">
-        <v>3</v>
-      </c>
-      <c r="E51" s="27" t="s">
+      <c r="D51" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="E51" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="F51" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="F51" s="26" t="s">
-        <v>323</v>
-      </c>
-      <c r="G51" s="29"/>
+      <c r="G51" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F51),0)&gt;0), MAX($G$1:G50)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H51" s="21" t="b">
         <f>A51=C51</f>
         <v>1</v>
@@ -3073,24 +3079,21 @@
         <v>17</v>
       </c>
       <c r="B52" s="27" t="s">
-        <v>342</v>
+        <v>315</v>
       </c>
       <c r="C52" s="28">
         <v>17</v>
       </c>
       <c r="D52" s="26">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="E52" s="27" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F52" s="26" t="s">
-        <v>351</v>
-      </c>
-      <c r="G52" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F52),0)&gt;0), MAX($G$1:G50)+1, ""))</f>
-        <v/>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="G52" s="29"/>
       <c r="H52" s="21" t="b">
         <f>A52=C52</f>
         <v>1</v>
@@ -3101,74 +3104,77 @@
         <v>17</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="C53" s="28">
         <v>17</v>
       </c>
       <c r="D53" s="26">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="E53" s="27" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="F53" s="26" t="s">
-        <v>324</v>
-      </c>
-      <c r="G53" s="29"/>
+        <v>349</v>
+      </c>
+      <c r="G53" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F53),0)&gt;0), MAX($G$1:G51)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H53" s="21" t="b">
         <f>A53=C53</f>
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A54" s="36">
+      <c r="A54" s="26">
         <v>17</v>
       </c>
-      <c r="B54" s="37" t="s">
-        <v>291</v>
-      </c>
-      <c r="C54" s="38">
+      <c r="B54" s="27" t="s">
+        <v>316</v>
+      </c>
+      <c r="C54" s="28">
         <v>17</v>
       </c>
-      <c r="D54" s="36" t="s">
-        <v>221</v>
-      </c>
-      <c r="E54" s="37" t="s">
-        <v>61</v>
-      </c>
-      <c r="F54" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="G54" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F54),0)&gt;0), MAX($G$1:G53)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D54" s="26">
+        <v>1.9</v>
+      </c>
+      <c r="E54" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F54" s="26" t="s">
+        <v>322</v>
+      </c>
+      <c r="G54" s="29"/>
       <c r="H54" s="21" t="b">
         <f>A54=C54</f>
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="26">
+      <c r="A55" s="36">
         <v>17</v>
       </c>
-      <c r="B55" s="27" t="s">
-        <v>316</v>
-      </c>
-      <c r="C55" s="28">
+      <c r="B55" s="37" t="s">
+        <v>289</v>
+      </c>
+      <c r="C55" s="38">
         <v>17</v>
       </c>
-      <c r="D55" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E55" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="F55" s="26" t="s">
-        <v>322</v>
-      </c>
-      <c r="G55" s="29"/>
+      <c r="D55" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E55" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="F55" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="G55" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F55),0)&gt;0), MAX($G$1:G54)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H55" s="21" t="b">
         <f>A55=C55</f>
         <v>1</v>
@@ -3179,19 +3185,19 @@
         <v>17</v>
       </c>
       <c r="B56" s="27" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="C56" s="28">
         <v>17</v>
       </c>
       <c r="D56" s="26">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E56" s="27" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F56" s="26" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="G56" s="29"/>
       <c r="H56" s="21" t="b">
@@ -3200,28 +3206,25 @@
       </c>
     </row>
     <row r="57" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A57" s="36">
+      <c r="A57" s="26">
         <v>17</v>
       </c>
-      <c r="B57" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="C57" s="38">
+      <c r="B57" s="27" t="s">
+        <v>317</v>
+      </c>
+      <c r="C57" s="28">
         <v>17</v>
       </c>
-      <c r="D57" s="36" t="s">
-        <v>222</v>
-      </c>
-      <c r="E57" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" s="36" t="s">
-        <v>109</v>
-      </c>
-      <c r="G57" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F57),0)&gt;0), MAX($G$1:G56)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D57" s="26">
+        <v>2</v>
+      </c>
+      <c r="E57" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F57" s="26" t="s">
+        <v>323</v>
+      </c>
+      <c r="G57" s="29"/>
       <c r="H57" s="21" t="b">
         <f>A57=C57</f>
         <v>1</v>
@@ -3232,16 +3235,16 @@
         <v>17</v>
       </c>
       <c r="B58" s="37" t="s">
-        <v>305</v>
+        <v>106</v>
       </c>
       <c r="C58" s="38">
         <v>17</v>
       </c>
       <c r="D58" s="36" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="E58" s="37" t="s">
-        <v>306</v>
+        <v>8</v>
       </c>
       <c r="F58" s="36" t="s">
         <v>107</v>
@@ -3256,26 +3259,26 @@
       </c>
     </row>
     <row r="59" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A59" s="33">
+      <c r="A59" s="36">
         <v>17</v>
       </c>
-      <c r="B59" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="C59" s="35">
+      <c r="B59" s="37" t="s">
+        <v>303</v>
+      </c>
+      <c r="C59" s="38">
         <v>17</v>
       </c>
-      <c r="D59" s="33" t="s">
-        <v>209</v>
-      </c>
-      <c r="E59" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F59" s="33" t="s">
-        <v>54</v>
+      <c r="D59" s="36" t="s">
+        <v>229</v>
+      </c>
+      <c r="E59" s="37" t="s">
+        <v>304</v>
+      </c>
+      <c r="F59" s="36" t="s">
+        <v>105</v>
       </c>
       <c r="G59" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F59),0)&gt;0), MAX($G$1:G54)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F59),0)&gt;0), MAX($G$1:G58)+1, ""))</f>
         <v/>
       </c>
       <c r="H59" s="21" t="b">
@@ -3284,26 +3287,26 @@
       </c>
     </row>
     <row r="60" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A60" s="26">
+      <c r="A60" s="33">
         <v>17</v>
       </c>
-      <c r="B60" s="27" t="s">
-        <v>358</v>
-      </c>
-      <c r="C60" s="28">
+      <c r="B60" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="C60" s="35">
         <v>17</v>
       </c>
-      <c r="D60" s="26">
-        <v>1.8</v>
-      </c>
-      <c r="E60" s="27" t="s">
+      <c r="D60" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="E60" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F60" s="26" t="s">
-        <v>359</v>
+      <c r="F60" s="33" t="s">
+        <v>53</v>
       </c>
       <c r="G60" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F60),0)&gt;0), MAX($G$1:G59)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F60),0)&gt;0), MAX($G$1:G55)+1, ""))</f>
         <v/>
       </c>
       <c r="H60" s="21" t="b">
@@ -3312,23 +3315,23 @@
       </c>
     </row>
     <row r="61" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A61" s="33">
+      <c r="A61" s="26">
         <v>17</v>
       </c>
-      <c r="B61" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="C61" s="35">
+      <c r="B61" s="27" t="s">
+        <v>356</v>
+      </c>
+      <c r="C61" s="28">
         <v>17</v>
       </c>
-      <c r="D61" s="33" t="s">
-        <v>213</v>
-      </c>
-      <c r="E61" s="34" t="s">
+      <c r="D61" s="26">
+        <v>1.8</v>
+      </c>
+      <c r="E61" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F61" s="33" t="s">
-        <v>50</v>
+      <c r="F61" s="26" t="s">
+        <v>357</v>
       </c>
       <c r="G61" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F61),0)&gt;0), MAX($G$1:G60)+1, ""))</f>
@@ -3340,23 +3343,23 @@
       </c>
     </row>
     <row r="62" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A62" s="36">
+      <c r="A62" s="33">
         <v>17</v>
       </c>
-      <c r="B62" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="C62" s="38">
+      <c r="B62" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="C62" s="35">
         <v>17</v>
       </c>
-      <c r="D62" s="36" t="s">
-        <v>221</v>
-      </c>
-      <c r="E62" s="37" t="s">
+      <c r="D62" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="E62" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F62" s="36" t="s">
-        <v>100</v>
+      <c r="F62" s="33" t="s">
+        <v>49</v>
       </c>
       <c r="G62" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F62),0)&gt;0), MAX($G$1:G61)+1, ""))</f>
@@ -3372,7 +3375,7 @@
         <v>17</v>
       </c>
       <c r="B63" s="37" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C63" s="38">
         <v>17</v>
@@ -3384,7 +3387,7 @@
         <v>8</v>
       </c>
       <c r="F63" s="36" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G63" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F63),0)&gt;0), MAX($G$1:G62)+1, ""))</f>
@@ -3396,28 +3399,30 @@
       </c>
     </row>
     <row r="64" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A64" s="33">
+      <c r="A64" s="36">
         <v>17</v>
       </c>
-      <c r="B64" s="34" t="s">
-        <v>329</v>
-      </c>
-      <c r="C64" s="35">
+      <c r="B64" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="C64" s="38">
         <v>17</v>
       </c>
-      <c r="D64" s="33">
-        <v>1.9</v>
-      </c>
-      <c r="E64" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="F64" s="33" t="s">
-        <v>331</v>
-      </c>
-      <c r="G64" s="29" t="s">
-        <v>328</v>
+      <c r="D64" s="36" t="s">
+        <v>217</v>
+      </c>
+      <c r="E64" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F64" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="G64" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F64),0)&gt;0), MAX($G$1:G63)+1, ""))</f>
+        <v/>
       </c>
       <c r="H64" s="21" t="b">
+        <f>A64=C64</f>
         <v>1</v>
       </c>
     </row>
@@ -3435,13 +3440,13 @@
         <v>1.9</v>
       </c>
       <c r="E65" s="34" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F65" s="33" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G65" s="29" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H65" s="21" t="b">
         <v>1</v>
@@ -3452,7 +3457,7 @@
         <v>17</v>
       </c>
       <c r="B66" s="34" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="C66" s="35">
         <v>17</v>
@@ -3461,13 +3466,13 @@
         <v>1.9</v>
       </c>
       <c r="E66" s="34" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F66" s="33" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G66" s="29" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H66" s="21" t="b">
         <v>1</v>
@@ -3478,47 +3483,45 @@
         <v>17</v>
       </c>
       <c r="B67" s="34" t="s">
-        <v>37</v>
+        <v>328</v>
       </c>
       <c r="C67" s="35">
         <v>17</v>
       </c>
-      <c r="D67" s="33" t="s">
-        <v>216</v>
+      <c r="D67" s="33">
+        <v>1.9</v>
       </c>
       <c r="E67" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="F67" s="33" t="s">
+        <v>329</v>
+      </c>
+      <c r="G67" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="H67" s="21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A68" s="33">
+        <v>17</v>
+      </c>
+      <c r="B68" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="C68" s="35">
+        <v>17</v>
+      </c>
+      <c r="D68" s="33" t="s">
+        <v>214</v>
+      </c>
+      <c r="E68" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F67" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="G67" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F67),0)&gt;0), MAX($G$1:G66)+1, ""))</f>
-        <v/>
-      </c>
-      <c r="H67" s="21" t="b">
-        <f>A67=C67</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A68" s="36">
-        <v>17</v>
-      </c>
-      <c r="B68" s="37" t="s">
-        <v>85</v>
-      </c>
-      <c r="C68" s="38">
-        <v>17</v>
-      </c>
-      <c r="D68" s="36" t="s">
-        <v>221</v>
-      </c>
-      <c r="E68" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F68" s="36" t="s">
-        <v>86</v>
+      <c r="F68" s="33" t="s">
+        <v>37</v>
       </c>
       <c r="G68" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F68),0)&gt;0), MAX($G$1:G67)+1, ""))</f>
@@ -3530,23 +3533,23 @@
       </c>
     </row>
     <row r="69" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A69" s="33">
+      <c r="A69" s="36">
         <v>17</v>
       </c>
-      <c r="B69" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="C69" s="35">
+      <c r="B69" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="C69" s="38">
         <v>17</v>
       </c>
-      <c r="D69" s="33" t="s">
-        <v>210</v>
-      </c>
-      <c r="E69" s="34" t="s">
+      <c r="D69" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E69" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F69" s="33" t="s">
-        <v>33</v>
+      <c r="F69" s="36" t="s">
+        <v>84</v>
       </c>
       <c r="G69" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F69),0)&gt;0), MAX($G$1:G68)+1, ""))</f>
@@ -3562,52 +3565,52 @@
         <v>17</v>
       </c>
       <c r="B70" s="34" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C70" s="35">
         <v>17</v>
       </c>
       <c r="D70" s="33" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E70" s="34" t="s">
         <v>8</v>
       </c>
       <c r="F70" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="G70" s="29" t="s">
-        <v>328</v>
+        <v>32</v>
+      </c>
+      <c r="G70" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F70),0)&gt;0), MAX($G$1:G69)+1, ""))</f>
+        <v/>
       </c>
       <c r="H70" s="21" t="b">
+        <f>A70=C70</f>
         <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A71" s="30">
-        <v>20</v>
-      </c>
-      <c r="B71" s="31" t="s">
-        <v>148</v>
-      </c>
-      <c r="C71" s="32">
-        <v>20</v>
-      </c>
-      <c r="D71" s="30" t="s">
-        <v>208</v>
-      </c>
-      <c r="E71" s="31" t="s">
+      <c r="A71" s="33">
+        <v>17</v>
+      </c>
+      <c r="B71" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="C71" s="35">
+        <v>17</v>
+      </c>
+      <c r="D71" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="E71" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F71" s="30" t="s">
-        <v>149</v>
-      </c>
-      <c r="G71" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F71),0)&gt;0), MAX($G$1:G67)+1, ""))</f>
-        <v/>
+      <c r="F71" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="G71" s="29" t="s">
+        <v>326</v>
       </c>
       <c r="H71" s="21" t="b">
-        <f>A71=C71</f>
         <v>1</v>
       </c>
     </row>
@@ -3622,7 +3625,7 @@
         <v>20</v>
       </c>
       <c r="D72" s="30" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E72" s="31" t="s">
         <v>8</v>
@@ -3631,7 +3634,7 @@
         <v>147</v>
       </c>
       <c r="G72" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F72),0)&gt;0), MAX($G$1:G71)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F72),0)&gt;0), MAX($G$1:G68)+1, ""))</f>
         <v/>
       </c>
       <c r="H72" s="21" t="b">
@@ -3650,7 +3653,7 @@
         <v>20</v>
       </c>
       <c r="D73" s="30" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E73" s="31" t="s">
         <v>8</v>
@@ -3678,10 +3681,10 @@
         <v>20</v>
       </c>
       <c r="D74" s="30" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="E74" s="31" t="s">
-        <v>307</v>
+        <v>8</v>
       </c>
       <c r="F74" s="30" t="s">
         <v>143</v>
@@ -3696,25 +3699,28 @@
       </c>
     </row>
     <row r="75" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A75" s="36">
+      <c r="A75" s="30">
         <v>20</v>
       </c>
-      <c r="B75" s="37" t="s">
-        <v>335</v>
-      </c>
-      <c r="C75" s="38">
+      <c r="B75" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="C75" s="32">
         <v>20</v>
       </c>
-      <c r="D75" s="36">
-        <v>3.4</v>
-      </c>
-      <c r="E75" s="37" t="s">
-        <v>338</v>
-      </c>
-      <c r="F75" s="36" t="s">
-        <v>336</v>
-      </c>
-      <c r="G75" s="29"/>
+      <c r="D75" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="E75" s="31" t="s">
+        <v>305</v>
+      </c>
+      <c r="F75" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="G75" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F75),0)&gt;0), MAX($G$1:G74)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H75" s="21" t="b">
         <f>A75=C75</f>
         <v>1</v>
@@ -3731,10 +3737,10 @@
         <v>20</v>
       </c>
       <c r="D76" s="36">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="E76" s="37" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F76" s="36" t="s">
         <v>334</v>
@@ -3746,28 +3752,25 @@
       </c>
     </row>
     <row r="77" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A77" s="30">
+      <c r="A77" s="36">
         <v>20</v>
       </c>
-      <c r="B77" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="C77" s="32">
+      <c r="B77" s="37" t="s">
+        <v>331</v>
+      </c>
+      <c r="C77" s="38">
         <v>20</v>
       </c>
-      <c r="D77" s="30" t="s">
-        <v>225</v>
-      </c>
-      <c r="E77" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F77" s="30" t="s">
-        <v>141</v>
-      </c>
-      <c r="G77" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F77),0)&gt;0), MAX($G$1:G76)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D77" s="36">
+        <v>3.3</v>
+      </c>
+      <c r="E77" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="F77" s="36" t="s">
+        <v>332</v>
+      </c>
+      <c r="G77" s="29"/>
       <c r="H77" s="21" t="b">
         <f>A77=C77</f>
         <v>1</v>
@@ -3778,19 +3781,19 @@
         <v>20</v>
       </c>
       <c r="B78" s="31" t="s">
-        <v>257</v>
+        <v>138</v>
       </c>
       <c r="C78" s="32">
         <v>20</v>
       </c>
       <c r="D78" s="30" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E78" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F78" s="30" t="s">
-        <v>258</v>
+        <v>139</v>
       </c>
       <c r="G78" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F78),0)&gt;0), MAX($G$1:G77)+1, ""))</f>
@@ -3806,19 +3809,19 @@
         <v>20</v>
       </c>
       <c r="B79" s="31" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C79" s="32">
         <v>20</v>
       </c>
-      <c r="D79" s="30">
-        <v>4.2</v>
+      <c r="D79" s="30" t="s">
+        <v>225</v>
       </c>
       <c r="E79" s="31" t="s">
-        <v>307</v>
-      </c>
-      <c r="F79" s="30">
-        <v>21765430</v>
+        <v>8</v>
+      </c>
+      <c r="F79" s="30" t="s">
+        <v>256</v>
       </c>
       <c r="G79" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F79),0)&gt;0), MAX($G$1:G78)+1, ""))</f>
@@ -3834,19 +3837,19 @@
         <v>20</v>
       </c>
       <c r="B80" s="31" t="s">
-        <v>138</v>
+        <v>254</v>
       </c>
       <c r="C80" s="32">
         <v>20</v>
       </c>
-      <c r="D80" s="30" t="s">
-        <v>212</v>
+      <c r="D80" s="30">
+        <v>4.2</v>
       </c>
       <c r="E80" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F80" s="30" t="s">
-        <v>139</v>
+        <v>305</v>
+      </c>
+      <c r="F80" s="30">
+        <v>21765430</v>
       </c>
       <c r="G80" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F80),0)&gt;0), MAX($G$1:G79)+1, ""))</f>
@@ -3862,13 +3865,13 @@
         <v>20</v>
       </c>
       <c r="B81" s="31" t="s">
-        <v>267</v>
+        <v>136</v>
       </c>
       <c r="C81" s="32">
         <v>20</v>
       </c>
       <c r="D81" s="30" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="E81" s="31" t="s">
         <v>8</v>
@@ -3890,19 +3893,19 @@
         <v>20</v>
       </c>
       <c r="B82" s="31" t="s">
-        <v>135</v>
+        <v>265</v>
       </c>
       <c r="C82" s="32">
         <v>20</v>
       </c>
       <c r="D82" s="30" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E82" s="31" t="s">
-        <v>307</v>
+        <v>8</v>
       </c>
       <c r="F82" s="30" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G82" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F82),0)&gt;0), MAX($G$1:G81)+1, ""))</f>
@@ -3918,16 +3921,16 @@
         <v>20</v>
       </c>
       <c r="B83" s="31" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C83" s="32">
         <v>20</v>
       </c>
       <c r="D83" s="30" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E83" s="31" t="s">
-        <v>133</v>
+        <v>305</v>
       </c>
       <c r="F83" s="30" t="s">
         <v>134</v>
@@ -3942,23 +3945,23 @@
       </c>
     </row>
     <row r="84" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A84" s="26">
+      <c r="A84" s="30">
         <v>20</v>
       </c>
-      <c r="B84" s="27" t="s">
-        <v>314</v>
-      </c>
-      <c r="C84" s="28">
+      <c r="B84" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="C84" s="32">
         <v>20</v>
       </c>
-      <c r="D84" s="26">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="E84" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="F84" s="26" t="s">
-        <v>320</v>
+      <c r="D84" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="E84" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="F84" s="30" t="s">
+        <v>132</v>
       </c>
       <c r="G84" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F84),0)&gt;0), MAX($G$1:G83)+1, ""))</f>
@@ -3970,23 +3973,23 @@
       </c>
     </row>
     <row r="85" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A85" s="30">
+      <c r="A85" s="26">
         <v>20</v>
       </c>
-      <c r="B85" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="C85" s="32">
+      <c r="B85" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="C85" s="28">
         <v>20</v>
       </c>
-      <c r="D85" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="E85" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F85" s="30" t="s">
-        <v>131</v>
+      <c r="D85" s="26">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E85" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F85" s="26" t="s">
+        <v>318</v>
       </c>
       <c r="G85" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F85),0)&gt;0), MAX($G$1:G84)+1, ""))</f>
@@ -4008,10 +4011,10 @@
         <v>20</v>
       </c>
       <c r="D86" s="30" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="E86" s="31" t="s">
-        <v>307</v>
+        <v>8</v>
       </c>
       <c r="F86" s="30" t="s">
         <v>129</v>
@@ -4026,23 +4029,23 @@
       </c>
     </row>
     <row r="87" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A87" s="26">
+      <c r="A87" s="30">
         <v>20</v>
       </c>
-      <c r="B87" s="27" t="s">
-        <v>352</v>
-      </c>
-      <c r="C87" s="28">
+      <c r="B87" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="C87" s="32">
         <v>20</v>
       </c>
-      <c r="D87" s="26">
-        <v>2.7</v>
-      </c>
-      <c r="E87" s="27" t="s">
-        <v>247</v>
-      </c>
-      <c r="F87" s="26" t="s">
-        <v>355</v>
+      <c r="D87" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="E87" s="31" t="s">
+        <v>305</v>
+      </c>
+      <c r="F87" s="30" t="s">
+        <v>127</v>
       </c>
       <c r="G87" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F87),0)&gt;0), MAX($G$1:G86)+1, ""))</f>
@@ -4054,23 +4057,23 @@
       </c>
     </row>
     <row r="88" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A88" s="30">
+      <c r="A88" s="26">
         <v>20</v>
       </c>
-      <c r="B88" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="C88" s="32">
+      <c r="B88" s="27" t="s">
+        <v>350</v>
+      </c>
+      <c r="C88" s="28">
         <v>20</v>
       </c>
-      <c r="D88" s="30" t="s">
-        <v>232</v>
-      </c>
-      <c r="E88" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F88" s="30" t="s">
-        <v>127</v>
+      <c r="D88" s="26">
+        <v>2.7</v>
+      </c>
+      <c r="E88" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="F88" s="26" t="s">
+        <v>353</v>
       </c>
       <c r="G88" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F88),0)&gt;0), MAX($G$1:G87)+1, ""))</f>
@@ -4092,7 +4095,7 @@
         <v>20</v>
       </c>
       <c r="D89" s="30" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="E89" s="31" t="s">
         <v>8</v>
@@ -4120,10 +4123,10 @@
         <v>20</v>
       </c>
       <c r="D90" s="30" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="E90" s="31" t="s">
-        <v>307</v>
+        <v>8</v>
       </c>
       <c r="F90" s="30" t="s">
         <v>123</v>
@@ -4142,19 +4145,19 @@
         <v>20</v>
       </c>
       <c r="B91" s="31" t="s">
-        <v>259</v>
+        <v>120</v>
       </c>
       <c r="C91" s="32">
         <v>20</v>
       </c>
       <c r="D91" s="30" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E91" s="31" t="s">
-        <v>8</v>
+        <v>305</v>
       </c>
       <c r="F91" s="30" t="s">
-        <v>260</v>
+        <v>121</v>
       </c>
       <c r="G91" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F91),0)&gt;0), MAX($G$1:G90)+1, ""))</f>
@@ -4170,19 +4173,19 @@
         <v>20</v>
       </c>
       <c r="B92" s="31" t="s">
-        <v>120</v>
+        <v>257</v>
       </c>
       <c r="C92" s="32">
         <v>20</v>
       </c>
       <c r="D92" s="30" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E92" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F92" s="30" t="s">
-        <v>121</v>
+        <v>258</v>
       </c>
       <c r="G92" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F92),0)&gt;0), MAX($G$1:G91)+1, ""))</f>
@@ -4204,7 +4207,7 @@
         <v>20</v>
       </c>
       <c r="D93" s="30" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="E93" s="31" t="s">
         <v>8</v>
@@ -4232,7 +4235,7 @@
         <v>20</v>
       </c>
       <c r="D94" s="30" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="E94" s="31" t="s">
         <v>8</v>
@@ -4250,23 +4253,23 @@
       </c>
     </row>
     <row r="95" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A95" s="26">
+      <c r="A95" s="30">
         <v>20</v>
       </c>
-      <c r="B95" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="C95" s="28">
+      <c r="B95" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="C95" s="32">
         <v>20</v>
       </c>
-      <c r="D95" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E95" s="27" t="s">
-        <v>301</v>
-      </c>
-      <c r="F95" s="26" t="s">
-        <v>300</v>
+      <c r="D95" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="E95" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F95" s="30" t="s">
+        <v>115</v>
       </c>
       <c r="G95" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F95),0)&gt;0), MAX($G$1:G94)+1, ""))</f>
@@ -4278,23 +4281,23 @@
       </c>
     </row>
     <row r="96" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A96" s="30">
+      <c r="A96" s="26">
         <v>20</v>
       </c>
-      <c r="B96" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="C96" s="32">
+      <c r="B96" s="27" t="s">
+        <v>297</v>
+      </c>
+      <c r="C96" s="28">
         <v>20</v>
       </c>
-      <c r="D96" s="30" t="s">
-        <v>221</v>
-      </c>
-      <c r="E96" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F96" s="30" t="s">
-        <v>115</v>
+      <c r="D96" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E96" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="F96" s="26" t="s">
+        <v>298</v>
       </c>
       <c r="G96" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F96),0)&gt;0), MAX($G$1:G95)+1, ""))</f>
@@ -4316,10 +4319,10 @@
         <v>20</v>
       </c>
       <c r="D97" s="30" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E97" s="31" t="s">
-        <v>301</v>
+        <v>8</v>
       </c>
       <c r="F97" s="30" t="s">
         <v>113</v>
@@ -4344,10 +4347,10 @@
         <v>20</v>
       </c>
       <c r="D98" s="30" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E98" s="31" t="s">
-        <v>8</v>
+        <v>299</v>
       </c>
       <c r="F98" s="30" t="s">
         <v>111</v>
@@ -4362,76 +4365,76 @@
       </c>
     </row>
     <row r="99" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A99" s="36">
+      <c r="A99" s="30">
         <v>20</v>
       </c>
-      <c r="B99" s="37" t="s">
-        <v>332</v>
-      </c>
-      <c r="C99" s="38">
+      <c r="B99" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="C99" s="32">
         <v>20</v>
       </c>
-      <c r="D99" s="36">
-        <v>3</v>
-      </c>
-      <c r="E99" s="37" t="s">
-        <v>306</v>
-      </c>
-      <c r="F99" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="G99" s="29"/>
+      <c r="D99" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="E99" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F99" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="G99" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F99),0)&gt;0), MAX($G$1:G98)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H99" s="21" t="b">
         <f>A99=C99</f>
         <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A100" s="26">
+      <c r="A100" s="36">
         <v>20</v>
       </c>
-      <c r="B100" s="27" t="s">
+      <c r="B100" s="37" t="s">
+        <v>330</v>
+      </c>
+      <c r="C100" s="38">
+        <v>20</v>
+      </c>
+      <c r="D100" s="36">
+        <v>3</v>
+      </c>
+      <c r="E100" s="37" t="s">
         <v>304</v>
       </c>
-      <c r="C100" s="28">
-        <v>20</v>
-      </c>
-      <c r="D100" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E100" s="27" t="s">
-        <v>301</v>
-      </c>
-      <c r="F100" s="26" t="s">
-        <v>303</v>
-      </c>
-      <c r="G100" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F100),0)&gt;0), MAX($G$1:G99)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="F100" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="G100" s="29"/>
       <c r="H100" s="21" t="b">
         <f>A100=C100</f>
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A101" s="30">
+      <c r="A101" s="26">
         <v>20</v>
       </c>
-      <c r="B101" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="C101" s="32">
+      <c r="B101" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C101" s="28">
         <v>20</v>
       </c>
-      <c r="D101" s="30" t="s">
-        <v>216</v>
-      </c>
-      <c r="E101" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="F101" s="30" t="s">
-        <v>106</v>
+      <c r="D101" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E101" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="F101" s="26" t="s">
+        <v>301</v>
       </c>
       <c r="G101" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F101),0)&gt;0), MAX($G$1:G100)+1, ""))</f>
@@ -4443,23 +4446,23 @@
       </c>
     </row>
     <row r="102" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A102" s="26">
+      <c r="A102" s="30">
         <v>20</v>
       </c>
-      <c r="B102" s="27" t="s">
-        <v>341</v>
-      </c>
-      <c r="C102" s="28">
+      <c r="B102" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="C102" s="32">
         <v>20</v>
       </c>
-      <c r="D102" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E102" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="F102" s="26" t="s">
-        <v>346</v>
+      <c r="D102" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="E102" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="F102" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G102" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F102),0)&gt;0), MAX($G$1:G101)+1, ""))</f>
@@ -4471,53 +4474,53 @@
       </c>
     </row>
     <row r="103" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A103" s="36">
+      <c r="A103" s="26">
         <v>20</v>
       </c>
-      <c r="B103" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="C103" s="38">
+      <c r="B103" s="27" t="s">
+        <v>339</v>
+      </c>
+      <c r="C103" s="28">
         <v>20</v>
       </c>
-      <c r="D103" s="36">
-        <v>3.2</v>
-      </c>
-      <c r="E103" s="37" t="s">
-        <v>338</v>
-      </c>
-      <c r="F103" s="36" t="s">
-        <v>334</v>
-      </c>
-      <c r="G103" s="29"/>
+      <c r="D103" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E103" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F103" s="26" t="s">
+        <v>344</v>
+      </c>
+      <c r="G103" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F103),0)&gt;0), MAX($G$1:G102)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H103" s="21" t="b">
         <f>A103=C103</f>
         <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A104" s="30">
+      <c r="A104" s="36">
         <v>20</v>
       </c>
-      <c r="B104" s="31" t="s">
-        <v>103</v>
-      </c>
-      <c r="C104" s="32">
+      <c r="B104" s="37" t="s">
+        <v>335</v>
+      </c>
+      <c r="C104" s="38">
         <v>20</v>
       </c>
-      <c r="D104" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="E104" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F104" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="G104" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F104),0)&gt;0), MAX($G$1:G103)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D104" s="36">
+        <v>3.2</v>
+      </c>
+      <c r="E104" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="F104" s="36" t="s">
+        <v>332</v>
+      </c>
+      <c r="G104" s="29"/>
       <c r="H104" s="21" t="b">
         <f>A104=C104</f>
         <v>1</v>
@@ -4528,19 +4531,19 @@
         <v>20</v>
       </c>
       <c r="B105" s="31" t="s">
-        <v>265</v>
+        <v>101</v>
       </c>
       <c r="C105" s="32">
         <v>20</v>
       </c>
-      <c r="D105" s="30">
-        <v>6.2</v>
+      <c r="D105" s="30" t="s">
+        <v>207</v>
       </c>
       <c r="E105" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F105" s="30" t="s">
-        <v>266</v>
+        <v>102</v>
       </c>
       <c r="G105" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F105),0)&gt;0), MAX($G$1:G104)+1, ""))</f>
@@ -4556,19 +4559,19 @@
         <v>20</v>
       </c>
       <c r="B106" s="31" t="s">
-        <v>101</v>
+        <v>263</v>
       </c>
       <c r="C106" s="32">
         <v>20</v>
       </c>
-      <c r="D106" s="30" t="s">
-        <v>217</v>
+      <c r="D106" s="30">
+        <v>6.2</v>
       </c>
       <c r="E106" s="31" t="s">
-        <v>301</v>
+        <v>8</v>
       </c>
       <c r="F106" s="30" t="s">
-        <v>102</v>
+        <v>264</v>
       </c>
       <c r="G106" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F106),0)&gt;0), MAX($G$1:G105)+1, ""))</f>
@@ -4580,23 +4583,23 @@
       </c>
     </row>
     <row r="107" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A107" s="26">
+      <c r="A107" s="30">
         <v>20</v>
       </c>
-      <c r="B107" s="27" t="s">
-        <v>302</v>
-      </c>
-      <c r="C107" s="28">
+      <c r="B107" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="C107" s="32">
         <v>20</v>
       </c>
-      <c r="D107" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E107" s="27" t="s">
-        <v>301</v>
-      </c>
-      <c r="F107" s="26" t="s">
-        <v>303</v>
+      <c r="D107" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="E107" s="31" t="s">
+        <v>299</v>
+      </c>
+      <c r="F107" s="30" t="s">
+        <v>100</v>
       </c>
       <c r="G107" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F107),0)&gt;0), MAX($G$1:G106)+1, ""))</f>
@@ -4608,23 +4611,23 @@
       </c>
     </row>
     <row r="108" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A108" s="30">
+      <c r="A108" s="26">
         <v>20</v>
       </c>
-      <c r="B108" s="31" t="s">
-        <v>97</v>
-      </c>
-      <c r="C108" s="32">
+      <c r="B108" s="27" t="s">
+        <v>300</v>
+      </c>
+      <c r="C108" s="28">
         <v>20</v>
       </c>
-      <c r="D108" s="30" t="s">
-        <v>218</v>
-      </c>
-      <c r="E108" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F108" s="30" t="s">
-        <v>98</v>
+      <c r="D108" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E108" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="F108" s="26" t="s">
+        <v>301</v>
       </c>
       <c r="G108" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F108),0)&gt;0), MAX($G$1:G107)+1, ""))</f>
@@ -4636,23 +4639,23 @@
       </c>
     </row>
     <row r="109" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A109" s="26">
+      <c r="A109" s="30">
         <v>20</v>
       </c>
-      <c r="B109" s="27" t="s">
-        <v>360</v>
-      </c>
-      <c r="C109" s="28">
+      <c r="B109" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="C109" s="32">
         <v>20</v>
       </c>
-      <c r="D109" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E109" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="F109" s="26" t="s">
-        <v>361</v>
+      <c r="D109" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="E109" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F109" s="30" t="s">
+        <v>96</v>
       </c>
       <c r="G109" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F109),0)&gt;0), MAX($G$1:G108)+1, ""))</f>
@@ -4664,23 +4667,23 @@
       </c>
     </row>
     <row r="110" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A110" s="30">
+      <c r="A110" s="26">
         <v>20</v>
       </c>
-      <c r="B110" s="31" t="s">
-        <v>93</v>
-      </c>
-      <c r="C110" s="32">
+      <c r="B110" s="27" t="s">
+        <v>358</v>
+      </c>
+      <c r="C110" s="28">
         <v>20</v>
       </c>
-      <c r="D110" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="E110" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F110" s="30" t="s">
-        <v>94</v>
+      <c r="D110" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E110" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F110" s="26" t="s">
+        <v>359</v>
       </c>
       <c r="G110" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F110),0)&gt;0), MAX($G$1:G109)+1, ""))</f>
@@ -4702,7 +4705,7 @@
         <v>20</v>
       </c>
       <c r="D111" s="30" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="E111" s="31" t="s">
         <v>8</v>
@@ -4724,19 +4727,19 @@
         <v>20</v>
       </c>
       <c r="B112" s="31" t="s">
-        <v>292</v>
+        <v>89</v>
       </c>
       <c r="C112" s="32">
         <v>20</v>
       </c>
-      <c r="D112" s="30">
-        <v>1.8</v>
+      <c r="D112" s="30" t="s">
+        <v>223</v>
       </c>
       <c r="E112" s="31" t="s">
-        <v>293</v>
+        <v>8</v>
       </c>
       <c r="F112" s="30" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G112" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F112),0)&gt;0), MAX($G$1:G111)+1, ""))</f>
@@ -4752,16 +4755,16 @@
         <v>20</v>
       </c>
       <c r="B113" s="31" t="s">
-        <v>89</v>
+        <v>290</v>
       </c>
       <c r="C113" s="32">
         <v>20</v>
       </c>
-      <c r="D113" s="30" t="s">
-        <v>224</v>
+      <c r="D113" s="30">
+        <v>1.8</v>
       </c>
       <c r="E113" s="31" t="s">
-        <v>8</v>
+        <v>291</v>
       </c>
       <c r="F113" s="30" t="s">
         <v>90</v>
@@ -4808,7 +4811,7 @@
         <v>20</v>
       </c>
       <c r="B115" s="31" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C115" s="32">
         <v>20</v>
@@ -4817,10 +4820,10 @@
         <v>220</v>
       </c>
       <c r="E115" s="31" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="F115" s="30" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G115" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F115),0)&gt;0), MAX($G$1:G114)+1, ""))</f>
@@ -4842,13 +4845,13 @@
         <v>20</v>
       </c>
       <c r="D116" s="30" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E116" s="31" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="F116" s="30" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G116" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F116),0)&gt;0), MAX($G$1:G115)+1, ""))</f>
@@ -4870,7 +4873,7 @@
         <v>20</v>
       </c>
       <c r="D117" s="30" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E117" s="31" t="s">
         <v>8</v>
@@ -4888,23 +4891,23 @@
       </c>
     </row>
     <row r="118" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A118" s="26">
-        <v>25</v>
-      </c>
-      <c r="B118" s="27" t="s">
-        <v>180</v>
-      </c>
-      <c r="C118" s="28">
-        <v>25</v>
-      </c>
-      <c r="D118" s="26" t="s">
-        <v>227</v>
-      </c>
-      <c r="E118" s="27" t="s">
+      <c r="A118" s="30">
+        <v>20</v>
+      </c>
+      <c r="B118" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="C118" s="32">
+        <v>20</v>
+      </c>
+      <c r="D118" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="E118" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F118" s="26" t="s">
-        <v>181</v>
+      <c r="F118" s="30" t="s">
+        <v>77</v>
       </c>
       <c r="G118" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F118),0)&gt;0), MAX($G$1:G117)+1, ""))</f>
@@ -4926,10 +4929,10 @@
         <v>25</v>
       </c>
       <c r="D119" s="26" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="E119" s="27" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="F119" s="26" t="s">
         <v>179</v>
@@ -4954,10 +4957,10 @@
         <v>25</v>
       </c>
       <c r="D120" s="26" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E120" s="27" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F120" s="26" t="s">
         <v>177</v>
@@ -4976,19 +4979,19 @@
         <v>25</v>
       </c>
       <c r="B121" s="27" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C121" s="28">
         <v>25</v>
       </c>
       <c r="D121" s="26" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="E121" s="27" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F121" s="26" t="s">
-        <v>326</v>
+        <v>175</v>
       </c>
       <c r="G121" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F121),0)&gt;0), MAX($G$1:G120)+1, ""))</f>
@@ -5004,19 +5007,19 @@
         <v>25</v>
       </c>
       <c r="B122" s="27" t="s">
-        <v>364</v>
+        <v>173</v>
       </c>
       <c r="C122" s="28">
         <v>25</v>
       </c>
-      <c r="D122" s="26">
-        <v>3</v>
+      <c r="D122" s="26" t="s">
+        <v>224</v>
       </c>
       <c r="E122" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F122" s="26" t="s">
-        <v>365</v>
+        <v>324</v>
       </c>
       <c r="G122" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F122),0)&gt;0), MAX($G$1:G121)+1, ""))</f>
@@ -5032,19 +5035,19 @@
         <v>25</v>
       </c>
       <c r="B123" s="27" t="s">
-        <v>174</v>
+        <v>362</v>
       </c>
       <c r="C123" s="28">
         <v>25</v>
       </c>
       <c r="D123" s="26">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="E123" s="27" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="F123" s="26" t="s">
-        <v>340</v>
+        <v>363</v>
       </c>
       <c r="G123" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F123),0)&gt;0), MAX($G$1:G122)+1, ""))</f>
@@ -5056,23 +5059,23 @@
       </c>
     </row>
     <row r="124" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A124" s="30">
+      <c r="A124" s="26">
         <v>25</v>
       </c>
-      <c r="B124" s="31" t="s">
-        <v>286</v>
-      </c>
-      <c r="C124" s="32">
+      <c r="B124" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="C124" s="28">
         <v>25</v>
       </c>
-      <c r="D124" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="E124" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="F124" s="30" t="s">
-        <v>104</v>
+      <c r="D124" s="26">
+        <v>2.7</v>
+      </c>
+      <c r="E124" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F124" s="26" t="s">
+        <v>338</v>
       </c>
       <c r="G124" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F124),0)&gt;0), MAX($G$1:G123)+1, ""))</f>
@@ -5094,13 +5097,13 @@
         <v>25</v>
       </c>
       <c r="D125" s="30" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E125" s="31" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F125" s="30" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G125" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F125),0)&gt;0), MAX($G$1:G124)+1, ""))</f>
@@ -5112,23 +5115,23 @@
       </c>
     </row>
     <row r="126" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A126" s="26">
+      <c r="A126" s="30">
         <v>25</v>
       </c>
-      <c r="B126" s="27" t="s">
-        <v>172</v>
-      </c>
-      <c r="C126" s="28">
+      <c r="B126" s="31" t="s">
+        <v>282</v>
+      </c>
+      <c r="C126" s="32">
         <v>25</v>
       </c>
-      <c r="D126" s="26" t="s">
-        <v>236</v>
-      </c>
-      <c r="E126" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F126" s="26" t="s">
-        <v>173</v>
+      <c r="D126" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E126" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="F126" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G126" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F126),0)&gt;0), MAX($G$1:G125)+1, ""))</f>
@@ -5150,10 +5153,10 @@
         <v>25</v>
       </c>
       <c r="D127" s="26" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="E127" s="27" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F127" s="26" t="s">
         <v>171</v>
@@ -5172,19 +5175,19 @@
         <v>25</v>
       </c>
       <c r="B128" s="27" t="s">
-        <v>362</v>
+        <v>168</v>
       </c>
       <c r="C128" s="28">
         <v>25</v>
       </c>
-      <c r="D128" s="26">
-        <v>3.4</v>
+      <c r="D128" s="26" t="s">
+        <v>217</v>
       </c>
       <c r="E128" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F128" s="26" t="s">
-        <v>363</v>
+        <v>169</v>
       </c>
       <c r="G128" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F128),0)&gt;0), MAX($G$1:G127)+1, ""))</f>
@@ -5196,23 +5199,23 @@
       </c>
     </row>
     <row r="129" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A129" s="30">
+      <c r="A129" s="26">
         <v>25</v>
       </c>
-      <c r="B129" s="31" t="s">
-        <v>280</v>
-      </c>
-      <c r="C129" s="32">
+      <c r="B129" s="27" t="s">
+        <v>360</v>
+      </c>
+      <c r="C129" s="28">
         <v>25</v>
       </c>
-      <c r="D129" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="E129" s="31" t="s">
+      <c r="D129" s="26">
+        <v>3.4</v>
+      </c>
+      <c r="E129" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F129" s="30" t="s">
-        <v>104</v>
+      <c r="F129" s="26" t="s">
+        <v>361</v>
       </c>
       <c r="G129" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F129),0)&gt;0), MAX($G$1:G128)+1, ""))</f>
@@ -5224,23 +5227,23 @@
       </c>
     </row>
     <row r="130" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A130" s="26">
+      <c r="A130" s="30">
         <v>25</v>
       </c>
-      <c r="B130" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="C130" s="28">
+      <c r="B130" s="31" t="s">
+        <v>278</v>
+      </c>
+      <c r="C130" s="32">
         <v>25</v>
       </c>
-      <c r="D130" s="26" t="s">
-        <v>223</v>
-      </c>
-      <c r="E130" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F130" s="26" t="s">
-        <v>169</v>
+      <c r="D130" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E130" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F130" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G130" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F130),0)&gt;0), MAX($G$1:G129)+1, ""))</f>
@@ -5262,10 +5265,10 @@
         <v>25</v>
       </c>
       <c r="D131" s="26" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="E131" s="27" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F131" s="26" t="s">
         <v>167</v>
@@ -5290,10 +5293,10 @@
         <v>25</v>
       </c>
       <c r="D132" s="26" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="E132" s="27" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="F132" s="26" t="s">
         <v>165</v>
@@ -5318,10 +5321,10 @@
         <v>25</v>
       </c>
       <c r="D133" s="26" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E133" s="27" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F133" s="26" t="s">
         <v>163</v>
@@ -5346,10 +5349,10 @@
         <v>25</v>
       </c>
       <c r="D134" s="26" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="E134" s="27" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F134" s="26" t="s">
         <v>161</v>
@@ -5368,19 +5371,19 @@
         <v>25</v>
       </c>
       <c r="B135" s="27" t="s">
-        <v>344</v>
+        <v>158</v>
       </c>
       <c r="C135" s="28">
         <v>25</v>
       </c>
-      <c r="D135" s="26">
-        <v>3.4</v>
+      <c r="D135" s="26" t="s">
+        <v>228</v>
       </c>
       <c r="E135" s="27" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F135" s="26" t="s">
-        <v>345</v>
+        <v>159</v>
       </c>
       <c r="G135" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F135),0)&gt;0), MAX($G$1:G134)+1, ""))</f>
@@ -5396,22 +5399,22 @@
         <v>25</v>
       </c>
       <c r="B136" s="27" t="s">
-        <v>312</v>
+        <v>342</v>
       </c>
       <c r="C136" s="28">
         <v>25</v>
       </c>
       <c r="D136" s="26">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="E136" s="27" t="s">
-        <v>311</v>
+        <v>81</v>
       </c>
       <c r="F136" s="26" t="s">
-        <v>313</v>
+        <v>343</v>
       </c>
       <c r="G136" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F136),0)&gt;0), MAX($G$1:G134)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F136),0)&gt;0), MAX($G$1:G135)+1, ""))</f>
         <v/>
       </c>
       <c r="H136" s="21" t="b">
@@ -5424,22 +5427,22 @@
         <v>25</v>
       </c>
       <c r="B137" s="27" t="s">
-        <v>158</v>
+        <v>310</v>
       </c>
       <c r="C137" s="28">
         <v>25</v>
       </c>
-      <c r="D137" s="26" t="s">
-        <v>229</v>
+      <c r="D137" s="26">
+        <v>3.9</v>
       </c>
       <c r="E137" s="27" t="s">
-        <v>83</v>
+        <v>309</v>
       </c>
       <c r="F137" s="26" t="s">
-        <v>159</v>
+        <v>311</v>
       </c>
       <c r="G137" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F137),0)&gt;0), MAX($G$1:G136)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F137),0)&gt;0), MAX($G$1:G135)+1, ""))</f>
         <v/>
       </c>
       <c r="H137" s="21" t="b">
@@ -5458,10 +5461,10 @@
         <v>25</v>
       </c>
       <c r="D138" s="26" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E138" s="27" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="F138" s="26" t="s">
         <v>157</v>
@@ -5486,10 +5489,10 @@
         <v>25</v>
       </c>
       <c r="D139" s="26" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="E139" s="27" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="F139" s="26" t="s">
         <v>155</v>
@@ -5508,19 +5511,19 @@
         <v>25</v>
       </c>
       <c r="B140" s="27" t="s">
-        <v>249</v>
+        <v>152</v>
       </c>
       <c r="C140" s="28">
         <v>25</v>
       </c>
-      <c r="D140" s="39" t="s">
-        <v>231</v>
+      <c r="D140" s="26" t="s">
+        <v>230</v>
       </c>
       <c r="E140" s="27" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F140" s="26" t="s">
-        <v>250</v>
+        <v>153</v>
       </c>
       <c r="G140" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F140),0)&gt;0), MAX($G$1:G139)+1, ""))</f>
@@ -5536,19 +5539,19 @@
         <v>25</v>
       </c>
       <c r="B141" s="27" t="s">
-        <v>152</v>
+        <v>247</v>
       </c>
       <c r="C141" s="28">
         <v>25</v>
       </c>
-      <c r="D141" s="26" t="s">
-        <v>237</v>
+      <c r="D141" s="39" t="s">
+        <v>229</v>
       </c>
       <c r="E141" s="27" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="F141" s="26" t="s">
-        <v>153</v>
+        <v>248</v>
       </c>
       <c r="G141" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F141),0)&gt;0), MAX($G$1:G140)+1, ""))</f>
@@ -5560,23 +5563,23 @@
       </c>
     </row>
     <row r="142" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A142" s="30">
+      <c r="A142" s="26">
         <v>25</v>
       </c>
-      <c r="B142" s="31" t="s">
-        <v>290</v>
-      </c>
-      <c r="C142" s="32">
+      <c r="B142" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C142" s="28">
         <v>25</v>
       </c>
-      <c r="D142" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="E142" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="F142" s="30" t="s">
-        <v>104</v>
+      <c r="D142" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="E142" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="F142" s="26" t="s">
+        <v>151</v>
       </c>
       <c r="G142" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F142),0)&gt;0), MAX($G$1:G141)+1, ""))</f>
@@ -5598,13 +5601,13 @@
         <v>25</v>
       </c>
       <c r="D143" s="30" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E143" s="31" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F143" s="30" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G143" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F143),0)&gt;0), MAX($G$1:G142)+1, ""))</f>
@@ -5620,19 +5623,19 @@
         <v>25</v>
       </c>
       <c r="B144" s="31" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C144" s="32">
         <v>25</v>
       </c>
       <c r="D144" s="30" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E144" s="31" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F144" s="30" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G144" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F144),0)&gt;0), MAX($G$1:G143)+1, ""))</f>
@@ -5644,23 +5647,23 @@
       </c>
     </row>
     <row r="145" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A145" s="26">
+      <c r="A145" s="30">
         <v>25</v>
       </c>
-      <c r="B145" s="27" t="s">
-        <v>254</v>
-      </c>
-      <c r="C145" s="28">
+      <c r="B145" s="31" t="s">
+        <v>287</v>
+      </c>
+      <c r="C145" s="32">
         <v>25</v>
       </c>
-      <c r="D145" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E145" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F145" s="26" t="s">
-        <v>255</v>
+      <c r="D145" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E145" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="F145" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G145" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B145),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E145),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F145),0)&gt;0), MAX($G$1:G144)+1, ""))</f>
@@ -5672,23 +5675,23 @@
       </c>
     </row>
     <row r="146" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A146" s="30">
+      <c r="A146" s="26">
         <v>25</v>
       </c>
-      <c r="B146" s="31" t="s">
-        <v>287</v>
-      </c>
-      <c r="C146" s="32">
+      <c r="B146" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="C146" s="28">
         <v>25</v>
       </c>
-      <c r="D146" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="E146" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="F146" s="30" t="s">
-        <v>104</v>
+      <c r="D146" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E146" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="F146" s="26" t="s">
+        <v>253</v>
       </c>
       <c r="G146" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F146),0)&gt;0), MAX($G$1:G145)+1, ""))</f>
@@ -5700,26 +5703,26 @@
       </c>
     </row>
     <row r="147" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A147" s="26">
+      <c r="A147" s="30">
         <v>25</v>
       </c>
-      <c r="B147" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="C147" s="28">
+      <c r="B147" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="C147" s="32">
         <v>25</v>
       </c>
-      <c r="D147" s="26" t="s">
-        <v>228</v>
-      </c>
-      <c r="E147" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="F147" s="26" t="s">
-        <v>151</v>
+      <c r="D147" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E147" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="F147" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G147" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F147),0)&gt;0), MAX($G$1:G145)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F147),0)&gt;0), MAX($G$1:G146)+1, ""))</f>
         <v/>
       </c>
       <c r="H147" s="21" t="b">
@@ -5728,26 +5731,26 @@
       </c>
     </row>
     <row r="148" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A148" s="30">
-        <v>30</v>
-      </c>
-      <c r="B148" s="31" t="s">
-        <v>194</v>
-      </c>
-      <c r="C148" s="32">
-        <v>30</v>
-      </c>
-      <c r="D148" s="30" t="s">
-        <v>234</v>
-      </c>
-      <c r="E148" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="F148" s="30" t="s">
-        <v>195</v>
+      <c r="A148" s="26">
+        <v>25</v>
+      </c>
+      <c r="B148" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="C148" s="28">
+        <v>25</v>
+      </c>
+      <c r="D148" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="E148" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F148" s="26" t="s">
+        <v>149</v>
       </c>
       <c r="G148" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F148),0)&gt;0), MAX($G$1:G147)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F148),0)&gt;0), MAX($G$1:G146)+1, ""))</f>
         <v/>
       </c>
       <c r="H148" s="21" t="b">
@@ -5760,19 +5763,19 @@
         <v>30</v>
       </c>
       <c r="B149" s="31" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C149" s="32">
         <v>30</v>
       </c>
       <c r="D149" s="30" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="E149" s="31" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F149" s="30" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G149" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B149),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E149),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F149),0)&gt;0), MAX($G$1:G148)+1, ""))</f>
@@ -5794,13 +5797,13 @@
         <v>30</v>
       </c>
       <c r="D150" s="30" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E150" s="31" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F150" s="30" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G150" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B150),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E150),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F150),0)&gt;0), MAX($G$1:G149)+1, ""))</f>
@@ -5816,16 +5819,16 @@
         <v>30</v>
       </c>
       <c r="B151" s="31" t="s">
-        <v>248</v>
+        <v>189</v>
       </c>
       <c r="C151" s="32">
         <v>30</v>
       </c>
       <c r="D151" s="30" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="E151" s="31" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F151" s="30" t="s">
         <v>190</v>
@@ -5844,19 +5847,19 @@
         <v>30</v>
       </c>
       <c r="B152" s="31" t="s">
-        <v>188</v>
+        <v>246</v>
       </c>
       <c r="C152" s="32">
         <v>30</v>
       </c>
       <c r="D152" s="30" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="E152" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F152" s="30" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G152" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B152),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E152),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F152),0)&gt;0), MAX($G$1:G151)+1, ""))</f>
@@ -5878,10 +5881,10 @@
         <v>30</v>
       </c>
       <c r="D153" s="30" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E153" s="31" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="F153" s="30" t="s">
         <v>187</v>
@@ -5906,10 +5909,10 @@
         <v>30</v>
       </c>
       <c r="D154" s="30" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="E154" s="31" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="F154" s="30" t="s">
         <v>185</v>
@@ -5928,19 +5931,19 @@
         <v>30</v>
       </c>
       <c r="B155" s="31" t="s">
-        <v>339</v>
+        <v>182</v>
       </c>
       <c r="C155" s="32">
         <v>30</v>
       </c>
-      <c r="D155" s="30">
-        <v>2.9</v>
+      <c r="D155" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="E155" s="31" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="F155" s="30" t="s">
-        <v>340</v>
+        <v>183</v>
       </c>
       <c r="G155" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F155),0)&gt;0), MAX($G$1:G154)+1, ""))</f>
@@ -5956,22 +5959,22 @@
         <v>30</v>
       </c>
       <c r="B156" s="31" t="s">
-        <v>182</v>
+        <v>337</v>
       </c>
       <c r="C156" s="32">
         <v>30</v>
       </c>
-      <c r="D156" s="30" t="s">
-        <v>240</v>
+      <c r="D156" s="30">
+        <v>2.9</v>
       </c>
       <c r="E156" s="31" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="F156" s="30" t="s">
-        <v>183</v>
+        <v>338</v>
       </c>
       <c r="G156" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B156),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E156),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F156),0)&gt;0), MAX($G$1:G154)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B156),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E156),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F156),0)&gt;0), MAX($G$1:G155)+1, ""))</f>
         <v/>
       </c>
       <c r="H156" s="21" t="b">
@@ -5980,26 +5983,26 @@
       </c>
     </row>
     <row r="157" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A157" s="26">
-        <v>40</v>
-      </c>
-      <c r="B157" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="C157" s="28">
-        <v>40</v>
-      </c>
-      <c r="D157" s="26" t="s">
-        <v>245</v>
-      </c>
-      <c r="E157" s="27" t="s">
-        <v>200</v>
-      </c>
-      <c r="F157" s="26" t="s">
-        <v>201</v>
+      <c r="A157" s="30">
+        <v>30</v>
+      </c>
+      <c r="B157" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="C157" s="32">
+        <v>30</v>
+      </c>
+      <c r="D157" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="E157" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="F157" s="30" t="s">
+        <v>181</v>
       </c>
       <c r="G157" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F157),0)&gt;0), MAX($G$1:G156)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F157),0)&gt;0), MAX($G$1:G155)+1, ""))</f>
         <v/>
       </c>
       <c r="H157" s="21" t="b">
@@ -6012,19 +6015,19 @@
         <v>40</v>
       </c>
       <c r="B158" s="27" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C158" s="28">
         <v>40</v>
       </c>
       <c r="D158" s="26" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E158" s="27" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F158" s="26" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G158" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B158),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E158),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F158),0)&gt;0), MAX($G$1:G157)+1, ""))</f>
@@ -6040,19 +6043,19 @@
         <v>40</v>
       </c>
       <c r="B159" s="27" t="s">
-        <v>251</v>
+        <v>194</v>
       </c>
       <c r="C159" s="28">
         <v>40</v>
       </c>
-      <c r="D159" s="26">
-        <v>8.3000000000000007</v>
+      <c r="D159" s="26" t="s">
+        <v>242</v>
       </c>
       <c r="E159" s="27" t="s">
-        <v>252</v>
+        <v>195</v>
       </c>
       <c r="F159" s="26" t="s">
-        <v>253</v>
+        <v>196</v>
       </c>
       <c r="G159" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F159),0)&gt;0), MAX($G$1:G158)+1, ""))</f>
@@ -6065,22 +6068,22 @@
     </row>
     <row r="160" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A160" s="26">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B160" s="27" t="s">
-        <v>296</v>
+        <v>249</v>
       </c>
       <c r="C160" s="28">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D160" s="26">
-        <v>10.199999999999999</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="E160" s="27" t="s">
-        <v>297</v>
+        <v>250</v>
       </c>
       <c r="F160" s="26" t="s">
-        <v>298</v>
+        <v>251</v>
       </c>
       <c r="G160" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B160),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E160),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F160),0)&gt;0), MAX($G$1:G159)+1, ""))</f>
@@ -6091,97 +6094,119 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A161" s="1"/>
-      <c r="C161" s="1"/>
-      <c r="D161" s="1"/>
-      <c r="F161" s="1"/>
-    </row>
-    <row r="162" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A161" s="26">
+        <v>45</v>
+      </c>
+      <c r="B161" s="27" t="s">
+        <v>294</v>
+      </c>
+      <c r="C161" s="28">
+        <v>45</v>
+      </c>
+      <c r="D161" s="26">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E161" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="F161" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="G161" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B161),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E161),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F161),0)&gt;0), MAX($G$1:G160)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H161" s="21" t="b">
+        <f>A161=C161</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="C162" s="1"/>
       <c r="D162" s="1"/>
       <c r="F162" s="1"/>
     </row>
-    <row r="163" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="C163" s="1"/>
       <c r="D163" s="1"/>
       <c r="F163" s="1"/>
     </row>
-    <row r="164" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="C164" s="1"/>
       <c r="D164" s="1"/>
       <c r="F164" s="1"/>
     </row>
-    <row r="165" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="C165" s="1"/>
       <c r="D165" s="1"/>
       <c r="F165" s="1"/>
     </row>
-    <row r="166" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="C166" s="1"/>
       <c r="D166" s="1"/>
       <c r="F166" s="1"/>
     </row>
-    <row r="167" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="C167" s="1"/>
       <c r="D167" s="1"/>
       <c r="F167" s="1"/>
     </row>
-    <row r="168" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="C168" s="1"/>
       <c r="D168" s="1"/>
       <c r="F168" s="1"/>
     </row>
-    <row r="169" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="C169" s="1"/>
       <c r="D169" s="1"/>
       <c r="F169" s="1"/>
     </row>
-    <row r="170" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="C170" s="1"/>
       <c r="D170" s="1"/>
       <c r="F170" s="1"/>
     </row>
-    <row r="171" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="C171" s="1"/>
       <c r="D171" s="1"/>
       <c r="F171" s="1"/>
     </row>
-    <row r="172" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="C172" s="1"/>
       <c r="D172" s="1"/>
       <c r="F172" s="1"/>
     </row>
-    <row r="173" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="C173" s="1"/>
       <c r="D173" s="1"/>
       <c r="F173" s="1"/>
     </row>
-    <row r="174" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="C174" s="1"/>
       <c r="D174" s="1"/>
       <c r="F174" s="1"/>
     </row>
-    <row r="175" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="C175" s="1"/>
       <c r="D175" s="1"/>
       <c r="F175" s="1"/>
     </row>
-    <row r="176" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="C176" s="1"/>
       <c r="D176" s="1"/>
@@ -11347,18 +11372,24 @@
       <c r="D1036" s="1"/>
       <c r="F1036" s="1"/>
     </row>
+    <row r="1037" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1037" s="1"/>
+      <c r="C1037" s="1"/>
+      <c r="D1037" s="1"/>
+      <c r="F1037" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H148">
+  <autoFilter ref="A1:H149">
     <sortState ref="A2:H147">
       <sortCondition ref="A2:A147"/>
       <sortCondition ref="B2:B147"/>
       <sortCondition ref="D2:D147"/>
     </sortState>
   </autoFilter>
-  <sortState ref="A2:H160">
-    <sortCondition ref="A2:A160"/>
-    <sortCondition ref="B2:B160"/>
-    <sortCondition ref="D2:D160"/>
+  <sortState ref="A2:H161">
+    <sortCondition ref="A2:A161"/>
+    <sortCondition ref="B2:B161"/>
+    <sortCondition ref="D2:D161"/>
   </sortState>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -11382,7 +11413,7 @@
   <sheetData>
     <row r="1" spans="1:6" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="19" t="str">
@@ -11395,7 +11426,7 @@
     </row>
     <row r="2" spans="1:6" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="17"/>

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -2475,7 +2475,7 @@
         <v>2.1</v>
       </c>
       <c r="E30" s="27" t="s">
-        <v>295</v>
+        <v>8</v>
       </c>
       <c r="F30" s="26" t="s">
         <v>307</v>

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Consulta" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$149</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$151</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$138</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Base!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="371">
   <si>
     <t>Grupo</t>
   </si>
@@ -1126,6 +1126,18 @@
   </si>
   <si>
     <t>CARLOS WENCESLEU ATÉ O PARQUE</t>
+  </si>
+  <si>
+    <t>PARANAGUA</t>
+  </si>
+  <si>
+    <t>21710-690</t>
+  </si>
+  <si>
+    <t>MARECHAL FONTENELE 3944</t>
+  </si>
+  <si>
+    <t>21750-001</t>
   </si>
 </sst>
 </file>
@@ -1643,7 +1655,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H1037"/>
+  <dimension ref="A1:H1039"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.453125" customWidth="1"/>
@@ -1949,7 +1961,7 @@
         <v>25</v>
       </c>
       <c r="G11" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B11),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E11),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F11),0)&gt;0), MAX($G$1:G10)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B11),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E11),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F11),0)&gt;0), MAX($G$1:G9)+1, ""))</f>
         <v/>
       </c>
       <c r="H11" s="21" t="b">
@@ -2046,19 +2058,19 @@
         <v>13</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>271</v>
+        <v>367</v>
       </c>
       <c r="C15" s="32">
         <v>13</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>270</v>
+        <v>8</v>
       </c>
       <c r="F15" s="30" t="s">
-        <v>25</v>
+        <v>368</v>
       </c>
       <c r="G15" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B15),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E15),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F15),0)&gt;0), MAX($G$1:G14)+1, ""))</f>
@@ -2074,19 +2086,19 @@
         <v>13</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>13</v>
+        <v>271</v>
       </c>
       <c r="C16" s="32">
         <v>13</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>8</v>
+        <v>270</v>
       </c>
       <c r="F16" s="30" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G16" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B16),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E16),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F16),0)&gt;0), MAX($G$1:G15)+1, ""))</f>
@@ -2102,19 +2114,19 @@
         <v>13</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C17" s="32">
         <v>13</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E17" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F17" s="30" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G17" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B17),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E17),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F17),0)&gt;0), MAX($G$1:G16)+1, ""))</f>
@@ -2130,19 +2142,19 @@
         <v>13</v>
       </c>
       <c r="B18" s="31" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C18" s="32">
         <v>13</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E18" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F18" s="30" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G18" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B18),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E18),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F18),0)&gt;0), MAX($G$1:G17)+1, ""))</f>
@@ -2154,23 +2166,23 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="26">
-        <v>15</v>
-      </c>
-      <c r="B19" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="28">
-        <v>15</v>
-      </c>
-      <c r="D19" s="26" t="s">
-        <v>210</v>
-      </c>
-      <c r="E19" s="27" t="s">
-        <v>305</v>
-      </c>
-      <c r="F19" s="26" t="s">
-        <v>75</v>
+      <c r="A19" s="30">
+        <v>13</v>
+      </c>
+      <c r="B19" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="32">
+        <v>13</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="30" t="s">
+        <v>9</v>
       </c>
       <c r="G19" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B19),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E19),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F19),0)&gt;0), MAX($G$1:G18)+1, ""))</f>
@@ -2186,19 +2198,19 @@
         <v>15</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C20" s="28">
         <v>15</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E20" s="27" t="s">
-        <v>8</v>
+        <v>305</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G20" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B20),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E20),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F20),0)&gt;0), MAX($G$1:G19)+1, ""))</f>
@@ -2214,22 +2226,22 @@
         <v>15</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>365</v>
+        <v>72</v>
       </c>
       <c r="C21" s="28">
         <v>15</v>
       </c>
-      <c r="D21" s="26">
-        <v>1</v>
+      <c r="D21" s="26" t="s">
+        <v>209</v>
       </c>
       <c r="E21" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G21" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F21),0)&gt;0), MAX($G$1:G18)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F21),0)&gt;0), MAX($G$1:G20)+1, ""))</f>
         <v/>
       </c>
       <c r="H21" s="21" t="b">
@@ -2242,22 +2254,22 @@
         <v>15</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>66</v>
+        <v>365</v>
       </c>
       <c r="C22" s="28">
         <v>15</v>
       </c>
-      <c r="D22" s="26" t="s">
-        <v>219</v>
+      <c r="D22" s="26">
+        <v>1</v>
       </c>
       <c r="E22" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G22" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B22),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E22),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F22),0)&gt;0), MAX($G$1:G21)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B22),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E22),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F22),0)&gt;0), MAX($G$1:G19)+1, ""))</f>
         <v/>
       </c>
       <c r="H22" s="21" t="b">
@@ -2270,19 +2282,19 @@
         <v>15</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C23" s="28">
         <v>15</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="E23" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G23" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B23),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E23),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F23),0)&gt;0), MAX($G$1:G22)+1, ""))</f>
@@ -2298,7 +2310,7 @@
         <v>15</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>266</v>
+        <v>64</v>
       </c>
       <c r="C24" s="28">
         <v>15</v>
@@ -2307,7 +2319,7 @@
         <v>206</v>
       </c>
       <c r="E24" s="27" t="s">
-        <v>267</v>
+        <v>8</v>
       </c>
       <c r="F24" s="26" t="s">
         <v>65</v>
@@ -2326,19 +2338,19 @@
         <v>15</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>345</v>
+        <v>266</v>
       </c>
       <c r="C25" s="28">
         <v>15</v>
       </c>
-      <c r="D25" s="26">
-        <v>2.5</v>
+      <c r="D25" s="26" t="s">
+        <v>206</v>
       </c>
       <c r="E25" s="27" t="s">
-        <v>8</v>
+        <v>267</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>346</v>
+        <v>65</v>
       </c>
       <c r="G25" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B25),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E25),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F25),0)&gt;0), MAX($G$1:G24)+1, ""))</f>
@@ -2354,19 +2366,19 @@
         <v>15</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>259</v>
+        <v>345</v>
       </c>
       <c r="C26" s="28">
         <v>15</v>
       </c>
-      <c r="D26" s="26" t="s">
-        <v>7</v>
+      <c r="D26" s="26">
+        <v>2.5</v>
       </c>
       <c r="E26" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F26" s="26" t="s">
-        <v>261</v>
+        <v>346</v>
       </c>
       <c r="G26" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B26),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E26),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F26),0)&gt;0), MAX($G$1:G25)+1, ""))</f>
@@ -2382,19 +2394,19 @@
         <v>15</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
       <c r="C27" s="28">
         <v>15</v>
       </c>
-      <c r="D27" s="26">
-        <v>2</v>
+      <c r="D27" s="26" t="s">
+        <v>7</v>
       </c>
       <c r="E27" s="27" t="s">
-        <v>352</v>
+        <v>8</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>348</v>
+        <v>261</v>
       </c>
       <c r="G27" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B27),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E27),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F27),0)&gt;0), MAX($G$1:G26)+1, ""))</f>
@@ -2410,19 +2422,19 @@
         <v>15</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>57</v>
+        <v>351</v>
       </c>
       <c r="C28" s="28">
         <v>15</v>
       </c>
-      <c r="D28" s="26" t="s">
-        <v>223</v>
+      <c r="D28" s="26">
+        <v>2</v>
       </c>
       <c r="E28" s="27" t="s">
-        <v>8</v>
+        <v>352</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>58</v>
+        <v>348</v>
       </c>
       <c r="G28" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B28),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E28),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F28),0)&gt;0), MAX($G$1:G27)+1, ""))</f>
@@ -2438,19 +2450,19 @@
         <v>15</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>268</v>
+        <v>57</v>
       </c>
       <c r="C29" s="28">
         <v>15</v>
       </c>
       <c r="D29" s="26" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="E29" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G29" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B29),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E29),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F29),0)&gt;0), MAX($G$1:G28)+1, ""))</f>
@@ -2466,19 +2478,19 @@
         <v>15</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>306</v>
+        <v>268</v>
       </c>
       <c r="C30" s="28">
         <v>15</v>
       </c>
-      <c r="D30" s="26">
-        <v>2.1</v>
+      <c r="D30" s="26" t="s">
+        <v>205</v>
       </c>
       <c r="E30" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>307</v>
+        <v>56</v>
       </c>
       <c r="G30" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B30),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E30),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F30),0)&gt;0), MAX($G$1:G29)+1, ""))</f>
@@ -2494,19 +2506,19 @@
         <v>15</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>54</v>
+        <v>306</v>
       </c>
       <c r="C31" s="28">
         <v>15</v>
       </c>
-      <c r="D31" s="26" t="s">
-        <v>204</v>
+      <c r="D31" s="26">
+        <v>2.1</v>
       </c>
       <c r="E31" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F31" s="26" t="s">
-        <v>55</v>
+        <v>307</v>
       </c>
       <c r="G31" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B31),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E31),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F31),0)&gt;0), MAX($G$1:G30)+1, ""))</f>
@@ -2522,19 +2534,19 @@
         <v>15</v>
       </c>
       <c r="B32" s="27" t="s">
-        <v>277</v>
+        <v>54</v>
       </c>
       <c r="C32" s="28">
         <v>15</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E32" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F32" s="26" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="G32" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B32),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E32),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F32),0)&gt;0), MAX($G$1:G31)+1, ""))</f>
@@ -2550,19 +2562,19 @@
         <v>15</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="C33" s="28">
         <v>15</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>21</v>
+        <v>210</v>
       </c>
       <c r="E33" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F33" s="26" t="s">
-        <v>262</v>
+        <v>75</v>
       </c>
       <c r="G33" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B33),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E33),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F33),0)&gt;0), MAX($G$1:G32)+1, ""))</f>
@@ -2578,19 +2590,19 @@
         <v>15</v>
       </c>
       <c r="B34" s="27" t="s">
-        <v>292</v>
+        <v>260</v>
       </c>
       <c r="C34" s="28">
         <v>15</v>
       </c>
-      <c r="D34" s="26">
-        <v>2.2000000000000002</v>
+      <c r="D34" s="26" t="s">
+        <v>21</v>
       </c>
       <c r="E34" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F34" s="26" t="s">
-        <v>293</v>
+        <v>262</v>
       </c>
       <c r="G34" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B34),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E34),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F34),0)&gt;0), MAX($G$1:G33)+1, ""))</f>
@@ -2606,19 +2618,19 @@
         <v>15</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>354</v>
+        <v>292</v>
       </c>
       <c r="C35" s="28">
         <v>15</v>
       </c>
       <c r="D35" s="26">
-        <v>1.5</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E35" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>355</v>
+        <v>293</v>
       </c>
       <c r="G35" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F35),0)&gt;0), MAX($G$1:G34)+1, ""))</f>
@@ -2634,19 +2646,19 @@
         <v>15</v>
       </c>
       <c r="B36" s="27" t="s">
-        <v>50</v>
+        <v>354</v>
       </c>
       <c r="C36" s="28">
         <v>15</v>
       </c>
-      <c r="D36" s="26" t="s">
-        <v>213</v>
+      <c r="D36" s="26">
+        <v>1.5</v>
       </c>
       <c r="E36" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F36" s="26" t="s">
-        <v>51</v>
+        <v>355</v>
       </c>
       <c r="G36" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B36),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E36),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F36),0)&gt;0), MAX($G$1:G35)+1, ""))</f>
@@ -2662,19 +2674,19 @@
         <v>15</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C37" s="28">
         <v>15</v>
       </c>
       <c r="D37" s="26" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="E37" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G37" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F37),0)&gt;0), MAX($G$1:G36)+1, ""))</f>
@@ -2690,19 +2702,19 @@
         <v>15</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C38" s="28">
         <v>15</v>
       </c>
       <c r="D38" s="26" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="E38" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F38" s="26" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G38" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F38),0)&gt;0), MAX($G$1:G37)+1, ""))</f>
@@ -2718,19 +2730,19 @@
         <v>15</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C39" s="28">
         <v>15</v>
       </c>
       <c r="D39" s="26" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="E39" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F39" s="26" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G39" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B39),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E39),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F39),0)&gt;0), MAX($G$1:G38)+1, ""))</f>
@@ -2746,19 +2758,19 @@
         <v>15</v>
       </c>
       <c r="B40" s="27" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C40" s="28">
         <v>15</v>
       </c>
       <c r="D40" s="26" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="E40" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F40" s="26" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G40" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B40),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E40),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F40),0)&gt;0), MAX($G$1:G39)+1, ""))</f>
@@ -2774,19 +2786,19 @@
         <v>15</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>308</v>
+        <v>40</v>
       </c>
       <c r="C41" s="28">
         <v>15</v>
       </c>
-      <c r="D41" s="26">
-        <v>2.2000000000000002</v>
+      <c r="D41" s="26" t="s">
+        <v>212</v>
       </c>
       <c r="E41" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F41" s="26" t="s">
-        <v>293</v>
+        <v>41</v>
       </c>
       <c r="G41" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B41),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E41),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F41),0)&gt;0), MAX($G$1:G40)+1, ""))</f>
@@ -2802,19 +2814,19 @@
         <v>15</v>
       </c>
       <c r="B42" s="27" t="s">
-        <v>244</v>
+        <v>308</v>
       </c>
       <c r="C42" s="28">
         <v>15</v>
       </c>
       <c r="D42" s="26">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E42" s="27" t="s">
-        <v>245</v>
+        <v>8</v>
       </c>
       <c r="F42" s="26" t="s">
-        <v>202</v>
+        <v>293</v>
       </c>
       <c r="G42" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B42),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E42),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F42),0)&gt;0), MAX($G$1:G41)+1, ""))</f>
@@ -2830,19 +2842,19 @@
         <v>15</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>38</v>
+        <v>244</v>
       </c>
       <c r="C43" s="28">
         <v>15</v>
       </c>
-      <c r="D43" s="26" t="s">
-        <v>211</v>
+      <c r="D43" s="26">
+        <v>2.1</v>
       </c>
       <c r="E43" s="27" t="s">
-        <v>8</v>
+        <v>245</v>
       </c>
       <c r="F43" s="26" t="s">
-        <v>39</v>
+        <v>202</v>
       </c>
       <c r="G43" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F43),0)&gt;0), MAX($G$1:G42)+1, ""))</f>
@@ -2858,19 +2870,19 @@
         <v>15</v>
       </c>
       <c r="B44" s="27" t="s">
-        <v>341</v>
+        <v>38</v>
       </c>
       <c r="C44" s="28">
         <v>15</v>
       </c>
-      <c r="D44" s="26">
-        <v>1.4</v>
+      <c r="D44" s="26" t="s">
+        <v>211</v>
       </c>
       <c r="E44" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F44" s="26" t="s">
-        <v>347</v>
+        <v>39</v>
       </c>
       <c r="G44" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F44),0)&gt;0), MAX($G$1:G43)+1, ""))</f>
@@ -2886,19 +2898,19 @@
         <v>15</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>34</v>
+        <v>341</v>
       </c>
       <c r="C45" s="28">
         <v>15</v>
       </c>
-      <c r="D45" s="26" t="s">
-        <v>210</v>
+      <c r="D45" s="26">
+        <v>1.4</v>
       </c>
       <c r="E45" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F45" s="26" t="s">
-        <v>35</v>
+        <v>347</v>
       </c>
       <c r="G45" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F45),0)&gt;0), MAX($G$1:G44)+1, ""))</f>
@@ -2914,19 +2926,19 @@
         <v>15</v>
       </c>
       <c r="B46" s="27" t="s">
-        <v>280</v>
+        <v>34</v>
       </c>
       <c r="C46" s="28">
         <v>15</v>
       </c>
       <c r="D46" s="26" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E46" s="27" t="s">
-        <v>267</v>
+        <v>8</v>
       </c>
       <c r="F46" s="26" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G46" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F46),0)&gt;0), MAX($G$1:G45)+1, ""))</f>
@@ -2938,23 +2950,23 @@
       </c>
     </row>
     <row r="47" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A47" s="33">
-        <v>17</v>
-      </c>
-      <c r="B47" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="C47" s="35">
-        <v>17</v>
-      </c>
-      <c r="D47" s="33" t="s">
-        <v>214</v>
-      </c>
-      <c r="E47" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" s="33" t="s">
-        <v>71</v>
+      <c r="A47" s="26">
+        <v>15</v>
+      </c>
+      <c r="B47" s="27" t="s">
+        <v>280</v>
+      </c>
+      <c r="C47" s="28">
+        <v>15</v>
+      </c>
+      <c r="D47" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="E47" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="F47" s="26" t="s">
+        <v>33</v>
       </c>
       <c r="G47" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F47),0)&gt;0), MAX($G$1:G46)+1, ""))</f>
@@ -2970,19 +2982,19 @@
         <v>17</v>
       </c>
       <c r="B48" s="34" t="s">
-        <v>281</v>
+        <v>70</v>
       </c>
       <c r="C48" s="35">
         <v>17</v>
       </c>
       <c r="D48" s="33" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="E48" s="34" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="F48" s="33" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G48" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F48),0)&gt;0), MAX($G$1:G47)+1, ""))</f>
@@ -2994,53 +3006,53 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="26">
+      <c r="A49" s="33">
         <v>17</v>
       </c>
-      <c r="B49" s="27" t="s">
-        <v>313</v>
-      </c>
-      <c r="C49" s="28">
+      <c r="B49" s="34" t="s">
+        <v>281</v>
+      </c>
+      <c r="C49" s="35">
         <v>17</v>
       </c>
-      <c r="D49" s="26">
-        <v>1.7</v>
-      </c>
-      <c r="E49" s="27" t="s">
+      <c r="D49" s="33" t="s">
+        <v>222</v>
+      </c>
+      <c r="E49" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="F49" s="26" t="s">
-        <v>319</v>
-      </c>
-      <c r="G49" s="29"/>
+      <c r="F49" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="G49" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F49),0)&gt;0), MAX($G$1:G48)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H49" s="21" t="b">
         <f>A49=C49</f>
         <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A50" s="33">
+      <c r="A50" s="26">
         <v>17</v>
       </c>
-      <c r="B50" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="C50" s="35">
+      <c r="B50" s="27" t="s">
+        <v>313</v>
+      </c>
+      <c r="C50" s="28">
         <v>17</v>
       </c>
-      <c r="D50" s="33" t="s">
-        <v>215</v>
-      </c>
-      <c r="E50" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F50" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="G50" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F50),0)&gt;0), MAX($G$1:G49)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D50" s="26">
+        <v>1.7</v>
+      </c>
+      <c r="E50" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F50" s="26" t="s">
+        <v>319</v>
+      </c>
+      <c r="G50" s="29"/>
       <c r="H50" s="21" t="b">
         <f>A50=C50</f>
         <v>1</v>
@@ -3051,19 +3063,19 @@
         <v>17</v>
       </c>
       <c r="B51" s="34" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C51" s="35">
         <v>17</v>
       </c>
       <c r="D51" s="33" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E51" s="34" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="F51" s="33" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G51" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F51),0)&gt;0), MAX($G$1:G50)+1, ""))</f>
@@ -3075,25 +3087,28 @@
       </c>
     </row>
     <row r="52" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="26">
+      <c r="A52" s="33">
         <v>17</v>
       </c>
-      <c r="B52" s="27" t="s">
-        <v>315</v>
-      </c>
-      <c r="C52" s="28">
+      <c r="B52" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="C52" s="35">
         <v>17</v>
       </c>
-      <c r="D52" s="26">
-        <v>3</v>
-      </c>
-      <c r="E52" s="27" t="s">
+      <c r="D52" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="E52" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="F52" s="26" t="s">
-        <v>321</v>
-      </c>
-      <c r="G52" s="29"/>
+      <c r="F52" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="G52" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F52),0)&gt;0), MAX($G$1:G51)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H52" s="21" t="b">
         <f>A52=C52</f>
         <v>1</v>
@@ -3104,24 +3119,21 @@
         <v>17</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>340</v>
+        <v>315</v>
       </c>
       <c r="C53" s="28">
         <v>17</v>
       </c>
       <c r="D53" s="26">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="E53" s="27" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F53" s="26" t="s">
-        <v>349</v>
-      </c>
-      <c r="G53" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F53),0)&gt;0), MAX($G$1:G51)+1, ""))</f>
-        <v/>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="G53" s="29"/>
       <c r="H53" s="21" t="b">
         <f>A53=C53</f>
         <v>1</v>
@@ -3132,74 +3144,77 @@
         <v>17</v>
       </c>
       <c r="B54" s="27" t="s">
-        <v>316</v>
+        <v>340</v>
       </c>
       <c r="C54" s="28">
         <v>17</v>
       </c>
       <c r="D54" s="26">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="E54" s="27" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="F54" s="26" t="s">
-        <v>322</v>
-      </c>
-      <c r="G54" s="29"/>
+        <v>349</v>
+      </c>
+      <c r="G54" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F54),0)&gt;0), MAX($G$1:G52)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H54" s="21" t="b">
         <f>A54=C54</f>
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="36">
+      <c r="A55" s="26">
         <v>17</v>
       </c>
-      <c r="B55" s="37" t="s">
-        <v>289</v>
-      </c>
-      <c r="C55" s="38">
+      <c r="B55" s="27" t="s">
+        <v>316</v>
+      </c>
+      <c r="C55" s="28">
         <v>17</v>
       </c>
-      <c r="D55" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="E55" s="37" t="s">
+      <c r="D55" s="26">
+        <v>1.9</v>
+      </c>
+      <c r="E55" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="F55" s="36" t="s">
-        <v>111</v>
-      </c>
-      <c r="G55" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F55),0)&gt;0), MAX($G$1:G54)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="F55" s="26" t="s">
+        <v>322</v>
+      </c>
+      <c r="G55" s="29"/>
       <c r="H55" s="21" t="b">
         <f>A55=C55</f>
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A56" s="26">
+      <c r="A56" s="36">
         <v>17</v>
       </c>
-      <c r="B56" s="27" t="s">
-        <v>314</v>
-      </c>
-      <c r="C56" s="28">
+      <c r="B56" s="37" t="s">
+        <v>289</v>
+      </c>
+      <c r="C56" s="38">
         <v>17</v>
       </c>
-      <c r="D56" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E56" s="27" t="s">
+      <c r="D56" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E56" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="F56" s="26" t="s">
-        <v>320</v>
-      </c>
-      <c r="G56" s="29"/>
+      <c r="F56" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="G56" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F56),0)&gt;0), MAX($G$1:G55)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H56" s="21" t="b">
         <f>A56=C56</f>
         <v>1</v>
@@ -3210,19 +3225,19 @@
         <v>17</v>
       </c>
       <c r="B57" s="27" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C57" s="28">
         <v>17</v>
       </c>
       <c r="D57" s="26">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E57" s="27" t="s">
         <v>60</v>
       </c>
       <c r="F57" s="26" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="G57" s="29"/>
       <c r="H57" s="21" t="b">
@@ -3231,28 +3246,25 @@
       </c>
     </row>
     <row r="58" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A58" s="36">
+      <c r="A58" s="26">
         <v>17</v>
       </c>
-      <c r="B58" s="37" t="s">
-        <v>106</v>
-      </c>
-      <c r="C58" s="38">
+      <c r="B58" s="27" t="s">
+        <v>317</v>
+      </c>
+      <c r="C58" s="28">
         <v>17</v>
       </c>
-      <c r="D58" s="36" t="s">
-        <v>220</v>
-      </c>
-      <c r="E58" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="G58" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F58),0)&gt;0), MAX($G$1:G57)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D58" s="26">
+        <v>2</v>
+      </c>
+      <c r="E58" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F58" s="26" t="s">
+        <v>323</v>
+      </c>
+      <c r="G58" s="29"/>
       <c r="H58" s="21" t="b">
         <f>A58=C58</f>
         <v>1</v>
@@ -3263,19 +3275,19 @@
         <v>17</v>
       </c>
       <c r="B59" s="37" t="s">
-        <v>303</v>
+        <v>106</v>
       </c>
       <c r="C59" s="38">
         <v>17</v>
       </c>
       <c r="D59" s="36" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="E59" s="37" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="F59" s="36" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G59" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F59),0)&gt;0), MAX($G$1:G58)+1, ""))</f>
@@ -3287,26 +3299,26 @@
       </c>
     </row>
     <row r="60" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A60" s="33">
+      <c r="A60" s="36">
         <v>17</v>
       </c>
-      <c r="B60" s="34" t="s">
-        <v>52</v>
-      </c>
-      <c r="C60" s="35">
+      <c r="B60" s="37" t="s">
+        <v>303</v>
+      </c>
+      <c r="C60" s="38">
         <v>17</v>
       </c>
-      <c r="D60" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="E60" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F60" s="33" t="s">
-        <v>53</v>
+      <c r="D60" s="36" t="s">
+        <v>229</v>
+      </c>
+      <c r="E60" s="37" t="s">
+        <v>304</v>
+      </c>
+      <c r="F60" s="36" t="s">
+        <v>105</v>
       </c>
       <c r="G60" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F60),0)&gt;0), MAX($G$1:G55)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F60),0)&gt;0), MAX($G$1:G59)+1, ""))</f>
         <v/>
       </c>
       <c r="H60" s="21" t="b">
@@ -3315,26 +3327,26 @@
       </c>
     </row>
     <row r="61" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A61" s="26">
+      <c r="A61" s="33">
         <v>17</v>
       </c>
-      <c r="B61" s="27" t="s">
-        <v>356</v>
-      </c>
-      <c r="C61" s="28">
+      <c r="B61" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="C61" s="35">
         <v>17</v>
       </c>
-      <c r="D61" s="26">
-        <v>1.8</v>
-      </c>
-      <c r="E61" s="27" t="s">
+      <c r="D61" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="E61" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F61" s="26" t="s">
-        <v>357</v>
+      <c r="F61" s="33" t="s">
+        <v>53</v>
       </c>
       <c r="G61" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F61),0)&gt;0), MAX($G$1:G60)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F61),0)&gt;0), MAX($G$1:G56)+1, ""))</f>
         <v/>
       </c>
       <c r="H61" s="21" t="b">
@@ -3343,23 +3355,23 @@
       </c>
     </row>
     <row r="62" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A62" s="33">
+      <c r="A62" s="26">
         <v>17</v>
       </c>
-      <c r="B62" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="C62" s="35">
+      <c r="B62" s="27" t="s">
+        <v>356</v>
+      </c>
+      <c r="C62" s="28">
         <v>17</v>
       </c>
-      <c r="D62" s="33" t="s">
-        <v>211</v>
-      </c>
-      <c r="E62" s="34" t="s">
+      <c r="D62" s="26">
+        <v>1.8</v>
+      </c>
+      <c r="E62" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F62" s="33" t="s">
-        <v>49</v>
+      <c r="F62" s="26" t="s">
+        <v>357</v>
       </c>
       <c r="G62" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F62),0)&gt;0), MAX($G$1:G61)+1, ""))</f>
@@ -3371,23 +3383,23 @@
       </c>
     </row>
     <row r="63" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A63" s="36">
+      <c r="A63" s="33">
         <v>17</v>
       </c>
-      <c r="B63" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="C63" s="38">
+      <c r="B63" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="C63" s="35">
         <v>17</v>
       </c>
-      <c r="D63" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="E63" s="37" t="s">
+      <c r="D63" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="E63" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F63" s="36" t="s">
-        <v>98</v>
+      <c r="F63" s="33" t="s">
+        <v>49</v>
       </c>
       <c r="G63" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F63),0)&gt;0), MAX($G$1:G62)+1, ""))</f>
@@ -3403,19 +3415,19 @@
         <v>17</v>
       </c>
       <c r="B64" s="37" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C64" s="38">
         <v>17</v>
       </c>
       <c r="D64" s="36" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E64" s="37" t="s">
         <v>8</v>
       </c>
       <c r="F64" s="36" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G64" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F64),0)&gt;0), MAX($G$1:G63)+1, ""))</f>
@@ -3427,28 +3439,30 @@
       </c>
     </row>
     <row r="65" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A65" s="33">
+      <c r="A65" s="36">
         <v>17</v>
       </c>
-      <c r="B65" s="34" t="s">
-        <v>327</v>
-      </c>
-      <c r="C65" s="35">
+      <c r="B65" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="C65" s="38">
         <v>17</v>
       </c>
-      <c r="D65" s="33">
-        <v>1.9</v>
-      </c>
-      <c r="E65" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F65" s="33" t="s">
-        <v>329</v>
-      </c>
-      <c r="G65" s="29" t="s">
-        <v>326</v>
+      <c r="D65" s="36" t="s">
+        <v>217</v>
+      </c>
+      <c r="E65" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F65" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="G65" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F65),0)&gt;0), MAX($G$1:G64)+1, ""))</f>
+        <v/>
       </c>
       <c r="H65" s="21" t="b">
+        <f>A65=C65</f>
         <v>1</v>
       </c>
     </row>
@@ -3457,7 +3471,7 @@
         <v>17</v>
       </c>
       <c r="B66" s="34" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C66" s="35">
         <v>17</v>
@@ -3483,7 +3497,7 @@
         <v>17</v>
       </c>
       <c r="B67" s="34" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C67" s="35">
         <v>17</v>
@@ -3509,47 +3523,45 @@
         <v>17</v>
       </c>
       <c r="B68" s="34" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="C68" s="35">
         <v>17</v>
       </c>
-      <c r="D68" s="33" t="s">
+      <c r="D68" s="33">
+        <v>1.9</v>
+      </c>
+      <c r="E68" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="F68" s="33" t="s">
+        <v>329</v>
+      </c>
+      <c r="G68" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="H68" s="21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A69" s="33">
+        <v>17</v>
+      </c>
+      <c r="B69" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="C69" s="35">
+        <v>17</v>
+      </c>
+      <c r="D69" s="33" t="s">
         <v>214</v>
       </c>
-      <c r="E68" s="34" t="s">
+      <c r="E69" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F68" s="33" t="s">
+      <c r="F69" s="33" t="s">
         <v>37</v>
-      </c>
-      <c r="G68" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F68),0)&gt;0), MAX($G$1:G67)+1, ""))</f>
-        <v/>
-      </c>
-      <c r="H68" s="21" t="b">
-        <f>A68=C68</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A69" s="36">
-        <v>17</v>
-      </c>
-      <c r="B69" s="37" t="s">
-        <v>83</v>
-      </c>
-      <c r="C69" s="38">
-        <v>17</v>
-      </c>
-      <c r="D69" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="E69" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F69" s="36" t="s">
-        <v>84</v>
       </c>
       <c r="G69" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F69),0)&gt;0), MAX($G$1:G68)+1, ""))</f>
@@ -3561,23 +3573,23 @@
       </c>
     </row>
     <row r="70" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A70" s="33">
+      <c r="A70" s="36">
         <v>17</v>
       </c>
-      <c r="B70" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="35">
+      <c r="B70" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="C70" s="38">
         <v>17</v>
       </c>
-      <c r="D70" s="33" t="s">
-        <v>208</v>
-      </c>
-      <c r="E70" s="34" t="s">
+      <c r="D70" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E70" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F70" s="33" t="s">
-        <v>32</v>
+      <c r="F70" s="36" t="s">
+        <v>84</v>
       </c>
       <c r="G70" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F70),0)&gt;0), MAX($G$1:G69)+1, ""))</f>
@@ -3593,52 +3605,52 @@
         <v>17</v>
       </c>
       <c r="B71" s="34" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C71" s="35">
         <v>17</v>
       </c>
       <c r="D71" s="33" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E71" s="34" t="s">
         <v>8</v>
       </c>
       <c r="F71" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="G71" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F71),0)&gt;0), MAX($G$1:G70)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H71" s="21" t="b">
+        <f>A71=C71</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A72" s="33">
+        <v>17</v>
+      </c>
+      <c r="B72" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="C72" s="35">
+        <v>17</v>
+      </c>
+      <c r="D72" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="E72" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F72" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="G71" s="29" t="s">
+      <c r="G72" s="29" t="s">
         <v>326</v>
       </c>
-      <c r="H71" s="21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A72" s="30">
-        <v>20</v>
-      </c>
-      <c r="B72" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="C72" s="32">
-        <v>20</v>
-      </c>
-      <c r="D72" s="30" t="s">
-        <v>206</v>
-      </c>
-      <c r="E72" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F72" s="30" t="s">
-        <v>147</v>
-      </c>
-      <c r="G72" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F72),0)&gt;0), MAX($G$1:G68)+1, ""))</f>
-        <v/>
-      </c>
       <c r="H72" s="21" t="b">
-        <f>A72=C72</f>
         <v>1</v>
       </c>
     </row>
@@ -3647,22 +3659,22 @@
         <v>20</v>
       </c>
       <c r="B73" s="31" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C73" s="32">
         <v>20</v>
       </c>
       <c r="D73" s="30" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E73" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F73" s="30" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G73" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F73),0)&gt;0), MAX($G$1:G72)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F73),0)&gt;0), MAX($G$1:G69)+1, ""))</f>
         <v/>
       </c>
       <c r="H73" s="21" t="b">
@@ -3675,19 +3687,19 @@
         <v>20</v>
       </c>
       <c r="B74" s="31" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C74" s="32">
         <v>20</v>
       </c>
       <c r="D74" s="30" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E74" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F74" s="30" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G74" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F74),0)&gt;0), MAX($G$1:G73)+1, ""))</f>
@@ -3703,22 +3715,22 @@
         <v>20</v>
       </c>
       <c r="B75" s="31" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C75" s="32">
         <v>20</v>
       </c>
       <c r="D75" s="30" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="E75" s="31" t="s">
-        <v>305</v>
+        <v>8</v>
       </c>
       <c r="F75" s="30" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G75" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F75),0)&gt;0), MAX($G$1:G74)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F75),0)&gt;0), MAX($G$1:G73)+1, ""))</f>
         <v/>
       </c>
       <c r="H75" s="21" t="b">
@@ -3727,25 +3739,28 @@
       </c>
     </row>
     <row r="76" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A76" s="36">
+      <c r="A76" s="30">
         <v>20</v>
       </c>
-      <c r="B76" s="37" t="s">
-        <v>333</v>
-      </c>
-      <c r="C76" s="38">
+      <c r="B76" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="C76" s="32">
         <v>20</v>
       </c>
-      <c r="D76" s="36">
-        <v>3.4</v>
-      </c>
-      <c r="E76" s="37" t="s">
-        <v>336</v>
-      </c>
-      <c r="F76" s="36" t="s">
-        <v>334</v>
-      </c>
-      <c r="G76" s="29"/>
+      <c r="D76" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="E76" s="31" t="s">
+        <v>305</v>
+      </c>
+      <c r="F76" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="G76" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F76),0)&gt;0), MAX($G$1:G75)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H76" s="21" t="b">
         <f>A76=C76</f>
         <v>1</v>
@@ -3756,19 +3771,19 @@
         <v>20</v>
       </c>
       <c r="B77" s="37" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C77" s="38">
         <v>20</v>
       </c>
       <c r="D77" s="36">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="E77" s="37" t="s">
         <v>336</v>
       </c>
       <c r="F77" s="36" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G77" s="29"/>
       <c r="H77" s="21" t="b">
@@ -3777,28 +3792,25 @@
       </c>
     </row>
     <row r="78" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A78" s="30">
+      <c r="A78" s="36">
         <v>20</v>
       </c>
-      <c r="B78" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="C78" s="32">
+      <c r="B78" s="37" t="s">
+        <v>331</v>
+      </c>
+      <c r="C78" s="38">
         <v>20</v>
       </c>
-      <c r="D78" s="30" t="s">
-        <v>223</v>
-      </c>
-      <c r="E78" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F78" s="30" t="s">
-        <v>139</v>
-      </c>
-      <c r="G78" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F78),0)&gt;0), MAX($G$1:G77)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D78" s="36">
+        <v>3.3</v>
+      </c>
+      <c r="E78" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="F78" s="36" t="s">
+        <v>332</v>
+      </c>
+      <c r="G78" s="29"/>
       <c r="H78" s="21" t="b">
         <f>A78=C78</f>
         <v>1</v>
@@ -3809,19 +3821,19 @@
         <v>20</v>
       </c>
       <c r="B79" s="31" t="s">
-        <v>255</v>
+        <v>138</v>
       </c>
       <c r="C79" s="32">
         <v>20</v>
       </c>
       <c r="D79" s="30" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E79" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F79" s="30" t="s">
-        <v>256</v>
+        <v>139</v>
       </c>
       <c r="G79" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F79),0)&gt;0), MAX($G$1:G78)+1, ""))</f>
@@ -3837,19 +3849,19 @@
         <v>20</v>
       </c>
       <c r="B80" s="31" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C80" s="32">
         <v>20</v>
       </c>
-      <c r="D80" s="30">
-        <v>4.2</v>
+      <c r="D80" s="30" t="s">
+        <v>225</v>
       </c>
       <c r="E80" s="31" t="s">
-        <v>305</v>
-      </c>
-      <c r="F80" s="30">
-        <v>21765430</v>
+        <v>8</v>
+      </c>
+      <c r="F80" s="30" t="s">
+        <v>256</v>
       </c>
       <c r="G80" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F80),0)&gt;0), MAX($G$1:G79)+1, ""))</f>
@@ -3865,19 +3877,19 @@
         <v>20</v>
       </c>
       <c r="B81" s="31" t="s">
-        <v>136</v>
+        <v>254</v>
       </c>
       <c r="C81" s="32">
         <v>20</v>
       </c>
-      <c r="D81" s="30" t="s">
-        <v>210</v>
+      <c r="D81" s="30">
+        <v>4.2</v>
       </c>
       <c r="E81" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F81" s="30" t="s">
-        <v>137</v>
+        <v>305</v>
+      </c>
+      <c r="F81" s="30">
+        <v>21765430</v>
       </c>
       <c r="G81" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F81),0)&gt;0), MAX($G$1:G80)+1, ""))</f>
@@ -3893,19 +3905,19 @@
         <v>20</v>
       </c>
       <c r="B82" s="31" t="s">
-        <v>265</v>
+        <v>136</v>
       </c>
       <c r="C82" s="32">
         <v>20</v>
       </c>
       <c r="D82" s="30" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="E82" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F82" s="30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G82" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F82),0)&gt;0), MAX($G$1:G81)+1, ""))</f>
@@ -3921,19 +3933,19 @@
         <v>20</v>
       </c>
       <c r="B83" s="31" t="s">
-        <v>133</v>
+        <v>265</v>
       </c>
       <c r="C83" s="32">
         <v>20</v>
       </c>
       <c r="D83" s="30" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E83" s="31" t="s">
-        <v>305</v>
+        <v>8</v>
       </c>
       <c r="F83" s="30" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G83" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F83),0)&gt;0), MAX($G$1:G82)+1, ""))</f>
@@ -3949,19 +3961,19 @@
         <v>20</v>
       </c>
       <c r="B84" s="31" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C84" s="32">
         <v>20</v>
       </c>
       <c r="D84" s="30" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E84" s="31" t="s">
-        <v>131</v>
+        <v>305</v>
       </c>
       <c r="F84" s="30" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G84" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F84),0)&gt;0), MAX($G$1:G83)+1, ""))</f>
@@ -3973,23 +3985,23 @@
       </c>
     </row>
     <row r="85" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A85" s="26">
+      <c r="A85" s="30">
         <v>20</v>
       </c>
-      <c r="B85" s="27" t="s">
-        <v>312</v>
-      </c>
-      <c r="C85" s="28">
+      <c r="B85" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="C85" s="32">
         <v>20</v>
       </c>
-      <c r="D85" s="26">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="E85" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="F85" s="26" t="s">
-        <v>318</v>
+      <c r="D85" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="E85" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="F85" s="30" t="s">
+        <v>132</v>
       </c>
       <c r="G85" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F85),0)&gt;0), MAX($G$1:G84)+1, ""))</f>
@@ -4001,23 +4013,23 @@
       </c>
     </row>
     <row r="86" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A86" s="30">
+      <c r="A86" s="26">
         <v>20</v>
       </c>
-      <c r="B86" s="31" t="s">
-        <v>128</v>
-      </c>
-      <c r="C86" s="32">
+      <c r="B86" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="C86" s="28">
         <v>20</v>
       </c>
-      <c r="D86" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="E86" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F86" s="30" t="s">
-        <v>129</v>
+      <c r="D86" s="26">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E86" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F86" s="26" t="s">
+        <v>318</v>
       </c>
       <c r="G86" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F86),0)&gt;0), MAX($G$1:G85)+1, ""))</f>
@@ -4033,19 +4045,19 @@
         <v>20</v>
       </c>
       <c r="B87" s="31" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C87" s="32">
         <v>20</v>
       </c>
       <c r="D87" s="30" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="E87" s="31" t="s">
-        <v>305</v>
+        <v>8</v>
       </c>
       <c r="F87" s="30" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G87" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F87),0)&gt;0), MAX($G$1:G86)+1, ""))</f>
@@ -4057,23 +4069,23 @@
       </c>
     </row>
     <row r="88" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A88" s="26">
+      <c r="A88" s="30">
         <v>20</v>
       </c>
-      <c r="B88" s="27" t="s">
-        <v>350</v>
-      </c>
-      <c r="C88" s="28">
+      <c r="B88" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="C88" s="32">
         <v>20</v>
       </c>
-      <c r="D88" s="26">
-        <v>2.7</v>
-      </c>
-      <c r="E88" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="F88" s="26" t="s">
-        <v>353</v>
+      <c r="D88" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="E88" s="31" t="s">
+        <v>305</v>
+      </c>
+      <c r="F88" s="30" t="s">
+        <v>127</v>
       </c>
       <c r="G88" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F88),0)&gt;0), MAX($G$1:G87)+1, ""))</f>
@@ -4085,23 +4097,23 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A89" s="30">
+      <c r="A89" s="26">
         <v>20</v>
       </c>
-      <c r="B89" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="C89" s="32">
+      <c r="B89" s="27" t="s">
+        <v>350</v>
+      </c>
+      <c r="C89" s="28">
         <v>20</v>
       </c>
-      <c r="D89" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="E89" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F89" s="30" t="s">
-        <v>125</v>
+      <c r="D89" s="26">
+        <v>2.7</v>
+      </c>
+      <c r="E89" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="F89" s="26" t="s">
+        <v>353</v>
       </c>
       <c r="G89" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F89),0)&gt;0), MAX($G$1:G88)+1, ""))</f>
@@ -4117,19 +4129,19 @@
         <v>20</v>
       </c>
       <c r="B90" s="31" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C90" s="32">
         <v>20</v>
       </c>
       <c r="D90" s="30" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="E90" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F90" s="30" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G90" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F90),0)&gt;0), MAX($G$1:G89)+1, ""))</f>
@@ -4145,19 +4157,19 @@
         <v>20</v>
       </c>
       <c r="B91" s="31" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C91" s="32">
         <v>20</v>
       </c>
       <c r="D91" s="30" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="E91" s="31" t="s">
-        <v>305</v>
+        <v>8</v>
       </c>
       <c r="F91" s="30" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G91" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F91),0)&gt;0), MAX($G$1:G90)+1, ""))</f>
@@ -4173,19 +4185,19 @@
         <v>20</v>
       </c>
       <c r="B92" s="31" t="s">
-        <v>257</v>
+        <v>120</v>
       </c>
       <c r="C92" s="32">
         <v>20</v>
       </c>
       <c r="D92" s="30" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E92" s="31" t="s">
-        <v>8</v>
+        <v>305</v>
       </c>
       <c r="F92" s="30" t="s">
-        <v>258</v>
+        <v>121</v>
       </c>
       <c r="G92" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F92),0)&gt;0), MAX($G$1:G91)+1, ""))</f>
@@ -4201,19 +4213,19 @@
         <v>20</v>
       </c>
       <c r="B93" s="31" t="s">
-        <v>118</v>
+        <v>257</v>
       </c>
       <c r="C93" s="32">
         <v>20</v>
       </c>
       <c r="D93" s="30" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E93" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F93" s="30" t="s">
-        <v>119</v>
+        <v>258</v>
       </c>
       <c r="G93" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F93),0)&gt;0), MAX($G$1:G92)+1, ""))</f>
@@ -4229,19 +4241,19 @@
         <v>20</v>
       </c>
       <c r="B94" s="31" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C94" s="32">
         <v>20</v>
       </c>
       <c r="D94" s="30" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="E94" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F94" s="30" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G94" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F94),0)&gt;0), MAX($G$1:G93)+1, ""))</f>
@@ -4257,19 +4269,19 @@
         <v>20</v>
       </c>
       <c r="B95" s="31" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C95" s="32">
         <v>20</v>
       </c>
       <c r="D95" s="30" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E95" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F95" s="30" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G95" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F95),0)&gt;0), MAX($G$1:G94)+1, ""))</f>
@@ -4281,23 +4293,23 @@
       </c>
     </row>
     <row r="96" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A96" s="26">
+      <c r="A96" s="30">
         <v>20</v>
       </c>
-      <c r="B96" s="27" t="s">
-        <v>297</v>
-      </c>
-      <c r="C96" s="28">
+      <c r="B96" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="C96" s="32">
         <v>20</v>
       </c>
-      <c r="D96" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E96" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="F96" s="26" t="s">
-        <v>298</v>
+      <c r="D96" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="E96" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="30" t="s">
+        <v>115</v>
       </c>
       <c r="G96" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F96),0)&gt;0), MAX($G$1:G95)+1, ""))</f>
@@ -4309,23 +4321,23 @@
       </c>
     </row>
     <row r="97" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A97" s="30">
+      <c r="A97" s="26">
         <v>20</v>
       </c>
-      <c r="B97" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="C97" s="32">
+      <c r="B97" s="27" t="s">
+        <v>297</v>
+      </c>
+      <c r="C97" s="28">
         <v>20</v>
       </c>
-      <c r="D97" s="30" t="s">
-        <v>219</v>
-      </c>
-      <c r="E97" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F97" s="30" t="s">
-        <v>113</v>
+      <c r="D97" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E97" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="F97" s="26" t="s">
+        <v>298</v>
       </c>
       <c r="G97" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F97),0)&gt;0), MAX($G$1:G96)+1, ""))</f>
@@ -4341,19 +4353,19 @@
         <v>20</v>
       </c>
       <c r="B98" s="31" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C98" s="32">
         <v>20</v>
       </c>
       <c r="D98" s="30" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E98" s="31" t="s">
-        <v>299</v>
+        <v>8</v>
       </c>
       <c r="F98" s="30" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G98" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F98),0)&gt;0), MAX($G$1:G97)+1, ""))</f>
@@ -4369,19 +4381,19 @@
         <v>20</v>
       </c>
       <c r="B99" s="31" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C99" s="32">
         <v>20</v>
       </c>
       <c r="D99" s="30" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E99" s="31" t="s">
-        <v>8</v>
+        <v>299</v>
       </c>
       <c r="F99" s="30" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G99" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F99),0)&gt;0), MAX($G$1:G98)+1, ""))</f>
@@ -4393,76 +4405,76 @@
       </c>
     </row>
     <row r="100" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A100" s="36">
+      <c r="A100" s="30">
         <v>20</v>
       </c>
-      <c r="B100" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="C100" s="38">
+      <c r="B100" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="C100" s="32">
         <v>20</v>
       </c>
-      <c r="D100" s="36">
-        <v>3</v>
-      </c>
-      <c r="E100" s="37" t="s">
-        <v>304</v>
-      </c>
-      <c r="F100" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="G100" s="29"/>
+      <c r="D100" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="E100" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F100" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="G100" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F100),0)&gt;0), MAX($G$1:G99)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H100" s="21" t="b">
         <f>A100=C100</f>
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A101" s="26">
+      <c r="A101" s="36">
         <v>20</v>
       </c>
-      <c r="B101" s="27" t="s">
-        <v>302</v>
-      </c>
-      <c r="C101" s="28">
+      <c r="B101" s="37" t="s">
+        <v>330</v>
+      </c>
+      <c r="C101" s="38">
         <v>20</v>
       </c>
-      <c r="D101" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E101" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="F101" s="26" t="s">
-        <v>301</v>
-      </c>
-      <c r="G101" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F101),0)&gt;0), MAX($G$1:G100)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D101" s="36">
+        <v>3</v>
+      </c>
+      <c r="E101" s="37" t="s">
+        <v>304</v>
+      </c>
+      <c r="F101" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="G101" s="29"/>
       <c r="H101" s="21" t="b">
         <f>A101=C101</f>
         <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A102" s="30">
+      <c r="A102" s="26">
         <v>20</v>
       </c>
-      <c r="B102" s="31" t="s">
-        <v>103</v>
-      </c>
-      <c r="C102" s="32">
+      <c r="B102" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C102" s="28">
         <v>20</v>
       </c>
-      <c r="D102" s="30" t="s">
-        <v>214</v>
-      </c>
-      <c r="E102" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="F102" s="30" t="s">
-        <v>104</v>
+      <c r="D102" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E102" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="F102" s="26" t="s">
+        <v>301</v>
       </c>
       <c r="G102" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F102),0)&gt;0), MAX($G$1:G101)+1, ""))</f>
@@ -4474,23 +4486,23 @@
       </c>
     </row>
     <row r="103" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A103" s="26">
+      <c r="A103" s="30">
         <v>20</v>
       </c>
-      <c r="B103" s="27" t="s">
-        <v>339</v>
-      </c>
-      <c r="C103" s="28">
+      <c r="B103" s="31" t="s">
+        <v>369</v>
+      </c>
+      <c r="C103" s="32">
         <v>20</v>
       </c>
-      <c r="D103" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E103" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F103" s="26" t="s">
-        <v>344</v>
+      <c r="D103" s="30">
+        <v>2.4</v>
+      </c>
+      <c r="E103" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="F103" s="30" t="s">
+        <v>370</v>
       </c>
       <c r="G103" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F103),0)&gt;0), MAX($G$1:G102)+1, ""))</f>
@@ -4502,48 +4514,51 @@
       </c>
     </row>
     <row r="104" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A104" s="36">
+      <c r="A104" s="30">
         <v>20</v>
       </c>
-      <c r="B104" s="37" t="s">
-        <v>335</v>
-      </c>
-      <c r="C104" s="38">
+      <c r="B104" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="C104" s="32">
         <v>20</v>
       </c>
-      <c r="D104" s="36">
-        <v>3.2</v>
-      </c>
-      <c r="E104" s="37" t="s">
-        <v>336</v>
-      </c>
-      <c r="F104" s="36" t="s">
-        <v>332</v>
-      </c>
-      <c r="G104" s="29"/>
+      <c r="D104" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="E104" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="F104" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="G104" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F104),0)&gt;0), MAX($G$1:G103)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H104" s="21" t="b">
         <f>A104=C104</f>
         <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A105" s="30">
+      <c r="A105" s="26">
         <v>20</v>
       </c>
-      <c r="B105" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="C105" s="32">
+      <c r="B105" s="27" t="s">
+        <v>339</v>
+      </c>
+      <c r="C105" s="28">
         <v>20</v>
       </c>
-      <c r="D105" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E105" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F105" s="30" t="s">
-        <v>102</v>
+      <c r="D105" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E105" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F105" s="26" t="s">
+        <v>344</v>
       </c>
       <c r="G105" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F105),0)&gt;0), MAX($G$1:G104)+1, ""))</f>
@@ -4555,28 +4570,25 @@
       </c>
     </row>
     <row r="106" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A106" s="30">
+      <c r="A106" s="36">
         <v>20</v>
       </c>
-      <c r="B106" s="31" t="s">
-        <v>263</v>
-      </c>
-      <c r="C106" s="32">
+      <c r="B106" s="37" t="s">
+        <v>335</v>
+      </c>
+      <c r="C106" s="38">
         <v>20</v>
       </c>
-      <c r="D106" s="30">
-        <v>6.2</v>
-      </c>
-      <c r="E106" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F106" s="30" t="s">
-        <v>264</v>
-      </c>
-      <c r="G106" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F106),0)&gt;0), MAX($G$1:G105)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D106" s="36">
+        <v>3.2</v>
+      </c>
+      <c r="E106" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="F106" s="36" t="s">
+        <v>332</v>
+      </c>
+      <c r="G106" s="29"/>
       <c r="H106" s="21" t="b">
         <f>A106=C106</f>
         <v>1</v>
@@ -4587,19 +4599,19 @@
         <v>20</v>
       </c>
       <c r="B107" s="31" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C107" s="32">
         <v>20</v>
       </c>
       <c r="D107" s="30" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="E107" s="31" t="s">
-        <v>299</v>
+        <v>8</v>
       </c>
       <c r="F107" s="30" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G107" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F107),0)&gt;0), MAX($G$1:G106)+1, ""))</f>
@@ -4611,23 +4623,23 @@
       </c>
     </row>
     <row r="108" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A108" s="26">
+      <c r="A108" s="30">
         <v>20</v>
       </c>
-      <c r="B108" s="27" t="s">
-        <v>300</v>
-      </c>
-      <c r="C108" s="28">
+      <c r="B108" s="31" t="s">
+        <v>263</v>
+      </c>
+      <c r="C108" s="32">
         <v>20</v>
       </c>
-      <c r="D108" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E108" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="F108" s="26" t="s">
-        <v>301</v>
+      <c r="D108" s="30">
+        <v>6.2</v>
+      </c>
+      <c r="E108" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F108" s="30" t="s">
+        <v>264</v>
       </c>
       <c r="G108" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F108),0)&gt;0), MAX($G$1:G107)+1, ""))</f>
@@ -4643,19 +4655,19 @@
         <v>20</v>
       </c>
       <c r="B109" s="31" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C109" s="32">
         <v>20</v>
       </c>
       <c r="D109" s="30" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E109" s="31" t="s">
-        <v>8</v>
+        <v>299</v>
       </c>
       <c r="F109" s="30" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G109" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F109),0)&gt;0), MAX($G$1:G108)+1, ""))</f>
@@ -4671,7 +4683,7 @@
         <v>20</v>
       </c>
       <c r="B110" s="27" t="s">
-        <v>358</v>
+        <v>300</v>
       </c>
       <c r="C110" s="28">
         <v>20</v>
@@ -4680,10 +4692,10 @@
         <v>2.4</v>
       </c>
       <c r="E110" s="27" t="s">
-        <v>81</v>
+        <v>299</v>
       </c>
       <c r="F110" s="26" t="s">
-        <v>359</v>
+        <v>301</v>
       </c>
       <c r="G110" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F110),0)&gt;0), MAX($G$1:G109)+1, ""))</f>
@@ -4699,19 +4711,19 @@
         <v>20</v>
       </c>
       <c r="B111" s="31" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C111" s="32">
         <v>20</v>
       </c>
       <c r="D111" s="30" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E111" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F111" s="30" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G111" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F111),0)&gt;0), MAX($G$1:G110)+1, ""))</f>
@@ -4723,23 +4735,23 @@
       </c>
     </row>
     <row r="112" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A112" s="30">
+      <c r="A112" s="26">
         <v>20</v>
       </c>
-      <c r="B112" s="31" t="s">
-        <v>89</v>
-      </c>
-      <c r="C112" s="32">
+      <c r="B112" s="27" t="s">
+        <v>358</v>
+      </c>
+      <c r="C112" s="28">
         <v>20</v>
       </c>
-      <c r="D112" s="30" t="s">
-        <v>223</v>
-      </c>
-      <c r="E112" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F112" s="30" t="s">
-        <v>90</v>
+      <c r="D112" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E112" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F112" s="26" t="s">
+        <v>359</v>
       </c>
       <c r="G112" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F112),0)&gt;0), MAX($G$1:G111)+1, ""))</f>
@@ -4755,19 +4767,19 @@
         <v>20</v>
       </c>
       <c r="B113" s="31" t="s">
-        <v>290</v>
+        <v>91</v>
       </c>
       <c r="C113" s="32">
         <v>20</v>
       </c>
-      <c r="D113" s="30">
-        <v>1.8</v>
+      <c r="D113" s="30" t="s">
+        <v>218</v>
       </c>
       <c r="E113" s="31" t="s">
-        <v>291</v>
+        <v>8</v>
       </c>
       <c r="F113" s="30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G113" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F113),0)&gt;0), MAX($G$1:G112)+1, ""))</f>
@@ -4783,19 +4795,19 @@
         <v>20</v>
       </c>
       <c r="B114" s="31" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C114" s="32">
         <v>20</v>
       </c>
       <c r="D114" s="30" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E114" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F114" s="30" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G114" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F114),0)&gt;0), MAX($G$1:G113)+1, ""))</f>
@@ -4811,19 +4823,19 @@
         <v>20</v>
       </c>
       <c r="B115" s="31" t="s">
-        <v>85</v>
+        <v>290</v>
       </c>
       <c r="C115" s="32">
         <v>20</v>
       </c>
-      <c r="D115" s="30" t="s">
-        <v>220</v>
+      <c r="D115" s="30">
+        <v>1.8</v>
       </c>
       <c r="E115" s="31" t="s">
-        <v>8</v>
+        <v>291</v>
       </c>
       <c r="F115" s="30" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G115" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F115),0)&gt;0), MAX($G$1:G114)+1, ""))</f>
@@ -4839,19 +4851,19 @@
         <v>20</v>
       </c>
       <c r="B116" s="31" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C116" s="32">
         <v>20</v>
       </c>
       <c r="D116" s="30" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E116" s="31" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F116" s="30" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G116" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F116),0)&gt;0), MAX($G$1:G115)+1, ""))</f>
@@ -4867,19 +4879,19 @@
         <v>20</v>
       </c>
       <c r="B117" s="31" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C117" s="32">
         <v>20</v>
       </c>
       <c r="D117" s="30" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E117" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F117" s="30" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G117" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F117),0)&gt;0), MAX($G$1:G116)+1, ""))</f>
@@ -4895,19 +4907,19 @@
         <v>20</v>
       </c>
       <c r="B118" s="31" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C118" s="32">
         <v>20</v>
       </c>
       <c r="D118" s="30" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E118" s="31" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="F118" s="30" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G118" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F118),0)&gt;0), MAX($G$1:G117)+1, ""))</f>
@@ -4919,23 +4931,23 @@
       </c>
     </row>
     <row r="119" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A119" s="26">
-        <v>25</v>
-      </c>
-      <c r="B119" s="27" t="s">
-        <v>178</v>
-      </c>
-      <c r="C119" s="28">
-        <v>25</v>
-      </c>
-      <c r="D119" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="E119" s="27" t="s">
+      <c r="A119" s="30">
+        <v>20</v>
+      </c>
+      <c r="B119" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="C119" s="32">
+        <v>20</v>
+      </c>
+      <c r="D119" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="E119" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F119" s="26" t="s">
-        <v>179</v>
+      <c r="F119" s="30" t="s">
+        <v>79</v>
       </c>
       <c r="G119" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F119),0)&gt;0), MAX($G$1:G118)+1, ""))</f>
@@ -4947,23 +4959,23 @@
       </c>
     </row>
     <row r="120" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A120" s="26">
-        <v>25</v>
-      </c>
-      <c r="B120" s="27" t="s">
-        <v>176</v>
-      </c>
-      <c r="C120" s="28">
-        <v>25</v>
-      </c>
-      <c r="D120" s="26" t="s">
-        <v>237</v>
-      </c>
-      <c r="E120" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="F120" s="26" t="s">
-        <v>177</v>
+      <c r="A120" s="30">
+        <v>20</v>
+      </c>
+      <c r="B120" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="C120" s="32">
+        <v>20</v>
+      </c>
+      <c r="D120" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="E120" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F120" s="30" t="s">
+        <v>77</v>
       </c>
       <c r="G120" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F120),0)&gt;0), MAX($G$1:G119)+1, ""))</f>
@@ -4979,19 +4991,19 @@
         <v>25</v>
       </c>
       <c r="B121" s="27" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C121" s="28">
         <v>25</v>
       </c>
       <c r="D121" s="26" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="E121" s="27" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="F121" s="26" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="G121" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F121),0)&gt;0), MAX($G$1:G120)+1, ""))</f>
@@ -5007,19 +5019,19 @@
         <v>25</v>
       </c>
       <c r="B122" s="27" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C122" s="28">
         <v>25</v>
       </c>
       <c r="D122" s="26" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="E122" s="27" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F122" s="26" t="s">
-        <v>324</v>
+        <v>177</v>
       </c>
       <c r="G122" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F122),0)&gt;0), MAX($G$1:G121)+1, ""))</f>
@@ -5035,19 +5047,19 @@
         <v>25</v>
       </c>
       <c r="B123" s="27" t="s">
-        <v>362</v>
+        <v>174</v>
       </c>
       <c r="C123" s="28">
         <v>25</v>
       </c>
-      <c r="D123" s="26">
-        <v>3</v>
+      <c r="D123" s="26" t="s">
+        <v>231</v>
       </c>
       <c r="E123" s="27" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F123" s="26" t="s">
-        <v>363</v>
+        <v>175</v>
       </c>
       <c r="G123" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F123),0)&gt;0), MAX($G$1:G122)+1, ""))</f>
@@ -5063,19 +5075,19 @@
         <v>25</v>
       </c>
       <c r="B124" s="27" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C124" s="28">
         <v>25</v>
       </c>
-      <c r="D124" s="26">
-        <v>2.7</v>
+      <c r="D124" s="26" t="s">
+        <v>224</v>
       </c>
       <c r="E124" s="27" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F124" s="26" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="G124" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F124),0)&gt;0), MAX($G$1:G123)+1, ""))</f>
@@ -5087,23 +5099,23 @@
       </c>
     </row>
     <row r="125" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A125" s="30">
+      <c r="A125" s="26">
         <v>25</v>
       </c>
-      <c r="B125" s="31" t="s">
-        <v>284</v>
-      </c>
-      <c r="C125" s="32">
+      <c r="B125" s="27" t="s">
+        <v>362</v>
+      </c>
+      <c r="C125" s="28">
         <v>25</v>
       </c>
-      <c r="D125" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E125" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F125" s="30" t="s">
-        <v>102</v>
+      <c r="D125" s="26">
+        <v>3</v>
+      </c>
+      <c r="E125" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F125" s="26" t="s">
+        <v>363</v>
       </c>
       <c r="G125" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F125),0)&gt;0), MAX($G$1:G124)+1, ""))</f>
@@ -5115,23 +5127,23 @@
       </c>
     </row>
     <row r="126" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A126" s="30">
+      <c r="A126" s="26">
         <v>25</v>
       </c>
-      <c r="B126" s="31" t="s">
-        <v>282</v>
-      </c>
-      <c r="C126" s="32">
+      <c r="B126" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="C126" s="28">
         <v>25</v>
       </c>
-      <c r="D126" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E126" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F126" s="30" t="s">
-        <v>102</v>
+      <c r="D126" s="26">
+        <v>2.7</v>
+      </c>
+      <c r="E126" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F126" s="26" t="s">
+        <v>338</v>
       </c>
       <c r="G126" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F126),0)&gt;0), MAX($G$1:G125)+1, ""))</f>
@@ -5143,23 +5155,23 @@
       </c>
     </row>
     <row r="127" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A127" s="26">
+      <c r="A127" s="30">
         <v>25</v>
       </c>
-      <c r="B127" s="27" t="s">
-        <v>170</v>
-      </c>
-      <c r="C127" s="28">
+      <c r="B127" s="31" t="s">
+        <v>284</v>
+      </c>
+      <c r="C127" s="32">
         <v>25</v>
       </c>
-      <c r="D127" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="E127" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="F127" s="26" t="s">
-        <v>171</v>
+      <c r="D127" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E127" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="F127" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G127" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F127),0)&gt;0), MAX($G$1:G126)+1, ""))</f>
@@ -5171,23 +5183,23 @@
       </c>
     </row>
     <row r="128" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A128" s="26">
+      <c r="A128" s="30">
         <v>25</v>
       </c>
-      <c r="B128" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="C128" s="28">
+      <c r="B128" s="31" t="s">
+        <v>282</v>
+      </c>
+      <c r="C128" s="32">
         <v>25</v>
       </c>
-      <c r="D128" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="E128" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F128" s="26" t="s">
-        <v>169</v>
+      <c r="D128" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E128" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="F128" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G128" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F128),0)&gt;0), MAX($G$1:G127)+1, ""))</f>
@@ -5203,19 +5215,19 @@
         <v>25</v>
       </c>
       <c r="B129" s="27" t="s">
-        <v>360</v>
+        <v>170</v>
       </c>
       <c r="C129" s="28">
         <v>25</v>
       </c>
-      <c r="D129" s="26">
-        <v>3.4</v>
+      <c r="D129" s="26" t="s">
+        <v>234</v>
       </c>
       <c r="E129" s="27" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F129" s="26" t="s">
-        <v>361</v>
+        <v>171</v>
       </c>
       <c r="G129" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F129),0)&gt;0), MAX($G$1:G128)+1, ""))</f>
@@ -5227,23 +5239,23 @@
       </c>
     </row>
     <row r="130" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A130" s="30">
+      <c r="A130" s="26">
         <v>25</v>
       </c>
-      <c r="B130" s="31" t="s">
-        <v>278</v>
-      </c>
-      <c r="C130" s="32">
+      <c r="B130" s="27" t="s">
+        <v>168</v>
+      </c>
+      <c r="C130" s="28">
         <v>25</v>
       </c>
-      <c r="D130" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E130" s="31" t="s">
+      <c r="D130" s="26" t="s">
+        <v>217</v>
+      </c>
+      <c r="E130" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F130" s="30" t="s">
-        <v>102</v>
+      <c r="F130" s="26" t="s">
+        <v>169</v>
       </c>
       <c r="G130" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F130),0)&gt;0), MAX($G$1:G129)+1, ""))</f>
@@ -5259,19 +5271,19 @@
         <v>25</v>
       </c>
       <c r="B131" s="27" t="s">
-        <v>166</v>
+        <v>360</v>
       </c>
       <c r="C131" s="28">
         <v>25</v>
       </c>
-      <c r="D131" s="26" t="s">
-        <v>221</v>
+      <c r="D131" s="26">
+        <v>3.4</v>
       </c>
       <c r="E131" s="27" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="F131" s="26" t="s">
-        <v>167</v>
+        <v>361</v>
       </c>
       <c r="G131" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F131),0)&gt;0), MAX($G$1:G130)+1, ""))</f>
@@ -5283,23 +5295,23 @@
       </c>
     </row>
     <row r="132" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A132" s="26">
+      <c r="A132" s="30">
         <v>25</v>
       </c>
-      <c r="B132" s="27" t="s">
-        <v>164</v>
-      </c>
-      <c r="C132" s="28">
+      <c r="B132" s="31" t="s">
+        <v>278</v>
+      </c>
+      <c r="C132" s="32">
         <v>25</v>
       </c>
-      <c r="D132" s="26" t="s">
-        <v>229</v>
-      </c>
-      <c r="E132" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="F132" s="26" t="s">
-        <v>165</v>
+      <c r="D132" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E132" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F132" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G132" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B132),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E132),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F132),0)&gt;0), MAX($G$1:G131)+1, ""))</f>
@@ -5315,19 +5327,19 @@
         <v>25</v>
       </c>
       <c r="B133" s="27" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C133" s="28">
         <v>25</v>
       </c>
       <c r="D133" s="26" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="E133" s="27" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="F133" s="26" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="G133" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F133),0)&gt;0), MAX($G$1:G132)+1, ""))</f>
@@ -5343,19 +5355,19 @@
         <v>25</v>
       </c>
       <c r="B134" s="27" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C134" s="28">
         <v>25</v>
       </c>
       <c r="D134" s="26" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="E134" s="27" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="F134" s="26" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G134" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F134),0)&gt;0), MAX($G$1:G133)+1, ""))</f>
@@ -5371,19 +5383,19 @@
         <v>25</v>
       </c>
       <c r="B135" s="27" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C135" s="28">
         <v>25</v>
       </c>
       <c r="D135" s="26" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E135" s="27" t="s">
         <v>81</v>
       </c>
       <c r="F135" s="26" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="G135" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F135),0)&gt;0), MAX($G$1:G134)+1, ""))</f>
@@ -5399,19 +5411,19 @@
         <v>25</v>
       </c>
       <c r="B136" s="27" t="s">
-        <v>342</v>
+        <v>160</v>
       </c>
       <c r="C136" s="28">
         <v>25</v>
       </c>
-      <c r="D136" s="26">
-        <v>3.4</v>
+      <c r="D136" s="26" t="s">
+        <v>236</v>
       </c>
       <c r="E136" s="27" t="s">
         <v>81</v>
       </c>
       <c r="F136" s="26" t="s">
-        <v>343</v>
+        <v>161</v>
       </c>
       <c r="G136" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F136),0)&gt;0), MAX($G$1:G135)+1, ""))</f>
@@ -5427,22 +5439,22 @@
         <v>25</v>
       </c>
       <c r="B137" s="27" t="s">
-        <v>310</v>
+        <v>158</v>
       </c>
       <c r="C137" s="28">
         <v>25</v>
       </c>
-      <c r="D137" s="26">
-        <v>3.9</v>
+      <c r="D137" s="26" t="s">
+        <v>228</v>
       </c>
       <c r="E137" s="27" t="s">
-        <v>309</v>
+        <v>81</v>
       </c>
       <c r="F137" s="26" t="s">
-        <v>311</v>
+        <v>159</v>
       </c>
       <c r="G137" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F137),0)&gt;0), MAX($G$1:G135)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F137),0)&gt;0), MAX($G$1:G136)+1, ""))</f>
         <v/>
       </c>
       <c r="H137" s="21" t="b">
@@ -5455,19 +5467,19 @@
         <v>25</v>
       </c>
       <c r="B138" s="27" t="s">
-        <v>156</v>
+        <v>342</v>
       </c>
       <c r="C138" s="28">
         <v>25</v>
       </c>
-      <c r="D138" s="26" t="s">
-        <v>227</v>
+      <c r="D138" s="26">
+        <v>3.4</v>
       </c>
       <c r="E138" s="27" t="s">
         <v>81</v>
       </c>
       <c r="F138" s="26" t="s">
-        <v>157</v>
+        <v>343</v>
       </c>
       <c r="G138" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F138),0)&gt;0), MAX($G$1:G137)+1, ""))</f>
@@ -5483,22 +5495,22 @@
         <v>25</v>
       </c>
       <c r="B139" s="27" t="s">
-        <v>154</v>
+        <v>310</v>
       </c>
       <c r="C139" s="28">
         <v>25</v>
       </c>
-      <c r="D139" s="26" t="s">
-        <v>224</v>
+      <c r="D139" s="26">
+        <v>3.9</v>
       </c>
       <c r="E139" s="27" t="s">
-        <v>8</v>
+        <v>309</v>
       </c>
       <c r="F139" s="26" t="s">
-        <v>155</v>
+        <v>311</v>
       </c>
       <c r="G139" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F139),0)&gt;0), MAX($G$1:G138)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F139),0)&gt;0), MAX($G$1:G137)+1, ""))</f>
         <v/>
       </c>
       <c r="H139" s="21" t="b">
@@ -5511,19 +5523,19 @@
         <v>25</v>
       </c>
       <c r="B140" s="27" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C140" s="28">
         <v>25</v>
       </c>
       <c r="D140" s="26" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E140" s="27" t="s">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="F140" s="26" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G140" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F140),0)&gt;0), MAX($G$1:G139)+1, ""))</f>
@@ -5539,19 +5551,19 @@
         <v>25</v>
       </c>
       <c r="B141" s="27" t="s">
-        <v>247</v>
+        <v>154</v>
       </c>
       <c r="C141" s="28">
         <v>25</v>
       </c>
-      <c r="D141" s="39" t="s">
-        <v>229</v>
+      <c r="D141" s="26" t="s">
+        <v>224</v>
       </c>
       <c r="E141" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F141" s="26" t="s">
-        <v>248</v>
+        <v>155</v>
       </c>
       <c r="G141" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F141),0)&gt;0), MAX($G$1:G140)+1, ""))</f>
@@ -5567,19 +5579,19 @@
         <v>25</v>
       </c>
       <c r="B142" s="27" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C142" s="28">
         <v>25</v>
       </c>
       <c r="D142" s="26" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="E142" s="27" t="s">
         <v>131</v>
       </c>
       <c r="F142" s="26" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G142" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F142),0)&gt;0), MAX($G$1:G141)+1, ""))</f>
@@ -5591,23 +5603,23 @@
       </c>
     </row>
     <row r="143" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A143" s="30">
+      <c r="A143" s="26">
         <v>25</v>
       </c>
-      <c r="B143" s="31" t="s">
-        <v>288</v>
-      </c>
-      <c r="C143" s="32">
+      <c r="B143" s="27" t="s">
+        <v>247</v>
+      </c>
+      <c r="C143" s="28">
         <v>25</v>
       </c>
-      <c r="D143" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E143" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F143" s="30" t="s">
-        <v>102</v>
+      <c r="D143" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="E143" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F143" s="26" t="s">
+        <v>248</v>
       </c>
       <c r="G143" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F143),0)&gt;0), MAX($G$1:G142)+1, ""))</f>
@@ -5619,23 +5631,23 @@
       </c>
     </row>
     <row r="144" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A144" s="30">
+      <c r="A144" s="26">
         <v>25</v>
       </c>
-      <c r="B144" s="31" t="s">
-        <v>286</v>
-      </c>
-      <c r="C144" s="32">
+      <c r="B144" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C144" s="28">
         <v>25</v>
       </c>
-      <c r="D144" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E144" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F144" s="30" t="s">
-        <v>102</v>
+      <c r="D144" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="E144" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="F144" s="26" t="s">
+        <v>151</v>
       </c>
       <c r="G144" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F144),0)&gt;0), MAX($G$1:G143)+1, ""))</f>
@@ -5651,7 +5663,7 @@
         <v>25</v>
       </c>
       <c r="B145" s="31" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C145" s="32">
         <v>25</v>
@@ -5675,23 +5687,23 @@
       </c>
     </row>
     <row r="146" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A146" s="26">
+      <c r="A146" s="30">
         <v>25</v>
       </c>
-      <c r="B146" s="27" t="s">
-        <v>252</v>
-      </c>
-      <c r="C146" s="28">
+      <c r="B146" s="31" t="s">
+        <v>286</v>
+      </c>
+      <c r="C146" s="32">
         <v>25</v>
       </c>
-      <c r="D146" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E146" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="F146" s="26" t="s">
-        <v>253</v>
+      <c r="D146" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E146" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="F146" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G146" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F146),0)&gt;0), MAX($G$1:G145)+1, ""))</f>
@@ -5707,7 +5719,7 @@
         <v>25</v>
       </c>
       <c r="B147" s="31" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C147" s="32">
         <v>25</v>
@@ -5735,22 +5747,22 @@
         <v>25</v>
       </c>
       <c r="B148" s="27" t="s">
-        <v>148</v>
+        <v>252</v>
       </c>
       <c r="C148" s="28">
         <v>25</v>
       </c>
-      <c r="D148" s="26" t="s">
-        <v>226</v>
+      <c r="D148" s="26">
+        <v>2.5</v>
       </c>
       <c r="E148" s="27" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="F148" s="26" t="s">
-        <v>149</v>
+        <v>253</v>
       </c>
       <c r="G148" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F148),0)&gt;0), MAX($G$1:G146)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F148),0)&gt;0), MAX($G$1:G147)+1, ""))</f>
         <v/>
       </c>
       <c r="H148" s="21" t="b">
@@ -5760,22 +5772,22 @@
     </row>
     <row r="149" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A149" s="30">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B149" s="31" t="s">
-        <v>192</v>
+        <v>285</v>
       </c>
       <c r="C149" s="32">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D149" s="30" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="E149" s="31" t="s">
-        <v>131</v>
+        <v>283</v>
       </c>
       <c r="F149" s="30" t="s">
-        <v>193</v>
+        <v>102</v>
       </c>
       <c r="G149" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B149),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E149),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F149),0)&gt;0), MAX($G$1:G148)+1, ""))</f>
@@ -5787,26 +5799,26 @@
       </c>
     </row>
     <row r="150" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A150" s="30">
-        <v>30</v>
-      </c>
-      <c r="B150" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="C150" s="32">
-        <v>30</v>
-      </c>
-      <c r="D150" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="E150" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="F150" s="30" t="s">
-        <v>190</v>
+      <c r="A150" s="26">
+        <v>25</v>
+      </c>
+      <c r="B150" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="C150" s="28">
+        <v>25</v>
+      </c>
+      <c r="D150" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="E150" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F150" s="26" t="s">
+        <v>149</v>
       </c>
       <c r="G150" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B150),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E150),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F150),0)&gt;0), MAX($G$1:G149)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B150),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E150),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F150),0)&gt;0), MAX($G$1:G148)+1, ""))</f>
         <v/>
       </c>
       <c r="H150" s="21" t="b">
@@ -5819,19 +5831,19 @@
         <v>30</v>
       </c>
       <c r="B151" s="31" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C151" s="32">
         <v>30</v>
       </c>
       <c r="D151" s="30" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="E151" s="31" t="s">
         <v>131</v>
       </c>
       <c r="F151" s="30" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="G151" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B151),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E151),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F151),0)&gt;0), MAX($G$1:G150)+1, ""))</f>
@@ -5847,19 +5859,19 @@
         <v>30</v>
       </c>
       <c r="B152" s="31" t="s">
-        <v>246</v>
+        <v>191</v>
       </c>
       <c r="C152" s="32">
         <v>30</v>
       </c>
       <c r="D152" s="30" t="s">
-        <v>217</v>
+        <v>241</v>
       </c>
       <c r="E152" s="31" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F152" s="30" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G152" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B152),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E152),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F152),0)&gt;0), MAX($G$1:G151)+1, ""))</f>
@@ -5875,19 +5887,19 @@
         <v>30</v>
       </c>
       <c r="B153" s="31" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C153" s="32">
         <v>30</v>
       </c>
       <c r="D153" s="30" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="E153" s="31" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F153" s="30" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G153" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B153),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E153),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F153),0)&gt;0), MAX($G$1:G152)+1, ""))</f>
@@ -5903,19 +5915,19 @@
         <v>30</v>
       </c>
       <c r="B154" s="31" t="s">
-        <v>184</v>
+        <v>246</v>
       </c>
       <c r="C154" s="32">
         <v>30</v>
       </c>
       <c r="D154" s="30" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="E154" s="31" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F154" s="30" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G154" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B154),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E154),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F154),0)&gt;0), MAX($G$1:G153)+1, ""))</f>
@@ -5931,19 +5943,19 @@
         <v>30</v>
       </c>
       <c r="B155" s="31" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C155" s="32">
         <v>30</v>
       </c>
       <c r="D155" s="30" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="E155" s="31" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="F155" s="30" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="G155" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F155),0)&gt;0), MAX($G$1:G154)+1, ""))</f>
@@ -5959,19 +5971,19 @@
         <v>30</v>
       </c>
       <c r="B156" s="31" t="s">
-        <v>337</v>
+        <v>184</v>
       </c>
       <c r="C156" s="32">
         <v>30</v>
       </c>
-      <c r="D156" s="30">
-        <v>2.9</v>
+      <c r="D156" s="30" t="s">
+        <v>228</v>
       </c>
       <c r="E156" s="31" t="s">
         <v>81</v>
       </c>
       <c r="F156" s="30" t="s">
-        <v>338</v>
+        <v>185</v>
       </c>
       <c r="G156" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B156),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E156),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F156),0)&gt;0), MAX($G$1:G155)+1, ""))</f>
@@ -5987,22 +5999,22 @@
         <v>30</v>
       </c>
       <c r="B157" s="31" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C157" s="32">
         <v>30</v>
       </c>
       <c r="D157" s="30" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E157" s="31" t="s">
         <v>131</v>
       </c>
       <c r="F157" s="30" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G157" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F157),0)&gt;0), MAX($G$1:G155)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F157),0)&gt;0), MAX($G$1:G156)+1, ""))</f>
         <v/>
       </c>
       <c r="H157" s="21" t="b">
@@ -6011,23 +6023,23 @@
       </c>
     </row>
     <row r="158" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A158" s="26">
-        <v>40</v>
-      </c>
-      <c r="B158" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="C158" s="28">
-        <v>40</v>
-      </c>
-      <c r="D158" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="E158" s="27" t="s">
-        <v>198</v>
-      </c>
-      <c r="F158" s="26" t="s">
-        <v>199</v>
+      <c r="A158" s="30">
+        <v>30</v>
+      </c>
+      <c r="B158" s="31" t="s">
+        <v>337</v>
+      </c>
+      <c r="C158" s="32">
+        <v>30</v>
+      </c>
+      <c r="D158" s="30">
+        <v>2.9</v>
+      </c>
+      <c r="E158" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="F158" s="30" t="s">
+        <v>338</v>
       </c>
       <c r="G158" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B158),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E158),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F158),0)&gt;0), MAX($G$1:G157)+1, ""))</f>
@@ -6039,26 +6051,26 @@
       </c>
     </row>
     <row r="159" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A159" s="26">
-        <v>40</v>
-      </c>
-      <c r="B159" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="C159" s="28">
-        <v>40</v>
-      </c>
-      <c r="D159" s="26" t="s">
-        <v>242</v>
-      </c>
-      <c r="E159" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="F159" s="26" t="s">
-        <v>196</v>
+      <c r="A159" s="30">
+        <v>30</v>
+      </c>
+      <c r="B159" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="C159" s="32">
+        <v>30</v>
+      </c>
+      <c r="D159" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="E159" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="F159" s="30" t="s">
+        <v>181</v>
       </c>
       <c r="G159" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F159),0)&gt;0), MAX($G$1:G158)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F159),0)&gt;0), MAX($G$1:G157)+1, ""))</f>
         <v/>
       </c>
       <c r="H159" s="21" t="b">
@@ -6071,19 +6083,19 @@
         <v>40</v>
       </c>
       <c r="B160" s="27" t="s">
-        <v>249</v>
+        <v>197</v>
       </c>
       <c r="C160" s="28">
         <v>40</v>
       </c>
-      <c r="D160" s="26">
-        <v>8.3000000000000007</v>
+      <c r="D160" s="26" t="s">
+        <v>243</v>
       </c>
       <c r="E160" s="27" t="s">
-        <v>250</v>
+        <v>198</v>
       </c>
       <c r="F160" s="26" t="s">
-        <v>251</v>
+        <v>199</v>
       </c>
       <c r="G160" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B160),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E160),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F160),0)&gt;0), MAX($G$1:G159)+1, ""))</f>
@@ -6096,22 +6108,22 @@
     </row>
     <row r="161" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A161" s="26">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B161" s="27" t="s">
-        <v>294</v>
+        <v>194</v>
       </c>
       <c r="C161" s="28">
-        <v>45</v>
-      </c>
-      <c r="D161" s="26">
-        <v>10.199999999999999</v>
+        <v>40</v>
+      </c>
+      <c r="D161" s="26" t="s">
+        <v>242</v>
       </c>
       <c r="E161" s="27" t="s">
-        <v>295</v>
+        <v>195</v>
       </c>
       <c r="F161" s="26" t="s">
-        <v>296</v>
+        <v>196</v>
       </c>
       <c r="G161" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B161),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E161),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F161),0)&gt;0), MAX($G$1:G160)+1, ""))</f>
@@ -6123,16 +6135,60 @@
       </c>
     </row>
     <row r="162" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A162" s="1"/>
-      <c r="C162" s="1"/>
-      <c r="D162" s="1"/>
-      <c r="F162" s="1"/>
+      <c r="A162" s="26">
+        <v>40</v>
+      </c>
+      <c r="B162" s="27" t="s">
+        <v>249</v>
+      </c>
+      <c r="C162" s="28">
+        <v>40</v>
+      </c>
+      <c r="D162" s="26">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E162" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="F162" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="G162" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B162),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E162),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F162),0)&gt;0), MAX($G$1:G161)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H162" s="21" t="b">
+        <f>A162=C162</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="163" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A163" s="1"/>
-      <c r="C163" s="1"/>
-      <c r="D163" s="1"/>
-      <c r="F163" s="1"/>
+      <c r="A163" s="26">
+        <v>45</v>
+      </c>
+      <c r="B163" s="27" t="s">
+        <v>294</v>
+      </c>
+      <c r="C163" s="28">
+        <v>45</v>
+      </c>
+      <c r="D163" s="26">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E163" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="F163" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="G163" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B163),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E163),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F163),0)&gt;0), MAX($G$1:G162)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H163" s="21" t="b">
+        <f>A163=C163</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="164" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
@@ -11378,18 +11434,30 @@
       <c r="D1037" s="1"/>
       <c r="F1037" s="1"/>
     </row>
+    <row r="1038" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1038" s="1"/>
+      <c r="C1038" s="1"/>
+      <c r="D1038" s="1"/>
+      <c r="F1038" s="1"/>
+    </row>
+    <row r="1039" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1039" s="1"/>
+      <c r="C1039" s="1"/>
+      <c r="D1039" s="1"/>
+      <c r="F1039" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H149">
+  <autoFilter ref="A1:H151">
     <sortState ref="A2:H147">
       <sortCondition ref="A2:A147"/>
       <sortCondition ref="B2:B147"/>
       <sortCondition ref="D2:D147"/>
     </sortState>
   </autoFilter>
-  <sortState ref="A2:H161">
-    <sortCondition ref="A2:A161"/>
-    <sortCondition ref="B2:B161"/>
-    <sortCondition ref="D2:D161"/>
+  <sortState ref="A2:H163">
+    <sortCondition ref="A2:A163"/>
+    <sortCondition ref="B2:B163"/>
+    <sortCondition ref="D2:D163"/>
   </sortState>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Consulta" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$163</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$138</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Base!$1:$1</definedName>
   </definedNames>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="373">
   <si>
     <t>Grupo</t>
   </si>
@@ -1095,9 +1095,6 @@
     <t>21721-280</t>
   </si>
   <si>
-    <t>MOEMA</t>
-  </si>
-  <si>
     <t>21710-370</t>
   </si>
   <si>
@@ -1138,6 +1135,15 @@
   </si>
   <si>
     <t>21750-001</t>
+  </si>
+  <si>
+    <t>MACACOLANDIAf</t>
+  </si>
+  <si>
+    <t>HELIANTO</t>
+  </si>
+  <si>
+    <t>21775-090</t>
   </si>
 </sst>
 </file>
@@ -1713,7 +1719,7 @@
         <v/>
       </c>
       <c r="H2" s="21" t="b">
-        <f>A2=C2</f>
+        <f t="shared" ref="H2:H33" si="0">A2=C2</f>
         <v>1</v>
       </c>
     </row>
@@ -1722,7 +1728,7 @@
         <v>13</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C3" s="28">
         <v>13</v>
@@ -1741,7 +1747,7 @@
         <v/>
       </c>
       <c r="H3" s="21" t="b">
-        <f>A3=C3</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1769,7 +1775,7 @@
         <v/>
       </c>
       <c r="H4" s="21" t="b">
-        <f>A4=C4</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1797,7 +1803,7 @@
         <v/>
       </c>
       <c r="H5" s="21" t="b">
-        <f>A5=C5</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1825,7 +1831,7 @@
         <v/>
       </c>
       <c r="H6" s="21" t="b">
-        <f>A6=C6</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1853,7 +1859,7 @@
         <v/>
       </c>
       <c r="H7" s="21" t="b">
-        <f>A7=C7</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1881,7 +1887,7 @@
         <v/>
       </c>
       <c r="H8" s="21" t="b">
-        <f>A8=C8</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1909,7 +1915,7 @@
         <v/>
       </c>
       <c r="H9" s="21" t="b">
-        <f>A9=C9</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1937,7 +1943,7 @@
         <v/>
       </c>
       <c r="H10" s="21" t="b">
-        <f>A10=C10</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1965,7 +1971,7 @@
         <v/>
       </c>
       <c r="H11" s="21" t="b">
-        <f>A11=C11</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1993,7 +1999,7 @@
         <v/>
       </c>
       <c r="H12" s="21" t="b">
-        <f>A12=C12</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2002,7 +2008,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C13" s="32">
         <v>13</v>
@@ -2021,7 +2027,7 @@
         <v/>
       </c>
       <c r="H13" s="21" t="b">
-        <f>A13=C13</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2049,7 +2055,7 @@
         <v/>
       </c>
       <c r="H14" s="21" t="b">
-        <f>A14=C14</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2058,7 +2064,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C15" s="32">
         <v>13</v>
@@ -2070,14 +2076,14 @@
         <v>8</v>
       </c>
       <c r="F15" s="30" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G15" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B15),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E15),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F15),0)&gt;0), MAX($G$1:G14)+1, ""))</f>
         <v/>
       </c>
       <c r="H15" s="21" t="b">
-        <f>A15=C15</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2105,7 +2111,7 @@
         <v/>
       </c>
       <c r="H16" s="21" t="b">
-        <f>A16=C16</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2133,7 +2139,7 @@
         <v/>
       </c>
       <c r="H17" s="21" t="b">
-        <f>A17=C17</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2161,7 +2167,7 @@
         <v/>
       </c>
       <c r="H18" s="21" t="b">
-        <f>A18=C18</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2189,7 +2195,7 @@
         <v/>
       </c>
       <c r="H19" s="21" t="b">
-        <f>A19=C19</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2217,7 +2223,7 @@
         <v/>
       </c>
       <c r="H20" s="21" t="b">
-        <f>A20=C20</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2245,7 +2251,7 @@
         <v/>
       </c>
       <c r="H21" s="21" t="b">
-        <f>A21=C21</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2254,7 +2260,7 @@
         <v>15</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C22" s="28">
         <v>15</v>
@@ -2273,7 +2279,7 @@
         <v/>
       </c>
       <c r="H22" s="21" t="b">
-        <f>A22=C22</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2301,7 +2307,7 @@
         <v/>
       </c>
       <c r="H23" s="21" t="b">
-        <f>A23=C23</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2329,7 +2335,7 @@
         <v/>
       </c>
       <c r="H24" s="21" t="b">
-        <f>A24=C24</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2357,7 +2363,7 @@
         <v/>
       </c>
       <c r="H25" s="21" t="b">
-        <f>A25=C25</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2385,7 +2391,7 @@
         <v/>
       </c>
       <c r="H26" s="21" t="b">
-        <f>A26=C26</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2413,7 +2419,7 @@
         <v/>
       </c>
       <c r="H27" s="21" t="b">
-        <f>A27=C27</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2441,7 +2447,7 @@
         <v/>
       </c>
       <c r="H28" s="21" t="b">
-        <f>A28=C28</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2469,7 +2475,7 @@
         <v/>
       </c>
       <c r="H29" s="21" t="b">
-        <f>A29=C29</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2497,7 +2503,7 @@
         <v/>
       </c>
       <c r="H30" s="21" t="b">
-        <f>A30=C30</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2525,7 +2531,7 @@
         <v/>
       </c>
       <c r="H31" s="21" t="b">
-        <f>A31=C31</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2553,7 +2559,7 @@
         <v/>
       </c>
       <c r="H32" s="21" t="b">
-        <f>A32=C32</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2581,7 +2587,7 @@
         <v/>
       </c>
       <c r="H33" s="21" t="b">
-        <f>A33=C33</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2609,7 +2615,7 @@
         <v/>
       </c>
       <c r="H34" s="21" t="b">
-        <f>A34=C34</f>
+        <f t="shared" ref="H34:H65" si="1">A34=C34</f>
         <v>1</v>
       </c>
     </row>
@@ -2637,7 +2643,7 @@
         <v/>
       </c>
       <c r="H35" s="21" t="b">
-        <f>A35=C35</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2665,7 +2671,7 @@
         <v/>
       </c>
       <c r="H36" s="21" t="b">
-        <f>A36=C36</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2693,7 +2699,7 @@
         <v/>
       </c>
       <c r="H37" s="21" t="b">
-        <f>A37=C37</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2721,7 +2727,7 @@
         <v/>
       </c>
       <c r="H38" s="21" t="b">
-        <f>A38=C38</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2749,7 +2755,7 @@
         <v/>
       </c>
       <c r="H39" s="21" t="b">
-        <f>A39=C39</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2777,7 +2783,7 @@
         <v/>
       </c>
       <c r="H40" s="21" t="b">
-        <f>A40=C40</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2805,7 +2811,7 @@
         <v/>
       </c>
       <c r="H41" s="21" t="b">
-        <f>A41=C41</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2833,7 +2839,7 @@
         <v/>
       </c>
       <c r="H42" s="21" t="b">
-        <f>A42=C42</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2861,7 +2867,7 @@
         <v/>
       </c>
       <c r="H43" s="21" t="b">
-        <f>A43=C43</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2889,7 +2895,7 @@
         <v/>
       </c>
       <c r="H44" s="21" t="b">
-        <f>A44=C44</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2917,7 +2923,7 @@
         <v/>
       </c>
       <c r="H45" s="21" t="b">
-        <f>A45=C45</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2945,7 +2951,7 @@
         <v/>
       </c>
       <c r="H46" s="21" t="b">
-        <f>A46=C46</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2973,7 +2979,7 @@
         <v/>
       </c>
       <c r="H47" s="21" t="b">
-        <f>A47=C47</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3001,7 +3007,7 @@
         <v/>
       </c>
       <c r="H48" s="21" t="b">
-        <f>A48=C48</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3029,7 +3035,7 @@
         <v/>
       </c>
       <c r="H49" s="21" t="b">
-        <f>A49=C49</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3054,7 +3060,7 @@
       </c>
       <c r="G50" s="29"/>
       <c r="H50" s="21" t="b">
-        <f>A50=C50</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3082,7 +3088,7 @@
         <v/>
       </c>
       <c r="H51" s="21" t="b">
-        <f>A51=C51</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3110,7 +3116,7 @@
         <v/>
       </c>
       <c r="H52" s="21" t="b">
-        <f>A52=C52</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3135,7 +3141,7 @@
       </c>
       <c r="G53" s="29"/>
       <c r="H53" s="21" t="b">
-        <f>A53=C53</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3163,7 +3169,7 @@
         <v/>
       </c>
       <c r="H54" s="21" t="b">
-        <f>A54=C54</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3188,7 +3194,7 @@
       </c>
       <c r="G55" s="29"/>
       <c r="H55" s="21" t="b">
-        <f>A55=C55</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3216,7 +3222,7 @@
         <v/>
       </c>
       <c r="H56" s="21" t="b">
-        <f>A56=C56</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3241,7 +3247,7 @@
       </c>
       <c r="G57" s="29"/>
       <c r="H57" s="21" t="b">
-        <f>A57=C57</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3266,7 +3272,7 @@
       </c>
       <c r="G58" s="29"/>
       <c r="H58" s="21" t="b">
-        <f>A58=C58</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3294,7 +3300,7 @@
         <v/>
       </c>
       <c r="H59" s="21" t="b">
-        <f>A59=C59</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3322,7 +3328,7 @@
         <v/>
       </c>
       <c r="H60" s="21" t="b">
-        <f>A60=C60</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3350,7 +3356,7 @@
         <v/>
       </c>
       <c r="H61" s="21" t="b">
-        <f>A61=C61</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3359,7 +3365,7 @@
         <v>17</v>
       </c>
       <c r="B62" s="27" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="C62" s="28">
         <v>17</v>
@@ -3371,14 +3377,14 @@
         <v>8</v>
       </c>
       <c r="F62" s="26" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G62" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F62),0)&gt;0), MAX($G$1:G61)+1, ""))</f>
         <v/>
       </c>
       <c r="H62" s="21" t="b">
-        <f>A62=C62</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3406,7 +3412,7 @@
         <v/>
       </c>
       <c r="H63" s="21" t="b">
-        <f>A63=C63</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3434,7 +3440,7 @@
         <v/>
       </c>
       <c r="H64" s="21" t="b">
-        <f>A64=C64</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3462,7 +3468,7 @@
         <v/>
       </c>
       <c r="H65" s="21" t="b">
-        <f>A65=C65</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -3678,7 +3684,7 @@
         <v/>
       </c>
       <c r="H73" s="21" t="b">
-        <f>A73=C73</f>
+        <f t="shared" ref="H73:H104" si="2">A73=C73</f>
         <v>1</v>
       </c>
     </row>
@@ -3706,7 +3712,7 @@
         <v/>
       </c>
       <c r="H74" s="21" t="b">
-        <f>A74=C74</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3734,7 +3740,7 @@
         <v/>
       </c>
       <c r="H75" s="21" t="b">
-        <f>A75=C75</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3762,7 +3768,7 @@
         <v/>
       </c>
       <c r="H76" s="21" t="b">
-        <f>A76=C76</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3787,7 +3793,7 @@
       </c>
       <c r="G77" s="29"/>
       <c r="H77" s="21" t="b">
-        <f>A77=C77</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3812,7 +3818,7 @@
       </c>
       <c r="G78" s="29"/>
       <c r="H78" s="21" t="b">
-        <f>A78=C78</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3840,7 +3846,7 @@
         <v/>
       </c>
       <c r="H79" s="21" t="b">
-        <f>A79=C79</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3868,7 +3874,7 @@
         <v/>
       </c>
       <c r="H80" s="21" t="b">
-        <f>A80=C80</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3896,7 +3902,7 @@
         <v/>
       </c>
       <c r="H81" s="21" t="b">
-        <f>A81=C81</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3924,7 +3930,7 @@
         <v/>
       </c>
       <c r="H82" s="21" t="b">
-        <f>A82=C82</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3952,7 +3958,7 @@
         <v/>
       </c>
       <c r="H83" s="21" t="b">
-        <f>A83=C83</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -3980,7 +3986,7 @@
         <v/>
       </c>
       <c r="H84" s="21" t="b">
-        <f>A84=C84</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4008,7 +4014,7 @@
         <v/>
       </c>
       <c r="H85" s="21" t="b">
-        <f>A85=C85</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4036,7 +4042,7 @@
         <v/>
       </c>
       <c r="H86" s="21" t="b">
-        <f>A86=C86</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4064,7 +4070,7 @@
         <v/>
       </c>
       <c r="H87" s="21" t="b">
-        <f>A87=C87</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4092,7 +4098,7 @@
         <v/>
       </c>
       <c r="H88" s="21" t="b">
-        <f>A88=C88</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4120,7 +4126,7 @@
         <v/>
       </c>
       <c r="H89" s="21" t="b">
-        <f>A89=C89</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4148,7 +4154,7 @@
         <v/>
       </c>
       <c r="H90" s="21" t="b">
-        <f>A90=C90</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4176,7 +4182,7 @@
         <v/>
       </c>
       <c r="H91" s="21" t="b">
-        <f>A91=C91</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4204,7 +4210,7 @@
         <v/>
       </c>
       <c r="H92" s="21" t="b">
-        <f>A92=C92</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4232,7 +4238,7 @@
         <v/>
       </c>
       <c r="H93" s="21" t="b">
-        <f>A93=C93</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4260,7 +4266,7 @@
         <v/>
       </c>
       <c r="H94" s="21" t="b">
-        <f>A94=C94</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4288,7 +4294,7 @@
         <v/>
       </c>
       <c r="H95" s="21" t="b">
-        <f>A95=C95</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4316,7 +4322,7 @@
         <v/>
       </c>
       <c r="H96" s="21" t="b">
-        <f>A96=C96</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4344,7 +4350,7 @@
         <v/>
       </c>
       <c r="H97" s="21" t="b">
-        <f>A97=C97</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4372,7 +4378,7 @@
         <v/>
       </c>
       <c r="H98" s="21" t="b">
-        <f>A98=C98</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4400,7 +4406,7 @@
         <v/>
       </c>
       <c r="H99" s="21" t="b">
-        <f>A99=C99</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4428,7 +4434,7 @@
         <v/>
       </c>
       <c r="H100" s="21" t="b">
-        <f>A100=C100</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4453,7 +4459,7 @@
       </c>
       <c r="G101" s="29"/>
       <c r="H101" s="21" t="b">
-        <f>A101=C101</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4481,7 +4487,7 @@
         <v/>
       </c>
       <c r="H102" s="21" t="b">
-        <f>A102=C102</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4490,7 +4496,7 @@
         <v>20</v>
       </c>
       <c r="B103" s="31" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C103" s="32">
         <v>20</v>
@@ -4502,14 +4508,14 @@
         <v>60</v>
       </c>
       <c r="F103" s="30" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G103" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F103),0)&gt;0), MAX($G$1:G102)+1, ""))</f>
         <v/>
       </c>
       <c r="H103" s="21" t="b">
-        <f>A103=C103</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4537,7 +4543,7 @@
         <v/>
       </c>
       <c r="H104" s="21" t="b">
-        <f>A104=C104</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4565,7 +4571,7 @@
         <v/>
       </c>
       <c r="H105" s="21" t="b">
-        <f>A105=C105</f>
+        <f t="shared" ref="H105:H136" si="3">A105=C105</f>
         <v>1</v>
       </c>
     </row>
@@ -4590,7 +4596,7 @@
       </c>
       <c r="G106" s="29"/>
       <c r="H106" s="21" t="b">
-        <f>A106=C106</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4618,7 +4624,7 @@
         <v/>
       </c>
       <c r="H107" s="21" t="b">
-        <f>A107=C107</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4646,7 +4652,7 @@
         <v/>
       </c>
       <c r="H108" s="21" t="b">
-        <f>A108=C108</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4674,7 +4680,7 @@
         <v/>
       </c>
       <c r="H109" s="21" t="b">
-        <f>A109=C109</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4702,7 +4708,7 @@
         <v/>
       </c>
       <c r="H110" s="21" t="b">
-        <f>A110=C110</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4730,7 +4736,7 @@
         <v/>
       </c>
       <c r="H111" s="21" t="b">
-        <f>A111=C111</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4739,7 +4745,7 @@
         <v>20</v>
       </c>
       <c r="B112" s="27" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C112" s="28">
         <v>20</v>
@@ -4751,14 +4757,14 @@
         <v>81</v>
       </c>
       <c r="F112" s="26" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G112" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F112),0)&gt;0), MAX($G$1:G111)+1, ""))</f>
         <v/>
       </c>
       <c r="H112" s="21" t="b">
-        <f>A112=C112</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4786,7 +4792,7 @@
         <v/>
       </c>
       <c r="H113" s="21" t="b">
-        <f>A113=C113</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4814,7 +4820,7 @@
         <v/>
       </c>
       <c r="H114" s="21" t="b">
-        <f>A114=C114</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4842,7 +4848,7 @@
         <v/>
       </c>
       <c r="H115" s="21" t="b">
-        <f>A115=C115</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4870,7 +4876,7 @@
         <v/>
       </c>
       <c r="H116" s="21" t="b">
-        <f>A116=C116</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4898,7 +4904,7 @@
         <v/>
       </c>
       <c r="H117" s="21" t="b">
-        <f>A117=C117</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4926,7 +4932,7 @@
         <v/>
       </c>
       <c r="H118" s="21" t="b">
-        <f>A118=C118</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4954,7 +4960,7 @@
         <v/>
       </c>
       <c r="H119" s="21" t="b">
-        <f>A119=C119</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -4982,7 +4988,7 @@
         <v/>
       </c>
       <c r="H120" s="21" t="b">
-        <f>A120=C120</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -5010,7 +5016,7 @@
         <v/>
       </c>
       <c r="H121" s="21" t="b">
-        <f>A121=C121</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -5038,7 +5044,7 @@
         <v/>
       </c>
       <c r="H122" s="21" t="b">
-        <f>A122=C122</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -5066,7 +5072,7 @@
         <v/>
       </c>
       <c r="H123" s="21" t="b">
-        <f>A123=C123</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -5094,7 +5100,7 @@
         <v/>
       </c>
       <c r="H124" s="21" t="b">
-        <f>A124=C124</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -5103,7 +5109,7 @@
         <v>25</v>
       </c>
       <c r="B125" s="27" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C125" s="28">
         <v>25</v>
@@ -5115,14 +5121,14 @@
         <v>8</v>
       </c>
       <c r="F125" s="26" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G125" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F125),0)&gt;0), MAX($G$1:G124)+1, ""))</f>
         <v/>
       </c>
       <c r="H125" s="21" t="b">
-        <f>A125=C125</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -5150,7 +5156,7 @@
         <v/>
       </c>
       <c r="H126" s="21" t="b">
-        <f>A126=C126</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -5178,7 +5184,7 @@
         <v/>
       </c>
       <c r="H127" s="21" t="b">
-        <f>A127=C127</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -5206,7 +5212,7 @@
         <v/>
       </c>
       <c r="H128" s="21" t="b">
-        <f>A128=C128</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -5224,7 +5230,7 @@
         <v>234</v>
       </c>
       <c r="E129" s="27" t="s">
-        <v>131</v>
+        <v>245</v>
       </c>
       <c r="F129" s="26" t="s">
         <v>171</v>
@@ -5234,7 +5240,7 @@
         <v/>
       </c>
       <c r="H129" s="21" t="b">
-        <f>A129=C129</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -5262,7 +5268,7 @@
         <v/>
       </c>
       <c r="H130" s="21" t="b">
-        <f>A130=C130</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -5271,7 +5277,7 @@
         <v>25</v>
       </c>
       <c r="B131" s="27" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C131" s="28">
         <v>25</v>
@@ -5283,14 +5289,14 @@
         <v>8</v>
       </c>
       <c r="F131" s="26" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G131" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F131),0)&gt;0), MAX($G$1:G130)+1, ""))</f>
         <v/>
       </c>
       <c r="H131" s="21" t="b">
-        <f>A131=C131</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -5318,7 +5324,7 @@
         <v/>
       </c>
       <c r="H132" s="21" t="b">
-        <f>A132=C132</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -5346,7 +5352,7 @@
         <v/>
       </c>
       <c r="H133" s="21" t="b">
-        <f>A133=C133</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -5374,7 +5380,7 @@
         <v/>
       </c>
       <c r="H134" s="21" t="b">
-        <f>A134=C134</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -5402,7 +5408,7 @@
         <v/>
       </c>
       <c r="H135" s="21" t="b">
-        <f>A135=C135</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -5430,7 +5436,7 @@
         <v/>
       </c>
       <c r="H136" s="21" t="b">
-        <f>A136=C136</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -5458,7 +5464,7 @@
         <v/>
       </c>
       <c r="H137" s="21" t="b">
-        <f>A137=C137</f>
+        <f t="shared" ref="H137:H163" si="4">A137=C137</f>
         <v>1</v>
       </c>
     </row>
@@ -5486,7 +5492,7 @@
         <v/>
       </c>
       <c r="H138" s="21" t="b">
-        <f>A138=C138</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -5514,7 +5520,7 @@
         <v/>
       </c>
       <c r="H139" s="21" t="b">
-        <f>A139=C139</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -5542,7 +5548,7 @@
         <v/>
       </c>
       <c r="H140" s="21" t="b">
-        <f>A140=C140</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -5570,7 +5576,7 @@
         <v/>
       </c>
       <c r="H141" s="21" t="b">
-        <f>A141=C141</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -5598,7 +5604,7 @@
         <v/>
       </c>
       <c r="H142" s="21" t="b">
-        <f>A142=C142</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -5626,7 +5632,7 @@
         <v/>
       </c>
       <c r="H143" s="21" t="b">
-        <f>A143=C143</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -5654,7 +5660,7 @@
         <v/>
       </c>
       <c r="H144" s="21" t="b">
-        <f>A144=C144</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -5682,7 +5688,7 @@
         <v/>
       </c>
       <c r="H145" s="21" t="b">
-        <f>A145=C145</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -5710,7 +5716,7 @@
         <v/>
       </c>
       <c r="H146" s="21" t="b">
-        <f>A146=C146</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -5738,7 +5744,7 @@
         <v/>
       </c>
       <c r="H147" s="21" t="b">
-        <f>A147=C147</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -5766,7 +5772,7 @@
         <v/>
       </c>
       <c r="H148" s="21" t="b">
-        <f>A148=C148</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -5794,7 +5800,7 @@
         <v/>
       </c>
       <c r="H149" s="21" t="b">
-        <f>A149=C149</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -5822,7 +5828,7 @@
         <v/>
       </c>
       <c r="H150" s="21" t="b">
-        <f>A150=C150</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -5850,7 +5856,7 @@
         <v/>
       </c>
       <c r="H151" s="21" t="b">
-        <f>A151=C151</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -5878,7 +5884,7 @@
         <v/>
       </c>
       <c r="H152" s="21" t="b">
-        <f>A152=C152</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -5906,7 +5912,7 @@
         <v/>
       </c>
       <c r="H153" s="21" t="b">
-        <f>A153=C153</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -5934,7 +5940,7 @@
         <v/>
       </c>
       <c r="H154" s="21" t="b">
-        <f>A154=C154</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -5962,7 +5968,7 @@
         <v/>
       </c>
       <c r="H155" s="21" t="b">
-        <f>A155=C155</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -5990,7 +5996,7 @@
         <v/>
       </c>
       <c r="H156" s="21" t="b">
-        <f>A156=C156</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -6018,7 +6024,7 @@
         <v/>
       </c>
       <c r="H157" s="21" t="b">
-        <f>A157=C157</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -6046,7 +6052,7 @@
         <v/>
       </c>
       <c r="H158" s="21" t="b">
-        <f>A158=C158</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -6074,7 +6080,7 @@
         <v/>
       </c>
       <c r="H159" s="21" t="b">
-        <f>A159=C159</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -6102,7 +6108,7 @@
         <v/>
       </c>
       <c r="H160" s="21" t="b">
-        <f>A160=C160</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -6130,7 +6136,7 @@
         <v/>
       </c>
       <c r="H161" s="21" t="b">
-        <f>A161=C161</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -6158,7 +6164,7 @@
         <v/>
       </c>
       <c r="H162" s="21" t="b">
-        <f>A162=C162</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -6186,15 +6192,37 @@
         <v/>
       </c>
       <c r="H163" s="21" t="b">
-        <f>A163=C163</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="164" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A164" s="1"/>
-      <c r="C164" s="1"/>
-      <c r="D164" s="1"/>
-      <c r="F164" s="1"/>
+      <c r="A164" s="26">
+        <v>20</v>
+      </c>
+      <c r="B164" s="27" t="s">
+        <v>371</v>
+      </c>
+      <c r="C164" s="28">
+        <v>20</v>
+      </c>
+      <c r="D164" s="26">
+        <v>1.5</v>
+      </c>
+      <c r="E164" s="31" t="s">
+        <v>299</v>
+      </c>
+      <c r="F164" s="26" t="s">
+        <v>372</v>
+      </c>
+      <c r="G164" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B164),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E164),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F164),0)&gt;0), MAX($G$1:G163)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H164" s="21" t="b">
+        <f t="shared" ref="H164" si="5">A164=C164</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="165" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
@@ -11447,7 +11475,7 @@
       <c r="F1039" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H151">
+  <autoFilter ref="A1:H163">
     <sortState ref="A2:H147">
       <sortCondition ref="A2:A147"/>
       <sortCondition ref="B2:B147"/>

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Consulta" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$163</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$138</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$167</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$142</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Base!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="379">
   <si>
     <t>Grupo</t>
   </si>
@@ -1144,6 +1144,24 @@
   </si>
   <si>
     <t>21775-090</t>
+  </si>
+  <si>
+    <t>BANDEIRA DE MELO</t>
+  </si>
+  <si>
+    <t>21760-010</t>
+  </si>
+  <si>
+    <t>21755-260</t>
+  </si>
+  <si>
+    <t>JOSE MARIA DE ABREU (RUA 1)</t>
+  </si>
+  <si>
+    <t>JOSE MARIA DE ABREU APÓS CAMPO SÃO LUIS</t>
+  </si>
+  <si>
+    <t>BANDEIRA DE MELO APÓS CAMPO SÃO LUIS</t>
   </si>
 </sst>
 </file>
@@ -1661,7 +1679,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H1039"/>
+  <dimension ref="A1:H1043"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.453125" customWidth="1"/>
@@ -1719,7 +1737,7 @@
         <v/>
       </c>
       <c r="H2" s="21" t="b">
-        <f t="shared" ref="H2:H33" si="0">A2=C2</f>
+        <f>A2=C2</f>
         <v>1</v>
       </c>
     </row>
@@ -1747,7 +1765,7 @@
         <v/>
       </c>
       <c r="H3" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A3=C3</f>
         <v>1</v>
       </c>
     </row>
@@ -1775,7 +1793,7 @@
         <v/>
       </c>
       <c r="H4" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A4=C4</f>
         <v>1</v>
       </c>
     </row>
@@ -1803,7 +1821,7 @@
         <v/>
       </c>
       <c r="H5" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A5=C5</f>
         <v>1</v>
       </c>
     </row>
@@ -1831,7 +1849,7 @@
         <v/>
       </c>
       <c r="H6" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A6=C6</f>
         <v>1</v>
       </c>
     </row>
@@ -1859,7 +1877,7 @@
         <v/>
       </c>
       <c r="H7" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A7=C7</f>
         <v>1</v>
       </c>
     </row>
@@ -1887,7 +1905,7 @@
         <v/>
       </c>
       <c r="H8" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A8=C8</f>
         <v>1</v>
       </c>
     </row>
@@ -1915,7 +1933,7 @@
         <v/>
       </c>
       <c r="H9" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A9=C9</f>
         <v>1</v>
       </c>
     </row>
@@ -1943,7 +1961,7 @@
         <v/>
       </c>
       <c r="H10" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A10=C10</f>
         <v>1</v>
       </c>
     </row>
@@ -1971,7 +1989,7 @@
         <v/>
       </c>
       <c r="H11" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A11=C11</f>
         <v>1</v>
       </c>
     </row>
@@ -1999,7 +2017,7 @@
         <v/>
       </c>
       <c r="H12" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A12=C12</f>
         <v>1</v>
       </c>
     </row>
@@ -2027,7 +2045,7 @@
         <v/>
       </c>
       <c r="H13" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A13=C13</f>
         <v>1</v>
       </c>
     </row>
@@ -2055,7 +2073,7 @@
         <v/>
       </c>
       <c r="H14" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A14=C14</f>
         <v>1</v>
       </c>
     </row>
@@ -2083,7 +2101,7 @@
         <v/>
       </c>
       <c r="H15" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A15=C15</f>
         <v>1</v>
       </c>
     </row>
@@ -2111,7 +2129,7 @@
         <v/>
       </c>
       <c r="H16" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A16=C16</f>
         <v>1</v>
       </c>
     </row>
@@ -2139,7 +2157,7 @@
         <v/>
       </c>
       <c r="H17" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A17=C17</f>
         <v>1</v>
       </c>
     </row>
@@ -2167,7 +2185,7 @@
         <v/>
       </c>
       <c r="H18" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A18=C18</f>
         <v>1</v>
       </c>
     </row>
@@ -2195,7 +2213,7 @@
         <v/>
       </c>
       <c r="H19" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A19=C19</f>
         <v>1</v>
       </c>
     </row>
@@ -2223,7 +2241,7 @@
         <v/>
       </c>
       <c r="H20" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A20=C20</f>
         <v>1</v>
       </c>
     </row>
@@ -2232,26 +2250,26 @@
         <v>15</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>72</v>
+        <v>373</v>
       </c>
       <c r="C21" s="28">
         <v>15</v>
       </c>
-      <c r="D21" s="26" t="s">
-        <v>209</v>
+      <c r="D21" s="26">
+        <v>2.1</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>8</v>
+        <v>245</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>73</v>
+        <v>374</v>
       </c>
       <c r="G21" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F21),0)&gt;0), MAX($G$1:G20)+1, ""))</f>
         <v/>
       </c>
       <c r="H21" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A21=C21</f>
         <v>1</v>
       </c>
     </row>
@@ -2260,26 +2278,26 @@
         <v>15</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>364</v>
+        <v>72</v>
       </c>
       <c r="C22" s="28">
         <v>15</v>
       </c>
-      <c r="D22" s="26">
-        <v>1</v>
+      <c r="D22" s="26" t="s">
+        <v>209</v>
       </c>
       <c r="E22" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G22" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B22),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E22),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F22),0)&gt;0), MAX($G$1:G19)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B22),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E22),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F22),0)&gt;0), MAX($G$1:G21)+1, ""))</f>
         <v/>
       </c>
       <c r="H22" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A22=C22</f>
         <v>1</v>
       </c>
     </row>
@@ -2288,26 +2306,26 @@
         <v>15</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>66</v>
+        <v>364</v>
       </c>
       <c r="C23" s="28">
         <v>15</v>
       </c>
-      <c r="D23" s="26" t="s">
-        <v>219</v>
+      <c r="D23" s="26">
+        <v>1</v>
       </c>
       <c r="E23" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G23" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B23),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E23),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F23),0)&gt;0), MAX($G$1:G22)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B23),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E23),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F23),0)&gt;0), MAX($G$1:G20)+1, ""))</f>
         <v/>
       </c>
       <c r="H23" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A23=C23</f>
         <v>1</v>
       </c>
     </row>
@@ -2316,26 +2334,26 @@
         <v>15</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C24" s="28">
         <v>15</v>
       </c>
       <c r="D24" s="26" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="E24" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G24" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B24),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E24),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F24),0)&gt;0), MAX($G$1:G23)+1, ""))</f>
         <v/>
       </c>
       <c r="H24" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A24=C24</f>
         <v>1</v>
       </c>
     </row>
@@ -2344,7 +2362,7 @@
         <v>15</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>266</v>
+        <v>64</v>
       </c>
       <c r="C25" s="28">
         <v>15</v>
@@ -2353,7 +2371,7 @@
         <v>206</v>
       </c>
       <c r="E25" s="27" t="s">
-        <v>267</v>
+        <v>8</v>
       </c>
       <c r="F25" s="26" t="s">
         <v>65</v>
@@ -2363,7 +2381,7 @@
         <v/>
       </c>
       <c r="H25" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A25=C25</f>
         <v>1</v>
       </c>
     </row>
@@ -2372,26 +2390,26 @@
         <v>15</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>345</v>
+        <v>266</v>
       </c>
       <c r="C26" s="28">
         <v>15</v>
       </c>
-      <c r="D26" s="26">
-        <v>2.5</v>
+      <c r="D26" s="26" t="s">
+        <v>206</v>
       </c>
       <c r="E26" s="27" t="s">
-        <v>8</v>
+        <v>267</v>
       </c>
       <c r="F26" s="26" t="s">
-        <v>346</v>
+        <v>65</v>
       </c>
       <c r="G26" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B26),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E26),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F26),0)&gt;0), MAX($G$1:G25)+1, ""))</f>
         <v/>
       </c>
       <c r="H26" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A26=C26</f>
         <v>1</v>
       </c>
     </row>
@@ -2400,26 +2418,26 @@
         <v>15</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>259</v>
+        <v>345</v>
       </c>
       <c r="C27" s="28">
         <v>15</v>
       </c>
-      <c r="D27" s="26" t="s">
-        <v>7</v>
+      <c r="D27" s="26">
+        <v>2.5</v>
       </c>
       <c r="E27" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>261</v>
+        <v>346</v>
       </c>
       <c r="G27" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B27),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E27),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F27),0)&gt;0), MAX($G$1:G26)+1, ""))</f>
         <v/>
       </c>
       <c r="H27" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A27=C27</f>
         <v>1</v>
       </c>
     </row>
@@ -2428,26 +2446,26 @@
         <v>15</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>351</v>
+        <v>259</v>
       </c>
       <c r="C28" s="28">
         <v>15</v>
       </c>
-      <c r="D28" s="26">
-        <v>2</v>
+      <c r="D28" s="26" t="s">
+        <v>7</v>
       </c>
       <c r="E28" s="27" t="s">
-        <v>352</v>
+        <v>8</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>348</v>
+        <v>261</v>
       </c>
       <c r="G28" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B28),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E28),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F28),0)&gt;0), MAX($G$1:G27)+1, ""))</f>
         <v/>
       </c>
       <c r="H28" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A28=C28</f>
         <v>1</v>
       </c>
     </row>
@@ -2456,26 +2474,26 @@
         <v>15</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>57</v>
+        <v>351</v>
       </c>
       <c r="C29" s="28">
         <v>15</v>
       </c>
-      <c r="D29" s="26" t="s">
-        <v>223</v>
+      <c r="D29" s="26">
+        <v>2</v>
       </c>
       <c r="E29" s="27" t="s">
-        <v>8</v>
+        <v>352</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>58</v>
+        <v>348</v>
       </c>
       <c r="G29" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B29),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E29),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F29),0)&gt;0), MAX($G$1:G28)+1, ""))</f>
         <v/>
       </c>
       <c r="H29" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A29=C29</f>
         <v>1</v>
       </c>
     </row>
@@ -2484,26 +2502,26 @@
         <v>15</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>268</v>
+        <v>57</v>
       </c>
       <c r="C30" s="28">
         <v>15</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="E30" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G30" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B30),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E30),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F30),0)&gt;0), MAX($G$1:G29)+1, ""))</f>
         <v/>
       </c>
       <c r="H30" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A30=C30</f>
         <v>1</v>
       </c>
     </row>
@@ -2512,26 +2530,26 @@
         <v>15</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>306</v>
+        <v>268</v>
       </c>
       <c r="C31" s="28">
         <v>15</v>
       </c>
-      <c r="D31" s="26">
-        <v>2.1</v>
+      <c r="D31" s="26" t="s">
+        <v>205</v>
       </c>
       <c r="E31" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F31" s="26" t="s">
-        <v>307</v>
+        <v>56</v>
       </c>
       <c r="G31" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B31),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E31),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F31),0)&gt;0), MAX($G$1:G30)+1, ""))</f>
         <v/>
       </c>
       <c r="H31" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A31=C31</f>
         <v>1</v>
       </c>
     </row>
@@ -2540,26 +2558,26 @@
         <v>15</v>
       </c>
       <c r="B32" s="27" t="s">
-        <v>54</v>
+        <v>306</v>
       </c>
       <c r="C32" s="28">
         <v>15</v>
       </c>
-      <c r="D32" s="26" t="s">
-        <v>204</v>
+      <c r="D32" s="26">
+        <v>2.1</v>
       </c>
       <c r="E32" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F32" s="26" t="s">
-        <v>55</v>
+        <v>307</v>
       </c>
       <c r="G32" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B32),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E32),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F32),0)&gt;0), MAX($G$1:G31)+1, ""))</f>
         <v/>
       </c>
       <c r="H32" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A32=C32</f>
         <v>1</v>
       </c>
     </row>
@@ -2568,26 +2586,26 @@
         <v>15</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>277</v>
+        <v>54</v>
       </c>
       <c r="C33" s="28">
         <v>15</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E33" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F33" s="26" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="G33" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B33),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E33),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F33),0)&gt;0), MAX($G$1:G32)+1, ""))</f>
         <v/>
       </c>
       <c r="H33" s="21" t="b">
-        <f t="shared" si="0"/>
+        <f>A33=C33</f>
         <v>1</v>
       </c>
     </row>
@@ -2596,26 +2614,26 @@
         <v>15</v>
       </c>
       <c r="B34" s="27" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="C34" s="28">
         <v>15</v>
       </c>
       <c r="D34" s="26" t="s">
-        <v>21</v>
+        <v>210</v>
       </c>
       <c r="E34" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F34" s="26" t="s">
-        <v>262</v>
+        <v>75</v>
       </c>
       <c r="G34" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B34),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E34),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F34),0)&gt;0), MAX($G$1:G33)+1, ""))</f>
         <v/>
       </c>
       <c r="H34" s="21" t="b">
-        <f t="shared" ref="H34:H65" si="1">A34=C34</f>
+        <f>A34=C34</f>
         <v>1</v>
       </c>
     </row>
@@ -2624,26 +2642,26 @@
         <v>15</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>292</v>
+        <v>260</v>
       </c>
       <c r="C35" s="28">
         <v>15</v>
       </c>
-      <c r="D35" s="26">
-        <v>2.2000000000000002</v>
+      <c r="D35" s="26" t="s">
+        <v>21</v>
       </c>
       <c r="E35" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>293</v>
+        <v>262</v>
       </c>
       <c r="G35" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F35),0)&gt;0), MAX($G$1:G34)+1, ""))</f>
         <v/>
       </c>
       <c r="H35" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A35=C35</f>
         <v>1</v>
       </c>
     </row>
@@ -2652,26 +2670,26 @@
         <v>15</v>
       </c>
       <c r="B36" s="27" t="s">
-        <v>354</v>
+        <v>292</v>
       </c>
       <c r="C36" s="28">
         <v>15</v>
       </c>
       <c r="D36" s="26">
-        <v>1.5</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E36" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F36" s="26" t="s">
-        <v>355</v>
+        <v>293</v>
       </c>
       <c r="G36" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B36),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E36),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F36),0)&gt;0), MAX($G$1:G35)+1, ""))</f>
         <v/>
       </c>
       <c r="H36" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A36=C36</f>
         <v>1</v>
       </c>
     </row>
@@ -2680,26 +2698,26 @@
         <v>15</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>50</v>
+        <v>376</v>
       </c>
       <c r="C37" s="28">
         <v>15</v>
       </c>
-      <c r="D37" s="26" t="s">
-        <v>213</v>
+      <c r="D37" s="26">
+        <v>2.1</v>
       </c>
       <c r="E37" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>51</v>
+        <v>375</v>
       </c>
       <c r="G37" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F37),0)&gt;0), MAX($G$1:G36)+1, ""))</f>
         <v/>
       </c>
       <c r="H37" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A37=C37</f>
         <v>1</v>
       </c>
     </row>
@@ -2708,26 +2726,26 @@
         <v>15</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>46</v>
+        <v>354</v>
       </c>
       <c r="C38" s="28">
         <v>15</v>
       </c>
-      <c r="D38" s="26" t="s">
-        <v>233</v>
+      <c r="D38" s="26">
+        <v>1.5</v>
       </c>
       <c r="E38" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F38" s="26" t="s">
-        <v>47</v>
+        <v>355</v>
       </c>
       <c r="G38" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F38),0)&gt;0), MAX($G$1:G37)+1, ""))</f>
         <v/>
       </c>
       <c r="H38" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A38=C38</f>
         <v>1</v>
       </c>
     </row>
@@ -2736,26 +2754,26 @@
         <v>15</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C39" s="28">
         <v>15</v>
       </c>
       <c r="D39" s="26" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="E39" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F39" s="26" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G39" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B39),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E39),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F39),0)&gt;0), MAX($G$1:G38)+1, ""))</f>
         <v/>
       </c>
       <c r="H39" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A39=C39</f>
         <v>1</v>
       </c>
     </row>
@@ -2764,26 +2782,26 @@
         <v>15</v>
       </c>
       <c r="B40" s="27" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C40" s="28">
         <v>15</v>
       </c>
       <c r="D40" s="26" t="s">
-        <v>206</v>
+        <v>233</v>
       </c>
       <c r="E40" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F40" s="26" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G40" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B40),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E40),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F40),0)&gt;0), MAX($G$1:G39)+1, ""))</f>
         <v/>
       </c>
       <c r="H40" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A40=C40</f>
         <v>1</v>
       </c>
     </row>
@@ -2792,26 +2810,26 @@
         <v>15</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C41" s="28">
         <v>15</v>
       </c>
       <c r="D41" s="26" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="E41" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F41" s="26" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G41" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B41),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E41),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F41),0)&gt;0), MAX($G$1:G40)+1, ""))</f>
         <v/>
       </c>
       <c r="H41" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A41=C41</f>
         <v>1</v>
       </c>
     </row>
@@ -2820,26 +2838,26 @@
         <v>15</v>
       </c>
       <c r="B42" s="27" t="s">
-        <v>308</v>
+        <v>40</v>
       </c>
       <c r="C42" s="28">
         <v>15</v>
       </c>
-      <c r="D42" s="26">
-        <v>2.2000000000000002</v>
+      <c r="D42" s="26" t="s">
+        <v>212</v>
       </c>
       <c r="E42" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F42" s="26" t="s">
-        <v>293</v>
+        <v>41</v>
       </c>
       <c r="G42" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B42),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E42),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F42),0)&gt;0), MAX($G$1:G41)+1, ""))</f>
         <v/>
       </c>
       <c r="H42" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A42=C42</f>
         <v>1</v>
       </c>
     </row>
@@ -2848,26 +2866,26 @@
         <v>15</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>244</v>
+        <v>308</v>
       </c>
       <c r="C43" s="28">
         <v>15</v>
       </c>
       <c r="D43" s="26">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E43" s="27" t="s">
-        <v>245</v>
+        <v>8</v>
       </c>
       <c r="F43" s="26" t="s">
-        <v>202</v>
+        <v>293</v>
       </c>
       <c r="G43" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F43),0)&gt;0), MAX($G$1:G42)+1, ""))</f>
         <v/>
       </c>
       <c r="H43" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A43=C43</f>
         <v>1</v>
       </c>
     </row>
@@ -2876,26 +2894,26 @@
         <v>15</v>
       </c>
       <c r="B44" s="27" t="s">
-        <v>38</v>
+        <v>244</v>
       </c>
       <c r="C44" s="28">
         <v>15</v>
       </c>
-      <c r="D44" s="26" t="s">
-        <v>211</v>
+      <c r="D44" s="26">
+        <v>2.1</v>
       </c>
       <c r="E44" s="27" t="s">
-        <v>8</v>
+        <v>245</v>
       </c>
       <c r="F44" s="26" t="s">
-        <v>39</v>
+        <v>202</v>
       </c>
       <c r="G44" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F44),0)&gt;0), MAX($G$1:G43)+1, ""))</f>
         <v/>
       </c>
       <c r="H44" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A44=C44</f>
         <v>1</v>
       </c>
     </row>
@@ -2904,26 +2922,26 @@
         <v>15</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>341</v>
+        <v>38</v>
       </c>
       <c r="C45" s="28">
         <v>15</v>
       </c>
-      <c r="D45" s="26">
-        <v>1.4</v>
+      <c r="D45" s="26" t="s">
+        <v>211</v>
       </c>
       <c r="E45" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F45" s="26" t="s">
-        <v>347</v>
+        <v>39</v>
       </c>
       <c r="G45" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F45),0)&gt;0), MAX($G$1:G44)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F45),0)&gt;0), MAX($G$1:G40)+1, ""))</f>
         <v/>
       </c>
       <c r="H45" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A45=C45</f>
         <v>1</v>
       </c>
     </row>
@@ -2932,26 +2950,26 @@
         <v>15</v>
       </c>
       <c r="B46" s="27" t="s">
-        <v>34</v>
+        <v>341</v>
       </c>
       <c r="C46" s="28">
         <v>15</v>
       </c>
-      <c r="D46" s="26" t="s">
-        <v>210</v>
+      <c r="D46" s="26">
+        <v>1.4</v>
       </c>
       <c r="E46" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F46" s="26" t="s">
-        <v>35</v>
+        <v>347</v>
       </c>
       <c r="G46" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F46),0)&gt;0), MAX($G$1:G45)+1, ""))</f>
         <v/>
       </c>
       <c r="H46" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A46=C46</f>
         <v>1</v>
       </c>
     </row>
@@ -2960,107 +2978,110 @@
         <v>15</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>280</v>
+        <v>34</v>
       </c>
       <c r="C47" s="28">
         <v>15</v>
       </c>
       <c r="D47" s="26" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E47" s="27" t="s">
-        <v>267</v>
+        <v>8</v>
       </c>
       <c r="F47" s="26" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G47" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F47),0)&gt;0), MAX($G$1:G46)+1, ""))</f>
         <v/>
       </c>
       <c r="H47" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A47=C47</f>
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A48" s="33">
-        <v>17</v>
-      </c>
-      <c r="B48" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="C48" s="35">
-        <v>17</v>
-      </c>
-      <c r="D48" s="33" t="s">
-        <v>214</v>
-      </c>
-      <c r="E48" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F48" s="33" t="s">
-        <v>71</v>
+      <c r="A48" s="26">
+        <v>15</v>
+      </c>
+      <c r="B48" s="27" t="s">
+        <v>280</v>
+      </c>
+      <c r="C48" s="28">
+        <v>15</v>
+      </c>
+      <c r="D48" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="E48" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="F48" s="26" t="s">
+        <v>33</v>
       </c>
       <c r="G48" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F48),0)&gt;0), MAX($G$1:G47)+1, ""))</f>
         <v/>
       </c>
       <c r="H48" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A48=C48</f>
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="33">
+      <c r="A49" s="26">
         <v>17</v>
       </c>
-      <c r="B49" s="34" t="s">
-        <v>281</v>
-      </c>
-      <c r="C49" s="35">
+      <c r="B49" s="27" t="s">
+        <v>378</v>
+      </c>
+      <c r="C49" s="28">
         <v>17</v>
       </c>
-      <c r="D49" s="33" t="s">
-        <v>222</v>
-      </c>
-      <c r="E49" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F49" s="33" t="s">
-        <v>68</v>
+      <c r="D49" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E49" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="F49" s="26" t="s">
+        <v>374</v>
       </c>
       <c r="G49" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F49),0)&gt;0), MAX($G$1:G48)+1, ""))</f>
         <v/>
       </c>
       <c r="H49" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A49=C49</f>
         <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A50" s="26">
+      <c r="A50" s="33">
         <v>17</v>
       </c>
-      <c r="B50" s="27" t="s">
-        <v>313</v>
-      </c>
-      <c r="C50" s="28">
+      <c r="B50" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="35">
         <v>17</v>
       </c>
-      <c r="D50" s="26">
-        <v>1.7</v>
-      </c>
-      <c r="E50" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="F50" s="26" t="s">
-        <v>319</v>
-      </c>
-      <c r="G50" s="29"/>
+      <c r="D50" s="33" t="s">
+        <v>214</v>
+      </c>
+      <c r="E50" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F50" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="G50" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F50),0)&gt;0), MAX($G$1:G49)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H50" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A50=C50</f>
         <v>1</v>
       </c>
     </row>
@@ -3069,107 +3090,107 @@
         <v>17</v>
       </c>
       <c r="B51" s="34" t="s">
-        <v>62</v>
+        <v>281</v>
       </c>
       <c r="C51" s="35">
         <v>17</v>
       </c>
       <c r="D51" s="33" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="E51" s="34" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F51" s="33" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G51" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F51),0)&gt;0), MAX($G$1:G50)+1, ""))</f>
         <v/>
       </c>
       <c r="H51" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A51=C51</f>
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="33">
+      <c r="A52" s="26">
         <v>17</v>
       </c>
-      <c r="B52" s="34" t="s">
+      <c r="B52" s="27" t="s">
+        <v>313</v>
+      </c>
+      <c r="C52" s="28">
+        <v>17</v>
+      </c>
+      <c r="D52" s="26">
+        <v>1.7</v>
+      </c>
+      <c r="E52" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F52" s="26" t="s">
+        <v>319</v>
+      </c>
+      <c r="G52" s="29"/>
+      <c r="H52" s="21" t="b">
+        <f>A52=C52</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A53" s="33">
+        <v>17</v>
+      </c>
+      <c r="B53" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C53" s="35">
+        <v>17</v>
+      </c>
+      <c r="D53" s="33" t="s">
+        <v>215</v>
+      </c>
+      <c r="E53" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F53" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="G53" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F53),0)&gt;0), MAX($G$1:G52)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H53" s="21" t="b">
+        <f>A53=C53</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="33">
+        <v>17</v>
+      </c>
+      <c r="B54" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="C52" s="35">
+      <c r="C54" s="35">
         <v>17</v>
       </c>
-      <c r="D52" s="33" t="s">
+      <c r="D54" s="33" t="s">
         <v>216</v>
       </c>
-      <c r="E52" s="34" t="s">
+      <c r="E54" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="F52" s="33" t="s">
+      <c r="F54" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="G52" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F52),0)&gt;0), MAX($G$1:G51)+1, ""))</f>
-        <v/>
-      </c>
-      <c r="H52" s="21" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="26">
-        <v>17</v>
-      </c>
-      <c r="B53" s="27" t="s">
-        <v>315</v>
-      </c>
-      <c r="C53" s="28">
-        <v>17</v>
-      </c>
-      <c r="D53" s="26">
-        <v>3</v>
-      </c>
-      <c r="E53" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="F53" s="26" t="s">
-        <v>321</v>
-      </c>
-      <c r="G53" s="29"/>
-      <c r="H53" s="21" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A54" s="26">
-        <v>17</v>
-      </c>
-      <c r="B54" s="27" t="s">
-        <v>340</v>
-      </c>
-      <c r="C54" s="28">
-        <v>17</v>
-      </c>
-      <c r="D54" s="26">
-        <v>3.3</v>
-      </c>
-      <c r="E54" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F54" s="26" t="s">
-        <v>349</v>
-      </c>
       <c r="G54" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F54),0)&gt;0), MAX($G$1:G52)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F54),0)&gt;0), MAX($G$1:G53)+1, ""))</f>
         <v/>
       </c>
       <c r="H54" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A54=C54</f>
         <v>1</v>
       </c>
     </row>
@@ -3178,51 +3199,51 @@
         <v>17</v>
       </c>
       <c r="B55" s="27" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C55" s="28">
         <v>17</v>
       </c>
       <c r="D55" s="26">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="E55" s="27" t="s">
         <v>60</v>
       </c>
       <c r="F55" s="26" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G55" s="29"/>
       <c r="H55" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A55=C55</f>
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A56" s="36">
+      <c r="A56" s="26">
         <v>17</v>
       </c>
-      <c r="B56" s="37" t="s">
-        <v>289</v>
-      </c>
-      <c r="C56" s="38">
+      <c r="B56" s="27" t="s">
+        <v>340</v>
+      </c>
+      <c r="C56" s="28">
         <v>17</v>
       </c>
-      <c r="D56" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="E56" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="F56" s="36" t="s">
-        <v>111</v>
+      <c r="D56" s="26">
+        <v>3.3</v>
+      </c>
+      <c r="E56" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F56" s="26" t="s">
+        <v>349</v>
       </c>
       <c r="G56" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F56),0)&gt;0), MAX($G$1:G55)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F56),0)&gt;0), MAX($G$1:G54)+1, ""))</f>
         <v/>
       </c>
       <c r="H56" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A56=C56</f>
         <v>1</v>
       </c>
     </row>
@@ -3231,244 +3252,241 @@
         <v>17</v>
       </c>
       <c r="B57" s="27" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C57" s="28">
         <v>17</v>
       </c>
       <c r="D57" s="26">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="E57" s="27" t="s">
         <v>60</v>
       </c>
       <c r="F57" s="26" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G57" s="29"/>
       <c r="H57" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A57=C57</f>
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A58" s="26">
+      <c r="A58" s="36">
         <v>17</v>
       </c>
-      <c r="B58" s="27" t="s">
-        <v>317</v>
-      </c>
-      <c r="C58" s="28">
+      <c r="B58" s="37" t="s">
+        <v>289</v>
+      </c>
+      <c r="C58" s="38">
         <v>17</v>
       </c>
-      <c r="D58" s="26">
-        <v>2</v>
-      </c>
-      <c r="E58" s="27" t="s">
+      <c r="D58" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E58" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="F58" s="26" t="s">
-        <v>323</v>
-      </c>
-      <c r="G58" s="29"/>
+      <c r="F58" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="G58" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F58),0)&gt;0), MAX($G$1:G57)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H58" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A58=C58</f>
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A59" s="36">
+      <c r="A59" s="26">
         <v>17</v>
       </c>
-      <c r="B59" s="37" t="s">
-        <v>106</v>
-      </c>
-      <c r="C59" s="38">
+      <c r="B59" s="27" t="s">
+        <v>314</v>
+      </c>
+      <c r="C59" s="28">
         <v>17</v>
       </c>
-      <c r="D59" s="36" t="s">
-        <v>220</v>
-      </c>
-      <c r="E59" s="37" t="s">
+      <c r="D59" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E59" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F59" s="26" t="s">
+        <v>320</v>
+      </c>
+      <c r="G59" s="29"/>
+      <c r="H59" s="21" t="b">
+        <f>A59=C59</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A60" s="26">
+        <v>17</v>
+      </c>
+      <c r="B60" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="C60" s="28">
+        <v>17</v>
+      </c>
+      <c r="D60" s="26">
+        <v>2.1</v>
+      </c>
+      <c r="E60" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F59" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="G59" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F59),0)&gt;0), MAX($G$1:G58)+1, ""))</f>
-        <v/>
-      </c>
-      <c r="H59" s="21" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A60" s="36">
-        <v>17</v>
-      </c>
-      <c r="B60" s="37" t="s">
-        <v>303</v>
-      </c>
-      <c r="C60" s="38">
-        <v>17</v>
-      </c>
-      <c r="D60" s="36" t="s">
-        <v>229</v>
-      </c>
-      <c r="E60" s="37" t="s">
-        <v>304</v>
-      </c>
-      <c r="F60" s="36" t="s">
-        <v>105</v>
+      <c r="F60" s="26" t="s">
+        <v>375</v>
       </c>
       <c r="G60" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F60),0)&gt;0), MAX($G$1:G59)+1, ""))</f>
         <v/>
       </c>
       <c r="H60" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A60=C60</f>
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A61" s="33">
+      <c r="A61" s="26">
         <v>17</v>
       </c>
-      <c r="B61" s="34" t="s">
-        <v>52</v>
-      </c>
-      <c r="C61" s="35">
+      <c r="B61" s="27" t="s">
+        <v>317</v>
+      </c>
+      <c r="C61" s="28">
         <v>17</v>
       </c>
-      <c r="D61" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="E61" s="34" t="s">
+      <c r="D61" s="26">
+        <v>2</v>
+      </c>
+      <c r="E61" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F61" s="26" t="s">
+        <v>323</v>
+      </c>
+      <c r="G61" s="29"/>
+      <c r="H61" s="21" t="b">
+        <f>A61=C61</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A62" s="36">
+        <v>17</v>
+      </c>
+      <c r="B62" s="37" t="s">
+        <v>106</v>
+      </c>
+      <c r="C62" s="38">
+        <v>17</v>
+      </c>
+      <c r="D62" s="36" t="s">
+        <v>220</v>
+      </c>
+      <c r="E62" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F61" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="G61" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F61),0)&gt;0), MAX($G$1:G56)+1, ""))</f>
-        <v/>
-      </c>
-      <c r="H61" s="21" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A62" s="26">
-        <v>17</v>
-      </c>
-      <c r="B62" s="27" t="s">
-        <v>370</v>
-      </c>
-      <c r="C62" s="28">
-        <v>17</v>
-      </c>
-      <c r="D62" s="26">
-        <v>1.8</v>
-      </c>
-      <c r="E62" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F62" s="26" t="s">
-        <v>356</v>
+      <c r="F62" s="36" t="s">
+        <v>107</v>
       </c>
       <c r="G62" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F62),0)&gt;0), MAX($G$1:G61)+1, ""))</f>
         <v/>
       </c>
       <c r="H62" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A62=C62</f>
         <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A63" s="33">
+      <c r="A63" s="36">
         <v>17</v>
       </c>
-      <c r="B63" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="C63" s="35">
+      <c r="B63" s="37" t="s">
+        <v>303</v>
+      </c>
+      <c r="C63" s="38">
         <v>17</v>
       </c>
-      <c r="D63" s="33" t="s">
-        <v>211</v>
-      </c>
-      <c r="E63" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F63" s="33" t="s">
-        <v>49</v>
+      <c r="D63" s="36" t="s">
+        <v>229</v>
+      </c>
+      <c r="E63" s="37" t="s">
+        <v>304</v>
+      </c>
+      <c r="F63" s="36" t="s">
+        <v>105</v>
       </c>
       <c r="G63" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F63),0)&gt;0), MAX($G$1:G62)+1, ""))</f>
         <v/>
       </c>
       <c r="H63" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A63=C63</f>
         <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A64" s="36">
+      <c r="A64" s="33">
         <v>17</v>
       </c>
-      <c r="B64" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="C64" s="38">
+      <c r="B64" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="C64" s="35">
         <v>17</v>
       </c>
-      <c r="D64" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="E64" s="37" t="s">
+      <c r="D64" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="E64" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F64" s="36" t="s">
-        <v>98</v>
+      <c r="F64" s="33" t="s">
+        <v>53</v>
       </c>
       <c r="G64" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F64),0)&gt;0), MAX($G$1:G63)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F64),0)&gt;0), MAX($G$1:G59)+1, ""))</f>
         <v/>
       </c>
       <c r="H64" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A64=C64</f>
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A65" s="36">
+      <c r="A65" s="26">
         <v>17</v>
       </c>
-      <c r="B65" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="C65" s="38">
+      <c r="B65" s="27" t="s">
+        <v>370</v>
+      </c>
+      <c r="C65" s="28">
         <v>17</v>
       </c>
-      <c r="D65" s="36" t="s">
-        <v>217</v>
-      </c>
-      <c r="E65" s="37" t="s">
+      <c r="D65" s="26">
+        <v>1.8</v>
+      </c>
+      <c r="E65" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F65" s="36" t="s">
-        <v>94</v>
+      <c r="F65" s="26" t="s">
+        <v>356</v>
       </c>
       <c r="G65" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F65),0)&gt;0), MAX($G$1:G64)+1, ""))</f>
         <v/>
       </c>
       <c r="H65" s="21" t="b">
-        <f t="shared" si="1"/>
+        <f>A65=C65</f>
         <v>1</v>
       </c>
     </row>
@@ -3477,97 +3495,103 @@
         <v>17</v>
       </c>
       <c r="B66" s="34" t="s">
-        <v>327</v>
+        <v>48</v>
       </c>
       <c r="C66" s="35">
         <v>17</v>
       </c>
-      <c r="D66" s="33">
-        <v>1.9</v>
+      <c r="D66" s="33" t="s">
+        <v>211</v>
       </c>
       <c r="E66" s="34" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="F66" s="33" t="s">
-        <v>329</v>
-      </c>
-      <c r="G66" s="29" t="s">
-        <v>326</v>
+        <v>49</v>
+      </c>
+      <c r="G66" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F66),0)&gt;0), MAX($G$1:G65)+1, ""))</f>
+        <v/>
       </c>
       <c r="H66" s="21" t="b">
+        <f>A66=C66</f>
         <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A67" s="33">
+      <c r="A67" s="36">
         <v>17</v>
       </c>
-      <c r="B67" s="34" t="s">
-        <v>325</v>
-      </c>
-      <c r="C67" s="35">
+      <c r="B67" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="C67" s="38">
         <v>17</v>
       </c>
-      <c r="D67" s="33">
-        <v>1.9</v>
-      </c>
-      <c r="E67" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F67" s="33" t="s">
-        <v>329</v>
-      </c>
-      <c r="G67" s="29" t="s">
-        <v>326</v>
+      <c r="D67" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E67" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F67" s="36" t="s">
+        <v>98</v>
+      </c>
+      <c r="G67" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F67),0)&gt;0), MAX($G$1:G66)+1, ""))</f>
+        <v/>
       </c>
       <c r="H67" s="21" t="b">
+        <f>A67=C67</f>
         <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A68" s="33">
+      <c r="A68" s="26">
         <v>17</v>
       </c>
-      <c r="B68" s="34" t="s">
-        <v>328</v>
-      </c>
-      <c r="C68" s="35">
+      <c r="B68" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C68" s="28">
         <v>17</v>
       </c>
-      <c r="D68" s="33">
-        <v>1.9</v>
-      </c>
-      <c r="E68" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F68" s="33" t="s">
-        <v>329</v>
-      </c>
-      <c r="G68" s="29" t="s">
-        <v>326</v>
+      <c r="D68" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="E68" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F68" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="G68" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F68),0)&gt;0), MAX($G$1:G67)+1, ""))</f>
+        <v/>
       </c>
       <c r="H68" s="21" t="b">
+        <f>A68=C68</f>
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A69" s="33">
+      <c r="A69" s="36">
         <v>17</v>
       </c>
-      <c r="B69" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="C69" s="35">
+      <c r="B69" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="C69" s="38">
         <v>17</v>
       </c>
-      <c r="D69" s="33" t="s">
-        <v>214</v>
-      </c>
-      <c r="E69" s="34" t="s">
+      <c r="D69" s="36" t="s">
+        <v>217</v>
+      </c>
+      <c r="E69" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F69" s="33" t="s">
-        <v>37</v>
+      <c r="F69" s="36" t="s">
+        <v>94</v>
       </c>
       <c r="G69" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F69),0)&gt;0), MAX($G$1:G68)+1, ""))</f>
@@ -3579,30 +3603,28 @@
       </c>
     </row>
     <row r="70" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A70" s="36">
+      <c r="A70" s="33">
         <v>17</v>
       </c>
-      <c r="B70" s="37" t="s">
-        <v>83</v>
-      </c>
-      <c r="C70" s="38">
+      <c r="B70" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="C70" s="35">
         <v>17</v>
       </c>
-      <c r="D70" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="E70" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F70" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="G70" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F70),0)&gt;0), MAX($G$1:G69)+1, ""))</f>
-        <v/>
+      <c r="D70" s="33">
+        <v>1.9</v>
+      </c>
+      <c r="E70" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="F70" s="33" t="s">
+        <v>329</v>
+      </c>
+      <c r="G70" s="29" t="s">
+        <v>326</v>
       </c>
       <c r="H70" s="21" t="b">
-        <f>A70=C70</f>
         <v>1</v>
       </c>
     </row>
@@ -3611,26 +3633,24 @@
         <v>17</v>
       </c>
       <c r="B71" s="34" t="s">
-        <v>31</v>
+        <v>325</v>
       </c>
       <c r="C71" s="35">
         <v>17</v>
       </c>
-      <c r="D71" s="33" t="s">
-        <v>208</v>
+      <c r="D71" s="33">
+        <v>1.9</v>
       </c>
       <c r="E71" s="34" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F71" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="G71" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F71),0)&gt;0), MAX($G$1:G70)+1, ""))</f>
-        <v/>
+        <v>329</v>
+      </c>
+      <c r="G71" s="29" t="s">
+        <v>326</v>
       </c>
       <c r="H71" s="21" t="b">
-        <f>A71=C71</f>
         <v>1</v>
       </c>
     </row>
@@ -3639,19 +3659,19 @@
         <v>17</v>
       </c>
       <c r="B72" s="34" t="s">
-        <v>29</v>
+        <v>328</v>
       </c>
       <c r="C72" s="35">
         <v>17</v>
       </c>
-      <c r="D72" s="33" t="s">
-        <v>207</v>
+      <c r="D72" s="33">
+        <v>1.9</v>
       </c>
       <c r="E72" s="34" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F72" s="33" t="s">
-        <v>30</v>
+        <v>329</v>
       </c>
       <c r="G72" s="29" t="s">
         <v>326</v>
@@ -3661,164 +3681,168 @@
       </c>
     </row>
     <row r="73" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A73" s="30">
-        <v>20</v>
-      </c>
-      <c r="B73" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="C73" s="32">
-        <v>20</v>
-      </c>
-      <c r="D73" s="30" t="s">
-        <v>206</v>
-      </c>
-      <c r="E73" s="31" t="s">
+      <c r="A73" s="33">
+        <v>17</v>
+      </c>
+      <c r="B73" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="C73" s="35">
+        <v>17</v>
+      </c>
+      <c r="D73" s="33" t="s">
+        <v>214</v>
+      </c>
+      <c r="E73" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F73" s="30" t="s">
-        <v>147</v>
+      <c r="F73" s="33" t="s">
+        <v>37</v>
       </c>
       <c r="G73" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F73),0)&gt;0), MAX($G$1:G69)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F73),0)&gt;0), MAX($G$1:G72)+1, ""))</f>
         <v/>
       </c>
       <c r="H73" s="21" t="b">
-        <f t="shared" ref="H73:H104" si="2">A73=C73</f>
+        <f>A73=C73</f>
         <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A74" s="30">
-        <v>20</v>
-      </c>
-      <c r="B74" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="C74" s="32">
-        <v>20</v>
-      </c>
-      <c r="D74" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="E74" s="31" t="s">
+      <c r="A74" s="36">
+        <v>17</v>
+      </c>
+      <c r="B74" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="C74" s="38">
+        <v>17</v>
+      </c>
+      <c r="D74" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E74" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F74" s="30" t="s">
-        <v>145</v>
+      <c r="F74" s="36" t="s">
+        <v>84</v>
       </c>
       <c r="G74" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F74),0)&gt;0), MAX($G$1:G73)+1, ""))</f>
         <v/>
       </c>
       <c r="H74" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A74=C74</f>
         <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A75" s="30">
+      <c r="A75" s="33">
+        <v>17</v>
+      </c>
+      <c r="B75" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="35">
+        <v>17</v>
+      </c>
+      <c r="D75" s="33" t="s">
+        <v>208</v>
+      </c>
+      <c r="E75" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F75" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="G75" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F75),0)&gt;0), MAX($G$1:G74)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H75" s="21" t="b">
+        <f>A75=C75</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A76" s="33">
+        <v>17</v>
+      </c>
+      <c r="B76" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="C76" s="35">
+        <v>17</v>
+      </c>
+      <c r="D76" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="E76" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F76" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="G76" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="H76" s="21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A77" s="30">
         <v>20</v>
       </c>
-      <c r="B75" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="C75" s="32">
+      <c r="B77" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="C77" s="32">
         <v>20</v>
       </c>
-      <c r="D75" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="E75" s="31" t="s">
+      <c r="D77" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="E77" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F75" s="30" t="s">
-        <v>143</v>
-      </c>
-      <c r="G75" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F75),0)&gt;0), MAX($G$1:G73)+1, ""))</f>
-        <v/>
-      </c>
-      <c r="H75" s="21" t="b">
-        <f t="shared" si="2"/>
+      <c r="F77" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="G77" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F77),0)&gt;0), MAX($G$1:G73)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H77" s="21" t="b">
+        <f>A77=C77</f>
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A76" s="30">
+    <row r="78" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A78" s="30">
         <v>20</v>
       </c>
-      <c r="B76" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="C76" s="32">
+      <c r="B78" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="C78" s="32">
         <v>20</v>
       </c>
-      <c r="D76" s="30" t="s">
-        <v>216</v>
-      </c>
-      <c r="E76" s="31" t="s">
-        <v>305</v>
-      </c>
-      <c r="F76" s="30" t="s">
-        <v>141</v>
-      </c>
-      <c r="G76" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F76),0)&gt;0), MAX($G$1:G75)+1, ""))</f>
-        <v/>
-      </c>
-      <c r="H76" s="21" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A77" s="36">
-        <v>20</v>
-      </c>
-      <c r="B77" s="37" t="s">
-        <v>333</v>
-      </c>
-      <c r="C77" s="38">
-        <v>20</v>
-      </c>
-      <c r="D77" s="36">
-        <v>3.4</v>
-      </c>
-      <c r="E77" s="37" t="s">
-        <v>336</v>
-      </c>
-      <c r="F77" s="36" t="s">
-        <v>334</v>
-      </c>
-      <c r="G77" s="29"/>
-      <c r="H77" s="21" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A78" s="36">
-        <v>20</v>
-      </c>
-      <c r="B78" s="37" t="s">
-        <v>331</v>
-      </c>
-      <c r="C78" s="38">
-        <v>20</v>
-      </c>
-      <c r="D78" s="36">
-        <v>3.3</v>
-      </c>
-      <c r="E78" s="37" t="s">
-        <v>336</v>
-      </c>
-      <c r="F78" s="36" t="s">
-        <v>332</v>
-      </c>
-      <c r="G78" s="29"/>
+      <c r="D78" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="E78" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F78" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="G78" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F78),0)&gt;0), MAX($G$1:G77)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H78" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A78=C78</f>
         <v>1</v>
       </c>
     </row>
@@ -3827,26 +3851,26 @@
         <v>20</v>
       </c>
       <c r="B79" s="31" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C79" s="32">
         <v>20</v>
       </c>
       <c r="D79" s="30" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="E79" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F79" s="30" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G79" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F79),0)&gt;0), MAX($G$1:G78)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F79),0)&gt;0), MAX($G$1:G77)+1, ""))</f>
         <v/>
       </c>
       <c r="H79" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A79=C79</f>
         <v>1</v>
       </c>
     </row>
@@ -3855,82 +3879,76 @@
         <v>20</v>
       </c>
       <c r="B80" s="31" t="s">
-        <v>255</v>
+        <v>140</v>
       </c>
       <c r="C80" s="32">
         <v>20</v>
       </c>
       <c r="D80" s="30" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="E80" s="31" t="s">
-        <v>8</v>
+        <v>305</v>
       </c>
       <c r="F80" s="30" t="s">
-        <v>256</v>
+        <v>141</v>
       </c>
       <c r="G80" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F80),0)&gt;0), MAX($G$1:G79)+1, ""))</f>
         <v/>
       </c>
       <c r="H80" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A80=C80</f>
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A81" s="30">
+      <c r="A81" s="36">
         <v>20</v>
       </c>
-      <c r="B81" s="31" t="s">
-        <v>254</v>
-      </c>
-      <c r="C81" s="32">
+      <c r="B81" s="37" t="s">
+        <v>333</v>
+      </c>
+      <c r="C81" s="38">
         <v>20</v>
       </c>
-      <c r="D81" s="30">
-        <v>4.2</v>
-      </c>
-      <c r="E81" s="31" t="s">
-        <v>305</v>
-      </c>
-      <c r="F81" s="30">
-        <v>21765430</v>
-      </c>
-      <c r="G81" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F81),0)&gt;0), MAX($G$1:G80)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D81" s="36">
+        <v>3.4</v>
+      </c>
+      <c r="E81" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="F81" s="36" t="s">
+        <v>334</v>
+      </c>
+      <c r="G81" s="29"/>
       <c r="H81" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A81=C81</f>
         <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A82" s="30">
+      <c r="A82" s="36">
         <v>20</v>
       </c>
-      <c r="B82" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="C82" s="32">
+      <c r="B82" s="37" t="s">
+        <v>331</v>
+      </c>
+      <c r="C82" s="38">
         <v>20</v>
       </c>
-      <c r="D82" s="30" t="s">
-        <v>210</v>
-      </c>
-      <c r="E82" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F82" s="30" t="s">
-        <v>137</v>
-      </c>
-      <c r="G82" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F82),0)&gt;0), MAX($G$1:G81)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D82" s="36">
+        <v>3.3</v>
+      </c>
+      <c r="E82" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="F82" s="36" t="s">
+        <v>332</v>
+      </c>
+      <c r="G82" s="29"/>
       <c r="H82" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A82=C82</f>
         <v>1</v>
       </c>
     </row>
@@ -3939,26 +3957,26 @@
         <v>20</v>
       </c>
       <c r="B83" s="31" t="s">
-        <v>265</v>
+        <v>138</v>
       </c>
       <c r="C83" s="32">
         <v>20</v>
       </c>
       <c r="D83" s="30" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E83" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F83" s="30" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G83" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F83),0)&gt;0), MAX($G$1:G82)+1, ""))</f>
         <v/>
       </c>
       <c r="H83" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A83=C83</f>
         <v>1</v>
       </c>
     </row>
@@ -3967,26 +3985,26 @@
         <v>20</v>
       </c>
       <c r="B84" s="31" t="s">
-        <v>133</v>
+        <v>255</v>
       </c>
       <c r="C84" s="32">
         <v>20</v>
       </c>
       <c r="D84" s="30" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="E84" s="31" t="s">
-        <v>305</v>
+        <v>8</v>
       </c>
       <c r="F84" s="30" t="s">
-        <v>134</v>
+        <v>256</v>
       </c>
       <c r="G84" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F84),0)&gt;0), MAX($G$1:G83)+1, ""))</f>
         <v/>
       </c>
       <c r="H84" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A84=C84</f>
         <v>1</v>
       </c>
     </row>
@@ -3995,54 +4013,54 @@
         <v>20</v>
       </c>
       <c r="B85" s="31" t="s">
-        <v>130</v>
+        <v>254</v>
       </c>
       <c r="C85" s="32">
         <v>20</v>
       </c>
-      <c r="D85" s="30" t="s">
-        <v>214</v>
+      <c r="D85" s="30">
+        <v>4.2</v>
       </c>
       <c r="E85" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="F85" s="30" t="s">
-        <v>132</v>
+        <v>305</v>
+      </c>
+      <c r="F85" s="30">
+        <v>21765430</v>
       </c>
       <c r="G85" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F85),0)&gt;0), MAX($G$1:G84)+1, ""))</f>
         <v/>
       </c>
       <c r="H85" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A85=C85</f>
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A86" s="26">
+      <c r="A86" s="30">
         <v>20</v>
       </c>
-      <c r="B86" s="27" t="s">
-        <v>312</v>
-      </c>
-      <c r="C86" s="28">
+      <c r="B86" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="C86" s="32">
         <v>20</v>
       </c>
-      <c r="D86" s="26">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="E86" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="F86" s="26" t="s">
-        <v>318</v>
+      <c r="D86" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="E86" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F86" s="30" t="s">
+        <v>137</v>
       </c>
       <c r="G86" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F86),0)&gt;0), MAX($G$1:G85)+1, ""))</f>
         <v/>
       </c>
       <c r="H86" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A86=C86</f>
         <v>1</v>
       </c>
     </row>
@@ -4051,26 +4069,26 @@
         <v>20</v>
       </c>
       <c r="B87" s="31" t="s">
-        <v>128</v>
+        <v>265</v>
       </c>
       <c r="C87" s="32">
         <v>20</v>
       </c>
       <c r="D87" s="30" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E87" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F87" s="30" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="G87" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F87),0)&gt;0), MAX($G$1:G86)+1, ""))</f>
         <v/>
       </c>
       <c r="H87" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A87=C87</f>
         <v>1</v>
       </c>
     </row>
@@ -4079,82 +4097,82 @@
         <v>20</v>
       </c>
       <c r="B88" s="31" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C88" s="32">
         <v>20</v>
       </c>
       <c r="D88" s="30" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="E88" s="31" t="s">
         <v>305</v>
       </c>
       <c r="F88" s="30" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="G88" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F88),0)&gt;0), MAX($G$1:G87)+1, ""))</f>
         <v/>
       </c>
       <c r="H88" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A88=C88</f>
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A89" s="26">
+      <c r="A89" s="30">
         <v>20</v>
       </c>
-      <c r="B89" s="27" t="s">
-        <v>350</v>
-      </c>
-      <c r="C89" s="28">
+      <c r="B89" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="C89" s="32">
         <v>20</v>
       </c>
-      <c r="D89" s="26">
-        <v>2.7</v>
-      </c>
-      <c r="E89" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="F89" s="26" t="s">
-        <v>353</v>
+      <c r="D89" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="E89" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="F89" s="30" t="s">
+        <v>132</v>
       </c>
       <c r="G89" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F89),0)&gt;0), MAX($G$1:G88)+1, ""))</f>
         <v/>
       </c>
       <c r="H89" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A89=C89</f>
         <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A90" s="30">
+      <c r="A90" s="26">
         <v>20</v>
       </c>
-      <c r="B90" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="C90" s="32">
+      <c r="B90" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="C90" s="28">
         <v>20</v>
       </c>
-      <c r="D90" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="E90" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F90" s="30" t="s">
-        <v>125</v>
+      <c r="D90" s="26">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E90" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F90" s="26" t="s">
+        <v>318</v>
       </c>
       <c r="G90" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F90),0)&gt;0), MAX($G$1:G89)+1, ""))</f>
         <v/>
       </c>
       <c r="H90" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A90=C90</f>
         <v>1</v>
       </c>
     </row>
@@ -4163,26 +4181,26 @@
         <v>20</v>
       </c>
       <c r="B91" s="31" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C91" s="32">
         <v>20</v>
       </c>
       <c r="D91" s="30" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="E91" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F91" s="30" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="G91" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F91),0)&gt;0), MAX($G$1:G90)+1, ""))</f>
         <v/>
       </c>
       <c r="H91" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A91=C91</f>
         <v>1</v>
       </c>
     </row>
@@ -4191,54 +4209,54 @@
         <v>20</v>
       </c>
       <c r="B92" s="31" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C92" s="32">
         <v>20</v>
       </c>
       <c r="D92" s="30" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="E92" s="31" t="s">
         <v>305</v>
       </c>
       <c r="F92" s="30" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="G92" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F92),0)&gt;0), MAX($G$1:G91)+1, ""))</f>
         <v/>
       </c>
       <c r="H92" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A92=C92</f>
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A93" s="30">
+      <c r="A93" s="26">
         <v>20</v>
       </c>
-      <c r="B93" s="31" t="s">
-        <v>257</v>
-      </c>
-      <c r="C93" s="32">
+      <c r="B93" s="27" t="s">
+        <v>350</v>
+      </c>
+      <c r="C93" s="28">
         <v>20</v>
       </c>
-      <c r="D93" s="30" t="s">
-        <v>225</v>
-      </c>
-      <c r="E93" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F93" s="30" t="s">
-        <v>258</v>
+      <c r="D93" s="26">
+        <v>2.7</v>
+      </c>
+      <c r="E93" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="F93" s="26" t="s">
+        <v>353</v>
       </c>
       <c r="G93" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F93),0)&gt;0), MAX($G$1:G92)+1, ""))</f>
         <v/>
       </c>
       <c r="H93" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A93=C93</f>
         <v>1</v>
       </c>
     </row>
@@ -4247,26 +4265,26 @@
         <v>20</v>
       </c>
       <c r="B94" s="31" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C94" s="32">
         <v>20</v>
       </c>
       <c r="D94" s="30" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E94" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F94" s="30" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="G94" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F94),0)&gt;0), MAX($G$1:G93)+1, ""))</f>
         <v/>
       </c>
       <c r="H94" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A94=C94</f>
         <v>1</v>
       </c>
     </row>
@@ -4275,26 +4293,26 @@
         <v>20</v>
       </c>
       <c r="B95" s="31" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C95" s="32">
         <v>20</v>
       </c>
       <c r="D95" s="30" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="E95" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F95" s="30" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="G95" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F95),0)&gt;0), MAX($G$1:G94)+1, ""))</f>
         <v/>
       </c>
       <c r="H95" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A95=C95</f>
         <v>1</v>
       </c>
     </row>
@@ -4303,26 +4321,26 @@
         <v>20</v>
       </c>
       <c r="B96" s="31" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C96" s="32">
         <v>20</v>
       </c>
       <c r="D96" s="30" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="E96" s="31" t="s">
-        <v>8</v>
+        <v>305</v>
       </c>
       <c r="F96" s="30" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G96" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F96),0)&gt;0), MAX($G$1:G95)+1, ""))</f>
         <v/>
       </c>
       <c r="H96" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A96=C96</f>
         <v>1</v>
       </c>
     </row>
@@ -4331,26 +4349,26 @@
         <v>20</v>
       </c>
       <c r="B97" s="27" t="s">
-        <v>297</v>
+        <v>371</v>
       </c>
       <c r="C97" s="28">
         <v>20</v>
       </c>
       <c r="D97" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E97" s="27" t="s">
+        <v>1.5</v>
+      </c>
+      <c r="E97" s="31" t="s">
         <v>299</v>
       </c>
       <c r="F97" s="26" t="s">
-        <v>298</v>
+        <v>372</v>
       </c>
       <c r="G97" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F97),0)&gt;0), MAX($G$1:G96)+1, ""))</f>
         <v/>
       </c>
       <c r="H97" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A97=C97</f>
         <v>1</v>
       </c>
     </row>
@@ -4359,26 +4377,26 @@
         <v>20</v>
       </c>
       <c r="B98" s="31" t="s">
-        <v>112</v>
+        <v>257</v>
       </c>
       <c r="C98" s="32">
         <v>20</v>
       </c>
       <c r="D98" s="30" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="E98" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F98" s="30" t="s">
-        <v>113</v>
+        <v>258</v>
       </c>
       <c r="G98" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F98),0)&gt;0), MAX($G$1:G97)+1, ""))</f>
         <v/>
       </c>
       <c r="H98" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A98=C98</f>
         <v>1</v>
       </c>
     </row>
@@ -4387,26 +4405,26 @@
         <v>20</v>
       </c>
       <c r="B99" s="31" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="C99" s="32">
         <v>20</v>
       </c>
       <c r="D99" s="30" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="E99" s="31" t="s">
-        <v>299</v>
+        <v>8</v>
       </c>
       <c r="F99" s="30" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="G99" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F99),0)&gt;0), MAX($G$1:G98)+1, ""))</f>
         <v/>
       </c>
       <c r="H99" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A99=C99</f>
         <v>1</v>
       </c>
     </row>
@@ -4415,51 +4433,54 @@
         <v>20</v>
       </c>
       <c r="B100" s="31" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C100" s="32">
         <v>20</v>
       </c>
       <c r="D100" s="30" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="E100" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F100" s="30" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="G100" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F100),0)&gt;0), MAX($G$1:G99)+1, ""))</f>
         <v/>
       </c>
       <c r="H100" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A100=C100</f>
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A101" s="36">
+      <c r="A101" s="30">
         <v>20</v>
       </c>
-      <c r="B101" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="C101" s="38">
+      <c r="B101" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="C101" s="32">
         <v>20</v>
       </c>
-      <c r="D101" s="36">
-        <v>3</v>
-      </c>
-      <c r="E101" s="37" t="s">
-        <v>304</v>
-      </c>
-      <c r="F101" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="G101" s="29"/>
+      <c r="D101" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="E101" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="30" t="s">
+        <v>115</v>
+      </c>
+      <c r="G101" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F101),0)&gt;0), MAX($G$1:G100)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H101" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A101=C101</f>
         <v>1</v>
       </c>
     </row>
@@ -4468,7 +4489,7 @@
         <v>20</v>
       </c>
       <c r="B102" s="27" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C102" s="28">
         <v>20</v>
@@ -4480,14 +4501,14 @@
         <v>299</v>
       </c>
       <c r="F102" s="26" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G102" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F102),0)&gt;0), MAX($G$1:G101)+1, ""))</f>
         <v/>
       </c>
       <c r="H102" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A102=C102</f>
         <v>1</v>
       </c>
     </row>
@@ -4496,26 +4517,26 @@
         <v>20</v>
       </c>
       <c r="B103" s="31" t="s">
-        <v>368</v>
+        <v>112</v>
       </c>
       <c r="C103" s="32">
         <v>20</v>
       </c>
-      <c r="D103" s="30">
-        <v>2.4</v>
+      <c r="D103" s="30" t="s">
+        <v>219</v>
       </c>
       <c r="E103" s="31" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="F103" s="30" t="s">
-        <v>369</v>
+        <v>113</v>
       </c>
       <c r="G103" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F103),0)&gt;0), MAX($G$1:G102)+1, ""))</f>
         <v/>
       </c>
       <c r="H103" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A103=C103</f>
         <v>1</v>
       </c>
     </row>
@@ -4524,54 +4545,54 @@
         <v>20</v>
       </c>
       <c r="B104" s="31" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C104" s="32">
         <v>20</v>
       </c>
       <c r="D104" s="30" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E104" s="31" t="s">
-        <v>60</v>
+        <v>299</v>
       </c>
       <c r="F104" s="30" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G104" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F104),0)&gt;0), MAX($G$1:G103)+1, ""))</f>
         <v/>
       </c>
       <c r="H104" s="21" t="b">
-        <f t="shared" si="2"/>
+        <f>A104=C104</f>
         <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A105" s="26">
+      <c r="A105" s="30">
         <v>20</v>
       </c>
-      <c r="B105" s="27" t="s">
-        <v>339</v>
-      </c>
-      <c r="C105" s="28">
+      <c r="B105" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="C105" s="32">
         <v>20</v>
       </c>
-      <c r="D105" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E105" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F105" s="26" t="s">
-        <v>344</v>
+      <c r="D105" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="E105" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F105" s="30" t="s">
+        <v>109</v>
       </c>
       <c r="G105" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F105),0)&gt;0), MAX($G$1:G104)+1, ""))</f>
         <v/>
       </c>
       <c r="H105" s="21" t="b">
-        <f t="shared" ref="H105:H136" si="3">A105=C105</f>
+        <f>A105=C105</f>
         <v>1</v>
       </c>
     </row>
@@ -4580,51 +4601,51 @@
         <v>20</v>
       </c>
       <c r="B106" s="37" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C106" s="38">
         <v>20</v>
       </c>
       <c r="D106" s="36">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="E106" s="37" t="s">
-        <v>336</v>
+        <v>304</v>
       </c>
       <c r="F106" s="36" t="s">
-        <v>332</v>
+        <v>105</v>
       </c>
       <c r="G106" s="29"/>
       <c r="H106" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A106=C106</f>
         <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A107" s="30">
+      <c r="A107" s="26">
         <v>20</v>
       </c>
-      <c r="B107" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="C107" s="32">
+      <c r="B107" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C107" s="28">
         <v>20</v>
       </c>
-      <c r="D107" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E107" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F107" s="30" t="s">
-        <v>102</v>
+      <c r="D107" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E107" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="F107" s="26" t="s">
+        <v>301</v>
       </c>
       <c r="G107" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F107),0)&gt;0), MAX($G$1:G106)+1, ""))</f>
         <v/>
       </c>
       <c r="H107" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A107=C107</f>
         <v>1</v>
       </c>
     </row>
@@ -4633,26 +4654,26 @@
         <v>20</v>
       </c>
       <c r="B108" s="31" t="s">
-        <v>263</v>
+        <v>368</v>
       </c>
       <c r="C108" s="32">
         <v>20</v>
       </c>
       <c r="D108" s="30">
-        <v>6.2</v>
+        <v>2.4</v>
       </c>
       <c r="E108" s="31" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F108" s="30" t="s">
-        <v>264</v>
+        <v>369</v>
       </c>
       <c r="G108" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F108),0)&gt;0), MAX($G$1:G107)+1, ""))</f>
         <v/>
       </c>
       <c r="H108" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A108=C108</f>
         <v>1</v>
       </c>
     </row>
@@ -4661,26 +4682,26 @@
         <v>20</v>
       </c>
       <c r="B109" s="31" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C109" s="32">
         <v>20</v>
       </c>
       <c r="D109" s="30" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E109" s="31" t="s">
-        <v>299</v>
+        <v>60</v>
       </c>
       <c r="F109" s="30" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G109" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F109),0)&gt;0), MAX($G$1:G108)+1, ""))</f>
         <v/>
       </c>
       <c r="H109" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A109=C109</f>
         <v>1</v>
       </c>
     </row>
@@ -4689,82 +4710,79 @@
         <v>20</v>
       </c>
       <c r="B110" s="27" t="s">
-        <v>300</v>
+        <v>339</v>
       </c>
       <c r="C110" s="28">
         <v>20</v>
       </c>
       <c r="D110" s="26">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="E110" s="27" t="s">
-        <v>299</v>
+        <v>81</v>
       </c>
       <c r="F110" s="26" t="s">
-        <v>301</v>
+        <v>344</v>
       </c>
       <c r="G110" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F110),0)&gt;0), MAX($G$1:G109)+1, ""))</f>
         <v/>
       </c>
       <c r="H110" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A110=C110</f>
         <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A111" s="30">
+      <c r="A111" s="36">
         <v>20</v>
       </c>
-      <c r="B111" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="C111" s="32">
+      <c r="B111" s="37" t="s">
+        <v>335</v>
+      </c>
+      <c r="C111" s="38">
         <v>20</v>
       </c>
-      <c r="D111" s="30" t="s">
-        <v>216</v>
-      </c>
-      <c r="E111" s="31" t="s">
+      <c r="D111" s="36">
+        <v>3.2</v>
+      </c>
+      <c r="E111" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="F111" s="36" t="s">
+        <v>332</v>
+      </c>
+      <c r="G111" s="29"/>
+      <c r="H111" s="21" t="b">
+        <f>A111=C111</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A112" s="30">
+        <v>20</v>
+      </c>
+      <c r="B112" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="C112" s="32">
+        <v>20</v>
+      </c>
+      <c r="D112" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E112" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F111" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="G111" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F111),0)&gt;0), MAX($G$1:G110)+1, ""))</f>
-        <v/>
-      </c>
-      <c r="H111" s="21" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A112" s="26">
-        <v>20</v>
-      </c>
-      <c r="B112" s="27" t="s">
-        <v>357</v>
-      </c>
-      <c r="C112" s="28">
-        <v>20</v>
-      </c>
-      <c r="D112" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E112" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F112" s="26" t="s">
-        <v>358</v>
+      <c r="F112" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G112" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F112),0)&gt;0), MAX($G$1:G111)+1, ""))</f>
         <v/>
       </c>
       <c r="H112" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A112=C112</f>
         <v>1</v>
       </c>
     </row>
@@ -4773,26 +4791,26 @@
         <v>20</v>
       </c>
       <c r="B113" s="31" t="s">
-        <v>91</v>
+        <v>263</v>
       </c>
       <c r="C113" s="32">
         <v>20</v>
       </c>
-      <c r="D113" s="30" t="s">
-        <v>218</v>
+      <c r="D113" s="30">
+        <v>6.2</v>
       </c>
       <c r="E113" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F113" s="30" t="s">
-        <v>92</v>
+        <v>264</v>
       </c>
       <c r="G113" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F113),0)&gt;0), MAX($G$1:G112)+1, ""))</f>
         <v/>
       </c>
       <c r="H113" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A113=C113</f>
         <v>1</v>
       </c>
     </row>
@@ -4801,54 +4819,54 @@
         <v>20</v>
       </c>
       <c r="B114" s="31" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C114" s="32">
         <v>20</v>
       </c>
       <c r="D114" s="30" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="E114" s="31" t="s">
-        <v>8</v>
+        <v>299</v>
       </c>
       <c r="F114" s="30" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G114" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F114),0)&gt;0), MAX($G$1:G113)+1, ""))</f>
         <v/>
       </c>
       <c r="H114" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A114=C114</f>
         <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A115" s="30">
+      <c r="A115" s="26">
         <v>20</v>
       </c>
-      <c r="B115" s="31" t="s">
-        <v>290</v>
-      </c>
-      <c r="C115" s="32">
+      <c r="B115" s="27" t="s">
+        <v>300</v>
+      </c>
+      <c r="C115" s="28">
         <v>20</v>
       </c>
-      <c r="D115" s="30">
-        <v>1.8</v>
-      </c>
-      <c r="E115" s="31" t="s">
-        <v>291</v>
-      </c>
-      <c r="F115" s="30" t="s">
-        <v>90</v>
+      <c r="D115" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E115" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="F115" s="26" t="s">
+        <v>301</v>
       </c>
       <c r="G115" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F115),0)&gt;0), MAX($G$1:G114)+1, ""))</f>
         <v/>
       </c>
       <c r="H115" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A115=C115</f>
         <v>1</v>
       </c>
     </row>
@@ -4857,54 +4875,54 @@
         <v>20</v>
       </c>
       <c r="B116" s="31" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C116" s="32">
         <v>20</v>
       </c>
       <c r="D116" s="30" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="E116" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F116" s="30" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G116" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F116),0)&gt;0), MAX($G$1:G115)+1, ""))</f>
         <v/>
       </c>
       <c r="H116" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A116=C116</f>
         <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A117" s="30">
+      <c r="A117" s="26">
         <v>20</v>
       </c>
-      <c r="B117" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="C117" s="32">
+      <c r="B117" s="27" t="s">
+        <v>357</v>
+      </c>
+      <c r="C117" s="28">
         <v>20</v>
       </c>
-      <c r="D117" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="E117" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F117" s="30" t="s">
-        <v>86</v>
+      <c r="D117" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E117" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F117" s="26" t="s">
+        <v>358</v>
       </c>
       <c r="G117" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F117),0)&gt;0), MAX($G$1:G116)+1, ""))</f>
         <v/>
       </c>
       <c r="H117" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A117=C117</f>
         <v>1</v>
       </c>
     </row>
@@ -4913,7 +4931,7 @@
         <v>20</v>
       </c>
       <c r="B118" s="31" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="C118" s="32">
         <v>20</v>
@@ -4922,17 +4940,17 @@
         <v>218</v>
       </c>
       <c r="E118" s="31" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F118" s="30" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="G118" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F118),0)&gt;0), MAX($G$1:G117)+1, ""))</f>
         <v/>
       </c>
       <c r="H118" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A118=C118</f>
         <v>1</v>
       </c>
     </row>
@@ -4941,26 +4959,26 @@
         <v>20</v>
       </c>
       <c r="B119" s="31" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C119" s="32">
         <v>20</v>
       </c>
       <c r="D119" s="30" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="E119" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F119" s="30" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G119" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F119),0)&gt;0), MAX($G$1:G118)+1, ""))</f>
         <v/>
       </c>
       <c r="H119" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A119=C119</f>
         <v>1</v>
       </c>
     </row>
@@ -4969,166 +4987,166 @@
         <v>20</v>
       </c>
       <c r="B120" s="31" t="s">
-        <v>76</v>
+        <v>290</v>
       </c>
       <c r="C120" s="32">
         <v>20</v>
       </c>
-      <c r="D120" s="30" t="s">
-        <v>216</v>
+      <c r="D120" s="30">
+        <v>1.8</v>
       </c>
       <c r="E120" s="31" t="s">
-        <v>8</v>
+        <v>291</v>
       </c>
       <c r="F120" s="30" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="G120" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F120),0)&gt;0), MAX($G$1:G119)+1, ""))</f>
         <v/>
       </c>
       <c r="H120" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A120=C120</f>
         <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A121" s="26">
-        <v>25</v>
-      </c>
-      <c r="B121" s="27" t="s">
-        <v>178</v>
-      </c>
-      <c r="C121" s="28">
-        <v>25</v>
-      </c>
-      <c r="D121" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="E121" s="27" t="s">
+      <c r="A121" s="30">
+        <v>20</v>
+      </c>
+      <c r="B121" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="C121" s="32">
+        <v>20</v>
+      </c>
+      <c r="D121" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="E121" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F121" s="26" t="s">
-        <v>179</v>
+      <c r="F121" s="30" t="s">
+        <v>88</v>
       </c>
       <c r="G121" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F121),0)&gt;0), MAX($G$1:G120)+1, ""))</f>
         <v/>
       </c>
       <c r="H121" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A121=C121</f>
         <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A122" s="26">
-        <v>25</v>
-      </c>
-      <c r="B122" s="27" t="s">
-        <v>176</v>
-      </c>
-      <c r="C122" s="28">
-        <v>25</v>
-      </c>
-      <c r="D122" s="26" t="s">
-        <v>237</v>
-      </c>
-      <c r="E122" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="F122" s="26" t="s">
-        <v>177</v>
+      <c r="A122" s="30">
+        <v>20</v>
+      </c>
+      <c r="B122" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="C122" s="32">
+        <v>20</v>
+      </c>
+      <c r="D122" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="E122" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F122" s="30" t="s">
+        <v>86</v>
       </c>
       <c r="G122" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F122),0)&gt;0), MAX($G$1:G121)+1, ""))</f>
         <v/>
       </c>
       <c r="H122" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A122=C122</f>
         <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A123" s="26">
-        <v>25</v>
-      </c>
-      <c r="B123" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="C123" s="28">
-        <v>25</v>
-      </c>
-      <c r="D123" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="E123" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="F123" s="26" t="s">
-        <v>175</v>
+      <c r="A123" s="30">
+        <v>20</v>
+      </c>
+      <c r="B123" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="C123" s="32">
+        <v>20</v>
+      </c>
+      <c r="D123" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="E123" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="F123" s="30" t="s">
+        <v>82</v>
       </c>
       <c r="G123" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F123),0)&gt;0), MAX($G$1:G122)+1, ""))</f>
         <v/>
       </c>
       <c r="H123" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A123=C123</f>
         <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A124" s="26">
-        <v>25</v>
-      </c>
-      <c r="B124" s="27" t="s">
-        <v>173</v>
-      </c>
-      <c r="C124" s="28">
-        <v>25</v>
-      </c>
-      <c r="D124" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="E124" s="27" t="s">
+      <c r="A124" s="30">
+        <v>20</v>
+      </c>
+      <c r="B124" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="C124" s="32">
+        <v>20</v>
+      </c>
+      <c r="D124" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="E124" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F124" s="26" t="s">
-        <v>324</v>
+      <c r="F124" s="30" t="s">
+        <v>79</v>
       </c>
       <c r="G124" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F124),0)&gt;0), MAX($G$1:G123)+1, ""))</f>
         <v/>
       </c>
       <c r="H124" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A124=C124</f>
         <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A125" s="26">
-        <v>25</v>
-      </c>
-      <c r="B125" s="27" t="s">
-        <v>361</v>
-      </c>
-      <c r="C125" s="28">
-        <v>25</v>
-      </c>
-      <c r="D125" s="26">
-        <v>3</v>
-      </c>
-      <c r="E125" s="27" t="s">
+      <c r="A125" s="30">
+        <v>20</v>
+      </c>
+      <c r="B125" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="C125" s="32">
+        <v>20</v>
+      </c>
+      <c r="D125" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="E125" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F125" s="26" t="s">
-        <v>362</v>
+      <c r="F125" s="30" t="s">
+        <v>77</v>
       </c>
       <c r="G125" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F125),0)&gt;0), MAX($G$1:G124)+1, ""))</f>
         <v/>
       </c>
       <c r="H125" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A125=C125</f>
         <v>1</v>
       </c>
     </row>
@@ -5137,82 +5155,82 @@
         <v>25</v>
       </c>
       <c r="B126" s="27" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C126" s="28">
         <v>25</v>
       </c>
-      <c r="D126" s="26">
-        <v>2.7</v>
+      <c r="D126" s="26" t="s">
+        <v>225</v>
       </c>
       <c r="E126" s="27" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F126" s="26" t="s">
-        <v>338</v>
+        <v>179</v>
       </c>
       <c r="G126" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F126),0)&gt;0), MAX($G$1:G125)+1, ""))</f>
         <v/>
       </c>
       <c r="H126" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A126=C126</f>
         <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A127" s="30">
+      <c r="A127" s="26">
         <v>25</v>
       </c>
-      <c r="B127" s="31" t="s">
-        <v>284</v>
-      </c>
-      <c r="C127" s="32">
+      <c r="B127" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="C127" s="28">
         <v>25</v>
       </c>
-      <c r="D127" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E127" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F127" s="30" t="s">
-        <v>102</v>
+      <c r="D127" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="E127" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="F127" s="26" t="s">
+        <v>177</v>
       </c>
       <c r="G127" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F127),0)&gt;0), MAX($G$1:G126)+1, ""))</f>
         <v/>
       </c>
       <c r="H127" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A127=C127</f>
         <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A128" s="30">
+      <c r="A128" s="26">
         <v>25</v>
       </c>
-      <c r="B128" s="31" t="s">
-        <v>282</v>
-      </c>
-      <c r="C128" s="32">
+      <c r="B128" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="C128" s="28">
         <v>25</v>
       </c>
-      <c r="D128" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E128" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F128" s="30" t="s">
-        <v>102</v>
+      <c r="D128" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="E128" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="F128" s="26" t="s">
+        <v>175</v>
       </c>
       <c r="G128" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F128),0)&gt;0), MAX($G$1:G127)+1, ""))</f>
         <v/>
       </c>
       <c r="H128" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A128=C128</f>
         <v>1</v>
       </c>
     </row>
@@ -5221,26 +5239,26 @@
         <v>25</v>
       </c>
       <c r="B129" s="27" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C129" s="28">
         <v>25</v>
       </c>
       <c r="D129" s="26" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="E129" s="27" t="s">
-        <v>245</v>
+        <v>8</v>
       </c>
       <c r="F129" s="26" t="s">
-        <v>171</v>
+        <v>324</v>
       </c>
       <c r="G129" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F129),0)&gt;0), MAX($G$1:G128)+1, ""))</f>
         <v/>
       </c>
       <c r="H129" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A129=C129</f>
         <v>1</v>
       </c>
     </row>
@@ -5249,26 +5267,26 @@
         <v>25</v>
       </c>
       <c r="B130" s="27" t="s">
-        <v>168</v>
+        <v>361</v>
       </c>
       <c r="C130" s="28">
         <v>25</v>
       </c>
-      <c r="D130" s="26" t="s">
-        <v>217</v>
+      <c r="D130" s="26">
+        <v>3</v>
       </c>
       <c r="E130" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F130" s="26" t="s">
-        <v>169</v>
+        <v>362</v>
       </c>
       <c r="G130" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F130),0)&gt;0), MAX($G$1:G129)+1, ""))</f>
         <v/>
       </c>
       <c r="H130" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A130=C130</f>
         <v>1</v>
       </c>
     </row>
@@ -5277,26 +5295,26 @@
         <v>25</v>
       </c>
       <c r="B131" s="27" t="s">
-        <v>359</v>
+        <v>172</v>
       </c>
       <c r="C131" s="28">
         <v>25</v>
       </c>
       <c r="D131" s="26">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="E131" s="27" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="F131" s="26" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="G131" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F131),0)&gt;0), MAX($G$1:G130)+1, ""))</f>
         <v/>
       </c>
       <c r="H131" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A131=C131</f>
         <v>1</v>
       </c>
     </row>
@@ -5305,7 +5323,7 @@
         <v>25</v>
       </c>
       <c r="B132" s="31" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C132" s="32">
         <v>25</v>
@@ -5314,7 +5332,7 @@
         <v>207</v>
       </c>
       <c r="E132" s="31" t="s">
-        <v>8</v>
+        <v>283</v>
       </c>
       <c r="F132" s="30" t="s">
         <v>102</v>
@@ -5324,35 +5342,35 @@
         <v/>
       </c>
       <c r="H132" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A132=C132</f>
         <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A133" s="26">
+      <c r="A133" s="30">
         <v>25</v>
       </c>
-      <c r="B133" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="C133" s="28">
+      <c r="B133" s="31" t="s">
+        <v>282</v>
+      </c>
+      <c r="C133" s="32">
         <v>25</v>
       </c>
-      <c r="D133" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="E133" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="F133" s="26" t="s">
-        <v>167</v>
+      <c r="D133" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E133" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="F133" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G133" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F133),0)&gt;0), MAX($G$1:G132)+1, ""))</f>
         <v/>
       </c>
       <c r="H133" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A133=C133</f>
         <v>1</v>
       </c>
     </row>
@@ -5361,26 +5379,26 @@
         <v>25</v>
       </c>
       <c r="B134" s="27" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C134" s="28">
         <v>25</v>
       </c>
       <c r="D134" s="26" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E134" s="27" t="s">
-        <v>131</v>
+        <v>245</v>
       </c>
       <c r="F134" s="26" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="G134" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F134),0)&gt;0), MAX($G$1:G133)+1, ""))</f>
         <v/>
       </c>
       <c r="H134" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A134=C134</f>
         <v>1</v>
       </c>
     </row>
@@ -5389,26 +5407,26 @@
         <v>25</v>
       </c>
       <c r="B135" s="27" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="C135" s="28">
         <v>25</v>
       </c>
       <c r="D135" s="26" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="E135" s="27" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F135" s="26" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="G135" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F135),0)&gt;0), MAX($G$1:G134)+1, ""))</f>
         <v/>
       </c>
       <c r="H135" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A135=C135</f>
         <v>1</v>
       </c>
     </row>
@@ -5417,54 +5435,54 @@
         <v>25</v>
       </c>
       <c r="B136" s="27" t="s">
-        <v>160</v>
+        <v>359</v>
       </c>
       <c r="C136" s="28">
         <v>25</v>
       </c>
-      <c r="D136" s="26" t="s">
-        <v>236</v>
+      <c r="D136" s="26">
+        <v>3.4</v>
       </c>
       <c r="E136" s="27" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F136" s="26" t="s">
-        <v>161</v>
+        <v>360</v>
       </c>
       <c r="G136" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F136),0)&gt;0), MAX($G$1:G135)+1, ""))</f>
         <v/>
       </c>
       <c r="H136" s="21" t="b">
-        <f t="shared" si="3"/>
+        <f>A136=C136</f>
         <v>1</v>
       </c>
     </row>
     <row r="137" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A137" s="26">
+      <c r="A137" s="30">
         <v>25</v>
       </c>
-      <c r="B137" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="C137" s="28">
+      <c r="B137" s="31" t="s">
+        <v>278</v>
+      </c>
+      <c r="C137" s="32">
         <v>25</v>
       </c>
-      <c r="D137" s="26" t="s">
-        <v>228</v>
-      </c>
-      <c r="E137" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F137" s="26" t="s">
-        <v>159</v>
+      <c r="D137" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E137" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F137" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G137" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F137),0)&gt;0), MAX($G$1:G136)+1, ""))</f>
         <v/>
       </c>
       <c r="H137" s="21" t="b">
-        <f t="shared" ref="H137:H163" si="4">A137=C137</f>
+        <f>A137=C137</f>
         <v>1</v>
       </c>
     </row>
@@ -5473,26 +5491,26 @@
         <v>25</v>
       </c>
       <c r="B138" s="27" t="s">
-        <v>342</v>
+        <v>166</v>
       </c>
       <c r="C138" s="28">
         <v>25</v>
       </c>
-      <c r="D138" s="26">
-        <v>3.4</v>
+      <c r="D138" s="26" t="s">
+        <v>221</v>
       </c>
       <c r="E138" s="27" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="F138" s="26" t="s">
-        <v>343</v>
+        <v>167</v>
       </c>
       <c r="G138" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F138),0)&gt;0), MAX($G$1:G137)+1, ""))</f>
         <v/>
       </c>
       <c r="H138" s="21" t="b">
-        <f t="shared" si="4"/>
+        <f>A138=C138</f>
         <v>1</v>
       </c>
     </row>
@@ -5501,26 +5519,26 @@
         <v>25</v>
       </c>
       <c r="B139" s="27" t="s">
-        <v>310</v>
+        <v>164</v>
       </c>
       <c r="C139" s="28">
         <v>25</v>
       </c>
-      <c r="D139" s="26">
-        <v>3.9</v>
+      <c r="D139" s="26" t="s">
+        <v>229</v>
       </c>
       <c r="E139" s="27" t="s">
-        <v>309</v>
+        <v>131</v>
       </c>
       <c r="F139" s="26" t="s">
-        <v>311</v>
+        <v>165</v>
       </c>
       <c r="G139" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F139),0)&gt;0), MAX($G$1:G137)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F139),0)&gt;0), MAX($G$1:G138)+1, ""))</f>
         <v/>
       </c>
       <c r="H139" s="21" t="b">
-        <f t="shared" si="4"/>
+        <f>A139=C139</f>
         <v>1</v>
       </c>
     </row>
@@ -5529,26 +5547,26 @@
         <v>25</v>
       </c>
       <c r="B140" s="27" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C140" s="28">
         <v>25</v>
       </c>
       <c r="D140" s="26" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="E140" s="27" t="s">
         <v>81</v>
       </c>
       <c r="F140" s="26" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="G140" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F140),0)&gt;0), MAX($G$1:G139)+1, ""))</f>
         <v/>
       </c>
       <c r="H140" s="21" t="b">
-        <f t="shared" si="4"/>
+        <f>A140=C140</f>
         <v>1</v>
       </c>
     </row>
@@ -5557,26 +5575,26 @@
         <v>25</v>
       </c>
       <c r="B141" s="27" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="C141" s="28">
         <v>25</v>
       </c>
       <c r="D141" s="26" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E141" s="27" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="F141" s="26" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="G141" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F141),0)&gt;0), MAX($G$1:G140)+1, ""))</f>
         <v/>
       </c>
       <c r="H141" s="21" t="b">
-        <f t="shared" si="4"/>
+        <f>A141=C141</f>
         <v>1</v>
       </c>
     </row>
@@ -5585,26 +5603,26 @@
         <v>25</v>
       </c>
       <c r="B142" s="27" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C142" s="28">
         <v>25</v>
       </c>
       <c r="D142" s="26" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E142" s="27" t="s">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="F142" s="26" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="G142" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F142),0)&gt;0), MAX($G$1:G141)+1, ""))</f>
         <v/>
       </c>
       <c r="H142" s="21" t="b">
-        <f t="shared" si="4"/>
+        <f>A142=C142</f>
         <v>1</v>
       </c>
     </row>
@@ -5613,26 +5631,26 @@
         <v>25</v>
       </c>
       <c r="B143" s="27" t="s">
-        <v>247</v>
+        <v>342</v>
       </c>
       <c r="C143" s="28">
         <v>25</v>
       </c>
-      <c r="D143" s="39" t="s">
-        <v>229</v>
+      <c r="D143" s="26">
+        <v>3.4</v>
       </c>
       <c r="E143" s="27" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="F143" s="26" t="s">
-        <v>248</v>
+        <v>343</v>
       </c>
       <c r="G143" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F143),0)&gt;0), MAX($G$1:G142)+1, ""))</f>
         <v/>
       </c>
       <c r="H143" s="21" t="b">
-        <f t="shared" si="4"/>
+        <f>A143=C143</f>
         <v>1</v>
       </c>
     </row>
@@ -5641,110 +5659,110 @@
         <v>25</v>
       </c>
       <c r="B144" s="27" t="s">
-        <v>150</v>
+        <v>310</v>
       </c>
       <c r="C144" s="28">
         <v>25</v>
       </c>
-      <c r="D144" s="26" t="s">
-        <v>235</v>
+      <c r="D144" s="26">
+        <v>3.9</v>
       </c>
       <c r="E144" s="27" t="s">
-        <v>131</v>
+        <v>309</v>
       </c>
       <c r="F144" s="26" t="s">
-        <v>151</v>
+        <v>311</v>
       </c>
       <c r="G144" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F144),0)&gt;0), MAX($G$1:G143)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F144),0)&gt;0), MAX($G$1:G142)+1, ""))</f>
         <v/>
       </c>
       <c r="H144" s="21" t="b">
-        <f t="shared" si="4"/>
+        <f>A144=C144</f>
         <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A145" s="30">
+      <c r="A145" s="26">
         <v>25</v>
       </c>
-      <c r="B145" s="31" t="s">
-        <v>288</v>
-      </c>
-      <c r="C145" s="32">
+      <c r="B145" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="C145" s="28">
         <v>25</v>
       </c>
-      <c r="D145" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E145" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F145" s="30" t="s">
-        <v>102</v>
+      <c r="D145" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="E145" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F145" s="26" t="s">
+        <v>157</v>
       </c>
       <c r="G145" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B145),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E145),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F145),0)&gt;0), MAX($G$1:G144)+1, ""))</f>
         <v/>
       </c>
       <c r="H145" s="21" t="b">
-        <f t="shared" si="4"/>
+        <f>A145=C145</f>
         <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A146" s="30">
+      <c r="A146" s="26">
         <v>25</v>
       </c>
-      <c r="B146" s="31" t="s">
-        <v>286</v>
-      </c>
-      <c r="C146" s="32">
+      <c r="B146" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="C146" s="28">
         <v>25</v>
       </c>
-      <c r="D146" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E146" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F146" s="30" t="s">
-        <v>102</v>
+      <c r="D146" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="E146" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F146" s="26" t="s">
+        <v>155</v>
       </c>
       <c r="G146" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F146),0)&gt;0), MAX($G$1:G145)+1, ""))</f>
         <v/>
       </c>
       <c r="H146" s="21" t="b">
-        <f t="shared" si="4"/>
+        <f>A146=C146</f>
         <v>1</v>
       </c>
     </row>
     <row r="147" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A147" s="30">
+      <c r="A147" s="26">
         <v>25</v>
       </c>
-      <c r="B147" s="31" t="s">
-        <v>287</v>
-      </c>
-      <c r="C147" s="32">
+      <c r="B147" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="C147" s="28">
         <v>25</v>
       </c>
-      <c r="D147" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E147" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F147" s="30" t="s">
-        <v>102</v>
+      <c r="D147" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="E147" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="F147" s="26" t="s">
+        <v>153</v>
       </c>
       <c r="G147" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F147),0)&gt;0), MAX($G$1:G146)+1, ""))</f>
         <v/>
       </c>
       <c r="H147" s="21" t="b">
-        <f t="shared" si="4"/>
+        <f>A147=C147</f>
         <v>1</v>
       </c>
     </row>
@@ -5753,222 +5771,222 @@
         <v>25</v>
       </c>
       <c r="B148" s="27" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C148" s="28">
         <v>25</v>
       </c>
-      <c r="D148" s="26">
-        <v>2.5</v>
+      <c r="D148" s="39" t="s">
+        <v>229</v>
       </c>
       <c r="E148" s="27" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="F148" s="26" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="G148" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F148),0)&gt;0), MAX($G$1:G147)+1, ""))</f>
         <v/>
       </c>
       <c r="H148" s="21" t="b">
-        <f t="shared" si="4"/>
+        <f>A148=C148</f>
         <v>1</v>
       </c>
     </row>
     <row r="149" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A149" s="30">
+      <c r="A149" s="26">
         <v>25</v>
       </c>
-      <c r="B149" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="C149" s="32">
+      <c r="B149" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C149" s="28">
         <v>25</v>
       </c>
-      <c r="D149" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E149" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F149" s="30" t="s">
-        <v>102</v>
+      <c r="D149" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="E149" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="F149" s="26" t="s">
+        <v>151</v>
       </c>
       <c r="G149" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B149),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E149),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F149),0)&gt;0), MAX($G$1:G148)+1, ""))</f>
         <v/>
       </c>
       <c r="H149" s="21" t="b">
-        <f t="shared" si="4"/>
+        <f>A149=C149</f>
         <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A150" s="26">
+      <c r="A150" s="30">
         <v>25</v>
       </c>
-      <c r="B150" s="27" t="s">
-        <v>148</v>
-      </c>
-      <c r="C150" s="28">
+      <c r="B150" s="31" t="s">
+        <v>288</v>
+      </c>
+      <c r="C150" s="32">
         <v>25</v>
       </c>
-      <c r="D150" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="E150" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F150" s="26" t="s">
-        <v>149</v>
+      <c r="D150" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E150" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="F150" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G150" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B150),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E150),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F150),0)&gt;0), MAX($G$1:G148)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B150),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E150),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F150),0)&gt;0), MAX($G$1:G149)+1, ""))</f>
         <v/>
       </c>
       <c r="H150" s="21" t="b">
-        <f t="shared" si="4"/>
+        <f>A150=C150</f>
         <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A151" s="30">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B151" s="31" t="s">
-        <v>192</v>
+        <v>286</v>
       </c>
       <c r="C151" s="32">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D151" s="30" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="E151" s="31" t="s">
-        <v>131</v>
+        <v>283</v>
       </c>
       <c r="F151" s="30" t="s">
-        <v>193</v>
+        <v>102</v>
       </c>
       <c r="G151" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B151),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E151),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F151),0)&gt;0), MAX($G$1:G150)+1, ""))</f>
         <v/>
       </c>
       <c r="H151" s="21" t="b">
-        <f t="shared" si="4"/>
+        <f>A151=C151</f>
         <v>1</v>
       </c>
     </row>
     <row r="152" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A152" s="30">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B152" s="31" t="s">
-        <v>191</v>
+        <v>287</v>
       </c>
       <c r="C152" s="32">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D152" s="30" t="s">
-        <v>241</v>
+        <v>207</v>
       </c>
       <c r="E152" s="31" t="s">
-        <v>131</v>
+        <v>283</v>
       </c>
       <c r="F152" s="30" t="s">
-        <v>190</v>
+        <v>102</v>
       </c>
       <c r="G152" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B152),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E152),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F152),0)&gt;0), MAX($G$1:G151)+1, ""))</f>
         <v/>
       </c>
       <c r="H152" s="21" t="b">
-        <f t="shared" si="4"/>
+        <f>A152=C152</f>
         <v>1</v>
       </c>
     </row>
     <row r="153" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A153" s="30">
-        <v>30</v>
-      </c>
-      <c r="B153" s="31" t="s">
-        <v>189</v>
-      </c>
-      <c r="C153" s="32">
-        <v>30</v>
-      </c>
-      <c r="D153" s="30" t="s">
-        <v>240</v>
-      </c>
-      <c r="E153" s="31" t="s">
+      <c r="A153" s="26">
+        <v>25</v>
+      </c>
+      <c r="B153" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="C153" s="28">
+        <v>25</v>
+      </c>
+      <c r="D153" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E153" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="F153" s="30" t="s">
-        <v>190</v>
+      <c r="F153" s="26" t="s">
+        <v>253</v>
       </c>
       <c r="G153" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B153),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E153),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F153),0)&gt;0), MAX($G$1:G152)+1, ""))</f>
         <v/>
       </c>
       <c r="H153" s="21" t="b">
-        <f t="shared" si="4"/>
+        <f>A153=C153</f>
         <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A154" s="30">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B154" s="31" t="s">
-        <v>246</v>
+        <v>285</v>
       </c>
       <c r="C154" s="32">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D154" s="30" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="E154" s="31" t="s">
-        <v>8</v>
+        <v>283</v>
       </c>
       <c r="F154" s="30" t="s">
-        <v>188</v>
+        <v>102</v>
       </c>
       <c r="G154" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B154),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E154),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F154),0)&gt;0), MAX($G$1:G153)+1, ""))</f>
         <v/>
       </c>
       <c r="H154" s="21" t="b">
-        <f t="shared" si="4"/>
+        <f>A154=C154</f>
         <v>1</v>
       </c>
     </row>
     <row r="155" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A155" s="30">
-        <v>30</v>
-      </c>
-      <c r="B155" s="31" t="s">
-        <v>186</v>
-      </c>
-      <c r="C155" s="32">
-        <v>30</v>
-      </c>
-      <c r="D155" s="30" t="s">
-        <v>229</v>
-      </c>
-      <c r="E155" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F155" s="30" t="s">
-        <v>187</v>
+      <c r="A155" s="26">
+        <v>25</v>
+      </c>
+      <c r="B155" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="C155" s="28">
+        <v>25</v>
+      </c>
+      <c r="D155" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="E155" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F155" s="26" t="s">
+        <v>149</v>
       </c>
       <c r="G155" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F155),0)&gt;0), MAX($G$1:G154)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F155),0)&gt;0), MAX($G$1:G153)+1, ""))</f>
         <v/>
       </c>
       <c r="H155" s="21" t="b">
-        <f t="shared" si="4"/>
+        <f>A155=C155</f>
         <v>1</v>
       </c>
     </row>
@@ -5977,26 +5995,26 @@
         <v>30</v>
       </c>
       <c r="B156" s="31" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C156" s="32">
         <v>30</v>
       </c>
       <c r="D156" s="30" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E156" s="31" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="F156" s="30" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="G156" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B156),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E156),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F156),0)&gt;0), MAX($G$1:G155)+1, ""))</f>
         <v/>
       </c>
       <c r="H156" s="21" t="b">
-        <f t="shared" si="4"/>
+        <f>A156=C156</f>
         <v>1</v>
       </c>
     </row>
@@ -6005,26 +6023,26 @@
         <v>30</v>
       </c>
       <c r="B157" s="31" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="C157" s="32">
         <v>30</v>
       </c>
       <c r="D157" s="30" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E157" s="31" t="s">
         <v>131</v>
       </c>
       <c r="F157" s="30" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="G157" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F157),0)&gt;0), MAX($G$1:G156)+1, ""))</f>
         <v/>
       </c>
       <c r="H157" s="21" t="b">
-        <f t="shared" si="4"/>
+        <f>A157=C157</f>
         <v>1</v>
       </c>
     </row>
@@ -6033,26 +6051,26 @@
         <v>30</v>
       </c>
       <c r="B158" s="31" t="s">
-        <v>337</v>
+        <v>189</v>
       </c>
       <c r="C158" s="32">
         <v>30</v>
       </c>
-      <c r="D158" s="30">
-        <v>2.9</v>
+      <c r="D158" s="30" t="s">
+        <v>240</v>
       </c>
       <c r="E158" s="31" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="F158" s="30" t="s">
-        <v>338</v>
+        <v>190</v>
       </c>
       <c r="G158" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B158),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E158),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F158),0)&gt;0), MAX($G$1:G157)+1, ""))</f>
         <v/>
       </c>
       <c r="H158" s="21" t="b">
-        <f t="shared" si="4"/>
+        <f>A158=C158</f>
         <v>1</v>
       </c>
     </row>
@@ -6061,192 +6079,280 @@
         <v>30</v>
       </c>
       <c r="B159" s="31" t="s">
-        <v>180</v>
+        <v>246</v>
       </c>
       <c r="C159" s="32">
         <v>30</v>
       </c>
       <c r="D159" s="30" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="E159" s="31" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="F159" s="30" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="G159" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F159),0)&gt;0), MAX($G$1:G157)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F159),0)&gt;0), MAX($G$1:G158)+1, ""))</f>
         <v/>
       </c>
       <c r="H159" s="21" t="b">
-        <f t="shared" si="4"/>
+        <f>A159=C159</f>
         <v>1</v>
       </c>
     </row>
     <row r="160" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A160" s="26">
-        <v>40</v>
-      </c>
-      <c r="B160" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="C160" s="28">
-        <v>40</v>
-      </c>
-      <c r="D160" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="E160" s="27" t="s">
-        <v>198</v>
-      </c>
-      <c r="F160" s="26" t="s">
-        <v>199</v>
+      <c r="A160" s="30">
+        <v>30</v>
+      </c>
+      <c r="B160" s="31" t="s">
+        <v>186</v>
+      </c>
+      <c r="C160" s="32">
+        <v>30</v>
+      </c>
+      <c r="D160" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="E160" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F160" s="30" t="s">
+        <v>187</v>
       </c>
       <c r="G160" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B160),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E160),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F160),0)&gt;0), MAX($G$1:G159)+1, ""))</f>
         <v/>
       </c>
       <c r="H160" s="21" t="b">
-        <f t="shared" si="4"/>
+        <f>A160=C160</f>
         <v>1</v>
       </c>
     </row>
     <row r="161" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A161" s="26">
-        <v>40</v>
-      </c>
-      <c r="B161" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="C161" s="28">
-        <v>40</v>
-      </c>
-      <c r="D161" s="26" t="s">
-        <v>242</v>
-      </c>
-      <c r="E161" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="F161" s="26" t="s">
-        <v>196</v>
+      <c r="A161" s="30">
+        <v>30</v>
+      </c>
+      <c r="B161" s="31" t="s">
+        <v>184</v>
+      </c>
+      <c r="C161" s="32">
+        <v>30</v>
+      </c>
+      <c r="D161" s="30" t="s">
+        <v>228</v>
+      </c>
+      <c r="E161" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="F161" s="30" t="s">
+        <v>185</v>
       </c>
       <c r="G161" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B161),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E161),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F161),0)&gt;0), MAX($G$1:G160)+1, ""))</f>
         <v/>
       </c>
       <c r="H161" s="21" t="b">
-        <f t="shared" si="4"/>
+        <f>A161=C161</f>
         <v>1</v>
       </c>
     </row>
     <row r="162" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A162" s="26">
-        <v>40</v>
-      </c>
-      <c r="B162" s="27" t="s">
-        <v>249</v>
-      </c>
-      <c r="C162" s="28">
-        <v>40</v>
-      </c>
-      <c r="D162" s="26">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="E162" s="27" t="s">
-        <v>250</v>
-      </c>
-      <c r="F162" s="26" t="s">
-        <v>251</v>
+      <c r="A162" s="30">
+        <v>30</v>
+      </c>
+      <c r="B162" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="C162" s="32">
+        <v>30</v>
+      </c>
+      <c r="D162" s="30" t="s">
+        <v>239</v>
+      </c>
+      <c r="E162" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="F162" s="30" t="s">
+        <v>183</v>
       </c>
       <c r="G162" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B162),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E162),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F162),0)&gt;0), MAX($G$1:G161)+1, ""))</f>
         <v/>
       </c>
       <c r="H162" s="21" t="b">
-        <f t="shared" si="4"/>
+        <f>A162=C162</f>
         <v>1</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A163" s="26">
-        <v>45</v>
-      </c>
-      <c r="B163" s="27" t="s">
-        <v>294</v>
-      </c>
-      <c r="C163" s="28">
-        <v>45</v>
-      </c>
-      <c r="D163" s="26">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="E163" s="27" t="s">
-        <v>295</v>
-      </c>
-      <c r="F163" s="26" t="s">
-        <v>296</v>
+      <c r="A163" s="30">
+        <v>30</v>
+      </c>
+      <c r="B163" s="31" t="s">
+        <v>337</v>
+      </c>
+      <c r="C163" s="32">
+        <v>30</v>
+      </c>
+      <c r="D163" s="30">
+        <v>2.9</v>
+      </c>
+      <c r="E163" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="F163" s="30" t="s">
+        <v>338</v>
       </c>
       <c r="G163" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B163),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E163),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F163),0)&gt;0), MAX($G$1:G162)+1, ""))</f>
         <v/>
       </c>
       <c r="H163" s="21" t="b">
-        <f t="shared" si="4"/>
+        <f>A163=C163</f>
         <v>1</v>
       </c>
     </row>
     <row r="164" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A164" s="26">
-        <v>20</v>
-      </c>
-      <c r="B164" s="27" t="s">
-        <v>371</v>
-      </c>
-      <c r="C164" s="28">
-        <v>20</v>
-      </c>
-      <c r="D164" s="26">
-        <v>1.5</v>
+      <c r="A164" s="30">
+        <v>30</v>
+      </c>
+      <c r="B164" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="C164" s="32">
+        <v>30</v>
+      </c>
+      <c r="D164" s="30" t="s">
+        <v>238</v>
       </c>
       <c r="E164" s="31" t="s">
-        <v>299</v>
-      </c>
-      <c r="F164" s="26" t="s">
-        <v>372</v>
+        <v>131</v>
+      </c>
+      <c r="F164" s="30" t="s">
+        <v>181</v>
       </c>
       <c r="G164" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B164),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E164),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F164),0)&gt;0), MAX($G$1:G163)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B164),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E164),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F164),0)&gt;0), MAX($G$1:G162)+1, ""))</f>
         <v/>
       </c>
       <c r="H164" s="21" t="b">
-        <f t="shared" ref="H164" si="5">A164=C164</f>
+        <f>A164=C164</f>
         <v>1</v>
       </c>
     </row>
     <row r="165" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A165" s="1"/>
-      <c r="C165" s="1"/>
-      <c r="D165" s="1"/>
-      <c r="F165" s="1"/>
+      <c r="A165" s="26">
+        <v>40</v>
+      </c>
+      <c r="B165" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="C165" s="28">
+        <v>40</v>
+      </c>
+      <c r="D165" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="E165" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="F165" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="G165" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B165),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E165),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F165),0)&gt;0), MAX($G$1:G164)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H165" s="21" t="b">
+        <f>A165=C165</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="166" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A166" s="1"/>
-      <c r="C166" s="1"/>
-      <c r="D166" s="1"/>
-      <c r="F166" s="1"/>
+      <c r="A166" s="26">
+        <v>40</v>
+      </c>
+      <c r="B166" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="C166" s="28">
+        <v>40</v>
+      </c>
+      <c r="D166" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="E166" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="F166" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="G166" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B166),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E166),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F166),0)&gt;0), MAX($G$1:G165)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H166" s="21" t="b">
+        <f>A166=C166</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="167" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A167" s="1"/>
-      <c r="C167" s="1"/>
-      <c r="D167" s="1"/>
-      <c r="F167" s="1"/>
+      <c r="A167" s="26">
+        <v>40</v>
+      </c>
+      <c r="B167" s="27" t="s">
+        <v>249</v>
+      </c>
+      <c r="C167" s="28">
+        <v>40</v>
+      </c>
+      <c r="D167" s="26">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E167" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="F167" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="G167" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B167),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E167),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F167),0)&gt;0), MAX($G$1:G166)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H167" s="21" t="b">
+        <f>A167=C167</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="168" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A168" s="1"/>
-      <c r="C168" s="1"/>
-      <c r="D168" s="1"/>
-      <c r="F168" s="1"/>
+      <c r="A168" s="26">
+        <v>45</v>
+      </c>
+      <c r="B168" s="27" t="s">
+        <v>294</v>
+      </c>
+      <c r="C168" s="28">
+        <v>45</v>
+      </c>
+      <c r="D168" s="26">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E168" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="F168" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="G168" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B168),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E168),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F168),0)&gt;0), MAX($G$1:G167)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H168" s="21" t="b">
+        <f>A168=C168</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="169" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
@@ -11474,18 +11580,42 @@
       <c r="D1039" s="1"/>
       <c r="F1039" s="1"/>
     </row>
+    <row r="1040" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1040" s="1"/>
+      <c r="C1040" s="1"/>
+      <c r="D1040" s="1"/>
+      <c r="F1040" s="1"/>
+    </row>
+    <row r="1041" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1041" s="1"/>
+      <c r="C1041" s="1"/>
+      <c r="D1041" s="1"/>
+      <c r="F1041" s="1"/>
+    </row>
+    <row r="1042" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1042" s="1"/>
+      <c r="C1042" s="1"/>
+      <c r="D1042" s="1"/>
+      <c r="F1042" s="1"/>
+    </row>
+    <row r="1043" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1043" s="1"/>
+      <c r="C1043" s="1"/>
+      <c r="D1043" s="1"/>
+      <c r="F1043" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H163">
+  <autoFilter ref="A1:H167">
     <sortState ref="A2:H147">
       <sortCondition ref="A2:A147"/>
       <sortCondition ref="B2:B147"/>
       <sortCondition ref="D2:D147"/>
     </sortState>
   </autoFilter>
-  <sortState ref="A2:H163">
-    <sortCondition ref="A2:A163"/>
-    <sortCondition ref="B2:B163"/>
-    <sortCondition ref="D2:D163"/>
+  <sortState ref="A2:H168">
+    <sortCondition ref="A2:A168"/>
+    <sortCondition ref="B2:B168"/>
+    <sortCondition ref="D2:D168"/>
   </sortState>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -3336,7 +3336,7 @@
         <v>17</v>
       </c>
       <c r="D60" s="26">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="E60" s="27" t="s">
         <v>8</v>

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Consulta" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$167</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$165</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$140</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Base!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="381">
   <si>
     <t>Grupo</t>
   </si>
@@ -1077,12 +1077,6 @@
     <t>21765-080</t>
   </si>
   <si>
-    <t>FREDERICO FAULHABER APÓS PIRPIRITUBA</t>
-  </si>
-  <si>
-    <t>FREDERICO FAULHABER ANTES PIRPIRITUBA</t>
-  </si>
-  <si>
     <t>Piraquara</t>
   </si>
   <si>
@@ -1158,10 +1152,22 @@
     <t>JOSE MARIA DE ABREU (RUA 1)</t>
   </si>
   <si>
-    <t>JOSE MARIA DE ABREU APÓS CAMPO SÃO LUIS</t>
-  </si>
-  <si>
-    <t>BANDEIRA DE MELO APÓS CAMPO SÃO LUIS</t>
+    <t>FREDERICO FAULHABER APÓS CAMPO SÃO LUIS</t>
+  </si>
+  <si>
+    <t>FREDERICO FAULHABER ANTES CAMPO SÃO LUIS</t>
+  </si>
+  <si>
+    <t>POSTO VAGÃO</t>
+  </si>
+  <si>
+    <t>Realengo - Av. Brasil</t>
+  </si>
+  <si>
+    <t>MORAIS JUNIOR</t>
+  </si>
+  <si>
+    <t>21710-100</t>
   </si>
 </sst>
 </file>
@@ -1679,11 +1685,11 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H1043"/>
+  <dimension ref="A1:H1041"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.453125" customWidth="1"/>
-    <col min="2" max="2" width="34.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.08984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.90625" customWidth="1"/>
     <col min="4" max="4" width="7.81640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.6328125" bestFit="1" customWidth="1"/>
@@ -1746,7 +1752,7 @@
         <v>13</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C3" s="28">
         <v>13</v>
@@ -2026,7 +2032,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C13" s="32">
         <v>13</v>
@@ -2082,7 +2088,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C15" s="32">
         <v>13</v>
@@ -2094,7 +2100,7 @@
         <v>8</v>
       </c>
       <c r="F15" s="30" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="G15" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B15),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E15),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F15),0)&gt;0), MAX($G$1:G14)+1, ""))</f>
@@ -2250,7 +2256,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C21" s="28">
         <v>15</v>
@@ -2262,7 +2268,7 @@
         <v>245</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="G21" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F21),0)&gt;0), MAX($G$1:G20)+1, ""))</f>
@@ -2306,7 +2312,7 @@
         <v>15</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C23" s="28">
         <v>15</v>
@@ -2474,7 +2480,7 @@
         <v>15</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>351</v>
+        <v>376</v>
       </c>
       <c r="C29" s="28">
         <v>15</v>
@@ -2483,7 +2489,7 @@
         <v>2</v>
       </c>
       <c r="E29" s="27" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F29" s="26" t="s">
         <v>348</v>
@@ -2698,7 +2704,7 @@
         <v>15</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C37" s="28">
         <v>15</v>
@@ -2710,7 +2716,7 @@
         <v>8</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G37" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F37),0)&gt;0), MAX($G$1:G36)+1, ""))</f>
@@ -2726,7 +2732,7 @@
         <v>15</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C38" s="28">
         <v>15</v>
@@ -2738,7 +2744,7 @@
         <v>8</v>
       </c>
       <c r="F38" s="26" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G38" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F38),0)&gt;0), MAX($G$1:G37)+1, ""))</f>
@@ -3030,23 +3036,23 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="26">
+      <c r="A49" s="33">
         <v>17</v>
       </c>
-      <c r="B49" s="27" t="s">
-        <v>378</v>
-      </c>
-      <c r="C49" s="28">
+      <c r="B49" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="C49" s="35">
         <v>17</v>
       </c>
-      <c r="D49" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E49" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="F49" s="26" t="s">
-        <v>374</v>
+      <c r="D49" s="33" t="s">
+        <v>214</v>
+      </c>
+      <c r="E49" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49" s="33" t="s">
+        <v>71</v>
       </c>
       <c r="G49" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F49),0)&gt;0), MAX($G$1:G48)+1, ""))</f>
@@ -3062,19 +3068,19 @@
         <v>17</v>
       </c>
       <c r="B50" s="34" t="s">
-        <v>70</v>
+        <v>281</v>
       </c>
       <c r="C50" s="35">
         <v>17</v>
       </c>
       <c r="D50" s="33" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E50" s="34" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F50" s="33" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G50" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F50),0)&gt;0), MAX($G$1:G49)+1, ""))</f>
@@ -3086,53 +3092,53 @@
       </c>
     </row>
     <row r="51" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="33">
+      <c r="A51" s="26">
         <v>17</v>
       </c>
-      <c r="B51" s="34" t="s">
-        <v>281</v>
-      </c>
-      <c r="C51" s="35">
+      <c r="B51" s="27" t="s">
+        <v>313</v>
+      </c>
+      <c r="C51" s="28">
         <v>17</v>
       </c>
-      <c r="D51" s="33" t="s">
-        <v>222</v>
-      </c>
-      <c r="E51" s="34" t="s">
+      <c r="D51" s="26">
+        <v>1.7</v>
+      </c>
+      <c r="E51" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="F51" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="G51" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F51),0)&gt;0), MAX($G$1:G50)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="F51" s="26" t="s">
+        <v>319</v>
+      </c>
+      <c r="G51" s="29"/>
       <c r="H51" s="21" t="b">
         <f>A51=C51</f>
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="26">
+      <c r="A52" s="33">
         <v>17</v>
       </c>
-      <c r="B52" s="27" t="s">
-        <v>313</v>
-      </c>
-      <c r="C52" s="28">
+      <c r="B52" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C52" s="35">
         <v>17</v>
       </c>
-      <c r="D52" s="26">
-        <v>1.7</v>
-      </c>
-      <c r="E52" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="F52" s="26" t="s">
-        <v>319</v>
-      </c>
-      <c r="G52" s="29"/>
+      <c r="D52" s="33" t="s">
+        <v>215</v>
+      </c>
+      <c r="E52" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="G52" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F52),0)&gt;0), MAX($G$1:G51)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H52" s="21" t="b">
         <f>A52=C52</f>
         <v>1</v>
@@ -3143,19 +3149,19 @@
         <v>17</v>
       </c>
       <c r="B53" s="34" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C53" s="35">
         <v>17</v>
       </c>
       <c r="D53" s="33" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E53" s="34" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F53" s="33" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G53" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F53),0)&gt;0), MAX($G$1:G52)+1, ""))</f>
@@ -3167,28 +3173,25 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A54" s="33">
+      <c r="A54" s="26">
         <v>17</v>
       </c>
-      <c r="B54" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="C54" s="35">
+      <c r="B54" s="27" t="s">
+        <v>315</v>
+      </c>
+      <c r="C54" s="28">
         <v>17</v>
       </c>
-      <c r="D54" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="E54" s="34" t="s">
+      <c r="D54" s="26">
+        <v>3</v>
+      </c>
+      <c r="E54" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="F54" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="G54" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F54),0)&gt;0), MAX($G$1:G53)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="F54" s="26" t="s">
+        <v>321</v>
+      </c>
+      <c r="G54" s="29"/>
       <c r="H54" s="21" t="b">
         <f>A54=C54</f>
         <v>1</v>
@@ -3199,21 +3202,24 @@
         <v>17</v>
       </c>
       <c r="B55" s="27" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="C55" s="28">
         <v>17</v>
       </c>
       <c r="D55" s="26">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="E55" s="27" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="F55" s="26" t="s">
-        <v>321</v>
-      </c>
-      <c r="G55" s="29"/>
+        <v>349</v>
+      </c>
+      <c r="G55" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F55),0)&gt;0), MAX($G$1:G53)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H55" s="21" t="b">
         <f>A55=C55</f>
         <v>1</v>
@@ -3224,77 +3230,74 @@
         <v>17</v>
       </c>
       <c r="B56" s="27" t="s">
-        <v>340</v>
+        <v>316</v>
       </c>
       <c r="C56" s="28">
         <v>17</v>
       </c>
       <c r="D56" s="26">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="E56" s="27" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F56" s="26" t="s">
-        <v>349</v>
-      </c>
-      <c r="G56" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F56),0)&gt;0), MAX($G$1:G54)+1, ""))</f>
-        <v/>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="G56" s="29"/>
       <c r="H56" s="21" t="b">
         <f>A56=C56</f>
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A57" s="26">
+      <c r="A57" s="36">
         <v>17</v>
       </c>
-      <c r="B57" s="27" t="s">
-        <v>316</v>
-      </c>
-      <c r="C57" s="28">
+      <c r="B57" s="37" t="s">
+        <v>289</v>
+      </c>
+      <c r="C57" s="38">
         <v>17</v>
       </c>
-      <c r="D57" s="26">
-        <v>1.9</v>
-      </c>
-      <c r="E57" s="27" t="s">
+      <c r="D57" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E57" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="F57" s="26" t="s">
-        <v>322</v>
-      </c>
-      <c r="G57" s="29"/>
+      <c r="F57" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="G57" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F57),0)&gt;0), MAX($G$1:G56)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H57" s="21" t="b">
         <f>A57=C57</f>
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A58" s="36">
+      <c r="A58" s="26">
         <v>17</v>
       </c>
-      <c r="B58" s="37" t="s">
-        <v>289</v>
-      </c>
-      <c r="C58" s="38">
+      <c r="B58" s="27" t="s">
+        <v>314</v>
+      </c>
+      <c r="C58" s="28">
         <v>17</v>
       </c>
-      <c r="D58" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="E58" s="37" t="s">
+      <c r="D58" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E58" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="F58" s="36" t="s">
-        <v>111</v>
-      </c>
-      <c r="G58" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F58),0)&gt;0), MAX($G$1:G57)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="F58" s="26" t="s">
+        <v>320</v>
+      </c>
+      <c r="G58" s="29"/>
       <c r="H58" s="21" t="b">
         <f>A58=C58</f>
         <v>1</v>
@@ -3305,19 +3308,19 @@
         <v>17</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C59" s="28">
         <v>17</v>
       </c>
       <c r="D59" s="26">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="E59" s="27" t="s">
         <v>60</v>
       </c>
       <c r="F59" s="26" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="G59" s="29"/>
       <c r="H59" s="21" t="b">
@@ -3326,23 +3329,23 @@
       </c>
     </row>
     <row r="60" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A60" s="26">
+      <c r="A60" s="36">
         <v>17</v>
       </c>
-      <c r="B60" s="27" t="s">
-        <v>377</v>
-      </c>
-      <c r="C60" s="28">
+      <c r="B60" s="37" t="s">
+        <v>106</v>
+      </c>
+      <c r="C60" s="38">
         <v>17</v>
       </c>
-      <c r="D60" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E60" s="27" t="s">
+      <c r="D60" s="36" t="s">
+        <v>220</v>
+      </c>
+      <c r="E60" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F60" s="26" t="s">
-        <v>375</v>
+      <c r="F60" s="36" t="s">
+        <v>107</v>
       </c>
       <c r="G60" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F60),0)&gt;0), MAX($G$1:G59)+1, ""))</f>
@@ -3354,51 +3357,54 @@
       </c>
     </row>
     <row r="61" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A61" s="26">
+      <c r="A61" s="36">
         <v>17</v>
       </c>
-      <c r="B61" s="27" t="s">
-        <v>317</v>
-      </c>
-      <c r="C61" s="28">
+      <c r="B61" s="37" t="s">
+        <v>303</v>
+      </c>
+      <c r="C61" s="38">
         <v>17</v>
       </c>
-      <c r="D61" s="26">
-        <v>2</v>
-      </c>
-      <c r="E61" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="F61" s="26" t="s">
-        <v>323</v>
-      </c>
-      <c r="G61" s="29"/>
+      <c r="D61" s="36" t="s">
+        <v>229</v>
+      </c>
+      <c r="E61" s="37" t="s">
+        <v>304</v>
+      </c>
+      <c r="F61" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="G61" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F61),0)&gt;0), MAX($G$1:G60)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H61" s="21" t="b">
         <f>A61=C61</f>
         <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A62" s="36">
+      <c r="A62" s="33">
         <v>17</v>
       </c>
-      <c r="B62" s="37" t="s">
-        <v>106</v>
-      </c>
-      <c r="C62" s="38">
+      <c r="B62" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="C62" s="35">
         <v>17</v>
       </c>
-      <c r="D62" s="36" t="s">
-        <v>220</v>
-      </c>
-      <c r="E62" s="37" t="s">
+      <c r="D62" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="E62" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F62" s="36" t="s">
-        <v>107</v>
+      <c r="F62" s="33" t="s">
+        <v>53</v>
       </c>
       <c r="G62" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F62),0)&gt;0), MAX($G$1:G61)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F62),0)&gt;0), MAX($G$1:G58)+1, ""))</f>
         <v/>
       </c>
       <c r="H62" s="21" t="b">
@@ -3407,23 +3413,23 @@
       </c>
     </row>
     <row r="63" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A63" s="36">
+      <c r="A63" s="26">
         <v>17</v>
       </c>
-      <c r="B63" s="37" t="s">
-        <v>303</v>
-      </c>
-      <c r="C63" s="38">
+      <c r="B63" s="27" t="s">
+        <v>368</v>
+      </c>
+      <c r="C63" s="28">
         <v>17</v>
       </c>
-      <c r="D63" s="36" t="s">
-        <v>229</v>
-      </c>
-      <c r="E63" s="37" t="s">
-        <v>304</v>
-      </c>
-      <c r="F63" s="36" t="s">
-        <v>105</v>
+      <c r="D63" s="26">
+        <v>1.8</v>
+      </c>
+      <c r="E63" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F63" s="26" t="s">
+        <v>354</v>
       </c>
       <c r="G63" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F63),0)&gt;0), MAX($G$1:G62)+1, ""))</f>
@@ -3435,26 +3441,26 @@
       </c>
     </row>
     <row r="64" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A64" s="33">
+      <c r="A64" s="26">
         <v>17</v>
       </c>
-      <c r="B64" s="34" t="s">
-        <v>52</v>
-      </c>
-      <c r="C64" s="35">
+      <c r="B64" s="27" t="s">
+        <v>379</v>
+      </c>
+      <c r="C64" s="28">
         <v>17</v>
       </c>
-      <c r="D64" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="E64" s="34" t="s">
+      <c r="D64" s="26">
+        <v>1.2</v>
+      </c>
+      <c r="E64" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F64" s="33" t="s">
-        <v>53</v>
+      <c r="F64" s="26" t="s">
+        <v>380</v>
       </c>
       <c r="G64" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F64),0)&gt;0), MAX($G$1:G59)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F64),0)&gt;0), MAX($G$1:G63)+1, ""))</f>
         <v/>
       </c>
       <c r="H64" s="21" t="b">
@@ -3463,23 +3469,23 @@
       </c>
     </row>
     <row r="65" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A65" s="26">
+      <c r="A65" s="33">
         <v>17</v>
       </c>
-      <c r="B65" s="27" t="s">
-        <v>370</v>
-      </c>
-      <c r="C65" s="28">
+      <c r="B65" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="C65" s="35">
         <v>17</v>
       </c>
-      <c r="D65" s="26">
-        <v>1.8</v>
-      </c>
-      <c r="E65" s="27" t="s">
+      <c r="D65" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="E65" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F65" s="26" t="s">
-        <v>356</v>
+      <c r="F65" s="33" t="s">
+        <v>49</v>
       </c>
       <c r="G65" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F65),0)&gt;0), MAX($G$1:G64)+1, ""))</f>
@@ -3491,23 +3497,23 @@
       </c>
     </row>
     <row r="66" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A66" s="33">
+      <c r="A66" s="36">
         <v>17</v>
       </c>
-      <c r="B66" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="C66" s="35">
+      <c r="B66" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="C66" s="38">
         <v>17</v>
       </c>
-      <c r="D66" s="33" t="s">
-        <v>211</v>
-      </c>
-      <c r="E66" s="34" t="s">
+      <c r="D66" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E66" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F66" s="33" t="s">
-        <v>49</v>
+      <c r="F66" s="36" t="s">
+        <v>98</v>
       </c>
       <c r="G66" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F66),0)&gt;0), MAX($G$1:G65)+1, ""))</f>
@@ -3519,23 +3525,23 @@
       </c>
     </row>
     <row r="67" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A67" s="36">
+      <c r="A67" s="26">
         <v>17</v>
       </c>
-      <c r="B67" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="C67" s="38">
+      <c r="B67" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C67" s="28">
         <v>17</v>
       </c>
-      <c r="D67" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="E67" s="37" t="s">
+      <c r="D67" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="E67" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F67" s="36" t="s">
-        <v>98</v>
+      <c r="F67" s="26" t="s">
+        <v>43</v>
       </c>
       <c r="G67" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F67),0)&gt;0), MAX($G$1:G66)+1, ""))</f>
@@ -3547,23 +3553,23 @@
       </c>
     </row>
     <row r="68" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A68" s="26">
+      <c r="A68" s="36">
         <v>17</v>
       </c>
-      <c r="B68" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="C68" s="28">
+      <c r="B68" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="C68" s="38">
         <v>17</v>
       </c>
-      <c r="D68" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="E68" s="27" t="s">
+      <c r="D68" s="36" t="s">
+        <v>217</v>
+      </c>
+      <c r="E68" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F68" s="26" t="s">
-        <v>43</v>
+      <c r="F68" s="36" t="s">
+        <v>94</v>
       </c>
       <c r="G68" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F68),0)&gt;0), MAX($G$1:G67)+1, ""))</f>
@@ -3575,30 +3581,28 @@
       </c>
     </row>
     <row r="69" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A69" s="36">
+      <c r="A69" s="33">
         <v>17</v>
       </c>
-      <c r="B69" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="C69" s="38">
+      <c r="B69" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="C69" s="35">
         <v>17</v>
       </c>
-      <c r="D69" s="36" t="s">
-        <v>217</v>
-      </c>
-      <c r="E69" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F69" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="G69" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F69),0)&gt;0), MAX($G$1:G68)+1, ""))</f>
-        <v/>
+      <c r="D69" s="33">
+        <v>1.9</v>
+      </c>
+      <c r="E69" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="F69" s="33" t="s">
+        <v>329</v>
+      </c>
+      <c r="G69" s="29" t="s">
+        <v>326</v>
       </c>
       <c r="H69" s="21" t="b">
-        <f>A69=C69</f>
         <v>1</v>
       </c>
     </row>
@@ -3607,7 +3611,7 @@
         <v>17</v>
       </c>
       <c r="B70" s="34" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C70" s="35">
         <v>17</v>
@@ -3633,7 +3637,7 @@
         <v>17</v>
       </c>
       <c r="B71" s="34" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C71" s="35">
         <v>17</v>
@@ -3659,45 +3663,47 @@
         <v>17</v>
       </c>
       <c r="B72" s="34" t="s">
-        <v>328</v>
+        <v>36</v>
       </c>
       <c r="C72" s="35">
         <v>17</v>
       </c>
-      <c r="D72" s="33">
-        <v>1.9</v>
+      <c r="D72" s="33" t="s">
+        <v>214</v>
       </c>
       <c r="E72" s="34" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="F72" s="33" t="s">
-        <v>329</v>
-      </c>
-      <c r="G72" s="29" t="s">
-        <v>326</v>
+        <v>37</v>
+      </c>
+      <c r="G72" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F72),0)&gt;0), MAX($G$1:G71)+1, ""))</f>
+        <v/>
       </c>
       <c r="H72" s="21" t="b">
+        <f>A72=C72</f>
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A73" s="33">
+      <c r="A73" s="36">
         <v>17</v>
       </c>
-      <c r="B73" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="C73" s="35">
+      <c r="B73" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="C73" s="38">
         <v>17</v>
       </c>
-      <c r="D73" s="33" t="s">
-        <v>214</v>
-      </c>
-      <c r="E73" s="34" t="s">
+      <c r="D73" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E73" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F73" s="33" t="s">
-        <v>37</v>
+      <c r="F73" s="36" t="s">
+        <v>84</v>
       </c>
       <c r="G73" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F73),0)&gt;0), MAX($G$1:G72)+1, ""))</f>
@@ -3709,23 +3715,23 @@
       </c>
     </row>
     <row r="74" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A74" s="36">
+      <c r="A74" s="33">
         <v>17</v>
       </c>
-      <c r="B74" s="37" t="s">
-        <v>83</v>
-      </c>
-      <c r="C74" s="38">
+      <c r="B74" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="35">
         <v>17</v>
       </c>
-      <c r="D74" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="E74" s="37" t="s">
+      <c r="D74" s="33" t="s">
+        <v>208</v>
+      </c>
+      <c r="E74" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F74" s="36" t="s">
-        <v>84</v>
+      <c r="F74" s="33" t="s">
+        <v>32</v>
       </c>
       <c r="G74" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F74),0)&gt;0), MAX($G$1:G73)+1, ""))</f>
@@ -3741,52 +3747,52 @@
         <v>17</v>
       </c>
       <c r="B75" s="34" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C75" s="35">
         <v>17</v>
       </c>
       <c r="D75" s="33" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E75" s="34" t="s">
         <v>8</v>
       </c>
       <c r="F75" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="G75" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F75),0)&gt;0), MAX($G$1:G74)+1, ""))</f>
-        <v/>
+        <v>30</v>
+      </c>
+      <c r="G75" s="29" t="s">
+        <v>326</v>
       </c>
       <c r="H75" s="21" t="b">
-        <f>A75=C75</f>
         <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A76" s="33">
-        <v>17</v>
-      </c>
-      <c r="B76" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="C76" s="35">
-        <v>17</v>
-      </c>
-      <c r="D76" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="E76" s="34" t="s">
+      <c r="A76" s="30">
+        <v>20</v>
+      </c>
+      <c r="B76" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="C76" s="32">
+        <v>20</v>
+      </c>
+      <c r="D76" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="E76" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F76" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="G76" s="29" t="s">
-        <v>326</v>
+      <c r="F76" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="G76" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F76),0)&gt;0), MAX($G$1:G72)+1, ""))</f>
+        <v/>
       </c>
       <c r="H76" s="21" t="b">
+        <f>A76=C76</f>
         <v>1</v>
       </c>
     </row>
@@ -3795,22 +3801,22 @@
         <v>20</v>
       </c>
       <c r="B77" s="31" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C77" s="32">
         <v>20</v>
       </c>
       <c r="D77" s="30" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E77" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F77" s="30" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G77" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F77),0)&gt;0), MAX($G$1:G73)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F77),0)&gt;0), MAX($G$1:G76)+1, ""))</f>
         <v/>
       </c>
       <c r="H77" s="21" t="b">
@@ -3823,22 +3829,22 @@
         <v>20</v>
       </c>
       <c r="B78" s="31" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C78" s="32">
         <v>20</v>
       </c>
       <c r="D78" s="30" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E78" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F78" s="30" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G78" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F78),0)&gt;0), MAX($G$1:G77)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F78),0)&gt;0), MAX($G$1:G76)+1, ""))</f>
         <v/>
       </c>
       <c r="H78" s="21" t="b">
@@ -3851,22 +3857,22 @@
         <v>20</v>
       </c>
       <c r="B79" s="31" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C79" s="32">
         <v>20</v>
       </c>
       <c r="D79" s="30" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E79" s="31" t="s">
-        <v>8</v>
+        <v>305</v>
       </c>
       <c r="F79" s="30" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G79" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F79),0)&gt;0), MAX($G$1:G77)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F79),0)&gt;0), MAX($G$1:G78)+1, ""))</f>
         <v/>
       </c>
       <c r="H79" s="21" t="b">
@@ -3875,28 +3881,25 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A80" s="30">
+      <c r="A80" s="36">
         <v>20</v>
       </c>
-      <c r="B80" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="C80" s="32">
+      <c r="B80" s="37" t="s">
+        <v>333</v>
+      </c>
+      <c r="C80" s="38">
         <v>20</v>
       </c>
-      <c r="D80" s="30" t="s">
-        <v>216</v>
-      </c>
-      <c r="E80" s="31" t="s">
-        <v>305</v>
-      </c>
-      <c r="F80" s="30" t="s">
-        <v>141</v>
-      </c>
-      <c r="G80" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F80),0)&gt;0), MAX($G$1:G79)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D80" s="36">
+        <v>3.4</v>
+      </c>
+      <c r="E80" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="F80" s="36" t="s">
+        <v>334</v>
+      </c>
+      <c r="G80" s="29"/>
       <c r="H80" s="21" t="b">
         <f>A80=C80</f>
         <v>1</v>
@@ -3907,19 +3910,19 @@
         <v>20</v>
       </c>
       <c r="B81" s="37" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C81" s="38">
         <v>20</v>
       </c>
       <c r="D81" s="36">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="E81" s="37" t="s">
         <v>336</v>
       </c>
       <c r="F81" s="36" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="G81" s="29"/>
       <c r="H81" s="21" t="b">
@@ -3928,25 +3931,28 @@
       </c>
     </row>
     <row r="82" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A82" s="36">
+      <c r="A82" s="30">
         <v>20</v>
       </c>
-      <c r="B82" s="37" t="s">
-        <v>331</v>
-      </c>
-      <c r="C82" s="38">
+      <c r="B82" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="C82" s="32">
         <v>20</v>
       </c>
-      <c r="D82" s="36">
-        <v>3.3</v>
-      </c>
-      <c r="E82" s="37" t="s">
-        <v>336</v>
-      </c>
-      <c r="F82" s="36" t="s">
-        <v>332</v>
-      </c>
-      <c r="G82" s="29"/>
+      <c r="D82" s="30" t="s">
+        <v>223</v>
+      </c>
+      <c r="E82" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F82" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="G82" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F82),0)&gt;0), MAX($G$1:G81)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H82" s="21" t="b">
         <f>A82=C82</f>
         <v>1</v>
@@ -3957,19 +3963,19 @@
         <v>20</v>
       </c>
       <c r="B83" s="31" t="s">
-        <v>138</v>
+        <v>255</v>
       </c>
       <c r="C83" s="32">
         <v>20</v>
       </c>
       <c r="D83" s="30" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E83" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F83" s="30" t="s">
-        <v>139</v>
+        <v>256</v>
       </c>
       <c r="G83" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F83),0)&gt;0), MAX($G$1:G82)+1, ""))</f>
@@ -3985,19 +3991,19 @@
         <v>20</v>
       </c>
       <c r="B84" s="31" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C84" s="32">
         <v>20</v>
       </c>
-      <c r="D84" s="30" t="s">
-        <v>225</v>
+      <c r="D84" s="30">
+        <v>4.2</v>
       </c>
       <c r="E84" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F84" s="30" t="s">
-        <v>256</v>
+        <v>305</v>
+      </c>
+      <c r="F84" s="30">
+        <v>21765430</v>
       </c>
       <c r="G84" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F84),0)&gt;0), MAX($G$1:G83)+1, ""))</f>
@@ -4013,19 +4019,19 @@
         <v>20</v>
       </c>
       <c r="B85" s="31" t="s">
-        <v>254</v>
+        <v>136</v>
       </c>
       <c r="C85" s="32">
         <v>20</v>
       </c>
-      <c r="D85" s="30">
-        <v>4.2</v>
+      <c r="D85" s="30" t="s">
+        <v>210</v>
       </c>
       <c r="E85" s="31" t="s">
-        <v>305</v>
-      </c>
-      <c r="F85" s="30">
-        <v>21765430</v>
+        <v>8</v>
+      </c>
+      <c r="F85" s="30" t="s">
+        <v>137</v>
       </c>
       <c r="G85" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F85),0)&gt;0), MAX($G$1:G84)+1, ""))</f>
@@ -4041,19 +4047,19 @@
         <v>20</v>
       </c>
       <c r="B86" s="31" t="s">
-        <v>136</v>
+        <v>265</v>
       </c>
       <c r="C86" s="32">
         <v>20</v>
       </c>
       <c r="D86" s="30" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="E86" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F86" s="30" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G86" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F86),0)&gt;0), MAX($G$1:G85)+1, ""))</f>
@@ -4069,19 +4075,19 @@
         <v>20</v>
       </c>
       <c r="B87" s="31" t="s">
-        <v>265</v>
+        <v>133</v>
       </c>
       <c r="C87" s="32">
         <v>20</v>
       </c>
       <c r="D87" s="30" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E87" s="31" t="s">
-        <v>8</v>
+        <v>305</v>
       </c>
       <c r="F87" s="30" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G87" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F87),0)&gt;0), MAX($G$1:G86)+1, ""))</f>
@@ -4097,19 +4103,19 @@
         <v>20</v>
       </c>
       <c r="B88" s="31" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C88" s="32">
         <v>20</v>
       </c>
       <c r="D88" s="30" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="E88" s="31" t="s">
-        <v>305</v>
+        <v>131</v>
       </c>
       <c r="F88" s="30" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G88" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F88),0)&gt;0), MAX($G$1:G87)+1, ""))</f>
@@ -4121,23 +4127,23 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A89" s="30">
+      <c r="A89" s="26">
         <v>20</v>
       </c>
-      <c r="B89" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="C89" s="32">
+      <c r="B89" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="C89" s="28">
         <v>20</v>
       </c>
-      <c r="D89" s="30" t="s">
-        <v>214</v>
-      </c>
-      <c r="E89" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="F89" s="30" t="s">
-        <v>132</v>
+      <c r="D89" s="26">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E89" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F89" s="26" t="s">
+        <v>318</v>
       </c>
       <c r="G89" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F89),0)&gt;0), MAX($G$1:G88)+1, ""))</f>
@@ -4149,23 +4155,23 @@
       </c>
     </row>
     <row r="90" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A90" s="26">
+      <c r="A90" s="30">
         <v>20</v>
       </c>
-      <c r="B90" s="27" t="s">
-        <v>312</v>
-      </c>
-      <c r="C90" s="28">
+      <c r="B90" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="C90" s="32">
         <v>20</v>
       </c>
-      <c r="D90" s="26">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="E90" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="F90" s="26" t="s">
-        <v>318</v>
+      <c r="D90" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="E90" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F90" s="30" t="s">
+        <v>129</v>
       </c>
       <c r="G90" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F90),0)&gt;0), MAX($G$1:G89)+1, ""))</f>
@@ -4181,19 +4187,19 @@
         <v>20</v>
       </c>
       <c r="B91" s="31" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C91" s="32">
         <v>20</v>
       </c>
       <c r="D91" s="30" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="E91" s="31" t="s">
-        <v>8</v>
+        <v>305</v>
       </c>
       <c r="F91" s="30" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G91" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F91),0)&gt;0), MAX($G$1:G90)+1, ""))</f>
@@ -4205,23 +4211,23 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A92" s="30">
+      <c r="A92" s="26">
         <v>20</v>
       </c>
-      <c r="B92" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="C92" s="32">
+      <c r="B92" s="27" t="s">
+        <v>375</v>
+      </c>
+      <c r="C92" s="28">
         <v>20</v>
       </c>
-      <c r="D92" s="30" t="s">
-        <v>234</v>
-      </c>
-      <c r="E92" s="31" t="s">
-        <v>305</v>
-      </c>
-      <c r="F92" s="30" t="s">
-        <v>127</v>
+      <c r="D92" s="26">
+        <v>2.7</v>
+      </c>
+      <c r="E92" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="F92" s="26" t="s">
+        <v>351</v>
       </c>
       <c r="G92" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F92),0)&gt;0), MAX($G$1:G91)+1, ""))</f>
@@ -4233,23 +4239,23 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A93" s="26">
+      <c r="A93" s="30">
         <v>20</v>
       </c>
-      <c r="B93" s="27" t="s">
-        <v>350</v>
-      </c>
-      <c r="C93" s="28">
+      <c r="B93" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="C93" s="32">
         <v>20</v>
       </c>
-      <c r="D93" s="26">
-        <v>2.7</v>
-      </c>
-      <c r="E93" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="F93" s="26" t="s">
-        <v>353</v>
+      <c r="D93" s="30" t="s">
+        <v>230</v>
+      </c>
+      <c r="E93" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F93" s="30" t="s">
+        <v>125</v>
       </c>
       <c r="G93" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F93),0)&gt;0), MAX($G$1:G92)+1, ""))</f>
@@ -4265,19 +4271,19 @@
         <v>20</v>
       </c>
       <c r="B94" s="31" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C94" s="32">
         <v>20</v>
       </c>
       <c r="D94" s="30" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="E94" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F94" s="30" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G94" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F94),0)&gt;0), MAX($G$1:G93)+1, ""))</f>
@@ -4293,19 +4299,19 @@
         <v>20</v>
       </c>
       <c r="B95" s="31" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C95" s="32">
         <v>20</v>
       </c>
       <c r="D95" s="30" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="E95" s="31" t="s">
-        <v>8</v>
+        <v>305</v>
       </c>
       <c r="F95" s="30" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G95" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F95),0)&gt;0), MAX($G$1:G94)+1, ""))</f>
@@ -4317,23 +4323,23 @@
       </c>
     </row>
     <row r="96" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A96" s="30">
+      <c r="A96" s="26">
         <v>20</v>
       </c>
-      <c r="B96" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="C96" s="32">
+      <c r="B96" s="27" t="s">
+        <v>369</v>
+      </c>
+      <c r="C96" s="28">
         <v>20</v>
       </c>
-      <c r="D96" s="30" t="s">
-        <v>223</v>
+      <c r="D96" s="26">
+        <v>1.5</v>
       </c>
       <c r="E96" s="31" t="s">
-        <v>305</v>
-      </c>
-      <c r="F96" s="30" t="s">
-        <v>121</v>
+        <v>299</v>
+      </c>
+      <c r="F96" s="26" t="s">
+        <v>370</v>
       </c>
       <c r="G96" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F96),0)&gt;0), MAX($G$1:G95)+1, ""))</f>
@@ -4345,23 +4351,23 @@
       </c>
     </row>
     <row r="97" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A97" s="26">
+      <c r="A97" s="30">
         <v>20</v>
       </c>
-      <c r="B97" s="27" t="s">
-        <v>371</v>
-      </c>
-      <c r="C97" s="28">
+      <c r="B97" s="31" t="s">
+        <v>257</v>
+      </c>
+      <c r="C97" s="32">
         <v>20</v>
       </c>
-      <c r="D97" s="26">
-        <v>1.5</v>
+      <c r="D97" s="30" t="s">
+        <v>225</v>
       </c>
       <c r="E97" s="31" t="s">
-        <v>299</v>
-      </c>
-      <c r="F97" s="26" t="s">
-        <v>372</v>
+        <v>8</v>
+      </c>
+      <c r="F97" s="30" t="s">
+        <v>258</v>
       </c>
       <c r="G97" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F97),0)&gt;0), MAX($G$1:G96)+1, ""))</f>
@@ -4377,19 +4383,19 @@
         <v>20</v>
       </c>
       <c r="B98" s="31" t="s">
-        <v>257</v>
+        <v>118</v>
       </c>
       <c r="C98" s="32">
         <v>20</v>
       </c>
       <c r="D98" s="30" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E98" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F98" s="30" t="s">
-        <v>258</v>
+        <v>119</v>
       </c>
       <c r="G98" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F98),0)&gt;0), MAX($G$1:G97)+1, ""))</f>
@@ -4405,19 +4411,19 @@
         <v>20</v>
       </c>
       <c r="B99" s="31" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C99" s="32">
         <v>20</v>
       </c>
       <c r="D99" s="30" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="E99" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F99" s="30" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G99" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F99),0)&gt;0), MAX($G$1:G98)+1, ""))</f>
@@ -4433,19 +4439,19 @@
         <v>20</v>
       </c>
       <c r="B100" s="31" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C100" s="32">
         <v>20</v>
       </c>
       <c r="D100" s="30" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="E100" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F100" s="30" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G100" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F100),0)&gt;0), MAX($G$1:G99)+1, ""))</f>
@@ -4457,23 +4463,23 @@
       </c>
     </row>
     <row r="101" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A101" s="30">
+      <c r="A101" s="26">
         <v>20</v>
       </c>
-      <c r="B101" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="C101" s="32">
+      <c r="B101" s="27" t="s">
+        <v>297</v>
+      </c>
+      <c r="C101" s="28">
         <v>20</v>
       </c>
-      <c r="D101" s="30" t="s">
-        <v>212</v>
-      </c>
-      <c r="E101" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F101" s="30" t="s">
-        <v>115</v>
+      <c r="D101" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E101" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="F101" s="26" t="s">
+        <v>298</v>
       </c>
       <c r="G101" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F101),0)&gt;0), MAX($G$1:G100)+1, ""))</f>
@@ -4485,23 +4491,23 @@
       </c>
     </row>
     <row r="102" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A102" s="26">
+      <c r="A102" s="30">
         <v>20</v>
       </c>
-      <c r="B102" s="27" t="s">
-        <v>297</v>
-      </c>
-      <c r="C102" s="28">
+      <c r="B102" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="C102" s="32">
         <v>20</v>
       </c>
-      <c r="D102" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E102" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="F102" s="26" t="s">
-        <v>298</v>
+      <c r="D102" s="30" t="s">
+        <v>219</v>
+      </c>
+      <c r="E102" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F102" s="30" t="s">
+        <v>113</v>
       </c>
       <c r="G102" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F102),0)&gt;0), MAX($G$1:G101)+1, ""))</f>
@@ -4517,19 +4523,19 @@
         <v>20</v>
       </c>
       <c r="B103" s="31" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C103" s="32">
         <v>20</v>
       </c>
       <c r="D103" s="30" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E103" s="31" t="s">
-        <v>8</v>
+        <v>299</v>
       </c>
       <c r="F103" s="30" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G103" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F103),0)&gt;0), MAX($G$1:G102)+1, ""))</f>
@@ -4545,19 +4551,19 @@
         <v>20</v>
       </c>
       <c r="B104" s="31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C104" s="32">
         <v>20</v>
       </c>
       <c r="D104" s="30" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E104" s="31" t="s">
-        <v>299</v>
+        <v>8</v>
       </c>
       <c r="F104" s="30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G104" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F104),0)&gt;0), MAX($G$1:G103)+1, ""))</f>
@@ -4569,76 +4575,76 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A105" s="30">
+      <c r="A105" s="36">
         <v>20</v>
       </c>
-      <c r="B105" s="31" t="s">
-        <v>108</v>
-      </c>
-      <c r="C105" s="32">
+      <c r="B105" s="37" t="s">
+        <v>330</v>
+      </c>
+      <c r="C105" s="38">
         <v>20</v>
       </c>
-      <c r="D105" s="30" t="s">
-        <v>218</v>
-      </c>
-      <c r="E105" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F105" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="G105" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F105),0)&gt;0), MAX($G$1:G104)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D105" s="36">
+        <v>3</v>
+      </c>
+      <c r="E105" s="37" t="s">
+        <v>304</v>
+      </c>
+      <c r="F105" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="G105" s="29"/>
       <c r="H105" s="21" t="b">
         <f>A105=C105</f>
         <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A106" s="36">
+      <c r="A106" s="26">
         <v>20</v>
       </c>
-      <c r="B106" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="C106" s="38">
+      <c r="B106" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C106" s="28">
         <v>20</v>
       </c>
-      <c r="D106" s="36">
-        <v>3</v>
-      </c>
-      <c r="E106" s="37" t="s">
-        <v>304</v>
-      </c>
-      <c r="F106" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="G106" s="29"/>
+      <c r="D106" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E106" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="F106" s="26" t="s">
+        <v>301</v>
+      </c>
+      <c r="G106" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F106),0)&gt;0), MAX($G$1:G105)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H106" s="21" t="b">
         <f>A106=C106</f>
         <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A107" s="26">
+      <c r="A107" s="30">
         <v>20</v>
       </c>
-      <c r="B107" s="27" t="s">
-        <v>302</v>
-      </c>
-      <c r="C107" s="28">
+      <c r="B107" s="31" t="s">
+        <v>366</v>
+      </c>
+      <c r="C107" s="32">
         <v>20</v>
       </c>
-      <c r="D107" s="26">
+      <c r="D107" s="30">
         <v>2.4</v>
       </c>
-      <c r="E107" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="F107" s="26" t="s">
-        <v>301</v>
+      <c r="E107" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="F107" s="30" t="s">
+        <v>367</v>
       </c>
       <c r="G107" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F107),0)&gt;0), MAX($G$1:G106)+1, ""))</f>
@@ -4654,19 +4660,19 @@
         <v>20</v>
       </c>
       <c r="B108" s="31" t="s">
-        <v>368</v>
+        <v>103</v>
       </c>
       <c r="C108" s="32">
         <v>20</v>
       </c>
-      <c r="D108" s="30">
-        <v>2.4</v>
+      <c r="D108" s="30" t="s">
+        <v>214</v>
       </c>
       <c r="E108" s="31" t="s">
         <v>60</v>
       </c>
       <c r="F108" s="30" t="s">
-        <v>369</v>
+        <v>104</v>
       </c>
       <c r="G108" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F108),0)&gt;0), MAX($G$1:G107)+1, ""))</f>
@@ -4678,23 +4684,23 @@
       </c>
     </row>
     <row r="109" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A109" s="30">
+      <c r="A109" s="26">
         <v>20</v>
       </c>
-      <c r="B109" s="31" t="s">
-        <v>103</v>
-      </c>
-      <c r="C109" s="32">
+      <c r="B109" s="27" t="s">
+        <v>339</v>
+      </c>
+      <c r="C109" s="28">
         <v>20</v>
       </c>
-      <c r="D109" s="30" t="s">
-        <v>214</v>
-      </c>
-      <c r="E109" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="F109" s="30" t="s">
-        <v>104</v>
+      <c r="D109" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E109" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F109" s="26" t="s">
+        <v>344</v>
       </c>
       <c r="G109" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F109),0)&gt;0), MAX($G$1:G108)+1, ""))</f>
@@ -4706,53 +4712,53 @@
       </c>
     </row>
     <row r="110" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A110" s="26">
+      <c r="A110" s="36">
         <v>20</v>
       </c>
-      <c r="B110" s="27" t="s">
-        <v>339</v>
-      </c>
-      <c r="C110" s="28">
+      <c r="B110" s="37" t="s">
+        <v>335</v>
+      </c>
+      <c r="C110" s="38">
         <v>20</v>
       </c>
-      <c r="D110" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E110" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F110" s="26" t="s">
-        <v>344</v>
-      </c>
-      <c r="G110" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F110),0)&gt;0), MAX($G$1:G109)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D110" s="36">
+        <v>3.2</v>
+      </c>
+      <c r="E110" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="F110" s="36" t="s">
+        <v>332</v>
+      </c>
+      <c r="G110" s="29"/>
       <c r="H110" s="21" t="b">
         <f>A110=C110</f>
         <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A111" s="36">
+      <c r="A111" s="30">
         <v>20</v>
       </c>
-      <c r="B111" s="37" t="s">
-        <v>335</v>
-      </c>
-      <c r="C111" s="38">
+      <c r="B111" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="C111" s="32">
         <v>20</v>
       </c>
-      <c r="D111" s="36">
-        <v>3.2</v>
-      </c>
-      <c r="E111" s="37" t="s">
-        <v>336</v>
-      </c>
-      <c r="F111" s="36" t="s">
-        <v>332</v>
-      </c>
-      <c r="G111" s="29"/>
+      <c r="D111" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E111" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F111" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="G111" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F111),0)&gt;0), MAX($G$1:G110)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H111" s="21" t="b">
         <f>A111=C111</f>
         <v>1</v>
@@ -4763,19 +4769,19 @@
         <v>20</v>
       </c>
       <c r="B112" s="31" t="s">
-        <v>101</v>
+        <v>263</v>
       </c>
       <c r="C112" s="32">
         <v>20</v>
       </c>
-      <c r="D112" s="30" t="s">
-        <v>207</v>
+      <c r="D112" s="30">
+        <v>6.2</v>
       </c>
       <c r="E112" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F112" s="30" t="s">
-        <v>102</v>
+        <v>264</v>
       </c>
       <c r="G112" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F112),0)&gt;0), MAX($G$1:G111)+1, ""))</f>
@@ -4791,19 +4797,19 @@
         <v>20</v>
       </c>
       <c r="B113" s="31" t="s">
-        <v>263</v>
+        <v>99</v>
       </c>
       <c r="C113" s="32">
         <v>20</v>
       </c>
-      <c r="D113" s="30">
-        <v>6.2</v>
+      <c r="D113" s="30" t="s">
+        <v>215</v>
       </c>
       <c r="E113" s="31" t="s">
-        <v>8</v>
+        <v>299</v>
       </c>
       <c r="F113" s="30" t="s">
-        <v>264</v>
+        <v>100</v>
       </c>
       <c r="G113" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F113),0)&gt;0), MAX($G$1:G112)+1, ""))</f>
@@ -4815,23 +4821,23 @@
       </c>
     </row>
     <row r="114" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A114" s="30">
+      <c r="A114" s="26">
         <v>20</v>
       </c>
-      <c r="B114" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="C114" s="32">
+      <c r="B114" s="27" t="s">
+        <v>300</v>
+      </c>
+      <c r="C114" s="28">
         <v>20</v>
       </c>
-      <c r="D114" s="30" t="s">
-        <v>215</v>
-      </c>
-      <c r="E114" s="31" t="s">
+      <c r="D114" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E114" s="27" t="s">
         <v>299</v>
       </c>
-      <c r="F114" s="30" t="s">
-        <v>100</v>
+      <c r="F114" s="26" t="s">
+        <v>301</v>
       </c>
       <c r="G114" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F114),0)&gt;0), MAX($G$1:G113)+1, ""))</f>
@@ -4843,23 +4849,23 @@
       </c>
     </row>
     <row r="115" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A115" s="26">
+      <c r="A115" s="30">
         <v>20</v>
       </c>
-      <c r="B115" s="27" t="s">
-        <v>300</v>
-      </c>
-      <c r="C115" s="28">
+      <c r="B115" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="C115" s="32">
         <v>20</v>
       </c>
-      <c r="D115" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E115" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="F115" s="26" t="s">
-        <v>301</v>
+      <c r="D115" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="E115" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F115" s="30" t="s">
+        <v>96</v>
       </c>
       <c r="G115" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F115),0)&gt;0), MAX($G$1:G114)+1, ""))</f>
@@ -4871,23 +4877,23 @@
       </c>
     </row>
     <row r="116" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A116" s="30">
+      <c r="A116" s="26">
         <v>20</v>
       </c>
-      <c r="B116" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="C116" s="32">
+      <c r="B116" s="27" t="s">
+        <v>355</v>
+      </c>
+      <c r="C116" s="28">
         <v>20</v>
       </c>
-      <c r="D116" s="30" t="s">
-        <v>216</v>
-      </c>
-      <c r="E116" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F116" s="30" t="s">
-        <v>96</v>
+      <c r="D116" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E116" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F116" s="26" t="s">
+        <v>356</v>
       </c>
       <c r="G116" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F116),0)&gt;0), MAX($G$1:G115)+1, ""))</f>
@@ -4899,23 +4905,23 @@
       </c>
     </row>
     <row r="117" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A117" s="26">
+      <c r="A117" s="30">
         <v>20</v>
       </c>
-      <c r="B117" s="27" t="s">
-        <v>357</v>
-      </c>
-      <c r="C117" s="28">
+      <c r="B117" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="C117" s="32">
         <v>20</v>
       </c>
-      <c r="D117" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E117" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F117" s="26" t="s">
-        <v>358</v>
+      <c r="D117" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="E117" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F117" s="30" t="s">
+        <v>92</v>
       </c>
       <c r="G117" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F117),0)&gt;0), MAX($G$1:G116)+1, ""))</f>
@@ -4931,19 +4937,19 @@
         <v>20</v>
       </c>
       <c r="B118" s="31" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C118" s="32">
         <v>20</v>
       </c>
       <c r="D118" s="30" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="E118" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F118" s="30" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G118" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F118),0)&gt;0), MAX($G$1:G117)+1, ""))</f>
@@ -4959,16 +4965,16 @@
         <v>20</v>
       </c>
       <c r="B119" s="31" t="s">
-        <v>89</v>
+        <v>290</v>
       </c>
       <c r="C119" s="32">
         <v>20</v>
       </c>
-      <c r="D119" s="30" t="s">
-        <v>223</v>
+      <c r="D119" s="30">
+        <v>1.8</v>
       </c>
       <c r="E119" s="31" t="s">
-        <v>8</v>
+        <v>291</v>
       </c>
       <c r="F119" s="30" t="s">
         <v>90</v>
@@ -4987,19 +4993,19 @@
         <v>20</v>
       </c>
       <c r="B120" s="31" t="s">
-        <v>290</v>
+        <v>87</v>
       </c>
       <c r="C120" s="32">
         <v>20</v>
       </c>
-      <c r="D120" s="30">
-        <v>1.8</v>
+      <c r="D120" s="30" t="s">
+        <v>222</v>
       </c>
       <c r="E120" s="31" t="s">
-        <v>291</v>
+        <v>8</v>
       </c>
       <c r="F120" s="30" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G120" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F120),0)&gt;0), MAX($G$1:G119)+1, ""))</f>
@@ -5015,19 +5021,19 @@
         <v>20</v>
       </c>
       <c r="B121" s="31" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C121" s="32">
         <v>20</v>
       </c>
       <c r="D121" s="30" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E121" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F121" s="30" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G121" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F121),0)&gt;0), MAX($G$1:G120)+1, ""))</f>
@@ -5043,19 +5049,19 @@
         <v>20</v>
       </c>
       <c r="B122" s="31" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C122" s="32">
         <v>20</v>
       </c>
       <c r="D122" s="30" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E122" s="31" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="F122" s="30" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G122" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F122),0)&gt;0), MAX($G$1:G121)+1, ""))</f>
@@ -5071,19 +5077,19 @@
         <v>20</v>
       </c>
       <c r="B123" s="31" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C123" s="32">
         <v>20</v>
       </c>
       <c r="D123" s="30" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E123" s="31" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F123" s="30" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G123" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F123),0)&gt;0), MAX($G$1:G122)+1, ""))</f>
@@ -5099,19 +5105,19 @@
         <v>20</v>
       </c>
       <c r="B124" s="31" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C124" s="32">
         <v>20</v>
       </c>
       <c r="D124" s="30" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E124" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F124" s="30" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G124" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F124),0)&gt;0), MAX($G$1:G123)+1, ""))</f>
@@ -5123,23 +5129,23 @@
       </c>
     </row>
     <row r="125" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A125" s="30">
-        <v>20</v>
-      </c>
-      <c r="B125" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="C125" s="32">
-        <v>20</v>
-      </c>
-      <c r="D125" s="30" t="s">
-        <v>216</v>
-      </c>
-      <c r="E125" s="31" t="s">
+      <c r="A125" s="26">
+        <v>25</v>
+      </c>
+      <c r="B125" s="27" t="s">
+        <v>178</v>
+      </c>
+      <c r="C125" s="28">
+        <v>25</v>
+      </c>
+      <c r="D125" s="26" t="s">
+        <v>225</v>
+      </c>
+      <c r="E125" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F125" s="30" t="s">
-        <v>77</v>
+      <c r="F125" s="26" t="s">
+        <v>179</v>
       </c>
       <c r="G125" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F125),0)&gt;0), MAX($G$1:G124)+1, ""))</f>
@@ -5155,19 +5161,19 @@
         <v>25</v>
       </c>
       <c r="B126" s="27" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C126" s="28">
         <v>25</v>
       </c>
       <c r="D126" s="26" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="E126" s="27" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F126" s="26" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G126" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F126),0)&gt;0), MAX($G$1:G125)+1, ""))</f>
@@ -5183,19 +5189,19 @@
         <v>25</v>
       </c>
       <c r="B127" s="27" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C127" s="28">
         <v>25</v>
       </c>
       <c r="D127" s="26" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E127" s="27" t="s">
         <v>131</v>
       </c>
       <c r="F127" s="26" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G127" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F127),0)&gt;0), MAX($G$1:G126)+1, ""))</f>
@@ -5211,19 +5217,19 @@
         <v>25</v>
       </c>
       <c r="B128" s="27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C128" s="28">
         <v>25</v>
       </c>
       <c r="D128" s="26" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="E128" s="27" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="F128" s="26" t="s">
-        <v>175</v>
+        <v>324</v>
       </c>
       <c r="G128" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F128),0)&gt;0), MAX($G$1:G127)+1, ""))</f>
@@ -5239,19 +5245,19 @@
         <v>25</v>
       </c>
       <c r="B129" s="27" t="s">
-        <v>173</v>
+        <v>359</v>
       </c>
       <c r="C129" s="28">
         <v>25</v>
       </c>
-      <c r="D129" s="26" t="s">
-        <v>224</v>
+      <c r="D129" s="26">
+        <v>3</v>
       </c>
       <c r="E129" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F129" s="26" t="s">
-        <v>324</v>
+        <v>360</v>
       </c>
       <c r="G129" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F129),0)&gt;0), MAX($G$1:G128)+1, ""))</f>
@@ -5267,19 +5273,19 @@
         <v>25</v>
       </c>
       <c r="B130" s="27" t="s">
-        <v>361</v>
+        <v>172</v>
       </c>
       <c r="C130" s="28">
         <v>25</v>
       </c>
       <c r="D130" s="26">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="E130" s="27" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="F130" s="26" t="s">
-        <v>362</v>
+        <v>338</v>
       </c>
       <c r="G130" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F130),0)&gt;0), MAX($G$1:G129)+1, ""))</f>
@@ -5291,23 +5297,23 @@
       </c>
     </row>
     <row r="131" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A131" s="26">
+      <c r="A131" s="30">
         <v>25</v>
       </c>
-      <c r="B131" s="27" t="s">
-        <v>172</v>
-      </c>
-      <c r="C131" s="28">
+      <c r="B131" s="31" t="s">
+        <v>284</v>
+      </c>
+      <c r="C131" s="32">
         <v>25</v>
       </c>
-      <c r="D131" s="26">
-        <v>2.7</v>
-      </c>
-      <c r="E131" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F131" s="26" t="s">
-        <v>338</v>
+      <c r="D131" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E131" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="F131" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G131" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F131),0)&gt;0), MAX($G$1:G130)+1, ""))</f>
@@ -5323,7 +5329,7 @@
         <v>25</v>
       </c>
       <c r="B132" s="31" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C132" s="32">
         <v>25</v>
@@ -5347,23 +5353,23 @@
       </c>
     </row>
     <row r="133" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A133" s="30">
+      <c r="A133" s="26">
         <v>25</v>
       </c>
-      <c r="B133" s="31" t="s">
-        <v>282</v>
-      </c>
-      <c r="C133" s="32">
+      <c r="B133" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="C133" s="28">
         <v>25</v>
       </c>
-      <c r="D133" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E133" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F133" s="30" t="s">
-        <v>102</v>
+      <c r="D133" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="E133" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="F133" s="26" t="s">
+        <v>171</v>
       </c>
       <c r="G133" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F133),0)&gt;0), MAX($G$1:G132)+1, ""))</f>
@@ -5379,19 +5385,19 @@
         <v>25</v>
       </c>
       <c r="B134" s="27" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C134" s="28">
         <v>25</v>
       </c>
       <c r="D134" s="26" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="E134" s="27" t="s">
-        <v>245</v>
+        <v>8</v>
       </c>
       <c r="F134" s="26" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G134" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F134),0)&gt;0), MAX($G$1:G133)+1, ""))</f>
@@ -5407,19 +5413,19 @@
         <v>25</v>
       </c>
       <c r="B135" s="27" t="s">
-        <v>168</v>
+        <v>357</v>
       </c>
       <c r="C135" s="28">
         <v>25</v>
       </c>
-      <c r="D135" s="26" t="s">
-        <v>217</v>
+      <c r="D135" s="26">
+        <v>3.4</v>
       </c>
       <c r="E135" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F135" s="26" t="s">
-        <v>169</v>
+        <v>358</v>
       </c>
       <c r="G135" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F135),0)&gt;0), MAX($G$1:G134)+1, ""))</f>
@@ -5431,23 +5437,23 @@
       </c>
     </row>
     <row r="136" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A136" s="26">
+      <c r="A136" s="30">
         <v>25</v>
       </c>
-      <c r="B136" s="27" t="s">
-        <v>359</v>
-      </c>
-      <c r="C136" s="28">
+      <c r="B136" s="31" t="s">
+        <v>278</v>
+      </c>
+      <c r="C136" s="32">
         <v>25</v>
       </c>
-      <c r="D136" s="26">
-        <v>3.4</v>
-      </c>
-      <c r="E136" s="27" t="s">
+      <c r="D136" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E136" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F136" s="26" t="s">
-        <v>360</v>
+      <c r="F136" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G136" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F136),0)&gt;0), MAX($G$1:G135)+1, ""))</f>
@@ -5459,23 +5465,23 @@
       </c>
     </row>
     <row r="137" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A137" s="30">
+      <c r="A137" s="26">
         <v>25</v>
       </c>
-      <c r="B137" s="31" t="s">
-        <v>278</v>
-      </c>
-      <c r="C137" s="32">
+      <c r="B137" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="C137" s="28">
         <v>25</v>
       </c>
-      <c r="D137" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E137" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F137" s="30" t="s">
-        <v>102</v>
+      <c r="D137" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="E137" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="F137" s="26" t="s">
+        <v>167</v>
       </c>
       <c r="G137" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F137),0)&gt;0), MAX($G$1:G136)+1, ""))</f>
@@ -5491,19 +5497,19 @@
         <v>25</v>
       </c>
       <c r="B138" s="27" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C138" s="28">
         <v>25</v>
       </c>
       <c r="D138" s="26" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="E138" s="27" t="s">
         <v>131</v>
       </c>
       <c r="F138" s="26" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G138" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F138),0)&gt;0), MAX($G$1:G137)+1, ""))</f>
@@ -5519,19 +5525,19 @@
         <v>25</v>
       </c>
       <c r="B139" s="27" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C139" s="28">
         <v>25</v>
       </c>
       <c r="D139" s="26" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E139" s="27" t="s">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="F139" s="26" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G139" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F139),0)&gt;0), MAX($G$1:G138)+1, ""))</f>
@@ -5547,19 +5553,19 @@
         <v>25</v>
       </c>
       <c r="B140" s="27" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C140" s="28">
         <v>25</v>
       </c>
       <c r="D140" s="26" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="E140" s="27" t="s">
         <v>81</v>
       </c>
       <c r="F140" s="26" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G140" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F140),0)&gt;0), MAX($G$1:G139)+1, ""))</f>
@@ -5575,19 +5581,19 @@
         <v>25</v>
       </c>
       <c r="B141" s="27" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C141" s="28">
         <v>25</v>
       </c>
       <c r="D141" s="26" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="E141" s="27" t="s">
         <v>81</v>
       </c>
       <c r="F141" s="26" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G141" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F141),0)&gt;0), MAX($G$1:G140)+1, ""))</f>
@@ -5603,19 +5609,19 @@
         <v>25</v>
       </c>
       <c r="B142" s="27" t="s">
-        <v>158</v>
+        <v>342</v>
       </c>
       <c r="C142" s="28">
         <v>25</v>
       </c>
-      <c r="D142" s="26" t="s">
-        <v>228</v>
+      <c r="D142" s="26">
+        <v>3.4</v>
       </c>
       <c r="E142" s="27" t="s">
         <v>81</v>
       </c>
       <c r="F142" s="26" t="s">
-        <v>159</v>
+        <v>343</v>
       </c>
       <c r="G142" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F142),0)&gt;0), MAX($G$1:G141)+1, ""))</f>
@@ -5631,22 +5637,22 @@
         <v>25</v>
       </c>
       <c r="B143" s="27" t="s">
-        <v>342</v>
+        <v>310</v>
       </c>
       <c r="C143" s="28">
         <v>25</v>
       </c>
       <c r="D143" s="26">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="E143" s="27" t="s">
-        <v>81</v>
+        <v>309</v>
       </c>
       <c r="F143" s="26" t="s">
-        <v>343</v>
+        <v>311</v>
       </c>
       <c r="G143" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F143),0)&gt;0), MAX($G$1:G142)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F143),0)&gt;0), MAX($G$1:G141)+1, ""))</f>
         <v/>
       </c>
       <c r="H143" s="21" t="b">
@@ -5659,22 +5665,22 @@
         <v>25</v>
       </c>
       <c r="B144" s="27" t="s">
-        <v>310</v>
+        <v>156</v>
       </c>
       <c r="C144" s="28">
         <v>25</v>
       </c>
-      <c r="D144" s="26">
-        <v>3.9</v>
+      <c r="D144" s="26" t="s">
+        <v>227</v>
       </c>
       <c r="E144" s="27" t="s">
-        <v>309</v>
+        <v>81</v>
       </c>
       <c r="F144" s="26" t="s">
-        <v>311</v>
+        <v>157</v>
       </c>
       <c r="G144" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F144),0)&gt;0), MAX($G$1:G142)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F144),0)&gt;0), MAX($G$1:G143)+1, ""))</f>
         <v/>
       </c>
       <c r="H144" s="21" t="b">
@@ -5687,19 +5693,19 @@
         <v>25</v>
       </c>
       <c r="B145" s="27" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C145" s="28">
         <v>25</v>
       </c>
       <c r="D145" s="26" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E145" s="27" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F145" s="26" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G145" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B145),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E145),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F145),0)&gt;0), MAX($G$1:G144)+1, ""))</f>
@@ -5715,19 +5721,19 @@
         <v>25</v>
       </c>
       <c r="B146" s="27" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C146" s="28">
         <v>25</v>
       </c>
       <c r="D146" s="26" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="E146" s="27" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F146" s="26" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G146" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F146),0)&gt;0), MAX($G$1:G145)+1, ""))</f>
@@ -5743,19 +5749,19 @@
         <v>25</v>
       </c>
       <c r="B147" s="27" t="s">
-        <v>152</v>
+        <v>247</v>
       </c>
       <c r="C147" s="28">
         <v>25</v>
       </c>
-      <c r="D147" s="26" t="s">
-        <v>230</v>
+      <c r="D147" s="39" t="s">
+        <v>229</v>
       </c>
       <c r="E147" s="27" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="F147" s="26" t="s">
-        <v>153</v>
+        <v>248</v>
       </c>
       <c r="G147" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F147),0)&gt;0), MAX($G$1:G146)+1, ""))</f>
@@ -5771,19 +5777,19 @@
         <v>25</v>
       </c>
       <c r="B148" s="27" t="s">
-        <v>247</v>
+        <v>150</v>
       </c>
       <c r="C148" s="28">
         <v>25</v>
       </c>
-      <c r="D148" s="39" t="s">
-        <v>229</v>
+      <c r="D148" s="26" t="s">
+        <v>235</v>
       </c>
       <c r="E148" s="27" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F148" s="26" t="s">
-        <v>248</v>
+        <v>151</v>
       </c>
       <c r="G148" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F148),0)&gt;0), MAX($G$1:G147)+1, ""))</f>
@@ -5795,23 +5801,23 @@
       </c>
     </row>
     <row r="149" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A149" s="26">
+      <c r="A149" s="30">
         <v>25</v>
       </c>
-      <c r="B149" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="C149" s="28">
+      <c r="B149" s="31" t="s">
+        <v>288</v>
+      </c>
+      <c r="C149" s="32">
         <v>25</v>
       </c>
-      <c r="D149" s="26" t="s">
-        <v>235</v>
-      </c>
-      <c r="E149" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="F149" s="26" t="s">
-        <v>151</v>
+      <c r="D149" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E149" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="F149" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G149" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B149),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E149),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F149),0)&gt;0), MAX($G$1:G148)+1, ""))</f>
@@ -5827,7 +5833,7 @@
         <v>25</v>
       </c>
       <c r="B150" s="31" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C150" s="32">
         <v>25</v>
@@ -5855,7 +5861,7 @@
         <v>25</v>
       </c>
       <c r="B151" s="31" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C151" s="32">
         <v>25</v>
@@ -5879,23 +5885,23 @@
       </c>
     </row>
     <row r="152" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A152" s="30">
+      <c r="A152" s="26">
         <v>25</v>
       </c>
-      <c r="B152" s="31" t="s">
-        <v>287</v>
-      </c>
-      <c r="C152" s="32">
+      <c r="B152" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="C152" s="28">
         <v>25</v>
       </c>
-      <c r="D152" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E152" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F152" s="30" t="s">
-        <v>102</v>
+      <c r="D152" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E152" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="F152" s="26" t="s">
+        <v>253</v>
       </c>
       <c r="G152" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B152),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E152),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F152),0)&gt;0), MAX($G$1:G151)+1, ""))</f>
@@ -5907,23 +5913,23 @@
       </c>
     </row>
     <row r="153" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A153" s="26">
+      <c r="A153" s="30">
         <v>25</v>
       </c>
-      <c r="B153" s="27" t="s">
-        <v>252</v>
-      </c>
-      <c r="C153" s="28">
+      <c r="B153" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="C153" s="32">
         <v>25</v>
       </c>
-      <c r="D153" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E153" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="F153" s="26" t="s">
-        <v>253</v>
+      <c r="D153" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E153" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="F153" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G153" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B153),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E153),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F153),0)&gt;0), MAX($G$1:G152)+1, ""))</f>
@@ -5935,26 +5941,26 @@
       </c>
     </row>
     <row r="154" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A154" s="30">
+      <c r="A154" s="26">
         <v>25</v>
       </c>
-      <c r="B154" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="C154" s="32">
+      <c r="B154" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="C154" s="28">
         <v>25</v>
       </c>
-      <c r="D154" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E154" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F154" s="30" t="s">
-        <v>102</v>
+      <c r="D154" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="E154" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F154" s="26" t="s">
+        <v>149</v>
       </c>
       <c r="G154" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B154),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E154),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F154),0)&gt;0), MAX($G$1:G153)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B154),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E154),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F154),0)&gt;0), MAX($G$1:G152)+1, ""))</f>
         <v/>
       </c>
       <c r="H154" s="21" t="b">
@@ -5963,26 +5969,26 @@
       </c>
     </row>
     <row r="155" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A155" s="26">
-        <v>25</v>
-      </c>
-      <c r="B155" s="27" t="s">
-        <v>148</v>
-      </c>
-      <c r="C155" s="28">
-        <v>25</v>
-      </c>
-      <c r="D155" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="E155" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F155" s="26" t="s">
-        <v>149</v>
+      <c r="A155" s="30">
+        <v>30</v>
+      </c>
+      <c r="B155" s="31" t="s">
+        <v>192</v>
+      </c>
+      <c r="C155" s="32">
+        <v>30</v>
+      </c>
+      <c r="D155" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="E155" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="F155" s="30" t="s">
+        <v>193</v>
       </c>
       <c r="G155" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F155),0)&gt;0), MAX($G$1:G153)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F155),0)&gt;0), MAX($G$1:G154)+1, ""))</f>
         <v/>
       </c>
       <c r="H155" s="21" t="b">
@@ -5995,19 +6001,19 @@
         <v>30</v>
       </c>
       <c r="B156" s="31" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C156" s="32">
         <v>30</v>
       </c>
       <c r="D156" s="30" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="E156" s="31" t="s">
         <v>131</v>
       </c>
       <c r="F156" s="30" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G156" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B156),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E156),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F156),0)&gt;0), MAX($G$1:G155)+1, ""))</f>
@@ -6023,13 +6029,13 @@
         <v>30</v>
       </c>
       <c r="B157" s="31" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C157" s="32">
         <v>30</v>
       </c>
       <c r="D157" s="30" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E157" s="31" t="s">
         <v>131</v>
@@ -6051,19 +6057,19 @@
         <v>30</v>
       </c>
       <c r="B158" s="31" t="s">
-        <v>189</v>
+        <v>246</v>
       </c>
       <c r="C158" s="32">
         <v>30</v>
       </c>
       <c r="D158" s="30" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="E158" s="31" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="F158" s="30" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G158" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B158),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E158),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F158),0)&gt;0), MAX($G$1:G157)+1, ""))</f>
@@ -6079,19 +6085,19 @@
         <v>30</v>
       </c>
       <c r="B159" s="31" t="s">
-        <v>246</v>
+        <v>186</v>
       </c>
       <c r="C159" s="32">
         <v>30</v>
       </c>
       <c r="D159" s="30" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="E159" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F159" s="30" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G159" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F159),0)&gt;0), MAX($G$1:G158)+1, ""))</f>
@@ -6107,19 +6113,19 @@
         <v>30</v>
       </c>
       <c r="B160" s="31" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C160" s="32">
         <v>30</v>
       </c>
       <c r="D160" s="30" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E160" s="31" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="F160" s="30" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G160" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B160),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E160),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F160),0)&gt;0), MAX($G$1:G159)+1, ""))</f>
@@ -6131,23 +6137,23 @@
       </c>
     </row>
     <row r="161" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A161" s="30">
+      <c r="A161" s="26">
         <v>30</v>
       </c>
-      <c r="B161" s="31" t="s">
-        <v>184</v>
-      </c>
-      <c r="C161" s="32">
+      <c r="B161" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="C161" s="28">
         <v>30</v>
       </c>
-      <c r="D161" s="30" t="s">
-        <v>228</v>
-      </c>
-      <c r="E161" s="31" t="s">
-        <v>81</v>
-      </c>
-      <c r="F161" s="30" t="s">
-        <v>185</v>
+      <c r="D161" s="26">
+        <v>5</v>
+      </c>
+      <c r="E161" s="27" t="s">
+        <v>378</v>
+      </c>
+      <c r="F161" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="G161" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B161),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E161),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F161),0)&gt;0), MAX($G$1:G160)+1, ""))</f>
@@ -11592,20 +11598,8 @@
       <c r="D1041" s="1"/>
       <c r="F1041" s="1"/>
     </row>
-    <row r="1042" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A1042" s="1"/>
-      <c r="C1042" s="1"/>
-      <c r="D1042" s="1"/>
-      <c r="F1042" s="1"/>
-    </row>
-    <row r="1043" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A1043" s="1"/>
-      <c r="C1043" s="1"/>
-      <c r="D1043" s="1"/>
-      <c r="F1043" s="1"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H167">
+  <autoFilter ref="A1:H165">
     <sortState ref="A2:H147">
       <sortCondition ref="A2:A147"/>
       <sortCondition ref="B2:B147"/>

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="386">
   <si>
     <t>Grupo</t>
   </si>
@@ -1168,6 +1168,21 @@
   </si>
   <si>
     <t>21710-100</t>
+  </si>
+  <si>
+    <t>Realengo - Cohab</t>
+  </si>
+  <si>
+    <t>21765-050</t>
+  </si>
+  <si>
+    <t>PARAPUA ATÉ PREDIOS (383)</t>
+  </si>
+  <si>
+    <t>PARAPUA APÓS PREDIOS (383)</t>
+  </si>
+  <si>
+    <t>TRAVESSA TUPY - UNIVERSAL</t>
   </si>
 </sst>
 </file>
@@ -2112,23 +2127,23 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="30">
+      <c r="A16" s="26">
         <v>13</v>
       </c>
-      <c r="B16" s="31" t="s">
-        <v>271</v>
-      </c>
-      <c r="C16" s="32">
+      <c r="B16" s="27" t="s">
+        <v>383</v>
+      </c>
+      <c r="C16" s="28">
         <v>13</v>
       </c>
-      <c r="D16" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="31" t="s">
-        <v>270</v>
-      </c>
-      <c r="F16" s="30" t="s">
-        <v>25</v>
+      <c r="D16" s="26">
+        <v>1</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>381</v>
+      </c>
+      <c r="F16" s="26" t="s">
+        <v>382</v>
       </c>
       <c r="G16" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B16),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E16),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F16),0)&gt;0), MAX($G$1:G15)+1, ""))</f>
@@ -2144,19 +2159,19 @@
         <v>13</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>13</v>
+        <v>271</v>
       </c>
       <c r="C17" s="32">
         <v>13</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>8</v>
+        <v>270</v>
       </c>
       <c r="F17" s="30" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G17" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B17),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E17),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F17),0)&gt;0), MAX($G$1:G16)+1, ""))</f>
@@ -2172,19 +2187,19 @@
         <v>13</v>
       </c>
       <c r="B18" s="31" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C18" s="32">
         <v>13</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E18" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F18" s="30" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G18" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B18),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E18),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F18),0)&gt;0), MAX($G$1:G17)+1, ""))</f>
@@ -2200,19 +2215,19 @@
         <v>13</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C19" s="32">
         <v>13</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E19" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F19" s="30" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G19" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B19),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E19),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F19),0)&gt;0), MAX($G$1:G18)+1, ""))</f>
@@ -2224,23 +2239,23 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="26">
-        <v>15</v>
-      </c>
-      <c r="B20" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" s="28">
-        <v>15</v>
-      </c>
-      <c r="D20" s="26" t="s">
-        <v>210</v>
-      </c>
-      <c r="E20" s="27" t="s">
-        <v>305</v>
-      </c>
-      <c r="F20" s="26" t="s">
-        <v>75</v>
+      <c r="A20" s="30">
+        <v>13</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="32">
+        <v>13</v>
+      </c>
+      <c r="D20" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="30" t="s">
+        <v>9</v>
       </c>
       <c r="G20" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B20),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E20),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F20),0)&gt;0), MAX($G$1:G19)+1, ""))</f>
@@ -2256,19 +2271,19 @@
         <v>15</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>371</v>
+        <v>74</v>
       </c>
       <c r="C21" s="28">
         <v>15</v>
       </c>
-      <c r="D21" s="26">
-        <v>2.1</v>
+      <c r="D21" s="26" t="s">
+        <v>210</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>245</v>
+        <v>305</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>372</v>
+        <v>75</v>
       </c>
       <c r="G21" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F21),0)&gt;0), MAX($G$1:G20)+1, ""))</f>
@@ -2284,19 +2299,19 @@
         <v>15</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>72</v>
+        <v>371</v>
       </c>
       <c r="C22" s="28">
         <v>15</v>
       </c>
-      <c r="D22" s="26" t="s">
-        <v>209</v>
+      <c r="D22" s="26">
+        <v>2.1</v>
       </c>
       <c r="E22" s="27" t="s">
-        <v>8</v>
+        <v>245</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>73</v>
+        <v>372</v>
       </c>
       <c r="G22" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B22),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E22),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F22),0)&gt;0), MAX($G$1:G21)+1, ""))</f>
@@ -2312,22 +2327,22 @@
         <v>15</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>362</v>
+        <v>72</v>
       </c>
       <c r="C23" s="28">
         <v>15</v>
       </c>
-      <c r="D23" s="26">
-        <v>1</v>
+      <c r="D23" s="26" t="s">
+        <v>209</v>
       </c>
       <c r="E23" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G23" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B23),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E23),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F23),0)&gt;0), MAX($G$1:G20)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B23),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E23),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F23),0)&gt;0), MAX($G$1:G22)+1, ""))</f>
         <v/>
       </c>
       <c r="H23" s="21" t="b">
@@ -2340,22 +2355,22 @@
         <v>15</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>66</v>
+        <v>362</v>
       </c>
       <c r="C24" s="28">
         <v>15</v>
       </c>
-      <c r="D24" s="26" t="s">
-        <v>219</v>
+      <c r="D24" s="26">
+        <v>1</v>
       </c>
       <c r="E24" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G24" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B24),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E24),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F24),0)&gt;0), MAX($G$1:G23)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B24),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E24),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F24),0)&gt;0), MAX($G$1:G21)+1, ""))</f>
         <v/>
       </c>
       <c r="H24" s="21" t="b">
@@ -2368,19 +2383,19 @@
         <v>15</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C25" s="28">
         <v>15</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="E25" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G25" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B25),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E25),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F25),0)&gt;0), MAX($G$1:G24)+1, ""))</f>
@@ -2396,7 +2411,7 @@
         <v>15</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>266</v>
+        <v>64</v>
       </c>
       <c r="C26" s="28">
         <v>15</v>
@@ -2405,7 +2420,7 @@
         <v>206</v>
       </c>
       <c r="E26" s="27" t="s">
-        <v>267</v>
+        <v>8</v>
       </c>
       <c r="F26" s="26" t="s">
         <v>65</v>
@@ -2424,19 +2439,19 @@
         <v>15</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>345</v>
+        <v>266</v>
       </c>
       <c r="C27" s="28">
         <v>15</v>
       </c>
-      <c r="D27" s="26">
-        <v>2.5</v>
+      <c r="D27" s="26" t="s">
+        <v>206</v>
       </c>
       <c r="E27" s="27" t="s">
-        <v>8</v>
+        <v>267</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>346</v>
+        <v>65</v>
       </c>
       <c r="G27" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B27),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E27),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F27),0)&gt;0), MAX($G$1:G26)+1, ""))</f>
@@ -2452,19 +2467,19 @@
         <v>15</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>259</v>
+        <v>345</v>
       </c>
       <c r="C28" s="28">
         <v>15</v>
       </c>
-      <c r="D28" s="26" t="s">
-        <v>7</v>
+      <c r="D28" s="26">
+        <v>2.5</v>
       </c>
       <c r="E28" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>261</v>
+        <v>346</v>
       </c>
       <c r="G28" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B28),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E28),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F28),0)&gt;0), MAX($G$1:G27)+1, ""))</f>
@@ -2480,19 +2495,19 @@
         <v>15</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>376</v>
+        <v>259</v>
       </c>
       <c r="C29" s="28">
         <v>15</v>
       </c>
-      <c r="D29" s="26">
-        <v>2</v>
+      <c r="D29" s="26" t="s">
+        <v>7</v>
       </c>
       <c r="E29" s="27" t="s">
-        <v>350</v>
+        <v>8</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>348</v>
+        <v>261</v>
       </c>
       <c r="G29" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B29),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E29),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F29),0)&gt;0), MAX($G$1:G28)+1, ""))</f>
@@ -2508,19 +2523,19 @@
         <v>15</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>57</v>
+        <v>376</v>
       </c>
       <c r="C30" s="28">
         <v>15</v>
       </c>
-      <c r="D30" s="26" t="s">
-        <v>223</v>
+      <c r="D30" s="26">
+        <v>2</v>
       </c>
       <c r="E30" s="27" t="s">
-        <v>8</v>
+        <v>350</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>58</v>
+        <v>348</v>
       </c>
       <c r="G30" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B30),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E30),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F30),0)&gt;0), MAX($G$1:G29)+1, ""))</f>
@@ -2536,19 +2551,19 @@
         <v>15</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>268</v>
+        <v>57</v>
       </c>
       <c r="C31" s="28">
         <v>15</v>
       </c>
       <c r="D31" s="26" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="E31" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F31" s="26" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G31" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B31),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E31),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F31),0)&gt;0), MAX($G$1:G30)+1, ""))</f>
@@ -2564,19 +2579,19 @@
         <v>15</v>
       </c>
       <c r="B32" s="27" t="s">
-        <v>306</v>
+        <v>268</v>
       </c>
       <c r="C32" s="28">
         <v>15</v>
       </c>
-      <c r="D32" s="26">
-        <v>2.1</v>
+      <c r="D32" s="26" t="s">
+        <v>205</v>
       </c>
       <c r="E32" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F32" s="26" t="s">
-        <v>307</v>
+        <v>56</v>
       </c>
       <c r="G32" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B32),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E32),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F32),0)&gt;0), MAX($G$1:G31)+1, ""))</f>
@@ -2592,19 +2607,19 @@
         <v>15</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>54</v>
+        <v>306</v>
       </c>
       <c r="C33" s="28">
         <v>15</v>
       </c>
-      <c r="D33" s="26" t="s">
-        <v>204</v>
+      <c r="D33" s="26">
+        <v>2.1</v>
       </c>
       <c r="E33" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F33" s="26" t="s">
-        <v>55</v>
+        <v>307</v>
       </c>
       <c r="G33" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B33),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E33),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F33),0)&gt;0), MAX($G$1:G32)+1, ""))</f>
@@ -2620,19 +2635,19 @@
         <v>15</v>
       </c>
       <c r="B34" s="27" t="s">
-        <v>277</v>
+        <v>54</v>
       </c>
       <c r="C34" s="28">
         <v>15</v>
       </c>
       <c r="D34" s="26" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E34" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F34" s="26" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="G34" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B34),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E34),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F34),0)&gt;0), MAX($G$1:G33)+1, ""))</f>
@@ -2648,19 +2663,19 @@
         <v>15</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="C35" s="28">
         <v>15</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>21</v>
+        <v>210</v>
       </c>
       <c r="E35" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>262</v>
+        <v>75</v>
       </c>
       <c r="G35" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F35),0)&gt;0), MAX($G$1:G34)+1, ""))</f>
@@ -2676,19 +2691,19 @@
         <v>15</v>
       </c>
       <c r="B36" s="27" t="s">
-        <v>292</v>
+        <v>260</v>
       </c>
       <c r="C36" s="28">
         <v>15</v>
       </c>
-      <c r="D36" s="26">
-        <v>2.2000000000000002</v>
+      <c r="D36" s="26" t="s">
+        <v>21</v>
       </c>
       <c r="E36" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F36" s="26" t="s">
-        <v>293</v>
+        <v>262</v>
       </c>
       <c r="G36" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B36),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E36),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F36),0)&gt;0), MAX($G$1:G35)+1, ""))</f>
@@ -2704,19 +2719,19 @@
         <v>15</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>374</v>
+        <v>292</v>
       </c>
       <c r="C37" s="28">
         <v>15</v>
       </c>
       <c r="D37" s="26">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E37" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>373</v>
+        <v>293</v>
       </c>
       <c r="G37" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F37),0)&gt;0), MAX($G$1:G36)+1, ""))</f>
@@ -2732,19 +2747,19 @@
         <v>15</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="C38" s="28">
         <v>15</v>
       </c>
       <c r="D38" s="26">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="E38" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F38" s="26" t="s">
-        <v>353</v>
+        <v>373</v>
       </c>
       <c r="G38" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F38),0)&gt;0), MAX($G$1:G37)+1, ""))</f>
@@ -2760,19 +2775,19 @@
         <v>15</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>50</v>
+        <v>352</v>
       </c>
       <c r="C39" s="28">
         <v>15</v>
       </c>
-      <c r="D39" s="26" t="s">
-        <v>213</v>
+      <c r="D39" s="26">
+        <v>1.5</v>
       </c>
       <c r="E39" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F39" s="26" t="s">
-        <v>51</v>
+        <v>353</v>
       </c>
       <c r="G39" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B39),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E39),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F39),0)&gt;0), MAX($G$1:G38)+1, ""))</f>
@@ -2788,19 +2803,19 @@
         <v>15</v>
       </c>
       <c r="B40" s="27" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C40" s="28">
         <v>15</v>
       </c>
       <c r="D40" s="26" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="E40" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F40" s="26" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G40" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B40),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E40),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F40),0)&gt;0), MAX($G$1:G39)+1, ""))</f>
@@ -2816,19 +2831,19 @@
         <v>15</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>44</v>
+        <v>384</v>
       </c>
       <c r="C41" s="28">
         <v>15</v>
       </c>
-      <c r="D41" s="26" t="s">
-        <v>225</v>
+      <c r="D41" s="26">
+        <v>1.3</v>
       </c>
       <c r="E41" s="27" t="s">
-        <v>8</v>
+        <v>381</v>
       </c>
       <c r="F41" s="26" t="s">
-        <v>45</v>
+        <v>382</v>
       </c>
       <c r="G41" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B41),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E41),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F41),0)&gt;0), MAX($G$1:G40)+1, ""))</f>
@@ -2844,19 +2859,19 @@
         <v>15</v>
       </c>
       <c r="B42" s="27" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C42" s="28">
         <v>15</v>
       </c>
       <c r="D42" s="26" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="E42" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F42" s="26" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G42" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B42),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E42),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F42),0)&gt;0), MAX($G$1:G41)+1, ""))</f>
@@ -2872,19 +2887,19 @@
         <v>15</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>308</v>
+        <v>44</v>
       </c>
       <c r="C43" s="28">
         <v>15</v>
       </c>
-      <c r="D43" s="26">
-        <v>2.2000000000000002</v>
+      <c r="D43" s="26" t="s">
+        <v>225</v>
       </c>
       <c r="E43" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F43" s="26" t="s">
-        <v>293</v>
+        <v>45</v>
       </c>
       <c r="G43" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F43),0)&gt;0), MAX($G$1:G42)+1, ""))</f>
@@ -2900,19 +2915,19 @@
         <v>15</v>
       </c>
       <c r="B44" s="27" t="s">
-        <v>244</v>
+        <v>40</v>
       </c>
       <c r="C44" s="28">
         <v>15</v>
       </c>
-      <c r="D44" s="26">
-        <v>2.1</v>
+      <c r="D44" s="26" t="s">
+        <v>212</v>
       </c>
       <c r="E44" s="27" t="s">
-        <v>245</v>
+        <v>8</v>
       </c>
       <c r="F44" s="26" t="s">
-        <v>202</v>
+        <v>41</v>
       </c>
       <c r="G44" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F44),0)&gt;0), MAX($G$1:G43)+1, ""))</f>
@@ -2928,22 +2943,22 @@
         <v>15</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>38</v>
+        <v>308</v>
       </c>
       <c r="C45" s="28">
         <v>15</v>
       </c>
-      <c r="D45" s="26" t="s">
-        <v>211</v>
+      <c r="D45" s="26">
+        <v>2.2000000000000002</v>
       </c>
       <c r="E45" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F45" s="26" t="s">
-        <v>39</v>
+        <v>293</v>
       </c>
       <c r="G45" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F45),0)&gt;0), MAX($G$1:G40)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F45),0)&gt;0), MAX($G$1:G44)+1, ""))</f>
         <v/>
       </c>
       <c r="H45" s="21" t="b">
@@ -2956,19 +2971,19 @@
         <v>15</v>
       </c>
       <c r="B46" s="27" t="s">
-        <v>341</v>
+        <v>244</v>
       </c>
       <c r="C46" s="28">
         <v>15</v>
       </c>
       <c r="D46" s="26">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="E46" s="27" t="s">
-        <v>8</v>
+        <v>245</v>
       </c>
       <c r="F46" s="26" t="s">
-        <v>347</v>
+        <v>202</v>
       </c>
       <c r="G46" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F46),0)&gt;0), MAX($G$1:G45)+1, ""))</f>
@@ -2984,22 +2999,22 @@
         <v>15</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C47" s="28">
         <v>15</v>
       </c>
       <c r="D47" s="26" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E47" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F47" s="26" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G47" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F47),0)&gt;0), MAX($G$1:G46)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F47),0)&gt;0), MAX($G$1:G42)+1, ""))</f>
         <v/>
       </c>
       <c r="H47" s="21" t="b">
@@ -3012,19 +3027,19 @@
         <v>15</v>
       </c>
       <c r="B48" s="27" t="s">
-        <v>280</v>
+        <v>341</v>
       </c>
       <c r="C48" s="28">
         <v>15</v>
       </c>
-      <c r="D48" s="26" t="s">
-        <v>209</v>
+      <c r="D48" s="26">
+        <v>1.4</v>
       </c>
       <c r="E48" s="27" t="s">
-        <v>267</v>
+        <v>8</v>
       </c>
       <c r="F48" s="26" t="s">
-        <v>33</v>
+        <v>347</v>
       </c>
       <c r="G48" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F48),0)&gt;0), MAX($G$1:G47)+1, ""))</f>
@@ -3036,23 +3051,23 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="33">
-        <v>17</v>
-      </c>
-      <c r="B49" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="C49" s="35">
-        <v>17</v>
-      </c>
-      <c r="D49" s="33" t="s">
-        <v>214</v>
-      </c>
-      <c r="E49" s="34" t="s">
+      <c r="A49" s="26">
+        <v>15</v>
+      </c>
+      <c r="B49" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="C49" s="28">
+        <v>15</v>
+      </c>
+      <c r="D49" s="26" t="s">
+        <v>210</v>
+      </c>
+      <c r="E49" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F49" s="33" t="s">
-        <v>71</v>
+      <c r="F49" s="26" t="s">
+        <v>35</v>
       </c>
       <c r="G49" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F49),0)&gt;0), MAX($G$1:G48)+1, ""))</f>
@@ -3064,23 +3079,23 @@
       </c>
     </row>
     <row r="50" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A50" s="33">
-        <v>17</v>
-      </c>
-      <c r="B50" s="34" t="s">
-        <v>281</v>
-      </c>
-      <c r="C50" s="35">
-        <v>17</v>
-      </c>
-      <c r="D50" s="33" t="s">
-        <v>222</v>
-      </c>
-      <c r="E50" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F50" s="33" t="s">
-        <v>68</v>
+      <c r="A50" s="26">
+        <v>15</v>
+      </c>
+      <c r="B50" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="C50" s="28">
+        <v>15</v>
+      </c>
+      <c r="D50" s="26">
+        <v>1.2</v>
+      </c>
+      <c r="E50" s="27" t="s">
+        <v>381</v>
+      </c>
+      <c r="F50" s="26" t="s">
+        <v>382</v>
       </c>
       <c r="G50" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F50),0)&gt;0), MAX($G$1:G49)+1, ""))</f>
@@ -3093,24 +3108,27 @@
     </row>
     <row r="51" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A51" s="26">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>313</v>
+        <v>280</v>
       </c>
       <c r="C51" s="28">
-        <v>17</v>
-      </c>
-      <c r="D51" s="26">
-        <v>1.7</v>
+        <v>15</v>
+      </c>
+      <c r="D51" s="26" t="s">
+        <v>209</v>
       </c>
       <c r="E51" s="27" t="s">
-        <v>60</v>
+        <v>267</v>
       </c>
       <c r="F51" s="26" t="s">
-        <v>319</v>
-      </c>
-      <c r="G51" s="29"/>
+        <v>33</v>
+      </c>
+      <c r="G51" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F51),0)&gt;0), MAX($G$1:G50)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H51" s="21" t="b">
         <f>A51=C51</f>
         <v>1</v>
@@ -3121,19 +3139,19 @@
         <v>17</v>
       </c>
       <c r="B52" s="34" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C52" s="35">
         <v>17</v>
       </c>
       <c r="D52" s="33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E52" s="34" t="s">
         <v>8</v>
       </c>
       <c r="F52" s="33" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="G52" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F52),0)&gt;0), MAX($G$1:G51)+1, ""))</f>
@@ -3149,19 +3167,19 @@
         <v>17</v>
       </c>
       <c r="B53" s="34" t="s">
-        <v>59</v>
+        <v>281</v>
       </c>
       <c r="C53" s="35">
         <v>17</v>
       </c>
       <c r="D53" s="33" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="E53" s="34" t="s">
         <v>60</v>
       </c>
       <c r="F53" s="33" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G53" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F53),0)&gt;0), MAX($G$1:G52)+1, ""))</f>
@@ -3177,19 +3195,19 @@
         <v>17</v>
       </c>
       <c r="B54" s="27" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C54" s="28">
         <v>17</v>
       </c>
       <c r="D54" s="26">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="E54" s="27" t="s">
         <v>60</v>
       </c>
       <c r="F54" s="26" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="G54" s="29"/>
       <c r="H54" s="21" t="b">
@@ -3198,26 +3216,26 @@
       </c>
     </row>
     <row r="55" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="26">
+      <c r="A55" s="33">
         <v>17</v>
       </c>
-      <c r="B55" s="27" t="s">
-        <v>340</v>
-      </c>
-      <c r="C55" s="28">
+      <c r="B55" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C55" s="35">
         <v>17</v>
       </c>
-      <c r="D55" s="26">
-        <v>3.3</v>
-      </c>
-      <c r="E55" s="27" t="s">
+      <c r="D55" s="33" t="s">
+        <v>215</v>
+      </c>
+      <c r="E55" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F55" s="26" t="s">
-        <v>349</v>
+      <c r="F55" s="33" t="s">
+        <v>63</v>
       </c>
       <c r="G55" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F55),0)&gt;0), MAX($G$1:G53)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F55),0)&gt;0), MAX($G$1:G54)+1, ""))</f>
         <v/>
       </c>
       <c r="H55" s="21" t="b">
@@ -3226,53 +3244,53 @@
       </c>
     </row>
     <row r="56" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A56" s="26">
+      <c r="A56" s="33">
         <v>17</v>
       </c>
-      <c r="B56" s="27" t="s">
-        <v>316</v>
-      </c>
-      <c r="C56" s="28">
+      <c r="B56" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="C56" s="35">
         <v>17</v>
       </c>
-      <c r="D56" s="26">
-        <v>1.9</v>
-      </c>
-      <c r="E56" s="27" t="s">
+      <c r="D56" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="E56" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="F56" s="26" t="s">
-        <v>322</v>
-      </c>
-      <c r="G56" s="29"/>
+      <c r="F56" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="G56" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F56),0)&gt;0), MAX($G$1:G55)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H56" s="21" t="b">
         <f>A56=C56</f>
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A57" s="36">
+      <c r="A57" s="26">
         <v>17</v>
       </c>
-      <c r="B57" s="37" t="s">
-        <v>289</v>
-      </c>
-      <c r="C57" s="38">
+      <c r="B57" s="27" t="s">
+        <v>315</v>
+      </c>
+      <c r="C57" s="28">
         <v>17</v>
       </c>
-      <c r="D57" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="E57" s="37" t="s">
+      <c r="D57" s="26">
+        <v>3</v>
+      </c>
+      <c r="E57" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="F57" s="36" t="s">
-        <v>111</v>
-      </c>
-      <c r="G57" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F57),0)&gt;0), MAX($G$1:G56)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="F57" s="26" t="s">
+        <v>321</v>
+      </c>
+      <c r="G57" s="29"/>
       <c r="H57" s="21" t="b">
         <f>A57=C57</f>
         <v>1</v>
@@ -3283,21 +3301,24 @@
         <v>17</v>
       </c>
       <c r="B58" s="27" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="C58" s="28">
         <v>17</v>
       </c>
       <c r="D58" s="26">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="E58" s="27" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="F58" s="26" t="s">
-        <v>320</v>
-      </c>
-      <c r="G58" s="29"/>
+        <v>349</v>
+      </c>
+      <c r="G58" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F58),0)&gt;0), MAX($G$1:G56)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H58" s="21" t="b">
         <f>A58=C58</f>
         <v>1</v>
@@ -3308,19 +3329,19 @@
         <v>17</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C59" s="28">
         <v>17</v>
       </c>
       <c r="D59" s="26">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="E59" s="27" t="s">
         <v>60</v>
       </c>
       <c r="F59" s="26" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G59" s="29"/>
       <c r="H59" s="21" t="b">
@@ -3333,19 +3354,19 @@
         <v>17</v>
       </c>
       <c r="B60" s="37" t="s">
-        <v>106</v>
+        <v>289</v>
       </c>
       <c r="C60" s="38">
         <v>17</v>
       </c>
       <c r="D60" s="36" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E60" s="37" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F60" s="36" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G60" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F60),0)&gt;0), MAX($G$1:G59)+1, ""))</f>
@@ -3357,79 +3378,73 @@
       </c>
     </row>
     <row r="61" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A61" s="36">
+      <c r="A61" s="26">
         <v>17</v>
       </c>
-      <c r="B61" s="37" t="s">
-        <v>303</v>
-      </c>
-      <c r="C61" s="38">
+      <c r="B61" s="27" t="s">
+        <v>314</v>
+      </c>
+      <c r="C61" s="28">
         <v>17</v>
       </c>
-      <c r="D61" s="36" t="s">
-        <v>229</v>
-      </c>
-      <c r="E61" s="37" t="s">
-        <v>304</v>
-      </c>
-      <c r="F61" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="G61" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F61),0)&gt;0), MAX($G$1:G60)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D61" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E61" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F61" s="26" t="s">
+        <v>320</v>
+      </c>
+      <c r="G61" s="29"/>
       <c r="H61" s="21" t="b">
         <f>A61=C61</f>
         <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A62" s="33">
+      <c r="A62" s="26">
         <v>17</v>
       </c>
-      <c r="B62" s="34" t="s">
-        <v>52</v>
-      </c>
-      <c r="C62" s="35">
+      <c r="B62" s="27" t="s">
+        <v>317</v>
+      </c>
+      <c r="C62" s="28">
         <v>17</v>
       </c>
-      <c r="D62" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="E62" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F62" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="G62" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F62),0)&gt;0), MAX($G$1:G58)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D62" s="26">
+        <v>2</v>
+      </c>
+      <c r="E62" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F62" s="26" t="s">
+        <v>323</v>
+      </c>
+      <c r="G62" s="29"/>
       <c r="H62" s="21" t="b">
         <f>A62=C62</f>
         <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A63" s="26">
+      <c r="A63" s="36">
         <v>17</v>
       </c>
-      <c r="B63" s="27" t="s">
-        <v>368</v>
-      </c>
-      <c r="C63" s="28">
+      <c r="B63" s="37" t="s">
+        <v>106</v>
+      </c>
+      <c r="C63" s="38">
         <v>17</v>
       </c>
-      <c r="D63" s="26">
-        <v>1.8</v>
-      </c>
-      <c r="E63" s="27" t="s">
+      <c r="D63" s="36" t="s">
+        <v>220</v>
+      </c>
+      <c r="E63" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F63" s="26" t="s">
-        <v>354</v>
+      <c r="F63" s="36" t="s">
+        <v>107</v>
       </c>
       <c r="G63" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F63),0)&gt;0), MAX($G$1:G62)+1, ""))</f>
@@ -3441,23 +3456,23 @@
       </c>
     </row>
     <row r="64" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A64" s="26">
+      <c r="A64" s="36">
         <v>17</v>
       </c>
-      <c r="B64" s="27" t="s">
-        <v>379</v>
-      </c>
-      <c r="C64" s="28">
+      <c r="B64" s="37" t="s">
+        <v>303</v>
+      </c>
+      <c r="C64" s="38">
         <v>17</v>
       </c>
-      <c r="D64" s="26">
-        <v>1.2</v>
-      </c>
-      <c r="E64" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F64" s="26" t="s">
-        <v>380</v>
+      <c r="D64" s="36" t="s">
+        <v>229</v>
+      </c>
+      <c r="E64" s="37" t="s">
+        <v>304</v>
+      </c>
+      <c r="F64" s="36" t="s">
+        <v>105</v>
       </c>
       <c r="G64" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F64),0)&gt;0), MAX($G$1:G63)+1, ""))</f>
@@ -3473,22 +3488,22 @@
         <v>17</v>
       </c>
       <c r="B65" s="34" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C65" s="35">
         <v>17</v>
       </c>
       <c r="D65" s="33" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E65" s="34" t="s">
         <v>8</v>
       </c>
       <c r="F65" s="33" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G65" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F65),0)&gt;0), MAX($G$1:G64)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F65),0)&gt;0), MAX($G$1:G61)+1, ""))</f>
         <v/>
       </c>
       <c r="H65" s="21" t="b">
@@ -3497,23 +3512,23 @@
       </c>
     </row>
     <row r="66" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A66" s="36">
+      <c r="A66" s="26">
         <v>17</v>
       </c>
-      <c r="B66" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="C66" s="38">
+      <c r="B66" s="27" t="s">
+        <v>368</v>
+      </c>
+      <c r="C66" s="28">
         <v>17</v>
       </c>
-      <c r="D66" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="E66" s="37" t="s">
+      <c r="D66" s="26">
+        <v>1.8</v>
+      </c>
+      <c r="E66" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F66" s="36" t="s">
-        <v>98</v>
+      <c r="F66" s="26" t="s">
+        <v>354</v>
       </c>
       <c r="G66" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F66),0)&gt;0), MAX($G$1:G65)+1, ""))</f>
@@ -3529,19 +3544,19 @@
         <v>17</v>
       </c>
       <c r="B67" s="27" t="s">
-        <v>42</v>
+        <v>379</v>
       </c>
       <c r="C67" s="28">
         <v>17</v>
       </c>
-      <c r="D67" s="26" t="s">
-        <v>206</v>
+      <c r="D67" s="26">
+        <v>1.2</v>
       </c>
       <c r="E67" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F67" s="26" t="s">
-        <v>43</v>
+        <v>380</v>
       </c>
       <c r="G67" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F67),0)&gt;0), MAX($G$1:G66)+1, ""))</f>
@@ -3553,23 +3568,23 @@
       </c>
     </row>
     <row r="68" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A68" s="36">
+      <c r="A68" s="33">
         <v>17</v>
       </c>
-      <c r="B68" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="C68" s="38">
+      <c r="B68" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="C68" s="35">
         <v>17</v>
       </c>
-      <c r="D68" s="36" t="s">
-        <v>217</v>
-      </c>
-      <c r="E68" s="37" t="s">
+      <c r="D68" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="E68" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F68" s="36" t="s">
-        <v>94</v>
+      <c r="F68" s="33" t="s">
+        <v>49</v>
       </c>
       <c r="G68" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F68),0)&gt;0), MAX($G$1:G67)+1, ""))</f>
@@ -3581,80 +3596,86 @@
       </c>
     </row>
     <row r="69" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A69" s="33">
+      <c r="A69" s="36">
         <v>17</v>
       </c>
-      <c r="B69" s="34" t="s">
-        <v>327</v>
-      </c>
-      <c r="C69" s="35">
+      <c r="B69" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="C69" s="38">
         <v>17</v>
       </c>
-      <c r="D69" s="33">
-        <v>1.9</v>
-      </c>
-      <c r="E69" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F69" s="33" t="s">
-        <v>329</v>
-      </c>
-      <c r="G69" s="29" t="s">
-        <v>326</v>
+      <c r="D69" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E69" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F69" s="36" t="s">
+        <v>98</v>
+      </c>
+      <c r="G69" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F69),0)&gt;0), MAX($G$1:G68)+1, ""))</f>
+        <v/>
       </c>
       <c r="H69" s="21" t="b">
+        <f>A69=C69</f>
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A70" s="33">
+      <c r="A70" s="26">
         <v>17</v>
       </c>
-      <c r="B70" s="34" t="s">
-        <v>325</v>
-      </c>
-      <c r="C70" s="35">
+      <c r="B70" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C70" s="28">
         <v>17</v>
       </c>
-      <c r="D70" s="33">
-        <v>1.9</v>
-      </c>
-      <c r="E70" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F70" s="33" t="s">
-        <v>329</v>
-      </c>
-      <c r="G70" s="29" t="s">
-        <v>326</v>
+      <c r="D70" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="E70" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F70" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="G70" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F70),0)&gt;0), MAX($G$1:G69)+1, ""))</f>
+        <v/>
       </c>
       <c r="H70" s="21" t="b">
+        <f>A70=C70</f>
         <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A71" s="33">
+      <c r="A71" s="36">
         <v>17</v>
       </c>
-      <c r="B71" s="34" t="s">
-        <v>328</v>
-      </c>
-      <c r="C71" s="35">
+      <c r="B71" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="C71" s="38">
         <v>17</v>
       </c>
-      <c r="D71" s="33">
-        <v>1.9</v>
-      </c>
-      <c r="E71" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F71" s="33" t="s">
-        <v>329</v>
-      </c>
-      <c r="G71" s="29" t="s">
-        <v>326</v>
+      <c r="D71" s="36" t="s">
+        <v>217</v>
+      </c>
+      <c r="E71" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F71" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="G71" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F71),0)&gt;0), MAX($G$1:G70)+1, ""))</f>
+        <v/>
       </c>
       <c r="H71" s="21" t="b">
+        <f>A71=C71</f>
         <v>1</v>
       </c>
     </row>
@@ -3663,54 +3684,50 @@
         <v>17</v>
       </c>
       <c r="B72" s="34" t="s">
-        <v>36</v>
+        <v>327</v>
       </c>
       <c r="C72" s="35">
         <v>17</v>
       </c>
-      <c r="D72" s="33" t="s">
-        <v>214</v>
+      <c r="D72" s="33">
+        <v>1.9</v>
       </c>
       <c r="E72" s="34" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F72" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="G72" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F72),0)&gt;0), MAX($G$1:G71)+1, ""))</f>
-        <v/>
+        <v>329</v>
+      </c>
+      <c r="G72" s="29" t="s">
+        <v>326</v>
       </c>
       <c r="H72" s="21" t="b">
-        <f>A72=C72</f>
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A73" s="36">
+      <c r="A73" s="33">
         <v>17</v>
       </c>
-      <c r="B73" s="37" t="s">
-        <v>83</v>
-      </c>
-      <c r="C73" s="38">
+      <c r="B73" s="34" t="s">
+        <v>325</v>
+      </c>
+      <c r="C73" s="35">
         <v>17</v>
       </c>
-      <c r="D73" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="E73" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F73" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="G73" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F73),0)&gt;0), MAX($G$1:G72)+1, ""))</f>
-        <v/>
+      <c r="D73" s="33">
+        <v>1.9</v>
+      </c>
+      <c r="E73" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="F73" s="33" t="s">
+        <v>329</v>
+      </c>
+      <c r="G73" s="29" t="s">
+        <v>326</v>
       </c>
       <c r="H73" s="21" t="b">
-        <f>A73=C73</f>
         <v>1</v>
       </c>
     </row>
@@ -3719,26 +3736,24 @@
         <v>17</v>
       </c>
       <c r="B74" s="34" t="s">
-        <v>31</v>
+        <v>328</v>
       </c>
       <c r="C74" s="35">
         <v>17</v>
       </c>
-      <c r="D74" s="33" t="s">
-        <v>208</v>
+      <c r="D74" s="33">
+        <v>1.9</v>
       </c>
       <c r="E74" s="34" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F74" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="G74" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F74),0)&gt;0), MAX($G$1:G73)+1, ""))</f>
-        <v/>
+        <v>329</v>
+      </c>
+      <c r="G74" s="29" t="s">
+        <v>326</v>
       </c>
       <c r="H74" s="21" t="b">
-        <f>A74=C74</f>
         <v>1</v>
       </c>
     </row>
@@ -3747,48 +3762,50 @@
         <v>17</v>
       </c>
       <c r="B75" s="34" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C75" s="35">
         <v>17</v>
       </c>
       <c r="D75" s="33" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="E75" s="34" t="s">
         <v>8</v>
       </c>
       <c r="F75" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="G75" s="29" t="s">
-        <v>326</v>
+        <v>37</v>
+      </c>
+      <c r="G75" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F75),0)&gt;0), MAX($G$1:G74)+1, ""))</f>
+        <v/>
       </c>
       <c r="H75" s="21" t="b">
+        <f>A75=C75</f>
         <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A76" s="30">
-        <v>20</v>
-      </c>
-      <c r="B76" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="C76" s="32">
-        <v>20</v>
-      </c>
-      <c r="D76" s="30" t="s">
-        <v>206</v>
-      </c>
-      <c r="E76" s="31" t="s">
+      <c r="A76" s="36">
+        <v>17</v>
+      </c>
+      <c r="B76" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="C76" s="38">
+        <v>17</v>
+      </c>
+      <c r="D76" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E76" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F76" s="30" t="s">
-        <v>147</v>
+      <c r="F76" s="36" t="s">
+        <v>84</v>
       </c>
       <c r="G76" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F76),0)&gt;0), MAX($G$1:G72)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F76),0)&gt;0), MAX($G$1:G75)+1, ""))</f>
         <v/>
       </c>
       <c r="H76" s="21" t="b">
@@ -3797,23 +3814,23 @@
       </c>
     </row>
     <row r="77" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A77" s="30">
-        <v>20</v>
-      </c>
-      <c r="B77" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="C77" s="32">
-        <v>20</v>
-      </c>
-      <c r="D77" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="E77" s="31" t="s">
+      <c r="A77" s="33">
+        <v>17</v>
+      </c>
+      <c r="B77" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="35">
+        <v>17</v>
+      </c>
+      <c r="D77" s="33" t="s">
+        <v>208</v>
+      </c>
+      <c r="E77" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F77" s="30" t="s">
-        <v>145</v>
+      <c r="F77" s="33" t="s">
+        <v>32</v>
       </c>
       <c r="G77" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F77),0)&gt;0), MAX($G$1:G76)+1, ""))</f>
@@ -3825,30 +3842,28 @@
       </c>
     </row>
     <row r="78" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A78" s="30">
-        <v>20</v>
-      </c>
-      <c r="B78" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="C78" s="32">
-        <v>20</v>
-      </c>
-      <c r="D78" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="E78" s="31" t="s">
+      <c r="A78" s="33">
+        <v>17</v>
+      </c>
+      <c r="B78" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="C78" s="35">
+        <v>17</v>
+      </c>
+      <c r="D78" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="E78" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F78" s="30" t="s">
-        <v>143</v>
-      </c>
-      <c r="G78" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F78),0)&gt;0), MAX($G$1:G76)+1, ""))</f>
-        <v/>
+      <c r="F78" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="G78" s="29" t="s">
+        <v>326</v>
       </c>
       <c r="H78" s="21" t="b">
-        <f>A78=C78</f>
         <v>1</v>
       </c>
     </row>
@@ -3857,22 +3872,22 @@
         <v>20</v>
       </c>
       <c r="B79" s="31" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="C79" s="32">
         <v>20</v>
       </c>
       <c r="D79" s="30" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="E79" s="31" t="s">
-        <v>305</v>
+        <v>8</v>
       </c>
       <c r="F79" s="30" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G79" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F79),0)&gt;0), MAX($G$1:G78)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F79),0)&gt;0), MAX($G$1:G75)+1, ""))</f>
         <v/>
       </c>
       <c r="H79" s="21" t="b">
@@ -3881,50 +3896,56 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A80" s="36">
+      <c r="A80" s="30">
         <v>20</v>
       </c>
-      <c r="B80" s="37" t="s">
-        <v>333</v>
-      </c>
-      <c r="C80" s="38">
+      <c r="B80" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="C80" s="32">
         <v>20</v>
       </c>
-      <c r="D80" s="36">
-        <v>3.4</v>
-      </c>
-      <c r="E80" s="37" t="s">
-        <v>336</v>
-      </c>
-      <c r="F80" s="36" t="s">
-        <v>334</v>
-      </c>
-      <c r="G80" s="29"/>
+      <c r="D80" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="E80" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F80" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="G80" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F80),0)&gt;0), MAX($G$1:G79)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H80" s="21" t="b">
         <f>A80=C80</f>
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A81" s="36">
+      <c r="A81" s="30">
         <v>20</v>
       </c>
-      <c r="B81" s="37" t="s">
-        <v>331</v>
-      </c>
-      <c r="C81" s="38">
+      <c r="B81" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="C81" s="32">
         <v>20</v>
       </c>
-      <c r="D81" s="36">
-        <v>3.3</v>
-      </c>
-      <c r="E81" s="37" t="s">
-        <v>336</v>
-      </c>
-      <c r="F81" s="36" t="s">
-        <v>332</v>
-      </c>
-      <c r="G81" s="29"/>
+      <c r="D81" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="E81" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F81" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="G81" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F81),0)&gt;0), MAX($G$1:G79)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H81" s="21" t="b">
         <f>A81=C81</f>
         <v>1</v>
@@ -3935,19 +3956,19 @@
         <v>20</v>
       </c>
       <c r="B82" s="31" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C82" s="32">
         <v>20</v>
       </c>
       <c r="D82" s="30" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="E82" s="31" t="s">
-        <v>8</v>
+        <v>305</v>
       </c>
       <c r="F82" s="30" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G82" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F82),0)&gt;0), MAX($G$1:G81)+1, ""))</f>
@@ -3959,56 +3980,50 @@
       </c>
     </row>
     <row r="83" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A83" s="30">
+      <c r="A83" s="36">
         <v>20</v>
       </c>
-      <c r="B83" s="31" t="s">
-        <v>255</v>
-      </c>
-      <c r="C83" s="32">
+      <c r="B83" s="37" t="s">
+        <v>333</v>
+      </c>
+      <c r="C83" s="38">
         <v>20</v>
       </c>
-      <c r="D83" s="30" t="s">
-        <v>225</v>
-      </c>
-      <c r="E83" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F83" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="G83" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F83),0)&gt;0), MAX($G$1:G82)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D83" s="36">
+        <v>3.4</v>
+      </c>
+      <c r="E83" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="F83" s="36" t="s">
+        <v>334</v>
+      </c>
+      <c r="G83" s="29"/>
       <c r="H83" s="21" t="b">
         <f>A83=C83</f>
         <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A84" s="30">
+      <c r="A84" s="36">
         <v>20</v>
       </c>
-      <c r="B84" s="31" t="s">
-        <v>254</v>
-      </c>
-      <c r="C84" s="32">
+      <c r="B84" s="37" t="s">
+        <v>331</v>
+      </c>
+      <c r="C84" s="38">
         <v>20</v>
       </c>
-      <c r="D84" s="30">
-        <v>4.2</v>
-      </c>
-      <c r="E84" s="31" t="s">
-        <v>305</v>
-      </c>
-      <c r="F84" s="30">
-        <v>21765430</v>
-      </c>
-      <c r="G84" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F84),0)&gt;0), MAX($G$1:G83)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D84" s="36">
+        <v>3.3</v>
+      </c>
+      <c r="E84" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="F84" s="36" t="s">
+        <v>332</v>
+      </c>
+      <c r="G84" s="29"/>
       <c r="H84" s="21" t="b">
         <f>A84=C84</f>
         <v>1</v>
@@ -4019,19 +4034,19 @@
         <v>20</v>
       </c>
       <c r="B85" s="31" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C85" s="32">
         <v>20</v>
       </c>
       <c r="D85" s="30" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="E85" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F85" s="30" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G85" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F85),0)&gt;0), MAX($G$1:G84)+1, ""))</f>
@@ -4047,19 +4062,19 @@
         <v>20</v>
       </c>
       <c r="B86" s="31" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C86" s="32">
         <v>20</v>
       </c>
       <c r="D86" s="30" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E86" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F86" s="30" t="s">
-        <v>135</v>
+        <v>256</v>
       </c>
       <c r="G86" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F86),0)&gt;0), MAX($G$1:G85)+1, ""))</f>
@@ -4075,19 +4090,19 @@
         <v>20</v>
       </c>
       <c r="B87" s="31" t="s">
-        <v>133</v>
+        <v>254</v>
       </c>
       <c r="C87" s="32">
         <v>20</v>
       </c>
-      <c r="D87" s="30" t="s">
-        <v>219</v>
+      <c r="D87" s="30">
+        <v>4.2</v>
       </c>
       <c r="E87" s="31" t="s">
         <v>305</v>
       </c>
-      <c r="F87" s="30" t="s">
-        <v>134</v>
+      <c r="F87" s="30">
+        <v>21765430</v>
       </c>
       <c r="G87" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F87),0)&gt;0), MAX($G$1:G86)+1, ""))</f>
@@ -4103,19 +4118,19 @@
         <v>20</v>
       </c>
       <c r="B88" s="31" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C88" s="32">
         <v>20</v>
       </c>
       <c r="D88" s="30" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E88" s="31" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="F88" s="30" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G88" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F88),0)&gt;0), MAX($G$1:G87)+1, ""))</f>
@@ -4127,23 +4142,23 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A89" s="26">
+      <c r="A89" s="30">
         <v>20</v>
       </c>
-      <c r="B89" s="27" t="s">
-        <v>312</v>
-      </c>
-      <c r="C89" s="28">
+      <c r="B89" s="31" t="s">
+        <v>265</v>
+      </c>
+      <c r="C89" s="32">
         <v>20</v>
       </c>
-      <c r="D89" s="26">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="E89" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="F89" s="26" t="s">
-        <v>318</v>
+      <c r="D89" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="E89" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F89" s="30" t="s">
+        <v>135</v>
       </c>
       <c r="G89" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F89),0)&gt;0), MAX($G$1:G88)+1, ""))</f>
@@ -4159,19 +4174,19 @@
         <v>20</v>
       </c>
       <c r="B90" s="31" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C90" s="32">
         <v>20</v>
       </c>
       <c r="D90" s="30" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E90" s="31" t="s">
-        <v>8</v>
+        <v>305</v>
       </c>
       <c r="F90" s="30" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="G90" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F90),0)&gt;0), MAX($G$1:G89)+1, ""))</f>
@@ -4187,19 +4202,19 @@
         <v>20</v>
       </c>
       <c r="B91" s="31" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C91" s="32">
         <v>20</v>
       </c>
       <c r="D91" s="30" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="E91" s="31" t="s">
-        <v>305</v>
+        <v>131</v>
       </c>
       <c r="F91" s="30" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="G91" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F91),0)&gt;0), MAX($G$1:G90)+1, ""))</f>
@@ -4215,19 +4230,19 @@
         <v>20</v>
       </c>
       <c r="B92" s="27" t="s">
-        <v>375</v>
+        <v>312</v>
       </c>
       <c r="C92" s="28">
         <v>20</v>
       </c>
       <c r="D92" s="26">
-        <v>2.7</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E92" s="27" t="s">
-        <v>245</v>
+        <v>60</v>
       </c>
       <c r="F92" s="26" t="s">
-        <v>351</v>
+        <v>318</v>
       </c>
       <c r="G92" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F92),0)&gt;0), MAX($G$1:G91)+1, ""))</f>
@@ -4243,19 +4258,19 @@
         <v>20</v>
       </c>
       <c r="B93" s="31" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C93" s="32">
         <v>20</v>
       </c>
       <c r="D93" s="30" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="E93" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F93" s="30" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G93" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F93),0)&gt;0), MAX($G$1:G92)+1, ""))</f>
@@ -4271,19 +4286,19 @@
         <v>20</v>
       </c>
       <c r="B94" s="31" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C94" s="32">
         <v>20</v>
       </c>
       <c r="D94" s="30" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="E94" s="31" t="s">
-        <v>8</v>
+        <v>305</v>
       </c>
       <c r="F94" s="30" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G94" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F94),0)&gt;0), MAX($G$1:G93)+1, ""))</f>
@@ -4295,23 +4310,23 @@
       </c>
     </row>
     <row r="95" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A95" s="30">
+      <c r="A95" s="26">
         <v>20</v>
       </c>
-      <c r="B95" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="C95" s="32">
+      <c r="B95" s="27" t="s">
+        <v>375</v>
+      </c>
+      <c r="C95" s="28">
         <v>20</v>
       </c>
-      <c r="D95" s="30" t="s">
-        <v>223</v>
-      </c>
-      <c r="E95" s="31" t="s">
-        <v>305</v>
-      </c>
-      <c r="F95" s="30" t="s">
-        <v>121</v>
+      <c r="D95" s="26">
+        <v>2.7</v>
+      </c>
+      <c r="E95" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="F95" s="26" t="s">
+        <v>351</v>
       </c>
       <c r="G95" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F95),0)&gt;0), MAX($G$1:G94)+1, ""))</f>
@@ -4323,23 +4338,23 @@
       </c>
     </row>
     <row r="96" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A96" s="26">
+      <c r="A96" s="30">
         <v>20</v>
       </c>
-      <c r="B96" s="27" t="s">
-        <v>369</v>
-      </c>
-      <c r="C96" s="28">
+      <c r="B96" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="C96" s="32">
         <v>20</v>
       </c>
-      <c r="D96" s="26">
-        <v>1.5</v>
+      <c r="D96" s="30" t="s">
+        <v>230</v>
       </c>
       <c r="E96" s="31" t="s">
-        <v>299</v>
-      </c>
-      <c r="F96" s="26" t="s">
-        <v>370</v>
+        <v>8</v>
+      </c>
+      <c r="F96" s="30" t="s">
+        <v>125</v>
       </c>
       <c r="G96" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F96),0)&gt;0), MAX($G$1:G95)+1, ""))</f>
@@ -4355,19 +4370,19 @@
         <v>20</v>
       </c>
       <c r="B97" s="31" t="s">
-        <v>257</v>
+        <v>122</v>
       </c>
       <c r="C97" s="32">
         <v>20</v>
       </c>
       <c r="D97" s="30" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="E97" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F97" s="30" t="s">
-        <v>258</v>
+        <v>123</v>
       </c>
       <c r="G97" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F97),0)&gt;0), MAX($G$1:G96)+1, ""))</f>
@@ -4383,19 +4398,19 @@
         <v>20</v>
       </c>
       <c r="B98" s="31" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C98" s="32">
         <v>20</v>
       </c>
       <c r="D98" s="30" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E98" s="31" t="s">
-        <v>8</v>
+        <v>305</v>
       </c>
       <c r="F98" s="30" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G98" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F98),0)&gt;0), MAX($G$1:G97)+1, ""))</f>
@@ -4407,23 +4422,23 @@
       </c>
     </row>
     <row r="99" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A99" s="30">
+      <c r="A99" s="26">
         <v>20</v>
       </c>
-      <c r="B99" s="31" t="s">
-        <v>116</v>
-      </c>
-      <c r="C99" s="32">
+      <c r="B99" s="27" t="s">
+        <v>369</v>
+      </c>
+      <c r="C99" s="28">
         <v>20</v>
       </c>
-      <c r="D99" s="30" t="s">
-        <v>208</v>
+      <c r="D99" s="26">
+        <v>1.5</v>
       </c>
       <c r="E99" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F99" s="30" t="s">
-        <v>117</v>
+        <v>299</v>
+      </c>
+      <c r="F99" s="26" t="s">
+        <v>370</v>
       </c>
       <c r="G99" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F99),0)&gt;0), MAX($G$1:G98)+1, ""))</f>
@@ -4439,19 +4454,19 @@
         <v>20</v>
       </c>
       <c r="B100" s="31" t="s">
-        <v>114</v>
+        <v>257</v>
       </c>
       <c r="C100" s="32">
         <v>20</v>
       </c>
       <c r="D100" s="30" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="E100" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F100" s="30" t="s">
-        <v>115</v>
+        <v>258</v>
       </c>
       <c r="G100" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F100),0)&gt;0), MAX($G$1:G99)+1, ""))</f>
@@ -4463,23 +4478,23 @@
       </c>
     </row>
     <row r="101" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A101" s="26">
+      <c r="A101" s="30">
         <v>20</v>
       </c>
-      <c r="B101" s="27" t="s">
-        <v>297</v>
-      </c>
-      <c r="C101" s="28">
+      <c r="B101" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C101" s="32">
         <v>20</v>
       </c>
-      <c r="D101" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E101" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="F101" s="26" t="s">
-        <v>298</v>
+      <c r="D101" s="30" t="s">
+        <v>227</v>
+      </c>
+      <c r="E101" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="30" t="s">
+        <v>119</v>
       </c>
       <c r="G101" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F101),0)&gt;0), MAX($G$1:G100)+1, ""))</f>
@@ -4495,19 +4510,19 @@
         <v>20</v>
       </c>
       <c r="B102" s="31" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C102" s="32">
         <v>20</v>
       </c>
       <c r="D102" s="30" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="E102" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F102" s="30" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G102" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F102),0)&gt;0), MAX($G$1:G101)+1, ""))</f>
@@ -4523,19 +4538,19 @@
         <v>20</v>
       </c>
       <c r="B103" s="31" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C103" s="32">
         <v>20</v>
       </c>
       <c r="D103" s="30" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="E103" s="31" t="s">
-        <v>299</v>
+        <v>8</v>
       </c>
       <c r="F103" s="30" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G103" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F103),0)&gt;0), MAX($G$1:G102)+1, ""))</f>
@@ -4547,23 +4562,23 @@
       </c>
     </row>
     <row r="104" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A104" s="30">
+      <c r="A104" s="26">
         <v>20</v>
       </c>
-      <c r="B104" s="31" t="s">
-        <v>108</v>
-      </c>
-      <c r="C104" s="32">
+      <c r="B104" s="27" t="s">
+        <v>297</v>
+      </c>
+      <c r="C104" s="28">
         <v>20</v>
       </c>
-      <c r="D104" s="30" t="s">
-        <v>218</v>
-      </c>
-      <c r="E104" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F104" s="30" t="s">
-        <v>109</v>
+      <c r="D104" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E104" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="F104" s="26" t="s">
+        <v>298</v>
       </c>
       <c r="G104" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F104),0)&gt;0), MAX($G$1:G103)+1, ""))</f>
@@ -4575,48 +4590,51 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A105" s="36">
+      <c r="A105" s="30">
         <v>20</v>
       </c>
-      <c r="B105" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="C105" s="38">
+      <c r="B105" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="C105" s="32">
         <v>20</v>
       </c>
-      <c r="D105" s="36">
-        <v>3</v>
-      </c>
-      <c r="E105" s="37" t="s">
-        <v>304</v>
-      </c>
-      <c r="F105" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="G105" s="29"/>
+      <c r="D105" s="30" t="s">
+        <v>219</v>
+      </c>
+      <c r="E105" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F105" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="G105" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F105),0)&gt;0), MAX($G$1:G104)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H105" s="21" t="b">
         <f>A105=C105</f>
         <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A106" s="26">
+      <c r="A106" s="30">
         <v>20</v>
       </c>
-      <c r="B106" s="27" t="s">
-        <v>302</v>
-      </c>
-      <c r="C106" s="28">
+      <c r="B106" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="C106" s="32">
         <v>20</v>
       </c>
-      <c r="D106" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E106" s="27" t="s">
+      <c r="D106" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="E106" s="31" t="s">
         <v>299</v>
       </c>
-      <c r="F106" s="26" t="s">
-        <v>301</v>
+      <c r="F106" s="30" t="s">
+        <v>111</v>
       </c>
       <c r="G106" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F106),0)&gt;0), MAX($G$1:G105)+1, ""))</f>
@@ -4632,19 +4650,19 @@
         <v>20</v>
       </c>
       <c r="B107" s="31" t="s">
-        <v>366</v>
+        <v>108</v>
       </c>
       <c r="C107" s="32">
         <v>20</v>
       </c>
-      <c r="D107" s="30">
-        <v>2.4</v>
+      <c r="D107" s="30" t="s">
+        <v>218</v>
       </c>
       <c r="E107" s="31" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="F107" s="30" t="s">
-        <v>367</v>
+        <v>109</v>
       </c>
       <c r="G107" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F107),0)&gt;0), MAX($G$1:G106)+1, ""))</f>
@@ -4656,28 +4674,25 @@
       </c>
     </row>
     <row r="108" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A108" s="30">
+      <c r="A108" s="36">
         <v>20</v>
       </c>
-      <c r="B108" s="31" t="s">
-        <v>103</v>
-      </c>
-      <c r="C108" s="32">
+      <c r="B108" s="37" t="s">
+        <v>330</v>
+      </c>
+      <c r="C108" s="38">
         <v>20</v>
       </c>
-      <c r="D108" s="30" t="s">
-        <v>214</v>
-      </c>
-      <c r="E108" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="F108" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="G108" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F108),0)&gt;0), MAX($G$1:G107)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D108" s="36">
+        <v>3</v>
+      </c>
+      <c r="E108" s="37" t="s">
+        <v>304</v>
+      </c>
+      <c r="F108" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="G108" s="29"/>
       <c r="H108" s="21" t="b">
         <f>A108=C108</f>
         <v>1</v>
@@ -4688,19 +4703,19 @@
         <v>20</v>
       </c>
       <c r="B109" s="27" t="s">
-        <v>339</v>
+        <v>302</v>
       </c>
       <c r="C109" s="28">
         <v>20</v>
       </c>
       <c r="D109" s="26">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="E109" s="27" t="s">
-        <v>81</v>
+        <v>299</v>
       </c>
       <c r="F109" s="26" t="s">
-        <v>344</v>
+        <v>301</v>
       </c>
       <c r="G109" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F109),0)&gt;0), MAX($G$1:G108)+1, ""))</f>
@@ -4712,25 +4727,28 @@
       </c>
     </row>
     <row r="110" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A110" s="36">
+      <c r="A110" s="30">
         <v>20</v>
       </c>
-      <c r="B110" s="37" t="s">
-        <v>335</v>
-      </c>
-      <c r="C110" s="38">
+      <c r="B110" s="31" t="s">
+        <v>366</v>
+      </c>
+      <c r="C110" s="32">
         <v>20</v>
       </c>
-      <c r="D110" s="36">
-        <v>3.2</v>
-      </c>
-      <c r="E110" s="37" t="s">
-        <v>336</v>
-      </c>
-      <c r="F110" s="36" t="s">
-        <v>332</v>
-      </c>
-      <c r="G110" s="29"/>
+      <c r="D110" s="30">
+        <v>2.4</v>
+      </c>
+      <c r="E110" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="F110" s="30" t="s">
+        <v>367</v>
+      </c>
+      <c r="G110" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F110),0)&gt;0), MAX($G$1:G109)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H110" s="21" t="b">
         <f>A110=C110</f>
         <v>1</v>
@@ -4741,19 +4759,19 @@
         <v>20</v>
       </c>
       <c r="B111" s="31" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C111" s="32">
         <v>20</v>
       </c>
       <c r="D111" s="30" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="E111" s="31" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F111" s="30" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G111" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F111),0)&gt;0), MAX($G$1:G110)+1, ""))</f>
@@ -4765,23 +4783,23 @@
       </c>
     </row>
     <row r="112" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A112" s="30">
+      <c r="A112" s="26">
         <v>20</v>
       </c>
-      <c r="B112" s="31" t="s">
-        <v>263</v>
-      </c>
-      <c r="C112" s="32">
+      <c r="B112" s="27" t="s">
+        <v>339</v>
+      </c>
+      <c r="C112" s="28">
         <v>20</v>
       </c>
-      <c r="D112" s="30">
-        <v>6.2</v>
-      </c>
-      <c r="E112" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F112" s="30" t="s">
-        <v>264</v>
+      <c r="D112" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E112" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F112" s="26" t="s">
+        <v>344</v>
       </c>
       <c r="G112" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F112),0)&gt;0), MAX($G$1:G111)+1, ""))</f>
@@ -4793,51 +4811,48 @@
       </c>
     </row>
     <row r="113" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A113" s="30">
+      <c r="A113" s="36">
         <v>20</v>
       </c>
-      <c r="B113" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="C113" s="32">
+      <c r="B113" s="37" t="s">
+        <v>335</v>
+      </c>
+      <c r="C113" s="38">
         <v>20</v>
       </c>
-      <c r="D113" s="30" t="s">
-        <v>215</v>
-      </c>
-      <c r="E113" s="31" t="s">
-        <v>299</v>
-      </c>
-      <c r="F113" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="G113" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F113),0)&gt;0), MAX($G$1:G112)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D113" s="36">
+        <v>3.2</v>
+      </c>
+      <c r="E113" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="F113" s="36" t="s">
+        <v>332</v>
+      </c>
+      <c r="G113" s="29"/>
       <c r="H113" s="21" t="b">
         <f>A113=C113</f>
         <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A114" s="26">
+      <c r="A114" s="30">
         <v>20</v>
       </c>
-      <c r="B114" s="27" t="s">
-        <v>300</v>
-      </c>
-      <c r="C114" s="28">
+      <c r="B114" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="C114" s="32">
         <v>20</v>
       </c>
-      <c r="D114" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E114" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="F114" s="26" t="s">
-        <v>301</v>
+      <c r="D114" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E114" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F114" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G114" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F114),0)&gt;0), MAX($G$1:G113)+1, ""))</f>
@@ -4853,19 +4868,19 @@
         <v>20</v>
       </c>
       <c r="B115" s="31" t="s">
-        <v>95</v>
+        <v>263</v>
       </c>
       <c r="C115" s="32">
         <v>20</v>
       </c>
-      <c r="D115" s="30" t="s">
-        <v>216</v>
+      <c r="D115" s="30">
+        <v>6.2</v>
       </c>
       <c r="E115" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F115" s="30" t="s">
-        <v>96</v>
+        <v>264</v>
       </c>
       <c r="G115" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F115),0)&gt;0), MAX($G$1:G114)+1, ""))</f>
@@ -4877,23 +4892,23 @@
       </c>
     </row>
     <row r="116" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A116" s="26">
+      <c r="A116" s="30">
         <v>20</v>
       </c>
-      <c r="B116" s="27" t="s">
-        <v>355</v>
-      </c>
-      <c r="C116" s="28">
+      <c r="B116" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="C116" s="32">
         <v>20</v>
       </c>
-      <c r="D116" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E116" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F116" s="26" t="s">
-        <v>356</v>
+      <c r="D116" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="E116" s="31" t="s">
+        <v>299</v>
+      </c>
+      <c r="F116" s="30" t="s">
+        <v>100</v>
       </c>
       <c r="G116" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F116),0)&gt;0), MAX($G$1:G115)+1, ""))</f>
@@ -4905,23 +4920,23 @@
       </c>
     </row>
     <row r="117" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A117" s="30">
+      <c r="A117" s="26">
         <v>20</v>
       </c>
-      <c r="B117" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="C117" s="32">
+      <c r="B117" s="27" t="s">
+        <v>300</v>
+      </c>
+      <c r="C117" s="28">
         <v>20</v>
       </c>
-      <c r="D117" s="30" t="s">
-        <v>218</v>
-      </c>
-      <c r="E117" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F117" s="30" t="s">
-        <v>92</v>
+      <c r="D117" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E117" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="F117" s="26" t="s">
+        <v>301</v>
       </c>
       <c r="G117" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F117),0)&gt;0), MAX($G$1:G116)+1, ""))</f>
@@ -4937,19 +4952,19 @@
         <v>20</v>
       </c>
       <c r="B118" s="31" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C118" s="32">
         <v>20</v>
       </c>
       <c r="D118" s="30" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="E118" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F118" s="30" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G118" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F118),0)&gt;0), MAX($G$1:G117)+1, ""))</f>
@@ -4961,23 +4976,23 @@
       </c>
     </row>
     <row r="119" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A119" s="30">
+      <c r="A119" s="26">
         <v>20</v>
       </c>
-      <c r="B119" s="31" t="s">
-        <v>290</v>
-      </c>
-      <c r="C119" s="32">
+      <c r="B119" s="27" t="s">
+        <v>355</v>
+      </c>
+      <c r="C119" s="28">
         <v>20</v>
       </c>
-      <c r="D119" s="30">
-        <v>1.8</v>
-      </c>
-      <c r="E119" s="31" t="s">
-        <v>291</v>
-      </c>
-      <c r="F119" s="30" t="s">
-        <v>90</v>
+      <c r="D119" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E119" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F119" s="26" t="s">
+        <v>356</v>
       </c>
       <c r="G119" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F119),0)&gt;0), MAX($G$1:G118)+1, ""))</f>
@@ -4993,19 +5008,19 @@
         <v>20</v>
       </c>
       <c r="B120" s="31" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C120" s="32">
         <v>20</v>
       </c>
       <c r="D120" s="30" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E120" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F120" s="30" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G120" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F120),0)&gt;0), MAX($G$1:G119)+1, ""))</f>
@@ -5021,19 +5036,19 @@
         <v>20</v>
       </c>
       <c r="B121" s="31" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C121" s="32">
         <v>20</v>
       </c>
       <c r="D121" s="30" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E121" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F121" s="30" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G121" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F121),0)&gt;0), MAX($G$1:G120)+1, ""))</f>
@@ -5049,19 +5064,19 @@
         <v>20</v>
       </c>
       <c r="B122" s="31" t="s">
-        <v>80</v>
+        <v>290</v>
       </c>
       <c r="C122" s="32">
         <v>20</v>
       </c>
-      <c r="D122" s="30" t="s">
-        <v>218</v>
+      <c r="D122" s="30">
+        <v>1.8</v>
       </c>
       <c r="E122" s="31" t="s">
-        <v>81</v>
+        <v>291</v>
       </c>
       <c r="F122" s="30" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G122" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F122),0)&gt;0), MAX($G$1:G121)+1, ""))</f>
@@ -5077,19 +5092,19 @@
         <v>20</v>
       </c>
       <c r="B123" s="31" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C123" s="32">
         <v>20</v>
       </c>
       <c r="D123" s="30" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E123" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F123" s="30" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G123" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F123),0)&gt;0), MAX($G$1:G122)+1, ""))</f>
@@ -5105,19 +5120,19 @@
         <v>20</v>
       </c>
       <c r="B124" s="31" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C124" s="32">
         <v>20</v>
       </c>
       <c r="D124" s="30" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="E124" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F124" s="30" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G124" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F124),0)&gt;0), MAX($G$1:G123)+1, ""))</f>
@@ -5129,23 +5144,23 @@
       </c>
     </row>
     <row r="125" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A125" s="26">
-        <v>25</v>
-      </c>
-      <c r="B125" s="27" t="s">
-        <v>178</v>
-      </c>
-      <c r="C125" s="28">
-        <v>25</v>
-      </c>
-      <c r="D125" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="E125" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F125" s="26" t="s">
-        <v>179</v>
+      <c r="A125" s="30">
+        <v>20</v>
+      </c>
+      <c r="B125" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="C125" s="32">
+        <v>20</v>
+      </c>
+      <c r="D125" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="E125" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="F125" s="30" t="s">
+        <v>82</v>
       </c>
       <c r="G125" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F125),0)&gt;0), MAX($G$1:G124)+1, ""))</f>
@@ -5157,23 +5172,23 @@
       </c>
     </row>
     <row r="126" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A126" s="26">
-        <v>25</v>
-      </c>
-      <c r="B126" s="27" t="s">
-        <v>176</v>
-      </c>
-      <c r="C126" s="28">
-        <v>25</v>
-      </c>
-      <c r="D126" s="26" t="s">
-        <v>237</v>
-      </c>
-      <c r="E126" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="F126" s="26" t="s">
-        <v>177</v>
+      <c r="A126" s="30">
+        <v>20</v>
+      </c>
+      <c r="B126" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="C126" s="32">
+        <v>20</v>
+      </c>
+      <c r="D126" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="E126" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F126" s="30" t="s">
+        <v>79</v>
       </c>
       <c r="G126" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F126),0)&gt;0), MAX($G$1:G125)+1, ""))</f>
@@ -5185,23 +5200,23 @@
       </c>
     </row>
     <row r="127" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A127" s="26">
-        <v>25</v>
-      </c>
-      <c r="B127" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="C127" s="28">
-        <v>25</v>
-      </c>
-      <c r="D127" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="E127" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="F127" s="26" t="s">
-        <v>175</v>
+      <c r="A127" s="30">
+        <v>20</v>
+      </c>
+      <c r="B127" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="C127" s="32">
+        <v>20</v>
+      </c>
+      <c r="D127" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="E127" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F127" s="30" t="s">
+        <v>77</v>
       </c>
       <c r="G127" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F127),0)&gt;0), MAX($G$1:G126)+1, ""))</f>
@@ -5217,19 +5232,19 @@
         <v>25</v>
       </c>
       <c r="B128" s="27" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C128" s="28">
         <v>25</v>
       </c>
       <c r="D128" s="26" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E128" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F128" s="26" t="s">
-        <v>324</v>
+        <v>179</v>
       </c>
       <c r="G128" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F128),0)&gt;0), MAX($G$1:G127)+1, ""))</f>
@@ -5245,19 +5260,19 @@
         <v>25</v>
       </c>
       <c r="B129" s="27" t="s">
-        <v>359</v>
+        <v>176</v>
       </c>
       <c r="C129" s="28">
         <v>25</v>
       </c>
-      <c r="D129" s="26">
-        <v>3</v>
+      <c r="D129" s="26" t="s">
+        <v>237</v>
       </c>
       <c r="E129" s="27" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F129" s="26" t="s">
-        <v>360</v>
+        <v>177</v>
       </c>
       <c r="G129" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F129),0)&gt;0), MAX($G$1:G128)+1, ""))</f>
@@ -5273,19 +5288,19 @@
         <v>25</v>
       </c>
       <c r="B130" s="27" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C130" s="28">
         <v>25</v>
       </c>
-      <c r="D130" s="26">
-        <v>2.7</v>
+      <c r="D130" s="26" t="s">
+        <v>231</v>
       </c>
       <c r="E130" s="27" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="F130" s="26" t="s">
-        <v>338</v>
+        <v>175</v>
       </c>
       <c r="G130" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F130),0)&gt;0), MAX($G$1:G129)+1, ""))</f>
@@ -5297,23 +5312,23 @@
       </c>
     </row>
     <row r="131" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A131" s="30">
+      <c r="A131" s="26">
         <v>25</v>
       </c>
-      <c r="B131" s="31" t="s">
-        <v>284</v>
-      </c>
-      <c r="C131" s="32">
+      <c r="B131" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="C131" s="28">
         <v>25</v>
       </c>
-      <c r="D131" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E131" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F131" s="30" t="s">
-        <v>102</v>
+      <c r="D131" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="E131" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F131" s="26" t="s">
+        <v>324</v>
       </c>
       <c r="G131" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F131),0)&gt;0), MAX($G$1:G130)+1, ""))</f>
@@ -5325,23 +5340,23 @@
       </c>
     </row>
     <row r="132" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A132" s="30">
+      <c r="A132" s="26">
         <v>25</v>
       </c>
-      <c r="B132" s="31" t="s">
-        <v>282</v>
-      </c>
-      <c r="C132" s="32">
+      <c r="B132" s="27" t="s">
+        <v>359</v>
+      </c>
+      <c r="C132" s="28">
         <v>25</v>
       </c>
-      <c r="D132" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E132" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F132" s="30" t="s">
-        <v>102</v>
+      <c r="D132" s="26">
+        <v>3</v>
+      </c>
+      <c r="E132" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F132" s="26" t="s">
+        <v>360</v>
       </c>
       <c r="G132" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B132),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E132),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F132),0)&gt;0), MAX($G$1:G131)+1, ""))</f>
@@ -5357,19 +5372,19 @@
         <v>25</v>
       </c>
       <c r="B133" s="27" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C133" s="28">
         <v>25</v>
       </c>
-      <c r="D133" s="26" t="s">
-        <v>234</v>
+      <c r="D133" s="26">
+        <v>2.7</v>
       </c>
       <c r="E133" s="27" t="s">
-        <v>245</v>
+        <v>81</v>
       </c>
       <c r="F133" s="26" t="s">
-        <v>171</v>
+        <v>338</v>
       </c>
       <c r="G133" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F133),0)&gt;0), MAX($G$1:G132)+1, ""))</f>
@@ -5381,23 +5396,23 @@
       </c>
     </row>
     <row r="134" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A134" s="26">
+      <c r="A134" s="30">
         <v>25</v>
       </c>
-      <c r="B134" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="C134" s="28">
+      <c r="B134" s="31" t="s">
+        <v>284</v>
+      </c>
+      <c r="C134" s="32">
         <v>25</v>
       </c>
-      <c r="D134" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="E134" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F134" s="26" t="s">
-        <v>169</v>
+      <c r="D134" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E134" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="F134" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G134" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F134),0)&gt;0), MAX($G$1:G133)+1, ""))</f>
@@ -5409,23 +5424,23 @@
       </c>
     </row>
     <row r="135" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A135" s="26">
+      <c r="A135" s="30">
         <v>25</v>
       </c>
-      <c r="B135" s="27" t="s">
-        <v>357</v>
-      </c>
-      <c r="C135" s="28">
+      <c r="B135" s="31" t="s">
+        <v>282</v>
+      </c>
+      <c r="C135" s="32">
         <v>25</v>
       </c>
-      <c r="D135" s="26">
-        <v>3.4</v>
-      </c>
-      <c r="E135" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F135" s="26" t="s">
-        <v>358</v>
+      <c r="D135" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E135" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="F135" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G135" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F135),0)&gt;0), MAX($G$1:G134)+1, ""))</f>
@@ -5437,23 +5452,23 @@
       </c>
     </row>
     <row r="136" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A136" s="30">
+      <c r="A136" s="26">
         <v>25</v>
       </c>
-      <c r="B136" s="31" t="s">
-        <v>278</v>
-      </c>
-      <c r="C136" s="32">
+      <c r="B136" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="C136" s="28">
         <v>25</v>
       </c>
-      <c r="D136" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E136" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F136" s="30" t="s">
-        <v>102</v>
+      <c r="D136" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="E136" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="F136" s="26" t="s">
+        <v>171</v>
       </c>
       <c r="G136" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F136),0)&gt;0), MAX($G$1:G135)+1, ""))</f>
@@ -5469,19 +5484,19 @@
         <v>25</v>
       </c>
       <c r="B137" s="27" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C137" s="28">
         <v>25</v>
       </c>
       <c r="D137" s="26" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E137" s="27" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="F137" s="26" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G137" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F137),0)&gt;0), MAX($G$1:G136)+1, ""))</f>
@@ -5497,19 +5512,19 @@
         <v>25</v>
       </c>
       <c r="B138" s="27" t="s">
-        <v>164</v>
+        <v>357</v>
       </c>
       <c r="C138" s="28">
         <v>25</v>
       </c>
-      <c r="D138" s="26" t="s">
-        <v>229</v>
+      <c r="D138" s="26">
+        <v>3.4</v>
       </c>
       <c r="E138" s="27" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="F138" s="26" t="s">
-        <v>165</v>
+        <v>358</v>
       </c>
       <c r="G138" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F138),0)&gt;0), MAX($G$1:G137)+1, ""))</f>
@@ -5521,23 +5536,23 @@
       </c>
     </row>
     <row r="139" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A139" s="26">
+      <c r="A139" s="30">
         <v>25</v>
       </c>
-      <c r="B139" s="27" t="s">
-        <v>162</v>
-      </c>
-      <c r="C139" s="28">
+      <c r="B139" s="31" t="s">
+        <v>278</v>
+      </c>
+      <c r="C139" s="32">
         <v>25</v>
       </c>
-      <c r="D139" s="26" t="s">
-        <v>232</v>
-      </c>
-      <c r="E139" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F139" s="26" t="s">
-        <v>163</v>
+      <c r="D139" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E139" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F139" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G139" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F139),0)&gt;0), MAX($G$1:G138)+1, ""))</f>
@@ -5553,19 +5568,19 @@
         <v>25</v>
       </c>
       <c r="B140" s="27" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C140" s="28">
         <v>25</v>
       </c>
       <c r="D140" s="26" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="E140" s="27" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="F140" s="26" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="G140" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F140),0)&gt;0), MAX($G$1:G139)+1, ""))</f>
@@ -5581,19 +5596,19 @@
         <v>25</v>
       </c>
       <c r="B141" s="27" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C141" s="28">
         <v>25</v>
       </c>
       <c r="D141" s="26" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E141" s="27" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="F141" s="26" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="G141" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F141),0)&gt;0), MAX($G$1:G140)+1, ""))</f>
@@ -5609,19 +5624,19 @@
         <v>25</v>
       </c>
       <c r="B142" s="27" t="s">
-        <v>342</v>
+        <v>162</v>
       </c>
       <c r="C142" s="28">
         <v>25</v>
       </c>
-      <c r="D142" s="26">
-        <v>3.4</v>
+      <c r="D142" s="26" t="s">
+        <v>232</v>
       </c>
       <c r="E142" s="27" t="s">
         <v>81</v>
       </c>
       <c r="F142" s="26" t="s">
-        <v>343</v>
+        <v>163</v>
       </c>
       <c r="G142" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F142),0)&gt;0), MAX($G$1:G141)+1, ""))</f>
@@ -5637,22 +5652,22 @@
         <v>25</v>
       </c>
       <c r="B143" s="27" t="s">
-        <v>310</v>
+        <v>160</v>
       </c>
       <c r="C143" s="28">
         <v>25</v>
       </c>
-      <c r="D143" s="26">
-        <v>3.9</v>
+      <c r="D143" s="26" t="s">
+        <v>236</v>
       </c>
       <c r="E143" s="27" t="s">
-        <v>309</v>
+        <v>81</v>
       </c>
       <c r="F143" s="26" t="s">
-        <v>311</v>
+        <v>161</v>
       </c>
       <c r="G143" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F143),0)&gt;0), MAX($G$1:G141)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F143),0)&gt;0), MAX($G$1:G142)+1, ""))</f>
         <v/>
       </c>
       <c r="H143" s="21" t="b">
@@ -5665,19 +5680,19 @@
         <v>25</v>
       </c>
       <c r="B144" s="27" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C144" s="28">
         <v>25</v>
       </c>
       <c r="D144" s="26" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E144" s="27" t="s">
         <v>81</v>
       </c>
       <c r="F144" s="26" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G144" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F144),0)&gt;0), MAX($G$1:G143)+1, ""))</f>
@@ -5693,19 +5708,19 @@
         <v>25</v>
       </c>
       <c r="B145" s="27" t="s">
-        <v>154</v>
+        <v>342</v>
       </c>
       <c r="C145" s="28">
         <v>25</v>
       </c>
-      <c r="D145" s="26" t="s">
-        <v>224</v>
+      <c r="D145" s="26">
+        <v>3.4</v>
       </c>
       <c r="E145" s="27" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="F145" s="26" t="s">
-        <v>155</v>
+        <v>343</v>
       </c>
       <c r="G145" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B145),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E145),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F145),0)&gt;0), MAX($G$1:G144)+1, ""))</f>
@@ -5721,22 +5736,22 @@
         <v>25</v>
       </c>
       <c r="B146" s="27" t="s">
-        <v>152</v>
+        <v>310</v>
       </c>
       <c r="C146" s="28">
         <v>25</v>
       </c>
-      <c r="D146" s="26" t="s">
-        <v>230</v>
+      <c r="D146" s="26">
+        <v>3.9</v>
       </c>
       <c r="E146" s="27" t="s">
-        <v>131</v>
+        <v>309</v>
       </c>
       <c r="F146" s="26" t="s">
-        <v>153</v>
+        <v>311</v>
       </c>
       <c r="G146" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F146),0)&gt;0), MAX($G$1:G145)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F146),0)&gt;0), MAX($G$1:G144)+1, ""))</f>
         <v/>
       </c>
       <c r="H146" s="21" t="b">
@@ -5749,19 +5764,19 @@
         <v>25</v>
       </c>
       <c r="B147" s="27" t="s">
-        <v>247</v>
+        <v>156</v>
       </c>
       <c r="C147" s="28">
         <v>25</v>
       </c>
-      <c r="D147" s="39" t="s">
-        <v>229</v>
+      <c r="D147" s="26" t="s">
+        <v>227</v>
       </c>
       <c r="E147" s="27" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="F147" s="26" t="s">
-        <v>248</v>
+        <v>157</v>
       </c>
       <c r="G147" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F147),0)&gt;0), MAX($G$1:G146)+1, ""))</f>
@@ -5777,19 +5792,19 @@
         <v>25</v>
       </c>
       <c r="B148" s="27" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C148" s="28">
         <v>25</v>
       </c>
       <c r="D148" s="26" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="E148" s="27" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="F148" s="26" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G148" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F148),0)&gt;0), MAX($G$1:G147)+1, ""))</f>
@@ -5801,23 +5816,23 @@
       </c>
     </row>
     <row r="149" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A149" s="30">
+      <c r="A149" s="26">
         <v>25</v>
       </c>
-      <c r="B149" s="31" t="s">
-        <v>288</v>
-      </c>
-      <c r="C149" s="32">
+      <c r="B149" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="C149" s="28">
         <v>25</v>
       </c>
-      <c r="D149" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E149" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F149" s="30" t="s">
-        <v>102</v>
+      <c r="D149" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="E149" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="F149" s="26" t="s">
+        <v>153</v>
       </c>
       <c r="G149" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B149),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E149),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F149),0)&gt;0), MAX($G$1:G148)+1, ""))</f>
@@ -5829,23 +5844,23 @@
       </c>
     </row>
     <row r="150" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A150" s="30">
+      <c r="A150" s="26">
         <v>25</v>
       </c>
-      <c r="B150" s="31" t="s">
-        <v>286</v>
-      </c>
-      <c r="C150" s="32">
+      <c r="B150" s="27" t="s">
+        <v>247</v>
+      </c>
+      <c r="C150" s="28">
         <v>25</v>
       </c>
-      <c r="D150" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E150" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F150" s="30" t="s">
-        <v>102</v>
+      <c r="D150" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="E150" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F150" s="26" t="s">
+        <v>248</v>
       </c>
       <c r="G150" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B150),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E150),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F150),0)&gt;0), MAX($G$1:G149)+1, ""))</f>
@@ -5857,23 +5872,23 @@
       </c>
     </row>
     <row r="151" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A151" s="30">
+      <c r="A151" s="26">
         <v>25</v>
       </c>
-      <c r="B151" s="31" t="s">
-        <v>287</v>
-      </c>
-      <c r="C151" s="32">
+      <c r="B151" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C151" s="28">
         <v>25</v>
       </c>
-      <c r="D151" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E151" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F151" s="30" t="s">
-        <v>102</v>
+      <c r="D151" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="E151" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="F151" s="26" t="s">
+        <v>151</v>
       </c>
       <c r="G151" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B151),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E151),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F151),0)&gt;0), MAX($G$1:G150)+1, ""))</f>
@@ -5885,23 +5900,23 @@
       </c>
     </row>
     <row r="152" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A152" s="26">
+      <c r="A152" s="30">
         <v>25</v>
       </c>
-      <c r="B152" s="27" t="s">
-        <v>252</v>
-      </c>
-      <c r="C152" s="28">
+      <c r="B152" s="31" t="s">
+        <v>288</v>
+      </c>
+      <c r="C152" s="32">
         <v>25</v>
       </c>
-      <c r="D152" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E152" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="F152" s="26" t="s">
-        <v>253</v>
+      <c r="D152" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E152" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="F152" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G152" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B152),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E152),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F152),0)&gt;0), MAX($G$1:G151)+1, ""))</f>
@@ -5917,7 +5932,7 @@
         <v>25</v>
       </c>
       <c r="B153" s="31" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C153" s="32">
         <v>25</v>
@@ -5941,26 +5956,26 @@
       </c>
     </row>
     <row r="154" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A154" s="26">
+      <c r="A154" s="30">
         <v>25</v>
       </c>
-      <c r="B154" s="27" t="s">
-        <v>148</v>
-      </c>
-      <c r="C154" s="28">
+      <c r="B154" s="31" t="s">
+        <v>287</v>
+      </c>
+      <c r="C154" s="32">
         <v>25</v>
       </c>
-      <c r="D154" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="E154" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F154" s="26" t="s">
-        <v>149</v>
+      <c r="D154" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E154" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="F154" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G154" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B154),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E154),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F154),0)&gt;0), MAX($G$1:G152)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B154),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E154),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F154),0)&gt;0), MAX($G$1:G153)+1, ""))</f>
         <v/>
       </c>
       <c r="H154" s="21" t="b">
@@ -5969,23 +5984,23 @@
       </c>
     </row>
     <row r="155" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A155" s="30">
-        <v>30</v>
-      </c>
-      <c r="B155" s="31" t="s">
-        <v>192</v>
-      </c>
-      <c r="C155" s="32">
-        <v>30</v>
-      </c>
-      <c r="D155" s="30" t="s">
-        <v>232</v>
-      </c>
-      <c r="E155" s="31" t="s">
+      <c r="A155" s="26">
+        <v>25</v>
+      </c>
+      <c r="B155" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="C155" s="28">
+        <v>25</v>
+      </c>
+      <c r="D155" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E155" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="F155" s="30" t="s">
-        <v>193</v>
+      <c r="F155" s="26" t="s">
+        <v>253</v>
       </c>
       <c r="G155" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F155),0)&gt;0), MAX($G$1:G154)+1, ""))</f>
@@ -5998,22 +6013,22 @@
     </row>
     <row r="156" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A156" s="30">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B156" s="31" t="s">
-        <v>191</v>
+        <v>285</v>
       </c>
       <c r="C156" s="32">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D156" s="30" t="s">
-        <v>241</v>
+        <v>207</v>
       </c>
       <c r="E156" s="31" t="s">
-        <v>131</v>
+        <v>283</v>
       </c>
       <c r="F156" s="30" t="s">
-        <v>190</v>
+        <v>102</v>
       </c>
       <c r="G156" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B156),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E156),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F156),0)&gt;0), MAX($G$1:G155)+1, ""))</f>
@@ -6025,26 +6040,26 @@
       </c>
     </row>
     <row r="157" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A157" s="30">
-        <v>30</v>
-      </c>
-      <c r="B157" s="31" t="s">
-        <v>189</v>
-      </c>
-      <c r="C157" s="32">
-        <v>30</v>
-      </c>
-      <c r="D157" s="30" t="s">
-        <v>240</v>
-      </c>
-      <c r="E157" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="F157" s="30" t="s">
-        <v>190</v>
+      <c r="A157" s="26">
+        <v>25</v>
+      </c>
+      <c r="B157" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="C157" s="28">
+        <v>25</v>
+      </c>
+      <c r="D157" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="E157" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F157" s="26" t="s">
+        <v>149</v>
       </c>
       <c r="G157" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F157),0)&gt;0), MAX($G$1:G156)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F157),0)&gt;0), MAX($G$1:G155)+1, ""))</f>
         <v/>
       </c>
       <c r="H157" s="21" t="b">
@@ -6057,19 +6072,19 @@
         <v>30</v>
       </c>
       <c r="B158" s="31" t="s">
-        <v>246</v>
+        <v>192</v>
       </c>
       <c r="C158" s="32">
         <v>30</v>
       </c>
       <c r="D158" s="30" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="E158" s="31" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F158" s="30" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="G158" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B158),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E158),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F158),0)&gt;0), MAX($G$1:G157)+1, ""))</f>
@@ -6085,19 +6100,19 @@
         <v>30</v>
       </c>
       <c r="B159" s="31" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C159" s="32">
         <v>30</v>
       </c>
       <c r="D159" s="30" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="E159" s="31" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F159" s="30" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G159" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F159),0)&gt;0), MAX($G$1:G158)+1, ""))</f>
@@ -6113,19 +6128,19 @@
         <v>30</v>
       </c>
       <c r="B160" s="31" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C160" s="32">
         <v>30</v>
       </c>
       <c r="D160" s="30" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="E160" s="31" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="F160" s="30" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="G160" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B160),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E160),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F160),0)&gt;0), MAX($G$1:G159)+1, ""))</f>
@@ -6137,23 +6152,23 @@
       </c>
     </row>
     <row r="161" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A161" s="26">
+      <c r="A161" s="30">
         <v>30</v>
       </c>
-      <c r="B161" s="27" t="s">
-        <v>377</v>
-      </c>
-      <c r="C161" s="28">
+      <c r="B161" s="31" t="s">
+        <v>246</v>
+      </c>
+      <c r="C161" s="32">
         <v>30</v>
       </c>
-      <c r="D161" s="26">
-        <v>5</v>
-      </c>
-      <c r="E161" s="27" t="s">
-        <v>378</v>
-      </c>
-      <c r="F161" s="26" t="s">
-        <v>25</v>
+      <c r="D161" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="E161" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F161" s="30" t="s">
+        <v>188</v>
       </c>
       <c r="G161" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B161),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E161),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F161),0)&gt;0), MAX($G$1:G160)+1, ""))</f>
@@ -6169,19 +6184,19 @@
         <v>30</v>
       </c>
       <c r="B162" s="31" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C162" s="32">
         <v>30</v>
       </c>
       <c r="D162" s="30" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="E162" s="31" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="F162" s="30" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="G162" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B162),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E162),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F162),0)&gt;0), MAX($G$1:G161)+1, ""))</f>
@@ -6197,19 +6212,19 @@
         <v>30</v>
       </c>
       <c r="B163" s="31" t="s">
-        <v>337</v>
+        <v>184</v>
       </c>
       <c r="C163" s="32">
         <v>30</v>
       </c>
-      <c r="D163" s="30">
-        <v>2.9</v>
+      <c r="D163" s="30" t="s">
+        <v>228</v>
       </c>
       <c r="E163" s="31" t="s">
         <v>81</v>
       </c>
       <c r="F163" s="30" t="s">
-        <v>338</v>
+        <v>185</v>
       </c>
       <c r="G163" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B163),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E163),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F163),0)&gt;0), MAX($G$1:G162)+1, ""))</f>
@@ -6221,26 +6236,26 @@
       </c>
     </row>
     <row r="164" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A164" s="30">
+      <c r="A164" s="26">
         <v>30</v>
       </c>
-      <c r="B164" s="31" t="s">
-        <v>180</v>
-      </c>
-      <c r="C164" s="32">
+      <c r="B164" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="C164" s="28">
         <v>30</v>
       </c>
-      <c r="D164" s="30" t="s">
-        <v>238</v>
-      </c>
-      <c r="E164" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="F164" s="30" t="s">
-        <v>181</v>
+      <c r="D164" s="26">
+        <v>5</v>
+      </c>
+      <c r="E164" s="27" t="s">
+        <v>378</v>
+      </c>
+      <c r="F164" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="G164" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B164),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E164),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F164),0)&gt;0), MAX($G$1:G162)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B164),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E164),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F164),0)&gt;0), MAX($G$1:G163)+1, ""))</f>
         <v/>
       </c>
       <c r="H164" s="21" t="b">
@@ -6249,23 +6264,23 @@
       </c>
     </row>
     <row r="165" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A165" s="26">
-        <v>40</v>
-      </c>
-      <c r="B165" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="C165" s="28">
-        <v>40</v>
-      </c>
-      <c r="D165" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="E165" s="27" t="s">
-        <v>198</v>
-      </c>
-      <c r="F165" s="26" t="s">
-        <v>199</v>
+      <c r="A165" s="30">
+        <v>30</v>
+      </c>
+      <c r="B165" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="C165" s="32">
+        <v>30</v>
+      </c>
+      <c r="D165" s="30" t="s">
+        <v>239</v>
+      </c>
+      <c r="E165" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="F165" s="30" t="s">
+        <v>183</v>
       </c>
       <c r="G165" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B165),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E165),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F165),0)&gt;0), MAX($G$1:G164)+1, ""))</f>
@@ -6277,23 +6292,23 @@
       </c>
     </row>
     <row r="166" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A166" s="26">
-        <v>40</v>
-      </c>
-      <c r="B166" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="C166" s="28">
-        <v>40</v>
-      </c>
-      <c r="D166" s="26" t="s">
-        <v>242</v>
-      </c>
-      <c r="E166" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="F166" s="26" t="s">
-        <v>196</v>
+      <c r="A166" s="30">
+        <v>30</v>
+      </c>
+      <c r="B166" s="31" t="s">
+        <v>337</v>
+      </c>
+      <c r="C166" s="32">
+        <v>30</v>
+      </c>
+      <c r="D166" s="30">
+        <v>2.9</v>
+      </c>
+      <c r="E166" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="F166" s="30" t="s">
+        <v>338</v>
       </c>
       <c r="G166" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B166),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E166),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F166),0)&gt;0), MAX($G$1:G165)+1, ""))</f>
@@ -6305,26 +6320,26 @@
       </c>
     </row>
     <row r="167" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A167" s="26">
-        <v>40</v>
-      </c>
-      <c r="B167" s="27" t="s">
-        <v>249</v>
-      </c>
-      <c r="C167" s="28">
-        <v>40</v>
-      </c>
-      <c r="D167" s="26">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="E167" s="27" t="s">
-        <v>250</v>
-      </c>
-      <c r="F167" s="26" t="s">
-        <v>251</v>
+      <c r="A167" s="30">
+        <v>30</v>
+      </c>
+      <c r="B167" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="C167" s="32">
+        <v>30</v>
+      </c>
+      <c r="D167" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="E167" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="F167" s="30" t="s">
+        <v>181</v>
       </c>
       <c r="G167" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B167),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E167),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F167),0)&gt;0), MAX($G$1:G166)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B167),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E167),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F167),0)&gt;0), MAX($G$1:G165)+1, ""))</f>
         <v/>
       </c>
       <c r="H167" s="21" t="b">
@@ -6334,22 +6349,22 @@
     </row>
     <row r="168" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A168" s="26">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B168" s="27" t="s">
-        <v>294</v>
+        <v>197</v>
       </c>
       <c r="C168" s="28">
-        <v>45</v>
-      </c>
-      <c r="D168" s="26">
-        <v>10.199999999999999</v>
+        <v>40</v>
+      </c>
+      <c r="D168" s="26" t="s">
+        <v>243</v>
       </c>
       <c r="E168" s="27" t="s">
-        <v>295</v>
+        <v>198</v>
       </c>
       <c r="F168" s="26" t="s">
-        <v>296</v>
+        <v>199</v>
       </c>
       <c r="G168" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B168),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E168),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F168),0)&gt;0), MAX($G$1:G167)+1, ""))</f>
@@ -6361,22 +6376,88 @@
       </c>
     </row>
     <row r="169" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A169" s="1"/>
-      <c r="C169" s="1"/>
-      <c r="D169" s="1"/>
-      <c r="F169" s="1"/>
+      <c r="A169" s="26">
+        <v>40</v>
+      </c>
+      <c r="B169" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="C169" s="28">
+        <v>40</v>
+      </c>
+      <c r="D169" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="E169" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="F169" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="G169" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B169),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E169),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F169),0)&gt;0), MAX($G$1:G168)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H169" s="21" t="b">
+        <f>A169=C169</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="170" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A170" s="1"/>
-      <c r="C170" s="1"/>
-      <c r="D170" s="1"/>
-      <c r="F170" s="1"/>
+      <c r="A170" s="26">
+        <v>40</v>
+      </c>
+      <c r="B170" s="27" t="s">
+        <v>249</v>
+      </c>
+      <c r="C170" s="28">
+        <v>40</v>
+      </c>
+      <c r="D170" s="26">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E170" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="F170" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="G170" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B170),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E170),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F170),0)&gt;0), MAX($G$1:G169)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H170" s="21" t="b">
+        <f>A170=C170</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="171" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A171" s="1"/>
-      <c r="C171" s="1"/>
-      <c r="D171" s="1"/>
-      <c r="F171" s="1"/>
+      <c r="A171" s="26">
+        <v>45</v>
+      </c>
+      <c r="B171" s="27" t="s">
+        <v>294</v>
+      </c>
+      <c r="C171" s="28">
+        <v>45</v>
+      </c>
+      <c r="D171" s="26">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E171" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="F171" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="G171" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B171),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E171),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F171),0)&gt;0), MAX($G$1:G170)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H171" s="21" t="b">
+        <f>A171=C171</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="172" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
@@ -11606,10 +11687,10 @@
       <sortCondition ref="D2:D147"/>
     </sortState>
   </autoFilter>
-  <sortState ref="A2:H168">
-    <sortCondition ref="A2:A168"/>
-    <sortCondition ref="B2:B168"/>
-    <sortCondition ref="D2:D168"/>
+  <sortState ref="A2:H171">
+    <sortCondition ref="A2:A171"/>
+    <sortCondition ref="B2:B171"/>
+    <sortCondition ref="D2:D171"/>
   </sortState>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Consulta" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$171</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$140</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Base!$1:$1</definedName>
   </definedNames>
@@ -4980,22 +4980,22 @@
         <v>20</v>
       </c>
       <c r="B119" s="27" t="s">
-        <v>355</v>
+        <v>310</v>
       </c>
       <c r="C119" s="28">
         <v>20</v>
       </c>
       <c r="D119" s="26">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="E119" s="27" t="s">
-        <v>81</v>
+        <v>309</v>
       </c>
       <c r="F119" s="26" t="s">
-        <v>356</v>
+        <v>311</v>
       </c>
       <c r="G119" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F119),0)&gt;0), MAX($G$1:G118)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F119),0)&gt;0), MAX($G$1:G117)+1, ""))</f>
         <v/>
       </c>
       <c r="H119" s="21" t="b">
@@ -5004,23 +5004,23 @@
       </c>
     </row>
     <row r="120" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A120" s="30">
+      <c r="A120" s="26">
         <v>20</v>
       </c>
-      <c r="B120" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="C120" s="32">
+      <c r="B120" s="27" t="s">
+        <v>355</v>
+      </c>
+      <c r="C120" s="28">
         <v>20</v>
       </c>
-      <c r="D120" s="30" t="s">
-        <v>218</v>
-      </c>
-      <c r="E120" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F120" s="30" t="s">
-        <v>92</v>
+      <c r="D120" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E120" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F120" s="26" t="s">
+        <v>356</v>
       </c>
       <c r="G120" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F120),0)&gt;0), MAX($G$1:G119)+1, ""))</f>
@@ -5036,19 +5036,19 @@
         <v>20</v>
       </c>
       <c r="B121" s="31" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C121" s="32">
         <v>20</v>
       </c>
       <c r="D121" s="30" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="E121" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F121" s="30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G121" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F121),0)&gt;0), MAX($G$1:G120)+1, ""))</f>
@@ -5064,16 +5064,16 @@
         <v>20</v>
       </c>
       <c r="B122" s="31" t="s">
-        <v>290</v>
+        <v>89</v>
       </c>
       <c r="C122" s="32">
         <v>20</v>
       </c>
-      <c r="D122" s="30">
-        <v>1.8</v>
+      <c r="D122" s="30" t="s">
+        <v>223</v>
       </c>
       <c r="E122" s="31" t="s">
-        <v>291</v>
+        <v>8</v>
       </c>
       <c r="F122" s="30" t="s">
         <v>90</v>
@@ -5092,19 +5092,19 @@
         <v>20</v>
       </c>
       <c r="B123" s="31" t="s">
-        <v>87</v>
+        <v>290</v>
       </c>
       <c r="C123" s="32">
         <v>20</v>
       </c>
-      <c r="D123" s="30" t="s">
-        <v>222</v>
+      <c r="D123" s="30">
+        <v>1.8</v>
       </c>
       <c r="E123" s="31" t="s">
-        <v>8</v>
+        <v>291</v>
       </c>
       <c r="F123" s="30" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G123" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F123),0)&gt;0), MAX($G$1:G122)+1, ""))</f>
@@ -5120,19 +5120,19 @@
         <v>20</v>
       </c>
       <c r="B124" s="31" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C124" s="32">
         <v>20</v>
       </c>
       <c r="D124" s="30" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E124" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F124" s="30" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G124" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F124),0)&gt;0), MAX($G$1:G123)+1, ""))</f>
@@ -5148,19 +5148,19 @@
         <v>20</v>
       </c>
       <c r="B125" s="31" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C125" s="32">
         <v>20</v>
       </c>
       <c r="D125" s="30" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E125" s="31" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F125" s="30" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G125" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F125),0)&gt;0), MAX($G$1:G124)+1, ""))</f>
@@ -5176,19 +5176,19 @@
         <v>20</v>
       </c>
       <c r="B126" s="31" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C126" s="32">
         <v>20</v>
       </c>
       <c r="D126" s="30" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E126" s="31" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="F126" s="30" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G126" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F126),0)&gt;0), MAX($G$1:G125)+1, ""))</f>
@@ -5204,19 +5204,19 @@
         <v>20</v>
       </c>
       <c r="B127" s="31" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C127" s="32">
         <v>20</v>
       </c>
       <c r="D127" s="30" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E127" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F127" s="30" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G127" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F127),0)&gt;0), MAX($G$1:G126)+1, ""))</f>
@@ -5228,23 +5228,23 @@
       </c>
     </row>
     <row r="128" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A128" s="26">
-        <v>25</v>
-      </c>
-      <c r="B128" s="27" t="s">
-        <v>178</v>
-      </c>
-      <c r="C128" s="28">
-        <v>25</v>
-      </c>
-      <c r="D128" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="E128" s="27" t="s">
+      <c r="A128" s="30">
+        <v>20</v>
+      </c>
+      <c r="B128" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="C128" s="32">
+        <v>20</v>
+      </c>
+      <c r="D128" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="E128" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F128" s="26" t="s">
-        <v>179</v>
+      <c r="F128" s="30" t="s">
+        <v>77</v>
       </c>
       <c r="G128" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F128),0)&gt;0), MAX($G$1:G127)+1, ""))</f>
@@ -5260,19 +5260,19 @@
         <v>25</v>
       </c>
       <c r="B129" s="27" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C129" s="28">
         <v>25</v>
       </c>
       <c r="D129" s="26" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="E129" s="27" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="F129" s="26" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G129" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F129),0)&gt;0), MAX($G$1:G128)+1, ""))</f>
@@ -5288,19 +5288,19 @@
         <v>25</v>
       </c>
       <c r="B130" s="27" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C130" s="28">
         <v>25</v>
       </c>
       <c r="D130" s="26" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="E130" s="27" t="s">
         <v>131</v>
       </c>
       <c r="F130" s="26" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G130" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F130),0)&gt;0), MAX($G$1:G129)+1, ""))</f>
@@ -5316,19 +5316,19 @@
         <v>25</v>
       </c>
       <c r="B131" s="27" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C131" s="28">
         <v>25</v>
       </c>
       <c r="D131" s="26" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="E131" s="27" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F131" s="26" t="s">
-        <v>324</v>
+        <v>175</v>
       </c>
       <c r="G131" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F131),0)&gt;0), MAX($G$1:G130)+1, ""))</f>
@@ -5344,19 +5344,19 @@
         <v>25</v>
       </c>
       <c r="B132" s="27" t="s">
-        <v>359</v>
+        <v>173</v>
       </c>
       <c r="C132" s="28">
         <v>25</v>
       </c>
-      <c r="D132" s="26">
-        <v>3</v>
+      <c r="D132" s="26" t="s">
+        <v>224</v>
       </c>
       <c r="E132" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F132" s="26" t="s">
-        <v>360</v>
+        <v>324</v>
       </c>
       <c r="G132" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B132),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E132),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F132),0)&gt;0), MAX($G$1:G131)+1, ""))</f>
@@ -5372,19 +5372,19 @@
         <v>25</v>
       </c>
       <c r="B133" s="27" t="s">
-        <v>172</v>
+        <v>359</v>
       </c>
       <c r="C133" s="28">
         <v>25</v>
       </c>
       <c r="D133" s="26">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="E133" s="27" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F133" s="26" t="s">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="G133" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F133),0)&gt;0), MAX($G$1:G132)+1, ""))</f>
@@ -5396,23 +5396,23 @@
       </c>
     </row>
     <row r="134" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A134" s="30">
+      <c r="A134" s="26">
         <v>25</v>
       </c>
-      <c r="B134" s="31" t="s">
-        <v>284</v>
-      </c>
-      <c r="C134" s="32">
+      <c r="B134" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="C134" s="28">
         <v>25</v>
       </c>
-      <c r="D134" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E134" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F134" s="30" t="s">
-        <v>102</v>
+      <c r="D134" s="26">
+        <v>2.7</v>
+      </c>
+      <c r="E134" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F134" s="26" t="s">
+        <v>338</v>
       </c>
       <c r="G134" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F134),0)&gt;0), MAX($G$1:G133)+1, ""))</f>
@@ -5428,7 +5428,7 @@
         <v>25</v>
       </c>
       <c r="B135" s="31" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C135" s="32">
         <v>25</v>
@@ -5452,23 +5452,23 @@
       </c>
     </row>
     <row r="136" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A136" s="26">
+      <c r="A136" s="30">
         <v>25</v>
       </c>
-      <c r="B136" s="27" t="s">
-        <v>170</v>
-      </c>
-      <c r="C136" s="28">
+      <c r="B136" s="31" t="s">
+        <v>282</v>
+      </c>
+      <c r="C136" s="32">
         <v>25</v>
       </c>
-      <c r="D136" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="E136" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="F136" s="26" t="s">
-        <v>171</v>
+      <c r="D136" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E136" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="F136" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G136" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F136),0)&gt;0), MAX($G$1:G135)+1, ""))</f>
@@ -5484,19 +5484,19 @@
         <v>25</v>
       </c>
       <c r="B137" s="27" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C137" s="28">
         <v>25</v>
       </c>
       <c r="D137" s="26" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="E137" s="27" t="s">
-        <v>8</v>
+        <v>245</v>
       </c>
       <c r="F137" s="26" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G137" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F137),0)&gt;0), MAX($G$1:G136)+1, ""))</f>
@@ -5512,19 +5512,19 @@
         <v>25</v>
       </c>
       <c r="B138" s="27" t="s">
-        <v>357</v>
+        <v>168</v>
       </c>
       <c r="C138" s="28">
         <v>25</v>
       </c>
-      <c r="D138" s="26">
-        <v>3.4</v>
+      <c r="D138" s="26" t="s">
+        <v>217</v>
       </c>
       <c r="E138" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F138" s="26" t="s">
-        <v>358</v>
+        <v>169</v>
       </c>
       <c r="G138" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F138),0)&gt;0), MAX($G$1:G137)+1, ""))</f>
@@ -5536,23 +5536,23 @@
       </c>
     </row>
     <row r="139" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A139" s="30">
+      <c r="A139" s="26">
         <v>25</v>
       </c>
-      <c r="B139" s="31" t="s">
-        <v>278</v>
-      </c>
-      <c r="C139" s="32">
+      <c r="B139" s="27" t="s">
+        <v>357</v>
+      </c>
+      <c r="C139" s="28">
         <v>25</v>
       </c>
-      <c r="D139" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E139" s="31" t="s">
+      <c r="D139" s="26">
+        <v>3.4</v>
+      </c>
+      <c r="E139" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F139" s="30" t="s">
-        <v>102</v>
+      <c r="F139" s="26" t="s">
+        <v>358</v>
       </c>
       <c r="G139" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F139),0)&gt;0), MAX($G$1:G138)+1, ""))</f>
@@ -5564,23 +5564,23 @@
       </c>
     </row>
     <row r="140" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A140" s="26">
+      <c r="A140" s="30">
         <v>25</v>
       </c>
-      <c r="B140" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="C140" s="28">
+      <c r="B140" s="31" t="s">
+        <v>278</v>
+      </c>
+      <c r="C140" s="32">
         <v>25</v>
       </c>
-      <c r="D140" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="E140" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="F140" s="26" t="s">
-        <v>167</v>
+      <c r="D140" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E140" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F140" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G140" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F140),0)&gt;0), MAX($G$1:G139)+1, ""))</f>
@@ -5596,19 +5596,19 @@
         <v>25</v>
       </c>
       <c r="B141" s="27" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C141" s="28">
         <v>25</v>
       </c>
       <c r="D141" s="26" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="E141" s="27" t="s">
         <v>131</v>
       </c>
       <c r="F141" s="26" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G141" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F141),0)&gt;0), MAX($G$1:G140)+1, ""))</f>
@@ -5624,19 +5624,19 @@
         <v>25</v>
       </c>
       <c r="B142" s="27" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C142" s="28">
         <v>25</v>
       </c>
       <c r="D142" s="26" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E142" s="27" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="F142" s="26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G142" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F142),0)&gt;0), MAX($G$1:G141)+1, ""))</f>
@@ -5652,19 +5652,19 @@
         <v>25</v>
       </c>
       <c r="B143" s="27" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C143" s="28">
         <v>25</v>
       </c>
       <c r="D143" s="26" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="E143" s="27" t="s">
         <v>81</v>
       </c>
       <c r="F143" s="26" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G143" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F143),0)&gt;0), MAX($G$1:G142)+1, ""))</f>
@@ -5680,19 +5680,19 @@
         <v>25</v>
       </c>
       <c r="B144" s="27" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C144" s="28">
         <v>25</v>
       </c>
       <c r="D144" s="26" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E144" s="27" t="s">
         <v>81</v>
       </c>
       <c r="F144" s="26" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G144" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F144),0)&gt;0), MAX($G$1:G143)+1, ""))</f>
@@ -5708,19 +5708,19 @@
         <v>25</v>
       </c>
       <c r="B145" s="27" t="s">
-        <v>342</v>
+        <v>158</v>
       </c>
       <c r="C145" s="28">
         <v>25</v>
       </c>
-      <c r="D145" s="26">
-        <v>3.4</v>
+      <c r="D145" s="26" t="s">
+        <v>228</v>
       </c>
       <c r="E145" s="27" t="s">
         <v>81</v>
       </c>
       <c r="F145" s="26" t="s">
-        <v>343</v>
+        <v>159</v>
       </c>
       <c r="G145" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B145),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E145),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F145),0)&gt;0), MAX($G$1:G144)+1, ""))</f>
@@ -5736,22 +5736,22 @@
         <v>25</v>
       </c>
       <c r="B146" s="27" t="s">
-        <v>310</v>
+        <v>342</v>
       </c>
       <c r="C146" s="28">
         <v>25</v>
       </c>
       <c r="D146" s="26">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="E146" s="27" t="s">
-        <v>309</v>
+        <v>81</v>
       </c>
       <c r="F146" s="26" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="G146" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F146),0)&gt;0), MAX($G$1:G144)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F146),0)&gt;0), MAX($G$1:G145)+1, ""))</f>
         <v/>
       </c>
       <c r="H146" s="21" t="b">
@@ -11680,11 +11680,11 @@
       <c r="F1041" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H165">
-    <sortState ref="A2:H147">
-      <sortCondition ref="A2:A147"/>
-      <sortCondition ref="B2:B147"/>
-      <sortCondition ref="D2:D147"/>
+  <autoFilter ref="A1:H171">
+    <sortState ref="A2:H171">
+      <sortCondition ref="A2:A171"/>
+      <sortCondition ref="B2:B171"/>
+      <sortCondition ref="D2:D171"/>
     </sortState>
   </autoFilter>
   <sortState ref="A2:H171">

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="390">
   <si>
     <t>Grupo</t>
   </si>
@@ -1183,6 +1183,18 @@
   </si>
   <si>
     <t>TRAVESSA TUPY - UNIVERSAL</t>
+  </si>
+  <si>
+    <t>APUCARANA</t>
+  </si>
+  <si>
+    <t>21735-040</t>
+  </si>
+  <si>
+    <t>21710-530</t>
+  </si>
+  <si>
+    <t>CORONEL VALENCIA</t>
   </si>
 </sst>
 </file>
@@ -3924,26 +3936,26 @@
       </c>
     </row>
     <row r="81" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A81" s="30">
+      <c r="A81" s="26">
         <v>20</v>
       </c>
-      <c r="B81" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="C81" s="32">
+      <c r="B81" s="27" t="s">
+        <v>386</v>
+      </c>
+      <c r="C81" s="28">
         <v>20</v>
       </c>
-      <c r="D81" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="E81" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F81" s="30" t="s">
-        <v>143</v>
+      <c r="D81" s="26">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E81" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F81" s="26" t="s">
+        <v>387</v>
       </c>
       <c r="G81" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F81),0)&gt;0), MAX($G$1:G79)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F81),0)&gt;0), MAX($G$1:G80)+1, ""))</f>
         <v/>
       </c>
       <c r="H81" s="21" t="b">
@@ -3956,22 +3968,22 @@
         <v>20</v>
       </c>
       <c r="B82" s="31" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C82" s="32">
         <v>20</v>
       </c>
       <c r="D82" s="30" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="E82" s="31" t="s">
-        <v>305</v>
+        <v>8</v>
       </c>
       <c r="F82" s="30" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G82" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F82),0)&gt;0), MAX($G$1:G81)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F82),0)&gt;0), MAX($G$1:G80)+1, ""))</f>
         <v/>
       </c>
       <c r="H82" s="21" t="b">
@@ -3980,25 +3992,28 @@
       </c>
     </row>
     <row r="83" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A83" s="36">
+      <c r="A83" s="30">
         <v>20</v>
       </c>
-      <c r="B83" s="37" t="s">
-        <v>333</v>
-      </c>
-      <c r="C83" s="38">
+      <c r="B83" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="C83" s="32">
         <v>20</v>
       </c>
-      <c r="D83" s="36">
-        <v>3.4</v>
-      </c>
-      <c r="E83" s="37" t="s">
-        <v>336</v>
-      </c>
-      <c r="F83" s="36" t="s">
-        <v>334</v>
-      </c>
-      <c r="G83" s="29"/>
+      <c r="D83" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="E83" s="31" t="s">
+        <v>305</v>
+      </c>
+      <c r="F83" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="G83" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F83),0)&gt;0), MAX($G$1:G82)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H83" s="21" t="b">
         <f>A83=C83</f>
         <v>1</v>
@@ -4009,19 +4024,19 @@
         <v>20</v>
       </c>
       <c r="B84" s="37" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C84" s="38">
         <v>20</v>
       </c>
       <c r="D84" s="36">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="E84" s="37" t="s">
         <v>336</v>
       </c>
       <c r="F84" s="36" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G84" s="29"/>
       <c r="H84" s="21" t="b">
@@ -4030,28 +4045,25 @@
       </c>
     </row>
     <row r="85" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A85" s="30">
+      <c r="A85" s="36">
         <v>20</v>
       </c>
-      <c r="B85" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="C85" s="32">
+      <c r="B85" s="37" t="s">
+        <v>331</v>
+      </c>
+      <c r="C85" s="38">
         <v>20</v>
       </c>
-      <c r="D85" s="30" t="s">
-        <v>223</v>
-      </c>
-      <c r="E85" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F85" s="30" t="s">
-        <v>139</v>
-      </c>
-      <c r="G85" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F85),0)&gt;0), MAX($G$1:G84)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D85" s="36">
+        <v>3.3</v>
+      </c>
+      <c r="E85" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="F85" s="36" t="s">
+        <v>332</v>
+      </c>
+      <c r="G85" s="29"/>
       <c r="H85" s="21" t="b">
         <f>A85=C85</f>
         <v>1</v>
@@ -4062,19 +4074,19 @@
         <v>20</v>
       </c>
       <c r="B86" s="31" t="s">
-        <v>255</v>
+        <v>138</v>
       </c>
       <c r="C86" s="32">
         <v>20</v>
       </c>
       <c r="D86" s="30" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E86" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F86" s="30" t="s">
-        <v>256</v>
+        <v>139</v>
       </c>
       <c r="G86" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F86),0)&gt;0), MAX($G$1:G85)+1, ""))</f>
@@ -4090,19 +4102,19 @@
         <v>20</v>
       </c>
       <c r="B87" s="31" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C87" s="32">
         <v>20</v>
       </c>
-      <c r="D87" s="30">
-        <v>4.2</v>
+      <c r="D87" s="30" t="s">
+        <v>225</v>
       </c>
       <c r="E87" s="31" t="s">
-        <v>305</v>
-      </c>
-      <c r="F87" s="30">
-        <v>21765430</v>
+        <v>8</v>
+      </c>
+      <c r="F87" s="30" t="s">
+        <v>256</v>
       </c>
       <c r="G87" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F87),0)&gt;0), MAX($G$1:G86)+1, ""))</f>
@@ -4118,19 +4130,19 @@
         <v>20</v>
       </c>
       <c r="B88" s="31" t="s">
-        <v>136</v>
+        <v>254</v>
       </c>
       <c r="C88" s="32">
         <v>20</v>
       </c>
-      <c r="D88" s="30" t="s">
-        <v>210</v>
+      <c r="D88" s="30">
+        <v>4.2</v>
       </c>
       <c r="E88" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F88" s="30" t="s">
-        <v>137</v>
+        <v>305</v>
+      </c>
+      <c r="F88" s="30">
+        <v>21765430</v>
       </c>
       <c r="G88" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F88),0)&gt;0), MAX($G$1:G87)+1, ""))</f>
@@ -4146,19 +4158,19 @@
         <v>20</v>
       </c>
       <c r="B89" s="31" t="s">
-        <v>265</v>
+        <v>136</v>
       </c>
       <c r="C89" s="32">
         <v>20</v>
       </c>
       <c r="D89" s="30" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="E89" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F89" s="30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G89" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F89),0)&gt;0), MAX($G$1:G88)+1, ""))</f>
@@ -4174,19 +4186,19 @@
         <v>20</v>
       </c>
       <c r="B90" s="31" t="s">
-        <v>133</v>
+        <v>265</v>
       </c>
       <c r="C90" s="32">
         <v>20</v>
       </c>
       <c r="D90" s="30" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E90" s="31" t="s">
-        <v>305</v>
+        <v>8</v>
       </c>
       <c r="F90" s="30" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G90" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F90),0)&gt;0), MAX($G$1:G89)+1, ""))</f>
@@ -4202,19 +4214,19 @@
         <v>20</v>
       </c>
       <c r="B91" s="31" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C91" s="32">
         <v>20</v>
       </c>
       <c r="D91" s="30" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E91" s="31" t="s">
-        <v>131</v>
+        <v>305</v>
       </c>
       <c r="F91" s="30" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G91" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F91),0)&gt;0), MAX($G$1:G90)+1, ""))</f>
@@ -4226,23 +4238,23 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A92" s="26">
+      <c r="A92" s="30">
         <v>20</v>
       </c>
-      <c r="B92" s="27" t="s">
-        <v>312</v>
-      </c>
-      <c r="C92" s="28">
+      <c r="B92" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="C92" s="32">
         <v>20</v>
       </c>
-      <c r="D92" s="26">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="E92" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="F92" s="26" t="s">
-        <v>318</v>
+      <c r="D92" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="E92" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="F92" s="30" t="s">
+        <v>132</v>
       </c>
       <c r="G92" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F92),0)&gt;0), MAX($G$1:G91)+1, ""))</f>
@@ -4254,23 +4266,23 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A93" s="30">
+      <c r="A93" s="26">
         <v>20</v>
       </c>
-      <c r="B93" s="31" t="s">
-        <v>128</v>
-      </c>
-      <c r="C93" s="32">
+      <c r="B93" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="C93" s="28">
         <v>20</v>
       </c>
-      <c r="D93" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="E93" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F93" s="30" t="s">
-        <v>129</v>
+      <c r="D93" s="26">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E93" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F93" s="26" t="s">
+        <v>318</v>
       </c>
       <c r="G93" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F93),0)&gt;0), MAX($G$1:G92)+1, ""))</f>
@@ -4282,23 +4294,23 @@
       </c>
     </row>
     <row r="94" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A94" s="30">
+      <c r="A94" s="26">
         <v>20</v>
       </c>
-      <c r="B94" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="C94" s="32">
+      <c r="B94" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="C94" s="28">
         <v>20</v>
       </c>
-      <c r="D94" s="30" t="s">
-        <v>234</v>
-      </c>
-      <c r="E94" s="31" t="s">
-        <v>305</v>
-      </c>
-      <c r="F94" s="30" t="s">
-        <v>127</v>
+      <c r="D94" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E94" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F94" s="26" t="s">
+        <v>388</v>
       </c>
       <c r="G94" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F94),0)&gt;0), MAX($G$1:G93)+1, ""))</f>
@@ -4310,23 +4322,23 @@
       </c>
     </row>
     <row r="95" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A95" s="26">
+      <c r="A95" s="30">
         <v>20</v>
       </c>
-      <c r="B95" s="27" t="s">
-        <v>375</v>
-      </c>
-      <c r="C95" s="28">
+      <c r="B95" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="C95" s="32">
         <v>20</v>
       </c>
-      <c r="D95" s="26">
-        <v>2.7</v>
-      </c>
-      <c r="E95" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="F95" s="26" t="s">
-        <v>351</v>
+      <c r="D95" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="E95" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F95" s="30" t="s">
+        <v>129</v>
       </c>
       <c r="G95" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F95),0)&gt;0), MAX($G$1:G94)+1, ""))</f>
@@ -4342,19 +4354,19 @@
         <v>20</v>
       </c>
       <c r="B96" s="31" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C96" s="32">
         <v>20</v>
       </c>
       <c r="D96" s="30" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="E96" s="31" t="s">
-        <v>8</v>
+        <v>305</v>
       </c>
       <c r="F96" s="30" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G96" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F96),0)&gt;0), MAX($G$1:G95)+1, ""))</f>
@@ -4366,23 +4378,23 @@
       </c>
     </row>
     <row r="97" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A97" s="30">
+      <c r="A97" s="26">
         <v>20</v>
       </c>
-      <c r="B97" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="C97" s="32">
+      <c r="B97" s="27" t="s">
+        <v>375</v>
+      </c>
+      <c r="C97" s="28">
         <v>20</v>
       </c>
-      <c r="D97" s="30" t="s">
-        <v>215</v>
-      </c>
-      <c r="E97" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F97" s="30" t="s">
-        <v>123</v>
+      <c r="D97" s="26">
+        <v>2.7</v>
+      </c>
+      <c r="E97" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="F97" s="26" t="s">
+        <v>351</v>
       </c>
       <c r="G97" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F97),0)&gt;0), MAX($G$1:G96)+1, ""))</f>
@@ -4398,19 +4410,19 @@
         <v>20</v>
       </c>
       <c r="B98" s="31" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C98" s="32">
         <v>20</v>
       </c>
       <c r="D98" s="30" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="E98" s="31" t="s">
-        <v>305</v>
+        <v>8</v>
       </c>
       <c r="F98" s="30" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G98" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F98),0)&gt;0), MAX($G$1:G97)+1, ""))</f>
@@ -4422,23 +4434,23 @@
       </c>
     </row>
     <row r="99" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A99" s="26">
+      <c r="A99" s="30">
         <v>20</v>
       </c>
-      <c r="B99" s="27" t="s">
-        <v>369</v>
-      </c>
-      <c r="C99" s="28">
+      <c r="B99" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="C99" s="32">
         <v>20</v>
       </c>
-      <c r="D99" s="26">
-        <v>1.5</v>
+      <c r="D99" s="30" t="s">
+        <v>215</v>
       </c>
       <c r="E99" s="31" t="s">
-        <v>299</v>
-      </c>
-      <c r="F99" s="26" t="s">
-        <v>370</v>
+        <v>8</v>
+      </c>
+      <c r="F99" s="30" t="s">
+        <v>123</v>
       </c>
       <c r="G99" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F99),0)&gt;0), MAX($G$1:G98)+1, ""))</f>
@@ -4454,19 +4466,19 @@
         <v>20</v>
       </c>
       <c r="B100" s="31" t="s">
-        <v>257</v>
+        <v>120</v>
       </c>
       <c r="C100" s="32">
         <v>20</v>
       </c>
       <c r="D100" s="30" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E100" s="31" t="s">
-        <v>8</v>
+        <v>305</v>
       </c>
       <c r="F100" s="30" t="s">
-        <v>258</v>
+        <v>121</v>
       </c>
       <c r="G100" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F100),0)&gt;0), MAX($G$1:G99)+1, ""))</f>
@@ -4478,23 +4490,23 @@
       </c>
     </row>
     <row r="101" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A101" s="30">
+      <c r="A101" s="26">
         <v>20</v>
       </c>
-      <c r="B101" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="C101" s="32">
+      <c r="B101" s="27" t="s">
+        <v>369</v>
+      </c>
+      <c r="C101" s="28">
         <v>20</v>
       </c>
-      <c r="D101" s="30" t="s">
-        <v>227</v>
+      <c r="D101" s="26">
+        <v>1.5</v>
       </c>
       <c r="E101" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F101" s="30" t="s">
-        <v>119</v>
+        <v>299</v>
+      </c>
+      <c r="F101" s="26" t="s">
+        <v>370</v>
       </c>
       <c r="G101" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F101),0)&gt;0), MAX($G$1:G100)+1, ""))</f>
@@ -4510,19 +4522,19 @@
         <v>20</v>
       </c>
       <c r="B102" s="31" t="s">
-        <v>116</v>
+        <v>257</v>
       </c>
       <c r="C102" s="32">
         <v>20</v>
       </c>
       <c r="D102" s="30" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="E102" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F102" s="30" t="s">
-        <v>117</v>
+        <v>258</v>
       </c>
       <c r="G102" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F102),0)&gt;0), MAX($G$1:G101)+1, ""))</f>
@@ -4538,19 +4550,19 @@
         <v>20</v>
       </c>
       <c r="B103" s="31" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C103" s="32">
         <v>20</v>
       </c>
       <c r="D103" s="30" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="E103" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F103" s="30" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G103" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F103),0)&gt;0), MAX($G$1:G102)+1, ""))</f>
@@ -4562,23 +4574,23 @@
       </c>
     </row>
     <row r="104" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A104" s="26">
+      <c r="A104" s="30">
         <v>20</v>
       </c>
-      <c r="B104" s="27" t="s">
-        <v>297</v>
-      </c>
-      <c r="C104" s="28">
+      <c r="B104" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="C104" s="32">
         <v>20</v>
       </c>
-      <c r="D104" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E104" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="F104" s="26" t="s">
-        <v>298</v>
+      <c r="D104" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="E104" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F104" s="30" t="s">
+        <v>117</v>
       </c>
       <c r="G104" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F104),0)&gt;0), MAX($G$1:G103)+1, ""))</f>
@@ -4594,19 +4606,19 @@
         <v>20</v>
       </c>
       <c r="B105" s="31" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C105" s="32">
         <v>20</v>
       </c>
       <c r="D105" s="30" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="E105" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F105" s="30" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G105" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F105),0)&gt;0), MAX($G$1:G104)+1, ""))</f>
@@ -4618,23 +4630,23 @@
       </c>
     </row>
     <row r="106" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A106" s="30">
+      <c r="A106" s="26">
         <v>20</v>
       </c>
-      <c r="B106" s="31" t="s">
-        <v>110</v>
-      </c>
-      <c r="C106" s="32">
+      <c r="B106" s="27" t="s">
+        <v>297</v>
+      </c>
+      <c r="C106" s="28">
         <v>20</v>
       </c>
-      <c r="D106" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="E106" s="31" t="s">
+      <c r="D106" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E106" s="27" t="s">
         <v>299</v>
       </c>
-      <c r="F106" s="30" t="s">
-        <v>111</v>
+      <c r="F106" s="26" t="s">
+        <v>298</v>
       </c>
       <c r="G106" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F106),0)&gt;0), MAX($G$1:G105)+1, ""))</f>
@@ -4650,19 +4662,19 @@
         <v>20</v>
       </c>
       <c r="B107" s="31" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C107" s="32">
         <v>20</v>
       </c>
       <c r="D107" s="30" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E107" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F107" s="30" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G107" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F107),0)&gt;0), MAX($G$1:G106)+1, ""))</f>
@@ -4674,48 +4686,51 @@
       </c>
     </row>
     <row r="108" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A108" s="36">
+      <c r="A108" s="30">
         <v>20</v>
       </c>
-      <c r="B108" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="C108" s="38">
+      <c r="B108" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="C108" s="32">
         <v>20</v>
       </c>
-      <c r="D108" s="36">
-        <v>3</v>
-      </c>
-      <c r="E108" s="37" t="s">
-        <v>304</v>
-      </c>
-      <c r="F108" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="G108" s="29"/>
+      <c r="D108" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="E108" s="31" t="s">
+        <v>299</v>
+      </c>
+      <c r="F108" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="G108" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F108),0)&gt;0), MAX($G$1:G107)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H108" s="21" t="b">
         <f>A108=C108</f>
         <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A109" s="26">
+      <c r="A109" s="30">
         <v>20</v>
       </c>
-      <c r="B109" s="27" t="s">
-        <v>302</v>
-      </c>
-      <c r="C109" s="28">
+      <c r="B109" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="C109" s="32">
         <v>20</v>
       </c>
-      <c r="D109" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E109" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="F109" s="26" t="s">
-        <v>301</v>
+      <c r="D109" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="E109" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F109" s="30" t="s">
+        <v>109</v>
       </c>
       <c r="G109" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F109),0)&gt;0), MAX($G$1:G108)+1, ""))</f>
@@ -4727,51 +4742,48 @@
       </c>
     </row>
     <row r="110" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A110" s="30">
+      <c r="A110" s="36">
         <v>20</v>
       </c>
-      <c r="B110" s="31" t="s">
-        <v>366</v>
-      </c>
-      <c r="C110" s="32">
+      <c r="B110" s="37" t="s">
+        <v>330</v>
+      </c>
+      <c r="C110" s="38">
         <v>20</v>
       </c>
-      <c r="D110" s="30">
-        <v>2.4</v>
-      </c>
-      <c r="E110" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="F110" s="30" t="s">
-        <v>367</v>
-      </c>
-      <c r="G110" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F110),0)&gt;0), MAX($G$1:G109)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D110" s="36">
+        <v>3</v>
+      </c>
+      <c r="E110" s="37" t="s">
+        <v>304</v>
+      </c>
+      <c r="F110" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="G110" s="29"/>
       <c r="H110" s="21" t="b">
         <f>A110=C110</f>
         <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A111" s="30">
+      <c r="A111" s="26">
         <v>20</v>
       </c>
-      <c r="B111" s="31" t="s">
-        <v>103</v>
-      </c>
-      <c r="C111" s="32">
+      <c r="B111" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C111" s="28">
         <v>20</v>
       </c>
-      <c r="D111" s="30" t="s">
-        <v>214</v>
-      </c>
-      <c r="E111" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="F111" s="30" t="s">
-        <v>104</v>
+      <c r="D111" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E111" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="F111" s="26" t="s">
+        <v>301</v>
       </c>
       <c r="G111" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F111),0)&gt;0), MAX($G$1:G110)+1, ""))</f>
@@ -4783,23 +4795,23 @@
       </c>
     </row>
     <row r="112" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A112" s="26">
+      <c r="A112" s="30">
         <v>20</v>
       </c>
-      <c r="B112" s="27" t="s">
-        <v>339</v>
-      </c>
-      <c r="C112" s="28">
+      <c r="B112" s="31" t="s">
+        <v>366</v>
+      </c>
+      <c r="C112" s="32">
         <v>20</v>
       </c>
-      <c r="D112" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E112" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F112" s="26" t="s">
-        <v>344</v>
+      <c r="D112" s="30">
+        <v>2.4</v>
+      </c>
+      <c r="E112" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="F112" s="30" t="s">
+        <v>367</v>
       </c>
       <c r="G112" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F112),0)&gt;0), MAX($G$1:G111)+1, ""))</f>
@@ -4811,48 +4823,51 @@
       </c>
     </row>
     <row r="113" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A113" s="36">
+      <c r="A113" s="30">
         <v>20</v>
       </c>
-      <c r="B113" s="37" t="s">
-        <v>335</v>
-      </c>
-      <c r="C113" s="38">
+      <c r="B113" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="C113" s="32">
         <v>20</v>
       </c>
-      <c r="D113" s="36">
-        <v>3.2</v>
-      </c>
-      <c r="E113" s="37" t="s">
-        <v>336</v>
-      </c>
-      <c r="F113" s="36" t="s">
-        <v>332</v>
-      </c>
-      <c r="G113" s="29"/>
+      <c r="D113" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="E113" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="F113" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="G113" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F113),0)&gt;0), MAX($G$1:G112)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H113" s="21" t="b">
         <f>A113=C113</f>
         <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A114" s="30">
+      <c r="A114" s="26">
         <v>20</v>
       </c>
-      <c r="B114" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="C114" s="32">
+      <c r="B114" s="27" t="s">
+        <v>339</v>
+      </c>
+      <c r="C114" s="28">
         <v>20</v>
       </c>
-      <c r="D114" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E114" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F114" s="30" t="s">
-        <v>102</v>
+      <c r="D114" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E114" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F114" s="26" t="s">
+        <v>344</v>
       </c>
       <c r="G114" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F114),0)&gt;0), MAX($G$1:G113)+1, ""))</f>
@@ -4864,28 +4879,25 @@
       </c>
     </row>
     <row r="115" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A115" s="30">
+      <c r="A115" s="36">
         <v>20</v>
       </c>
-      <c r="B115" s="31" t="s">
-        <v>263</v>
-      </c>
-      <c r="C115" s="32">
+      <c r="B115" s="37" t="s">
+        <v>335</v>
+      </c>
+      <c r="C115" s="38">
         <v>20</v>
       </c>
-      <c r="D115" s="30">
-        <v>6.2</v>
-      </c>
-      <c r="E115" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F115" s="30" t="s">
-        <v>264</v>
-      </c>
-      <c r="G115" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F115),0)&gt;0), MAX($G$1:G114)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D115" s="36">
+        <v>3.2</v>
+      </c>
+      <c r="E115" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="F115" s="36" t="s">
+        <v>332</v>
+      </c>
+      <c r="G115" s="29"/>
       <c r="H115" s="21" t="b">
         <f>A115=C115</f>
         <v>1</v>
@@ -4896,19 +4908,19 @@
         <v>20</v>
       </c>
       <c r="B116" s="31" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C116" s="32">
         <v>20</v>
       </c>
       <c r="D116" s="30" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="E116" s="31" t="s">
-        <v>299</v>
+        <v>8</v>
       </c>
       <c r="F116" s="30" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G116" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F116),0)&gt;0), MAX($G$1:G115)+1, ""))</f>
@@ -4920,23 +4932,23 @@
       </c>
     </row>
     <row r="117" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A117" s="26">
+      <c r="A117" s="30">
         <v>20</v>
       </c>
-      <c r="B117" s="27" t="s">
-        <v>300</v>
-      </c>
-      <c r="C117" s="28">
+      <c r="B117" s="31" t="s">
+        <v>263</v>
+      </c>
+      <c r="C117" s="32">
         <v>20</v>
       </c>
-      <c r="D117" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E117" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="F117" s="26" t="s">
-        <v>301</v>
+      <c r="D117" s="30">
+        <v>6.2</v>
+      </c>
+      <c r="E117" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F117" s="30" t="s">
+        <v>264</v>
       </c>
       <c r="G117" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F117),0)&gt;0), MAX($G$1:G116)+1, ""))</f>
@@ -4952,19 +4964,19 @@
         <v>20</v>
       </c>
       <c r="B118" s="31" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C118" s="32">
         <v>20</v>
       </c>
       <c r="D118" s="30" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E118" s="31" t="s">
-        <v>8</v>
+        <v>299</v>
       </c>
       <c r="F118" s="30" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G118" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F118),0)&gt;0), MAX($G$1:G117)+1, ""))</f>
@@ -4980,22 +4992,22 @@
         <v>20</v>
       </c>
       <c r="B119" s="27" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C119" s="28">
         <v>20</v>
       </c>
       <c r="D119" s="26">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="E119" s="27" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="F119" s="26" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="G119" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F119),0)&gt;0), MAX($G$1:G117)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F119),0)&gt;0), MAX($G$1:G118)+1, ""))</f>
         <v/>
       </c>
       <c r="H119" s="21" t="b">
@@ -5004,23 +5016,23 @@
       </c>
     </row>
     <row r="120" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A120" s="26">
+      <c r="A120" s="30">
         <v>20</v>
       </c>
-      <c r="B120" s="27" t="s">
-        <v>355</v>
-      </c>
-      <c r="C120" s="28">
+      <c r="B120" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="C120" s="32">
         <v>20</v>
       </c>
-      <c r="D120" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E120" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F120" s="26" t="s">
-        <v>356</v>
+      <c r="D120" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="E120" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F120" s="30" t="s">
+        <v>96</v>
       </c>
       <c r="G120" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F120),0)&gt;0), MAX($G$1:G119)+1, ""))</f>
@@ -5032,26 +5044,26 @@
       </c>
     </row>
     <row r="121" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A121" s="30">
+      <c r="A121" s="26">
         <v>20</v>
       </c>
-      <c r="B121" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="C121" s="32">
+      <c r="B121" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="C121" s="28">
         <v>20</v>
       </c>
-      <c r="D121" s="30" t="s">
-        <v>218</v>
-      </c>
-      <c r="E121" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F121" s="30" t="s">
-        <v>92</v>
+      <c r="D121" s="26">
+        <v>3.9</v>
+      </c>
+      <c r="E121" s="27" t="s">
+        <v>309</v>
+      </c>
+      <c r="F121" s="26" t="s">
+        <v>311</v>
       </c>
       <c r="G121" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F121),0)&gt;0), MAX($G$1:G120)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F121),0)&gt;0), MAX($G$1:G119)+1, ""))</f>
         <v/>
       </c>
       <c r="H121" s="21" t="b">
@@ -5060,23 +5072,23 @@
       </c>
     </row>
     <row r="122" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A122" s="30">
+      <c r="A122" s="26">
         <v>20</v>
       </c>
-      <c r="B122" s="31" t="s">
-        <v>89</v>
-      </c>
-      <c r="C122" s="32">
+      <c r="B122" s="27" t="s">
+        <v>355</v>
+      </c>
+      <c r="C122" s="28">
         <v>20</v>
       </c>
-      <c r="D122" s="30" t="s">
-        <v>223</v>
-      </c>
-      <c r="E122" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F122" s="30" t="s">
-        <v>90</v>
+      <c r="D122" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E122" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F122" s="26" t="s">
+        <v>356</v>
       </c>
       <c r="G122" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F122),0)&gt;0), MAX($G$1:G121)+1, ""))</f>
@@ -5092,19 +5104,19 @@
         <v>20</v>
       </c>
       <c r="B123" s="31" t="s">
-        <v>290</v>
+        <v>91</v>
       </c>
       <c r="C123" s="32">
         <v>20</v>
       </c>
-      <c r="D123" s="30">
-        <v>1.8</v>
+      <c r="D123" s="30" t="s">
+        <v>218</v>
       </c>
       <c r="E123" s="31" t="s">
-        <v>291</v>
+        <v>8</v>
       </c>
       <c r="F123" s="30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G123" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F123),0)&gt;0), MAX($G$1:G122)+1, ""))</f>
@@ -5120,19 +5132,19 @@
         <v>20</v>
       </c>
       <c r="B124" s="31" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C124" s="32">
         <v>20</v>
       </c>
       <c r="D124" s="30" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E124" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F124" s="30" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G124" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F124),0)&gt;0), MAX($G$1:G123)+1, ""))</f>
@@ -5148,19 +5160,19 @@
         <v>20</v>
       </c>
       <c r="B125" s="31" t="s">
-        <v>85</v>
+        <v>290</v>
       </c>
       <c r="C125" s="32">
         <v>20</v>
       </c>
-      <c r="D125" s="30" t="s">
-        <v>220</v>
+      <c r="D125" s="30">
+        <v>1.8</v>
       </c>
       <c r="E125" s="31" t="s">
-        <v>8</v>
+        <v>291</v>
       </c>
       <c r="F125" s="30" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G125" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F125),0)&gt;0), MAX($G$1:G124)+1, ""))</f>
@@ -5176,19 +5188,19 @@
         <v>20</v>
       </c>
       <c r="B126" s="31" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C126" s="32">
         <v>20</v>
       </c>
       <c r="D126" s="30" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E126" s="31" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F126" s="30" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G126" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F126),0)&gt;0), MAX($G$1:G125)+1, ""))</f>
@@ -5204,19 +5216,19 @@
         <v>20</v>
       </c>
       <c r="B127" s="31" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C127" s="32">
         <v>20</v>
       </c>
       <c r="D127" s="30" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E127" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F127" s="30" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G127" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F127),0)&gt;0), MAX($G$1:G126)+1, ""))</f>
@@ -5232,19 +5244,19 @@
         <v>20</v>
       </c>
       <c r="B128" s="31" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C128" s="32">
         <v>20</v>
       </c>
       <c r="D128" s="30" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E128" s="31" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="F128" s="30" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G128" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F128),0)&gt;0), MAX($G$1:G127)+1, ""))</f>
@@ -5256,23 +5268,23 @@
       </c>
     </row>
     <row r="129" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A129" s="26">
-        <v>25</v>
-      </c>
-      <c r="B129" s="27" t="s">
-        <v>178</v>
-      </c>
-      <c r="C129" s="28">
-        <v>25</v>
-      </c>
-      <c r="D129" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="E129" s="27" t="s">
+      <c r="A129" s="30">
+        <v>20</v>
+      </c>
+      <c r="B129" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="C129" s="32">
+        <v>20</v>
+      </c>
+      <c r="D129" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="E129" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F129" s="26" t="s">
-        <v>179</v>
+      <c r="F129" s="30" t="s">
+        <v>79</v>
       </c>
       <c r="G129" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F129),0)&gt;0), MAX($G$1:G128)+1, ""))</f>
@@ -5284,23 +5296,23 @@
       </c>
     </row>
     <row r="130" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A130" s="26">
-        <v>25</v>
-      </c>
-      <c r="B130" s="27" t="s">
-        <v>176</v>
-      </c>
-      <c r="C130" s="28">
-        <v>25</v>
-      </c>
-      <c r="D130" s="26" t="s">
-        <v>237</v>
-      </c>
-      <c r="E130" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="F130" s="26" t="s">
-        <v>177</v>
+      <c r="A130" s="30">
+        <v>20</v>
+      </c>
+      <c r="B130" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="C130" s="32">
+        <v>20</v>
+      </c>
+      <c r="D130" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="E130" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F130" s="30" t="s">
+        <v>77</v>
       </c>
       <c r="G130" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F130),0)&gt;0), MAX($G$1:G129)+1, ""))</f>
@@ -5316,19 +5328,19 @@
         <v>25</v>
       </c>
       <c r="B131" s="27" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C131" s="28">
         <v>25</v>
       </c>
       <c r="D131" s="26" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="E131" s="27" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="F131" s="26" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="G131" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F131),0)&gt;0), MAX($G$1:G130)+1, ""))</f>
@@ -5344,19 +5356,19 @@
         <v>25</v>
       </c>
       <c r="B132" s="27" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C132" s="28">
         <v>25</v>
       </c>
       <c r="D132" s="26" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="E132" s="27" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F132" s="26" t="s">
-        <v>324</v>
+        <v>177</v>
       </c>
       <c r="G132" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B132),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E132),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F132),0)&gt;0), MAX($G$1:G131)+1, ""))</f>
@@ -5372,19 +5384,19 @@
         <v>25</v>
       </c>
       <c r="B133" s="27" t="s">
-        <v>359</v>
+        <v>174</v>
       </c>
       <c r="C133" s="28">
         <v>25</v>
       </c>
-      <c r="D133" s="26">
-        <v>3</v>
+      <c r="D133" s="26" t="s">
+        <v>231</v>
       </c>
       <c r="E133" s="27" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F133" s="26" t="s">
-        <v>360</v>
+        <v>175</v>
       </c>
       <c r="G133" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F133),0)&gt;0), MAX($G$1:G132)+1, ""))</f>
@@ -5400,19 +5412,19 @@
         <v>25</v>
       </c>
       <c r="B134" s="27" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C134" s="28">
         <v>25</v>
       </c>
-      <c r="D134" s="26">
-        <v>2.7</v>
+      <c r="D134" s="26" t="s">
+        <v>224</v>
       </c>
       <c r="E134" s="27" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F134" s="26" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="G134" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F134),0)&gt;0), MAX($G$1:G133)+1, ""))</f>
@@ -5424,23 +5436,23 @@
       </c>
     </row>
     <row r="135" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A135" s="30">
+      <c r="A135" s="26">
         <v>25</v>
       </c>
-      <c r="B135" s="31" t="s">
-        <v>284</v>
-      </c>
-      <c r="C135" s="32">
+      <c r="B135" s="27" t="s">
+        <v>359</v>
+      </c>
+      <c r="C135" s="28">
         <v>25</v>
       </c>
-      <c r="D135" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E135" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F135" s="30" t="s">
-        <v>102</v>
+      <c r="D135" s="26">
+        <v>3</v>
+      </c>
+      <c r="E135" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F135" s="26" t="s">
+        <v>360</v>
       </c>
       <c r="G135" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F135),0)&gt;0), MAX($G$1:G134)+1, ""))</f>
@@ -5452,23 +5464,23 @@
       </c>
     </row>
     <row r="136" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A136" s="30">
+      <c r="A136" s="26">
         <v>25</v>
       </c>
-      <c r="B136" s="31" t="s">
-        <v>282</v>
-      </c>
-      <c r="C136" s="32">
+      <c r="B136" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="C136" s="28">
         <v>25</v>
       </c>
-      <c r="D136" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E136" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F136" s="30" t="s">
-        <v>102</v>
+      <c r="D136" s="26">
+        <v>2.7</v>
+      </c>
+      <c r="E136" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F136" s="26" t="s">
+        <v>338</v>
       </c>
       <c r="G136" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F136),0)&gt;0), MAX($G$1:G135)+1, ""))</f>
@@ -5480,23 +5492,23 @@
       </c>
     </row>
     <row r="137" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A137" s="26">
+      <c r="A137" s="30">
         <v>25</v>
       </c>
-      <c r="B137" s="27" t="s">
-        <v>170</v>
-      </c>
-      <c r="C137" s="28">
+      <c r="B137" s="31" t="s">
+        <v>284</v>
+      </c>
+      <c r="C137" s="32">
         <v>25</v>
       </c>
-      <c r="D137" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="E137" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="F137" s="26" t="s">
-        <v>171</v>
+      <c r="D137" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E137" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="F137" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G137" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F137),0)&gt;0), MAX($G$1:G136)+1, ""))</f>
@@ -5508,23 +5520,23 @@
       </c>
     </row>
     <row r="138" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A138" s="26">
+      <c r="A138" s="30">
         <v>25</v>
       </c>
-      <c r="B138" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="C138" s="28">
+      <c r="B138" s="31" t="s">
+        <v>282</v>
+      </c>
+      <c r="C138" s="32">
         <v>25</v>
       </c>
-      <c r="D138" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="E138" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F138" s="26" t="s">
-        <v>169</v>
+      <c r="D138" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E138" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="F138" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G138" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F138),0)&gt;0), MAX($G$1:G137)+1, ""))</f>
@@ -5540,19 +5552,19 @@
         <v>25</v>
       </c>
       <c r="B139" s="27" t="s">
-        <v>357</v>
+        <v>170</v>
       </c>
       <c r="C139" s="28">
         <v>25</v>
       </c>
-      <c r="D139" s="26">
-        <v>3.4</v>
+      <c r="D139" s="26" t="s">
+        <v>234</v>
       </c>
       <c r="E139" s="27" t="s">
-        <v>8</v>
+        <v>245</v>
       </c>
       <c r="F139" s="26" t="s">
-        <v>358</v>
+        <v>171</v>
       </c>
       <c r="G139" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F139),0)&gt;0), MAX($G$1:G138)+1, ""))</f>
@@ -5564,23 +5576,23 @@
       </c>
     </row>
     <row r="140" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A140" s="30">
+      <c r="A140" s="26">
         <v>25</v>
       </c>
-      <c r="B140" s="31" t="s">
-        <v>278</v>
-      </c>
-      <c r="C140" s="32">
+      <c r="B140" s="27" t="s">
+        <v>168</v>
+      </c>
+      <c r="C140" s="28">
         <v>25</v>
       </c>
-      <c r="D140" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E140" s="31" t="s">
+      <c r="D140" s="26" t="s">
+        <v>217</v>
+      </c>
+      <c r="E140" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F140" s="30" t="s">
-        <v>102</v>
+      <c r="F140" s="26" t="s">
+        <v>169</v>
       </c>
       <c r="G140" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F140),0)&gt;0), MAX($G$1:G139)+1, ""))</f>
@@ -5596,19 +5608,19 @@
         <v>25</v>
       </c>
       <c r="B141" s="27" t="s">
-        <v>166</v>
+        <v>357</v>
       </c>
       <c r="C141" s="28">
         <v>25</v>
       </c>
-      <c r="D141" s="26" t="s">
-        <v>221</v>
+      <c r="D141" s="26">
+        <v>3.4</v>
       </c>
       <c r="E141" s="27" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="F141" s="26" t="s">
-        <v>167</v>
+        <v>358</v>
       </c>
       <c r="G141" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F141),0)&gt;0), MAX($G$1:G140)+1, ""))</f>
@@ -5620,23 +5632,23 @@
       </c>
     </row>
     <row r="142" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A142" s="26">
+      <c r="A142" s="30">
         <v>25</v>
       </c>
-      <c r="B142" s="27" t="s">
-        <v>164</v>
-      </c>
-      <c r="C142" s="28">
+      <c r="B142" s="31" t="s">
+        <v>278</v>
+      </c>
+      <c r="C142" s="32">
         <v>25</v>
       </c>
-      <c r="D142" s="26" t="s">
-        <v>229</v>
-      </c>
-      <c r="E142" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="F142" s="26" t="s">
-        <v>165</v>
+      <c r="D142" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E142" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F142" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G142" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F142),0)&gt;0), MAX($G$1:G141)+1, ""))</f>
@@ -5652,19 +5664,19 @@
         <v>25</v>
       </c>
       <c r="B143" s="27" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C143" s="28">
         <v>25</v>
       </c>
       <c r="D143" s="26" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="E143" s="27" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="F143" s="26" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="G143" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F143),0)&gt;0), MAX($G$1:G142)+1, ""))</f>
@@ -5680,19 +5692,19 @@
         <v>25</v>
       </c>
       <c r="B144" s="27" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C144" s="28">
         <v>25</v>
       </c>
       <c r="D144" s="26" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="E144" s="27" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="F144" s="26" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G144" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F144),0)&gt;0), MAX($G$1:G143)+1, ""))</f>
@@ -5708,19 +5720,19 @@
         <v>25</v>
       </c>
       <c r="B145" s="27" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C145" s="28">
         <v>25</v>
       </c>
       <c r="D145" s="26" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E145" s="27" t="s">
         <v>81</v>
       </c>
       <c r="F145" s="26" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="G145" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B145),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E145),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F145),0)&gt;0), MAX($G$1:G144)+1, ""))</f>
@@ -5736,19 +5748,19 @@
         <v>25</v>
       </c>
       <c r="B146" s="27" t="s">
-        <v>342</v>
+        <v>160</v>
       </c>
       <c r="C146" s="28">
         <v>25</v>
       </c>
-      <c r="D146" s="26">
-        <v>3.4</v>
+      <c r="D146" s="26" t="s">
+        <v>236</v>
       </c>
       <c r="E146" s="27" t="s">
         <v>81</v>
       </c>
       <c r="F146" s="26" t="s">
-        <v>343</v>
+        <v>161</v>
       </c>
       <c r="G146" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F146),0)&gt;0), MAX($G$1:G145)+1, ""))</f>
@@ -5764,19 +5776,19 @@
         <v>25</v>
       </c>
       <c r="B147" s="27" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C147" s="28">
         <v>25</v>
       </c>
       <c r="D147" s="26" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E147" s="27" t="s">
         <v>81</v>
       </c>
       <c r="F147" s="26" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G147" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F147),0)&gt;0), MAX($G$1:G146)+1, ""))</f>
@@ -5792,19 +5804,19 @@
         <v>25</v>
       </c>
       <c r="B148" s="27" t="s">
-        <v>154</v>
+        <v>342</v>
       </c>
       <c r="C148" s="28">
         <v>25</v>
       </c>
-      <c r="D148" s="26" t="s">
-        <v>224</v>
+      <c r="D148" s="26">
+        <v>3.4</v>
       </c>
       <c r="E148" s="27" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="F148" s="26" t="s">
-        <v>155</v>
+        <v>343</v>
       </c>
       <c r="G148" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F148),0)&gt;0), MAX($G$1:G147)+1, ""))</f>
@@ -5820,19 +5832,19 @@
         <v>25</v>
       </c>
       <c r="B149" s="27" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C149" s="28">
         <v>25</v>
       </c>
       <c r="D149" s="26" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E149" s="27" t="s">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="F149" s="26" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G149" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B149),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E149),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F149),0)&gt;0), MAX($G$1:G148)+1, ""))</f>
@@ -5848,19 +5860,19 @@
         <v>25</v>
       </c>
       <c r="B150" s="27" t="s">
-        <v>247</v>
+        <v>154</v>
       </c>
       <c r="C150" s="28">
         <v>25</v>
       </c>
-      <c r="D150" s="39" t="s">
-        <v>229</v>
+      <c r="D150" s="26" t="s">
+        <v>224</v>
       </c>
       <c r="E150" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F150" s="26" t="s">
-        <v>248</v>
+        <v>155</v>
       </c>
       <c r="G150" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B150),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E150),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F150),0)&gt;0), MAX($G$1:G149)+1, ""))</f>
@@ -5876,19 +5888,19 @@
         <v>25</v>
       </c>
       <c r="B151" s="27" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C151" s="28">
         <v>25</v>
       </c>
       <c r="D151" s="26" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="E151" s="27" t="s">
         <v>131</v>
       </c>
       <c r="F151" s="26" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G151" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B151),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E151),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F151),0)&gt;0), MAX($G$1:G150)+1, ""))</f>
@@ -5900,23 +5912,23 @@
       </c>
     </row>
     <row r="152" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A152" s="30">
+      <c r="A152" s="26">
         <v>25</v>
       </c>
-      <c r="B152" s="31" t="s">
-        <v>288</v>
-      </c>
-      <c r="C152" s="32">
+      <c r="B152" s="27" t="s">
+        <v>247</v>
+      </c>
+      <c r="C152" s="28">
         <v>25</v>
       </c>
-      <c r="D152" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E152" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F152" s="30" t="s">
-        <v>102</v>
+      <c r="D152" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="E152" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F152" s="26" t="s">
+        <v>248</v>
       </c>
       <c r="G152" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B152),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E152),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F152),0)&gt;0), MAX($G$1:G151)+1, ""))</f>
@@ -5928,23 +5940,23 @@
       </c>
     </row>
     <row r="153" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A153" s="30">
+      <c r="A153" s="26">
         <v>25</v>
       </c>
-      <c r="B153" s="31" t="s">
-        <v>286</v>
-      </c>
-      <c r="C153" s="32">
+      <c r="B153" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C153" s="28">
         <v>25</v>
       </c>
-      <c r="D153" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E153" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F153" s="30" t="s">
-        <v>102</v>
+      <c r="D153" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="E153" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="F153" s="26" t="s">
+        <v>151</v>
       </c>
       <c r="G153" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B153),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E153),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F153),0)&gt;0), MAX($G$1:G152)+1, ""))</f>
@@ -5960,7 +5972,7 @@
         <v>25</v>
       </c>
       <c r="B154" s="31" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C154" s="32">
         <v>25</v>
@@ -5984,23 +5996,23 @@
       </c>
     </row>
     <row r="155" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A155" s="26">
+      <c r="A155" s="30">
         <v>25</v>
       </c>
-      <c r="B155" s="27" t="s">
-        <v>252</v>
-      </c>
-      <c r="C155" s="28">
+      <c r="B155" s="31" t="s">
+        <v>286</v>
+      </c>
+      <c r="C155" s="32">
         <v>25</v>
       </c>
-      <c r="D155" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E155" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="F155" s="26" t="s">
-        <v>253</v>
+      <c r="D155" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E155" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="F155" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G155" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F155),0)&gt;0), MAX($G$1:G154)+1, ""))</f>
@@ -6016,7 +6028,7 @@
         <v>25</v>
       </c>
       <c r="B156" s="31" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C156" s="32">
         <v>25</v>
@@ -6044,22 +6056,22 @@
         <v>25</v>
       </c>
       <c r="B157" s="27" t="s">
-        <v>148</v>
+        <v>252</v>
       </c>
       <c r="C157" s="28">
         <v>25</v>
       </c>
-      <c r="D157" s="26" t="s">
-        <v>226</v>
+      <c r="D157" s="26">
+        <v>2.5</v>
       </c>
       <c r="E157" s="27" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="F157" s="26" t="s">
-        <v>149</v>
+        <v>253</v>
       </c>
       <c r="G157" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F157),0)&gt;0), MAX($G$1:G155)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F157),0)&gt;0), MAX($G$1:G156)+1, ""))</f>
         <v/>
       </c>
       <c r="H157" s="21" t="b">
@@ -6069,22 +6081,22 @@
     </row>
     <row r="158" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A158" s="30">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B158" s="31" t="s">
-        <v>192</v>
+        <v>285</v>
       </c>
       <c r="C158" s="32">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D158" s="30" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="E158" s="31" t="s">
-        <v>131</v>
+        <v>283</v>
       </c>
       <c r="F158" s="30" t="s">
-        <v>193</v>
+        <v>102</v>
       </c>
       <c r="G158" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B158),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E158),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F158),0)&gt;0), MAX($G$1:G157)+1, ""))</f>
@@ -6096,26 +6108,26 @@
       </c>
     </row>
     <row r="159" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A159" s="30">
-        <v>30</v>
-      </c>
-      <c r="B159" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="C159" s="32">
-        <v>30</v>
-      </c>
-      <c r="D159" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="E159" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="F159" s="30" t="s">
-        <v>190</v>
+      <c r="A159" s="26">
+        <v>25</v>
+      </c>
+      <c r="B159" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="C159" s="28">
+        <v>25</v>
+      </c>
+      <c r="D159" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="E159" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F159" s="26" t="s">
+        <v>149</v>
       </c>
       <c r="G159" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F159),0)&gt;0), MAX($G$1:G158)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F159),0)&gt;0), MAX($G$1:G157)+1, ""))</f>
         <v/>
       </c>
       <c r="H159" s="21" t="b">
@@ -6128,19 +6140,19 @@
         <v>30</v>
       </c>
       <c r="B160" s="31" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C160" s="32">
         <v>30</v>
       </c>
       <c r="D160" s="30" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="E160" s="31" t="s">
         <v>131</v>
       </c>
       <c r="F160" s="30" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="G160" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B160),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E160),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F160),0)&gt;0), MAX($G$1:G159)+1, ""))</f>
@@ -6156,19 +6168,19 @@
         <v>30</v>
       </c>
       <c r="B161" s="31" t="s">
-        <v>246</v>
+        <v>191</v>
       </c>
       <c r="C161" s="32">
         <v>30</v>
       </c>
       <c r="D161" s="30" t="s">
-        <v>217</v>
+        <v>241</v>
       </c>
       <c r="E161" s="31" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F161" s="30" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G161" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B161),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E161),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F161),0)&gt;0), MAX($G$1:G160)+1, ""))</f>
@@ -6184,19 +6196,19 @@
         <v>30</v>
       </c>
       <c r="B162" s="31" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C162" s="32">
         <v>30</v>
       </c>
       <c r="D162" s="30" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="E162" s="31" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F162" s="30" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G162" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B162),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E162),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F162),0)&gt;0), MAX($G$1:G161)+1, ""))</f>
@@ -6212,19 +6224,19 @@
         <v>30</v>
       </c>
       <c r="B163" s="31" t="s">
-        <v>184</v>
+        <v>246</v>
       </c>
       <c r="C163" s="32">
         <v>30</v>
       </c>
       <c r="D163" s="30" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="E163" s="31" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F163" s="30" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G163" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B163),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E163),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F163),0)&gt;0), MAX($G$1:G162)+1, ""))</f>
@@ -6236,23 +6248,23 @@
       </c>
     </row>
     <row r="164" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A164" s="26">
+      <c r="A164" s="30">
         <v>30</v>
       </c>
-      <c r="B164" s="27" t="s">
-        <v>377</v>
-      </c>
-      <c r="C164" s="28">
+      <c r="B164" s="31" t="s">
+        <v>186</v>
+      </c>
+      <c r="C164" s="32">
         <v>30</v>
       </c>
-      <c r="D164" s="26">
-        <v>5</v>
-      </c>
-      <c r="E164" s="27" t="s">
-        <v>378</v>
-      </c>
-      <c r="F164" s="26" t="s">
-        <v>25</v>
+      <c r="D164" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="E164" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F164" s="30" t="s">
+        <v>187</v>
       </c>
       <c r="G164" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B164),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E164),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F164),0)&gt;0), MAX($G$1:G163)+1, ""))</f>
@@ -6268,19 +6280,19 @@
         <v>30</v>
       </c>
       <c r="B165" s="31" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C165" s="32">
         <v>30</v>
       </c>
       <c r="D165" s="30" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="E165" s="31" t="s">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="F165" s="30" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G165" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B165),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E165),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F165),0)&gt;0), MAX($G$1:G164)+1, ""))</f>
@@ -6292,23 +6304,23 @@
       </c>
     </row>
     <row r="166" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A166" s="30">
+      <c r="A166" s="26">
         <v>30</v>
       </c>
-      <c r="B166" s="31" t="s">
-        <v>337</v>
-      </c>
-      <c r="C166" s="32">
+      <c r="B166" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="C166" s="28">
         <v>30</v>
       </c>
-      <c r="D166" s="30">
-        <v>2.9</v>
-      </c>
-      <c r="E166" s="31" t="s">
-        <v>81</v>
-      </c>
-      <c r="F166" s="30" t="s">
-        <v>338</v>
+      <c r="D166" s="26">
+        <v>5</v>
+      </c>
+      <c r="E166" s="27" t="s">
+        <v>378</v>
+      </c>
+      <c r="F166" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="G166" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B166),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E166),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F166),0)&gt;0), MAX($G$1:G165)+1, ""))</f>
@@ -6324,22 +6336,22 @@
         <v>30</v>
       </c>
       <c r="B167" s="31" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C167" s="32">
         <v>30</v>
       </c>
       <c r="D167" s="30" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E167" s="31" t="s">
         <v>131</v>
       </c>
       <c r="F167" s="30" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G167" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B167),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E167),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F167),0)&gt;0), MAX($G$1:G165)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B167),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E167),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F167),0)&gt;0), MAX($G$1:G166)+1, ""))</f>
         <v/>
       </c>
       <c r="H167" s="21" t="b">
@@ -6348,23 +6360,23 @@
       </c>
     </row>
     <row r="168" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A168" s="26">
-        <v>40</v>
-      </c>
-      <c r="B168" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="C168" s="28">
-        <v>40</v>
-      </c>
-      <c r="D168" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="E168" s="27" t="s">
-        <v>198</v>
-      </c>
-      <c r="F168" s="26" t="s">
-        <v>199</v>
+      <c r="A168" s="30">
+        <v>30</v>
+      </c>
+      <c r="B168" s="31" t="s">
+        <v>337</v>
+      </c>
+      <c r="C168" s="32">
+        <v>30</v>
+      </c>
+      <c r="D168" s="30">
+        <v>2.9</v>
+      </c>
+      <c r="E168" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="F168" s="30" t="s">
+        <v>338</v>
       </c>
       <c r="G168" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B168),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E168),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F168),0)&gt;0), MAX($G$1:G167)+1, ""))</f>
@@ -6376,26 +6388,26 @@
       </c>
     </row>
     <row r="169" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A169" s="26">
-        <v>40</v>
-      </c>
-      <c r="B169" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="C169" s="28">
-        <v>40</v>
-      </c>
-      <c r="D169" s="26" t="s">
-        <v>242</v>
-      </c>
-      <c r="E169" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="F169" s="26" t="s">
-        <v>196</v>
+      <c r="A169" s="30">
+        <v>30</v>
+      </c>
+      <c r="B169" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="C169" s="32">
+        <v>30</v>
+      </c>
+      <c r="D169" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="E169" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="F169" s="30" t="s">
+        <v>181</v>
       </c>
       <c r="G169" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B169),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E169),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F169),0)&gt;0), MAX($G$1:G168)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B169),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E169),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F169),0)&gt;0), MAX($G$1:G167)+1, ""))</f>
         <v/>
       </c>
       <c r="H169" s="21" t="b">
@@ -6408,19 +6420,19 @@
         <v>40</v>
       </c>
       <c r="B170" s="27" t="s">
-        <v>249</v>
+        <v>197</v>
       </c>
       <c r="C170" s="28">
         <v>40</v>
       </c>
-      <c r="D170" s="26">
-        <v>8.3000000000000007</v>
+      <c r="D170" s="26" t="s">
+        <v>243</v>
       </c>
       <c r="E170" s="27" t="s">
-        <v>250</v>
+        <v>198</v>
       </c>
       <c r="F170" s="26" t="s">
-        <v>251</v>
+        <v>199</v>
       </c>
       <c r="G170" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B170),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E170),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F170),0)&gt;0), MAX($G$1:G169)+1, ""))</f>
@@ -6433,22 +6445,22 @@
     </row>
     <row r="171" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A171" s="26">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B171" s="27" t="s">
-        <v>294</v>
+        <v>194</v>
       </c>
       <c r="C171" s="28">
-        <v>45</v>
-      </c>
-      <c r="D171" s="26">
-        <v>10.199999999999999</v>
+        <v>40</v>
+      </c>
+      <c r="D171" s="26" t="s">
+        <v>242</v>
       </c>
       <c r="E171" s="27" t="s">
-        <v>295</v>
+        <v>195</v>
       </c>
       <c r="F171" s="26" t="s">
-        <v>296</v>
+        <v>196</v>
       </c>
       <c r="G171" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B171),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E171),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F171),0)&gt;0), MAX($G$1:G170)+1, ""))</f>
@@ -6460,16 +6472,60 @@
       </c>
     </row>
     <row r="172" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A172" s="1"/>
-      <c r="C172" s="1"/>
-      <c r="D172" s="1"/>
-      <c r="F172" s="1"/>
+      <c r="A172" s="26">
+        <v>40</v>
+      </c>
+      <c r="B172" s="27" t="s">
+        <v>249</v>
+      </c>
+      <c r="C172" s="28">
+        <v>40</v>
+      </c>
+      <c r="D172" s="26">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E172" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="F172" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="G172" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B172),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E172),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F172),0)&gt;0), MAX($G$1:G171)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H172" s="21" t="b">
+        <f>A172=C172</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="173" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A173" s="1"/>
-      <c r="C173" s="1"/>
-      <c r="D173" s="1"/>
-      <c r="F173" s="1"/>
+      <c r="A173" s="26">
+        <v>45</v>
+      </c>
+      <c r="B173" s="27" t="s">
+        <v>294</v>
+      </c>
+      <c r="C173" s="28">
+        <v>45</v>
+      </c>
+      <c r="D173" s="26">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E173" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="F173" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="G173" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B173),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E173),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F173),0)&gt;0), MAX($G$1:G172)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H173" s="21" t="b">
+        <f>A173=C173</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="174" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
@@ -11687,10 +11743,10 @@
       <sortCondition ref="D2:D171"/>
     </sortState>
   </autoFilter>
-  <sortState ref="A2:H171">
-    <sortCondition ref="A2:A171"/>
-    <sortCondition ref="B2:B171"/>
-    <sortCondition ref="D2:D171"/>
+  <sortState ref="A2:H173">
+    <sortCondition ref="A2:A173"/>
+    <sortCondition ref="B2:B173"/>
+    <sortCondition ref="D2:D173"/>
   </sortState>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="391">
   <si>
     <t>Grupo</t>
   </si>
@@ -1195,6 +1195,9 @@
   </si>
   <si>
     <t>CORONEL VALENCIA</t>
+  </si>
+  <si>
+    <t>MOEMA</t>
   </si>
 </sst>
 </file>
@@ -3556,19 +3559,19 @@
         <v>17</v>
       </c>
       <c r="B67" s="27" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="C67" s="28">
         <v>17</v>
       </c>
       <c r="D67" s="26">
-        <v>1.2</v>
-      </c>
-      <c r="E67" s="27" t="s">
+        <v>1.4</v>
+      </c>
+      <c r="E67" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F67" s="26" t="s">
-        <v>380</v>
+        <v>354</v>
       </c>
       <c r="G67" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F67),0)&gt;0), MAX($G$1:G66)+1, ""))</f>
@@ -3580,23 +3583,23 @@
       </c>
     </row>
     <row r="68" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A68" s="33">
+      <c r="A68" s="26">
         <v>17</v>
       </c>
-      <c r="B68" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="C68" s="35">
+      <c r="B68" s="27" t="s">
+        <v>379</v>
+      </c>
+      <c r="C68" s="28">
         <v>17</v>
       </c>
-      <c r="D68" s="33" t="s">
-        <v>211</v>
-      </c>
-      <c r="E68" s="34" t="s">
+      <c r="D68" s="26">
+        <v>1.2</v>
+      </c>
+      <c r="E68" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F68" s="33" t="s">
-        <v>49</v>
+      <c r="F68" s="26" t="s">
+        <v>380</v>
       </c>
       <c r="G68" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F68),0)&gt;0), MAX($G$1:G67)+1, ""))</f>
@@ -3608,23 +3611,23 @@
       </c>
     </row>
     <row r="69" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A69" s="36">
+      <c r="A69" s="33">
         <v>17</v>
       </c>
-      <c r="B69" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="C69" s="38">
+      <c r="B69" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="C69" s="35">
         <v>17</v>
       </c>
-      <c r="D69" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="E69" s="37" t="s">
+      <c r="D69" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="E69" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F69" s="36" t="s">
-        <v>98</v>
+      <c r="F69" s="33" t="s">
+        <v>49</v>
       </c>
       <c r="G69" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F69),0)&gt;0), MAX($G$1:G68)+1, ""))</f>
@@ -3636,23 +3639,23 @@
       </c>
     </row>
     <row r="70" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A70" s="26">
+      <c r="A70" s="36">
         <v>17</v>
       </c>
-      <c r="B70" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="C70" s="28">
+      <c r="B70" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="C70" s="38">
         <v>17</v>
       </c>
-      <c r="D70" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="E70" s="27" t="s">
+      <c r="D70" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E70" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F70" s="26" t="s">
-        <v>43</v>
+      <c r="F70" s="36" t="s">
+        <v>98</v>
       </c>
       <c r="G70" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F70),0)&gt;0), MAX($G$1:G69)+1, ""))</f>
@@ -3664,23 +3667,23 @@
       </c>
     </row>
     <row r="71" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A71" s="36">
+      <c r="A71" s="26">
         <v>17</v>
       </c>
-      <c r="B71" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="C71" s="38">
+      <c r="B71" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C71" s="28">
         <v>17</v>
       </c>
-      <c r="D71" s="36" t="s">
-        <v>217</v>
-      </c>
-      <c r="E71" s="37" t="s">
+      <c r="D71" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="E71" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F71" s="36" t="s">
-        <v>94</v>
+      <c r="F71" s="26" t="s">
+        <v>43</v>
       </c>
       <c r="G71" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F71),0)&gt;0), MAX($G$1:G70)+1, ""))</f>
@@ -3692,28 +3695,30 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A72" s="33">
+      <c r="A72" s="36">
         <v>17</v>
       </c>
-      <c r="B72" s="34" t="s">
-        <v>327</v>
-      </c>
-      <c r="C72" s="35">
+      <c r="B72" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="C72" s="38">
         <v>17</v>
       </c>
-      <c r="D72" s="33">
-        <v>1.9</v>
-      </c>
-      <c r="E72" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F72" s="33" t="s">
-        <v>329</v>
-      </c>
-      <c r="G72" s="29" t="s">
-        <v>326</v>
+      <c r="D72" s="36" t="s">
+        <v>217</v>
+      </c>
+      <c r="E72" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F72" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="G72" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F72),0)&gt;0), MAX($G$1:G71)+1, ""))</f>
+        <v/>
       </c>
       <c r="H72" s="21" t="b">
+        <f>A72=C72</f>
         <v>1</v>
       </c>
     </row>
@@ -3722,7 +3727,7 @@
         <v>17</v>
       </c>
       <c r="B73" s="34" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C73" s="35">
         <v>17</v>
@@ -3748,7 +3753,7 @@
         <v>17</v>
       </c>
       <c r="B74" s="34" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C74" s="35">
         <v>17</v>
@@ -3774,47 +3779,45 @@
         <v>17</v>
       </c>
       <c r="B75" s="34" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="C75" s="35">
         <v>17</v>
       </c>
-      <c r="D75" s="33" t="s">
+      <c r="D75" s="33">
+        <v>1.9</v>
+      </c>
+      <c r="E75" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="F75" s="33" t="s">
+        <v>329</v>
+      </c>
+      <c r="G75" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="H75" s="21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A76" s="33">
+        <v>17</v>
+      </c>
+      <c r="B76" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="C76" s="35">
+        <v>17</v>
+      </c>
+      <c r="D76" s="33" t="s">
         <v>214</v>
       </c>
-      <c r="E75" s="34" t="s">
+      <c r="E76" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F75" s="33" t="s">
+      <c r="F76" s="33" t="s">
         <v>37</v>
-      </c>
-      <c r="G75" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F75),0)&gt;0), MAX($G$1:G74)+1, ""))</f>
-        <v/>
-      </c>
-      <c r="H75" s="21" t="b">
-        <f>A75=C75</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A76" s="36">
-        <v>17</v>
-      </c>
-      <c r="B76" s="37" t="s">
-        <v>83</v>
-      </c>
-      <c r="C76" s="38">
-        <v>17</v>
-      </c>
-      <c r="D76" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="E76" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F76" s="36" t="s">
-        <v>84</v>
       </c>
       <c r="G76" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F76),0)&gt;0), MAX($G$1:G75)+1, ""))</f>
@@ -3826,23 +3829,23 @@
       </c>
     </row>
     <row r="77" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A77" s="33">
+      <c r="A77" s="36">
         <v>17</v>
       </c>
-      <c r="B77" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="35">
+      <c r="B77" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="C77" s="38">
         <v>17</v>
       </c>
-      <c r="D77" s="33" t="s">
-        <v>208</v>
-      </c>
-      <c r="E77" s="34" t="s">
+      <c r="D77" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E77" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F77" s="33" t="s">
-        <v>32</v>
+      <c r="F77" s="36" t="s">
+        <v>84</v>
       </c>
       <c r="G77" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F77),0)&gt;0), MAX($G$1:G76)+1, ""))</f>
@@ -3858,52 +3861,52 @@
         <v>17</v>
       </c>
       <c r="B78" s="34" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C78" s="35">
         <v>17</v>
       </c>
       <c r="D78" s="33" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E78" s="34" t="s">
         <v>8</v>
       </c>
       <c r="F78" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="G78" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F78),0)&gt;0), MAX($G$1:G77)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H78" s="21" t="b">
+        <f>A78=C78</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A79" s="33">
+        <v>17</v>
+      </c>
+      <c r="B79" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="C79" s="35">
+        <v>17</v>
+      </c>
+      <c r="D79" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="E79" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F79" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="G78" s="29" t="s">
+      <c r="G79" s="29" t="s">
         <v>326</v>
       </c>
-      <c r="H78" s="21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A79" s="30">
-        <v>20</v>
-      </c>
-      <c r="B79" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="C79" s="32">
-        <v>20</v>
-      </c>
-      <c r="D79" s="30" t="s">
-        <v>206</v>
-      </c>
-      <c r="E79" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F79" s="30" t="s">
-        <v>147</v>
-      </c>
-      <c r="G79" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F79),0)&gt;0), MAX($G$1:G75)+1, ""))</f>
-        <v/>
-      </c>
       <c r="H79" s="21" t="b">
-        <f>A79=C79</f>
         <v>1</v>
       </c>
     </row>
@@ -3912,22 +3915,22 @@
         <v>20</v>
       </c>
       <c r="B80" s="31" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C80" s="32">
         <v>20</v>
       </c>
       <c r="D80" s="30" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E80" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F80" s="30" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G80" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F80),0)&gt;0), MAX($G$1:G79)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F80),0)&gt;0), MAX($G$1:G76)+1, ""))</f>
         <v/>
       </c>
       <c r="H80" s="21" t="b">
@@ -3936,23 +3939,23 @@
       </c>
     </row>
     <row r="81" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A81" s="26">
+      <c r="A81" s="30">
         <v>20</v>
       </c>
-      <c r="B81" s="27" t="s">
-        <v>386</v>
-      </c>
-      <c r="C81" s="28">
+      <c r="B81" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="C81" s="32">
         <v>20</v>
       </c>
-      <c r="D81" s="26">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="E81" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="F81" s="26" t="s">
-        <v>387</v>
+      <c r="D81" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="E81" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F81" s="30" t="s">
+        <v>145</v>
       </c>
       <c r="G81" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F81),0)&gt;0), MAX($G$1:G80)+1, ""))</f>
@@ -3964,26 +3967,26 @@
       </c>
     </row>
     <row r="82" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A82" s="30">
+      <c r="A82" s="26">
         <v>20</v>
       </c>
-      <c r="B82" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="C82" s="32">
+      <c r="B82" s="27" t="s">
+        <v>386</v>
+      </c>
+      <c r="C82" s="28">
         <v>20</v>
       </c>
-      <c r="D82" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="E82" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F82" s="30" t="s">
-        <v>143</v>
+      <c r="D82" s="26">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E82" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F82" s="26" t="s">
+        <v>387</v>
       </c>
       <c r="G82" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F82),0)&gt;0), MAX($G$1:G80)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F82),0)&gt;0), MAX($G$1:G81)+1, ""))</f>
         <v/>
       </c>
       <c r="H82" s="21" t="b">
@@ -3996,22 +3999,22 @@
         <v>20</v>
       </c>
       <c r="B83" s="31" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C83" s="32">
         <v>20</v>
       </c>
       <c r="D83" s="30" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="E83" s="31" t="s">
-        <v>305</v>
+        <v>8</v>
       </c>
       <c r="F83" s="30" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G83" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F83),0)&gt;0), MAX($G$1:G82)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F83),0)&gt;0), MAX($G$1:G81)+1, ""))</f>
         <v/>
       </c>
       <c r="H83" s="21" t="b">
@@ -4020,25 +4023,28 @@
       </c>
     </row>
     <row r="84" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A84" s="36">
+      <c r="A84" s="30">
         <v>20</v>
       </c>
-      <c r="B84" s="37" t="s">
-        <v>333</v>
-      </c>
-      <c r="C84" s="38">
+      <c r="B84" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="C84" s="32">
         <v>20</v>
       </c>
-      <c r="D84" s="36">
-        <v>3.4</v>
-      </c>
-      <c r="E84" s="37" t="s">
-        <v>336</v>
-      </c>
-      <c r="F84" s="36" t="s">
-        <v>334</v>
-      </c>
-      <c r="G84" s="29"/>
+      <c r="D84" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="E84" s="31" t="s">
+        <v>305</v>
+      </c>
+      <c r="F84" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="G84" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F84),0)&gt;0), MAX($G$1:G83)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H84" s="21" t="b">
         <f>A84=C84</f>
         <v>1</v>
@@ -4049,19 +4055,19 @@
         <v>20</v>
       </c>
       <c r="B85" s="37" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C85" s="38">
         <v>20</v>
       </c>
       <c r="D85" s="36">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="E85" s="37" t="s">
         <v>336</v>
       </c>
       <c r="F85" s="36" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G85" s="29"/>
       <c r="H85" s="21" t="b">
@@ -4070,28 +4076,25 @@
       </c>
     </row>
     <row r="86" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A86" s="30">
+      <c r="A86" s="36">
         <v>20</v>
       </c>
-      <c r="B86" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="C86" s="32">
+      <c r="B86" s="37" t="s">
+        <v>331</v>
+      </c>
+      <c r="C86" s="38">
         <v>20</v>
       </c>
-      <c r="D86" s="30" t="s">
-        <v>223</v>
-      </c>
-      <c r="E86" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F86" s="30" t="s">
-        <v>139</v>
-      </c>
-      <c r="G86" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F86),0)&gt;0), MAX($G$1:G85)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D86" s="36">
+        <v>3.3</v>
+      </c>
+      <c r="E86" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="F86" s="36" t="s">
+        <v>332</v>
+      </c>
+      <c r="G86" s="29"/>
       <c r="H86" s="21" t="b">
         <f>A86=C86</f>
         <v>1</v>
@@ -4102,19 +4105,19 @@
         <v>20</v>
       </c>
       <c r="B87" s="31" t="s">
-        <v>255</v>
+        <v>138</v>
       </c>
       <c r="C87" s="32">
         <v>20</v>
       </c>
       <c r="D87" s="30" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E87" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F87" s="30" t="s">
-        <v>256</v>
+        <v>139</v>
       </c>
       <c r="G87" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F87),0)&gt;0), MAX($G$1:G86)+1, ""))</f>
@@ -4130,19 +4133,19 @@
         <v>20</v>
       </c>
       <c r="B88" s="31" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C88" s="32">
         <v>20</v>
       </c>
-      <c r="D88" s="30">
-        <v>4.2</v>
+      <c r="D88" s="30" t="s">
+        <v>225</v>
       </c>
       <c r="E88" s="31" t="s">
-        <v>305</v>
-      </c>
-      <c r="F88" s="30">
-        <v>21765430</v>
+        <v>8</v>
+      </c>
+      <c r="F88" s="30" t="s">
+        <v>256</v>
       </c>
       <c r="G88" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F88),0)&gt;0), MAX($G$1:G87)+1, ""))</f>
@@ -4158,19 +4161,19 @@
         <v>20</v>
       </c>
       <c r="B89" s="31" t="s">
-        <v>136</v>
+        <v>254</v>
       </c>
       <c r="C89" s="32">
         <v>20</v>
       </c>
-      <c r="D89" s="30" t="s">
-        <v>210</v>
+      <c r="D89" s="30">
+        <v>4.2</v>
       </c>
       <c r="E89" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F89" s="30" t="s">
-        <v>137</v>
+        <v>305</v>
+      </c>
+      <c r="F89" s="30">
+        <v>21765430</v>
       </c>
       <c r="G89" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F89),0)&gt;0), MAX($G$1:G88)+1, ""))</f>
@@ -4186,19 +4189,19 @@
         <v>20</v>
       </c>
       <c r="B90" s="31" t="s">
-        <v>265</v>
+        <v>136</v>
       </c>
       <c r="C90" s="32">
         <v>20</v>
       </c>
       <c r="D90" s="30" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="E90" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F90" s="30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G90" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F90),0)&gt;0), MAX($G$1:G89)+1, ""))</f>
@@ -4214,19 +4217,19 @@
         <v>20</v>
       </c>
       <c r="B91" s="31" t="s">
-        <v>133</v>
+        <v>265</v>
       </c>
       <c r="C91" s="32">
         <v>20</v>
       </c>
       <c r="D91" s="30" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E91" s="31" t="s">
-        <v>305</v>
+        <v>8</v>
       </c>
       <c r="F91" s="30" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G91" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F91),0)&gt;0), MAX($G$1:G90)+1, ""))</f>
@@ -4242,19 +4245,19 @@
         <v>20</v>
       </c>
       <c r="B92" s="31" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C92" s="32">
         <v>20</v>
       </c>
       <c r="D92" s="30" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E92" s="31" t="s">
-        <v>131</v>
+        <v>305</v>
       </c>
       <c r="F92" s="30" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G92" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F92),0)&gt;0), MAX($G$1:G91)+1, ""))</f>
@@ -4266,23 +4269,23 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A93" s="26">
+      <c r="A93" s="30">
         <v>20</v>
       </c>
-      <c r="B93" s="27" t="s">
-        <v>312</v>
-      </c>
-      <c r="C93" s="28">
+      <c r="B93" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="C93" s="32">
         <v>20</v>
       </c>
-      <c r="D93" s="26">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="E93" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="F93" s="26" t="s">
-        <v>318</v>
+      <c r="D93" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="E93" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="F93" s="30" t="s">
+        <v>132</v>
       </c>
       <c r="G93" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F93),0)&gt;0), MAX($G$1:G92)+1, ""))</f>
@@ -4298,19 +4301,19 @@
         <v>20</v>
       </c>
       <c r="B94" s="27" t="s">
-        <v>389</v>
+        <v>312</v>
       </c>
       <c r="C94" s="28">
         <v>20</v>
       </c>
       <c r="D94" s="26">
-        <v>2.5</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E94" s="27" t="s">
         <v>60</v>
       </c>
       <c r="F94" s="26" t="s">
-        <v>388</v>
+        <v>318</v>
       </c>
       <c r="G94" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F94),0)&gt;0), MAX($G$1:G93)+1, ""))</f>
@@ -4322,23 +4325,23 @@
       </c>
     </row>
     <row r="95" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A95" s="30">
+      <c r="A95" s="26">
         <v>20</v>
       </c>
-      <c r="B95" s="31" t="s">
-        <v>128</v>
-      </c>
-      <c r="C95" s="32">
+      <c r="B95" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="C95" s="28">
         <v>20</v>
       </c>
-      <c r="D95" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="E95" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F95" s="30" t="s">
-        <v>129</v>
+      <c r="D95" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E95" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F95" s="26" t="s">
+        <v>388</v>
       </c>
       <c r="G95" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F95),0)&gt;0), MAX($G$1:G94)+1, ""))</f>
@@ -4354,19 +4357,19 @@
         <v>20</v>
       </c>
       <c r="B96" s="31" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C96" s="32">
         <v>20</v>
       </c>
       <c r="D96" s="30" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="E96" s="31" t="s">
-        <v>305</v>
+        <v>8</v>
       </c>
       <c r="F96" s="30" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G96" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F96),0)&gt;0), MAX($G$1:G95)+1, ""))</f>
@@ -4378,23 +4381,23 @@
       </c>
     </row>
     <row r="97" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A97" s="26">
+      <c r="A97" s="30">
         <v>20</v>
       </c>
-      <c r="B97" s="27" t="s">
-        <v>375</v>
-      </c>
-      <c r="C97" s="28">
+      <c r="B97" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="C97" s="32">
         <v>20</v>
       </c>
-      <c r="D97" s="26">
-        <v>2.7</v>
-      </c>
-      <c r="E97" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="F97" s="26" t="s">
-        <v>351</v>
+      <c r="D97" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="E97" s="31" t="s">
+        <v>305</v>
+      </c>
+      <c r="F97" s="30" t="s">
+        <v>127</v>
       </c>
       <c r="G97" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F97),0)&gt;0), MAX($G$1:G96)+1, ""))</f>
@@ -4406,23 +4409,23 @@
       </c>
     </row>
     <row r="98" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A98" s="30">
+      <c r="A98" s="26">
         <v>20</v>
       </c>
-      <c r="B98" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="C98" s="32">
+      <c r="B98" s="27" t="s">
+        <v>375</v>
+      </c>
+      <c r="C98" s="28">
         <v>20</v>
       </c>
-      <c r="D98" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="E98" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F98" s="30" t="s">
-        <v>125</v>
+      <c r="D98" s="26">
+        <v>2.7</v>
+      </c>
+      <c r="E98" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="F98" s="26" t="s">
+        <v>351</v>
       </c>
       <c r="G98" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F98),0)&gt;0), MAX($G$1:G97)+1, ""))</f>
@@ -4438,19 +4441,19 @@
         <v>20</v>
       </c>
       <c r="B99" s="31" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C99" s="32">
         <v>20</v>
       </c>
       <c r="D99" s="30" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="E99" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F99" s="30" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G99" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F99),0)&gt;0), MAX($G$1:G98)+1, ""))</f>
@@ -4466,19 +4469,19 @@
         <v>20</v>
       </c>
       <c r="B100" s="31" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C100" s="32">
         <v>20</v>
       </c>
       <c r="D100" s="30" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="E100" s="31" t="s">
-        <v>305</v>
+        <v>8</v>
       </c>
       <c r="F100" s="30" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G100" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F100),0)&gt;0), MAX($G$1:G99)+1, ""))</f>
@@ -4490,23 +4493,23 @@
       </c>
     </row>
     <row r="101" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A101" s="26">
+      <c r="A101" s="30">
         <v>20</v>
       </c>
-      <c r="B101" s="27" t="s">
-        <v>369</v>
-      </c>
-      <c r="C101" s="28">
+      <c r="B101" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="C101" s="32">
         <v>20</v>
       </c>
-      <c r="D101" s="26">
-        <v>1.5</v>
+      <c r="D101" s="30" t="s">
+        <v>223</v>
       </c>
       <c r="E101" s="31" t="s">
-        <v>299</v>
-      </c>
-      <c r="F101" s="26" t="s">
-        <v>370</v>
+        <v>305</v>
+      </c>
+      <c r="F101" s="30" t="s">
+        <v>121</v>
       </c>
       <c r="G101" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F101),0)&gt;0), MAX($G$1:G100)+1, ""))</f>
@@ -4518,23 +4521,23 @@
       </c>
     </row>
     <row r="102" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A102" s="30">
+      <c r="A102" s="26">
         <v>20</v>
       </c>
-      <c r="B102" s="31" t="s">
-        <v>257</v>
-      </c>
-      <c r="C102" s="32">
+      <c r="B102" s="27" t="s">
+        <v>369</v>
+      </c>
+      <c r="C102" s="28">
         <v>20</v>
       </c>
-      <c r="D102" s="30" t="s">
-        <v>225</v>
+      <c r="D102" s="26">
+        <v>1.5</v>
       </c>
       <c r="E102" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F102" s="30" t="s">
-        <v>258</v>
+        <v>299</v>
+      </c>
+      <c r="F102" s="26" t="s">
+        <v>370</v>
       </c>
       <c r="G102" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F102),0)&gt;0), MAX($G$1:G101)+1, ""))</f>
@@ -4550,19 +4553,19 @@
         <v>20</v>
       </c>
       <c r="B103" s="31" t="s">
-        <v>118</v>
+        <v>257</v>
       </c>
       <c r="C103" s="32">
         <v>20</v>
       </c>
       <c r="D103" s="30" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E103" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F103" s="30" t="s">
-        <v>119</v>
+        <v>258</v>
       </c>
       <c r="G103" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F103),0)&gt;0), MAX($G$1:G102)+1, ""))</f>
@@ -4578,19 +4581,19 @@
         <v>20</v>
       </c>
       <c r="B104" s="31" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C104" s="32">
         <v>20</v>
       </c>
       <c r="D104" s="30" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="E104" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F104" s="30" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G104" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F104),0)&gt;0), MAX($G$1:G103)+1, ""))</f>
@@ -4606,19 +4609,19 @@
         <v>20</v>
       </c>
       <c r="B105" s="31" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C105" s="32">
         <v>20</v>
       </c>
       <c r="D105" s="30" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E105" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F105" s="30" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G105" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F105),0)&gt;0), MAX($G$1:G104)+1, ""))</f>
@@ -4630,23 +4633,23 @@
       </c>
     </row>
     <row r="106" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A106" s="26">
+      <c r="A106" s="30">
         <v>20</v>
       </c>
-      <c r="B106" s="27" t="s">
-        <v>297</v>
-      </c>
-      <c r="C106" s="28">
+      <c r="B106" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="C106" s="32">
         <v>20</v>
       </c>
-      <c r="D106" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E106" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="F106" s="26" t="s">
-        <v>298</v>
+      <c r="D106" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="E106" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F106" s="30" t="s">
+        <v>115</v>
       </c>
       <c r="G106" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F106),0)&gt;0), MAX($G$1:G105)+1, ""))</f>
@@ -4658,23 +4661,23 @@
       </c>
     </row>
     <row r="107" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A107" s="30">
+      <c r="A107" s="26">
         <v>20</v>
       </c>
-      <c r="B107" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="C107" s="32">
+      <c r="B107" s="27" t="s">
+        <v>297</v>
+      </c>
+      <c r="C107" s="28">
         <v>20</v>
       </c>
-      <c r="D107" s="30" t="s">
-        <v>219</v>
-      </c>
-      <c r="E107" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F107" s="30" t="s">
-        <v>113</v>
+      <c r="D107" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E107" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="F107" s="26" t="s">
+        <v>298</v>
       </c>
       <c r="G107" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F107),0)&gt;0), MAX($G$1:G106)+1, ""))</f>
@@ -4690,19 +4693,19 @@
         <v>20</v>
       </c>
       <c r="B108" s="31" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C108" s="32">
         <v>20</v>
       </c>
       <c r="D108" s="30" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E108" s="31" t="s">
-        <v>299</v>
+        <v>8</v>
       </c>
       <c r="F108" s="30" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G108" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F108),0)&gt;0), MAX($G$1:G107)+1, ""))</f>
@@ -4718,19 +4721,19 @@
         <v>20</v>
       </c>
       <c r="B109" s="31" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C109" s="32">
         <v>20</v>
       </c>
       <c r="D109" s="30" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E109" s="31" t="s">
-        <v>8</v>
+        <v>299</v>
       </c>
       <c r="F109" s="30" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G109" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F109),0)&gt;0), MAX($G$1:G108)+1, ""))</f>
@@ -4742,76 +4745,76 @@
       </c>
     </row>
     <row r="110" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A110" s="36">
+      <c r="A110" s="30">
         <v>20</v>
       </c>
-      <c r="B110" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="C110" s="38">
+      <c r="B110" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="C110" s="32">
         <v>20</v>
       </c>
-      <c r="D110" s="36">
-        <v>3</v>
-      </c>
-      <c r="E110" s="37" t="s">
-        <v>304</v>
-      </c>
-      <c r="F110" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="G110" s="29"/>
+      <c r="D110" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="E110" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F110" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="G110" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F110),0)&gt;0), MAX($G$1:G109)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H110" s="21" t="b">
         <f>A110=C110</f>
         <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A111" s="26">
+      <c r="A111" s="36">
         <v>20</v>
       </c>
-      <c r="B111" s="27" t="s">
-        <v>302</v>
-      </c>
-      <c r="C111" s="28">
+      <c r="B111" s="37" t="s">
+        <v>330</v>
+      </c>
+      <c r="C111" s="38">
         <v>20</v>
       </c>
-      <c r="D111" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E111" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="F111" s="26" t="s">
-        <v>301</v>
-      </c>
-      <c r="G111" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F111),0)&gt;0), MAX($G$1:G110)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D111" s="36">
+        <v>3</v>
+      </c>
+      <c r="E111" s="37" t="s">
+        <v>304</v>
+      </c>
+      <c r="F111" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="G111" s="29"/>
       <c r="H111" s="21" t="b">
         <f>A111=C111</f>
         <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A112" s="30">
+      <c r="A112" s="26">
         <v>20</v>
       </c>
-      <c r="B112" s="31" t="s">
-        <v>366</v>
-      </c>
-      <c r="C112" s="32">
+      <c r="B112" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C112" s="28">
         <v>20</v>
       </c>
-      <c r="D112" s="30">
+      <c r="D112" s="26">
         <v>2.4</v>
       </c>
-      <c r="E112" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="F112" s="30" t="s">
-        <v>367</v>
+      <c r="E112" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="F112" s="26" t="s">
+        <v>301</v>
       </c>
       <c r="G112" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F112),0)&gt;0), MAX($G$1:G111)+1, ""))</f>
@@ -4827,19 +4830,19 @@
         <v>20</v>
       </c>
       <c r="B113" s="31" t="s">
-        <v>103</v>
+        <v>366</v>
       </c>
       <c r="C113" s="32">
         <v>20</v>
       </c>
-      <c r="D113" s="30" t="s">
-        <v>214</v>
+      <c r="D113" s="30">
+        <v>2.4</v>
       </c>
       <c r="E113" s="31" t="s">
         <v>60</v>
       </c>
       <c r="F113" s="30" t="s">
-        <v>104</v>
+        <v>367</v>
       </c>
       <c r="G113" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F113),0)&gt;0), MAX($G$1:G112)+1, ""))</f>
@@ -4851,23 +4854,23 @@
       </c>
     </row>
     <row r="114" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A114" s="26">
+      <c r="A114" s="30">
         <v>20</v>
       </c>
-      <c r="B114" s="27" t="s">
-        <v>339</v>
-      </c>
-      <c r="C114" s="28">
+      <c r="B114" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="C114" s="32">
         <v>20</v>
       </c>
-      <c r="D114" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E114" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F114" s="26" t="s">
-        <v>344</v>
+      <c r="D114" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="E114" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="F114" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G114" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F114),0)&gt;0), MAX($G$1:G113)+1, ""))</f>
@@ -4879,53 +4882,53 @@
       </c>
     </row>
     <row r="115" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A115" s="36">
+      <c r="A115" s="26">
         <v>20</v>
       </c>
-      <c r="B115" s="37" t="s">
-        <v>335</v>
-      </c>
-      <c r="C115" s="38">
+      <c r="B115" s="27" t="s">
+        <v>339</v>
+      </c>
+      <c r="C115" s="28">
         <v>20</v>
       </c>
-      <c r="D115" s="36">
-        <v>3.2</v>
-      </c>
-      <c r="E115" s="37" t="s">
-        <v>336</v>
-      </c>
-      <c r="F115" s="36" t="s">
-        <v>332</v>
-      </c>
-      <c r="G115" s="29"/>
+      <c r="D115" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E115" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F115" s="26" t="s">
+        <v>344</v>
+      </c>
+      <c r="G115" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F115),0)&gt;0), MAX($G$1:G114)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H115" s="21" t="b">
         <f>A115=C115</f>
         <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A116" s="30">
+      <c r="A116" s="36">
         <v>20</v>
       </c>
-      <c r="B116" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="C116" s="32">
+      <c r="B116" s="37" t="s">
+        <v>335</v>
+      </c>
+      <c r="C116" s="38">
         <v>20</v>
       </c>
-      <c r="D116" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E116" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F116" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="G116" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F116),0)&gt;0), MAX($G$1:G115)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D116" s="36">
+        <v>3.2</v>
+      </c>
+      <c r="E116" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="F116" s="36" t="s">
+        <v>332</v>
+      </c>
+      <c r="G116" s="29"/>
       <c r="H116" s="21" t="b">
         <f>A116=C116</f>
         <v>1</v>
@@ -4936,19 +4939,19 @@
         <v>20</v>
       </c>
       <c r="B117" s="31" t="s">
-        <v>263</v>
+        <v>101</v>
       </c>
       <c r="C117" s="32">
         <v>20</v>
       </c>
-      <c r="D117" s="30">
-        <v>6.2</v>
+      <c r="D117" s="30" t="s">
+        <v>207</v>
       </c>
       <c r="E117" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F117" s="30" t="s">
-        <v>264</v>
+        <v>102</v>
       </c>
       <c r="G117" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F117),0)&gt;0), MAX($G$1:G116)+1, ""))</f>
@@ -4964,19 +4967,19 @@
         <v>20</v>
       </c>
       <c r="B118" s="31" t="s">
-        <v>99</v>
+        <v>263</v>
       </c>
       <c r="C118" s="32">
         <v>20</v>
       </c>
-      <c r="D118" s="30" t="s">
-        <v>215</v>
+      <c r="D118" s="30">
+        <v>6.2</v>
       </c>
       <c r="E118" s="31" t="s">
-        <v>299</v>
+        <v>8</v>
       </c>
       <c r="F118" s="30" t="s">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="G118" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F118),0)&gt;0), MAX($G$1:G117)+1, ""))</f>
@@ -4988,23 +4991,23 @@
       </c>
     </row>
     <row r="119" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A119" s="26">
+      <c r="A119" s="30">
         <v>20</v>
       </c>
-      <c r="B119" s="27" t="s">
-        <v>300</v>
-      </c>
-      <c r="C119" s="28">
+      <c r="B119" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="C119" s="32">
         <v>20</v>
       </c>
-      <c r="D119" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E119" s="27" t="s">
+      <c r="D119" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="E119" s="31" t="s">
         <v>299</v>
       </c>
-      <c r="F119" s="26" t="s">
-        <v>301</v>
+      <c r="F119" s="30" t="s">
+        <v>100</v>
       </c>
       <c r="G119" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F119),0)&gt;0), MAX($G$1:G118)+1, ""))</f>
@@ -5016,23 +5019,23 @@
       </c>
     </row>
     <row r="120" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A120" s="30">
+      <c r="A120" s="26">
         <v>20</v>
       </c>
-      <c r="B120" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="C120" s="32">
+      <c r="B120" s="27" t="s">
+        <v>300</v>
+      </c>
+      <c r="C120" s="28">
         <v>20</v>
       </c>
-      <c r="D120" s="30" t="s">
-        <v>216</v>
-      </c>
-      <c r="E120" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F120" s="30" t="s">
-        <v>96</v>
+      <c r="D120" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E120" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="F120" s="26" t="s">
+        <v>301</v>
       </c>
       <c r="G120" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F120),0)&gt;0), MAX($G$1:G119)+1, ""))</f>
@@ -5044,26 +5047,26 @@
       </c>
     </row>
     <row r="121" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A121" s="26">
+      <c r="A121" s="30">
         <v>20</v>
       </c>
-      <c r="B121" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="C121" s="28">
+      <c r="B121" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="C121" s="32">
         <v>20</v>
       </c>
-      <c r="D121" s="26">
-        <v>3.9</v>
-      </c>
-      <c r="E121" s="27" t="s">
-        <v>309</v>
-      </c>
-      <c r="F121" s="26" t="s">
-        <v>311</v>
+      <c r="D121" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="E121" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F121" s="30" t="s">
+        <v>96</v>
       </c>
       <c r="G121" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F121),0)&gt;0), MAX($G$1:G119)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F121),0)&gt;0), MAX($G$1:G120)+1, ""))</f>
         <v/>
       </c>
       <c r="H121" s="21" t="b">
@@ -5076,22 +5079,22 @@
         <v>20</v>
       </c>
       <c r="B122" s="27" t="s">
-        <v>355</v>
+        <v>310</v>
       </c>
       <c r="C122" s="28">
         <v>20</v>
       </c>
       <c r="D122" s="26">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="E122" s="27" t="s">
-        <v>81</v>
+        <v>309</v>
       </c>
       <c r="F122" s="26" t="s">
-        <v>356</v>
+        <v>311</v>
       </c>
       <c r="G122" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F122),0)&gt;0), MAX($G$1:G121)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F122),0)&gt;0), MAX($G$1:G120)+1, ""))</f>
         <v/>
       </c>
       <c r="H122" s="21" t="b">
@@ -5100,23 +5103,23 @@
       </c>
     </row>
     <row r="123" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A123" s="30">
+      <c r="A123" s="26">
         <v>20</v>
       </c>
-      <c r="B123" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="C123" s="32">
+      <c r="B123" s="27" t="s">
+        <v>355</v>
+      </c>
+      <c r="C123" s="28">
         <v>20</v>
       </c>
-      <c r="D123" s="30" t="s">
-        <v>218</v>
-      </c>
-      <c r="E123" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F123" s="30" t="s">
-        <v>92</v>
+      <c r="D123" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E123" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F123" s="26" t="s">
+        <v>356</v>
       </c>
       <c r="G123" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F123),0)&gt;0), MAX($G$1:G122)+1, ""))</f>
@@ -5132,19 +5135,19 @@
         <v>20</v>
       </c>
       <c r="B124" s="31" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C124" s="32">
         <v>20</v>
       </c>
       <c r="D124" s="30" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="E124" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F124" s="30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G124" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F124),0)&gt;0), MAX($G$1:G123)+1, ""))</f>
@@ -5160,16 +5163,16 @@
         <v>20</v>
       </c>
       <c r="B125" s="31" t="s">
-        <v>290</v>
+        <v>89</v>
       </c>
       <c r="C125" s="32">
         <v>20</v>
       </c>
-      <c r="D125" s="30">
-        <v>1.8</v>
+      <c r="D125" s="30" t="s">
+        <v>223</v>
       </c>
       <c r="E125" s="31" t="s">
-        <v>291</v>
+        <v>8</v>
       </c>
       <c r="F125" s="30" t="s">
         <v>90</v>
@@ -5188,19 +5191,19 @@
         <v>20</v>
       </c>
       <c r="B126" s="31" t="s">
-        <v>87</v>
+        <v>290</v>
       </c>
       <c r="C126" s="32">
         <v>20</v>
       </c>
-      <c r="D126" s="30" t="s">
-        <v>222</v>
+      <c r="D126" s="30">
+        <v>1.8</v>
       </c>
       <c r="E126" s="31" t="s">
-        <v>8</v>
+        <v>291</v>
       </c>
       <c r="F126" s="30" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G126" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F126),0)&gt;0), MAX($G$1:G125)+1, ""))</f>
@@ -5216,19 +5219,19 @@
         <v>20</v>
       </c>
       <c r="B127" s="31" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C127" s="32">
         <v>20</v>
       </c>
       <c r="D127" s="30" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E127" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F127" s="30" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G127" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F127),0)&gt;0), MAX($G$1:G126)+1, ""))</f>
@@ -5244,19 +5247,19 @@
         <v>20</v>
       </c>
       <c r="B128" s="31" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C128" s="32">
         <v>20</v>
       </c>
       <c r="D128" s="30" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E128" s="31" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F128" s="30" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G128" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F128),0)&gt;0), MAX($G$1:G127)+1, ""))</f>
@@ -5272,19 +5275,19 @@
         <v>20</v>
       </c>
       <c r="B129" s="31" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C129" s="32">
         <v>20</v>
       </c>
       <c r="D129" s="30" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E129" s="31" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="F129" s="30" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G129" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F129),0)&gt;0), MAX($G$1:G128)+1, ""))</f>
@@ -5300,19 +5303,19 @@
         <v>20</v>
       </c>
       <c r="B130" s="31" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C130" s="32">
         <v>20</v>
       </c>
       <c r="D130" s="30" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E130" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F130" s="30" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G130" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F130),0)&gt;0), MAX($G$1:G129)+1, ""))</f>
@@ -5324,23 +5327,23 @@
       </c>
     </row>
     <row r="131" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A131" s="26">
-        <v>25</v>
-      </c>
-      <c r="B131" s="27" t="s">
-        <v>178</v>
-      </c>
-      <c r="C131" s="28">
-        <v>25</v>
-      </c>
-      <c r="D131" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="E131" s="27" t="s">
+      <c r="A131" s="30">
+        <v>20</v>
+      </c>
+      <c r="B131" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="C131" s="32">
+        <v>20</v>
+      </c>
+      <c r="D131" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="E131" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F131" s="26" t="s">
-        <v>179</v>
+      <c r="F131" s="30" t="s">
+        <v>77</v>
       </c>
       <c r="G131" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F131),0)&gt;0), MAX($G$1:G130)+1, ""))</f>
@@ -5356,19 +5359,19 @@
         <v>25</v>
       </c>
       <c r="B132" s="27" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C132" s="28">
         <v>25</v>
       </c>
       <c r="D132" s="26" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="E132" s="27" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="F132" s="26" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G132" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B132),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E132),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F132),0)&gt;0), MAX($G$1:G131)+1, ""))</f>
@@ -5384,19 +5387,19 @@
         <v>25</v>
       </c>
       <c r="B133" s="27" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C133" s="28">
         <v>25</v>
       </c>
       <c r="D133" s="26" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="E133" s="27" t="s">
         <v>131</v>
       </c>
       <c r="F133" s="26" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G133" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F133),0)&gt;0), MAX($G$1:G132)+1, ""))</f>
@@ -5412,19 +5415,19 @@
         <v>25</v>
       </c>
       <c r="B134" s="27" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C134" s="28">
         <v>25</v>
       </c>
       <c r="D134" s="26" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="E134" s="27" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F134" s="26" t="s">
-        <v>324</v>
+        <v>175</v>
       </c>
       <c r="G134" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F134),0)&gt;0), MAX($G$1:G133)+1, ""))</f>
@@ -5440,19 +5443,19 @@
         <v>25</v>
       </c>
       <c r="B135" s="27" t="s">
-        <v>359</v>
+        <v>173</v>
       </c>
       <c r="C135" s="28">
         <v>25</v>
       </c>
-      <c r="D135" s="26">
-        <v>3</v>
+      <c r="D135" s="26" t="s">
+        <v>224</v>
       </c>
       <c r="E135" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F135" s="26" t="s">
-        <v>360</v>
+        <v>324</v>
       </c>
       <c r="G135" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F135),0)&gt;0), MAX($G$1:G134)+1, ""))</f>
@@ -5468,19 +5471,19 @@
         <v>25</v>
       </c>
       <c r="B136" s="27" t="s">
-        <v>172</v>
+        <v>359</v>
       </c>
       <c r="C136" s="28">
         <v>25</v>
       </c>
       <c r="D136" s="26">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="E136" s="27" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F136" s="26" t="s">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="G136" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F136),0)&gt;0), MAX($G$1:G135)+1, ""))</f>
@@ -5492,23 +5495,23 @@
       </c>
     </row>
     <row r="137" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A137" s="30">
+      <c r="A137" s="26">
         <v>25</v>
       </c>
-      <c r="B137" s="31" t="s">
-        <v>284</v>
-      </c>
-      <c r="C137" s="32">
+      <c r="B137" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="C137" s="28">
         <v>25</v>
       </c>
-      <c r="D137" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E137" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F137" s="30" t="s">
-        <v>102</v>
+      <c r="D137" s="26">
+        <v>2.7</v>
+      </c>
+      <c r="E137" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F137" s="26" t="s">
+        <v>338</v>
       </c>
       <c r="G137" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F137),0)&gt;0), MAX($G$1:G136)+1, ""))</f>
@@ -5524,7 +5527,7 @@
         <v>25</v>
       </c>
       <c r="B138" s="31" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C138" s="32">
         <v>25</v>
@@ -5548,23 +5551,23 @@
       </c>
     </row>
     <row r="139" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A139" s="26">
+      <c r="A139" s="30">
         <v>25</v>
       </c>
-      <c r="B139" s="27" t="s">
-        <v>170</v>
-      </c>
-      <c r="C139" s="28">
+      <c r="B139" s="31" t="s">
+        <v>282</v>
+      </c>
+      <c r="C139" s="32">
         <v>25</v>
       </c>
-      <c r="D139" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="E139" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="F139" s="26" t="s">
-        <v>171</v>
+      <c r="D139" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E139" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="F139" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G139" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F139),0)&gt;0), MAX($G$1:G138)+1, ""))</f>
@@ -5580,19 +5583,19 @@
         <v>25</v>
       </c>
       <c r="B140" s="27" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C140" s="28">
         <v>25</v>
       </c>
       <c r="D140" s="26" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="E140" s="27" t="s">
-        <v>8</v>
+        <v>245</v>
       </c>
       <c r="F140" s="26" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G140" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F140),0)&gt;0), MAX($G$1:G139)+1, ""))</f>
@@ -5608,19 +5611,19 @@
         <v>25</v>
       </c>
       <c r="B141" s="27" t="s">
-        <v>357</v>
+        <v>168</v>
       </c>
       <c r="C141" s="28">
         <v>25</v>
       </c>
-      <c r="D141" s="26">
-        <v>3.4</v>
+      <c r="D141" s="26" t="s">
+        <v>217</v>
       </c>
       <c r="E141" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F141" s="26" t="s">
-        <v>358</v>
+        <v>169</v>
       </c>
       <c r="G141" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F141),0)&gt;0), MAX($G$1:G140)+1, ""))</f>
@@ -5632,23 +5635,23 @@
       </c>
     </row>
     <row r="142" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A142" s="30">
+      <c r="A142" s="26">
         <v>25</v>
       </c>
-      <c r="B142" s="31" t="s">
-        <v>278</v>
-      </c>
-      <c r="C142" s="32">
+      <c r="B142" s="27" t="s">
+        <v>357</v>
+      </c>
+      <c r="C142" s="28">
         <v>25</v>
       </c>
-      <c r="D142" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E142" s="31" t="s">
+      <c r="D142" s="26">
+        <v>3.4</v>
+      </c>
+      <c r="E142" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F142" s="30" t="s">
-        <v>102</v>
+      <c r="F142" s="26" t="s">
+        <v>358</v>
       </c>
       <c r="G142" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F142),0)&gt;0), MAX($G$1:G141)+1, ""))</f>
@@ -5660,23 +5663,23 @@
       </c>
     </row>
     <row r="143" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A143" s="26">
+      <c r="A143" s="30">
         <v>25</v>
       </c>
-      <c r="B143" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="C143" s="28">
+      <c r="B143" s="31" t="s">
+        <v>278</v>
+      </c>
+      <c r="C143" s="32">
         <v>25</v>
       </c>
-      <c r="D143" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="E143" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="F143" s="26" t="s">
-        <v>167</v>
+      <c r="D143" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E143" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F143" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G143" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F143),0)&gt;0), MAX($G$1:G142)+1, ""))</f>
@@ -5692,19 +5695,19 @@
         <v>25</v>
       </c>
       <c r="B144" s="27" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C144" s="28">
         <v>25</v>
       </c>
       <c r="D144" s="26" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="E144" s="27" t="s">
         <v>131</v>
       </c>
       <c r="F144" s="26" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G144" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F144),0)&gt;0), MAX($G$1:G143)+1, ""))</f>
@@ -5720,19 +5723,19 @@
         <v>25</v>
       </c>
       <c r="B145" s="27" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C145" s="28">
         <v>25</v>
       </c>
       <c r="D145" s="26" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E145" s="27" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="F145" s="26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G145" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B145),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E145),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F145),0)&gt;0), MAX($G$1:G144)+1, ""))</f>
@@ -5748,19 +5751,19 @@
         <v>25</v>
       </c>
       <c r="B146" s="27" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C146" s="28">
         <v>25</v>
       </c>
       <c r="D146" s="26" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="E146" s="27" t="s">
         <v>81</v>
       </c>
       <c r="F146" s="26" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G146" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F146),0)&gt;0), MAX($G$1:G145)+1, ""))</f>
@@ -5776,19 +5779,19 @@
         <v>25</v>
       </c>
       <c r="B147" s="27" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C147" s="28">
         <v>25</v>
       </c>
       <c r="D147" s="26" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E147" s="27" t="s">
         <v>81</v>
       </c>
       <c r="F147" s="26" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G147" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F147),0)&gt;0), MAX($G$1:G146)+1, ""))</f>
@@ -5804,19 +5807,19 @@
         <v>25</v>
       </c>
       <c r="B148" s="27" t="s">
-        <v>342</v>
+        <v>158</v>
       </c>
       <c r="C148" s="28">
         <v>25</v>
       </c>
-      <c r="D148" s="26">
-        <v>3.4</v>
+      <c r="D148" s="26" t="s">
+        <v>228</v>
       </c>
       <c r="E148" s="27" t="s">
         <v>81</v>
       </c>
       <c r="F148" s="26" t="s">
-        <v>343</v>
+        <v>159</v>
       </c>
       <c r="G148" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F148),0)&gt;0), MAX($G$1:G147)+1, ""))</f>
@@ -5832,19 +5835,19 @@
         <v>25</v>
       </c>
       <c r="B149" s="27" t="s">
-        <v>156</v>
+        <v>342</v>
       </c>
       <c r="C149" s="28">
         <v>25</v>
       </c>
-      <c r="D149" s="26" t="s">
-        <v>227</v>
+      <c r="D149" s="26">
+        <v>3.4</v>
       </c>
       <c r="E149" s="27" t="s">
         <v>81</v>
       </c>
       <c r="F149" s="26" t="s">
-        <v>157</v>
+        <v>343</v>
       </c>
       <c r="G149" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B149),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E149),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F149),0)&gt;0), MAX($G$1:G148)+1, ""))</f>
@@ -5860,19 +5863,19 @@
         <v>25</v>
       </c>
       <c r="B150" s="27" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C150" s="28">
         <v>25</v>
       </c>
       <c r="D150" s="26" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E150" s="27" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="F150" s="26" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G150" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B150),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E150),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F150),0)&gt;0), MAX($G$1:G149)+1, ""))</f>
@@ -5888,19 +5891,19 @@
         <v>25</v>
       </c>
       <c r="B151" s="27" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C151" s="28">
         <v>25</v>
       </c>
       <c r="D151" s="26" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="E151" s="27" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="F151" s="26" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G151" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B151),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E151),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F151),0)&gt;0), MAX($G$1:G150)+1, ""))</f>
@@ -5916,19 +5919,19 @@
         <v>25</v>
       </c>
       <c r="B152" s="27" t="s">
-        <v>247</v>
+        <v>152</v>
       </c>
       <c r="C152" s="28">
         <v>25</v>
       </c>
-      <c r="D152" s="39" t="s">
-        <v>229</v>
+      <c r="D152" s="26" t="s">
+        <v>230</v>
       </c>
       <c r="E152" s="27" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F152" s="26" t="s">
-        <v>248</v>
+        <v>153</v>
       </c>
       <c r="G152" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B152),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E152),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F152),0)&gt;0), MAX($G$1:G151)+1, ""))</f>
@@ -5944,19 +5947,19 @@
         <v>25</v>
       </c>
       <c r="B153" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C153" s="28">
         <v>25</v>
       </c>
-      <c r="D153" s="26" t="s">
-        <v>235</v>
+      <c r="D153" s="39" t="s">
+        <v>229</v>
       </c>
       <c r="E153" s="27" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="F153" s="26" t="s">
-        <v>151</v>
+        <v>248</v>
       </c>
       <c r="G153" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B153),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E153),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F153),0)&gt;0), MAX($G$1:G152)+1, ""))</f>
@@ -5968,23 +5971,23 @@
       </c>
     </row>
     <row r="154" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A154" s="30">
+      <c r="A154" s="26">
         <v>25</v>
       </c>
-      <c r="B154" s="31" t="s">
-        <v>288</v>
-      </c>
-      <c r="C154" s="32">
+      <c r="B154" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C154" s="28">
         <v>25</v>
       </c>
-      <c r="D154" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E154" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F154" s="30" t="s">
-        <v>102</v>
+      <c r="D154" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="E154" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="F154" s="26" t="s">
+        <v>151</v>
       </c>
       <c r="G154" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B154),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E154),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F154),0)&gt;0), MAX($G$1:G153)+1, ""))</f>
@@ -6000,7 +6003,7 @@
         <v>25</v>
       </c>
       <c r="B155" s="31" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C155" s="32">
         <v>25</v>
@@ -6028,7 +6031,7 @@
         <v>25</v>
       </c>
       <c r="B156" s="31" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C156" s="32">
         <v>25</v>
@@ -6052,23 +6055,23 @@
       </c>
     </row>
     <row r="157" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A157" s="26">
+      <c r="A157" s="30">
         <v>25</v>
       </c>
-      <c r="B157" s="27" t="s">
-        <v>252</v>
-      </c>
-      <c r="C157" s="28">
+      <c r="B157" s="31" t="s">
+        <v>287</v>
+      </c>
+      <c r="C157" s="32">
         <v>25</v>
       </c>
-      <c r="D157" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E157" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="F157" s="26" t="s">
-        <v>253</v>
+      <c r="D157" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E157" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="F157" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G157" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F157),0)&gt;0), MAX($G$1:G156)+1, ""))</f>
@@ -6080,23 +6083,23 @@
       </c>
     </row>
     <row r="158" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A158" s="30">
+      <c r="A158" s="26">
         <v>25</v>
       </c>
-      <c r="B158" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="C158" s="32">
+      <c r="B158" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="C158" s="28">
         <v>25</v>
       </c>
-      <c r="D158" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E158" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F158" s="30" t="s">
-        <v>102</v>
+      <c r="D158" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E158" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="F158" s="26" t="s">
+        <v>253</v>
       </c>
       <c r="G158" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B158),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E158),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F158),0)&gt;0), MAX($G$1:G157)+1, ""))</f>
@@ -6108,26 +6111,26 @@
       </c>
     </row>
     <row r="159" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A159" s="26">
+      <c r="A159" s="30">
         <v>25</v>
       </c>
-      <c r="B159" s="27" t="s">
-        <v>148</v>
-      </c>
-      <c r="C159" s="28">
+      <c r="B159" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="C159" s="32">
         <v>25</v>
       </c>
-      <c r="D159" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="E159" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F159" s="26" t="s">
-        <v>149</v>
+      <c r="D159" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E159" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="F159" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G159" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F159),0)&gt;0), MAX($G$1:G157)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F159),0)&gt;0), MAX($G$1:G158)+1, ""))</f>
         <v/>
       </c>
       <c r="H159" s="21" t="b">
@@ -6136,26 +6139,26 @@
       </c>
     </row>
     <row r="160" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A160" s="30">
-        <v>30</v>
-      </c>
-      <c r="B160" s="31" t="s">
-        <v>192</v>
-      </c>
-      <c r="C160" s="32">
-        <v>30</v>
-      </c>
-      <c r="D160" s="30" t="s">
-        <v>232</v>
-      </c>
-      <c r="E160" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="F160" s="30" t="s">
-        <v>193</v>
+      <c r="A160" s="26">
+        <v>25</v>
+      </c>
+      <c r="B160" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="C160" s="28">
+        <v>25</v>
+      </c>
+      <c r="D160" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="E160" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F160" s="26" t="s">
+        <v>149</v>
       </c>
       <c r="G160" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B160),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E160),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F160),0)&gt;0), MAX($G$1:G159)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B160),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E160),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F160),0)&gt;0), MAX($G$1:G158)+1, ""))</f>
         <v/>
       </c>
       <c r="H160" s="21" t="b">
@@ -6168,19 +6171,19 @@
         <v>30</v>
       </c>
       <c r="B161" s="31" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C161" s="32">
         <v>30</v>
       </c>
       <c r="D161" s="30" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="E161" s="31" t="s">
         <v>131</v>
       </c>
       <c r="F161" s="30" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="G161" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B161),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E161),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F161),0)&gt;0), MAX($G$1:G160)+1, ""))</f>
@@ -6196,13 +6199,13 @@
         <v>30</v>
       </c>
       <c r="B162" s="31" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C162" s="32">
         <v>30</v>
       </c>
       <c r="D162" s="30" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E162" s="31" t="s">
         <v>131</v>
@@ -6224,19 +6227,19 @@
         <v>30</v>
       </c>
       <c r="B163" s="31" t="s">
-        <v>246</v>
+        <v>189</v>
       </c>
       <c r="C163" s="32">
         <v>30</v>
       </c>
       <c r="D163" s="30" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="E163" s="31" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F163" s="30" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G163" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B163),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E163),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F163),0)&gt;0), MAX($G$1:G162)+1, ""))</f>
@@ -6252,19 +6255,19 @@
         <v>30</v>
       </c>
       <c r="B164" s="31" t="s">
-        <v>186</v>
+        <v>246</v>
       </c>
       <c r="C164" s="32">
         <v>30</v>
       </c>
       <c r="D164" s="30" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="E164" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F164" s="30" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G164" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B164),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E164),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F164),0)&gt;0), MAX($G$1:G163)+1, ""))</f>
@@ -6280,19 +6283,19 @@
         <v>30</v>
       </c>
       <c r="B165" s="31" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C165" s="32">
         <v>30</v>
       </c>
       <c r="D165" s="30" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E165" s="31" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F165" s="30" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G165" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B165),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E165),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F165),0)&gt;0), MAX($G$1:G164)+1, ""))</f>
@@ -6304,23 +6307,23 @@
       </c>
     </row>
     <row r="166" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A166" s="26">
+      <c r="A166" s="30">
         <v>30</v>
       </c>
-      <c r="B166" s="27" t="s">
-        <v>377</v>
-      </c>
-      <c r="C166" s="28">
+      <c r="B166" s="31" t="s">
+        <v>184</v>
+      </c>
+      <c r="C166" s="32">
         <v>30</v>
       </c>
-      <c r="D166" s="26">
-        <v>5</v>
-      </c>
-      <c r="E166" s="27" t="s">
-        <v>378</v>
-      </c>
-      <c r="F166" s="26" t="s">
-        <v>25</v>
+      <c r="D166" s="30" t="s">
+        <v>228</v>
+      </c>
+      <c r="E166" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="F166" s="30" t="s">
+        <v>185</v>
       </c>
       <c r="G166" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B166),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E166),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F166),0)&gt;0), MAX($G$1:G165)+1, ""))</f>
@@ -6332,23 +6335,23 @@
       </c>
     </row>
     <row r="167" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A167" s="30">
+      <c r="A167" s="26">
         <v>30</v>
       </c>
-      <c r="B167" s="31" t="s">
-        <v>182</v>
-      </c>
-      <c r="C167" s="32">
+      <c r="B167" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="C167" s="28">
         <v>30</v>
       </c>
-      <c r="D167" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="E167" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="F167" s="30" t="s">
-        <v>183</v>
+      <c r="D167" s="26">
+        <v>5</v>
+      </c>
+      <c r="E167" s="27" t="s">
+        <v>378</v>
+      </c>
+      <c r="F167" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="G167" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B167),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E167),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F167),0)&gt;0), MAX($G$1:G166)+1, ""))</f>
@@ -6364,19 +6367,19 @@
         <v>30</v>
       </c>
       <c r="B168" s="31" t="s">
-        <v>337</v>
+        <v>182</v>
       </c>
       <c r="C168" s="32">
         <v>30</v>
       </c>
-      <c r="D168" s="30">
-        <v>2.9</v>
+      <c r="D168" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="E168" s="31" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="F168" s="30" t="s">
-        <v>338</v>
+        <v>183</v>
       </c>
       <c r="G168" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B168),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E168),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F168),0)&gt;0), MAX($G$1:G167)+1, ""))</f>
@@ -6392,22 +6395,22 @@
         <v>30</v>
       </c>
       <c r="B169" s="31" t="s">
-        <v>180</v>
+        <v>337</v>
       </c>
       <c r="C169" s="32">
         <v>30</v>
       </c>
-      <c r="D169" s="30" t="s">
-        <v>238</v>
+      <c r="D169" s="30">
+        <v>2.9</v>
       </c>
       <c r="E169" s="31" t="s">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="F169" s="30" t="s">
-        <v>181</v>
+        <v>338</v>
       </c>
       <c r="G169" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B169),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E169),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F169),0)&gt;0), MAX($G$1:G167)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B169),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E169),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F169),0)&gt;0), MAX($G$1:G168)+1, ""))</f>
         <v/>
       </c>
       <c r="H169" s="21" t="b">
@@ -6416,26 +6419,26 @@
       </c>
     </row>
     <row r="170" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A170" s="26">
-        <v>40</v>
-      </c>
-      <c r="B170" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="C170" s="28">
-        <v>40</v>
-      </c>
-      <c r="D170" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="E170" s="27" t="s">
-        <v>198</v>
-      </c>
-      <c r="F170" s="26" t="s">
-        <v>199</v>
+      <c r="A170" s="30">
+        <v>30</v>
+      </c>
+      <c r="B170" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="C170" s="32">
+        <v>30</v>
+      </c>
+      <c r="D170" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="E170" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="F170" s="30" t="s">
+        <v>181</v>
       </c>
       <c r="G170" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B170),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E170),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F170),0)&gt;0), MAX($G$1:G169)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B170),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E170),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F170),0)&gt;0), MAX($G$1:G168)+1, ""))</f>
         <v/>
       </c>
       <c r="H170" s="21" t="b">
@@ -6448,19 +6451,19 @@
         <v>40</v>
       </c>
       <c r="B171" s="27" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C171" s="28">
         <v>40</v>
       </c>
       <c r="D171" s="26" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E171" s="27" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F171" s="26" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G171" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B171),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E171),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F171),0)&gt;0), MAX($G$1:G170)+1, ""))</f>
@@ -6476,19 +6479,19 @@
         <v>40</v>
       </c>
       <c r="B172" s="27" t="s">
-        <v>249</v>
+        <v>194</v>
       </c>
       <c r="C172" s="28">
         <v>40</v>
       </c>
-      <c r="D172" s="26">
-        <v>8.3000000000000007</v>
+      <c r="D172" s="26" t="s">
+        <v>242</v>
       </c>
       <c r="E172" s="27" t="s">
-        <v>250</v>
+        <v>195</v>
       </c>
       <c r="F172" s="26" t="s">
-        <v>251</v>
+        <v>196</v>
       </c>
       <c r="G172" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B172),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E172),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F172),0)&gt;0), MAX($G$1:G171)+1, ""))</f>
@@ -6501,22 +6504,22 @@
     </row>
     <row r="173" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A173" s="26">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B173" s="27" t="s">
-        <v>294</v>
+        <v>249</v>
       </c>
       <c r="C173" s="28">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D173" s="26">
-        <v>10.199999999999999</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="E173" s="27" t="s">
-        <v>295</v>
+        <v>250</v>
       </c>
       <c r="F173" s="26" t="s">
-        <v>296</v>
+        <v>251</v>
       </c>
       <c r="G173" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B173),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E173),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F173),0)&gt;0), MAX($G$1:G172)+1, ""))</f>
@@ -6528,10 +6531,32 @@
       </c>
     </row>
     <row r="174" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A174" s="1"/>
-      <c r="C174" s="1"/>
-      <c r="D174" s="1"/>
-      <c r="F174" s="1"/>
+      <c r="A174" s="26">
+        <v>45</v>
+      </c>
+      <c r="B174" s="27" t="s">
+        <v>294</v>
+      </c>
+      <c r="C174" s="28">
+        <v>45</v>
+      </c>
+      <c r="D174" s="26">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E174" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="F174" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="G174" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B174),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E174),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F174),0)&gt;0), MAX($G$1:G173)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H174" s="21" t="b">
+        <f>A174=C174</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="175" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
@@ -11743,10 +11768,10 @@
       <sortCondition ref="D2:D171"/>
     </sortState>
   </autoFilter>
-  <sortState ref="A2:H173">
-    <sortCondition ref="A2:A173"/>
-    <sortCondition ref="B2:B173"/>
-    <sortCondition ref="D2:D173"/>
+  <sortState ref="A2:H174">
+    <sortCondition ref="A2:A174"/>
+    <sortCondition ref="B2:B174"/>
+    <sortCondition ref="D2:D174"/>
   </sortState>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Consulta" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$171</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$175</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$141</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Base!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="393">
   <si>
     <t>Grupo</t>
   </si>
@@ -1176,12 +1176,6 @@
     <t>21765-050</t>
   </si>
   <si>
-    <t>PARAPUA ATÉ PREDIOS (383)</t>
-  </si>
-  <si>
-    <t>PARAPUA APÓS PREDIOS (383)</t>
-  </si>
-  <si>
     <t>TRAVESSA TUPY - UNIVERSAL</t>
   </si>
   <si>
@@ -1198,6 +1192,18 @@
   </si>
   <si>
     <t>MOEMA</t>
+  </si>
+  <si>
+    <t>PARAPUÃ ATÉ PREDIOS (383)</t>
+  </si>
+  <si>
+    <t>PARAPUÃ APÓS PREDIOS (383)</t>
+  </si>
+  <si>
+    <t>ANIBAL ESTEVES</t>
+  </si>
+  <si>
+    <t>21710-040</t>
   </si>
 </sst>
 </file>
@@ -1715,7 +1721,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H1041"/>
+  <dimension ref="A1:H1042"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.453125" customWidth="1"/>
@@ -2146,7 +2152,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="C16" s="28">
         <v>13</v>
@@ -2286,22 +2292,22 @@
         <v>15</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>74</v>
+        <v>391</v>
       </c>
       <c r="C21" s="28">
         <v>15</v>
       </c>
-      <c r="D21" s="26" t="s">
-        <v>210</v>
+      <c r="D21" s="26">
+        <v>1</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>305</v>
+        <v>8</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>75</v>
+        <v>392</v>
       </c>
       <c r="G21" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F21),0)&gt;0), MAX($G$1:G20)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F21),0)&gt;0), MAX($G$1:G19)+1, ""))</f>
         <v/>
       </c>
       <c r="H21" s="21" t="b">
@@ -2314,22 +2320,22 @@
         <v>15</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>371</v>
+        <v>74</v>
       </c>
       <c r="C22" s="28">
         <v>15</v>
       </c>
-      <c r="D22" s="26">
-        <v>2.1</v>
+      <c r="D22" s="26" t="s">
+        <v>210</v>
       </c>
       <c r="E22" s="27" t="s">
-        <v>245</v>
+        <v>305</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>372</v>
+        <v>75</v>
       </c>
       <c r="G22" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B22),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E22),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F22),0)&gt;0), MAX($G$1:G21)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B22),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E22),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F22),0)&gt;0), MAX($G$1:G20)+1, ""))</f>
         <v/>
       </c>
       <c r="H22" s="21" t="b">
@@ -2342,19 +2348,19 @@
         <v>15</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>72</v>
+        <v>371</v>
       </c>
       <c r="C23" s="28">
         <v>15</v>
       </c>
-      <c r="D23" s="26" t="s">
-        <v>209</v>
+      <c r="D23" s="26">
+        <v>2.1</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>8</v>
+        <v>245</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>73</v>
+        <v>372</v>
       </c>
       <c r="G23" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B23),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E23),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F23),0)&gt;0), MAX($G$1:G22)+1, ""))</f>
@@ -2370,22 +2376,22 @@
         <v>15</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>362</v>
+        <v>72</v>
       </c>
       <c r="C24" s="28">
         <v>15</v>
       </c>
-      <c r="D24" s="26">
-        <v>1</v>
+      <c r="D24" s="26" t="s">
+        <v>209</v>
       </c>
       <c r="E24" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G24" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B24),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E24),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F24),0)&gt;0), MAX($G$1:G21)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B24),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E24),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F24),0)&gt;0), MAX($G$1:G23)+1, ""))</f>
         <v/>
       </c>
       <c r="H24" s="21" t="b">
@@ -2398,22 +2404,22 @@
         <v>15</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>66</v>
+        <v>362</v>
       </c>
       <c r="C25" s="28">
         <v>15</v>
       </c>
-      <c r="D25" s="26" t="s">
-        <v>219</v>
+      <c r="D25" s="26">
+        <v>1</v>
       </c>
       <c r="E25" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G25" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B25),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E25),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F25),0)&gt;0), MAX($G$1:G24)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B25),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E25),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F25),0)&gt;0), MAX($G$1:G22)+1, ""))</f>
         <v/>
       </c>
       <c r="H25" s="21" t="b">
@@ -2426,19 +2432,19 @@
         <v>15</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C26" s="28">
         <v>15</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="E26" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F26" s="26" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G26" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B26),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E26),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F26),0)&gt;0), MAX($G$1:G25)+1, ""))</f>
@@ -2454,7 +2460,7 @@
         <v>15</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>266</v>
+        <v>64</v>
       </c>
       <c r="C27" s="28">
         <v>15</v>
@@ -2463,7 +2469,7 @@
         <v>206</v>
       </c>
       <c r="E27" s="27" t="s">
-        <v>267</v>
+        <v>8</v>
       </c>
       <c r="F27" s="26" t="s">
         <v>65</v>
@@ -2482,19 +2488,19 @@
         <v>15</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>345</v>
+        <v>266</v>
       </c>
       <c r="C28" s="28">
         <v>15</v>
       </c>
-      <c r="D28" s="26">
-        <v>2.5</v>
+      <c r="D28" s="26" t="s">
+        <v>206</v>
       </c>
       <c r="E28" s="27" t="s">
-        <v>8</v>
+        <v>267</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>346</v>
+        <v>65</v>
       </c>
       <c r="G28" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B28),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E28),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F28),0)&gt;0), MAX($G$1:G27)+1, ""))</f>
@@ -2510,19 +2516,19 @@
         <v>15</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>259</v>
+        <v>345</v>
       </c>
       <c r="C29" s="28">
         <v>15</v>
       </c>
-      <c r="D29" s="26" t="s">
-        <v>7</v>
+      <c r="D29" s="26">
+        <v>2.5</v>
       </c>
       <c r="E29" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>261</v>
+        <v>346</v>
       </c>
       <c r="G29" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B29),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E29),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F29),0)&gt;0), MAX($G$1:G28)+1, ""))</f>
@@ -2538,19 +2544,19 @@
         <v>15</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>376</v>
+        <v>259</v>
       </c>
       <c r="C30" s="28">
         <v>15</v>
       </c>
-      <c r="D30" s="26">
-        <v>2</v>
+      <c r="D30" s="26" t="s">
+        <v>7</v>
       </c>
       <c r="E30" s="27" t="s">
-        <v>350</v>
+        <v>8</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>348</v>
+        <v>261</v>
       </c>
       <c r="G30" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B30),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E30),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F30),0)&gt;0), MAX($G$1:G29)+1, ""))</f>
@@ -2566,19 +2572,19 @@
         <v>15</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>57</v>
+        <v>376</v>
       </c>
       <c r="C31" s="28">
         <v>15</v>
       </c>
-      <c r="D31" s="26" t="s">
-        <v>223</v>
+      <c r="D31" s="26">
+        <v>2</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>8</v>
+        <v>350</v>
       </c>
       <c r="F31" s="26" t="s">
-        <v>58</v>
+        <v>348</v>
       </c>
       <c r="G31" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B31),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E31),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F31),0)&gt;0), MAX($G$1:G30)+1, ""))</f>
@@ -2594,19 +2600,19 @@
         <v>15</v>
       </c>
       <c r="B32" s="27" t="s">
-        <v>268</v>
+        <v>57</v>
       </c>
       <c r="C32" s="28">
         <v>15</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="E32" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F32" s="26" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G32" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B32),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E32),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F32),0)&gt;0), MAX($G$1:G31)+1, ""))</f>
@@ -2622,19 +2628,19 @@
         <v>15</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>306</v>
+        <v>268</v>
       </c>
       <c r="C33" s="28">
         <v>15</v>
       </c>
-      <c r="D33" s="26">
-        <v>2.1</v>
+      <c r="D33" s="26" t="s">
+        <v>205</v>
       </c>
       <c r="E33" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F33" s="26" t="s">
-        <v>307</v>
+        <v>56</v>
       </c>
       <c r="G33" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B33),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E33),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F33),0)&gt;0), MAX($G$1:G32)+1, ""))</f>
@@ -2650,19 +2656,19 @@
         <v>15</v>
       </c>
       <c r="B34" s="27" t="s">
-        <v>54</v>
+        <v>306</v>
       </c>
       <c r="C34" s="28">
         <v>15</v>
       </c>
-      <c r="D34" s="26" t="s">
-        <v>204</v>
+      <c r="D34" s="26">
+        <v>2.1</v>
       </c>
       <c r="E34" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F34" s="26" t="s">
-        <v>55</v>
+        <v>307</v>
       </c>
       <c r="G34" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B34),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E34),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F34),0)&gt;0), MAX($G$1:G33)+1, ""))</f>
@@ -2678,19 +2684,19 @@
         <v>15</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>277</v>
+        <v>54</v>
       </c>
       <c r="C35" s="28">
         <v>15</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E35" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="G35" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F35),0)&gt;0), MAX($G$1:G34)+1, ""))</f>
@@ -2706,19 +2712,19 @@
         <v>15</v>
       </c>
       <c r="B36" s="27" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="C36" s="28">
         <v>15</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>21</v>
+        <v>210</v>
       </c>
       <c r="E36" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F36" s="26" t="s">
-        <v>262</v>
+        <v>75</v>
       </c>
       <c r="G36" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B36),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E36),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F36),0)&gt;0), MAX($G$1:G35)+1, ""))</f>
@@ -2734,19 +2740,19 @@
         <v>15</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>292</v>
+        <v>260</v>
       </c>
       <c r="C37" s="28">
         <v>15</v>
       </c>
-      <c r="D37" s="26">
-        <v>2.2000000000000002</v>
+      <c r="D37" s="26" t="s">
+        <v>21</v>
       </c>
       <c r="E37" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>293</v>
+        <v>262</v>
       </c>
       <c r="G37" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F37),0)&gt;0), MAX($G$1:G36)+1, ""))</f>
@@ -2762,19 +2768,19 @@
         <v>15</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>374</v>
+        <v>292</v>
       </c>
       <c r="C38" s="28">
         <v>15</v>
       </c>
       <c r="D38" s="26">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E38" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F38" s="26" t="s">
-        <v>373</v>
+        <v>293</v>
       </c>
       <c r="G38" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F38),0)&gt;0), MAX($G$1:G37)+1, ""))</f>
@@ -2790,19 +2796,19 @@
         <v>15</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="C39" s="28">
         <v>15</v>
       </c>
       <c r="D39" s="26">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="E39" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F39" s="26" t="s">
-        <v>353</v>
+        <v>373</v>
       </c>
       <c r="G39" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B39),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E39),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F39),0)&gt;0), MAX($G$1:G38)+1, ""))</f>
@@ -2818,19 +2824,19 @@
         <v>15</v>
       </c>
       <c r="B40" s="27" t="s">
-        <v>50</v>
+        <v>352</v>
       </c>
       <c r="C40" s="28">
         <v>15</v>
       </c>
-      <c r="D40" s="26" t="s">
-        <v>213</v>
+      <c r="D40" s="26">
+        <v>1.5</v>
       </c>
       <c r="E40" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F40" s="26" t="s">
-        <v>51</v>
+        <v>353</v>
       </c>
       <c r="G40" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B40),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E40),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F40),0)&gt;0), MAX($G$1:G39)+1, ""))</f>
@@ -2846,19 +2852,19 @@
         <v>15</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>384</v>
+        <v>50</v>
       </c>
       <c r="C41" s="28">
         <v>15</v>
       </c>
-      <c r="D41" s="26">
-        <v>1.3</v>
+      <c r="D41" s="26" t="s">
+        <v>213</v>
       </c>
       <c r="E41" s="27" t="s">
-        <v>381</v>
+        <v>8</v>
       </c>
       <c r="F41" s="26" t="s">
-        <v>382</v>
+        <v>51</v>
       </c>
       <c r="G41" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B41),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E41),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F41),0)&gt;0), MAX($G$1:G40)+1, ""))</f>
@@ -2874,19 +2880,19 @@
         <v>15</v>
       </c>
       <c r="B42" s="27" t="s">
-        <v>46</v>
+        <v>390</v>
       </c>
       <c r="C42" s="28">
         <v>15</v>
       </c>
-      <c r="D42" s="26" t="s">
-        <v>233</v>
+      <c r="D42" s="26">
+        <v>1.3</v>
       </c>
       <c r="E42" s="27" t="s">
-        <v>8</v>
+        <v>381</v>
       </c>
       <c r="F42" s="26" t="s">
-        <v>47</v>
+        <v>382</v>
       </c>
       <c r="G42" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B42),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E42),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F42),0)&gt;0), MAX($G$1:G41)+1, ""))</f>
@@ -2902,19 +2908,19 @@
         <v>15</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C43" s="28">
         <v>15</v>
       </c>
       <c r="D43" s="26" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="E43" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F43" s="26" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G43" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F43),0)&gt;0), MAX($G$1:G42)+1, ""))</f>
@@ -2930,19 +2936,19 @@
         <v>15</v>
       </c>
       <c r="B44" s="27" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C44" s="28">
         <v>15</v>
       </c>
       <c r="D44" s="26" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="E44" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F44" s="26" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G44" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F44),0)&gt;0), MAX($G$1:G43)+1, ""))</f>
@@ -2958,19 +2964,19 @@
         <v>15</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>308</v>
+        <v>40</v>
       </c>
       <c r="C45" s="28">
         <v>15</v>
       </c>
-      <c r="D45" s="26">
-        <v>2.2000000000000002</v>
+      <c r="D45" s="26" t="s">
+        <v>212</v>
       </c>
       <c r="E45" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F45" s="26" t="s">
-        <v>293</v>
+        <v>41</v>
       </c>
       <c r="G45" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F45),0)&gt;0), MAX($G$1:G44)+1, ""))</f>
@@ -2986,19 +2992,19 @@
         <v>15</v>
       </c>
       <c r="B46" s="27" t="s">
-        <v>244</v>
+        <v>308</v>
       </c>
       <c r="C46" s="28">
         <v>15</v>
       </c>
       <c r="D46" s="26">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E46" s="27" t="s">
-        <v>245</v>
+        <v>8</v>
       </c>
       <c r="F46" s="26" t="s">
-        <v>202</v>
+        <v>293</v>
       </c>
       <c r="G46" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F46),0)&gt;0), MAX($G$1:G45)+1, ""))</f>
@@ -3014,22 +3020,22 @@
         <v>15</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>38</v>
+        <v>244</v>
       </c>
       <c r="C47" s="28">
         <v>15</v>
       </c>
-      <c r="D47" s="26" t="s">
-        <v>211</v>
+      <c r="D47" s="26">
+        <v>2.1</v>
       </c>
       <c r="E47" s="27" t="s">
-        <v>8</v>
+        <v>245</v>
       </c>
       <c r="F47" s="26" t="s">
-        <v>39</v>
+        <v>202</v>
       </c>
       <c r="G47" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F47),0)&gt;0), MAX($G$1:G42)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F47),0)&gt;0), MAX($G$1:G46)+1, ""))</f>
         <v/>
       </c>
       <c r="H47" s="21" t="b">
@@ -3042,22 +3048,22 @@
         <v>15</v>
       </c>
       <c r="B48" s="27" t="s">
-        <v>341</v>
+        <v>38</v>
       </c>
       <c r="C48" s="28">
         <v>15</v>
       </c>
-      <c r="D48" s="26">
-        <v>1.4</v>
+      <c r="D48" s="26" t="s">
+        <v>211</v>
       </c>
       <c r="E48" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F48" s="26" t="s">
-        <v>347</v>
+        <v>39</v>
       </c>
       <c r="G48" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F48),0)&gt;0), MAX($G$1:G47)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F48),0)&gt;0), MAX($G$1:G43)+1, ""))</f>
         <v/>
       </c>
       <c r="H48" s="21" t="b">
@@ -3070,19 +3076,19 @@
         <v>15</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>34</v>
+        <v>341</v>
       </c>
       <c r="C49" s="28">
         <v>15</v>
       </c>
-      <c r="D49" s="26" t="s">
-        <v>210</v>
+      <c r="D49" s="26">
+        <v>1.4</v>
       </c>
       <c r="E49" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F49" s="26" t="s">
-        <v>35</v>
+        <v>347</v>
       </c>
       <c r="G49" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F49),0)&gt;0), MAX($G$1:G48)+1, ""))</f>
@@ -3098,19 +3104,19 @@
         <v>15</v>
       </c>
       <c r="B50" s="27" t="s">
-        <v>385</v>
+        <v>34</v>
       </c>
       <c r="C50" s="28">
         <v>15</v>
       </c>
-      <c r="D50" s="26">
-        <v>1.2</v>
+      <c r="D50" s="26" t="s">
+        <v>210</v>
       </c>
       <c r="E50" s="27" t="s">
-        <v>381</v>
+        <v>8</v>
       </c>
       <c r="F50" s="26" t="s">
-        <v>382</v>
+        <v>35</v>
       </c>
       <c r="G50" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F50),0)&gt;0), MAX($G$1:G49)+1, ""))</f>
@@ -3126,19 +3132,19 @@
         <v>15</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>280</v>
+        <v>383</v>
       </c>
       <c r="C51" s="28">
         <v>15</v>
       </c>
-      <c r="D51" s="26" t="s">
-        <v>209</v>
+      <c r="D51" s="26">
+        <v>1.2</v>
       </c>
       <c r="E51" s="27" t="s">
-        <v>267</v>
+        <v>381</v>
       </c>
       <c r="F51" s="26" t="s">
-        <v>33</v>
+        <v>382</v>
       </c>
       <c r="G51" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F51),0)&gt;0), MAX($G$1:G50)+1, ""))</f>
@@ -3150,23 +3156,23 @@
       </c>
     </row>
     <row r="52" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="33">
-        <v>17</v>
-      </c>
-      <c r="B52" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="C52" s="35">
-        <v>17</v>
-      </c>
-      <c r="D52" s="33" t="s">
-        <v>214</v>
-      </c>
-      <c r="E52" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F52" s="33" t="s">
-        <v>71</v>
+      <c r="A52" s="26">
+        <v>15</v>
+      </c>
+      <c r="B52" s="27" t="s">
+        <v>280</v>
+      </c>
+      <c r="C52" s="28">
+        <v>15</v>
+      </c>
+      <c r="D52" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="E52" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="F52" s="26" t="s">
+        <v>33</v>
       </c>
       <c r="G52" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F52),0)&gt;0), MAX($G$1:G51)+1, ""))</f>
@@ -3182,19 +3188,19 @@
         <v>17</v>
       </c>
       <c r="B53" s="34" t="s">
-        <v>281</v>
+        <v>70</v>
       </c>
       <c r="C53" s="35">
         <v>17</v>
       </c>
       <c r="D53" s="33" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="E53" s="34" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="F53" s="33" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G53" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F53),0)&gt;0), MAX($G$1:G52)+1, ""))</f>
@@ -3206,53 +3212,53 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A54" s="26">
+      <c r="A54" s="33">
         <v>17</v>
       </c>
-      <c r="B54" s="27" t="s">
-        <v>313</v>
-      </c>
-      <c r="C54" s="28">
+      <c r="B54" s="34" t="s">
+        <v>281</v>
+      </c>
+      <c r="C54" s="35">
         <v>17</v>
       </c>
-      <c r="D54" s="26">
-        <v>1.7</v>
-      </c>
-      <c r="E54" s="27" t="s">
+      <c r="D54" s="33" t="s">
+        <v>222</v>
+      </c>
+      <c r="E54" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="F54" s="26" t="s">
-        <v>319</v>
-      </c>
-      <c r="G54" s="29"/>
+      <c r="F54" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="G54" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F54),0)&gt;0), MAX($G$1:G53)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H54" s="21" t="b">
         <f>A54=C54</f>
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="33">
+      <c r="A55" s="26">
         <v>17</v>
       </c>
-      <c r="B55" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="C55" s="35">
+      <c r="B55" s="27" t="s">
+        <v>313</v>
+      </c>
+      <c r="C55" s="28">
         <v>17</v>
       </c>
-      <c r="D55" s="33" t="s">
-        <v>215</v>
-      </c>
-      <c r="E55" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F55" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="G55" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F55),0)&gt;0), MAX($G$1:G54)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D55" s="26">
+        <v>1.7</v>
+      </c>
+      <c r="E55" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F55" s="26" t="s">
+        <v>319</v>
+      </c>
+      <c r="G55" s="29"/>
       <c r="H55" s="21" t="b">
         <f>A55=C55</f>
         <v>1</v>
@@ -3263,19 +3269,19 @@
         <v>17</v>
       </c>
       <c r="B56" s="34" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C56" s="35">
         <v>17</v>
       </c>
       <c r="D56" s="33" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E56" s="34" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="F56" s="33" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G56" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F56),0)&gt;0), MAX($G$1:G55)+1, ""))</f>
@@ -3287,25 +3293,28 @@
       </c>
     </row>
     <row r="57" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A57" s="26">
+      <c r="A57" s="33">
         <v>17</v>
       </c>
-      <c r="B57" s="27" t="s">
-        <v>315</v>
-      </c>
-      <c r="C57" s="28">
+      <c r="B57" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="C57" s="35">
         <v>17</v>
       </c>
-      <c r="D57" s="26">
-        <v>3</v>
-      </c>
-      <c r="E57" s="27" t="s">
+      <c r="D57" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="E57" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="F57" s="26" t="s">
-        <v>321</v>
-      </c>
-      <c r="G57" s="29"/>
+      <c r="F57" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="G57" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F57),0)&gt;0), MAX($G$1:G56)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H57" s="21" t="b">
         <f>A57=C57</f>
         <v>1</v>
@@ -3316,24 +3325,21 @@
         <v>17</v>
       </c>
       <c r="B58" s="27" t="s">
-        <v>340</v>
+        <v>315</v>
       </c>
       <c r="C58" s="28">
         <v>17</v>
       </c>
       <c r="D58" s="26">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="E58" s="27" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F58" s="26" t="s">
-        <v>349</v>
-      </c>
-      <c r="G58" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F58),0)&gt;0), MAX($G$1:G56)+1, ""))</f>
-        <v/>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="G58" s="29"/>
       <c r="H58" s="21" t="b">
         <f>A58=C58</f>
         <v>1</v>
@@ -3344,74 +3350,77 @@
         <v>17</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>316</v>
+        <v>340</v>
       </c>
       <c r="C59" s="28">
         <v>17</v>
       </c>
       <c r="D59" s="26">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="E59" s="27" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="F59" s="26" t="s">
-        <v>322</v>
-      </c>
-      <c r="G59" s="29"/>
+        <v>349</v>
+      </c>
+      <c r="G59" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F59),0)&gt;0), MAX($G$1:G57)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H59" s="21" t="b">
         <f>A59=C59</f>
         <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A60" s="36">
+      <c r="A60" s="26">
         <v>17</v>
       </c>
-      <c r="B60" s="37" t="s">
-        <v>289</v>
-      </c>
-      <c r="C60" s="38">
+      <c r="B60" s="27" t="s">
+        <v>316</v>
+      </c>
+      <c r="C60" s="28">
         <v>17</v>
       </c>
-      <c r="D60" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="E60" s="37" t="s">
+      <c r="D60" s="26">
+        <v>1.9</v>
+      </c>
+      <c r="E60" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="F60" s="36" t="s">
-        <v>111</v>
-      </c>
-      <c r="G60" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F60),0)&gt;0), MAX($G$1:G59)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="F60" s="26" t="s">
+        <v>322</v>
+      </c>
+      <c r="G60" s="29"/>
       <c r="H60" s="21" t="b">
         <f>A60=C60</f>
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A61" s="26">
+      <c r="A61" s="36">
         <v>17</v>
       </c>
-      <c r="B61" s="27" t="s">
-        <v>314</v>
-      </c>
-      <c r="C61" s="28">
+      <c r="B61" s="37" t="s">
+        <v>289</v>
+      </c>
+      <c r="C61" s="38">
         <v>17</v>
       </c>
-      <c r="D61" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E61" s="27" t="s">
+      <c r="D61" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E61" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="F61" s="26" t="s">
-        <v>320</v>
-      </c>
-      <c r="G61" s="29"/>
+      <c r="F61" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="G61" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F61),0)&gt;0), MAX($G$1:G60)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H61" s="21" t="b">
         <f>A61=C61</f>
         <v>1</v>
@@ -3422,19 +3431,19 @@
         <v>17</v>
       </c>
       <c r="B62" s="27" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C62" s="28">
         <v>17</v>
       </c>
       <c r="D62" s="26">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E62" s="27" t="s">
         <v>60</v>
       </c>
       <c r="F62" s="26" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="G62" s="29"/>
       <c r="H62" s="21" t="b">
@@ -3443,28 +3452,25 @@
       </c>
     </row>
     <row r="63" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A63" s="36">
+      <c r="A63" s="26">
         <v>17</v>
       </c>
-      <c r="B63" s="37" t="s">
-        <v>106</v>
-      </c>
-      <c r="C63" s="38">
+      <c r="B63" s="27" t="s">
+        <v>317</v>
+      </c>
+      <c r="C63" s="28">
         <v>17</v>
       </c>
-      <c r="D63" s="36" t="s">
-        <v>220</v>
-      </c>
-      <c r="E63" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F63" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="G63" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F63),0)&gt;0), MAX($G$1:G62)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D63" s="26">
+        <v>2</v>
+      </c>
+      <c r="E63" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F63" s="26" t="s">
+        <v>323</v>
+      </c>
+      <c r="G63" s="29"/>
       <c r="H63" s="21" t="b">
         <f>A63=C63</f>
         <v>1</v>
@@ -3475,19 +3481,19 @@
         <v>17</v>
       </c>
       <c r="B64" s="37" t="s">
-        <v>303</v>
+        <v>106</v>
       </c>
       <c r="C64" s="38">
         <v>17</v>
       </c>
       <c r="D64" s="36" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="E64" s="37" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="F64" s="36" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G64" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F64),0)&gt;0), MAX($G$1:G63)+1, ""))</f>
@@ -3499,26 +3505,26 @@
       </c>
     </row>
     <row r="65" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A65" s="33">
+      <c r="A65" s="36">
         <v>17</v>
       </c>
-      <c r="B65" s="34" t="s">
-        <v>52</v>
-      </c>
-      <c r="C65" s="35">
+      <c r="B65" s="37" t="s">
+        <v>303</v>
+      </c>
+      <c r="C65" s="38">
         <v>17</v>
       </c>
-      <c r="D65" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="E65" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F65" s="33" t="s">
-        <v>53</v>
+      <c r="D65" s="36" t="s">
+        <v>229</v>
+      </c>
+      <c r="E65" s="37" t="s">
+        <v>304</v>
+      </c>
+      <c r="F65" s="36" t="s">
+        <v>105</v>
       </c>
       <c r="G65" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F65),0)&gt;0), MAX($G$1:G61)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F65),0)&gt;0), MAX($G$1:G64)+1, ""))</f>
         <v/>
       </c>
       <c r="H65" s="21" t="b">
@@ -3527,26 +3533,26 @@
       </c>
     </row>
     <row r="66" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A66" s="26">
+      <c r="A66" s="33">
         <v>17</v>
       </c>
-      <c r="B66" s="27" t="s">
-        <v>368</v>
-      </c>
-      <c r="C66" s="28">
+      <c r="B66" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="C66" s="35">
         <v>17</v>
       </c>
-      <c r="D66" s="26">
-        <v>1.8</v>
-      </c>
-      <c r="E66" s="27" t="s">
+      <c r="D66" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="E66" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F66" s="26" t="s">
-        <v>354</v>
+      <c r="F66" s="33" t="s">
+        <v>53</v>
       </c>
       <c r="G66" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F66),0)&gt;0), MAX($G$1:G65)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F66),0)&gt;0), MAX($G$1:G62)+1, ""))</f>
         <v/>
       </c>
       <c r="H66" s="21" t="b">
@@ -3559,15 +3565,15 @@
         <v>17</v>
       </c>
       <c r="B67" s="27" t="s">
-        <v>390</v>
+        <v>368</v>
       </c>
       <c r="C67" s="28">
         <v>17</v>
       </c>
       <c r="D67" s="26">
-        <v>1.4</v>
-      </c>
-      <c r="E67" s="31" t="s">
+        <v>1.8</v>
+      </c>
+      <c r="E67" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F67" s="26" t="s">
@@ -3587,19 +3593,19 @@
         <v>17</v>
       </c>
       <c r="B68" s="27" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="C68" s="28">
         <v>17</v>
       </c>
       <c r="D68" s="26">
-        <v>1.2</v>
-      </c>
-      <c r="E68" s="27" t="s">
+        <v>1.4</v>
+      </c>
+      <c r="E68" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F68" s="26" t="s">
-        <v>380</v>
+        <v>354</v>
       </c>
       <c r="G68" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F68),0)&gt;0), MAX($G$1:G67)+1, ""))</f>
@@ -3611,23 +3617,23 @@
       </c>
     </row>
     <row r="69" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A69" s="33">
+      <c r="A69" s="26">
         <v>17</v>
       </c>
-      <c r="B69" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="C69" s="35">
+      <c r="B69" s="27" t="s">
+        <v>379</v>
+      </c>
+      <c r="C69" s="28">
         <v>17</v>
       </c>
-      <c r="D69" s="33" t="s">
-        <v>211</v>
-      </c>
-      <c r="E69" s="34" t="s">
+      <c r="D69" s="26">
+        <v>1.2</v>
+      </c>
+      <c r="E69" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F69" s="33" t="s">
-        <v>49</v>
+      <c r="F69" s="26" t="s">
+        <v>380</v>
       </c>
       <c r="G69" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F69),0)&gt;0), MAX($G$1:G68)+1, ""))</f>
@@ -3639,23 +3645,23 @@
       </c>
     </row>
     <row r="70" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A70" s="36">
+      <c r="A70" s="33">
         <v>17</v>
       </c>
-      <c r="B70" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="C70" s="38">
+      <c r="B70" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="C70" s="35">
         <v>17</v>
       </c>
-      <c r="D70" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="E70" s="37" t="s">
+      <c r="D70" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="E70" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F70" s="36" t="s">
-        <v>98</v>
+      <c r="F70" s="33" t="s">
+        <v>49</v>
       </c>
       <c r="G70" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F70),0)&gt;0), MAX($G$1:G69)+1, ""))</f>
@@ -3667,23 +3673,23 @@
       </c>
     </row>
     <row r="71" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A71" s="26">
+      <c r="A71" s="36">
         <v>17</v>
       </c>
-      <c r="B71" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="C71" s="28">
+      <c r="B71" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="C71" s="38">
         <v>17</v>
       </c>
-      <c r="D71" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="E71" s="27" t="s">
+      <c r="D71" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E71" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F71" s="26" t="s">
-        <v>43</v>
+      <c r="F71" s="36" t="s">
+        <v>98</v>
       </c>
       <c r="G71" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F71),0)&gt;0), MAX($G$1:G70)+1, ""))</f>
@@ -3695,23 +3701,23 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A72" s="36">
+      <c r="A72" s="26">
         <v>17</v>
       </c>
-      <c r="B72" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="C72" s="38">
+      <c r="B72" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C72" s="28">
         <v>17</v>
       </c>
-      <c r="D72" s="36" t="s">
-        <v>217</v>
-      </c>
-      <c r="E72" s="37" t="s">
+      <c r="D72" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="E72" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F72" s="36" t="s">
-        <v>94</v>
+      <c r="F72" s="26" t="s">
+        <v>43</v>
       </c>
       <c r="G72" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F72),0)&gt;0), MAX($G$1:G71)+1, ""))</f>
@@ -3723,28 +3729,30 @@
       </c>
     </row>
     <row r="73" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A73" s="33">
+      <c r="A73" s="36">
         <v>17</v>
       </c>
-      <c r="B73" s="34" t="s">
-        <v>327</v>
-      </c>
-      <c r="C73" s="35">
+      <c r="B73" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="C73" s="38">
         <v>17</v>
       </c>
-      <c r="D73" s="33">
-        <v>1.9</v>
-      </c>
-      <c r="E73" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F73" s="33" t="s">
-        <v>329</v>
-      </c>
-      <c r="G73" s="29" t="s">
-        <v>326</v>
+      <c r="D73" s="36" t="s">
+        <v>217</v>
+      </c>
+      <c r="E73" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F73" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="G73" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F73),0)&gt;0), MAX($G$1:G72)+1, ""))</f>
+        <v/>
       </c>
       <c r="H73" s="21" t="b">
+        <f>A73=C73</f>
         <v>1</v>
       </c>
     </row>
@@ -3753,7 +3761,7 @@
         <v>17</v>
       </c>
       <c r="B74" s="34" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C74" s="35">
         <v>17</v>
@@ -3779,7 +3787,7 @@
         <v>17</v>
       </c>
       <c r="B75" s="34" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C75" s="35">
         <v>17</v>
@@ -3805,47 +3813,45 @@
         <v>17</v>
       </c>
       <c r="B76" s="34" t="s">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="C76" s="35">
         <v>17</v>
       </c>
-      <c r="D76" s="33" t="s">
+      <c r="D76" s="33">
+        <v>1.9</v>
+      </c>
+      <c r="E76" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="F76" s="33" t="s">
+        <v>329</v>
+      </c>
+      <c r="G76" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="H76" s="21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A77" s="33">
+        <v>17</v>
+      </c>
+      <c r="B77" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="C77" s="35">
+        <v>17</v>
+      </c>
+      <c r="D77" s="33" t="s">
         <v>214</v>
       </c>
-      <c r="E76" s="34" t="s">
+      <c r="E77" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F76" s="33" t="s">
+      <c r="F77" s="33" t="s">
         <v>37</v>
-      </c>
-      <c r="G76" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F76),0)&gt;0), MAX($G$1:G75)+1, ""))</f>
-        <v/>
-      </c>
-      <c r="H76" s="21" t="b">
-        <f>A76=C76</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A77" s="36">
-        <v>17</v>
-      </c>
-      <c r="B77" s="37" t="s">
-        <v>83</v>
-      </c>
-      <c r="C77" s="38">
-        <v>17</v>
-      </c>
-      <c r="D77" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="E77" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F77" s="36" t="s">
-        <v>84</v>
       </c>
       <c r="G77" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F77),0)&gt;0), MAX($G$1:G76)+1, ""))</f>
@@ -3857,23 +3863,23 @@
       </c>
     </row>
     <row r="78" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A78" s="33">
+      <c r="A78" s="36">
         <v>17</v>
       </c>
-      <c r="B78" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="35">
+      <c r="B78" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="C78" s="38">
         <v>17</v>
       </c>
-      <c r="D78" s="33" t="s">
-        <v>208</v>
-      </c>
-      <c r="E78" s="34" t="s">
+      <c r="D78" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E78" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F78" s="33" t="s">
-        <v>32</v>
+      <c r="F78" s="36" t="s">
+        <v>84</v>
       </c>
       <c r="G78" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F78),0)&gt;0), MAX($G$1:G77)+1, ""))</f>
@@ -3889,52 +3895,52 @@
         <v>17</v>
       </c>
       <c r="B79" s="34" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C79" s="35">
         <v>17</v>
       </c>
       <c r="D79" s="33" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E79" s="34" t="s">
         <v>8</v>
       </c>
       <c r="F79" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="G79" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F79),0)&gt;0), MAX($G$1:G78)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H79" s="21" t="b">
+        <f>A79=C79</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A80" s="33">
+        <v>17</v>
+      </c>
+      <c r="B80" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="C80" s="35">
+        <v>17</v>
+      </c>
+      <c r="D80" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="E80" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F80" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="G79" s="29" t="s">
+      <c r="G80" s="29" t="s">
         <v>326</v>
       </c>
-      <c r="H79" s="21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A80" s="30">
-        <v>20</v>
-      </c>
-      <c r="B80" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="C80" s="32">
-        <v>20</v>
-      </c>
-      <c r="D80" s="30" t="s">
-        <v>206</v>
-      </c>
-      <c r="E80" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F80" s="30" t="s">
-        <v>147</v>
-      </c>
-      <c r="G80" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E80),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F80),0)&gt;0), MAX($G$1:G76)+1, ""))</f>
-        <v/>
-      </c>
       <c r="H80" s="21" t="b">
-        <f>A80=C80</f>
         <v>1</v>
       </c>
     </row>
@@ -3943,22 +3949,22 @@
         <v>20</v>
       </c>
       <c r="B81" s="31" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C81" s="32">
         <v>20</v>
       </c>
       <c r="D81" s="30" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E81" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F81" s="30" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G81" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F81),0)&gt;0), MAX($G$1:G80)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F81),0)&gt;0), MAX($G$1:G77)+1, ""))</f>
         <v/>
       </c>
       <c r="H81" s="21" t="b">
@@ -3967,23 +3973,23 @@
       </c>
     </row>
     <row r="82" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A82" s="26">
+      <c r="A82" s="30">
         <v>20</v>
       </c>
-      <c r="B82" s="27" t="s">
-        <v>386</v>
-      </c>
-      <c r="C82" s="28">
+      <c r="B82" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="C82" s="32">
         <v>20</v>
       </c>
-      <c r="D82" s="26">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="E82" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="F82" s="26" t="s">
-        <v>387</v>
+      <c r="D82" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="E82" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F82" s="30" t="s">
+        <v>145</v>
       </c>
       <c r="G82" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F82),0)&gt;0), MAX($G$1:G81)+1, ""))</f>
@@ -3995,26 +4001,26 @@
       </c>
     </row>
     <row r="83" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A83" s="30">
+      <c r="A83" s="26">
         <v>20</v>
       </c>
-      <c r="B83" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="C83" s="32">
+      <c r="B83" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="C83" s="28">
         <v>20</v>
       </c>
-      <c r="D83" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="E83" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F83" s="30" t="s">
-        <v>143</v>
+      <c r="D83" s="26">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E83" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F83" s="26" t="s">
+        <v>385</v>
       </c>
       <c r="G83" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F83),0)&gt;0), MAX($G$1:G81)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F83),0)&gt;0), MAX($G$1:G82)+1, ""))</f>
         <v/>
       </c>
       <c r="H83" s="21" t="b">
@@ -4027,22 +4033,22 @@
         <v>20</v>
       </c>
       <c r="B84" s="31" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C84" s="32">
         <v>20</v>
       </c>
       <c r="D84" s="30" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="E84" s="31" t="s">
-        <v>305</v>
+        <v>8</v>
       </c>
       <c r="F84" s="30" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G84" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F84),0)&gt;0), MAX($G$1:G83)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F84),0)&gt;0), MAX($G$1:G82)+1, ""))</f>
         <v/>
       </c>
       <c r="H84" s="21" t="b">
@@ -4051,25 +4057,28 @@
       </c>
     </row>
     <row r="85" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A85" s="36">
+      <c r="A85" s="30">
         <v>20</v>
       </c>
-      <c r="B85" s="37" t="s">
-        <v>333</v>
-      </c>
-      <c r="C85" s="38">
+      <c r="B85" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="C85" s="32">
         <v>20</v>
       </c>
-      <c r="D85" s="36">
-        <v>3.4</v>
-      </c>
-      <c r="E85" s="37" t="s">
-        <v>336</v>
-      </c>
-      <c r="F85" s="36" t="s">
-        <v>334</v>
-      </c>
-      <c r="G85" s="29"/>
+      <c r="D85" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="E85" s="31" t="s">
+        <v>305</v>
+      </c>
+      <c r="F85" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="G85" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F85),0)&gt;0), MAX($G$1:G84)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H85" s="21" t="b">
         <f>A85=C85</f>
         <v>1</v>
@@ -4080,19 +4089,19 @@
         <v>20</v>
       </c>
       <c r="B86" s="37" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C86" s="38">
         <v>20</v>
       </c>
       <c r="D86" s="36">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="E86" s="37" t="s">
         <v>336</v>
       </c>
       <c r="F86" s="36" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G86" s="29"/>
       <c r="H86" s="21" t="b">
@@ -4101,28 +4110,25 @@
       </c>
     </row>
     <row r="87" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A87" s="30">
+      <c r="A87" s="36">
         <v>20</v>
       </c>
-      <c r="B87" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="C87" s="32">
+      <c r="B87" s="37" t="s">
+        <v>331</v>
+      </c>
+      <c r="C87" s="38">
         <v>20</v>
       </c>
-      <c r="D87" s="30" t="s">
-        <v>223</v>
-      </c>
-      <c r="E87" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F87" s="30" t="s">
-        <v>139</v>
-      </c>
-      <c r="G87" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F87),0)&gt;0), MAX($G$1:G86)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D87" s="36">
+        <v>3.3</v>
+      </c>
+      <c r="E87" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="F87" s="36" t="s">
+        <v>332</v>
+      </c>
+      <c r="G87" s="29"/>
       <c r="H87" s="21" t="b">
         <f>A87=C87</f>
         <v>1</v>
@@ -4133,19 +4139,19 @@
         <v>20</v>
       </c>
       <c r="B88" s="31" t="s">
-        <v>255</v>
+        <v>138</v>
       </c>
       <c r="C88" s="32">
         <v>20</v>
       </c>
       <c r="D88" s="30" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E88" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F88" s="30" t="s">
-        <v>256</v>
+        <v>139</v>
       </c>
       <c r="G88" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F88),0)&gt;0), MAX($G$1:G87)+1, ""))</f>
@@ -4161,19 +4167,19 @@
         <v>20</v>
       </c>
       <c r="B89" s="31" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C89" s="32">
         <v>20</v>
       </c>
-      <c r="D89" s="30">
-        <v>4.2</v>
+      <c r="D89" s="30" t="s">
+        <v>225</v>
       </c>
       <c r="E89" s="31" t="s">
-        <v>305</v>
-      </c>
-      <c r="F89" s="30">
-        <v>21765430</v>
+        <v>8</v>
+      </c>
+      <c r="F89" s="30" t="s">
+        <v>256</v>
       </c>
       <c r="G89" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F89),0)&gt;0), MAX($G$1:G88)+1, ""))</f>
@@ -4189,19 +4195,19 @@
         <v>20</v>
       </c>
       <c r="B90" s="31" t="s">
-        <v>136</v>
+        <v>254</v>
       </c>
       <c r="C90" s="32">
         <v>20</v>
       </c>
-      <c r="D90" s="30" t="s">
-        <v>210</v>
+      <c r="D90" s="30">
+        <v>4.2</v>
       </c>
       <c r="E90" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F90" s="30" t="s">
-        <v>137</v>
+        <v>305</v>
+      </c>
+      <c r="F90" s="30">
+        <v>21765430</v>
       </c>
       <c r="G90" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F90),0)&gt;0), MAX($G$1:G89)+1, ""))</f>
@@ -4217,19 +4223,19 @@
         <v>20</v>
       </c>
       <c r="B91" s="31" t="s">
-        <v>265</v>
+        <v>136</v>
       </c>
       <c r="C91" s="32">
         <v>20</v>
       </c>
       <c r="D91" s="30" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="E91" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F91" s="30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G91" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F91),0)&gt;0), MAX($G$1:G90)+1, ""))</f>
@@ -4245,19 +4251,19 @@
         <v>20</v>
       </c>
       <c r="B92" s="31" t="s">
-        <v>133</v>
+        <v>265</v>
       </c>
       <c r="C92" s="32">
         <v>20</v>
       </c>
       <c r="D92" s="30" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E92" s="31" t="s">
-        <v>305</v>
+        <v>8</v>
       </c>
       <c r="F92" s="30" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G92" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F92),0)&gt;0), MAX($G$1:G91)+1, ""))</f>
@@ -4273,19 +4279,19 @@
         <v>20</v>
       </c>
       <c r="B93" s="31" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C93" s="32">
         <v>20</v>
       </c>
       <c r="D93" s="30" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E93" s="31" t="s">
-        <v>131</v>
+        <v>305</v>
       </c>
       <c r="F93" s="30" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G93" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F93),0)&gt;0), MAX($G$1:G92)+1, ""))</f>
@@ -4297,23 +4303,23 @@
       </c>
     </row>
     <row r="94" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A94" s="26">
+      <c r="A94" s="30">
         <v>20</v>
       </c>
-      <c r="B94" s="27" t="s">
-        <v>312</v>
-      </c>
-      <c r="C94" s="28">
+      <c r="B94" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="C94" s="32">
         <v>20</v>
       </c>
-      <c r="D94" s="26">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="E94" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="F94" s="26" t="s">
-        <v>318</v>
+      <c r="D94" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="E94" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="F94" s="30" t="s">
+        <v>132</v>
       </c>
       <c r="G94" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F94),0)&gt;0), MAX($G$1:G93)+1, ""))</f>
@@ -4329,19 +4335,19 @@
         <v>20</v>
       </c>
       <c r="B95" s="27" t="s">
-        <v>389</v>
+        <v>312</v>
       </c>
       <c r="C95" s="28">
         <v>20</v>
       </c>
       <c r="D95" s="26">
-        <v>2.5</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E95" s="27" t="s">
         <v>60</v>
       </c>
       <c r="F95" s="26" t="s">
-        <v>388</v>
+        <v>318</v>
       </c>
       <c r="G95" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F95),0)&gt;0), MAX($G$1:G94)+1, ""))</f>
@@ -4353,23 +4359,23 @@
       </c>
     </row>
     <row r="96" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A96" s="30">
+      <c r="A96" s="26">
         <v>20</v>
       </c>
-      <c r="B96" s="31" t="s">
-        <v>128</v>
-      </c>
-      <c r="C96" s="32">
+      <c r="B96" s="27" t="s">
+        <v>387</v>
+      </c>
+      <c r="C96" s="28">
         <v>20</v>
       </c>
-      <c r="D96" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="E96" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F96" s="30" t="s">
-        <v>129</v>
+      <c r="D96" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E96" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F96" s="26" t="s">
+        <v>386</v>
       </c>
       <c r="G96" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F96),0)&gt;0), MAX($G$1:G95)+1, ""))</f>
@@ -4385,19 +4391,19 @@
         <v>20</v>
       </c>
       <c r="B97" s="31" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C97" s="32">
         <v>20</v>
       </c>
       <c r="D97" s="30" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="E97" s="31" t="s">
-        <v>305</v>
+        <v>8</v>
       </c>
       <c r="F97" s="30" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G97" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F97),0)&gt;0), MAX($G$1:G96)+1, ""))</f>
@@ -4409,23 +4415,23 @@
       </c>
     </row>
     <row r="98" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A98" s="26">
+      <c r="A98" s="30">
         <v>20</v>
       </c>
-      <c r="B98" s="27" t="s">
-        <v>375</v>
-      </c>
-      <c r="C98" s="28">
+      <c r="B98" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="C98" s="32">
         <v>20</v>
       </c>
-      <c r="D98" s="26">
-        <v>2.7</v>
-      </c>
-      <c r="E98" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="F98" s="26" t="s">
-        <v>351</v>
+      <c r="D98" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="E98" s="31" t="s">
+        <v>305</v>
+      </c>
+      <c r="F98" s="30" t="s">
+        <v>127</v>
       </c>
       <c r="G98" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F98),0)&gt;0), MAX($G$1:G97)+1, ""))</f>
@@ -4437,23 +4443,23 @@
       </c>
     </row>
     <row r="99" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A99" s="30">
+      <c r="A99" s="26">
         <v>20</v>
       </c>
-      <c r="B99" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="C99" s="32">
+      <c r="B99" s="27" t="s">
+        <v>375</v>
+      </c>
+      <c r="C99" s="28">
         <v>20</v>
       </c>
-      <c r="D99" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="E99" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F99" s="30" t="s">
-        <v>125</v>
+      <c r="D99" s="26">
+        <v>2.7</v>
+      </c>
+      <c r="E99" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="F99" s="26" t="s">
+        <v>351</v>
       </c>
       <c r="G99" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F99),0)&gt;0), MAX($G$1:G98)+1, ""))</f>
@@ -4469,19 +4475,19 @@
         <v>20</v>
       </c>
       <c r="B100" s="31" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C100" s="32">
         <v>20</v>
       </c>
       <c r="D100" s="30" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="E100" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F100" s="30" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G100" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F100),0)&gt;0), MAX($G$1:G99)+1, ""))</f>
@@ -4497,19 +4503,19 @@
         <v>20</v>
       </c>
       <c r="B101" s="31" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C101" s="32">
         <v>20</v>
       </c>
       <c r="D101" s="30" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="E101" s="31" t="s">
-        <v>305</v>
+        <v>8</v>
       </c>
       <c r="F101" s="30" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G101" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F101),0)&gt;0), MAX($G$1:G100)+1, ""))</f>
@@ -4521,23 +4527,23 @@
       </c>
     </row>
     <row r="102" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A102" s="26">
+      <c r="A102" s="30">
         <v>20</v>
       </c>
-      <c r="B102" s="27" t="s">
-        <v>369</v>
-      </c>
-      <c r="C102" s="28">
+      <c r="B102" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="C102" s="32">
         <v>20</v>
       </c>
-      <c r="D102" s="26">
-        <v>1.5</v>
+      <c r="D102" s="30" t="s">
+        <v>223</v>
       </c>
       <c r="E102" s="31" t="s">
-        <v>299</v>
-      </c>
-      <c r="F102" s="26" t="s">
-        <v>370</v>
+        <v>305</v>
+      </c>
+      <c r="F102" s="30" t="s">
+        <v>121</v>
       </c>
       <c r="G102" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F102),0)&gt;0), MAX($G$1:G101)+1, ""))</f>
@@ -4549,23 +4555,23 @@
       </c>
     </row>
     <row r="103" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A103" s="30">
+      <c r="A103" s="26">
         <v>20</v>
       </c>
-      <c r="B103" s="31" t="s">
-        <v>257</v>
-      </c>
-      <c r="C103" s="32">
+      <c r="B103" s="27" t="s">
+        <v>369</v>
+      </c>
+      <c r="C103" s="28">
         <v>20</v>
       </c>
-      <c r="D103" s="30" t="s">
-        <v>225</v>
+      <c r="D103" s="26">
+        <v>1.5</v>
       </c>
       <c r="E103" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F103" s="30" t="s">
-        <v>258</v>
+        <v>299</v>
+      </c>
+      <c r="F103" s="26" t="s">
+        <v>370</v>
       </c>
       <c r="G103" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F103),0)&gt;0), MAX($G$1:G102)+1, ""))</f>
@@ -4581,19 +4587,19 @@
         <v>20</v>
       </c>
       <c r="B104" s="31" t="s">
-        <v>118</v>
+        <v>257</v>
       </c>
       <c r="C104" s="32">
         <v>20</v>
       </c>
       <c r="D104" s="30" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E104" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F104" s="30" t="s">
-        <v>119</v>
+        <v>258</v>
       </c>
       <c r="G104" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F104),0)&gt;0), MAX($G$1:G103)+1, ""))</f>
@@ -4609,19 +4615,19 @@
         <v>20</v>
       </c>
       <c r="B105" s="31" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C105" s="32">
         <v>20</v>
       </c>
       <c r="D105" s="30" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="E105" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F105" s="30" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G105" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F105),0)&gt;0), MAX($G$1:G104)+1, ""))</f>
@@ -4637,19 +4643,19 @@
         <v>20</v>
       </c>
       <c r="B106" s="31" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C106" s="32">
         <v>20</v>
       </c>
       <c r="D106" s="30" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E106" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F106" s="30" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G106" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F106),0)&gt;0), MAX($G$1:G105)+1, ""))</f>
@@ -4661,23 +4667,23 @@
       </c>
     </row>
     <row r="107" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A107" s="26">
+      <c r="A107" s="30">
         <v>20</v>
       </c>
-      <c r="B107" s="27" t="s">
-        <v>297</v>
-      </c>
-      <c r="C107" s="28">
+      <c r="B107" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="C107" s="32">
         <v>20</v>
       </c>
-      <c r="D107" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E107" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="F107" s="26" t="s">
-        <v>298</v>
+      <c r="D107" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="E107" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F107" s="30" t="s">
+        <v>115</v>
       </c>
       <c r="G107" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F107),0)&gt;0), MAX($G$1:G106)+1, ""))</f>
@@ -4689,23 +4695,23 @@
       </c>
     </row>
     <row r="108" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A108" s="30">
+      <c r="A108" s="26">
         <v>20</v>
       </c>
-      <c r="B108" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="C108" s="32">
+      <c r="B108" s="27" t="s">
+        <v>297</v>
+      </c>
+      <c r="C108" s="28">
         <v>20</v>
       </c>
-      <c r="D108" s="30" t="s">
-        <v>219</v>
-      </c>
-      <c r="E108" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F108" s="30" t="s">
-        <v>113</v>
+      <c r="D108" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E108" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="F108" s="26" t="s">
+        <v>298</v>
       </c>
       <c r="G108" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F108),0)&gt;0), MAX($G$1:G107)+1, ""))</f>
@@ -4721,19 +4727,19 @@
         <v>20</v>
       </c>
       <c r="B109" s="31" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C109" s="32">
         <v>20</v>
       </c>
       <c r="D109" s="30" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E109" s="31" t="s">
-        <v>299</v>
+        <v>8</v>
       </c>
       <c r="F109" s="30" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G109" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F109),0)&gt;0), MAX($G$1:G108)+1, ""))</f>
@@ -4749,19 +4755,19 @@
         <v>20</v>
       </c>
       <c r="B110" s="31" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C110" s="32">
         <v>20</v>
       </c>
       <c r="D110" s="30" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E110" s="31" t="s">
-        <v>8</v>
+        <v>299</v>
       </c>
       <c r="F110" s="30" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G110" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F110),0)&gt;0), MAX($G$1:G109)+1, ""))</f>
@@ -4773,76 +4779,76 @@
       </c>
     </row>
     <row r="111" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A111" s="36">
+      <c r="A111" s="30">
         <v>20</v>
       </c>
-      <c r="B111" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="C111" s="38">
+      <c r="B111" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="C111" s="32">
         <v>20</v>
       </c>
-      <c r="D111" s="36">
-        <v>3</v>
-      </c>
-      <c r="E111" s="37" t="s">
-        <v>304</v>
-      </c>
-      <c r="F111" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="G111" s="29"/>
+      <c r="D111" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="E111" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F111" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="G111" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F111),0)&gt;0), MAX($G$1:G110)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H111" s="21" t="b">
         <f>A111=C111</f>
         <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A112" s="26">
+      <c r="A112" s="36">
         <v>20</v>
       </c>
-      <c r="B112" s="27" t="s">
-        <v>302</v>
-      </c>
-      <c r="C112" s="28">
+      <c r="B112" s="37" t="s">
+        <v>330</v>
+      </c>
+      <c r="C112" s="38">
         <v>20</v>
       </c>
-      <c r="D112" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E112" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="F112" s="26" t="s">
-        <v>301</v>
-      </c>
-      <c r="G112" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F112),0)&gt;0), MAX($G$1:G111)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D112" s="36">
+        <v>3</v>
+      </c>
+      <c r="E112" s="37" t="s">
+        <v>304</v>
+      </c>
+      <c r="F112" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="G112" s="29"/>
       <c r="H112" s="21" t="b">
         <f>A112=C112</f>
         <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A113" s="30">
+      <c r="A113" s="26">
         <v>20</v>
       </c>
-      <c r="B113" s="31" t="s">
-        <v>366</v>
-      </c>
-      <c r="C113" s="32">
+      <c r="B113" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C113" s="28">
         <v>20</v>
       </c>
-      <c r="D113" s="30">
+      <c r="D113" s="26">
         <v>2.4</v>
       </c>
-      <c r="E113" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="F113" s="30" t="s">
-        <v>367</v>
+      <c r="E113" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="F113" s="26" t="s">
+        <v>301</v>
       </c>
       <c r="G113" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F113),0)&gt;0), MAX($G$1:G112)+1, ""))</f>
@@ -4858,19 +4864,19 @@
         <v>20</v>
       </c>
       <c r="B114" s="31" t="s">
-        <v>103</v>
+        <v>366</v>
       </c>
       <c r="C114" s="32">
         <v>20</v>
       </c>
-      <c r="D114" s="30" t="s">
-        <v>214</v>
+      <c r="D114" s="30">
+        <v>2.4</v>
       </c>
       <c r="E114" s="31" t="s">
         <v>60</v>
       </c>
       <c r="F114" s="30" t="s">
-        <v>104</v>
+        <v>367</v>
       </c>
       <c r="G114" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F114),0)&gt;0), MAX($G$1:G113)+1, ""))</f>
@@ -4882,23 +4888,23 @@
       </c>
     </row>
     <row r="115" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A115" s="26">
+      <c r="A115" s="30">
         <v>20</v>
       </c>
-      <c r="B115" s="27" t="s">
-        <v>339</v>
-      </c>
-      <c r="C115" s="28">
+      <c r="B115" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="C115" s="32">
         <v>20</v>
       </c>
-      <c r="D115" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E115" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F115" s="26" t="s">
-        <v>344</v>
+      <c r="D115" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="E115" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="F115" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G115" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F115),0)&gt;0), MAX($G$1:G114)+1, ""))</f>
@@ -4910,53 +4916,53 @@
       </c>
     </row>
     <row r="116" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A116" s="36">
+      <c r="A116" s="26">
         <v>20</v>
       </c>
-      <c r="B116" s="37" t="s">
-        <v>335</v>
-      </c>
-      <c r="C116" s="38">
+      <c r="B116" s="27" t="s">
+        <v>339</v>
+      </c>
+      <c r="C116" s="28">
         <v>20</v>
       </c>
-      <c r="D116" s="36">
-        <v>3.2</v>
-      </c>
-      <c r="E116" s="37" t="s">
-        <v>336</v>
-      </c>
-      <c r="F116" s="36" t="s">
-        <v>332</v>
-      </c>
-      <c r="G116" s="29"/>
+      <c r="D116" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E116" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F116" s="26" t="s">
+        <v>344</v>
+      </c>
+      <c r="G116" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F116),0)&gt;0), MAX($G$1:G115)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H116" s="21" t="b">
         <f>A116=C116</f>
         <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A117" s="30">
+      <c r="A117" s="36">
         <v>20</v>
       </c>
-      <c r="B117" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="C117" s="32">
+      <c r="B117" s="37" t="s">
+        <v>335</v>
+      </c>
+      <c r="C117" s="38">
         <v>20</v>
       </c>
-      <c r="D117" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E117" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F117" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="G117" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F117),0)&gt;0), MAX($G$1:G116)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D117" s="36">
+        <v>3.2</v>
+      </c>
+      <c r="E117" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="F117" s="36" t="s">
+        <v>332</v>
+      </c>
+      <c r="G117" s="29"/>
       <c r="H117" s="21" t="b">
         <f>A117=C117</f>
         <v>1</v>
@@ -4967,19 +4973,19 @@
         <v>20</v>
       </c>
       <c r="B118" s="31" t="s">
-        <v>263</v>
+        <v>101</v>
       </c>
       <c r="C118" s="32">
         <v>20</v>
       </c>
-      <c r="D118" s="30">
-        <v>6.2</v>
+      <c r="D118" s="30" t="s">
+        <v>207</v>
       </c>
       <c r="E118" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F118" s="30" t="s">
-        <v>264</v>
+        <v>102</v>
       </c>
       <c r="G118" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F118),0)&gt;0), MAX($G$1:G117)+1, ""))</f>
@@ -4995,19 +5001,19 @@
         <v>20</v>
       </c>
       <c r="B119" s="31" t="s">
-        <v>99</v>
+        <v>263</v>
       </c>
       <c r="C119" s="32">
         <v>20</v>
       </c>
-      <c r="D119" s="30" t="s">
-        <v>215</v>
+      <c r="D119" s="30">
+        <v>6.2</v>
       </c>
       <c r="E119" s="31" t="s">
-        <v>299</v>
+        <v>8</v>
       </c>
       <c r="F119" s="30" t="s">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="G119" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F119),0)&gt;0), MAX($G$1:G118)+1, ""))</f>
@@ -5019,23 +5025,23 @@
       </c>
     </row>
     <row r="120" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A120" s="26">
+      <c r="A120" s="30">
         <v>20</v>
       </c>
-      <c r="B120" s="27" t="s">
-        <v>300</v>
-      </c>
-      <c r="C120" s="28">
+      <c r="B120" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="C120" s="32">
         <v>20</v>
       </c>
-      <c r="D120" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E120" s="27" t="s">
+      <c r="D120" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="E120" s="31" t="s">
         <v>299</v>
       </c>
-      <c r="F120" s="26" t="s">
-        <v>301</v>
+      <c r="F120" s="30" t="s">
+        <v>100</v>
       </c>
       <c r="G120" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F120),0)&gt;0), MAX($G$1:G119)+1, ""))</f>
@@ -5047,23 +5053,23 @@
       </c>
     </row>
     <row r="121" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A121" s="30">
+      <c r="A121" s="26">
         <v>20</v>
       </c>
-      <c r="B121" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="C121" s="32">
+      <c r="B121" s="27" t="s">
+        <v>300</v>
+      </c>
+      <c r="C121" s="28">
         <v>20</v>
       </c>
-      <c r="D121" s="30" t="s">
-        <v>216</v>
-      </c>
-      <c r="E121" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F121" s="30" t="s">
-        <v>96</v>
+      <c r="D121" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E121" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="F121" s="26" t="s">
+        <v>301</v>
       </c>
       <c r="G121" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F121),0)&gt;0), MAX($G$1:G120)+1, ""))</f>
@@ -5075,26 +5081,26 @@
       </c>
     </row>
     <row r="122" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A122" s="26">
+      <c r="A122" s="30">
         <v>20</v>
       </c>
-      <c r="B122" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="C122" s="28">
+      <c r="B122" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="C122" s="32">
         <v>20</v>
       </c>
-      <c r="D122" s="26">
-        <v>3.9</v>
-      </c>
-      <c r="E122" s="27" t="s">
-        <v>309</v>
-      </c>
-      <c r="F122" s="26" t="s">
-        <v>311</v>
+      <c r="D122" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="E122" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F122" s="30" t="s">
+        <v>96</v>
       </c>
       <c r="G122" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F122),0)&gt;0), MAX($G$1:G120)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F122),0)&gt;0), MAX($G$1:G121)+1, ""))</f>
         <v/>
       </c>
       <c r="H122" s="21" t="b">
@@ -5107,47 +5113,47 @@
         <v>20</v>
       </c>
       <c r="B123" s="27" t="s">
-        <v>355</v>
+        <v>310</v>
       </c>
       <c r="C123" s="28">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D123" s="26">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="E123" s="27" t="s">
-        <v>81</v>
+        <v>309</v>
       </c>
       <c r="F123" s="26" t="s">
-        <v>356</v>
+        <v>311</v>
       </c>
       <c r="G123" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F123),0)&gt;0), MAX($G$1:G122)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F123),0)&gt;0), MAX($G$1:G121)+1, ""))</f>
         <v/>
       </c>
       <c r="H123" s="21" t="b">
         <f>A123=C123</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A124" s="30">
+      <c r="A124" s="26">
         <v>20</v>
       </c>
-      <c r="B124" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="C124" s="32">
+      <c r="B124" s="27" t="s">
+        <v>355</v>
+      </c>
+      <c r="C124" s="28">
         <v>20</v>
       </c>
-      <c r="D124" s="30" t="s">
-        <v>218</v>
-      </c>
-      <c r="E124" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F124" s="30" t="s">
-        <v>92</v>
+      <c r="D124" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E124" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F124" s="26" t="s">
+        <v>356</v>
       </c>
       <c r="G124" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F124),0)&gt;0), MAX($G$1:G123)+1, ""))</f>
@@ -5163,19 +5169,19 @@
         <v>20</v>
       </c>
       <c r="B125" s="31" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C125" s="32">
         <v>20</v>
       </c>
       <c r="D125" s="30" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="E125" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F125" s="30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G125" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F125),0)&gt;0), MAX($G$1:G124)+1, ""))</f>
@@ -5191,16 +5197,16 @@
         <v>20</v>
       </c>
       <c r="B126" s="31" t="s">
-        <v>290</v>
+        <v>89</v>
       </c>
       <c r="C126" s="32">
         <v>20</v>
       </c>
-      <c r="D126" s="30">
-        <v>1.8</v>
+      <c r="D126" s="30" t="s">
+        <v>223</v>
       </c>
       <c r="E126" s="31" t="s">
-        <v>291</v>
+        <v>8</v>
       </c>
       <c r="F126" s="30" t="s">
         <v>90</v>
@@ -5219,19 +5225,19 @@
         <v>20</v>
       </c>
       <c r="B127" s="31" t="s">
-        <v>87</v>
+        <v>290</v>
       </c>
       <c r="C127" s="32">
         <v>20</v>
       </c>
-      <c r="D127" s="30" t="s">
-        <v>222</v>
+      <c r="D127" s="30">
+        <v>1.8</v>
       </c>
       <c r="E127" s="31" t="s">
-        <v>8</v>
+        <v>291</v>
       </c>
       <c r="F127" s="30" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G127" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F127),0)&gt;0), MAX($G$1:G126)+1, ""))</f>
@@ -5247,19 +5253,19 @@
         <v>20</v>
       </c>
       <c r="B128" s="31" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C128" s="32">
         <v>20</v>
       </c>
       <c r="D128" s="30" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E128" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F128" s="30" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G128" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F128),0)&gt;0), MAX($G$1:G127)+1, ""))</f>
@@ -5275,19 +5281,19 @@
         <v>20</v>
       </c>
       <c r="B129" s="31" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C129" s="32">
         <v>20</v>
       </c>
       <c r="D129" s="30" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E129" s="31" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F129" s="30" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G129" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F129),0)&gt;0), MAX($G$1:G128)+1, ""))</f>
@@ -5303,19 +5309,19 @@
         <v>20</v>
       </c>
       <c r="B130" s="31" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C130" s="32">
         <v>20</v>
       </c>
       <c r="D130" s="30" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E130" s="31" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="F130" s="30" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G130" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F130),0)&gt;0), MAX($G$1:G129)+1, ""))</f>
@@ -5331,19 +5337,19 @@
         <v>20</v>
       </c>
       <c r="B131" s="31" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C131" s="32">
         <v>20</v>
       </c>
       <c r="D131" s="30" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E131" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F131" s="30" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G131" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F131),0)&gt;0), MAX($G$1:G130)+1, ""))</f>
@@ -5355,23 +5361,23 @@
       </c>
     </row>
     <row r="132" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A132" s="26">
-        <v>25</v>
-      </c>
-      <c r="B132" s="27" t="s">
-        <v>178</v>
-      </c>
-      <c r="C132" s="28">
-        <v>25</v>
-      </c>
-      <c r="D132" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="E132" s="27" t="s">
+      <c r="A132" s="30">
+        <v>20</v>
+      </c>
+      <c r="B132" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="C132" s="32">
+        <v>20</v>
+      </c>
+      <c r="D132" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="E132" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F132" s="26" t="s">
-        <v>179</v>
+      <c r="F132" s="30" t="s">
+        <v>77</v>
       </c>
       <c r="G132" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B132),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E132),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F132),0)&gt;0), MAX($G$1:G131)+1, ""))</f>
@@ -5387,19 +5393,19 @@
         <v>25</v>
       </c>
       <c r="B133" s="27" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C133" s="28">
         <v>25</v>
       </c>
       <c r="D133" s="26" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="E133" s="27" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="F133" s="26" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G133" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F133),0)&gt;0), MAX($G$1:G132)+1, ""))</f>
@@ -5415,19 +5421,19 @@
         <v>25</v>
       </c>
       <c r="B134" s="27" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C134" s="28">
         <v>25</v>
       </c>
       <c r="D134" s="26" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="E134" s="27" t="s">
         <v>131</v>
       </c>
       <c r="F134" s="26" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G134" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F134),0)&gt;0), MAX($G$1:G133)+1, ""))</f>
@@ -5443,19 +5449,19 @@
         <v>25</v>
       </c>
       <c r="B135" s="27" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C135" s="28">
         <v>25</v>
       </c>
       <c r="D135" s="26" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="E135" s="27" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F135" s="26" t="s">
-        <v>324</v>
+        <v>175</v>
       </c>
       <c r="G135" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F135),0)&gt;0), MAX($G$1:G134)+1, ""))</f>
@@ -5471,19 +5477,19 @@
         <v>25</v>
       </c>
       <c r="B136" s="27" t="s">
-        <v>359</v>
+        <v>173</v>
       </c>
       <c r="C136" s="28">
         <v>25</v>
       </c>
-      <c r="D136" s="26">
-        <v>3</v>
+      <c r="D136" s="26" t="s">
+        <v>224</v>
       </c>
       <c r="E136" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F136" s="26" t="s">
-        <v>360</v>
+        <v>324</v>
       </c>
       <c r="G136" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F136),0)&gt;0), MAX($G$1:G135)+1, ""))</f>
@@ -5499,19 +5505,19 @@
         <v>25</v>
       </c>
       <c r="B137" s="27" t="s">
-        <v>172</v>
+        <v>359</v>
       </c>
       <c r="C137" s="28">
         <v>25</v>
       </c>
       <c r="D137" s="26">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="E137" s="27" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F137" s="26" t="s">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="G137" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F137),0)&gt;0), MAX($G$1:G136)+1, ""))</f>
@@ -5523,23 +5529,23 @@
       </c>
     </row>
     <row r="138" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A138" s="30">
+      <c r="A138" s="26">
         <v>25</v>
       </c>
-      <c r="B138" s="31" t="s">
-        <v>284</v>
-      </c>
-      <c r="C138" s="32">
+      <c r="B138" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="C138" s="28">
         <v>25</v>
       </c>
-      <c r="D138" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E138" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F138" s="30" t="s">
-        <v>102</v>
+      <c r="D138" s="26">
+        <v>2.7</v>
+      </c>
+      <c r="E138" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F138" s="26" t="s">
+        <v>338</v>
       </c>
       <c r="G138" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F138),0)&gt;0), MAX($G$1:G137)+1, ""))</f>
@@ -5555,7 +5561,7 @@
         <v>25</v>
       </c>
       <c r="B139" s="31" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C139" s="32">
         <v>25</v>
@@ -5579,23 +5585,23 @@
       </c>
     </row>
     <row r="140" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A140" s="26">
+      <c r="A140" s="30">
         <v>25</v>
       </c>
-      <c r="B140" s="27" t="s">
-        <v>170</v>
-      </c>
-      <c r="C140" s="28">
+      <c r="B140" s="31" t="s">
+        <v>282</v>
+      </c>
+      <c r="C140" s="32">
         <v>25</v>
       </c>
-      <c r="D140" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="E140" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="F140" s="26" t="s">
-        <v>171</v>
+      <c r="D140" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E140" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="F140" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G140" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F140),0)&gt;0), MAX($G$1:G139)+1, ""))</f>
@@ -5611,19 +5617,19 @@
         <v>25</v>
       </c>
       <c r="B141" s="27" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C141" s="28">
         <v>25</v>
       </c>
       <c r="D141" s="26" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="E141" s="27" t="s">
-        <v>8</v>
+        <v>245</v>
       </c>
       <c r="F141" s="26" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G141" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F141),0)&gt;0), MAX($G$1:G140)+1, ""))</f>
@@ -5639,19 +5645,19 @@
         <v>25</v>
       </c>
       <c r="B142" s="27" t="s">
-        <v>357</v>
+        <v>168</v>
       </c>
       <c r="C142" s="28">
         <v>25</v>
       </c>
-      <c r="D142" s="26">
-        <v>3.4</v>
+      <c r="D142" s="26" t="s">
+        <v>217</v>
       </c>
       <c r="E142" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F142" s="26" t="s">
-        <v>358</v>
+        <v>169</v>
       </c>
       <c r="G142" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F142),0)&gt;0), MAX($G$1:G141)+1, ""))</f>
@@ -5663,23 +5669,23 @@
       </c>
     </row>
     <row r="143" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A143" s="30">
+      <c r="A143" s="26">
         <v>25</v>
       </c>
-      <c r="B143" s="31" t="s">
-        <v>278</v>
-      </c>
-      <c r="C143" s="32">
+      <c r="B143" s="27" t="s">
+        <v>357</v>
+      </c>
+      <c r="C143" s="28">
         <v>25</v>
       </c>
-      <c r="D143" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E143" s="31" t="s">
+      <c r="D143" s="26">
+        <v>3.4</v>
+      </c>
+      <c r="E143" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F143" s="30" t="s">
-        <v>102</v>
+      <c r="F143" s="26" t="s">
+        <v>358</v>
       </c>
       <c r="G143" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F143),0)&gt;0), MAX($G$1:G142)+1, ""))</f>
@@ -5691,23 +5697,23 @@
       </c>
     </row>
     <row r="144" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A144" s="26">
+      <c r="A144" s="30">
         <v>25</v>
       </c>
-      <c r="B144" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="C144" s="28">
+      <c r="B144" s="31" t="s">
+        <v>278</v>
+      </c>
+      <c r="C144" s="32">
         <v>25</v>
       </c>
-      <c r="D144" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="E144" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="F144" s="26" t="s">
-        <v>167</v>
+      <c r="D144" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E144" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F144" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G144" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F144),0)&gt;0), MAX($G$1:G143)+1, ""))</f>
@@ -5723,19 +5729,19 @@
         <v>25</v>
       </c>
       <c r="B145" s="27" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C145" s="28">
         <v>25</v>
       </c>
       <c r="D145" s="26" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="E145" s="27" t="s">
         <v>131</v>
       </c>
       <c r="F145" s="26" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G145" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B145),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E145),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F145),0)&gt;0), MAX($G$1:G144)+1, ""))</f>
@@ -5751,19 +5757,19 @@
         <v>25</v>
       </c>
       <c r="B146" s="27" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C146" s="28">
         <v>25</v>
       </c>
       <c r="D146" s="26" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E146" s="27" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="F146" s="26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G146" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F146),0)&gt;0), MAX($G$1:G145)+1, ""))</f>
@@ -5779,19 +5785,19 @@
         <v>25</v>
       </c>
       <c r="B147" s="27" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C147" s="28">
         <v>25</v>
       </c>
       <c r="D147" s="26" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="E147" s="27" t="s">
         <v>81</v>
       </c>
       <c r="F147" s="26" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G147" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F147),0)&gt;0), MAX($G$1:G146)+1, ""))</f>
@@ -5807,19 +5813,19 @@
         <v>25</v>
       </c>
       <c r="B148" s="27" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C148" s="28">
         <v>25</v>
       </c>
       <c r="D148" s="26" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E148" s="27" t="s">
         <v>81</v>
       </c>
       <c r="F148" s="26" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G148" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F148),0)&gt;0), MAX($G$1:G147)+1, ""))</f>
@@ -5835,19 +5841,19 @@
         <v>25</v>
       </c>
       <c r="B149" s="27" t="s">
-        <v>342</v>
+        <v>158</v>
       </c>
       <c r="C149" s="28">
         <v>25</v>
       </c>
-      <c r="D149" s="26">
-        <v>3.4</v>
+      <c r="D149" s="26" t="s">
+        <v>228</v>
       </c>
       <c r="E149" s="27" t="s">
         <v>81</v>
       </c>
       <c r="F149" s="26" t="s">
-        <v>343</v>
+        <v>159</v>
       </c>
       <c r="G149" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B149),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E149),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F149),0)&gt;0), MAX($G$1:G148)+1, ""))</f>
@@ -5863,19 +5869,19 @@
         <v>25</v>
       </c>
       <c r="B150" s="27" t="s">
-        <v>156</v>
+        <v>342</v>
       </c>
       <c r="C150" s="28">
         <v>25</v>
       </c>
-      <c r="D150" s="26" t="s">
-        <v>227</v>
+      <c r="D150" s="26">
+        <v>3.4</v>
       </c>
       <c r="E150" s="27" t="s">
         <v>81</v>
       </c>
       <c r="F150" s="26" t="s">
-        <v>157</v>
+        <v>343</v>
       </c>
       <c r="G150" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B150),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E150),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F150),0)&gt;0), MAX($G$1:G149)+1, ""))</f>
@@ -5891,19 +5897,19 @@
         <v>25</v>
       </c>
       <c r="B151" s="27" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C151" s="28">
         <v>25</v>
       </c>
       <c r="D151" s="26" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E151" s="27" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="F151" s="26" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G151" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B151),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E151),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F151),0)&gt;0), MAX($G$1:G150)+1, ""))</f>
@@ -5919,19 +5925,19 @@
         <v>25</v>
       </c>
       <c r="B152" s="27" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C152" s="28">
         <v>25</v>
       </c>
       <c r="D152" s="26" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="E152" s="27" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="F152" s="26" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G152" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B152),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E152),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F152),0)&gt;0), MAX($G$1:G151)+1, ""))</f>
@@ -5947,19 +5953,19 @@
         <v>25</v>
       </c>
       <c r="B153" s="27" t="s">
-        <v>247</v>
+        <v>152</v>
       </c>
       <c r="C153" s="28">
         <v>25</v>
       </c>
-      <c r="D153" s="39" t="s">
-        <v>229</v>
+      <c r="D153" s="26" t="s">
+        <v>230</v>
       </c>
       <c r="E153" s="27" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F153" s="26" t="s">
-        <v>248</v>
+        <v>153</v>
       </c>
       <c r="G153" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B153),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E153),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F153),0)&gt;0), MAX($G$1:G152)+1, ""))</f>
@@ -5975,19 +5981,19 @@
         <v>25</v>
       </c>
       <c r="B154" s="27" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C154" s="28">
         <v>25</v>
       </c>
-      <c r="D154" s="26" t="s">
-        <v>235</v>
+      <c r="D154" s="39" t="s">
+        <v>229</v>
       </c>
       <c r="E154" s="27" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="F154" s="26" t="s">
-        <v>151</v>
+        <v>248</v>
       </c>
       <c r="G154" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B154),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E154),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F154),0)&gt;0), MAX($G$1:G153)+1, ""))</f>
@@ -5999,23 +6005,23 @@
       </c>
     </row>
     <row r="155" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A155" s="30">
+      <c r="A155" s="26">
         <v>25</v>
       </c>
-      <c r="B155" s="31" t="s">
-        <v>288</v>
-      </c>
-      <c r="C155" s="32">
+      <c r="B155" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C155" s="28">
         <v>25</v>
       </c>
-      <c r="D155" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E155" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F155" s="30" t="s">
-        <v>102</v>
+      <c r="D155" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="E155" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="F155" s="26" t="s">
+        <v>151</v>
       </c>
       <c r="G155" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F155),0)&gt;0), MAX($G$1:G154)+1, ""))</f>
@@ -6031,7 +6037,7 @@
         <v>25</v>
       </c>
       <c r="B156" s="31" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C156" s="32">
         <v>25</v>
@@ -6059,7 +6065,7 @@
         <v>25</v>
       </c>
       <c r="B157" s="31" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C157" s="32">
         <v>25</v>
@@ -6083,23 +6089,23 @@
       </c>
     </row>
     <row r="158" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A158" s="26">
+      <c r="A158" s="30">
         <v>25</v>
       </c>
-      <c r="B158" s="27" t="s">
-        <v>252</v>
-      </c>
-      <c r="C158" s="28">
+      <c r="B158" s="31" t="s">
+        <v>287</v>
+      </c>
+      <c r="C158" s="32">
         <v>25</v>
       </c>
-      <c r="D158" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E158" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="F158" s="26" t="s">
-        <v>253</v>
+      <c r="D158" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E158" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="F158" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G158" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B158),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E158),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F158),0)&gt;0), MAX($G$1:G157)+1, ""))</f>
@@ -6111,23 +6117,23 @@
       </c>
     </row>
     <row r="159" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A159" s="30">
+      <c r="A159" s="26">
         <v>25</v>
       </c>
-      <c r="B159" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="C159" s="32">
+      <c r="B159" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="C159" s="28">
         <v>25</v>
       </c>
-      <c r="D159" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E159" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F159" s="30" t="s">
-        <v>102</v>
+      <c r="D159" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E159" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="F159" s="26" t="s">
+        <v>253</v>
       </c>
       <c r="G159" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F159),0)&gt;0), MAX($G$1:G158)+1, ""))</f>
@@ -6139,26 +6145,26 @@
       </c>
     </row>
     <row r="160" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A160" s="26">
+      <c r="A160" s="30">
         <v>25</v>
       </c>
-      <c r="B160" s="27" t="s">
-        <v>148</v>
-      </c>
-      <c r="C160" s="28">
+      <c r="B160" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="C160" s="32">
         <v>25</v>
       </c>
-      <c r="D160" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="E160" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F160" s="26" t="s">
-        <v>149</v>
+      <c r="D160" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E160" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="F160" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G160" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B160),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E160),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F160),0)&gt;0), MAX($G$1:G158)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B160),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E160),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F160),0)&gt;0), MAX($G$1:G159)+1, ""))</f>
         <v/>
       </c>
       <c r="H160" s="21" t="b">
@@ -6167,26 +6173,26 @@
       </c>
     </row>
     <row r="161" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A161" s="30">
-        <v>30</v>
-      </c>
-      <c r="B161" s="31" t="s">
-        <v>192</v>
-      </c>
-      <c r="C161" s="32">
-        <v>30</v>
-      </c>
-      <c r="D161" s="30" t="s">
-        <v>232</v>
-      </c>
-      <c r="E161" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="F161" s="30" t="s">
-        <v>193</v>
+      <c r="A161" s="26">
+        <v>25</v>
+      </c>
+      <c r="B161" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="C161" s="28">
+        <v>25</v>
+      </c>
+      <c r="D161" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="E161" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F161" s="26" t="s">
+        <v>149</v>
       </c>
       <c r="G161" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B161),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E161),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F161),0)&gt;0), MAX($G$1:G160)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B161),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E161),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F161),0)&gt;0), MAX($G$1:G159)+1, ""))</f>
         <v/>
       </c>
       <c r="H161" s="21" t="b">
@@ -6199,19 +6205,19 @@
         <v>30</v>
       </c>
       <c r="B162" s="31" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C162" s="32">
         <v>30</v>
       </c>
       <c r="D162" s="30" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="E162" s="31" t="s">
         <v>131</v>
       </c>
       <c r="F162" s="30" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="G162" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B162),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E162),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F162),0)&gt;0), MAX($G$1:G161)+1, ""))</f>
@@ -6227,13 +6233,13 @@
         <v>30</v>
       </c>
       <c r="B163" s="31" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C163" s="32">
         <v>30</v>
       </c>
       <c r="D163" s="30" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E163" s="31" t="s">
         <v>131</v>
@@ -6255,19 +6261,19 @@
         <v>30</v>
       </c>
       <c r="B164" s="31" t="s">
-        <v>246</v>
+        <v>189</v>
       </c>
       <c r="C164" s="32">
         <v>30</v>
       </c>
       <c r="D164" s="30" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="E164" s="31" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F164" s="30" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G164" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B164),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E164),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F164),0)&gt;0), MAX($G$1:G163)+1, ""))</f>
@@ -6283,19 +6289,19 @@
         <v>30</v>
       </c>
       <c r="B165" s="31" t="s">
-        <v>186</v>
+        <v>246</v>
       </c>
       <c r="C165" s="32">
         <v>30</v>
       </c>
       <c r="D165" s="30" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="E165" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F165" s="30" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G165" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B165),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E165),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F165),0)&gt;0), MAX($G$1:G164)+1, ""))</f>
@@ -6311,19 +6317,19 @@
         <v>30</v>
       </c>
       <c r="B166" s="31" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C166" s="32">
         <v>30</v>
       </c>
       <c r="D166" s="30" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E166" s="31" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F166" s="30" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G166" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B166),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E166),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F166),0)&gt;0), MAX($G$1:G165)+1, ""))</f>
@@ -6335,23 +6341,23 @@
       </c>
     </row>
     <row r="167" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A167" s="26">
+      <c r="A167" s="30">
         <v>30</v>
       </c>
-      <c r="B167" s="27" t="s">
-        <v>377</v>
-      </c>
-      <c r="C167" s="28">
+      <c r="B167" s="31" t="s">
+        <v>184</v>
+      </c>
+      <c r="C167" s="32">
         <v>30</v>
       </c>
-      <c r="D167" s="26">
-        <v>5</v>
-      </c>
-      <c r="E167" s="27" t="s">
-        <v>378</v>
-      </c>
-      <c r="F167" s="26" t="s">
-        <v>25</v>
+      <c r="D167" s="30" t="s">
+        <v>228</v>
+      </c>
+      <c r="E167" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="F167" s="30" t="s">
+        <v>185</v>
       </c>
       <c r="G167" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B167),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E167),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F167),0)&gt;0), MAX($G$1:G166)+1, ""))</f>
@@ -6363,23 +6369,23 @@
       </c>
     </row>
     <row r="168" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A168" s="30">
+      <c r="A168" s="26">
         <v>30</v>
       </c>
-      <c r="B168" s="31" t="s">
-        <v>182</v>
-      </c>
-      <c r="C168" s="32">
+      <c r="B168" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="C168" s="28">
         <v>30</v>
       </c>
-      <c r="D168" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="E168" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="F168" s="30" t="s">
-        <v>183</v>
+      <c r="D168" s="26">
+        <v>5</v>
+      </c>
+      <c r="E168" s="27" t="s">
+        <v>378</v>
+      </c>
+      <c r="F168" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="G168" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B168),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E168),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F168),0)&gt;0), MAX($G$1:G167)+1, ""))</f>
@@ -6395,19 +6401,19 @@
         <v>30</v>
       </c>
       <c r="B169" s="31" t="s">
-        <v>337</v>
+        <v>182</v>
       </c>
       <c r="C169" s="32">
         <v>30</v>
       </c>
-      <c r="D169" s="30">
-        <v>2.9</v>
+      <c r="D169" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="E169" s="31" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="F169" s="30" t="s">
-        <v>338</v>
+        <v>183</v>
       </c>
       <c r="G169" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B169),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E169),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F169),0)&gt;0), MAX($G$1:G168)+1, ""))</f>
@@ -6423,22 +6429,22 @@
         <v>30</v>
       </c>
       <c r="B170" s="31" t="s">
-        <v>180</v>
+        <v>337</v>
       </c>
       <c r="C170" s="32">
         <v>30</v>
       </c>
-      <c r="D170" s="30" t="s">
-        <v>238</v>
+      <c r="D170" s="30">
+        <v>2.9</v>
       </c>
       <c r="E170" s="31" t="s">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="F170" s="30" t="s">
-        <v>181</v>
+        <v>338</v>
       </c>
       <c r="G170" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B170),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E170),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F170),0)&gt;0), MAX($G$1:G168)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B170),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E170),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F170),0)&gt;0), MAX($G$1:G169)+1, ""))</f>
         <v/>
       </c>
       <c r="H170" s="21" t="b">
@@ -6447,26 +6453,26 @@
       </c>
     </row>
     <row r="171" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A171" s="26">
-        <v>40</v>
-      </c>
-      <c r="B171" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="C171" s="28">
-        <v>40</v>
-      </c>
-      <c r="D171" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="E171" s="27" t="s">
-        <v>198</v>
-      </c>
-      <c r="F171" s="26" t="s">
-        <v>199</v>
+      <c r="A171" s="30">
+        <v>30</v>
+      </c>
+      <c r="B171" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="C171" s="32">
+        <v>30</v>
+      </c>
+      <c r="D171" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="E171" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="F171" s="30" t="s">
+        <v>181</v>
       </c>
       <c r="G171" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B171),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E171),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F171),0)&gt;0), MAX($G$1:G170)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B171),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E171),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F171),0)&gt;0), MAX($G$1:G169)+1, ""))</f>
         <v/>
       </c>
       <c r="H171" s="21" t="b">
@@ -6479,19 +6485,19 @@
         <v>40</v>
       </c>
       <c r="B172" s="27" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C172" s="28">
         <v>40</v>
       </c>
       <c r="D172" s="26" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E172" s="27" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F172" s="26" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G172" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B172),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E172),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F172),0)&gt;0), MAX($G$1:G171)+1, ""))</f>
@@ -6507,19 +6513,19 @@
         <v>40</v>
       </c>
       <c r="B173" s="27" t="s">
-        <v>249</v>
+        <v>194</v>
       </c>
       <c r="C173" s="28">
         <v>40</v>
       </c>
-      <c r="D173" s="26">
-        <v>8.3000000000000007</v>
+      <c r="D173" s="26" t="s">
+        <v>242</v>
       </c>
       <c r="E173" s="27" t="s">
-        <v>250</v>
+        <v>195</v>
       </c>
       <c r="F173" s="26" t="s">
-        <v>251</v>
+        <v>196</v>
       </c>
       <c r="G173" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B173),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E173),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F173),0)&gt;0), MAX($G$1:G172)+1, ""))</f>
@@ -6532,22 +6538,22 @@
     </row>
     <row r="174" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A174" s="26">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B174" s="27" t="s">
-        <v>294</v>
+        <v>249</v>
       </c>
       <c r="C174" s="28">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D174" s="26">
-        <v>10.199999999999999</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="E174" s="27" t="s">
-        <v>295</v>
+        <v>250</v>
       </c>
       <c r="F174" s="26" t="s">
-        <v>296</v>
+        <v>251</v>
       </c>
       <c r="G174" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B174),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E174),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F174),0)&gt;0), MAX($G$1:G173)+1, ""))</f>
@@ -6559,10 +6565,32 @@
       </c>
     </row>
     <row r="175" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A175" s="1"/>
-      <c r="C175" s="1"/>
-      <c r="D175" s="1"/>
-      <c r="F175" s="1"/>
+      <c r="A175" s="26">
+        <v>45</v>
+      </c>
+      <c r="B175" s="27" t="s">
+        <v>294</v>
+      </c>
+      <c r="C175" s="28">
+        <v>45</v>
+      </c>
+      <c r="D175" s="26">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E175" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="F175" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="G175" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B175),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E175),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F175),0)&gt;0), MAX($G$1:G174)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H175" s="21" t="b">
+        <f>A175=C175</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="176" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
@@ -11760,12 +11788,18 @@
       <c r="D1041" s="1"/>
       <c r="F1041" s="1"/>
     </row>
+    <row r="1042" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1042" s="1"/>
+      <c r="C1042" s="1"/>
+      <c r="D1042" s="1"/>
+      <c r="F1042" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H171">
-    <sortState ref="A2:H171">
-      <sortCondition ref="A2:A171"/>
-      <sortCondition ref="B2:B171"/>
-      <sortCondition ref="D2:D171"/>
+  <autoFilter ref="A1:H175">
+    <sortState ref="A2:H175">
+      <sortCondition ref="A2:A175"/>
+      <sortCondition ref="B2:B175"/>
+      <sortCondition ref="D2:D175"/>
     </sortState>
   </autoFilter>
   <sortState ref="A2:H174">

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Consulta" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$175</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$181</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$146</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Base!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="403">
   <si>
     <t>Grupo</t>
   </si>
@@ -1053,9 +1053,6 @@
     <t>SANTO INACIO</t>
   </si>
   <si>
-    <t>PROFESSOR HELIO VIANA</t>
-  </si>
-  <si>
     <t>21775-190</t>
   </si>
   <si>
@@ -1204,6 +1201,39 @@
   </si>
   <si>
     <t>21710-040</t>
+  </si>
+  <si>
+    <t>PROFESSOR HELIO VIANA (RUA F)</t>
+  </si>
+  <si>
+    <t>FRECHEIRINHA</t>
+  </si>
+  <si>
+    <t>21775-150</t>
+  </si>
+  <si>
+    <t>CASTANHEIRO</t>
+  </si>
+  <si>
+    <t>21710-430</t>
+  </si>
+  <si>
+    <t>REGENCIA ANTES DO CAMPO SÃO LUIZ</t>
+  </si>
+  <si>
+    <t>21760-150</t>
+  </si>
+  <si>
+    <t>REGENCIA DEPOIS DO CAMPO SÃO LUIZ</t>
+  </si>
+  <si>
+    <t>21760-210</t>
+  </si>
+  <si>
+    <t>GRÃO MOGOL ANTES DO CAMPO SÃO LUIZ</t>
+  </si>
+  <si>
+    <t>GRÃO MOGOL DEPOIS DO CAMPO SÃO LUIZ</t>
   </si>
 </sst>
 </file>
@@ -1721,7 +1751,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H1042"/>
+  <dimension ref="A1:H1048"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.453125" customWidth="1"/>
@@ -1788,7 +1818,7 @@
         <v>13</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C3" s="28">
         <v>13</v>
@@ -2068,7 +2098,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C13" s="32">
         <v>13</v>
@@ -2124,7 +2154,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C15" s="32">
         <v>13</v>
@@ -2136,7 +2166,7 @@
         <v>8</v>
       </c>
       <c r="F15" s="30" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G15" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B15),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E15),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F15),0)&gt;0), MAX($G$1:G14)+1, ""))</f>
@@ -2152,7 +2182,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C16" s="28">
         <v>13</v>
@@ -2161,10 +2191,10 @@
         <v>1</v>
       </c>
       <c r="E16" s="27" t="s">
+        <v>380</v>
+      </c>
+      <c r="F16" s="26" t="s">
         <v>381</v>
-      </c>
-      <c r="F16" s="26" t="s">
-        <v>382</v>
       </c>
       <c r="G16" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B16),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E16),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F16),0)&gt;0), MAX($G$1:G15)+1, ""))</f>
@@ -2292,7 +2322,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C21" s="28">
         <v>15</v>
@@ -2304,7 +2334,7 @@
         <v>8</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G21" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F21),0)&gt;0), MAX($G$1:G19)+1, ""))</f>
@@ -2348,7 +2378,7 @@
         <v>15</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C23" s="28">
         <v>15</v>
@@ -2360,7 +2390,7 @@
         <v>245</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G23" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B23),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E23),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F23),0)&gt;0), MAX($G$1:G22)+1, ""))</f>
@@ -2404,7 +2434,7 @@
         <v>15</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C25" s="28">
         <v>15</v>
@@ -2516,7 +2546,7 @@
         <v>15</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C29" s="28">
         <v>15</v>
@@ -2528,7 +2558,7 @@
         <v>8</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G29" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B29),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E29),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F29),0)&gt;0), MAX($G$1:G28)+1, ""))</f>
@@ -2572,7 +2602,7 @@
         <v>15</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C31" s="28">
         <v>15</v>
@@ -2581,10 +2611,10 @@
         <v>2</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F31" s="26" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G31" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B31),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E31),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F31),0)&gt;0), MAX($G$1:G30)+1, ""))</f>
@@ -2684,19 +2714,19 @@
         <v>15</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>54</v>
+        <v>401</v>
       </c>
       <c r="C35" s="28">
         <v>15</v>
       </c>
-      <c r="D35" s="26" t="s">
-        <v>204</v>
+      <c r="D35" s="26">
+        <v>2.2000000000000002</v>
       </c>
       <c r="E35" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>55</v>
+        <v>400</v>
       </c>
       <c r="G35" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F35),0)&gt;0), MAX($G$1:G34)+1, ""))</f>
@@ -2712,19 +2742,19 @@
         <v>15</v>
       </c>
       <c r="B36" s="27" t="s">
-        <v>277</v>
+        <v>54</v>
       </c>
       <c r="C36" s="28">
         <v>15</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E36" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F36" s="26" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="G36" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B36),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E36),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F36),0)&gt;0), MAX($G$1:G35)+1, ""))</f>
@@ -2740,19 +2770,19 @@
         <v>15</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="C37" s="28">
         <v>15</v>
       </c>
       <c r="D37" s="26" t="s">
-        <v>21</v>
+        <v>210</v>
       </c>
       <c r="E37" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>262</v>
+        <v>75</v>
       </c>
       <c r="G37" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F37),0)&gt;0), MAX($G$1:G36)+1, ""))</f>
@@ -2768,19 +2798,19 @@
         <v>15</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>292</v>
+        <v>260</v>
       </c>
       <c r="C38" s="28">
         <v>15</v>
       </c>
-      <c r="D38" s="26">
-        <v>2.2000000000000002</v>
+      <c r="D38" s="26" t="s">
+        <v>21</v>
       </c>
       <c r="E38" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F38" s="26" t="s">
-        <v>293</v>
+        <v>262</v>
       </c>
       <c r="G38" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F38),0)&gt;0), MAX($G$1:G37)+1, ""))</f>
@@ -2796,19 +2826,19 @@
         <v>15</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>374</v>
+        <v>292</v>
       </c>
       <c r="C39" s="28">
         <v>15</v>
       </c>
       <c r="D39" s="26">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E39" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F39" s="26" t="s">
-        <v>373</v>
+        <v>293</v>
       </c>
       <c r="G39" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B39),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E39),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F39),0)&gt;0), MAX($G$1:G38)+1, ""))</f>
@@ -2824,19 +2854,19 @@
         <v>15</v>
       </c>
       <c r="B40" s="27" t="s">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="C40" s="28">
         <v>15</v>
       </c>
       <c r="D40" s="26">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="E40" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F40" s="26" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="G40" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B40),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E40),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F40),0)&gt;0), MAX($G$1:G39)+1, ""))</f>
@@ -2852,19 +2882,19 @@
         <v>15</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>50</v>
+        <v>351</v>
       </c>
       <c r="C41" s="28">
         <v>15</v>
       </c>
-      <c r="D41" s="26" t="s">
-        <v>213</v>
+      <c r="D41" s="26">
+        <v>1.5</v>
       </c>
       <c r="E41" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F41" s="26" t="s">
-        <v>51</v>
+        <v>352</v>
       </c>
       <c r="G41" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B41),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E41),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F41),0)&gt;0), MAX($G$1:G40)+1, ""))</f>
@@ -2880,19 +2910,19 @@
         <v>15</v>
       </c>
       <c r="B42" s="27" t="s">
-        <v>390</v>
+        <v>50</v>
       </c>
       <c r="C42" s="28">
         <v>15</v>
       </c>
-      <c r="D42" s="26">
-        <v>1.3</v>
+      <c r="D42" s="26" t="s">
+        <v>213</v>
       </c>
       <c r="E42" s="27" t="s">
-        <v>381</v>
+        <v>8</v>
       </c>
       <c r="F42" s="26" t="s">
-        <v>382</v>
+        <v>51</v>
       </c>
       <c r="G42" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B42),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E42),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F42),0)&gt;0), MAX($G$1:G41)+1, ""))</f>
@@ -2908,19 +2938,19 @@
         <v>15</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>46</v>
+        <v>389</v>
       </c>
       <c r="C43" s="28">
         <v>15</v>
       </c>
-      <c r="D43" s="26" t="s">
-        <v>233</v>
+      <c r="D43" s="26">
+        <v>1.3</v>
       </c>
       <c r="E43" s="27" t="s">
-        <v>8</v>
+        <v>380</v>
       </c>
       <c r="F43" s="26" t="s">
-        <v>47</v>
+        <v>381</v>
       </c>
       <c r="G43" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F43),0)&gt;0), MAX($G$1:G42)+1, ""))</f>
@@ -2936,19 +2966,19 @@
         <v>15</v>
       </c>
       <c r="B44" s="27" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C44" s="28">
         <v>15</v>
       </c>
       <c r="D44" s="26" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="E44" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F44" s="26" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G44" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F44),0)&gt;0), MAX($G$1:G43)+1, ""))</f>
@@ -2964,19 +2994,19 @@
         <v>15</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C45" s="28">
         <v>15</v>
       </c>
       <c r="D45" s="26" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="E45" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F45" s="26" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G45" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F45),0)&gt;0), MAX($G$1:G44)+1, ""))</f>
@@ -2992,19 +3022,19 @@
         <v>15</v>
       </c>
       <c r="B46" s="27" t="s">
-        <v>308</v>
+        <v>40</v>
       </c>
       <c r="C46" s="28">
         <v>15</v>
       </c>
-      <c r="D46" s="26">
-        <v>2.2000000000000002</v>
+      <c r="D46" s="26" t="s">
+        <v>212</v>
       </c>
       <c r="E46" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F46" s="26" t="s">
-        <v>293</v>
+        <v>41</v>
       </c>
       <c r="G46" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F46),0)&gt;0), MAX($G$1:G45)+1, ""))</f>
@@ -3020,19 +3050,19 @@
         <v>15</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>244</v>
+        <v>397</v>
       </c>
       <c r="C47" s="28">
         <v>15</v>
       </c>
       <c r="D47" s="26">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="E47" s="27" t="s">
-        <v>245</v>
+        <v>8</v>
       </c>
       <c r="F47" s="26" t="s">
-        <v>202</v>
+        <v>398</v>
       </c>
       <c r="G47" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F47),0)&gt;0), MAX($G$1:G46)+1, ""))</f>
@@ -3048,22 +3078,22 @@
         <v>15</v>
       </c>
       <c r="B48" s="27" t="s">
-        <v>38</v>
+        <v>308</v>
       </c>
       <c r="C48" s="28">
         <v>15</v>
       </c>
-      <c r="D48" s="26" t="s">
-        <v>211</v>
+      <c r="D48" s="26">
+        <v>2.2000000000000002</v>
       </c>
       <c r="E48" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F48" s="26" t="s">
-        <v>39</v>
+        <v>293</v>
       </c>
       <c r="G48" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F48),0)&gt;0), MAX($G$1:G43)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F48),0)&gt;0), MAX($G$1:G47)+1, ""))</f>
         <v/>
       </c>
       <c r="H48" s="21" t="b">
@@ -3076,19 +3106,19 @@
         <v>15</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>341</v>
+        <v>244</v>
       </c>
       <c r="C49" s="28">
         <v>15</v>
       </c>
       <c r="D49" s="26">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="E49" s="27" t="s">
-        <v>8</v>
+        <v>245</v>
       </c>
       <c r="F49" s="26" t="s">
-        <v>347</v>
+        <v>202</v>
       </c>
       <c r="G49" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F49),0)&gt;0), MAX($G$1:G48)+1, ""))</f>
@@ -3104,22 +3134,22 @@
         <v>15</v>
       </c>
       <c r="B50" s="27" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C50" s="28">
         <v>15</v>
       </c>
       <c r="D50" s="26" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E50" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F50" s="26" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G50" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F50),0)&gt;0), MAX($G$1:G49)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F50),0)&gt;0), MAX($G$1:G45)+1, ""))</f>
         <v/>
       </c>
       <c r="H50" s="21" t="b">
@@ -3132,19 +3162,19 @@
         <v>15</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>383</v>
+        <v>341</v>
       </c>
       <c r="C51" s="28">
         <v>15</v>
       </c>
       <c r="D51" s="26">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E51" s="27" t="s">
-        <v>381</v>
+        <v>8</v>
       </c>
       <c r="F51" s="26" t="s">
-        <v>382</v>
+        <v>346</v>
       </c>
       <c r="G51" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F51),0)&gt;0), MAX($G$1:G50)+1, ""))</f>
@@ -3160,19 +3190,19 @@
         <v>15</v>
       </c>
       <c r="B52" s="27" t="s">
-        <v>280</v>
+        <v>34</v>
       </c>
       <c r="C52" s="28">
         <v>15</v>
       </c>
       <c r="D52" s="26" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E52" s="27" t="s">
-        <v>267</v>
+        <v>8</v>
       </c>
       <c r="F52" s="26" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G52" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F52),0)&gt;0), MAX($G$1:G51)+1, ""))</f>
@@ -3184,23 +3214,23 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="33">
-        <v>17</v>
-      </c>
-      <c r="B53" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="C53" s="35">
-        <v>17</v>
-      </c>
-      <c r="D53" s="33" t="s">
-        <v>214</v>
-      </c>
-      <c r="E53" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" s="33" t="s">
-        <v>71</v>
+      <c r="A53" s="26">
+        <v>15</v>
+      </c>
+      <c r="B53" s="27" t="s">
+        <v>382</v>
+      </c>
+      <c r="C53" s="28">
+        <v>15</v>
+      </c>
+      <c r="D53" s="26">
+        <v>1.2</v>
+      </c>
+      <c r="E53" s="27" t="s">
+        <v>380</v>
+      </c>
+      <c r="F53" s="26" t="s">
+        <v>381</v>
       </c>
       <c r="G53" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F53),0)&gt;0), MAX($G$1:G52)+1, ""))</f>
@@ -3212,26 +3242,26 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A54" s="33">
-        <v>17</v>
-      </c>
-      <c r="B54" s="34" t="s">
-        <v>281</v>
-      </c>
-      <c r="C54" s="35">
-        <v>17</v>
-      </c>
-      <c r="D54" s="33" t="s">
-        <v>222</v>
-      </c>
-      <c r="E54" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F54" s="33" t="s">
-        <v>68</v>
+      <c r="A54" s="26">
+        <v>15</v>
+      </c>
+      <c r="B54" s="27" t="s">
+        <v>280</v>
+      </c>
+      <c r="C54" s="28">
+        <v>15</v>
+      </c>
+      <c r="D54" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="E54" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="F54" s="26" t="s">
+        <v>33</v>
       </c>
       <c r="G54" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F54),0)&gt;0), MAX($G$1:G53)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F54),0)&gt;0), MAX($G$1:G49)+1, ""))</f>
         <v/>
       </c>
       <c r="H54" s="21" t="b">
@@ -3240,25 +3270,28 @@
       </c>
     </row>
     <row r="55" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="26">
+      <c r="A55" s="33">
         <v>17</v>
       </c>
-      <c r="B55" s="27" t="s">
-        <v>313</v>
-      </c>
-      <c r="C55" s="28">
+      <c r="B55" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="C55" s="35">
         <v>17</v>
       </c>
-      <c r="D55" s="26">
-        <v>1.7</v>
-      </c>
-      <c r="E55" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="F55" s="26" t="s">
-        <v>319</v>
-      </c>
-      <c r="G55" s="29"/>
+      <c r="D55" s="33" t="s">
+        <v>214</v>
+      </c>
+      <c r="E55" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F55" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="G55" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F55),0)&gt;0), MAX($G$1:G54)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H55" s="21" t="b">
         <f>A55=C55</f>
         <v>1</v>
@@ -3269,19 +3302,19 @@
         <v>17</v>
       </c>
       <c r="B56" s="34" t="s">
-        <v>62</v>
+        <v>281</v>
       </c>
       <c r="C56" s="35">
         <v>17</v>
       </c>
       <c r="D56" s="33" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="E56" s="34" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F56" s="33" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G56" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F56),0)&gt;0), MAX($G$1:G55)+1, ""))</f>
@@ -3293,28 +3326,25 @@
       </c>
     </row>
     <row r="57" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A57" s="33">
+      <c r="A57" s="26">
         <v>17</v>
       </c>
-      <c r="B57" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="C57" s="35">
+      <c r="B57" s="27" t="s">
+        <v>313</v>
+      </c>
+      <c r="C57" s="28">
         <v>17</v>
       </c>
-      <c r="D57" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="E57" s="34" t="s">
+      <c r="D57" s="26">
+        <v>1.7</v>
+      </c>
+      <c r="E57" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="F57" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="G57" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F57),0)&gt;0), MAX($G$1:G56)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="F57" s="26" t="s">
+        <v>319</v>
+      </c>
+      <c r="G57" s="29"/>
       <c r="H57" s="21" t="b">
         <f>A57=C57</f>
         <v>1</v>
@@ -3325,19 +3355,19 @@
         <v>17</v>
       </c>
       <c r="B58" s="27" t="s">
-        <v>315</v>
+        <v>395</v>
       </c>
       <c r="C58" s="28">
         <v>17</v>
       </c>
       <c r="D58" s="26">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="E58" s="27" t="s">
         <v>60</v>
       </c>
       <c r="F58" s="26" t="s">
-        <v>321</v>
+        <v>396</v>
       </c>
       <c r="G58" s="29"/>
       <c r="H58" s="21" t="b">
@@ -3346,26 +3376,26 @@
       </c>
     </row>
     <row r="59" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A59" s="26">
+      <c r="A59" s="33">
         <v>17</v>
       </c>
-      <c r="B59" s="27" t="s">
-        <v>340</v>
-      </c>
-      <c r="C59" s="28">
+      <c r="B59" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C59" s="35">
         <v>17</v>
       </c>
-      <c r="D59" s="26">
-        <v>3.3</v>
-      </c>
-      <c r="E59" s="27" t="s">
+      <c r="D59" s="33" t="s">
+        <v>215</v>
+      </c>
+      <c r="E59" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F59" s="26" t="s">
-        <v>349</v>
+      <c r="F59" s="33" t="s">
+        <v>63</v>
       </c>
       <c r="G59" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F59),0)&gt;0), MAX($G$1:G57)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F59),0)&gt;0), MAX($G$1:G58)+1, ""))</f>
         <v/>
       </c>
       <c r="H59" s="21" t="b">
@@ -3374,53 +3404,53 @@
       </c>
     </row>
     <row r="60" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A60" s="26">
+      <c r="A60" s="33">
         <v>17</v>
       </c>
-      <c r="B60" s="27" t="s">
-        <v>316</v>
-      </c>
-      <c r="C60" s="28">
+      <c r="B60" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="C60" s="35">
         <v>17</v>
       </c>
-      <c r="D60" s="26">
-        <v>1.9</v>
-      </c>
-      <c r="E60" s="27" t="s">
+      <c r="D60" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="E60" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="F60" s="26" t="s">
-        <v>322</v>
-      </c>
-      <c r="G60" s="29"/>
+      <c r="F60" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="G60" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F60),0)&gt;0), MAX($G$1:G59)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H60" s="21" t="b">
         <f>A60=C60</f>
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A61" s="36">
+      <c r="A61" s="26">
         <v>17</v>
       </c>
-      <c r="B61" s="37" t="s">
-        <v>289</v>
-      </c>
-      <c r="C61" s="38">
+      <c r="B61" s="27" t="s">
+        <v>315</v>
+      </c>
+      <c r="C61" s="28">
         <v>17</v>
       </c>
-      <c r="D61" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="E61" s="37" t="s">
+      <c r="D61" s="26">
+        <v>3</v>
+      </c>
+      <c r="E61" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="F61" s="36" t="s">
-        <v>111</v>
-      </c>
-      <c r="G61" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F61),0)&gt;0), MAX($G$1:G60)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="F61" s="26" t="s">
+        <v>321</v>
+      </c>
+      <c r="G61" s="29"/>
       <c r="H61" s="21" t="b">
         <f>A61=C61</f>
         <v>1</v>
@@ -3431,21 +3461,24 @@
         <v>17</v>
       </c>
       <c r="B62" s="27" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="C62" s="28">
         <v>17</v>
       </c>
       <c r="D62" s="26">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="E62" s="27" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="F62" s="26" t="s">
-        <v>320</v>
-      </c>
-      <c r="G62" s="29"/>
+        <v>348</v>
+      </c>
+      <c r="G62" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F62),0)&gt;0), MAX($G$1:G60)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H62" s="21" t="b">
         <f>A62=C62</f>
         <v>1</v>
@@ -3456,19 +3489,19 @@
         <v>17</v>
       </c>
       <c r="B63" s="27" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C63" s="28">
         <v>17</v>
       </c>
       <c r="D63" s="26">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="E63" s="27" t="s">
         <v>60</v>
       </c>
       <c r="F63" s="26" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G63" s="29"/>
       <c r="H63" s="21" t="b">
@@ -3481,19 +3514,19 @@
         <v>17</v>
       </c>
       <c r="B64" s="37" t="s">
-        <v>106</v>
+        <v>289</v>
       </c>
       <c r="C64" s="38">
         <v>17</v>
       </c>
       <c r="D64" s="36" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E64" s="37" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F64" s="36" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G64" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F64),0)&gt;0), MAX($G$1:G63)+1, ""))</f>
@@ -3505,23 +3538,23 @@
       </c>
     </row>
     <row r="65" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A65" s="36">
+      <c r="A65" s="26">
         <v>17</v>
       </c>
-      <c r="B65" s="37" t="s">
-        <v>303</v>
-      </c>
-      <c r="C65" s="38">
+      <c r="B65" s="27" t="s">
+        <v>402</v>
+      </c>
+      <c r="C65" s="28">
         <v>17</v>
       </c>
-      <c r="D65" s="36" t="s">
-        <v>229</v>
-      </c>
-      <c r="E65" s="37" t="s">
-        <v>304</v>
-      </c>
-      <c r="F65" s="36" t="s">
-        <v>105</v>
+      <c r="D65" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E65" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F65" s="26" t="s">
+        <v>400</v>
       </c>
       <c r="G65" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F65),0)&gt;0), MAX($G$1:G64)+1, ""))</f>
@@ -3533,28 +3566,25 @@
       </c>
     </row>
     <row r="66" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A66" s="33">
+      <c r="A66" s="26">
         <v>17</v>
       </c>
-      <c r="B66" s="34" t="s">
-        <v>52</v>
-      </c>
-      <c r="C66" s="35">
+      <c r="B66" s="27" t="s">
+        <v>314</v>
+      </c>
+      <c r="C66" s="28">
         <v>17</v>
       </c>
-      <c r="D66" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="E66" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F66" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="G66" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F66),0)&gt;0), MAX($G$1:G62)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D66" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E66" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F66" s="26" t="s">
+        <v>320</v>
+      </c>
+      <c r="G66" s="29"/>
       <c r="H66" s="21" t="b">
         <f>A66=C66</f>
         <v>1</v>
@@ -3565,47 +3595,44 @@
         <v>17</v>
       </c>
       <c r="B67" s="27" t="s">
-        <v>368</v>
+        <v>317</v>
       </c>
       <c r="C67" s="28">
         <v>17</v>
       </c>
       <c r="D67" s="26">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E67" s="27" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F67" s="26" t="s">
-        <v>354</v>
-      </c>
-      <c r="G67" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F67),0)&gt;0), MAX($G$1:G66)+1, ""))</f>
-        <v/>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="G67" s="29"/>
       <c r="H67" s="21" t="b">
         <f>A67=C67</f>
         <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A68" s="26">
+      <c r="A68" s="36">
         <v>17</v>
       </c>
-      <c r="B68" s="27" t="s">
-        <v>388</v>
-      </c>
-      <c r="C68" s="28">
+      <c r="B68" s="37" t="s">
+        <v>106</v>
+      </c>
+      <c r="C68" s="38">
         <v>17</v>
       </c>
-      <c r="D68" s="26">
-        <v>1.4</v>
-      </c>
-      <c r="E68" s="31" t="s">
+      <c r="D68" s="36" t="s">
+        <v>220</v>
+      </c>
+      <c r="E68" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F68" s="26" t="s">
-        <v>354</v>
+      <c r="F68" s="36" t="s">
+        <v>107</v>
       </c>
       <c r="G68" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F68),0)&gt;0), MAX($G$1:G67)+1, ""))</f>
@@ -3617,23 +3644,23 @@
       </c>
     </row>
     <row r="69" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A69" s="26">
+      <c r="A69" s="36">
         <v>17</v>
       </c>
-      <c r="B69" s="27" t="s">
-        <v>379</v>
-      </c>
-      <c r="C69" s="28">
+      <c r="B69" s="37" t="s">
+        <v>303</v>
+      </c>
+      <c r="C69" s="38">
         <v>17</v>
       </c>
-      <c r="D69" s="26">
-        <v>1.2</v>
-      </c>
-      <c r="E69" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F69" s="26" t="s">
-        <v>380</v>
+      <c r="D69" s="36" t="s">
+        <v>229</v>
+      </c>
+      <c r="E69" s="37" t="s">
+        <v>304</v>
+      </c>
+      <c r="F69" s="36" t="s">
+        <v>105</v>
       </c>
       <c r="G69" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F69),0)&gt;0), MAX($G$1:G68)+1, ""))</f>
@@ -3649,22 +3676,22 @@
         <v>17</v>
       </c>
       <c r="B70" s="34" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C70" s="35">
         <v>17</v>
       </c>
       <c r="D70" s="33" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E70" s="34" t="s">
         <v>8</v>
       </c>
       <c r="F70" s="33" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G70" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F70),0)&gt;0), MAX($G$1:G69)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F70),0)&gt;0), MAX($G$1:G65)+1, ""))</f>
         <v/>
       </c>
       <c r="H70" s="21" t="b">
@@ -3673,23 +3700,23 @@
       </c>
     </row>
     <row r="71" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A71" s="36">
+      <c r="A71" s="26">
         <v>17</v>
       </c>
-      <c r="B71" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="C71" s="38">
+      <c r="B71" s="27" t="s">
+        <v>367</v>
+      </c>
+      <c r="C71" s="28">
         <v>17</v>
       </c>
-      <c r="D71" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="E71" s="37" t="s">
+      <c r="D71" s="26">
+        <v>1.8</v>
+      </c>
+      <c r="E71" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F71" s="36" t="s">
-        <v>98</v>
+      <c r="F71" s="26" t="s">
+        <v>353</v>
       </c>
       <c r="G71" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F71),0)&gt;0), MAX($G$1:G70)+1, ""))</f>
@@ -3705,19 +3732,19 @@
         <v>17</v>
       </c>
       <c r="B72" s="27" t="s">
-        <v>42</v>
+        <v>387</v>
       </c>
       <c r="C72" s="28">
         <v>17</v>
       </c>
-      <c r="D72" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="E72" s="27" t="s">
+      <c r="D72" s="26">
+        <v>1.4</v>
+      </c>
+      <c r="E72" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F72" s="26" t="s">
-        <v>43</v>
+        <v>353</v>
       </c>
       <c r="G72" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F72),0)&gt;0), MAX($G$1:G71)+1, ""))</f>
@@ -3729,23 +3756,23 @@
       </c>
     </row>
     <row r="73" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A73" s="36">
+      <c r="A73" s="26">
         <v>17</v>
       </c>
-      <c r="B73" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="C73" s="38">
+      <c r="B73" s="27" t="s">
+        <v>378</v>
+      </c>
+      <c r="C73" s="28">
         <v>17</v>
       </c>
-      <c r="D73" s="36" t="s">
-        <v>217</v>
-      </c>
-      <c r="E73" s="37" t="s">
+      <c r="D73" s="26">
+        <v>1.2</v>
+      </c>
+      <c r="E73" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F73" s="36" t="s">
-        <v>94</v>
+      <c r="F73" s="26" t="s">
+        <v>379</v>
       </c>
       <c r="G73" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F73),0)&gt;0), MAX($G$1:G72)+1, ""))</f>
@@ -3761,97 +3788,103 @@
         <v>17</v>
       </c>
       <c r="B74" s="34" t="s">
-        <v>327</v>
+        <v>48</v>
       </c>
       <c r="C74" s="35">
         <v>17</v>
       </c>
-      <c r="D74" s="33">
-        <v>1.9</v>
+      <c r="D74" s="33" t="s">
+        <v>211</v>
       </c>
       <c r="E74" s="34" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="F74" s="33" t="s">
-        <v>329</v>
-      </c>
-      <c r="G74" s="29" t="s">
-        <v>326</v>
+        <v>49</v>
+      </c>
+      <c r="G74" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F74),0)&gt;0), MAX($G$1:G73)+1, ""))</f>
+        <v/>
       </c>
       <c r="H74" s="21" t="b">
+        <f>A74=C74</f>
         <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A75" s="33">
+      <c r="A75" s="36">
         <v>17</v>
       </c>
-      <c r="B75" s="34" t="s">
-        <v>325</v>
-      </c>
-      <c r="C75" s="35">
+      <c r="B75" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="C75" s="38">
         <v>17</v>
       </c>
-      <c r="D75" s="33">
-        <v>1.9</v>
-      </c>
-      <c r="E75" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F75" s="33" t="s">
-        <v>329</v>
-      </c>
-      <c r="G75" s="29" t="s">
-        <v>326</v>
+      <c r="D75" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E75" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F75" s="36" t="s">
+        <v>98</v>
+      </c>
+      <c r="G75" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F75),0)&gt;0), MAX($G$1:G74)+1, ""))</f>
+        <v/>
       </c>
       <c r="H75" s="21" t="b">
+        <f>A75=C75</f>
         <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A76" s="33">
+      <c r="A76" s="26">
         <v>17</v>
       </c>
-      <c r="B76" s="34" t="s">
-        <v>328</v>
-      </c>
-      <c r="C76" s="35">
+      <c r="B76" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C76" s="28">
         <v>17</v>
       </c>
-      <c r="D76" s="33">
-        <v>1.9</v>
-      </c>
-      <c r="E76" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F76" s="33" t="s">
-        <v>329</v>
-      </c>
-      <c r="G76" s="29" t="s">
-        <v>326</v>
+      <c r="D76" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="E76" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F76" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="G76" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F76),0)&gt;0), MAX($G$1:G75)+1, ""))</f>
+        <v/>
       </c>
       <c r="H76" s="21" t="b">
+        <f>A76=C76</f>
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A77" s="33">
+      <c r="A77" s="36">
         <v>17</v>
       </c>
-      <c r="B77" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="C77" s="35">
+      <c r="B77" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="C77" s="38">
         <v>17</v>
       </c>
-      <c r="D77" s="33" t="s">
-        <v>214</v>
-      </c>
-      <c r="E77" s="34" t="s">
+      <c r="D77" s="36" t="s">
+        <v>217</v>
+      </c>
+      <c r="E77" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F77" s="33" t="s">
-        <v>37</v>
+      <c r="F77" s="36" t="s">
+        <v>94</v>
       </c>
       <c r="G77" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F77),0)&gt;0), MAX($G$1:G76)+1, ""))</f>
@@ -3863,23 +3896,23 @@
       </c>
     </row>
     <row r="78" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A78" s="36">
+      <c r="A78" s="26">
         <v>17</v>
       </c>
-      <c r="B78" s="37" t="s">
-        <v>83</v>
-      </c>
-      <c r="C78" s="38">
+      <c r="B78" s="27" t="s">
+        <v>399</v>
+      </c>
+      <c r="C78" s="28">
         <v>17</v>
       </c>
-      <c r="D78" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="E78" s="37" t="s">
+      <c r="D78" s="26">
+        <v>2</v>
+      </c>
+      <c r="E78" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F78" s="36" t="s">
-        <v>84</v>
+      <c r="F78" s="26" t="s">
+        <v>398</v>
       </c>
       <c r="G78" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F78),0)&gt;0), MAX($G$1:G77)+1, ""))</f>
@@ -3895,26 +3928,24 @@
         <v>17</v>
       </c>
       <c r="B79" s="34" t="s">
-        <v>31</v>
+        <v>327</v>
       </c>
       <c r="C79" s="35">
         <v>17</v>
       </c>
-      <c r="D79" s="33" t="s">
-        <v>208</v>
+      <c r="D79" s="33">
+        <v>1.9</v>
       </c>
       <c r="E79" s="34" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F79" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="G79" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F79),0)&gt;0), MAX($G$1:G78)+1, ""))</f>
-        <v/>
+        <v>329</v>
+      </c>
+      <c r="G79" s="29" t="s">
+        <v>326</v>
       </c>
       <c r="H79" s="21" t="b">
-        <f>A79=C79</f>
         <v>1</v>
       </c>
     </row>
@@ -3923,19 +3954,19 @@
         <v>17</v>
       </c>
       <c r="B80" s="34" t="s">
-        <v>29</v>
+        <v>325</v>
       </c>
       <c r="C80" s="35">
         <v>17</v>
       </c>
-      <c r="D80" s="33" t="s">
-        <v>207</v>
+      <c r="D80" s="33">
+        <v>1.9</v>
       </c>
       <c r="E80" s="34" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F80" s="33" t="s">
-        <v>30</v>
+        <v>329</v>
       </c>
       <c r="G80" s="29" t="s">
         <v>326</v>
@@ -3945,51 +3976,49 @@
       </c>
     </row>
     <row r="81" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A81" s="30">
-        <v>20</v>
-      </c>
-      <c r="B81" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="C81" s="32">
-        <v>20</v>
-      </c>
-      <c r="D81" s="30" t="s">
-        <v>206</v>
-      </c>
-      <c r="E81" s="31" t="s">
+      <c r="A81" s="33">
+        <v>17</v>
+      </c>
+      <c r="B81" s="34" t="s">
+        <v>328</v>
+      </c>
+      <c r="C81" s="35">
+        <v>17</v>
+      </c>
+      <c r="D81" s="33">
+        <v>1.9</v>
+      </c>
+      <c r="E81" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="F81" s="33" t="s">
+        <v>329</v>
+      </c>
+      <c r="G81" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="H81" s="21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A82" s="33">
+        <v>17</v>
+      </c>
+      <c r="B82" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="C82" s="35">
+        <v>17</v>
+      </c>
+      <c r="D82" s="33" t="s">
+        <v>214</v>
+      </c>
+      <c r="E82" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F81" s="30" t="s">
-        <v>147</v>
-      </c>
-      <c r="G81" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F81),0)&gt;0), MAX($G$1:G77)+1, ""))</f>
-        <v/>
-      </c>
-      <c r="H81" s="21" t="b">
-        <f>A81=C81</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A82" s="30">
-        <v>20</v>
-      </c>
-      <c r="B82" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="C82" s="32">
-        <v>20</v>
-      </c>
-      <c r="D82" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="E82" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F82" s="30" t="s">
-        <v>145</v>
+      <c r="F82" s="33" t="s">
+        <v>37</v>
       </c>
       <c r="G82" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F82),0)&gt;0), MAX($G$1:G81)+1, ""))</f>
@@ -4001,23 +4030,23 @@
       </c>
     </row>
     <row r="83" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A83" s="26">
-        <v>20</v>
-      </c>
-      <c r="B83" s="27" t="s">
-        <v>384</v>
-      </c>
-      <c r="C83" s="28">
-        <v>20</v>
-      </c>
-      <c r="D83" s="26">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="E83" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="F83" s="26" t="s">
-        <v>385</v>
+      <c r="A83" s="36">
+        <v>17</v>
+      </c>
+      <c r="B83" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="C83" s="38">
+        <v>17</v>
+      </c>
+      <c r="D83" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E83" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" s="36" t="s">
+        <v>84</v>
       </c>
       <c r="G83" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F83),0)&gt;0), MAX($G$1:G82)+1, ""))</f>
@@ -4029,26 +4058,26 @@
       </c>
     </row>
     <row r="84" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A84" s="30">
-        <v>20</v>
-      </c>
-      <c r="B84" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="C84" s="32">
-        <v>20</v>
-      </c>
-      <c r="D84" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="E84" s="31" t="s">
+      <c r="A84" s="33">
+        <v>17</v>
+      </c>
+      <c r="B84" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" s="35">
+        <v>17</v>
+      </c>
+      <c r="D84" s="33" t="s">
+        <v>208</v>
+      </c>
+      <c r="E84" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F84" s="30" t="s">
-        <v>143</v>
+      <c r="F84" s="33" t="s">
+        <v>32</v>
       </c>
       <c r="G84" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F84),0)&gt;0), MAX($G$1:G82)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F84),0)&gt;0), MAX($G$1:G83)+1, ""))</f>
         <v/>
       </c>
       <c r="H84" s="21" t="b">
@@ -4057,101 +4086,105 @@
       </c>
     </row>
     <row r="85" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A85" s="30">
+      <c r="A85" s="33">
+        <v>17</v>
+      </c>
+      <c r="B85" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="C85" s="35">
+        <v>17</v>
+      </c>
+      <c r="D85" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="E85" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F85" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="G85" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="H85" s="21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A86" s="30">
         <v>20</v>
       </c>
-      <c r="B85" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="C85" s="32">
+      <c r="B86" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="C86" s="32">
         <v>20</v>
       </c>
-      <c r="D85" s="30" t="s">
-        <v>216</v>
-      </c>
-      <c r="E85" s="31" t="s">
-        <v>305</v>
-      </c>
-      <c r="F85" s="30" t="s">
-        <v>141</v>
-      </c>
-      <c r="G85" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F85),0)&gt;0), MAX($G$1:G84)+1, ""))</f>
-        <v/>
-      </c>
-      <c r="H85" s="21" t="b">
-        <f>A85=C85</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A86" s="36">
-        <v>20</v>
-      </c>
-      <c r="B86" s="37" t="s">
-        <v>333</v>
-      </c>
-      <c r="C86" s="38">
-        <v>20</v>
-      </c>
-      <c r="D86" s="36">
-        <v>3.4</v>
-      </c>
-      <c r="E86" s="37" t="s">
-        <v>336</v>
-      </c>
-      <c r="F86" s="36" t="s">
-        <v>334</v>
-      </c>
-      <c r="G86" s="29"/>
+      <c r="D86" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="E86" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F86" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="G86" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F86),0)&gt;0), MAX($G$1:G82)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H86" s="21" t="b">
         <f>A86=C86</f>
         <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A87" s="36">
+      <c r="A87" s="30">
         <v>20</v>
       </c>
-      <c r="B87" s="37" t="s">
-        <v>331</v>
-      </c>
-      <c r="C87" s="38">
+      <c r="B87" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="C87" s="32">
         <v>20</v>
       </c>
-      <c r="D87" s="36">
-        <v>3.3</v>
-      </c>
-      <c r="E87" s="37" t="s">
-        <v>336</v>
-      </c>
-      <c r="F87" s="36" t="s">
-        <v>332</v>
-      </c>
-      <c r="G87" s="29"/>
+      <c r="D87" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="E87" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F87" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="G87" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F87),0)&gt;0), MAX($G$1:G86)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H87" s="21" t="b">
         <f>A87=C87</f>
         <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A88" s="30">
+      <c r="A88" s="26">
         <v>20</v>
       </c>
-      <c r="B88" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="C88" s="32">
+      <c r="B88" s="27" t="s">
+        <v>383</v>
+      </c>
+      <c r="C88" s="28">
         <v>20</v>
       </c>
-      <c r="D88" s="30" t="s">
-        <v>223</v>
-      </c>
-      <c r="E88" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F88" s="30" t="s">
-        <v>139</v>
+      <c r="D88" s="26">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E88" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F88" s="26" t="s">
+        <v>384</v>
       </c>
       <c r="G88" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F88),0)&gt;0), MAX($G$1:G87)+1, ""))</f>
@@ -4167,22 +4200,22 @@
         <v>20</v>
       </c>
       <c r="B89" s="31" t="s">
-        <v>255</v>
+        <v>142</v>
       </c>
       <c r="C89" s="32">
         <v>20</v>
       </c>
       <c r="D89" s="30" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="E89" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F89" s="30" t="s">
-        <v>256</v>
+        <v>143</v>
       </c>
       <c r="G89" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F89),0)&gt;0), MAX($G$1:G88)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F89),0)&gt;0), MAX($G$1:G87)+1, ""))</f>
         <v/>
       </c>
       <c r="H89" s="21" t="b">
@@ -4195,19 +4228,19 @@
         <v>20</v>
       </c>
       <c r="B90" s="31" t="s">
-        <v>254</v>
+        <v>140</v>
       </c>
       <c r="C90" s="32">
         <v>20</v>
       </c>
-      <c r="D90" s="30">
-        <v>4.2</v>
+      <c r="D90" s="30" t="s">
+        <v>216</v>
       </c>
       <c r="E90" s="31" t="s">
         <v>305</v>
       </c>
-      <c r="F90" s="30">
-        <v>21765430</v>
+      <c r="F90" s="30" t="s">
+        <v>141</v>
       </c>
       <c r="G90" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F90),0)&gt;0), MAX($G$1:G89)+1, ""))</f>
@@ -4219,56 +4252,50 @@
       </c>
     </row>
     <row r="91" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A91" s="30">
+      <c r="A91" s="36">
         <v>20</v>
       </c>
-      <c r="B91" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="C91" s="32">
+      <c r="B91" s="37" t="s">
+        <v>333</v>
+      </c>
+      <c r="C91" s="38">
         <v>20</v>
       </c>
-      <c r="D91" s="30" t="s">
-        <v>210</v>
-      </c>
-      <c r="E91" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F91" s="30" t="s">
-        <v>137</v>
-      </c>
-      <c r="G91" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F91),0)&gt;0), MAX($G$1:G90)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D91" s="36">
+        <v>3.4</v>
+      </c>
+      <c r="E91" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="F91" s="36" t="s">
+        <v>334</v>
+      </c>
+      <c r="G91" s="29"/>
       <c r="H91" s="21" t="b">
         <f>A91=C91</f>
         <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A92" s="30">
+      <c r="A92" s="36">
         <v>20</v>
       </c>
-      <c r="B92" s="31" t="s">
-        <v>265</v>
-      </c>
-      <c r="C92" s="32">
+      <c r="B92" s="37" t="s">
+        <v>331</v>
+      </c>
+      <c r="C92" s="38">
         <v>20</v>
       </c>
-      <c r="D92" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="E92" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F92" s="30" t="s">
-        <v>135</v>
-      </c>
-      <c r="G92" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E92),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F92),0)&gt;0), MAX($G$1:G91)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D92" s="36">
+        <v>3.3</v>
+      </c>
+      <c r="E92" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="F92" s="36" t="s">
+        <v>332</v>
+      </c>
+      <c r="G92" s="29"/>
       <c r="H92" s="21" t="b">
         <f>A92=C92</f>
         <v>1</v>
@@ -4279,19 +4306,19 @@
         <v>20</v>
       </c>
       <c r="B93" s="31" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C93" s="32">
         <v>20</v>
       </c>
       <c r="D93" s="30" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E93" s="31" t="s">
-        <v>305</v>
+        <v>8</v>
       </c>
       <c r="F93" s="30" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G93" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F93),0)&gt;0), MAX($G$1:G92)+1, ""))</f>
@@ -4307,19 +4334,19 @@
         <v>20</v>
       </c>
       <c r="B94" s="31" t="s">
-        <v>130</v>
+        <v>255</v>
       </c>
       <c r="C94" s="32">
         <v>20</v>
       </c>
       <c r="D94" s="30" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="E94" s="31" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="F94" s="30" t="s">
-        <v>132</v>
+        <v>256</v>
       </c>
       <c r="G94" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F94),0)&gt;0), MAX($G$1:G93)+1, ""))</f>
@@ -4331,23 +4358,23 @@
       </c>
     </row>
     <row r="95" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A95" s="26">
+      <c r="A95" s="30">
         <v>20</v>
       </c>
-      <c r="B95" s="27" t="s">
-        <v>312</v>
-      </c>
-      <c r="C95" s="28">
+      <c r="B95" s="31" t="s">
+        <v>254</v>
+      </c>
+      <c r="C95" s="32">
         <v>20</v>
       </c>
-      <c r="D95" s="26">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="E95" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="F95" s="26" t="s">
-        <v>318</v>
+      <c r="D95" s="30">
+        <v>4.2</v>
+      </c>
+      <c r="E95" s="31" t="s">
+        <v>305</v>
+      </c>
+      <c r="F95" s="30">
+        <v>21765430</v>
       </c>
       <c r="G95" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F95),0)&gt;0), MAX($G$1:G94)+1, ""))</f>
@@ -4359,23 +4386,23 @@
       </c>
     </row>
     <row r="96" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A96" s="26">
+      <c r="A96" s="30">
         <v>20</v>
       </c>
-      <c r="B96" s="27" t="s">
-        <v>387</v>
-      </c>
-      <c r="C96" s="28">
+      <c r="B96" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="C96" s="32">
         <v>20</v>
       </c>
-      <c r="D96" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E96" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="F96" s="26" t="s">
-        <v>386</v>
+      <c r="D96" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="E96" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="30" t="s">
+        <v>137</v>
       </c>
       <c r="G96" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F96),0)&gt;0), MAX($G$1:G95)+1, ""))</f>
@@ -4391,19 +4418,19 @@
         <v>20</v>
       </c>
       <c r="B97" s="31" t="s">
-        <v>128</v>
+        <v>265</v>
       </c>
       <c r="C97" s="32">
         <v>20</v>
       </c>
       <c r="D97" s="30" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E97" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F97" s="30" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="G97" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F97),0)&gt;0), MAX($G$1:G96)+1, ""))</f>
@@ -4419,19 +4446,19 @@
         <v>20</v>
       </c>
       <c r="B98" s="31" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C98" s="32">
         <v>20</v>
       </c>
       <c r="D98" s="30" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="E98" s="31" t="s">
         <v>305</v>
       </c>
       <c r="F98" s="30" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="G98" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F98),0)&gt;0), MAX($G$1:G97)+1, ""))</f>
@@ -4443,23 +4470,23 @@
       </c>
     </row>
     <row r="99" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A99" s="26">
+      <c r="A99" s="30">
         <v>20</v>
       </c>
-      <c r="B99" s="27" t="s">
-        <v>375</v>
-      </c>
-      <c r="C99" s="28">
+      <c r="B99" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="C99" s="32">
         <v>20</v>
       </c>
-      <c r="D99" s="26">
-        <v>2.7</v>
-      </c>
-      <c r="E99" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="F99" s="26" t="s">
-        <v>351</v>
+      <c r="D99" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="E99" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="F99" s="30" t="s">
+        <v>132</v>
       </c>
       <c r="G99" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F99),0)&gt;0), MAX($G$1:G98)+1, ""))</f>
@@ -4471,23 +4498,23 @@
       </c>
     </row>
     <row r="100" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A100" s="30">
+      <c r="A100" s="26">
         <v>20</v>
       </c>
-      <c r="B100" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="C100" s="32">
+      <c r="B100" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="C100" s="28">
         <v>20</v>
       </c>
-      <c r="D100" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="E100" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F100" s="30" t="s">
-        <v>125</v>
+      <c r="D100" s="26">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E100" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F100" s="26" t="s">
+        <v>318</v>
       </c>
       <c r="G100" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F100),0)&gt;0), MAX($G$1:G99)+1, ""))</f>
@@ -4499,23 +4526,23 @@
       </c>
     </row>
     <row r="101" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A101" s="30">
+      <c r="A101" s="26">
         <v>20</v>
       </c>
-      <c r="B101" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="C101" s="32">
+      <c r="B101" s="27" t="s">
+        <v>386</v>
+      </c>
+      <c r="C101" s="28">
         <v>20</v>
       </c>
-      <c r="D101" s="30" t="s">
-        <v>215</v>
-      </c>
-      <c r="E101" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F101" s="30" t="s">
-        <v>123</v>
+      <c r="D101" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E101" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F101" s="26" t="s">
+        <v>385</v>
       </c>
       <c r="G101" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F101),0)&gt;0), MAX($G$1:G100)+1, ""))</f>
@@ -4531,19 +4558,19 @@
         <v>20</v>
       </c>
       <c r="B102" s="31" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C102" s="32">
         <v>20</v>
       </c>
       <c r="D102" s="30" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E102" s="31" t="s">
-        <v>305</v>
+        <v>8</v>
       </c>
       <c r="F102" s="30" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="G102" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F102),0)&gt;0), MAX($G$1:G101)+1, ""))</f>
@@ -4555,23 +4582,23 @@
       </c>
     </row>
     <row r="103" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A103" s="26">
+      <c r="A103" s="30">
         <v>20</v>
       </c>
-      <c r="B103" s="27" t="s">
-        <v>369</v>
-      </c>
-      <c r="C103" s="28">
+      <c r="B103" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="C103" s="32">
         <v>20</v>
       </c>
-      <c r="D103" s="26">
-        <v>1.5</v>
+      <c r="D103" s="30" t="s">
+        <v>234</v>
       </c>
       <c r="E103" s="31" t="s">
-        <v>299</v>
-      </c>
-      <c r="F103" s="26" t="s">
-        <v>370</v>
+        <v>305</v>
+      </c>
+      <c r="F103" s="30" t="s">
+        <v>127</v>
       </c>
       <c r="G103" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F103),0)&gt;0), MAX($G$1:G102)+1, ""))</f>
@@ -4583,23 +4610,23 @@
       </c>
     </row>
     <row r="104" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A104" s="30">
+      <c r="A104" s="26">
         <v>20</v>
       </c>
-      <c r="B104" s="31" t="s">
-        <v>257</v>
-      </c>
-      <c r="C104" s="32">
+      <c r="B104" s="27" t="s">
+        <v>374</v>
+      </c>
+      <c r="C104" s="28">
         <v>20</v>
       </c>
-      <c r="D104" s="30" t="s">
-        <v>225</v>
-      </c>
-      <c r="E104" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F104" s="30" t="s">
-        <v>258</v>
+      <c r="D104" s="26">
+        <v>2.7</v>
+      </c>
+      <c r="E104" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="F104" s="26" t="s">
+        <v>350</v>
       </c>
       <c r="G104" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F104),0)&gt;0), MAX($G$1:G103)+1, ""))</f>
@@ -4615,19 +4642,19 @@
         <v>20</v>
       </c>
       <c r="B105" s="31" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C105" s="32">
         <v>20</v>
       </c>
       <c r="D105" s="30" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E105" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F105" s="30" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="G105" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F105),0)&gt;0), MAX($G$1:G104)+1, ""))</f>
@@ -4643,19 +4670,19 @@
         <v>20</v>
       </c>
       <c r="B106" s="31" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C106" s="32">
         <v>20</v>
       </c>
       <c r="D106" s="30" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="E106" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F106" s="30" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="G106" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F106),0)&gt;0), MAX($G$1:G105)+1, ""))</f>
@@ -4671,19 +4698,19 @@
         <v>20</v>
       </c>
       <c r="B107" s="31" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C107" s="32">
         <v>20</v>
       </c>
       <c r="D107" s="30" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="E107" s="31" t="s">
-        <v>8</v>
+        <v>305</v>
       </c>
       <c r="F107" s="30" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G107" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F107),0)&gt;0), MAX($G$1:G106)+1, ""))</f>
@@ -4699,19 +4726,19 @@
         <v>20</v>
       </c>
       <c r="B108" s="27" t="s">
-        <v>297</v>
+        <v>368</v>
       </c>
       <c r="C108" s="28">
         <v>20</v>
       </c>
       <c r="D108" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E108" s="27" t="s">
+        <v>1.5</v>
+      </c>
+      <c r="E108" s="31" t="s">
         <v>299</v>
       </c>
       <c r="F108" s="26" t="s">
-        <v>298</v>
+        <v>369</v>
       </c>
       <c r="G108" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F108),0)&gt;0), MAX($G$1:G107)+1, ""))</f>
@@ -4727,19 +4754,19 @@
         <v>20</v>
       </c>
       <c r="B109" s="31" t="s">
-        <v>112</v>
+        <v>257</v>
       </c>
       <c r="C109" s="32">
         <v>20</v>
       </c>
       <c r="D109" s="30" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="E109" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F109" s="30" t="s">
-        <v>113</v>
+        <v>258</v>
       </c>
       <c r="G109" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F109),0)&gt;0), MAX($G$1:G108)+1, ""))</f>
@@ -4755,19 +4782,19 @@
         <v>20</v>
       </c>
       <c r="B110" s="31" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="C110" s="32">
         <v>20</v>
       </c>
       <c r="D110" s="30" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="E110" s="31" t="s">
-        <v>299</v>
+        <v>8</v>
       </c>
       <c r="F110" s="30" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="G110" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F110),0)&gt;0), MAX($G$1:G109)+1, ""))</f>
@@ -4783,19 +4810,19 @@
         <v>20</v>
       </c>
       <c r="B111" s="31" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C111" s="32">
         <v>20</v>
       </c>
       <c r="D111" s="30" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="E111" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F111" s="30" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="G111" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F111),0)&gt;0), MAX($G$1:G110)+1, ""))</f>
@@ -4807,25 +4834,28 @@
       </c>
     </row>
     <row r="112" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A112" s="36">
+      <c r="A112" s="30">
         <v>20</v>
       </c>
-      <c r="B112" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="C112" s="38">
+      <c r="B112" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="C112" s="32">
         <v>20</v>
       </c>
-      <c r="D112" s="36">
-        <v>3</v>
-      </c>
-      <c r="E112" s="37" t="s">
-        <v>304</v>
-      </c>
-      <c r="F112" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="G112" s="29"/>
+      <c r="D112" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="E112" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F112" s="30" t="s">
+        <v>115</v>
+      </c>
+      <c r="G112" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F112),0)&gt;0), MAX($G$1:G111)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H112" s="21" t="b">
         <f>A112=C112</f>
         <v>1</v>
@@ -4836,7 +4866,7 @@
         <v>20</v>
       </c>
       <c r="B113" s="27" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="C113" s="28">
         <v>20</v>
@@ -4848,7 +4878,7 @@
         <v>299</v>
       </c>
       <c r="F113" s="26" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G113" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F113),0)&gt;0), MAX($G$1:G112)+1, ""))</f>
@@ -4864,19 +4894,19 @@
         <v>20</v>
       </c>
       <c r="B114" s="31" t="s">
-        <v>366</v>
+        <v>112</v>
       </c>
       <c r="C114" s="32">
         <v>20</v>
       </c>
-      <c r="D114" s="30">
-        <v>2.4</v>
+      <c r="D114" s="30" t="s">
+        <v>219</v>
       </c>
       <c r="E114" s="31" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="F114" s="30" t="s">
-        <v>367</v>
+        <v>113</v>
       </c>
       <c r="G114" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F114),0)&gt;0), MAX($G$1:G113)+1, ""))</f>
@@ -4892,19 +4922,19 @@
         <v>20</v>
       </c>
       <c r="B115" s="31" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C115" s="32">
         <v>20</v>
       </c>
       <c r="D115" s="30" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E115" s="31" t="s">
-        <v>60</v>
+        <v>299</v>
       </c>
       <c r="F115" s="30" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G115" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F115),0)&gt;0), MAX($G$1:G114)+1, ""))</f>
@@ -4916,23 +4946,23 @@
       </c>
     </row>
     <row r="116" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A116" s="26">
+      <c r="A116" s="30">
         <v>20</v>
       </c>
-      <c r="B116" s="27" t="s">
-        <v>339</v>
-      </c>
-      <c r="C116" s="28">
+      <c r="B116" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="C116" s="32">
         <v>20</v>
       </c>
-      <c r="D116" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E116" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F116" s="26" t="s">
-        <v>344</v>
+      <c r="D116" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="E116" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F116" s="30" t="s">
+        <v>109</v>
       </c>
       <c r="G116" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F116),0)&gt;0), MAX($G$1:G115)+1, ""))</f>
@@ -4948,19 +4978,19 @@
         <v>20</v>
       </c>
       <c r="B117" s="37" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C117" s="38">
         <v>20</v>
       </c>
       <c r="D117" s="36">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="E117" s="37" t="s">
-        <v>336</v>
+        <v>304</v>
       </c>
       <c r="F117" s="36" t="s">
-        <v>332</v>
+        <v>105</v>
       </c>
       <c r="G117" s="29"/>
       <c r="H117" s="21" t="b">
@@ -4969,23 +4999,23 @@
       </c>
     </row>
     <row r="118" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A118" s="30">
+      <c r="A118" s="26">
         <v>20</v>
       </c>
-      <c r="B118" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="C118" s="32">
+      <c r="B118" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C118" s="28">
         <v>20</v>
       </c>
-      <c r="D118" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E118" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F118" s="30" t="s">
-        <v>102</v>
+      <c r="D118" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E118" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="F118" s="26" t="s">
+        <v>301</v>
       </c>
       <c r="G118" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F118),0)&gt;0), MAX($G$1:G117)+1, ""))</f>
@@ -5001,19 +5031,19 @@
         <v>20</v>
       </c>
       <c r="B119" s="31" t="s">
-        <v>263</v>
+        <v>365</v>
       </c>
       <c r="C119" s="32">
         <v>20</v>
       </c>
       <c r="D119" s="30">
-        <v>6.2</v>
+        <v>2.4</v>
       </c>
       <c r="E119" s="31" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F119" s="30" t="s">
-        <v>264</v>
+        <v>366</v>
       </c>
       <c r="G119" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F119),0)&gt;0), MAX($G$1:G118)+1, ""))</f>
@@ -5029,19 +5059,19 @@
         <v>20</v>
       </c>
       <c r="B120" s="31" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C120" s="32">
         <v>20</v>
       </c>
       <c r="D120" s="30" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E120" s="31" t="s">
-        <v>299</v>
+        <v>60</v>
       </c>
       <c r="F120" s="30" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G120" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F120),0)&gt;0), MAX($G$1:G119)+1, ""))</f>
@@ -5057,19 +5087,19 @@
         <v>20</v>
       </c>
       <c r="B121" s="27" t="s">
-        <v>300</v>
+        <v>339</v>
       </c>
       <c r="C121" s="28">
         <v>20</v>
       </c>
       <c r="D121" s="26">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="E121" s="27" t="s">
-        <v>299</v>
+        <v>81</v>
       </c>
       <c r="F121" s="26" t="s">
-        <v>301</v>
+        <v>343</v>
       </c>
       <c r="G121" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F121),0)&gt;0), MAX($G$1:G120)+1, ""))</f>
@@ -5081,79 +5111,76 @@
       </c>
     </row>
     <row r="122" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A122" s="30">
+      <c r="A122" s="36">
         <v>20</v>
       </c>
-      <c r="B122" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="C122" s="32">
+      <c r="B122" s="37" t="s">
+        <v>335</v>
+      </c>
+      <c r="C122" s="38">
         <v>20</v>
       </c>
-      <c r="D122" s="30" t="s">
-        <v>216</v>
-      </c>
-      <c r="E122" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F122" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="G122" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F122),0)&gt;0), MAX($G$1:G121)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D122" s="36">
+        <v>3.2</v>
+      </c>
+      <c r="E122" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="F122" s="36" t="s">
+        <v>332</v>
+      </c>
+      <c r="G122" s="29"/>
       <c r="H122" s="21" t="b">
         <f>A122=C122</f>
         <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A123" s="26">
+      <c r="A123" s="30">
         <v>20</v>
       </c>
-      <c r="B123" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="C123" s="28">
-        <v>23</v>
-      </c>
-      <c r="D123" s="26">
-        <v>3.9</v>
-      </c>
-      <c r="E123" s="27" t="s">
-        <v>309</v>
-      </c>
-      <c r="F123" s="26" t="s">
-        <v>311</v>
+      <c r="B123" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="C123" s="32">
+        <v>20</v>
+      </c>
+      <c r="D123" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E123" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F123" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G123" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F123),0)&gt;0), MAX($G$1:G121)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F123),0)&gt;0), MAX($G$1:G122)+1, ""))</f>
         <v/>
       </c>
       <c r="H123" s="21" t="b">
         <f>A123=C123</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A124" s="26">
+      <c r="A124" s="30">
         <v>20</v>
       </c>
-      <c r="B124" s="27" t="s">
-        <v>355</v>
-      </c>
-      <c r="C124" s="28">
+      <c r="B124" s="31" t="s">
+        <v>263</v>
+      </c>
+      <c r="C124" s="32">
         <v>20</v>
       </c>
-      <c r="D124" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E124" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F124" s="26" t="s">
-        <v>356</v>
+      <c r="D124" s="30">
+        <v>6.2</v>
+      </c>
+      <c r="E124" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F124" s="30" t="s">
+        <v>264</v>
       </c>
       <c r="G124" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F124),0)&gt;0), MAX($G$1:G123)+1, ""))</f>
@@ -5169,19 +5196,19 @@
         <v>20</v>
       </c>
       <c r="B125" s="31" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C125" s="32">
         <v>20</v>
       </c>
       <c r="D125" s="30" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E125" s="31" t="s">
-        <v>8</v>
+        <v>299</v>
       </c>
       <c r="F125" s="30" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G125" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F125),0)&gt;0), MAX($G$1:G124)+1, ""))</f>
@@ -5193,23 +5220,23 @@
       </c>
     </row>
     <row r="126" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A126" s="30">
+      <c r="A126" s="26">
         <v>20</v>
       </c>
-      <c r="B126" s="31" t="s">
-        <v>89</v>
-      </c>
-      <c r="C126" s="32">
+      <c r="B126" s="27" t="s">
+        <v>300</v>
+      </c>
+      <c r="C126" s="28">
         <v>20</v>
       </c>
-      <c r="D126" s="30" t="s">
-        <v>223</v>
-      </c>
-      <c r="E126" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F126" s="30" t="s">
-        <v>90</v>
+      <c r="D126" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E126" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="F126" s="26" t="s">
+        <v>301</v>
       </c>
       <c r="G126" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F126),0)&gt;0), MAX($G$1:G125)+1, ""))</f>
@@ -5225,19 +5252,19 @@
         <v>20</v>
       </c>
       <c r="B127" s="31" t="s">
-        <v>290</v>
+        <v>95</v>
       </c>
       <c r="C127" s="32">
         <v>20</v>
       </c>
-      <c r="D127" s="30">
-        <v>1.8</v>
+      <c r="D127" s="30" t="s">
+        <v>216</v>
       </c>
       <c r="E127" s="31" t="s">
-        <v>291</v>
+        <v>8</v>
       </c>
       <c r="F127" s="30" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="G127" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F127),0)&gt;0), MAX($G$1:G126)+1, ""))</f>
@@ -5249,51 +5276,51 @@
       </c>
     </row>
     <row r="128" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A128" s="30">
+      <c r="A128" s="26">
         <v>20</v>
       </c>
-      <c r="B128" s="31" t="s">
-        <v>87</v>
-      </c>
-      <c r="C128" s="32">
-        <v>20</v>
-      </c>
-      <c r="D128" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="E128" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F128" s="30" t="s">
-        <v>88</v>
+      <c r="B128" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="C128" s="28">
+        <v>23</v>
+      </c>
+      <c r="D128" s="26">
+        <v>3.9</v>
+      </c>
+      <c r="E128" s="27" t="s">
+        <v>309</v>
+      </c>
+      <c r="F128" s="26" t="s">
+        <v>311</v>
       </c>
       <c r="G128" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F128),0)&gt;0), MAX($G$1:G127)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F128),0)&gt;0), MAX($G$1:G126)+1, ""))</f>
         <v/>
       </c>
       <c r="H128" s="21" t="b">
         <f>A128=C128</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A129" s="30">
+      <c r="A129" s="26">
         <v>20</v>
       </c>
-      <c r="B129" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="C129" s="32">
+      <c r="B129" s="27" t="s">
+        <v>354</v>
+      </c>
+      <c r="C129" s="28">
         <v>20</v>
       </c>
-      <c r="D129" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="E129" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F129" s="30" t="s">
-        <v>86</v>
+      <c r="D129" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E129" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F129" s="26" t="s">
+        <v>355</v>
       </c>
       <c r="G129" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F129),0)&gt;0), MAX($G$1:G128)+1, ""))</f>
@@ -5309,7 +5336,7 @@
         <v>20</v>
       </c>
       <c r="B130" s="31" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="C130" s="32">
         <v>20</v>
@@ -5318,10 +5345,10 @@
         <v>218</v>
       </c>
       <c r="E130" s="31" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F130" s="30" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="G130" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F130),0)&gt;0), MAX($G$1:G129)+1, ""))</f>
@@ -5337,19 +5364,19 @@
         <v>20</v>
       </c>
       <c r="B131" s="31" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C131" s="32">
         <v>20</v>
       </c>
       <c r="D131" s="30" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="E131" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F131" s="30" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G131" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F131),0)&gt;0), MAX($G$1:G130)+1, ""))</f>
@@ -5365,19 +5392,19 @@
         <v>20</v>
       </c>
       <c r="B132" s="31" t="s">
-        <v>76</v>
+        <v>290</v>
       </c>
       <c r="C132" s="32">
         <v>20</v>
       </c>
-      <c r="D132" s="30" t="s">
-        <v>216</v>
+      <c r="D132" s="30">
+        <v>1.8</v>
       </c>
       <c r="E132" s="31" t="s">
-        <v>8</v>
+        <v>291</v>
       </c>
       <c r="F132" s="30" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="G132" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B132),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E132),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F132),0)&gt;0), MAX($G$1:G131)+1, ""))</f>
@@ -5389,23 +5416,23 @@
       </c>
     </row>
     <row r="133" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A133" s="26">
-        <v>25</v>
-      </c>
-      <c r="B133" s="27" t="s">
-        <v>178</v>
-      </c>
-      <c r="C133" s="28">
-        <v>25</v>
-      </c>
-      <c r="D133" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="E133" s="27" t="s">
+      <c r="A133" s="30">
+        <v>20</v>
+      </c>
+      <c r="B133" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="C133" s="32">
+        <v>20</v>
+      </c>
+      <c r="D133" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="E133" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F133" s="26" t="s">
-        <v>179</v>
+      <c r="F133" s="30" t="s">
+        <v>88</v>
       </c>
       <c r="G133" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F133),0)&gt;0), MAX($G$1:G132)+1, ""))</f>
@@ -5417,23 +5444,23 @@
       </c>
     </row>
     <row r="134" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A134" s="26">
-        <v>25</v>
-      </c>
-      <c r="B134" s="27" t="s">
-        <v>176</v>
-      </c>
-      <c r="C134" s="28">
-        <v>25</v>
-      </c>
-      <c r="D134" s="26" t="s">
-        <v>237</v>
-      </c>
-      <c r="E134" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="F134" s="26" t="s">
-        <v>177</v>
+      <c r="A134" s="30">
+        <v>20</v>
+      </c>
+      <c r="B134" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="C134" s="32">
+        <v>20</v>
+      </c>
+      <c r="D134" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="E134" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F134" s="30" t="s">
+        <v>86</v>
       </c>
       <c r="G134" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F134),0)&gt;0), MAX($G$1:G133)+1, ""))</f>
@@ -5445,23 +5472,23 @@
       </c>
     </row>
     <row r="135" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A135" s="26">
-        <v>25</v>
-      </c>
-      <c r="B135" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="C135" s="28">
-        <v>25</v>
-      </c>
-      <c r="D135" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="E135" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="F135" s="26" t="s">
-        <v>175</v>
+      <c r="A135" s="30">
+        <v>20</v>
+      </c>
+      <c r="B135" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="C135" s="32">
+        <v>20</v>
+      </c>
+      <c r="D135" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="E135" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="F135" s="30" t="s">
+        <v>82</v>
       </c>
       <c r="G135" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F135),0)&gt;0), MAX($G$1:G134)+1, ""))</f>
@@ -5473,23 +5500,23 @@
       </c>
     </row>
     <row r="136" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A136" s="26">
-        <v>25</v>
-      </c>
-      <c r="B136" s="27" t="s">
-        <v>173</v>
-      </c>
-      <c r="C136" s="28">
-        <v>25</v>
-      </c>
-      <c r="D136" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="E136" s="27" t="s">
+      <c r="A136" s="30">
+        <v>20</v>
+      </c>
+      <c r="B136" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="C136" s="32">
+        <v>20</v>
+      </c>
+      <c r="D136" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="E136" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F136" s="26" t="s">
-        <v>324</v>
+      <c r="F136" s="30" t="s">
+        <v>79</v>
       </c>
       <c r="G136" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F136),0)&gt;0), MAX($G$1:G135)+1, ""))</f>
@@ -5501,23 +5528,23 @@
       </c>
     </row>
     <row r="137" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A137" s="26">
-        <v>25</v>
-      </c>
-      <c r="B137" s="27" t="s">
-        <v>359</v>
-      </c>
-      <c r="C137" s="28">
-        <v>25</v>
-      </c>
-      <c r="D137" s="26">
-        <v>3</v>
-      </c>
-      <c r="E137" s="27" t="s">
+      <c r="A137" s="30">
+        <v>20</v>
+      </c>
+      <c r="B137" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="C137" s="32">
+        <v>20</v>
+      </c>
+      <c r="D137" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="E137" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F137" s="26" t="s">
-        <v>360</v>
+      <c r="F137" s="30" t="s">
+        <v>77</v>
       </c>
       <c r="G137" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F137),0)&gt;0), MAX($G$1:G136)+1, ""))</f>
@@ -5533,19 +5560,19 @@
         <v>25</v>
       </c>
       <c r="B138" s="27" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C138" s="28">
         <v>25</v>
       </c>
-      <c r="D138" s="26">
-        <v>2.7</v>
+      <c r="D138" s="26" t="s">
+        <v>225</v>
       </c>
       <c r="E138" s="27" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F138" s="26" t="s">
-        <v>338</v>
+        <v>179</v>
       </c>
       <c r="G138" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F138),0)&gt;0), MAX($G$1:G137)+1, ""))</f>
@@ -5557,23 +5584,23 @@
       </c>
     </row>
     <row r="139" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A139" s="30">
+      <c r="A139" s="26">
         <v>25</v>
       </c>
-      <c r="B139" s="31" t="s">
-        <v>284</v>
-      </c>
-      <c r="C139" s="32">
+      <c r="B139" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="C139" s="28">
         <v>25</v>
       </c>
-      <c r="D139" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E139" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F139" s="30" t="s">
-        <v>102</v>
+      <c r="D139" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="E139" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="F139" s="26" t="s">
+        <v>177</v>
       </c>
       <c r="G139" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F139),0)&gt;0), MAX($G$1:G138)+1, ""))</f>
@@ -5585,23 +5612,23 @@
       </c>
     </row>
     <row r="140" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A140" s="30">
+      <c r="A140" s="26">
         <v>25</v>
       </c>
-      <c r="B140" s="31" t="s">
-        <v>282</v>
-      </c>
-      <c r="C140" s="32">
+      <c r="B140" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="C140" s="28">
         <v>25</v>
       </c>
-      <c r="D140" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E140" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F140" s="30" t="s">
-        <v>102</v>
+      <c r="D140" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="E140" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="F140" s="26" t="s">
+        <v>175</v>
       </c>
       <c r="G140" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F140),0)&gt;0), MAX($G$1:G139)+1, ""))</f>
@@ -5617,19 +5644,19 @@
         <v>25</v>
       </c>
       <c r="B141" s="27" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C141" s="28">
         <v>25</v>
       </c>
       <c r="D141" s="26" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="E141" s="27" t="s">
-        <v>245</v>
+        <v>8</v>
       </c>
       <c r="F141" s="26" t="s">
-        <v>171</v>
+        <v>324</v>
       </c>
       <c r="G141" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F141),0)&gt;0), MAX($G$1:G140)+1, ""))</f>
@@ -5645,19 +5672,19 @@
         <v>25</v>
       </c>
       <c r="B142" s="27" t="s">
-        <v>168</v>
+        <v>358</v>
       </c>
       <c r="C142" s="28">
         <v>25</v>
       </c>
-      <c r="D142" s="26" t="s">
-        <v>217</v>
+      <c r="D142" s="26">
+        <v>3</v>
       </c>
       <c r="E142" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F142" s="26" t="s">
-        <v>169</v>
+        <v>359</v>
       </c>
       <c r="G142" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F142),0)&gt;0), MAX($G$1:G141)+1, ""))</f>
@@ -5673,19 +5700,19 @@
         <v>25</v>
       </c>
       <c r="B143" s="27" t="s">
-        <v>357</v>
+        <v>172</v>
       </c>
       <c r="C143" s="28">
         <v>25</v>
       </c>
       <c r="D143" s="26">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="E143" s="27" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="F143" s="26" t="s">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="G143" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F143),0)&gt;0), MAX($G$1:G142)+1, ""))</f>
@@ -5701,7 +5728,7 @@
         <v>25</v>
       </c>
       <c r="B144" s="31" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C144" s="32">
         <v>25</v>
@@ -5710,7 +5737,7 @@
         <v>207</v>
       </c>
       <c r="E144" s="31" t="s">
-        <v>8</v>
+        <v>283</v>
       </c>
       <c r="F144" s="30" t="s">
         <v>102</v>
@@ -5725,23 +5752,23 @@
       </c>
     </row>
     <row r="145" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A145" s="26">
+      <c r="A145" s="30">
         <v>25</v>
       </c>
-      <c r="B145" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="C145" s="28">
+      <c r="B145" s="31" t="s">
+        <v>282</v>
+      </c>
+      <c r="C145" s="32">
         <v>25</v>
       </c>
-      <c r="D145" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="E145" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="F145" s="26" t="s">
-        <v>167</v>
+      <c r="D145" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E145" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="F145" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G145" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B145),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E145),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F145),0)&gt;0), MAX($G$1:G144)+1, ""))</f>
@@ -5757,19 +5784,19 @@
         <v>25</v>
       </c>
       <c r="B146" s="27" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C146" s="28">
         <v>25</v>
       </c>
       <c r="D146" s="26" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E146" s="27" t="s">
-        <v>131</v>
+        <v>245</v>
       </c>
       <c r="F146" s="26" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="G146" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F146),0)&gt;0), MAX($G$1:G145)+1, ""))</f>
@@ -5785,19 +5812,19 @@
         <v>25</v>
       </c>
       <c r="B147" s="27" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="C147" s="28">
         <v>25</v>
       </c>
       <c r="D147" s="26" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="E147" s="27" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F147" s="26" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="G147" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F147),0)&gt;0), MAX($G$1:G146)+1, ""))</f>
@@ -5813,19 +5840,19 @@
         <v>25</v>
       </c>
       <c r="B148" s="27" t="s">
-        <v>160</v>
+        <v>356</v>
       </c>
       <c r="C148" s="28">
         <v>25</v>
       </c>
-      <c r="D148" s="26" t="s">
-        <v>236</v>
+      <c r="D148" s="26">
+        <v>3.4</v>
       </c>
       <c r="E148" s="27" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F148" s="26" t="s">
-        <v>161</v>
+        <v>357</v>
       </c>
       <c r="G148" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F148),0)&gt;0), MAX($G$1:G147)+1, ""))</f>
@@ -5837,23 +5864,23 @@
       </c>
     </row>
     <row r="149" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A149" s="26">
+      <c r="A149" s="30">
         <v>25</v>
       </c>
-      <c r="B149" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="C149" s="28">
+      <c r="B149" s="31" t="s">
+        <v>278</v>
+      </c>
+      <c r="C149" s="32">
         <v>25</v>
       </c>
-      <c r="D149" s="26" t="s">
-        <v>228</v>
-      </c>
-      <c r="E149" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F149" s="26" t="s">
-        <v>159</v>
+      <c r="D149" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E149" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F149" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G149" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B149),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E149),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F149),0)&gt;0), MAX($G$1:G148)+1, ""))</f>
@@ -5869,19 +5896,19 @@
         <v>25</v>
       </c>
       <c r="B150" s="27" t="s">
-        <v>342</v>
+        <v>166</v>
       </c>
       <c r="C150" s="28">
         <v>25</v>
       </c>
-      <c r="D150" s="26">
-        <v>3.4</v>
+      <c r="D150" s="26" t="s">
+        <v>221</v>
       </c>
       <c r="E150" s="27" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="F150" s="26" t="s">
-        <v>343</v>
+        <v>167</v>
       </c>
       <c r="G150" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B150),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E150),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F150),0)&gt;0), MAX($G$1:G149)+1, ""))</f>
@@ -5897,19 +5924,19 @@
         <v>25</v>
       </c>
       <c r="B151" s="27" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="C151" s="28">
         <v>25</v>
       </c>
       <c r="D151" s="26" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E151" s="27" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="F151" s="26" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="G151" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B151),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E151),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F151),0)&gt;0), MAX($G$1:G150)+1, ""))</f>
@@ -5925,19 +5952,19 @@
         <v>25</v>
       </c>
       <c r="B152" s="27" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C152" s="28">
         <v>25</v>
       </c>
       <c r="D152" s="26" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="E152" s="27" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="F152" s="26" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G152" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B152),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E152),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F152),0)&gt;0), MAX($G$1:G151)+1, ""))</f>
@@ -5953,19 +5980,19 @@
         <v>25</v>
       </c>
       <c r="B153" s="27" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="C153" s="28">
         <v>25</v>
       </c>
       <c r="D153" s="26" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="E153" s="27" t="s">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="F153" s="26" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="G153" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B153),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E153),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F153),0)&gt;0), MAX($G$1:G152)+1, ""))</f>
@@ -5981,19 +6008,19 @@
         <v>25</v>
       </c>
       <c r="B154" s="27" t="s">
-        <v>247</v>
+        <v>158</v>
       </c>
       <c r="C154" s="28">
         <v>25</v>
       </c>
-      <c r="D154" s="39" t="s">
-        <v>229</v>
+      <c r="D154" s="26" t="s">
+        <v>228</v>
       </c>
       <c r="E154" s="27" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="F154" s="26" t="s">
-        <v>248</v>
+        <v>159</v>
       </c>
       <c r="G154" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B154),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E154),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F154),0)&gt;0), MAX($G$1:G153)+1, ""))</f>
@@ -6009,19 +6036,19 @@
         <v>25</v>
       </c>
       <c r="B155" s="27" t="s">
-        <v>150</v>
+        <v>392</v>
       </c>
       <c r="C155" s="28">
         <v>25</v>
       </c>
-      <c r="D155" s="26" t="s">
-        <v>235</v>
+      <c r="D155" s="26">
+        <v>3.4</v>
       </c>
       <c r="E155" s="27" t="s">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="F155" s="26" t="s">
-        <v>151</v>
+        <v>342</v>
       </c>
       <c r="G155" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F155),0)&gt;0), MAX($G$1:G154)+1, ""))</f>
@@ -6033,26 +6060,26 @@
       </c>
     </row>
     <row r="156" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A156" s="30">
+      <c r="A156" s="26">
         <v>25</v>
       </c>
-      <c r="B156" s="31" t="s">
-        <v>288</v>
-      </c>
-      <c r="C156" s="32">
+      <c r="B156" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="C156" s="28">
         <v>25</v>
       </c>
-      <c r="D156" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E156" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F156" s="30" t="s">
-        <v>102</v>
+      <c r="D156" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="E156" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F156" s="26" t="s">
+        <v>157</v>
       </c>
       <c r="G156" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B156),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E156),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F156),0)&gt;0), MAX($G$1:G155)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B156),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E156),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F156),0)&gt;0), MAX($G$1:G154)+1, ""))</f>
         <v/>
       </c>
       <c r="H156" s="21" t="b">
@@ -6061,23 +6088,23 @@
       </c>
     </row>
     <row r="157" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A157" s="30">
+      <c r="A157" s="26">
         <v>25</v>
       </c>
-      <c r="B157" s="31" t="s">
-        <v>286</v>
-      </c>
-      <c r="C157" s="32">
+      <c r="B157" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="C157" s="28">
         <v>25</v>
       </c>
-      <c r="D157" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E157" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F157" s="30" t="s">
-        <v>102</v>
+      <c r="D157" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="E157" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F157" s="26" t="s">
+        <v>155</v>
       </c>
       <c r="G157" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F157),0)&gt;0), MAX($G$1:G156)+1, ""))</f>
@@ -6089,23 +6116,23 @@
       </c>
     </row>
     <row r="158" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A158" s="30">
+      <c r="A158" s="26">
         <v>25</v>
       </c>
-      <c r="B158" s="31" t="s">
-        <v>287</v>
-      </c>
-      <c r="C158" s="32">
+      <c r="B158" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="C158" s="28">
         <v>25</v>
       </c>
-      <c r="D158" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E158" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F158" s="30" t="s">
-        <v>102</v>
+      <c r="D158" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="E158" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="F158" s="26" t="s">
+        <v>153</v>
       </c>
       <c r="G158" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B158),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E158),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F158),0)&gt;0), MAX($G$1:G157)+1, ""))</f>
@@ -6121,19 +6148,19 @@
         <v>25</v>
       </c>
       <c r="B159" s="27" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C159" s="28">
         <v>25</v>
       </c>
-      <c r="D159" s="26">
-        <v>2.5</v>
+      <c r="D159" s="39" t="s">
+        <v>229</v>
       </c>
       <c r="E159" s="27" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="F159" s="26" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="G159" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F159),0)&gt;0), MAX($G$1:G158)+1, ""))</f>
@@ -6145,23 +6172,23 @@
       </c>
     </row>
     <row r="160" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A160" s="30">
+      <c r="A160" s="26">
         <v>25</v>
       </c>
-      <c r="B160" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="C160" s="32">
+      <c r="B160" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C160" s="28">
         <v>25</v>
       </c>
-      <c r="D160" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E160" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F160" s="30" t="s">
-        <v>102</v>
+      <c r="D160" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="E160" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="F160" s="26" t="s">
+        <v>151</v>
       </c>
       <c r="G160" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B160),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E160),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F160),0)&gt;0), MAX($G$1:G159)+1, ""))</f>
@@ -6173,26 +6200,26 @@
       </c>
     </row>
     <row r="161" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A161" s="26">
+      <c r="A161" s="30">
         <v>25</v>
       </c>
-      <c r="B161" s="27" t="s">
-        <v>148</v>
-      </c>
-      <c r="C161" s="28">
+      <c r="B161" s="31" t="s">
+        <v>288</v>
+      </c>
+      <c r="C161" s="32">
         <v>25</v>
       </c>
-      <c r="D161" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="E161" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F161" s="26" t="s">
-        <v>149</v>
+      <c r="D161" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E161" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="F161" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G161" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B161),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E161),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F161),0)&gt;0), MAX($G$1:G159)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B161),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E161),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F161),0)&gt;0), MAX($G$1:G160)+1, ""))</f>
         <v/>
       </c>
       <c r="H161" s="21" t="b">
@@ -6202,22 +6229,22 @@
     </row>
     <row r="162" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A162" s="30">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B162" s="31" t="s">
-        <v>192</v>
+        <v>286</v>
       </c>
       <c r="C162" s="32">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D162" s="30" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="E162" s="31" t="s">
-        <v>131</v>
+        <v>283</v>
       </c>
       <c r="F162" s="30" t="s">
-        <v>193</v>
+        <v>102</v>
       </c>
       <c r="G162" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B162),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E162),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F162),0)&gt;0), MAX($G$1:G161)+1, ""))</f>
@@ -6230,22 +6257,22 @@
     </row>
     <row r="163" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A163" s="30">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B163" s="31" t="s">
-        <v>191</v>
+        <v>287</v>
       </c>
       <c r="C163" s="32">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D163" s="30" t="s">
-        <v>241</v>
+        <v>207</v>
       </c>
       <c r="E163" s="31" t="s">
-        <v>131</v>
+        <v>283</v>
       </c>
       <c r="F163" s="30" t="s">
-        <v>190</v>
+        <v>102</v>
       </c>
       <c r="G163" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B163),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E163),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F163),0)&gt;0), MAX($G$1:G162)+1, ""))</f>
@@ -6257,23 +6284,23 @@
       </c>
     </row>
     <row r="164" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A164" s="30">
-        <v>30</v>
-      </c>
-      <c r="B164" s="31" t="s">
-        <v>189</v>
-      </c>
-      <c r="C164" s="32">
-        <v>30</v>
-      </c>
-      <c r="D164" s="30" t="s">
-        <v>240</v>
-      </c>
-      <c r="E164" s="31" t="s">
+      <c r="A164" s="26">
+        <v>25</v>
+      </c>
+      <c r="B164" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="C164" s="28">
+        <v>25</v>
+      </c>
+      <c r="D164" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E164" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="F164" s="30" t="s">
-        <v>190</v>
+      <c r="F164" s="26" t="s">
+        <v>253</v>
       </c>
       <c r="G164" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B164),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E164),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F164),0)&gt;0), MAX($G$1:G163)+1, ""))</f>
@@ -6286,22 +6313,22 @@
     </row>
     <row r="165" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A165" s="30">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B165" s="31" t="s">
-        <v>246</v>
+        <v>285</v>
       </c>
       <c r="C165" s="32">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D165" s="30" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="E165" s="31" t="s">
-        <v>8</v>
+        <v>283</v>
       </c>
       <c r="F165" s="30" t="s">
-        <v>188</v>
+        <v>102</v>
       </c>
       <c r="G165" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B165),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E165),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F165),0)&gt;0), MAX($G$1:G164)+1, ""))</f>
@@ -6313,26 +6340,26 @@
       </c>
     </row>
     <row r="166" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A166" s="30">
-        <v>30</v>
-      </c>
-      <c r="B166" s="31" t="s">
-        <v>186</v>
-      </c>
-      <c r="C166" s="32">
-        <v>30</v>
-      </c>
-      <c r="D166" s="30" t="s">
-        <v>229</v>
-      </c>
-      <c r="E166" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F166" s="30" t="s">
-        <v>187</v>
+      <c r="A166" s="26">
+        <v>25</v>
+      </c>
+      <c r="B166" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="C166" s="28">
+        <v>25</v>
+      </c>
+      <c r="D166" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="E166" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F166" s="26" t="s">
+        <v>149</v>
       </c>
       <c r="G166" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B166),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E166),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F166),0)&gt;0), MAX($G$1:G165)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B166),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E166),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F166),0)&gt;0), MAX($G$1:G164)+1, ""))</f>
         <v/>
       </c>
       <c r="H166" s="21" t="b">
@@ -6345,19 +6372,19 @@
         <v>30</v>
       </c>
       <c r="B167" s="31" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C167" s="32">
         <v>30</v>
       </c>
       <c r="D167" s="30" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E167" s="31" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="F167" s="30" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="G167" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B167),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E167),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F167),0)&gt;0), MAX($G$1:G166)+1, ""))</f>
@@ -6369,23 +6396,23 @@
       </c>
     </row>
     <row r="168" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A168" s="26">
+      <c r="A168" s="30">
         <v>30</v>
       </c>
-      <c r="B168" s="27" t="s">
-        <v>377</v>
-      </c>
-      <c r="C168" s="28">
+      <c r="B168" s="31" t="s">
+        <v>191</v>
+      </c>
+      <c r="C168" s="32">
         <v>30</v>
       </c>
-      <c r="D168" s="26">
-        <v>5</v>
-      </c>
-      <c r="E168" s="27" t="s">
-        <v>378</v>
-      </c>
-      <c r="F168" s="26" t="s">
-        <v>25</v>
+      <c r="D168" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="E168" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="F168" s="30" t="s">
+        <v>190</v>
       </c>
       <c r="G168" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B168),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E168),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F168),0)&gt;0), MAX($G$1:G167)+1, ""))</f>
@@ -6401,19 +6428,19 @@
         <v>30</v>
       </c>
       <c r="B169" s="31" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C169" s="32">
         <v>30</v>
       </c>
       <c r="D169" s="30" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E169" s="31" t="s">
         <v>131</v>
       </c>
       <c r="F169" s="30" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="G169" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B169),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E169),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F169),0)&gt;0), MAX($G$1:G168)+1, ""))</f>
@@ -6429,19 +6456,19 @@
         <v>30</v>
       </c>
       <c r="B170" s="31" t="s">
-        <v>337</v>
+        <v>246</v>
       </c>
       <c r="C170" s="32">
         <v>30</v>
       </c>
-      <c r="D170" s="30">
-        <v>2.9</v>
+      <c r="D170" s="30" t="s">
+        <v>217</v>
       </c>
       <c r="E170" s="31" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F170" s="30" t="s">
-        <v>338</v>
+        <v>188</v>
       </c>
       <c r="G170" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B170),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E170),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F170),0)&gt;0), MAX($G$1:G169)+1, ""))</f>
@@ -6453,26 +6480,26 @@
       </c>
     </row>
     <row r="171" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A171" s="30">
+      <c r="A171" s="26">
         <v>30</v>
       </c>
-      <c r="B171" s="31" t="s">
-        <v>180</v>
-      </c>
-      <c r="C171" s="32">
+      <c r="B171" s="27" t="s">
+        <v>393</v>
+      </c>
+      <c r="C171" s="28">
         <v>30</v>
       </c>
-      <c r="D171" s="30" t="s">
-        <v>238</v>
-      </c>
-      <c r="E171" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="F171" s="30" t="s">
-        <v>181</v>
+      <c r="D171" s="26">
+        <v>3.6</v>
+      </c>
+      <c r="E171" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F171" s="26" t="s">
+        <v>394</v>
       </c>
       <c r="G171" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B171),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E171),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F171),0)&gt;0), MAX($G$1:G169)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B171),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E171),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F171),0)&gt;0), MAX($G$1:G170)+1, ""))</f>
         <v/>
       </c>
       <c r="H171" s="21" t="b">
@@ -6481,23 +6508,23 @@
       </c>
     </row>
     <row r="172" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A172" s="26">
-        <v>40</v>
-      </c>
-      <c r="B172" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="C172" s="28">
-        <v>40</v>
-      </c>
-      <c r="D172" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="E172" s="27" t="s">
-        <v>198</v>
-      </c>
-      <c r="F172" s="26" t="s">
-        <v>199</v>
+      <c r="A172" s="30">
+        <v>30</v>
+      </c>
+      <c r="B172" s="31" t="s">
+        <v>186</v>
+      </c>
+      <c r="C172" s="32">
+        <v>30</v>
+      </c>
+      <c r="D172" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="E172" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F172" s="30" t="s">
+        <v>187</v>
       </c>
       <c r="G172" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B172),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E172),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F172),0)&gt;0), MAX($G$1:G171)+1, ""))</f>
@@ -6509,23 +6536,23 @@
       </c>
     </row>
     <row r="173" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A173" s="26">
-        <v>40</v>
-      </c>
-      <c r="B173" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="C173" s="28">
-        <v>40</v>
-      </c>
-      <c r="D173" s="26" t="s">
-        <v>242</v>
-      </c>
-      <c r="E173" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="F173" s="26" t="s">
-        <v>196</v>
+      <c r="A173" s="30">
+        <v>30</v>
+      </c>
+      <c r="B173" s="31" t="s">
+        <v>184</v>
+      </c>
+      <c r="C173" s="32">
+        <v>30</v>
+      </c>
+      <c r="D173" s="30" t="s">
+        <v>228</v>
+      </c>
+      <c r="E173" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="F173" s="30" t="s">
+        <v>185</v>
       </c>
       <c r="G173" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B173),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E173),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F173),0)&gt;0), MAX($G$1:G172)+1, ""))</f>
@@ -6538,22 +6565,22 @@
     </row>
     <row r="174" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A174" s="26">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B174" s="27" t="s">
-        <v>249</v>
+        <v>376</v>
       </c>
       <c r="C174" s="28">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D174" s="26">
-        <v>8.3000000000000007</v>
+        <v>5</v>
       </c>
       <c r="E174" s="27" t="s">
-        <v>250</v>
+        <v>377</v>
       </c>
       <c r="F174" s="26" t="s">
-        <v>251</v>
+        <v>25</v>
       </c>
       <c r="G174" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B174),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E174),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F174),0)&gt;0), MAX($G$1:G173)+1, ""))</f>
@@ -6565,23 +6592,23 @@
       </c>
     </row>
     <row r="175" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A175" s="26">
-        <v>45</v>
-      </c>
-      <c r="B175" s="27" t="s">
-        <v>294</v>
-      </c>
-      <c r="C175" s="28">
-        <v>45</v>
-      </c>
-      <c r="D175" s="26">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="E175" s="27" t="s">
-        <v>295</v>
-      </c>
-      <c r="F175" s="26" t="s">
-        <v>296</v>
+      <c r="A175" s="30">
+        <v>30</v>
+      </c>
+      <c r="B175" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="C175" s="32">
+        <v>30</v>
+      </c>
+      <c r="D175" s="30" t="s">
+        <v>239</v>
+      </c>
+      <c r="E175" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="F175" s="30" t="s">
+        <v>183</v>
       </c>
       <c r="G175" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B175),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E175),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F175),0)&gt;0), MAX($G$1:G174)+1, ""))</f>
@@ -6593,102 +6620,234 @@
       </c>
     </row>
     <row r="176" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A176" s="1"/>
-      <c r="C176" s="1"/>
-      <c r="D176" s="1"/>
-      <c r="F176" s="1"/>
-    </row>
-    <row r="177" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A177" s="1"/>
-      <c r="C177" s="1"/>
-      <c r="D177" s="1"/>
-      <c r="F177" s="1"/>
-    </row>
-    <row r="178" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A178" s="1"/>
-      <c r="C178" s="1"/>
-      <c r="D178" s="1"/>
-      <c r="F178" s="1"/>
-    </row>
-    <row r="179" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A179" s="1"/>
-      <c r="C179" s="1"/>
-      <c r="D179" s="1"/>
-      <c r="F179" s="1"/>
-    </row>
-    <row r="180" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A180" s="1"/>
-      <c r="C180" s="1"/>
-      <c r="D180" s="1"/>
-      <c r="F180" s="1"/>
-    </row>
-    <row r="181" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A181" s="1"/>
-      <c r="C181" s="1"/>
-      <c r="D181" s="1"/>
-      <c r="F181" s="1"/>
-    </row>
-    <row r="182" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A176" s="30">
+        <v>30</v>
+      </c>
+      <c r="B176" s="31" t="s">
+        <v>337</v>
+      </c>
+      <c r="C176" s="32">
+        <v>30</v>
+      </c>
+      <c r="D176" s="30">
+        <v>2.9</v>
+      </c>
+      <c r="E176" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="F176" s="30" t="s">
+        <v>338</v>
+      </c>
+      <c r="G176" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B176),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E176),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F176),0)&gt;0), MAX($G$1:G175)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H176" s="21" t="b">
+        <f>A176=C176</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A177" s="30">
+        <v>30</v>
+      </c>
+      <c r="B177" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="C177" s="32">
+        <v>30</v>
+      </c>
+      <c r="D177" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="E177" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="F177" s="30" t="s">
+        <v>181</v>
+      </c>
+      <c r="G177" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B177),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E177),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F177),0)&gt;0), MAX($G$1:G175)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H177" s="21" t="b">
+        <f>A177=C177</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A178" s="26">
+        <v>40</v>
+      </c>
+      <c r="B178" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="C178" s="28">
+        <v>40</v>
+      </c>
+      <c r="D178" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="E178" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="F178" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="G178" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B178),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E178),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F178),0)&gt;0), MAX($G$1:G177)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H178" s="21" t="b">
+        <f>A178=C178</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A179" s="26">
+        <v>40</v>
+      </c>
+      <c r="B179" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="C179" s="28">
+        <v>40</v>
+      </c>
+      <c r="D179" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="E179" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="F179" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="G179" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B179),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E179),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F179),0)&gt;0), MAX($G$1:G178)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H179" s="21" t="b">
+        <f>A179=C179</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A180" s="26">
+        <v>40</v>
+      </c>
+      <c r="B180" s="27" t="s">
+        <v>249</v>
+      </c>
+      <c r="C180" s="28">
+        <v>40</v>
+      </c>
+      <c r="D180" s="26">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E180" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="F180" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="G180" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B180),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E180),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F180),0)&gt;0), MAX($G$1:G179)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H180" s="21" t="b">
+        <f>A180=C180</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A181" s="26">
+        <v>45</v>
+      </c>
+      <c r="B181" s="27" t="s">
+        <v>294</v>
+      </c>
+      <c r="C181" s="28">
+        <v>45</v>
+      </c>
+      <c r="D181" s="26">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E181" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="F181" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="G181" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B181),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E181),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F181),0)&gt;0), MAX($G$1:G180)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H181" s="21" t="b">
+        <f>A181=C181</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="C182" s="1"/>
       <c r="D182" s="1"/>
       <c r="F182" s="1"/>
     </row>
-    <row r="183" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="C183" s="1"/>
       <c r="D183" s="1"/>
       <c r="F183" s="1"/>
     </row>
-    <row r="184" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="C184" s="1"/>
       <c r="D184" s="1"/>
       <c r="F184" s="1"/>
     </row>
-    <row r="185" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="C185" s="1"/>
       <c r="D185" s="1"/>
       <c r="F185" s="1"/>
     </row>
-    <row r="186" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="C186" s="1"/>
       <c r="D186" s="1"/>
       <c r="F186" s="1"/>
     </row>
-    <row r="187" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="C187" s="1"/>
       <c r="D187" s="1"/>
       <c r="F187" s="1"/>
     </row>
-    <row r="188" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="C188" s="1"/>
       <c r="D188" s="1"/>
       <c r="F188" s="1"/>
     </row>
-    <row r="189" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="C189" s="1"/>
       <c r="D189" s="1"/>
       <c r="F189" s="1"/>
     </row>
-    <row r="190" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="C190" s="1"/>
       <c r="D190" s="1"/>
       <c r="F190" s="1"/>
     </row>
-    <row r="191" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="C191" s="1"/>
       <c r="D191" s="1"/>
       <c r="F191" s="1"/>
     </row>
-    <row r="192" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="C192" s="1"/>
       <c r="D192" s="1"/>
@@ -11794,12 +11953,48 @@
       <c r="D1042" s="1"/>
       <c r="F1042" s="1"/>
     </row>
+    <row r="1043" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1043" s="1"/>
+      <c r="C1043" s="1"/>
+      <c r="D1043" s="1"/>
+      <c r="F1043" s="1"/>
+    </row>
+    <row r="1044" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1044" s="1"/>
+      <c r="C1044" s="1"/>
+      <c r="D1044" s="1"/>
+      <c r="F1044" s="1"/>
+    </row>
+    <row r="1045" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1045" s="1"/>
+      <c r="C1045" s="1"/>
+      <c r="D1045" s="1"/>
+      <c r="F1045" s="1"/>
+    </row>
+    <row r="1046" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1046" s="1"/>
+      <c r="C1046" s="1"/>
+      <c r="D1046" s="1"/>
+      <c r="F1046" s="1"/>
+    </row>
+    <row r="1047" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1047" s="1"/>
+      <c r="C1047" s="1"/>
+      <c r="D1047" s="1"/>
+      <c r="F1047" s="1"/>
+    </row>
+    <row r="1048" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1048" s="1"/>
+      <c r="C1048" s="1"/>
+      <c r="D1048" s="1"/>
+      <c r="F1048" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H175">
-    <sortState ref="A2:H175">
-      <sortCondition ref="A2:A175"/>
-      <sortCondition ref="B2:B175"/>
-      <sortCondition ref="D2:D175"/>
+  <autoFilter ref="A1:H181">
+    <sortState ref="A2:H181">
+      <sortCondition ref="A2:A181"/>
+      <sortCondition ref="B2:B181"/>
+      <sortCondition ref="D2:D181"/>
     </sortState>
   </autoFilter>
   <sortState ref="A2:H174">

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Consulta" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$183</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$146</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Base!$1:$1</definedName>
   </definedNames>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="407">
   <si>
     <t>Grupo</t>
   </si>
@@ -1234,6 +1234,18 @@
   </si>
   <si>
     <t>GRÃO MOGOL DEPOIS DO CAMPO SÃO LUIZ</t>
+  </si>
+  <si>
+    <t>RANGEL PESTANA</t>
+  </si>
+  <si>
+    <t>21820-040</t>
+  </si>
+  <si>
+    <t>BURACO DO FAIM</t>
+  </si>
+  <si>
+    <t>21810-007</t>
   </si>
 </sst>
 </file>
@@ -1751,7 +1763,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H1048"/>
+  <dimension ref="A1:H1050"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.453125" customWidth="1"/>
@@ -6480,26 +6492,26 @@
       </c>
     </row>
     <row r="171" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A171" s="26">
+      <c r="A171" s="30">
         <v>30</v>
       </c>
-      <c r="B171" s="27" t="s">
-        <v>393</v>
-      </c>
-      <c r="C171" s="28">
+      <c r="B171" s="31" t="s">
+        <v>405</v>
+      </c>
+      <c r="C171" s="32">
         <v>30</v>
       </c>
-      <c r="D171" s="26">
-        <v>3.6</v>
-      </c>
-      <c r="E171" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F171" s="26" t="s">
-        <v>394</v>
+      <c r="D171" s="30">
+        <v>6.2</v>
+      </c>
+      <c r="E171" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="F171" s="30" t="s">
+        <v>406</v>
       </c>
       <c r="G171" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B171),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E171),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F171),0)&gt;0), MAX($G$1:G170)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B171),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E171),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F171),0)&gt;0), MAX($G$1:G169)+1, ""))</f>
         <v/>
       </c>
       <c r="H171" s="21" t="b">
@@ -6508,23 +6520,23 @@
       </c>
     </row>
     <row r="172" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A172" s="30">
+      <c r="A172" s="26">
         <v>30</v>
       </c>
-      <c r="B172" s="31" t="s">
-        <v>186</v>
-      </c>
-      <c r="C172" s="32">
+      <c r="B172" s="27" t="s">
+        <v>393</v>
+      </c>
+      <c r="C172" s="28">
         <v>30</v>
       </c>
-      <c r="D172" s="30" t="s">
-        <v>229</v>
-      </c>
-      <c r="E172" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F172" s="30" t="s">
-        <v>187</v>
+      <c r="D172" s="26">
+        <v>3.6</v>
+      </c>
+      <c r="E172" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F172" s="26" t="s">
+        <v>394</v>
       </c>
       <c r="G172" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B172),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E172),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F172),0)&gt;0), MAX($G$1:G171)+1, ""))</f>
@@ -6540,19 +6552,19 @@
         <v>30</v>
       </c>
       <c r="B173" s="31" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C173" s="32">
         <v>30</v>
       </c>
       <c r="D173" s="30" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E173" s="31" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F173" s="30" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G173" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B173),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E173),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F173),0)&gt;0), MAX($G$1:G172)+1, ""))</f>
@@ -6564,23 +6576,23 @@
       </c>
     </row>
     <row r="174" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A174" s="26">
+      <c r="A174" s="30">
         <v>30</v>
       </c>
-      <c r="B174" s="27" t="s">
-        <v>376</v>
-      </c>
-      <c r="C174" s="28">
+      <c r="B174" s="31" t="s">
+        <v>184</v>
+      </c>
+      <c r="C174" s="32">
         <v>30</v>
       </c>
-      <c r="D174" s="26">
-        <v>5</v>
-      </c>
-      <c r="E174" s="27" t="s">
-        <v>377</v>
-      </c>
-      <c r="F174" s="26" t="s">
-        <v>25</v>
+      <c r="D174" s="30" t="s">
+        <v>228</v>
+      </c>
+      <c r="E174" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="F174" s="30" t="s">
+        <v>185</v>
       </c>
       <c r="G174" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B174),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E174),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F174),0)&gt;0), MAX($G$1:G173)+1, ""))</f>
@@ -6592,23 +6604,23 @@
       </c>
     </row>
     <row r="175" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A175" s="30">
+      <c r="A175" s="26">
         <v>30</v>
       </c>
-      <c r="B175" s="31" t="s">
-        <v>182</v>
-      </c>
-      <c r="C175" s="32">
+      <c r="B175" s="27" t="s">
+        <v>376</v>
+      </c>
+      <c r="C175" s="28">
         <v>30</v>
       </c>
-      <c r="D175" s="30" t="s">
-        <v>239</v>
-      </c>
-      <c r="E175" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="F175" s="30" t="s">
-        <v>183</v>
+      <c r="D175" s="26">
+        <v>5</v>
+      </c>
+      <c r="E175" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="F175" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="G175" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B175),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E175),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F175),0)&gt;0), MAX($G$1:G174)+1, ""))</f>
@@ -6624,22 +6636,22 @@
         <v>30</v>
       </c>
       <c r="B176" s="31" t="s">
-        <v>337</v>
+        <v>403</v>
       </c>
       <c r="C176" s="32">
         <v>30</v>
       </c>
       <c r="D176" s="30">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="E176" s="31" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="F176" s="30" t="s">
-        <v>338</v>
+        <v>404</v>
       </c>
       <c r="G176" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B176),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E176),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F176),0)&gt;0), MAX($G$1:G175)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B176),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E176),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F176),0)&gt;0), MAX($G$1:G174)+1, ""))</f>
         <v/>
       </c>
       <c r="H176" s="21" t="b">
@@ -6652,22 +6664,22 @@
         <v>30</v>
       </c>
       <c r="B177" s="31" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C177" s="32">
         <v>30</v>
       </c>
       <c r="D177" s="30" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E177" s="31" t="s">
         <v>131</v>
       </c>
       <c r="F177" s="30" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G177" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B177),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E177),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F177),0)&gt;0), MAX($G$1:G175)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B177),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E177),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F177),0)&gt;0), MAX($G$1:G176)+1, ""))</f>
         <v/>
       </c>
       <c r="H177" s="21" t="b">
@@ -6676,23 +6688,23 @@
       </c>
     </row>
     <row r="178" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A178" s="26">
-        <v>40</v>
-      </c>
-      <c r="B178" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="C178" s="28">
-        <v>40</v>
-      </c>
-      <c r="D178" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="E178" s="27" t="s">
-        <v>198</v>
-      </c>
-      <c r="F178" s="26" t="s">
-        <v>199</v>
+      <c r="A178" s="30">
+        <v>30</v>
+      </c>
+      <c r="B178" s="31" t="s">
+        <v>337</v>
+      </c>
+      <c r="C178" s="32">
+        <v>30</v>
+      </c>
+      <c r="D178" s="30">
+        <v>2.9</v>
+      </c>
+      <c r="E178" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="F178" s="30" t="s">
+        <v>338</v>
       </c>
       <c r="G178" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B178),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E178),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F178),0)&gt;0), MAX($G$1:G177)+1, ""))</f>
@@ -6704,26 +6716,26 @@
       </c>
     </row>
     <row r="179" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A179" s="26">
-        <v>40</v>
-      </c>
-      <c r="B179" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="C179" s="28">
-        <v>40</v>
-      </c>
-      <c r="D179" s="26" t="s">
-        <v>242</v>
-      </c>
-      <c r="E179" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="F179" s="26" t="s">
-        <v>196</v>
+      <c r="A179" s="30">
+        <v>30</v>
+      </c>
+      <c r="B179" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="C179" s="32">
+        <v>30</v>
+      </c>
+      <c r="D179" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="E179" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="F179" s="30" t="s">
+        <v>181</v>
       </c>
       <c r="G179" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B179),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E179),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F179),0)&gt;0), MAX($G$1:G178)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B179),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E179),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F179),0)&gt;0), MAX($G$1:G177)+1, ""))</f>
         <v/>
       </c>
       <c r="H179" s="21" t="b">
@@ -6736,22 +6748,22 @@
         <v>40</v>
       </c>
       <c r="B180" s="27" t="s">
-        <v>249</v>
+        <v>197</v>
       </c>
       <c r="C180" s="28">
         <v>40</v>
       </c>
-      <c r="D180" s="26">
-        <v>8.3000000000000007</v>
+      <c r="D180" s="26" t="s">
+        <v>243</v>
       </c>
       <c r="E180" s="27" t="s">
-        <v>250</v>
+        <v>198</v>
       </c>
       <c r="F180" s="26" t="s">
-        <v>251</v>
+        <v>199</v>
       </c>
       <c r="G180" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B180),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E180),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F180),0)&gt;0), MAX($G$1:G179)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B180),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E180),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F180),0)&gt;0), MAX($G$1:G177)+1, ""))</f>
         <v/>
       </c>
       <c r="H180" s="21" t="b">
@@ -6761,22 +6773,22 @@
     </row>
     <row r="181" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A181" s="26">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B181" s="27" t="s">
-        <v>294</v>
+        <v>194</v>
       </c>
       <c r="C181" s="28">
-        <v>45</v>
-      </c>
-      <c r="D181" s="26">
-        <v>10.199999999999999</v>
+        <v>40</v>
+      </c>
+      <c r="D181" s="26" t="s">
+        <v>242</v>
       </c>
       <c r="E181" s="27" t="s">
-        <v>295</v>
+        <v>195</v>
       </c>
       <c r="F181" s="26" t="s">
-        <v>296</v>
+        <v>196</v>
       </c>
       <c r="G181" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B181),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E181),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F181),0)&gt;0), MAX($G$1:G180)+1, ""))</f>
@@ -6788,16 +6800,60 @@
       </c>
     </row>
     <row r="182" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A182" s="1"/>
-      <c r="C182" s="1"/>
-      <c r="D182" s="1"/>
-      <c r="F182" s="1"/>
+      <c r="A182" s="26">
+        <v>40</v>
+      </c>
+      <c r="B182" s="27" t="s">
+        <v>249</v>
+      </c>
+      <c r="C182" s="28">
+        <v>40</v>
+      </c>
+      <c r="D182" s="26">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E182" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="F182" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="G182" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B182),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E182),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F182),0)&gt;0), MAX($G$1:G181)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H182" s="21" t="b">
+        <f>A182=C182</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="183" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A183" s="1"/>
-      <c r="C183" s="1"/>
-      <c r="D183" s="1"/>
-      <c r="F183" s="1"/>
+      <c r="A183" s="26">
+        <v>45</v>
+      </c>
+      <c r="B183" s="27" t="s">
+        <v>294</v>
+      </c>
+      <c r="C183" s="28">
+        <v>45</v>
+      </c>
+      <c r="D183" s="26">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E183" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="F183" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="G183" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B183),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E183),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F183),0)&gt;0), MAX($G$1:G182)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H183" s="21" t="b">
+        <f>A183=C183</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="184" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
@@ -11989,12 +12045,24 @@
       <c r="D1048" s="1"/>
       <c r="F1048" s="1"/>
     </row>
+    <row r="1049" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1049" s="1"/>
+      <c r="C1049" s="1"/>
+      <c r="D1049" s="1"/>
+      <c r="F1049" s="1"/>
+    </row>
+    <row r="1050" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1050" s="1"/>
+      <c r="C1050" s="1"/>
+      <c r="D1050" s="1"/>
+      <c r="F1050" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H181">
-    <sortState ref="A2:H181">
-      <sortCondition ref="A2:A181"/>
-      <sortCondition ref="B2:B181"/>
-      <sortCondition ref="D2:D181"/>
+  <autoFilter ref="A1:H183">
+    <sortState ref="A2:H183">
+      <sortCondition ref="A2:A183"/>
+      <sortCondition ref="B2:B183"/>
+      <sortCondition ref="D2:D183"/>
     </sortState>
   </autoFilter>
   <sortState ref="A2:H174">

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Consulta" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$183</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$184</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$147</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Base!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="408">
   <si>
     <t>Grupo</t>
   </si>
@@ -759,9 +759,6 @@
     <t>6,2</t>
   </si>
   <si>
-    <t>SALVADOR SABATE</t>
-  </si>
-  <si>
     <t>Jardim Novo</t>
   </si>
   <si>
@@ -1246,6 +1243,12 @@
   </si>
   <si>
     <t>21810-007</t>
+  </si>
+  <si>
+    <t>SALVADOR SABATE ATÉ BANDEIRA DE MELO</t>
+  </si>
+  <si>
+    <t>SALVADOR SABATE APÓS BANDEIRA DE MELO</t>
   </si>
 </sst>
 </file>
@@ -1763,7 +1766,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H1050"/>
+  <dimension ref="A1:H1051"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.453125" customWidth="1"/>
@@ -1802,7 +1805,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C2" s="32">
         <v>13</v>
@@ -1811,7 +1814,7 @@
         <v>21</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F2" s="30" t="s">
         <v>25</v>
@@ -1830,7 +1833,7 @@
         <v>13</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C3" s="28">
         <v>13</v>
@@ -1886,7 +1889,7 @@
         <v>13</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C5" s="32">
         <v>13</v>
@@ -1895,7 +1898,7 @@
         <v>21</v>
       </c>
       <c r="E5" s="31" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F5" s="30" t="s">
         <v>25</v>
@@ -1914,7 +1917,7 @@
         <v>13</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C6" s="32">
         <v>13</v>
@@ -1923,7 +1926,7 @@
         <v>21</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F6" s="30" t="s">
         <v>25</v>
@@ -1970,7 +1973,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C8" s="32">
         <v>13</v>
@@ -1979,7 +1982,7 @@
         <v>21</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F8" s="30" t="s">
         <v>25</v>
@@ -1998,7 +2001,7 @@
         <v>13</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C9" s="32">
         <v>13</v>
@@ -2007,7 +2010,7 @@
         <v>21</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F9" s="30" t="s">
         <v>25</v>
@@ -2054,7 +2057,7 @@
         <v>13</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C11" s="32">
         <v>13</v>
@@ -2063,7 +2066,7 @@
         <v>21</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F11" s="30" t="s">
         <v>25</v>
@@ -2082,7 +2085,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C12" s="32">
         <v>13</v>
@@ -2091,7 +2094,7 @@
         <v>21</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F12" s="30" t="s">
         <v>25</v>
@@ -2110,7 +2113,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C13" s="32">
         <v>13</v>
@@ -2166,7 +2169,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C15" s="32">
         <v>13</v>
@@ -2178,7 +2181,7 @@
         <v>8</v>
       </c>
       <c r="F15" s="30" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G15" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B15),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E15),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F15),0)&gt;0), MAX($G$1:G14)+1, ""))</f>
@@ -2194,7 +2197,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C16" s="28">
         <v>13</v>
@@ -2203,10 +2206,10 @@
         <v>1</v>
       </c>
       <c r="E16" s="27" t="s">
+        <v>379</v>
+      </c>
+      <c r="F16" s="26" t="s">
         <v>380</v>
-      </c>
-      <c r="F16" s="26" t="s">
-        <v>381</v>
       </c>
       <c r="G16" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B16),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E16),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F16),0)&gt;0), MAX($G$1:G15)+1, ""))</f>
@@ -2222,7 +2225,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C17" s="32">
         <v>13</v>
@@ -2231,7 +2234,7 @@
         <v>21</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F17" s="30" t="s">
         <v>25</v>
@@ -2334,7 +2337,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C21" s="28">
         <v>15</v>
@@ -2346,7 +2349,7 @@
         <v>8</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G21" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F21),0)&gt;0), MAX($G$1:G19)+1, ""))</f>
@@ -2371,7 +2374,7 @@
         <v>210</v>
       </c>
       <c r="E22" s="27" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F22" s="26" t="s">
         <v>75</v>
@@ -2390,7 +2393,7 @@
         <v>15</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C23" s="28">
         <v>15</v>
@@ -2399,10 +2402,10 @@
         <v>2.1</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G23" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B23),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E23),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F23),0)&gt;0), MAX($G$1:G22)+1, ""))</f>
@@ -2446,7 +2449,7 @@
         <v>15</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C25" s="28">
         <v>15</v>
@@ -2530,7 +2533,7 @@
         <v>15</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C28" s="28">
         <v>15</v>
@@ -2539,7 +2542,7 @@
         <v>206</v>
       </c>
       <c r="E28" s="27" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F28" s="26" t="s">
         <v>65</v>
@@ -2558,7 +2561,7 @@
         <v>15</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C29" s="28">
         <v>15</v>
@@ -2570,7 +2573,7 @@
         <v>8</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G29" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B29),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E29),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F29),0)&gt;0), MAX($G$1:G28)+1, ""))</f>
@@ -2586,7 +2589,7 @@
         <v>15</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C30" s="28">
         <v>15</v>
@@ -2598,7 +2601,7 @@
         <v>8</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G30" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B30),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E30),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F30),0)&gt;0), MAX($G$1:G29)+1, ""))</f>
@@ -2614,7 +2617,7 @@
         <v>15</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C31" s="28">
         <v>15</v>
@@ -2623,10 +2626,10 @@
         <v>2</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F31" s="26" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G31" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B31),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E31),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F31),0)&gt;0), MAX($G$1:G30)+1, ""))</f>
@@ -2670,7 +2673,7 @@
         <v>15</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C33" s="28">
         <v>15</v>
@@ -2698,7 +2701,7 @@
         <v>15</v>
       </c>
       <c r="B34" s="27" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C34" s="28">
         <v>15</v>
@@ -2710,7 +2713,7 @@
         <v>8</v>
       </c>
       <c r="F34" s="26" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G34" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B34),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E34),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F34),0)&gt;0), MAX($G$1:G33)+1, ""))</f>
@@ -2726,7 +2729,7 @@
         <v>15</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C35" s="28">
         <v>15</v>
@@ -2738,7 +2741,7 @@
         <v>8</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G35" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F35),0)&gt;0), MAX($G$1:G34)+1, ""))</f>
@@ -2782,7 +2785,7 @@
         <v>15</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C37" s="28">
         <v>15</v>
@@ -2810,7 +2813,7 @@
         <v>15</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C38" s="28">
         <v>15</v>
@@ -2822,7 +2825,7 @@
         <v>8</v>
       </c>
       <c r="F38" s="26" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G38" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F38),0)&gt;0), MAX($G$1:G37)+1, ""))</f>
@@ -2838,7 +2841,7 @@
         <v>15</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C39" s="28">
         <v>15</v>
@@ -2850,7 +2853,7 @@
         <v>8</v>
       </c>
       <c r="F39" s="26" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G39" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B39),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E39),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F39),0)&gt;0), MAX($G$1:G38)+1, ""))</f>
@@ -2866,7 +2869,7 @@
         <v>15</v>
       </c>
       <c r="B40" s="27" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C40" s="28">
         <v>15</v>
@@ -2878,7 +2881,7 @@
         <v>8</v>
       </c>
       <c r="F40" s="26" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G40" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B40),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E40),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F40),0)&gt;0), MAX($G$1:G39)+1, ""))</f>
@@ -2894,7 +2897,7 @@
         <v>15</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C41" s="28">
         <v>15</v>
@@ -2906,7 +2909,7 @@
         <v>8</v>
       </c>
       <c r="F41" s="26" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G41" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B41),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E41),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F41),0)&gt;0), MAX($G$1:G40)+1, ""))</f>
@@ -2950,7 +2953,7 @@
         <v>15</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C43" s="28">
         <v>15</v>
@@ -2959,10 +2962,10 @@
         <v>1.3</v>
       </c>
       <c r="E43" s="27" t="s">
+        <v>379</v>
+      </c>
+      <c r="F43" s="26" t="s">
         <v>380</v>
-      </c>
-      <c r="F43" s="26" t="s">
-        <v>381</v>
       </c>
       <c r="G43" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F43),0)&gt;0), MAX($G$1:G42)+1, ""))</f>
@@ -3062,7 +3065,7 @@
         <v>15</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C47" s="28">
         <v>15</v>
@@ -3074,7 +3077,7 @@
         <v>8</v>
       </c>
       <c r="F47" s="26" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G47" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F47),0)&gt;0), MAX($G$1:G46)+1, ""))</f>
@@ -3090,7 +3093,7 @@
         <v>15</v>
       </c>
       <c r="B48" s="27" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C48" s="28">
         <v>15</v>
@@ -3102,7 +3105,7 @@
         <v>8</v>
       </c>
       <c r="F48" s="26" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G48" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F48),0)&gt;0), MAX($G$1:G47)+1, ""))</f>
@@ -3118,7 +3121,7 @@
         <v>15</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>244</v>
+        <v>406</v>
       </c>
       <c r="C49" s="28">
         <v>15</v>
@@ -3127,13 +3130,13 @@
         <v>2.1</v>
       </c>
       <c r="E49" s="27" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F49" s="26" t="s">
         <v>202</v>
       </c>
       <c r="G49" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F49),0)&gt;0), MAX($G$1:G48)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F49),0)&gt;0), MAX($G$1:G47)+1, ""))</f>
         <v/>
       </c>
       <c r="H49" s="21" t="b">
@@ -3161,7 +3164,7 @@
         <v>39</v>
       </c>
       <c r="G50" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F50),0)&gt;0), MAX($G$1:G45)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F50),0)&gt;0), MAX($G$1:G44)+1, ""))</f>
         <v/>
       </c>
       <c r="H50" s="21" t="b">
@@ -3174,7 +3177,7 @@
         <v>15</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C51" s="28">
         <v>15</v>
@@ -3186,7 +3189,7 @@
         <v>8</v>
       </c>
       <c r="F51" s="26" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G51" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F51),0)&gt;0), MAX($G$1:G50)+1, ""))</f>
@@ -3230,7 +3233,7 @@
         <v>15</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C53" s="28">
         <v>15</v>
@@ -3239,10 +3242,10 @@
         <v>1.2</v>
       </c>
       <c r="E53" s="27" t="s">
+        <v>379</v>
+      </c>
+      <c r="F53" s="26" t="s">
         <v>380</v>
-      </c>
-      <c r="F53" s="26" t="s">
-        <v>381</v>
       </c>
       <c r="G53" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F53),0)&gt;0), MAX($G$1:G52)+1, ""))</f>
@@ -3258,7 +3261,7 @@
         <v>15</v>
       </c>
       <c r="B54" s="27" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C54" s="28">
         <v>15</v>
@@ -3267,7 +3270,7 @@
         <v>209</v>
       </c>
       <c r="E54" s="27" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F54" s="26" t="s">
         <v>33</v>
@@ -3314,7 +3317,7 @@
         <v>17</v>
       </c>
       <c r="B56" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C56" s="35">
         <v>17</v>
@@ -3342,7 +3345,7 @@
         <v>17</v>
       </c>
       <c r="B57" s="27" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C57" s="28">
         <v>17</v>
@@ -3354,7 +3357,7 @@
         <v>60</v>
       </c>
       <c r="F57" s="26" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G57" s="29"/>
       <c r="H57" s="21" t="b">
@@ -3367,7 +3370,7 @@
         <v>17</v>
       </c>
       <c r="B58" s="27" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C58" s="28">
         <v>17</v>
@@ -3379,7 +3382,7 @@
         <v>60</v>
       </c>
       <c r="F58" s="26" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G58" s="29"/>
       <c r="H58" s="21" t="b">
@@ -3448,7 +3451,7 @@
         <v>17</v>
       </c>
       <c r="B61" s="27" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C61" s="28">
         <v>17</v>
@@ -3460,7 +3463,7 @@
         <v>60</v>
       </c>
       <c r="F61" s="26" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G61" s="29"/>
       <c r="H61" s="21" t="b">
@@ -3473,7 +3476,7 @@
         <v>17</v>
       </c>
       <c r="B62" s="27" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C62" s="28">
         <v>17</v>
@@ -3485,7 +3488,7 @@
         <v>8</v>
       </c>
       <c r="F62" s="26" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G62" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F62),0)&gt;0), MAX($G$1:G60)+1, ""))</f>
@@ -3501,7 +3504,7 @@
         <v>17</v>
       </c>
       <c r="B63" s="27" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C63" s="28">
         <v>17</v>
@@ -3513,7 +3516,7 @@
         <v>60</v>
       </c>
       <c r="F63" s="26" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G63" s="29"/>
       <c r="H63" s="21" t="b">
@@ -3526,7 +3529,7 @@
         <v>17</v>
       </c>
       <c r="B64" s="37" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C64" s="38">
         <v>17</v>
@@ -3554,7 +3557,7 @@
         <v>17</v>
       </c>
       <c r="B65" s="27" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C65" s="28">
         <v>17</v>
@@ -3566,7 +3569,7 @@
         <v>8</v>
       </c>
       <c r="F65" s="26" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G65" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F65),0)&gt;0), MAX($G$1:G64)+1, ""))</f>
@@ -3582,7 +3585,7 @@
         <v>17</v>
       </c>
       <c r="B66" s="27" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C66" s="28">
         <v>17</v>
@@ -3594,7 +3597,7 @@
         <v>60</v>
       </c>
       <c r="F66" s="26" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G66" s="29"/>
       <c r="H66" s="21" t="b">
@@ -3607,7 +3610,7 @@
         <v>17</v>
       </c>
       <c r="B67" s="27" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C67" s="28">
         <v>17</v>
@@ -3619,7 +3622,7 @@
         <v>60</v>
       </c>
       <c r="F67" s="26" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G67" s="29"/>
       <c r="H67" s="21" t="b">
@@ -3660,7 +3663,7 @@
         <v>17</v>
       </c>
       <c r="B69" s="37" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C69" s="38">
         <v>17</v>
@@ -3669,7 +3672,7 @@
         <v>229</v>
       </c>
       <c r="E69" s="37" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F69" s="36" t="s">
         <v>105</v>
@@ -3716,7 +3719,7 @@
         <v>17</v>
       </c>
       <c r="B71" s="27" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C71" s="28">
         <v>17</v>
@@ -3728,7 +3731,7 @@
         <v>8</v>
       </c>
       <c r="F71" s="26" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G71" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F71),0)&gt;0), MAX($G$1:G70)+1, ""))</f>
@@ -3744,7 +3747,7 @@
         <v>17</v>
       </c>
       <c r="B72" s="27" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C72" s="28">
         <v>17</v>
@@ -3756,7 +3759,7 @@
         <v>8</v>
       </c>
       <c r="F72" s="26" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G72" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F72),0)&gt;0), MAX($G$1:G71)+1, ""))</f>
@@ -3772,7 +3775,7 @@
         <v>17</v>
       </c>
       <c r="B73" s="27" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C73" s="28">
         <v>17</v>
@@ -3784,7 +3787,7 @@
         <v>8</v>
       </c>
       <c r="F73" s="26" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G73" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F73),0)&gt;0), MAX($G$1:G72)+1, ""))</f>
@@ -3912,7 +3915,7 @@
         <v>17</v>
       </c>
       <c r="B78" s="27" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C78" s="28">
         <v>17</v>
@@ -3924,7 +3927,7 @@
         <v>8</v>
       </c>
       <c r="F78" s="26" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G78" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F78),0)&gt;0), MAX($G$1:G77)+1, ""))</f>
@@ -3936,28 +3939,30 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A79" s="33">
+      <c r="A79" s="26">
         <v>17</v>
       </c>
-      <c r="B79" s="34" t="s">
-        <v>327</v>
-      </c>
-      <c r="C79" s="35">
+      <c r="B79" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="C79" s="28">
         <v>17</v>
       </c>
-      <c r="D79" s="33">
-        <v>1.9</v>
-      </c>
-      <c r="E79" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F79" s="33" t="s">
-        <v>329</v>
-      </c>
-      <c r="G79" s="29" t="s">
-        <v>326</v>
+      <c r="D79" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E79" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="F79" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="G79" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F79),0)&gt;0), MAX($G$1:G77)+1, ""))</f>
+        <v/>
       </c>
       <c r="H79" s="21" t="b">
+        <f>A79=C79</f>
         <v>1</v>
       </c>
     </row>
@@ -3966,7 +3971,7 @@
         <v>17</v>
       </c>
       <c r="B80" s="34" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C80" s="35">
         <v>17</v>
@@ -3978,10 +3983,10 @@
         <v>60</v>
       </c>
       <c r="F80" s="33" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G80" s="29" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H80" s="21" t="b">
         <v>1</v>
@@ -3992,7 +3997,7 @@
         <v>17</v>
       </c>
       <c r="B81" s="34" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C81" s="35">
         <v>17</v>
@@ -4004,10 +4009,10 @@
         <v>60</v>
       </c>
       <c r="F81" s="33" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G81" s="29" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H81" s="21" t="b">
         <v>1</v>
@@ -4018,47 +4023,45 @@
         <v>17</v>
       </c>
       <c r="B82" s="34" t="s">
-        <v>36</v>
+        <v>327</v>
       </c>
       <c r="C82" s="35">
         <v>17</v>
       </c>
-      <c r="D82" s="33" t="s">
+      <c r="D82" s="33">
+        <v>1.9</v>
+      </c>
+      <c r="E82" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="F82" s="33" t="s">
+        <v>328</v>
+      </c>
+      <c r="G82" s="29" t="s">
+        <v>325</v>
+      </c>
+      <c r="H82" s="21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A83" s="33">
+        <v>17</v>
+      </c>
+      <c r="B83" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="C83" s="35">
+        <v>17</v>
+      </c>
+      <c r="D83" s="33" t="s">
         <v>214</v>
       </c>
-      <c r="E82" s="34" t="s">
+      <c r="E83" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F82" s="33" t="s">
+      <c r="F83" s="33" t="s">
         <v>37</v>
-      </c>
-      <c r="G82" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F82),0)&gt;0), MAX($G$1:G81)+1, ""))</f>
-        <v/>
-      </c>
-      <c r="H82" s="21" t="b">
-        <f>A82=C82</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A83" s="36">
-        <v>17</v>
-      </c>
-      <c r="B83" s="37" t="s">
-        <v>83</v>
-      </c>
-      <c r="C83" s="38">
-        <v>17</v>
-      </c>
-      <c r="D83" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="E83" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F83" s="36" t="s">
-        <v>84</v>
       </c>
       <c r="G83" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F83),0)&gt;0), MAX($G$1:G82)+1, ""))</f>
@@ -4070,23 +4073,23 @@
       </c>
     </row>
     <row r="84" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A84" s="33">
+      <c r="A84" s="36">
         <v>17</v>
       </c>
-      <c r="B84" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="C84" s="35">
+      <c r="B84" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="C84" s="38">
         <v>17</v>
       </c>
-      <c r="D84" s="33" t="s">
-        <v>208</v>
-      </c>
-      <c r="E84" s="34" t="s">
+      <c r="D84" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E84" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F84" s="33" t="s">
-        <v>32</v>
+      <c r="F84" s="36" t="s">
+        <v>84</v>
       </c>
       <c r="G84" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F84),0)&gt;0), MAX($G$1:G83)+1, ""))</f>
@@ -4102,52 +4105,52 @@
         <v>17</v>
       </c>
       <c r="B85" s="34" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C85" s="35">
         <v>17</v>
       </c>
       <c r="D85" s="33" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E85" s="34" t="s">
         <v>8</v>
       </c>
       <c r="F85" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="G85" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F85),0)&gt;0), MAX($G$1:G84)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H85" s="21" t="b">
+        <f>A85=C85</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A86" s="33">
+        <v>17</v>
+      </c>
+      <c r="B86" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="C86" s="35">
+        <v>17</v>
+      </c>
+      <c r="D86" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="E86" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F86" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="G85" s="29" t="s">
-        <v>326</v>
-      </c>
-      <c r="H85" s="21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A86" s="30">
-        <v>20</v>
-      </c>
-      <c r="B86" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="C86" s="32">
-        <v>20</v>
-      </c>
-      <c r="D86" s="30" t="s">
-        <v>206</v>
-      </c>
-      <c r="E86" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F86" s="30" t="s">
-        <v>147</v>
-      </c>
-      <c r="G86" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F86),0)&gt;0), MAX($G$1:G82)+1, ""))</f>
-        <v/>
+      <c r="G86" s="29" t="s">
+        <v>325</v>
       </c>
       <c r="H86" s="21" t="b">
-        <f>A86=C86</f>
         <v>1</v>
       </c>
     </row>
@@ -4156,22 +4159,22 @@
         <v>20</v>
       </c>
       <c r="B87" s="31" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C87" s="32">
         <v>20</v>
       </c>
       <c r="D87" s="30" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E87" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F87" s="30" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G87" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F87),0)&gt;0), MAX($G$1:G86)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F87),0)&gt;0), MAX($G$1:G83)+1, ""))</f>
         <v/>
       </c>
       <c r="H87" s="21" t="b">
@@ -4180,23 +4183,23 @@
       </c>
     </row>
     <row r="88" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A88" s="26">
+      <c r="A88" s="30">
         <v>20</v>
       </c>
-      <c r="B88" s="27" t="s">
-        <v>383</v>
-      </c>
-      <c r="C88" s="28">
+      <c r="B88" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="C88" s="32">
         <v>20</v>
       </c>
-      <c r="D88" s="26">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="E88" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="F88" s="26" t="s">
-        <v>384</v>
+      <c r="D88" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="E88" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F88" s="30" t="s">
+        <v>145</v>
       </c>
       <c r="G88" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F88),0)&gt;0), MAX($G$1:G87)+1, ""))</f>
@@ -4208,26 +4211,26 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A89" s="30">
+      <c r="A89" s="26">
         <v>20</v>
       </c>
-      <c r="B89" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="C89" s="32">
+      <c r="B89" s="27" t="s">
+        <v>382</v>
+      </c>
+      <c r="C89" s="28">
         <v>20</v>
       </c>
-      <c r="D89" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="E89" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F89" s="30" t="s">
-        <v>143</v>
+      <c r="D89" s="26">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E89" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F89" s="26" t="s">
+        <v>383</v>
       </c>
       <c r="G89" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F89),0)&gt;0), MAX($G$1:G87)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F89),0)&gt;0), MAX($G$1:G88)+1, ""))</f>
         <v/>
       </c>
       <c r="H89" s="21" t="b">
@@ -4240,22 +4243,22 @@
         <v>20</v>
       </c>
       <c r="B90" s="31" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C90" s="32">
         <v>20</v>
       </c>
       <c r="D90" s="30" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="E90" s="31" t="s">
-        <v>305</v>
+        <v>8</v>
       </c>
       <c r="F90" s="30" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G90" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F90),0)&gt;0), MAX($G$1:G89)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F90),0)&gt;0), MAX($G$1:G88)+1, ""))</f>
         <v/>
       </c>
       <c r="H90" s="21" t="b">
@@ -4264,25 +4267,28 @@
       </c>
     </row>
     <row r="91" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A91" s="36">
+      <c r="A91" s="30">
         <v>20</v>
       </c>
-      <c r="B91" s="37" t="s">
-        <v>333</v>
-      </c>
-      <c r="C91" s="38">
+      <c r="B91" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="C91" s="32">
         <v>20</v>
       </c>
-      <c r="D91" s="36">
-        <v>3.4</v>
-      </c>
-      <c r="E91" s="37" t="s">
-        <v>336</v>
-      </c>
-      <c r="F91" s="36" t="s">
-        <v>334</v>
-      </c>
-      <c r="G91" s="29"/>
+      <c r="D91" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="E91" s="31" t="s">
+        <v>304</v>
+      </c>
+      <c r="F91" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="G91" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F91),0)&gt;0), MAX($G$1:G90)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H91" s="21" t="b">
         <f>A91=C91</f>
         <v>1</v>
@@ -4293,19 +4299,19 @@
         <v>20</v>
       </c>
       <c r="B92" s="37" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C92" s="38">
         <v>20</v>
       </c>
       <c r="D92" s="36">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="E92" s="37" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F92" s="36" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G92" s="29"/>
       <c r="H92" s="21" t="b">
@@ -4314,28 +4320,25 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A93" s="30">
+      <c r="A93" s="36">
         <v>20</v>
       </c>
-      <c r="B93" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="C93" s="32">
+      <c r="B93" s="37" t="s">
+        <v>330</v>
+      </c>
+      <c r="C93" s="38">
         <v>20</v>
       </c>
-      <c r="D93" s="30" t="s">
-        <v>223</v>
-      </c>
-      <c r="E93" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F93" s="30" t="s">
-        <v>139</v>
-      </c>
-      <c r="G93" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F93),0)&gt;0), MAX($G$1:G92)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D93" s="36">
+        <v>3.3</v>
+      </c>
+      <c r="E93" s="37" t="s">
+        <v>335</v>
+      </c>
+      <c r="F93" s="36" t="s">
+        <v>331</v>
+      </c>
+      <c r="G93" s="29"/>
       <c r="H93" s="21" t="b">
         <f>A93=C93</f>
         <v>1</v>
@@ -4346,19 +4349,19 @@
         <v>20</v>
       </c>
       <c r="B94" s="31" t="s">
-        <v>255</v>
+        <v>138</v>
       </c>
       <c r="C94" s="32">
         <v>20</v>
       </c>
       <c r="D94" s="30" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E94" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F94" s="30" t="s">
-        <v>256</v>
+        <v>139</v>
       </c>
       <c r="G94" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F94),0)&gt;0), MAX($G$1:G93)+1, ""))</f>
@@ -4379,14 +4382,14 @@
       <c r="C95" s="32">
         <v>20</v>
       </c>
-      <c r="D95" s="30">
-        <v>4.2</v>
+      <c r="D95" s="30" t="s">
+        <v>225</v>
       </c>
       <c r="E95" s="31" t="s">
-        <v>305</v>
-      </c>
-      <c r="F95" s="30">
-        <v>21765430</v>
+        <v>8</v>
+      </c>
+      <c r="F95" s="30" t="s">
+        <v>255</v>
       </c>
       <c r="G95" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F95),0)&gt;0), MAX($G$1:G94)+1, ""))</f>
@@ -4402,19 +4405,19 @@
         <v>20</v>
       </c>
       <c r="B96" s="31" t="s">
-        <v>136</v>
+        <v>253</v>
       </c>
       <c r="C96" s="32">
         <v>20</v>
       </c>
-      <c r="D96" s="30" t="s">
-        <v>210</v>
+      <c r="D96" s="30">
+        <v>4.2</v>
       </c>
       <c r="E96" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F96" s="30" t="s">
-        <v>137</v>
+        <v>304</v>
+      </c>
+      <c r="F96" s="30">
+        <v>21765430</v>
       </c>
       <c r="G96" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F96),0)&gt;0), MAX($G$1:G95)+1, ""))</f>
@@ -4430,19 +4433,19 @@
         <v>20</v>
       </c>
       <c r="B97" s="31" t="s">
-        <v>265</v>
+        <v>136</v>
       </c>
       <c r="C97" s="32">
         <v>20</v>
       </c>
       <c r="D97" s="30" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="E97" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F97" s="30" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G97" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F97),0)&gt;0), MAX($G$1:G96)+1, ""))</f>
@@ -4458,19 +4461,19 @@
         <v>20</v>
       </c>
       <c r="B98" s="31" t="s">
-        <v>133</v>
+        <v>264</v>
       </c>
       <c r="C98" s="32">
         <v>20</v>
       </c>
       <c r="D98" s="30" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E98" s="31" t="s">
-        <v>305</v>
+        <v>8</v>
       </c>
       <c r="F98" s="30" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G98" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F98),0)&gt;0), MAX($G$1:G97)+1, ""))</f>
@@ -4486,19 +4489,19 @@
         <v>20</v>
       </c>
       <c r="B99" s="31" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C99" s="32">
         <v>20</v>
       </c>
       <c r="D99" s="30" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E99" s="31" t="s">
-        <v>131</v>
+        <v>304</v>
       </c>
       <c r="F99" s="30" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G99" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F99),0)&gt;0), MAX($G$1:G98)+1, ""))</f>
@@ -4510,23 +4513,23 @@
       </c>
     </row>
     <row r="100" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A100" s="26">
+      <c r="A100" s="30">
         <v>20</v>
       </c>
-      <c r="B100" s="27" t="s">
-        <v>312</v>
-      </c>
-      <c r="C100" s="28">
+      <c r="B100" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="C100" s="32">
         <v>20</v>
       </c>
-      <c r="D100" s="26">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="E100" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="F100" s="26" t="s">
-        <v>318</v>
+      <c r="D100" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="E100" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="F100" s="30" t="s">
+        <v>132</v>
       </c>
       <c r="G100" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F100),0)&gt;0), MAX($G$1:G99)+1, ""))</f>
@@ -4542,19 +4545,19 @@
         <v>20</v>
       </c>
       <c r="B101" s="27" t="s">
-        <v>386</v>
+        <v>311</v>
       </c>
       <c r="C101" s="28">
         <v>20</v>
       </c>
       <c r="D101" s="26">
-        <v>2.5</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E101" s="27" t="s">
         <v>60</v>
       </c>
       <c r="F101" s="26" t="s">
-        <v>385</v>
+        <v>317</v>
       </c>
       <c r="G101" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F101),0)&gt;0), MAX($G$1:G100)+1, ""))</f>
@@ -4566,23 +4569,23 @@
       </c>
     </row>
     <row r="102" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A102" s="30">
+      <c r="A102" s="26">
         <v>20</v>
       </c>
-      <c r="B102" s="31" t="s">
-        <v>128</v>
-      </c>
-      <c r="C102" s="32">
+      <c r="B102" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="C102" s="28">
         <v>20</v>
       </c>
-      <c r="D102" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="E102" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F102" s="30" t="s">
-        <v>129</v>
+      <c r="D102" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E102" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F102" s="26" t="s">
+        <v>384</v>
       </c>
       <c r="G102" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F102),0)&gt;0), MAX($G$1:G101)+1, ""))</f>
@@ -4598,19 +4601,19 @@
         <v>20</v>
       </c>
       <c r="B103" s="31" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C103" s="32">
         <v>20</v>
       </c>
       <c r="D103" s="30" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="E103" s="31" t="s">
-        <v>305</v>
+        <v>8</v>
       </c>
       <c r="F103" s="30" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G103" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F103),0)&gt;0), MAX($G$1:G102)+1, ""))</f>
@@ -4622,23 +4625,23 @@
       </c>
     </row>
     <row r="104" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A104" s="26">
+      <c r="A104" s="30">
         <v>20</v>
       </c>
-      <c r="B104" s="27" t="s">
-        <v>374</v>
-      </c>
-      <c r="C104" s="28">
+      <c r="B104" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="C104" s="32">
         <v>20</v>
       </c>
-      <c r="D104" s="26">
-        <v>2.7</v>
-      </c>
-      <c r="E104" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="F104" s="26" t="s">
-        <v>350</v>
+      <c r="D104" s="30" t="s">
+        <v>234</v>
+      </c>
+      <c r="E104" s="31" t="s">
+        <v>304</v>
+      </c>
+      <c r="F104" s="30" t="s">
+        <v>127</v>
       </c>
       <c r="G104" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F104),0)&gt;0), MAX($G$1:G103)+1, ""))</f>
@@ -4650,23 +4653,23 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A105" s="30">
+      <c r="A105" s="26">
         <v>20</v>
       </c>
-      <c r="B105" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="C105" s="32">
+      <c r="B105" s="27" t="s">
+        <v>373</v>
+      </c>
+      <c r="C105" s="28">
         <v>20</v>
       </c>
-      <c r="D105" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="E105" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F105" s="30" t="s">
-        <v>125</v>
+      <c r="D105" s="26">
+        <v>2.7</v>
+      </c>
+      <c r="E105" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="F105" s="26" t="s">
+        <v>349</v>
       </c>
       <c r="G105" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F105),0)&gt;0), MAX($G$1:G104)+1, ""))</f>
@@ -4682,19 +4685,19 @@
         <v>20</v>
       </c>
       <c r="B106" s="31" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C106" s="32">
         <v>20</v>
       </c>
       <c r="D106" s="30" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="E106" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F106" s="30" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G106" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F106),0)&gt;0), MAX($G$1:G105)+1, ""))</f>
@@ -4710,19 +4713,19 @@
         <v>20</v>
       </c>
       <c r="B107" s="31" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C107" s="32">
         <v>20</v>
       </c>
       <c r="D107" s="30" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="E107" s="31" t="s">
-        <v>305</v>
+        <v>8</v>
       </c>
       <c r="F107" s="30" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G107" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F107),0)&gt;0), MAX($G$1:G106)+1, ""))</f>
@@ -4734,23 +4737,23 @@
       </c>
     </row>
     <row r="108" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A108" s="26">
+      <c r="A108" s="30">
         <v>20</v>
       </c>
-      <c r="B108" s="27" t="s">
-        <v>368</v>
-      </c>
-      <c r="C108" s="28">
+      <c r="B108" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="C108" s="32">
         <v>20</v>
       </c>
-      <c r="D108" s="26">
-        <v>1.5</v>
+      <c r="D108" s="30" t="s">
+        <v>223</v>
       </c>
       <c r="E108" s="31" t="s">
-        <v>299</v>
-      </c>
-      <c r="F108" s="26" t="s">
-        <v>369</v>
+        <v>304</v>
+      </c>
+      <c r="F108" s="30" t="s">
+        <v>121</v>
       </c>
       <c r="G108" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F108),0)&gt;0), MAX($G$1:G107)+1, ""))</f>
@@ -4762,23 +4765,23 @@
       </c>
     </row>
     <row r="109" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A109" s="30">
+      <c r="A109" s="26">
         <v>20</v>
       </c>
-      <c r="B109" s="31" t="s">
-        <v>257</v>
-      </c>
-      <c r="C109" s="32">
+      <c r="B109" s="27" t="s">
+        <v>367</v>
+      </c>
+      <c r="C109" s="28">
         <v>20</v>
       </c>
-      <c r="D109" s="30" t="s">
-        <v>225</v>
+      <c r="D109" s="26">
+        <v>1.5</v>
       </c>
       <c r="E109" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F109" s="30" t="s">
-        <v>258</v>
+        <v>298</v>
+      </c>
+      <c r="F109" s="26" t="s">
+        <v>368</v>
       </c>
       <c r="G109" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F109),0)&gt;0), MAX($G$1:G108)+1, ""))</f>
@@ -4794,19 +4797,19 @@
         <v>20</v>
       </c>
       <c r="B110" s="31" t="s">
-        <v>118</v>
+        <v>256</v>
       </c>
       <c r="C110" s="32">
         <v>20</v>
       </c>
       <c r="D110" s="30" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E110" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F110" s="30" t="s">
-        <v>119</v>
+        <v>257</v>
       </c>
       <c r="G110" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F110),0)&gt;0), MAX($G$1:G109)+1, ""))</f>
@@ -4822,19 +4825,19 @@
         <v>20</v>
       </c>
       <c r="B111" s="31" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C111" s="32">
         <v>20</v>
       </c>
       <c r="D111" s="30" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="E111" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F111" s="30" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G111" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F111),0)&gt;0), MAX($G$1:G110)+1, ""))</f>
@@ -4850,19 +4853,19 @@
         <v>20</v>
       </c>
       <c r="B112" s="31" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C112" s="32">
         <v>20</v>
       </c>
       <c r="D112" s="30" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E112" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F112" s="30" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G112" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F112),0)&gt;0), MAX($G$1:G111)+1, ""))</f>
@@ -4874,23 +4877,23 @@
       </c>
     </row>
     <row r="113" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A113" s="26">
+      <c r="A113" s="30">
         <v>20</v>
       </c>
-      <c r="B113" s="27" t="s">
-        <v>297</v>
-      </c>
-      <c r="C113" s="28">
+      <c r="B113" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="C113" s="32">
         <v>20</v>
       </c>
-      <c r="D113" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E113" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="F113" s="26" t="s">
-        <v>298</v>
+      <c r="D113" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="E113" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F113" s="30" t="s">
+        <v>115</v>
       </c>
       <c r="G113" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F113),0)&gt;0), MAX($G$1:G112)+1, ""))</f>
@@ -4902,23 +4905,23 @@
       </c>
     </row>
     <row r="114" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A114" s="30">
+      <c r="A114" s="26">
         <v>20</v>
       </c>
-      <c r="B114" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="C114" s="32">
+      <c r="B114" s="27" t="s">
+        <v>296</v>
+      </c>
+      <c r="C114" s="28">
         <v>20</v>
       </c>
-      <c r="D114" s="30" t="s">
-        <v>219</v>
-      </c>
-      <c r="E114" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F114" s="30" t="s">
-        <v>113</v>
+      <c r="D114" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E114" s="27" t="s">
+        <v>298</v>
+      </c>
+      <c r="F114" s="26" t="s">
+        <v>297</v>
       </c>
       <c r="G114" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F114),0)&gt;0), MAX($G$1:G113)+1, ""))</f>
@@ -4934,19 +4937,19 @@
         <v>20</v>
       </c>
       <c r="B115" s="31" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C115" s="32">
         <v>20</v>
       </c>
       <c r="D115" s="30" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E115" s="31" t="s">
-        <v>299</v>
+        <v>8</v>
       </c>
       <c r="F115" s="30" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G115" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F115),0)&gt;0), MAX($G$1:G114)+1, ""))</f>
@@ -4962,19 +4965,19 @@
         <v>20</v>
       </c>
       <c r="B116" s="31" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C116" s="32">
         <v>20</v>
       </c>
       <c r="D116" s="30" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E116" s="31" t="s">
-        <v>8</v>
+        <v>298</v>
       </c>
       <c r="F116" s="30" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G116" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F116),0)&gt;0), MAX($G$1:G115)+1, ""))</f>
@@ -4986,76 +4989,76 @@
       </c>
     </row>
     <row r="117" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A117" s="36">
+      <c r="A117" s="30">
         <v>20</v>
       </c>
-      <c r="B117" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="C117" s="38">
+      <c r="B117" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="C117" s="32">
         <v>20</v>
       </c>
-      <c r="D117" s="36">
-        <v>3</v>
-      </c>
-      <c r="E117" s="37" t="s">
-        <v>304</v>
-      </c>
-      <c r="F117" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="G117" s="29"/>
+      <c r="D117" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="E117" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F117" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="G117" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F117),0)&gt;0), MAX($G$1:G116)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H117" s="21" t="b">
         <f>A117=C117</f>
         <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A118" s="26">
+      <c r="A118" s="36">
         <v>20</v>
       </c>
-      <c r="B118" s="27" t="s">
-        <v>302</v>
-      </c>
-      <c r="C118" s="28">
+      <c r="B118" s="37" t="s">
+        <v>329</v>
+      </c>
+      <c r="C118" s="38">
         <v>20</v>
       </c>
-      <c r="D118" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E118" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="F118" s="26" t="s">
-        <v>301</v>
-      </c>
-      <c r="G118" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F118),0)&gt;0), MAX($G$1:G117)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D118" s="36">
+        <v>3</v>
+      </c>
+      <c r="E118" s="37" t="s">
+        <v>303</v>
+      </c>
+      <c r="F118" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="G118" s="29"/>
       <c r="H118" s="21" t="b">
         <f>A118=C118</f>
         <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A119" s="30">
+      <c r="A119" s="26">
         <v>20</v>
       </c>
-      <c r="B119" s="31" t="s">
-        <v>365</v>
-      </c>
-      <c r="C119" s="32">
+      <c r="B119" s="27" t="s">
+        <v>301</v>
+      </c>
+      <c r="C119" s="28">
         <v>20</v>
       </c>
-      <c r="D119" s="30">
+      <c r="D119" s="26">
         <v>2.4</v>
       </c>
-      <c r="E119" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="F119" s="30" t="s">
-        <v>366</v>
+      <c r="E119" s="27" t="s">
+        <v>298</v>
+      </c>
+      <c r="F119" s="26" t="s">
+        <v>300</v>
       </c>
       <c r="G119" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F119),0)&gt;0), MAX($G$1:G118)+1, ""))</f>
@@ -5071,19 +5074,19 @@
         <v>20</v>
       </c>
       <c r="B120" s="31" t="s">
-        <v>103</v>
+        <v>364</v>
       </c>
       <c r="C120" s="32">
         <v>20</v>
       </c>
-      <c r="D120" s="30" t="s">
-        <v>214</v>
+      <c r="D120" s="30">
+        <v>2.4</v>
       </c>
       <c r="E120" s="31" t="s">
         <v>60</v>
       </c>
       <c r="F120" s="30" t="s">
-        <v>104</v>
+        <v>365</v>
       </c>
       <c r="G120" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F120),0)&gt;0), MAX($G$1:G119)+1, ""))</f>
@@ -5095,23 +5098,23 @@
       </c>
     </row>
     <row r="121" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A121" s="26">
+      <c r="A121" s="30">
         <v>20</v>
       </c>
-      <c r="B121" s="27" t="s">
-        <v>339</v>
-      </c>
-      <c r="C121" s="28">
+      <c r="B121" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="C121" s="32">
         <v>20</v>
       </c>
-      <c r="D121" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E121" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F121" s="26" t="s">
-        <v>343</v>
+      <c r="D121" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="E121" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="F121" s="30" t="s">
+        <v>104</v>
       </c>
       <c r="G121" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F121),0)&gt;0), MAX($G$1:G120)+1, ""))</f>
@@ -5123,53 +5126,53 @@
       </c>
     </row>
     <row r="122" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A122" s="36">
+      <c r="A122" s="26">
         <v>20</v>
       </c>
-      <c r="B122" s="37" t="s">
-        <v>335</v>
-      </c>
-      <c r="C122" s="38">
+      <c r="B122" s="27" t="s">
+        <v>338</v>
+      </c>
+      <c r="C122" s="28">
         <v>20</v>
       </c>
-      <c r="D122" s="36">
-        <v>3.2</v>
-      </c>
-      <c r="E122" s="37" t="s">
-        <v>336</v>
-      </c>
-      <c r="F122" s="36" t="s">
-        <v>332</v>
-      </c>
-      <c r="G122" s="29"/>
+      <c r="D122" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E122" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F122" s="26" t="s">
+        <v>342</v>
+      </c>
+      <c r="G122" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F122),0)&gt;0), MAX($G$1:G121)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H122" s="21" t="b">
         <f>A122=C122</f>
         <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A123" s="30">
+      <c r="A123" s="36">
         <v>20</v>
       </c>
-      <c r="B123" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="C123" s="32">
+      <c r="B123" s="37" t="s">
+        <v>334</v>
+      </c>
+      <c r="C123" s="38">
         <v>20</v>
       </c>
-      <c r="D123" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E123" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F123" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="G123" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F123),0)&gt;0), MAX($G$1:G122)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D123" s="36">
+        <v>3.2</v>
+      </c>
+      <c r="E123" s="37" t="s">
+        <v>335</v>
+      </c>
+      <c r="F123" s="36" t="s">
+        <v>331</v>
+      </c>
+      <c r="G123" s="29"/>
       <c r="H123" s="21" t="b">
         <f>A123=C123</f>
         <v>1</v>
@@ -5180,19 +5183,19 @@
         <v>20</v>
       </c>
       <c r="B124" s="31" t="s">
-        <v>263</v>
+        <v>101</v>
       </c>
       <c r="C124" s="32">
         <v>20</v>
       </c>
-      <c r="D124" s="30">
-        <v>6.2</v>
+      <c r="D124" s="30" t="s">
+        <v>207</v>
       </c>
       <c r="E124" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F124" s="30" t="s">
-        <v>264</v>
+        <v>102</v>
       </c>
       <c r="G124" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F124),0)&gt;0), MAX($G$1:G123)+1, ""))</f>
@@ -5208,19 +5211,19 @@
         <v>20</v>
       </c>
       <c r="B125" s="31" t="s">
-        <v>99</v>
+        <v>262</v>
       </c>
       <c r="C125" s="32">
         <v>20</v>
       </c>
-      <c r="D125" s="30" t="s">
-        <v>215</v>
+      <c r="D125" s="30">
+        <v>6.2</v>
       </c>
       <c r="E125" s="31" t="s">
-        <v>299</v>
+        <v>8</v>
       </c>
       <c r="F125" s="30" t="s">
-        <v>100</v>
+        <v>263</v>
       </c>
       <c r="G125" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F125),0)&gt;0), MAX($G$1:G124)+1, ""))</f>
@@ -5232,23 +5235,23 @@
       </c>
     </row>
     <row r="126" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A126" s="26">
+      <c r="A126" s="30">
         <v>20</v>
       </c>
-      <c r="B126" s="27" t="s">
-        <v>300</v>
-      </c>
-      <c r="C126" s="28">
+      <c r="B126" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="C126" s="32">
         <v>20</v>
       </c>
-      <c r="D126" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E126" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="F126" s="26" t="s">
-        <v>301</v>
+      <c r="D126" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="E126" s="31" t="s">
+        <v>298</v>
+      </c>
+      <c r="F126" s="30" t="s">
+        <v>100</v>
       </c>
       <c r="G126" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F126),0)&gt;0), MAX($G$1:G125)+1, ""))</f>
@@ -5260,23 +5263,23 @@
       </c>
     </row>
     <row r="127" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A127" s="30">
+      <c r="A127" s="26">
         <v>20</v>
       </c>
-      <c r="B127" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="C127" s="32">
+      <c r="B127" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="C127" s="28">
         <v>20</v>
       </c>
-      <c r="D127" s="30" t="s">
-        <v>216</v>
-      </c>
-      <c r="E127" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F127" s="30" t="s">
-        <v>96</v>
+      <c r="D127" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E127" s="27" t="s">
+        <v>298</v>
+      </c>
+      <c r="F127" s="26" t="s">
+        <v>300</v>
       </c>
       <c r="G127" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F127),0)&gt;0), MAX($G$1:G126)+1, ""))</f>
@@ -5288,31 +5291,31 @@
       </c>
     </row>
     <row r="128" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A128" s="26">
+      <c r="A128" s="30">
         <v>20</v>
       </c>
-      <c r="B128" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="C128" s="28">
-        <v>23</v>
-      </c>
-      <c r="D128" s="26">
-        <v>3.9</v>
-      </c>
-      <c r="E128" s="27" t="s">
-        <v>309</v>
-      </c>
-      <c r="F128" s="26" t="s">
-        <v>311</v>
+      <c r="B128" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="C128" s="32">
+        <v>20</v>
+      </c>
+      <c r="D128" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="E128" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F128" s="30" t="s">
+        <v>96</v>
       </c>
       <c r="G128" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F128),0)&gt;0), MAX($G$1:G126)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F128),0)&gt;0), MAX($G$1:G127)+1, ""))</f>
         <v/>
       </c>
       <c r="H128" s="21" t="b">
         <f>A128=C128</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
@@ -5320,47 +5323,47 @@
         <v>20</v>
       </c>
       <c r="B129" s="27" t="s">
-        <v>354</v>
+        <v>309</v>
       </c>
       <c r="C129" s="28">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D129" s="26">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="E129" s="27" t="s">
-        <v>81</v>
+        <v>308</v>
       </c>
       <c r="F129" s="26" t="s">
-        <v>355</v>
+        <v>310</v>
       </c>
       <c r="G129" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F129),0)&gt;0), MAX($G$1:G128)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F129),0)&gt;0), MAX($G$1:G127)+1, ""))</f>
         <v/>
       </c>
       <c r="H129" s="21" t="b">
         <f>A129=C129</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A130" s="30">
+      <c r="A130" s="26">
         <v>20</v>
       </c>
-      <c r="B130" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="C130" s="32">
+      <c r="B130" s="27" t="s">
+        <v>353</v>
+      </c>
+      <c r="C130" s="28">
         <v>20</v>
       </c>
-      <c r="D130" s="30" t="s">
-        <v>218</v>
-      </c>
-      <c r="E130" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F130" s="30" t="s">
-        <v>92</v>
+      <c r="D130" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E130" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F130" s="26" t="s">
+        <v>354</v>
       </c>
       <c r="G130" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F130),0)&gt;0), MAX($G$1:G129)+1, ""))</f>
@@ -5376,19 +5379,19 @@
         <v>20</v>
       </c>
       <c r="B131" s="31" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C131" s="32">
         <v>20</v>
       </c>
       <c r="D131" s="30" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="E131" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F131" s="30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G131" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F131),0)&gt;0), MAX($G$1:G130)+1, ""))</f>
@@ -5404,16 +5407,16 @@
         <v>20</v>
       </c>
       <c r="B132" s="31" t="s">
-        <v>290</v>
+        <v>89</v>
       </c>
       <c r="C132" s="32">
         <v>20</v>
       </c>
-      <c r="D132" s="30">
-        <v>1.8</v>
+      <c r="D132" s="30" t="s">
+        <v>223</v>
       </c>
       <c r="E132" s="31" t="s">
-        <v>291</v>
+        <v>8</v>
       </c>
       <c r="F132" s="30" t="s">
         <v>90</v>
@@ -5432,19 +5435,19 @@
         <v>20</v>
       </c>
       <c r="B133" s="31" t="s">
-        <v>87</v>
+        <v>289</v>
       </c>
       <c r="C133" s="32">
         <v>20</v>
       </c>
-      <c r="D133" s="30" t="s">
-        <v>222</v>
+      <c r="D133" s="30">
+        <v>1.8</v>
       </c>
       <c r="E133" s="31" t="s">
-        <v>8</v>
+        <v>290</v>
       </c>
       <c r="F133" s="30" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G133" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F133),0)&gt;0), MAX($G$1:G132)+1, ""))</f>
@@ -5460,19 +5463,19 @@
         <v>20</v>
       </c>
       <c r="B134" s="31" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C134" s="32">
         <v>20</v>
       </c>
       <c r="D134" s="30" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E134" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F134" s="30" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G134" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F134),0)&gt;0), MAX($G$1:G133)+1, ""))</f>
@@ -5488,19 +5491,19 @@
         <v>20</v>
       </c>
       <c r="B135" s="31" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C135" s="32">
         <v>20</v>
       </c>
       <c r="D135" s="30" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E135" s="31" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F135" s="30" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G135" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F135),0)&gt;0), MAX($G$1:G134)+1, ""))</f>
@@ -5516,19 +5519,19 @@
         <v>20</v>
       </c>
       <c r="B136" s="31" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C136" s="32">
         <v>20</v>
       </c>
       <c r="D136" s="30" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E136" s="31" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="F136" s="30" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G136" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F136),0)&gt;0), MAX($G$1:G135)+1, ""))</f>
@@ -5544,19 +5547,19 @@
         <v>20</v>
       </c>
       <c r="B137" s="31" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C137" s="32">
         <v>20</v>
       </c>
       <c r="D137" s="30" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E137" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F137" s="30" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G137" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F137),0)&gt;0), MAX($G$1:G136)+1, ""))</f>
@@ -5568,23 +5571,23 @@
       </c>
     </row>
     <row r="138" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A138" s="26">
-        <v>25</v>
-      </c>
-      <c r="B138" s="27" t="s">
-        <v>178</v>
-      </c>
-      <c r="C138" s="28">
-        <v>25</v>
-      </c>
-      <c r="D138" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="E138" s="27" t="s">
+      <c r="A138" s="30">
+        <v>20</v>
+      </c>
+      <c r="B138" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="C138" s="32">
+        <v>20</v>
+      </c>
+      <c r="D138" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="E138" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F138" s="26" t="s">
-        <v>179</v>
+      <c r="F138" s="30" t="s">
+        <v>77</v>
       </c>
       <c r="G138" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F138),0)&gt;0), MAX($G$1:G137)+1, ""))</f>
@@ -5600,19 +5603,19 @@
         <v>25</v>
       </c>
       <c r="B139" s="27" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C139" s="28">
         <v>25</v>
       </c>
       <c r="D139" s="26" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="E139" s="27" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="F139" s="26" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G139" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F139),0)&gt;0), MAX($G$1:G138)+1, ""))</f>
@@ -5628,19 +5631,19 @@
         <v>25</v>
       </c>
       <c r="B140" s="27" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C140" s="28">
         <v>25</v>
       </c>
       <c r="D140" s="26" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="E140" s="27" t="s">
         <v>131</v>
       </c>
       <c r="F140" s="26" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G140" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F140),0)&gt;0), MAX($G$1:G139)+1, ""))</f>
@@ -5656,19 +5659,19 @@
         <v>25</v>
       </c>
       <c r="B141" s="27" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C141" s="28">
         <v>25</v>
       </c>
       <c r="D141" s="26" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="E141" s="27" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F141" s="26" t="s">
-        <v>324</v>
+        <v>175</v>
       </c>
       <c r="G141" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F141),0)&gt;0), MAX($G$1:G140)+1, ""))</f>
@@ -5684,19 +5687,19 @@
         <v>25</v>
       </c>
       <c r="B142" s="27" t="s">
-        <v>358</v>
+        <v>173</v>
       </c>
       <c r="C142" s="28">
         <v>25</v>
       </c>
-      <c r="D142" s="26">
-        <v>3</v>
+      <c r="D142" s="26" t="s">
+        <v>224</v>
       </c>
       <c r="E142" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F142" s="26" t="s">
-        <v>359</v>
+        <v>323</v>
       </c>
       <c r="G142" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F142),0)&gt;0), MAX($G$1:G141)+1, ""))</f>
@@ -5712,19 +5715,19 @@
         <v>25</v>
       </c>
       <c r="B143" s="27" t="s">
-        <v>172</v>
+        <v>357</v>
       </c>
       <c r="C143" s="28">
         <v>25</v>
       </c>
       <c r="D143" s="26">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="E143" s="27" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F143" s="26" t="s">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="G143" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F143),0)&gt;0), MAX($G$1:G142)+1, ""))</f>
@@ -5736,23 +5739,23 @@
       </c>
     </row>
     <row r="144" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A144" s="30">
+      <c r="A144" s="26">
         <v>25</v>
       </c>
-      <c r="B144" s="31" t="s">
-        <v>284</v>
-      </c>
-      <c r="C144" s="32">
+      <c r="B144" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="C144" s="28">
         <v>25</v>
       </c>
-      <c r="D144" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E144" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F144" s="30" t="s">
-        <v>102</v>
+      <c r="D144" s="26">
+        <v>2.7</v>
+      </c>
+      <c r="E144" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F144" s="26" t="s">
+        <v>337</v>
       </c>
       <c r="G144" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F144),0)&gt;0), MAX($G$1:G143)+1, ""))</f>
@@ -5768,7 +5771,7 @@
         <v>25</v>
       </c>
       <c r="B145" s="31" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C145" s="32">
         <v>25</v>
@@ -5777,7 +5780,7 @@
         <v>207</v>
       </c>
       <c r="E145" s="31" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F145" s="30" t="s">
         <v>102</v>
@@ -5792,23 +5795,23 @@
       </c>
     </row>
     <row r="146" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A146" s="26">
+      <c r="A146" s="30">
         <v>25</v>
       </c>
-      <c r="B146" s="27" t="s">
-        <v>170</v>
-      </c>
-      <c r="C146" s="28">
+      <c r="B146" s="31" t="s">
+        <v>281</v>
+      </c>
+      <c r="C146" s="32">
         <v>25</v>
       </c>
-      <c r="D146" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="E146" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="F146" s="26" t="s">
-        <v>171</v>
+      <c r="D146" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E146" s="31" t="s">
+        <v>282</v>
+      </c>
+      <c r="F146" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G146" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F146),0)&gt;0), MAX($G$1:G145)+1, ""))</f>
@@ -5824,19 +5827,19 @@
         <v>25</v>
       </c>
       <c r="B147" s="27" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C147" s="28">
         <v>25</v>
       </c>
       <c r="D147" s="26" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="E147" s="27" t="s">
-        <v>8</v>
+        <v>244</v>
       </c>
       <c r="F147" s="26" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G147" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F147),0)&gt;0), MAX($G$1:G146)+1, ""))</f>
@@ -5852,19 +5855,19 @@
         <v>25</v>
       </c>
       <c r="B148" s="27" t="s">
-        <v>356</v>
+        <v>168</v>
       </c>
       <c r="C148" s="28">
         <v>25</v>
       </c>
-      <c r="D148" s="26">
-        <v>3.4</v>
+      <c r="D148" s="26" t="s">
+        <v>217</v>
       </c>
       <c r="E148" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F148" s="26" t="s">
-        <v>357</v>
+        <v>169</v>
       </c>
       <c r="G148" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F148),0)&gt;0), MAX($G$1:G147)+1, ""))</f>
@@ -5876,23 +5879,23 @@
       </c>
     </row>
     <row r="149" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A149" s="30">
+      <c r="A149" s="26">
         <v>25</v>
       </c>
-      <c r="B149" s="31" t="s">
-        <v>278</v>
-      </c>
-      <c r="C149" s="32">
+      <c r="B149" s="27" t="s">
+        <v>355</v>
+      </c>
+      <c r="C149" s="28">
         <v>25</v>
       </c>
-      <c r="D149" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E149" s="31" t="s">
+      <c r="D149" s="26">
+        <v>3.4</v>
+      </c>
+      <c r="E149" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F149" s="30" t="s">
-        <v>102</v>
+      <c r="F149" s="26" t="s">
+        <v>356</v>
       </c>
       <c r="G149" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B149),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E149),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F149),0)&gt;0), MAX($G$1:G148)+1, ""))</f>
@@ -5904,23 +5907,23 @@
       </c>
     </row>
     <row r="150" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A150" s="26">
+      <c r="A150" s="30">
         <v>25</v>
       </c>
-      <c r="B150" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="C150" s="28">
+      <c r="B150" s="31" t="s">
+        <v>277</v>
+      </c>
+      <c r="C150" s="32">
         <v>25</v>
       </c>
-      <c r="D150" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="E150" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="F150" s="26" t="s">
-        <v>167</v>
+      <c r="D150" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E150" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F150" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G150" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B150),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E150),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F150),0)&gt;0), MAX($G$1:G149)+1, ""))</f>
@@ -5936,19 +5939,19 @@
         <v>25</v>
       </c>
       <c r="B151" s="27" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C151" s="28">
         <v>25</v>
       </c>
       <c r="D151" s="26" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="E151" s="27" t="s">
         <v>131</v>
       </c>
       <c r="F151" s="26" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G151" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B151),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E151),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F151),0)&gt;0), MAX($G$1:G150)+1, ""))</f>
@@ -5964,19 +5967,19 @@
         <v>25</v>
       </c>
       <c r="B152" s="27" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C152" s="28">
         <v>25</v>
       </c>
       <c r="D152" s="26" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E152" s="27" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="F152" s="26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G152" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B152),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E152),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F152),0)&gt;0), MAX($G$1:G151)+1, ""))</f>
@@ -5992,19 +5995,19 @@
         <v>25</v>
       </c>
       <c r="B153" s="27" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C153" s="28">
         <v>25</v>
       </c>
       <c r="D153" s="26" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="E153" s="27" t="s">
         <v>81</v>
       </c>
       <c r="F153" s="26" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G153" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B153),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E153),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F153),0)&gt;0), MAX($G$1:G152)+1, ""))</f>
@@ -6020,19 +6023,19 @@
         <v>25</v>
       </c>
       <c r="B154" s="27" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C154" s="28">
         <v>25</v>
       </c>
       <c r="D154" s="26" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E154" s="27" t="s">
         <v>81</v>
       </c>
       <c r="F154" s="26" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G154" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B154),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E154),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F154),0)&gt;0), MAX($G$1:G153)+1, ""))</f>
@@ -6048,19 +6051,19 @@
         <v>25</v>
       </c>
       <c r="B155" s="27" t="s">
-        <v>392</v>
+        <v>158</v>
       </c>
       <c r="C155" s="28">
         <v>25</v>
       </c>
-      <c r="D155" s="26">
-        <v>3.4</v>
+      <c r="D155" s="26" t="s">
+        <v>228</v>
       </c>
       <c r="E155" s="27" t="s">
         <v>81</v>
       </c>
       <c r="F155" s="26" t="s">
-        <v>342</v>
+        <v>159</v>
       </c>
       <c r="G155" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F155),0)&gt;0), MAX($G$1:G154)+1, ""))</f>
@@ -6076,22 +6079,22 @@
         <v>25</v>
       </c>
       <c r="B156" s="27" t="s">
-        <v>156</v>
+        <v>391</v>
       </c>
       <c r="C156" s="28">
         <v>25</v>
       </c>
-      <c r="D156" s="26" t="s">
-        <v>227</v>
+      <c r="D156" s="26">
+        <v>3.4</v>
       </c>
       <c r="E156" s="27" t="s">
         <v>81</v>
       </c>
       <c r="F156" s="26" t="s">
-        <v>157</v>
+        <v>341</v>
       </c>
       <c r="G156" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B156),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E156),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F156),0)&gt;0), MAX($G$1:G154)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B156),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E156),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F156),0)&gt;0), MAX($G$1:G155)+1, ""))</f>
         <v/>
       </c>
       <c r="H156" s="21" t="b">
@@ -6104,22 +6107,22 @@
         <v>25</v>
       </c>
       <c r="B157" s="27" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C157" s="28">
         <v>25</v>
       </c>
       <c r="D157" s="26" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E157" s="27" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="F157" s="26" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G157" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F157),0)&gt;0), MAX($G$1:G156)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F157),0)&gt;0), MAX($G$1:G155)+1, ""))</f>
         <v/>
       </c>
       <c r="H157" s="21" t="b">
@@ -6132,19 +6135,19 @@
         <v>25</v>
       </c>
       <c r="B158" s="27" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C158" s="28">
         <v>25</v>
       </c>
       <c r="D158" s="26" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="E158" s="27" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="F158" s="26" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G158" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B158),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E158),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F158),0)&gt;0), MAX($G$1:G157)+1, ""))</f>
@@ -6160,19 +6163,19 @@
         <v>25</v>
       </c>
       <c r="B159" s="27" t="s">
-        <v>247</v>
+        <v>152</v>
       </c>
       <c r="C159" s="28">
         <v>25</v>
       </c>
-      <c r="D159" s="39" t="s">
-        <v>229</v>
+      <c r="D159" s="26" t="s">
+        <v>230</v>
       </c>
       <c r="E159" s="27" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F159" s="26" t="s">
-        <v>248</v>
+        <v>153</v>
       </c>
       <c r="G159" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F159),0)&gt;0), MAX($G$1:G158)+1, ""))</f>
@@ -6188,19 +6191,19 @@
         <v>25</v>
       </c>
       <c r="B160" s="27" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="C160" s="28">
         <v>25</v>
       </c>
-      <c r="D160" s="26" t="s">
-        <v>235</v>
+      <c r="D160" s="39" t="s">
+        <v>229</v>
       </c>
       <c r="E160" s="27" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="F160" s="26" t="s">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="G160" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B160),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E160),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F160),0)&gt;0), MAX($G$1:G159)+1, ""))</f>
@@ -6212,23 +6215,23 @@
       </c>
     </row>
     <row r="161" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A161" s="30">
+      <c r="A161" s="26">
         <v>25</v>
       </c>
-      <c r="B161" s="31" t="s">
-        <v>288</v>
-      </c>
-      <c r="C161" s="32">
+      <c r="B161" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C161" s="28">
         <v>25</v>
       </c>
-      <c r="D161" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E161" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F161" s="30" t="s">
-        <v>102</v>
+      <c r="D161" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="E161" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="F161" s="26" t="s">
+        <v>151</v>
       </c>
       <c r="G161" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B161),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E161),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F161),0)&gt;0), MAX($G$1:G160)+1, ""))</f>
@@ -6244,7 +6247,7 @@
         <v>25</v>
       </c>
       <c r="B162" s="31" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C162" s="32">
         <v>25</v>
@@ -6253,7 +6256,7 @@
         <v>207</v>
       </c>
       <c r="E162" s="31" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F162" s="30" t="s">
         <v>102</v>
@@ -6272,7 +6275,7 @@
         <v>25</v>
       </c>
       <c r="B163" s="31" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C163" s="32">
         <v>25</v>
@@ -6281,7 +6284,7 @@
         <v>207</v>
       </c>
       <c r="E163" s="31" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F163" s="30" t="s">
         <v>102</v>
@@ -6296,23 +6299,23 @@
       </c>
     </row>
     <row r="164" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A164" s="26">
+      <c r="A164" s="30">
         <v>25</v>
       </c>
-      <c r="B164" s="27" t="s">
-        <v>252</v>
-      </c>
-      <c r="C164" s="28">
+      <c r="B164" s="31" t="s">
+        <v>286</v>
+      </c>
+      <c r="C164" s="32">
         <v>25</v>
       </c>
-      <c r="D164" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E164" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="F164" s="26" t="s">
-        <v>253</v>
+      <c r="D164" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E164" s="31" t="s">
+        <v>282</v>
+      </c>
+      <c r="F164" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G164" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B164),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E164),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F164),0)&gt;0), MAX($G$1:G163)+1, ""))</f>
@@ -6324,23 +6327,23 @@
       </c>
     </row>
     <row r="165" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A165" s="30">
+      <c r="A165" s="26">
         <v>25</v>
       </c>
-      <c r="B165" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="C165" s="32">
+      <c r="B165" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="C165" s="28">
         <v>25</v>
       </c>
-      <c r="D165" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E165" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="F165" s="30" t="s">
-        <v>102</v>
+      <c r="D165" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E165" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="F165" s="26" t="s">
+        <v>252</v>
       </c>
       <c r="G165" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B165),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E165),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F165),0)&gt;0), MAX($G$1:G164)+1, ""))</f>
@@ -6352,26 +6355,26 @@
       </c>
     </row>
     <row r="166" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A166" s="26">
+      <c r="A166" s="30">
         <v>25</v>
       </c>
-      <c r="B166" s="27" t="s">
-        <v>148</v>
-      </c>
-      <c r="C166" s="28">
+      <c r="B166" s="31" t="s">
+        <v>284</v>
+      </c>
+      <c r="C166" s="32">
         <v>25</v>
       </c>
-      <c r="D166" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="E166" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F166" s="26" t="s">
-        <v>149</v>
+      <c r="D166" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E166" s="31" t="s">
+        <v>282</v>
+      </c>
+      <c r="F166" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G166" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B166),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E166),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F166),0)&gt;0), MAX($G$1:G164)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B166),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E166),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F166),0)&gt;0), MAX($G$1:G165)+1, ""))</f>
         <v/>
       </c>
       <c r="H166" s="21" t="b">
@@ -6380,26 +6383,26 @@
       </c>
     </row>
     <row r="167" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A167" s="30">
-        <v>30</v>
-      </c>
-      <c r="B167" s="31" t="s">
-        <v>192</v>
-      </c>
-      <c r="C167" s="32">
-        <v>30</v>
-      </c>
-      <c r="D167" s="30" t="s">
-        <v>232</v>
-      </c>
-      <c r="E167" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="F167" s="30" t="s">
-        <v>193</v>
+      <c r="A167" s="26">
+        <v>25</v>
+      </c>
+      <c r="B167" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="C167" s="28">
+        <v>25</v>
+      </c>
+      <c r="D167" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="E167" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F167" s="26" t="s">
+        <v>149</v>
       </c>
       <c r="G167" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B167),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E167),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F167),0)&gt;0), MAX($G$1:G166)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B167),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E167),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F167),0)&gt;0), MAX($G$1:G165)+1, ""))</f>
         <v/>
       </c>
       <c r="H167" s="21" t="b">
@@ -6412,19 +6415,19 @@
         <v>30</v>
       </c>
       <c r="B168" s="31" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C168" s="32">
         <v>30</v>
       </c>
       <c r="D168" s="30" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="E168" s="31" t="s">
         <v>131</v>
       </c>
       <c r="F168" s="30" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="G168" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B168),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E168),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F168),0)&gt;0), MAX($G$1:G167)+1, ""))</f>
@@ -6440,13 +6443,13 @@
         <v>30</v>
       </c>
       <c r="B169" s="31" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C169" s="32">
         <v>30</v>
       </c>
       <c r="D169" s="30" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E169" s="31" t="s">
         <v>131</v>
@@ -6468,19 +6471,19 @@
         <v>30</v>
       </c>
       <c r="B170" s="31" t="s">
-        <v>246</v>
+        <v>189</v>
       </c>
       <c r="C170" s="32">
         <v>30</v>
       </c>
       <c r="D170" s="30" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="E170" s="31" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F170" s="30" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G170" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B170),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E170),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F170),0)&gt;0), MAX($G$1:G169)+1, ""))</f>
@@ -6496,22 +6499,22 @@
         <v>30</v>
       </c>
       <c r="B171" s="31" t="s">
-        <v>405</v>
+        <v>245</v>
       </c>
       <c r="C171" s="32">
         <v>30</v>
       </c>
-      <c r="D171" s="30">
-        <v>6.2</v>
+      <c r="D171" s="30" t="s">
+        <v>217</v>
       </c>
       <c r="E171" s="31" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="F171" s="30" t="s">
-        <v>406</v>
+        <v>188</v>
       </c>
       <c r="G171" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B171),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E171),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F171),0)&gt;0), MAX($G$1:G169)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B171),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E171),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F171),0)&gt;0), MAX($G$1:G170)+1, ""))</f>
         <v/>
       </c>
       <c r="H171" s="21" t="b">
@@ -6520,26 +6523,26 @@
       </c>
     </row>
     <row r="172" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A172" s="26">
+      <c r="A172" s="30">
         <v>30</v>
       </c>
-      <c r="B172" s="27" t="s">
-        <v>393</v>
-      </c>
-      <c r="C172" s="28">
+      <c r="B172" s="31" t="s">
+        <v>404</v>
+      </c>
+      <c r="C172" s="32">
         <v>30</v>
       </c>
-      <c r="D172" s="26">
-        <v>3.6</v>
-      </c>
-      <c r="E172" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F172" s="26" t="s">
-        <v>394</v>
+      <c r="D172" s="30">
+        <v>6.2</v>
+      </c>
+      <c r="E172" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="F172" s="30" t="s">
+        <v>405</v>
       </c>
       <c r="G172" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B172),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E172),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F172),0)&gt;0), MAX($G$1:G171)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B172),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E172),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F172),0)&gt;0), MAX($G$1:G170)+1, ""))</f>
         <v/>
       </c>
       <c r="H172" s="21" t="b">
@@ -6548,23 +6551,23 @@
       </c>
     </row>
     <row r="173" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A173" s="30">
+      <c r="A173" s="26">
         <v>30</v>
       </c>
-      <c r="B173" s="31" t="s">
-        <v>186</v>
-      </c>
-      <c r="C173" s="32">
+      <c r="B173" s="27" t="s">
+        <v>392</v>
+      </c>
+      <c r="C173" s="28">
         <v>30</v>
       </c>
-      <c r="D173" s="30" t="s">
-        <v>229</v>
-      </c>
-      <c r="E173" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F173" s="30" t="s">
-        <v>187</v>
+      <c r="D173" s="26">
+        <v>3.6</v>
+      </c>
+      <c r="E173" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F173" s="26" t="s">
+        <v>393</v>
       </c>
       <c r="G173" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B173),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E173),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F173),0)&gt;0), MAX($G$1:G172)+1, ""))</f>
@@ -6580,19 +6583,19 @@
         <v>30</v>
       </c>
       <c r="B174" s="31" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C174" s="32">
         <v>30</v>
       </c>
       <c r="D174" s="30" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E174" s="31" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F174" s="30" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G174" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B174),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E174),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F174),0)&gt;0), MAX($G$1:G173)+1, ""))</f>
@@ -6604,23 +6607,23 @@
       </c>
     </row>
     <row r="175" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A175" s="26">
+      <c r="A175" s="30">
         <v>30</v>
       </c>
-      <c r="B175" s="27" t="s">
-        <v>376</v>
-      </c>
-      <c r="C175" s="28">
+      <c r="B175" s="31" t="s">
+        <v>184</v>
+      </c>
+      <c r="C175" s="32">
         <v>30</v>
       </c>
-      <c r="D175" s="26">
-        <v>5</v>
-      </c>
-      <c r="E175" s="27" t="s">
-        <v>377</v>
-      </c>
-      <c r="F175" s="26" t="s">
-        <v>25</v>
+      <c r="D175" s="30" t="s">
+        <v>228</v>
+      </c>
+      <c r="E175" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="F175" s="30" t="s">
+        <v>185</v>
       </c>
       <c r="G175" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B175),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E175),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F175),0)&gt;0), MAX($G$1:G174)+1, ""))</f>
@@ -6632,26 +6635,26 @@
       </c>
     </row>
     <row r="176" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A176" s="30">
+      <c r="A176" s="26">
         <v>30</v>
       </c>
-      <c r="B176" s="31" t="s">
-        <v>403</v>
-      </c>
-      <c r="C176" s="32">
+      <c r="B176" s="27" t="s">
+        <v>375</v>
+      </c>
+      <c r="C176" s="28">
         <v>30</v>
       </c>
-      <c r="D176" s="30">
-        <v>5.5</v>
-      </c>
-      <c r="E176" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="F176" s="30" t="s">
-        <v>404</v>
+      <c r="D176" s="26">
+        <v>5</v>
+      </c>
+      <c r="E176" s="27" t="s">
+        <v>376</v>
+      </c>
+      <c r="F176" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="G176" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B176),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E176),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F176),0)&gt;0), MAX($G$1:G174)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B176),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E176),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F176),0)&gt;0), MAX($G$1:G175)+1, ""))</f>
         <v/>
       </c>
       <c r="H176" s="21" t="b">
@@ -6664,22 +6667,22 @@
         <v>30</v>
       </c>
       <c r="B177" s="31" t="s">
-        <v>182</v>
+        <v>402</v>
       </c>
       <c r="C177" s="32">
         <v>30</v>
       </c>
-      <c r="D177" s="30" t="s">
-        <v>239</v>
+      <c r="D177" s="30">
+        <v>5.5</v>
       </c>
       <c r="E177" s="31" t="s">
         <v>131</v>
       </c>
       <c r="F177" s="30" t="s">
-        <v>183</v>
+        <v>403</v>
       </c>
       <c r="G177" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B177),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E177),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F177),0)&gt;0), MAX($G$1:G176)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B177),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E177),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F177),0)&gt;0), MAX($G$1:G175)+1, ""))</f>
         <v/>
       </c>
       <c r="H177" s="21" t="b">
@@ -6692,19 +6695,19 @@
         <v>30</v>
       </c>
       <c r="B178" s="31" t="s">
-        <v>337</v>
+        <v>182</v>
       </c>
       <c r="C178" s="32">
         <v>30</v>
       </c>
-      <c r="D178" s="30">
-        <v>2.9</v>
+      <c r="D178" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="E178" s="31" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="F178" s="30" t="s">
-        <v>338</v>
+        <v>183</v>
       </c>
       <c r="G178" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B178),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E178),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F178),0)&gt;0), MAX($G$1:G177)+1, ""))</f>
@@ -6720,22 +6723,22 @@
         <v>30</v>
       </c>
       <c r="B179" s="31" t="s">
-        <v>180</v>
+        <v>336</v>
       </c>
       <c r="C179" s="32">
         <v>30</v>
       </c>
-      <c r="D179" s="30" t="s">
-        <v>238</v>
+      <c r="D179" s="30">
+        <v>2.9</v>
       </c>
       <c r="E179" s="31" t="s">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="F179" s="30" t="s">
-        <v>181</v>
+        <v>337</v>
       </c>
       <c r="G179" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B179),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E179),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F179),0)&gt;0), MAX($G$1:G177)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B179),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E179),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F179),0)&gt;0), MAX($G$1:G178)+1, ""))</f>
         <v/>
       </c>
       <c r="H179" s="21" t="b">
@@ -6744,26 +6747,26 @@
       </c>
     </row>
     <row r="180" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A180" s="26">
-        <v>40</v>
-      </c>
-      <c r="B180" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="C180" s="28">
-        <v>40</v>
-      </c>
-      <c r="D180" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="E180" s="27" t="s">
-        <v>198</v>
-      </c>
-      <c r="F180" s="26" t="s">
-        <v>199</v>
+      <c r="A180" s="30">
+        <v>30</v>
+      </c>
+      <c r="B180" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="C180" s="32">
+        <v>30</v>
+      </c>
+      <c r="D180" s="30" t="s">
+        <v>238</v>
+      </c>
+      <c r="E180" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="F180" s="30" t="s">
+        <v>181</v>
       </c>
       <c r="G180" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B180),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E180),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F180),0)&gt;0), MAX($G$1:G177)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B180),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E180),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F180),0)&gt;0), MAX($G$1:G178)+1, ""))</f>
         <v/>
       </c>
       <c r="H180" s="21" t="b">
@@ -6776,22 +6779,22 @@
         <v>40</v>
       </c>
       <c r="B181" s="27" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C181" s="28">
         <v>40</v>
       </c>
       <c r="D181" s="26" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E181" s="27" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F181" s="26" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G181" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B181),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E181),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F181),0)&gt;0), MAX($G$1:G180)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B181),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E181),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F181),0)&gt;0), MAX($G$1:G178)+1, ""))</f>
         <v/>
       </c>
       <c r="H181" s="21" t="b">
@@ -6804,19 +6807,19 @@
         <v>40</v>
       </c>
       <c r="B182" s="27" t="s">
-        <v>249</v>
+        <v>194</v>
       </c>
       <c r="C182" s="28">
         <v>40</v>
       </c>
-      <c r="D182" s="26">
-        <v>8.3000000000000007</v>
+      <c r="D182" s="26" t="s">
+        <v>242</v>
       </c>
       <c r="E182" s="27" t="s">
-        <v>250</v>
+        <v>195</v>
       </c>
       <c r="F182" s="26" t="s">
-        <v>251</v>
+        <v>196</v>
       </c>
       <c r="G182" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B182),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E182),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F182),0)&gt;0), MAX($G$1:G181)+1, ""))</f>
@@ -6829,22 +6832,22 @@
     </row>
     <row r="183" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A183" s="26">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B183" s="27" t="s">
-        <v>294</v>
+        <v>248</v>
       </c>
       <c r="C183" s="28">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D183" s="26">
-        <v>10.199999999999999</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="E183" s="27" t="s">
-        <v>295</v>
+        <v>249</v>
       </c>
       <c r="F183" s="26" t="s">
-        <v>296</v>
+        <v>250</v>
       </c>
       <c r="G183" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B183),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E183),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F183),0)&gt;0), MAX($G$1:G182)+1, ""))</f>
@@ -6856,10 +6859,32 @@
       </c>
     </row>
     <row r="184" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A184" s="1"/>
-      <c r="C184" s="1"/>
-      <c r="D184" s="1"/>
-      <c r="F184" s="1"/>
+      <c r="A184" s="26">
+        <v>45</v>
+      </c>
+      <c r="B184" s="27" t="s">
+        <v>293</v>
+      </c>
+      <c r="C184" s="28">
+        <v>45</v>
+      </c>
+      <c r="D184" s="26">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E184" s="27" t="s">
+        <v>294</v>
+      </c>
+      <c r="F184" s="26" t="s">
+        <v>295</v>
+      </c>
+      <c r="G184" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B184),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E184),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F184),0)&gt;0), MAX($G$1:G183)+1, ""))</f>
+        <v/>
+      </c>
+      <c r="H184" s="21" t="b">
+        <f>A184=C184</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="185" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
@@ -12057,12 +12082,18 @@
       <c r="D1050" s="1"/>
       <c r="F1050" s="1"/>
     </row>
+    <row r="1051" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A1051" s="1"/>
+      <c r="C1051" s="1"/>
+      <c r="D1051" s="1"/>
+      <c r="F1051" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H183">
-    <sortState ref="A2:H183">
-      <sortCondition ref="A2:A183"/>
-      <sortCondition ref="B2:B183"/>
-      <sortCondition ref="D2:D183"/>
+  <autoFilter ref="A1:H184">
+    <sortState ref="A2:H184">
+      <sortCondition ref="A2:A184"/>
+      <sortCondition ref="B2:B184"/>
+      <sortCondition ref="D2:D184"/>
     </sortState>
   </autoFilter>
   <sortState ref="A2:H174">

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Consulta" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$184</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$183</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$146</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Base!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="407">
   <si>
     <t>Grupo</t>
   </si>
@@ -1188,12 +1188,6 @@
     <t>MOEMA</t>
   </si>
   <si>
-    <t>PARAPUÃ ATÉ PREDIOS (383)</t>
-  </si>
-  <si>
-    <t>PARAPUÃ APÓS PREDIOS (383)</t>
-  </si>
-  <si>
     <t>ANIBAL ESTEVES</t>
   </si>
   <si>
@@ -1249,6 +1243,9 @@
   </si>
   <si>
     <t>SALVADOR SABATE APÓS BANDEIRA DE MELO</t>
+  </si>
+  <si>
+    <t>PIRAPUÃ (383)</t>
   </si>
 </sst>
 </file>
@@ -1766,7 +1763,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H1051"/>
+  <dimension ref="A1:H1050"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.453125" customWidth="1"/>
@@ -2197,7 +2194,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="C16" s="28">
         <v>13</v>
@@ -2337,7 +2334,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C21" s="28">
         <v>15</v>
@@ -2349,7 +2346,7 @@
         <v>8</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G21" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F21),0)&gt;0), MAX($G$1:G19)+1, ""))</f>
@@ -2729,7 +2726,7 @@
         <v>15</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C35" s="28">
         <v>15</v>
@@ -2741,7 +2738,7 @@
         <v>8</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G35" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F35),0)&gt;0), MAX($G$1:G34)+1, ""))</f>
@@ -2953,19 +2950,19 @@
         <v>15</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>388</v>
+        <v>46</v>
       </c>
       <c r="C43" s="28">
         <v>15</v>
       </c>
-      <c r="D43" s="26">
-        <v>1.3</v>
+      <c r="D43" s="26" t="s">
+        <v>233</v>
       </c>
       <c r="E43" s="27" t="s">
-        <v>379</v>
+        <v>8</v>
       </c>
       <c r="F43" s="26" t="s">
-        <v>380</v>
+        <v>47</v>
       </c>
       <c r="G43" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F43),0)&gt;0), MAX($G$1:G42)+1, ""))</f>
@@ -2981,19 +2978,19 @@
         <v>15</v>
       </c>
       <c r="B44" s="27" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C44" s="28">
         <v>15</v>
       </c>
       <c r="D44" s="26" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="E44" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F44" s="26" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G44" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F44),0)&gt;0), MAX($G$1:G43)+1, ""))</f>
@@ -3009,19 +3006,19 @@
         <v>15</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C45" s="28">
         <v>15</v>
       </c>
       <c r="D45" s="26" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="E45" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F45" s="26" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G45" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F45),0)&gt;0), MAX($G$1:G44)+1, ""))</f>
@@ -3037,19 +3034,19 @@
         <v>15</v>
       </c>
       <c r="B46" s="27" t="s">
-        <v>40</v>
+        <v>394</v>
       </c>
       <c r="C46" s="28">
         <v>15</v>
       </c>
-      <c r="D46" s="26" t="s">
-        <v>212</v>
+      <c r="D46" s="26">
+        <v>1.8</v>
       </c>
       <c r="E46" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F46" s="26" t="s">
-        <v>41</v>
+        <v>395</v>
       </c>
       <c r="G46" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F46),0)&gt;0), MAX($G$1:G45)+1, ""))</f>
@@ -3065,19 +3062,19 @@
         <v>15</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>396</v>
+        <v>307</v>
       </c>
       <c r="C47" s="28">
         <v>15</v>
       </c>
       <c r="D47" s="26">
-        <v>1.8</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E47" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F47" s="26" t="s">
-        <v>397</v>
+        <v>292</v>
       </c>
       <c r="G47" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F47),0)&gt;0), MAX($G$1:G46)+1, ""))</f>
@@ -3093,22 +3090,22 @@
         <v>15</v>
       </c>
       <c r="B48" s="27" t="s">
-        <v>307</v>
+        <v>404</v>
       </c>
       <c r="C48" s="28">
         <v>15</v>
       </c>
       <c r="D48" s="26">
-        <v>2.2000000000000002</v>
+        <v>2.1</v>
       </c>
       <c r="E48" s="27" t="s">
-        <v>8</v>
+        <v>244</v>
       </c>
       <c r="F48" s="26" t="s">
-        <v>292</v>
+        <v>202</v>
       </c>
       <c r="G48" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F48),0)&gt;0), MAX($G$1:G47)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F48),0)&gt;0), MAX($G$1:G46)+1, ""))</f>
         <v/>
       </c>
       <c r="H48" s="21" t="b">
@@ -3121,22 +3118,22 @@
         <v>15</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>406</v>
+        <v>38</v>
       </c>
       <c r="C49" s="28">
         <v>15</v>
       </c>
-      <c r="D49" s="26">
-        <v>2.1</v>
+      <c r="D49" s="26" t="s">
+        <v>211</v>
       </c>
       <c r="E49" s="27" t="s">
-        <v>244</v>
+        <v>8</v>
       </c>
       <c r="F49" s="26" t="s">
-        <v>202</v>
+        <v>39</v>
       </c>
       <c r="G49" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F49),0)&gt;0), MAX($G$1:G47)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F49),0)&gt;0), MAX($G$1:G43)+1, ""))</f>
         <v/>
       </c>
       <c r="H49" s="21" t="b">
@@ -3149,22 +3146,22 @@
         <v>15</v>
       </c>
       <c r="B50" s="27" t="s">
-        <v>38</v>
+        <v>340</v>
       </c>
       <c r="C50" s="28">
         <v>15</v>
       </c>
-      <c r="D50" s="26" t="s">
-        <v>211</v>
+      <c r="D50" s="26">
+        <v>1.4</v>
       </c>
       <c r="E50" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F50" s="26" t="s">
-        <v>39</v>
+        <v>345</v>
       </c>
       <c r="G50" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F50),0)&gt;0), MAX($G$1:G44)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F50),0)&gt;0), MAX($G$1:G49)+1, ""))</f>
         <v/>
       </c>
       <c r="H50" s="21" t="b">
@@ -3177,19 +3174,19 @@
         <v>15</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>340</v>
+        <v>34</v>
       </c>
       <c r="C51" s="28">
         <v>15</v>
       </c>
-      <c r="D51" s="26">
-        <v>1.4</v>
+      <c r="D51" s="26" t="s">
+        <v>210</v>
       </c>
       <c r="E51" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F51" s="26" t="s">
-        <v>345</v>
+        <v>35</v>
       </c>
       <c r="G51" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F51),0)&gt;0), MAX($G$1:G50)+1, ""))</f>
@@ -3205,19 +3202,19 @@
         <v>15</v>
       </c>
       <c r="B52" s="27" t="s">
-        <v>34</v>
+        <v>381</v>
       </c>
       <c r="C52" s="28">
         <v>15</v>
       </c>
-      <c r="D52" s="26" t="s">
-        <v>210</v>
+      <c r="D52" s="26">
+        <v>1.2</v>
       </c>
       <c r="E52" s="27" t="s">
-        <v>8</v>
+        <v>379</v>
       </c>
       <c r="F52" s="26" t="s">
-        <v>35</v>
+        <v>380</v>
       </c>
       <c r="G52" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F52),0)&gt;0), MAX($G$1:G51)+1, ""))</f>
@@ -3233,22 +3230,22 @@
         <v>15</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>381</v>
+        <v>279</v>
       </c>
       <c r="C53" s="28">
         <v>15</v>
       </c>
-      <c r="D53" s="26">
-        <v>1.2</v>
+      <c r="D53" s="26" t="s">
+        <v>209</v>
       </c>
       <c r="E53" s="27" t="s">
-        <v>379</v>
+        <v>266</v>
       </c>
       <c r="F53" s="26" t="s">
-        <v>380</v>
+        <v>33</v>
       </c>
       <c r="G53" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F53),0)&gt;0), MAX($G$1:G52)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F53),0)&gt;0), MAX($G$1:G48)+1, ""))</f>
         <v/>
       </c>
       <c r="H53" s="21" t="b">
@@ -3257,26 +3254,26 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A54" s="26">
-        <v>15</v>
-      </c>
-      <c r="B54" s="27" t="s">
-        <v>279</v>
-      </c>
-      <c r="C54" s="28">
-        <v>15</v>
-      </c>
-      <c r="D54" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="E54" s="27" t="s">
-        <v>266</v>
-      </c>
-      <c r="F54" s="26" t="s">
-        <v>33</v>
+      <c r="A54" s="33">
+        <v>17</v>
+      </c>
+      <c r="B54" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="C54" s="35">
+        <v>17</v>
+      </c>
+      <c r="D54" s="33" t="s">
+        <v>214</v>
+      </c>
+      <c r="E54" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F54" s="33" t="s">
+        <v>71</v>
       </c>
       <c r="G54" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F54),0)&gt;0), MAX($G$1:G49)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F54),0)&gt;0), MAX($G$1:G53)+1, ""))</f>
         <v/>
       </c>
       <c r="H54" s="21" t="b">
@@ -3289,19 +3286,19 @@
         <v>17</v>
       </c>
       <c r="B55" s="34" t="s">
-        <v>70</v>
+        <v>280</v>
       </c>
       <c r="C55" s="35">
         <v>17</v>
       </c>
       <c r="D55" s="33" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E55" s="34" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F55" s="33" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G55" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F55),0)&gt;0), MAX($G$1:G54)+1, ""))</f>
@@ -3313,28 +3310,25 @@
       </c>
     </row>
     <row r="56" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A56" s="33">
+      <c r="A56" s="26">
         <v>17</v>
       </c>
-      <c r="B56" s="34" t="s">
-        <v>280</v>
-      </c>
-      <c r="C56" s="35">
+      <c r="B56" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="C56" s="28">
         <v>17</v>
       </c>
-      <c r="D56" s="33" t="s">
-        <v>222</v>
-      </c>
-      <c r="E56" s="34" t="s">
+      <c r="D56" s="26">
+        <v>1.7</v>
+      </c>
+      <c r="E56" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="F56" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="G56" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E56),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F56),0)&gt;0), MAX($G$1:G55)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="F56" s="26" t="s">
+        <v>318</v>
+      </c>
+      <c r="G56" s="29"/>
       <c r="H56" s="21" t="b">
         <f>A56=C56</f>
         <v>1</v>
@@ -3345,19 +3339,19 @@
         <v>17</v>
       </c>
       <c r="B57" s="27" t="s">
-        <v>312</v>
+        <v>392</v>
       </c>
       <c r="C57" s="28">
         <v>17</v>
       </c>
       <c r="D57" s="26">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="E57" s="27" t="s">
         <v>60</v>
       </c>
       <c r="F57" s="26" t="s">
-        <v>318</v>
+        <v>393</v>
       </c>
       <c r="G57" s="29"/>
       <c r="H57" s="21" t="b">
@@ -3366,25 +3360,28 @@
       </c>
     </row>
     <row r="58" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A58" s="26">
+      <c r="A58" s="33">
         <v>17</v>
       </c>
-      <c r="B58" s="27" t="s">
-        <v>394</v>
-      </c>
-      <c r="C58" s="28">
+      <c r="B58" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C58" s="35">
         <v>17</v>
       </c>
-      <c r="D58" s="26">
-        <v>1.3</v>
-      </c>
-      <c r="E58" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="F58" s="26" t="s">
-        <v>395</v>
-      </c>
-      <c r="G58" s="29"/>
+      <c r="D58" s="33" t="s">
+        <v>215</v>
+      </c>
+      <c r="E58" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="G58" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F58),0)&gt;0), MAX($G$1:G57)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H58" s="21" t="b">
         <f>A58=C58</f>
         <v>1</v>
@@ -3395,19 +3392,19 @@
         <v>17</v>
       </c>
       <c r="B59" s="34" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C59" s="35">
         <v>17</v>
       </c>
       <c r="D59" s="33" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E59" s="34" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F59" s="33" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G59" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F59),0)&gt;0), MAX($G$1:G58)+1, ""))</f>
@@ -3419,28 +3416,25 @@
       </c>
     </row>
     <row r="60" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A60" s="33">
+      <c r="A60" s="26">
         <v>17</v>
       </c>
-      <c r="B60" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="C60" s="35">
+      <c r="B60" s="27" t="s">
+        <v>314</v>
+      </c>
+      <c r="C60" s="28">
         <v>17</v>
       </c>
-      <c r="D60" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="E60" s="34" t="s">
+      <c r="D60" s="26">
+        <v>3</v>
+      </c>
+      <c r="E60" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="F60" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="G60" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F60),0)&gt;0), MAX($G$1:G59)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="F60" s="26" t="s">
+        <v>320</v>
+      </c>
+      <c r="G60" s="29"/>
       <c r="H60" s="21" t="b">
         <f>A60=C60</f>
         <v>1</v>
@@ -3451,21 +3445,24 @@
         <v>17</v>
       </c>
       <c r="B61" s="27" t="s">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="C61" s="28">
         <v>17</v>
       </c>
       <c r="D61" s="26">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="E61" s="27" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="F61" s="26" t="s">
-        <v>320</v>
-      </c>
-      <c r="G61" s="29"/>
+        <v>347</v>
+      </c>
+      <c r="G61" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F61),0)&gt;0), MAX($G$1:G59)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H61" s="21" t="b">
         <f>A61=C61</f>
         <v>1</v>
@@ -3476,72 +3473,72 @@
         <v>17</v>
       </c>
       <c r="B62" s="27" t="s">
-        <v>339</v>
+        <v>315</v>
       </c>
       <c r="C62" s="28">
         <v>17</v>
       </c>
       <c r="D62" s="26">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="E62" s="27" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F62" s="26" t="s">
-        <v>347</v>
-      </c>
-      <c r="G62" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F62),0)&gt;0), MAX($G$1:G60)+1, ""))</f>
-        <v/>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="G62" s="29"/>
       <c r="H62" s="21" t="b">
         <f>A62=C62</f>
         <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A63" s="26">
+      <c r="A63" s="36">
         <v>17</v>
       </c>
-      <c r="B63" s="27" t="s">
-        <v>315</v>
-      </c>
-      <c r="C63" s="28">
+      <c r="B63" s="37" t="s">
+        <v>288</v>
+      </c>
+      <c r="C63" s="38">
         <v>17</v>
       </c>
-      <c r="D63" s="26">
-        <v>1.9</v>
-      </c>
-      <c r="E63" s="27" t="s">
+      <c r="D63" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E63" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="F63" s="26" t="s">
-        <v>321</v>
-      </c>
-      <c r="G63" s="29"/>
+      <c r="F63" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="G63" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F63),0)&gt;0), MAX($G$1:G62)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H63" s="21" t="b">
         <f>A63=C63</f>
         <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A64" s="36">
+      <c r="A64" s="26">
         <v>17</v>
       </c>
-      <c r="B64" s="37" t="s">
-        <v>288</v>
-      </c>
-      <c r="C64" s="38">
+      <c r="B64" s="27" t="s">
+        <v>399</v>
+      </c>
+      <c r="C64" s="28">
         <v>17</v>
       </c>
-      <c r="D64" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="E64" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="F64" s="36" t="s">
-        <v>111</v>
+      <c r="D64" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E64" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F64" s="26" t="s">
+        <v>397</v>
       </c>
       <c r="G64" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F64),0)&gt;0), MAX($G$1:G63)+1, ""))</f>
@@ -3557,24 +3554,21 @@
         <v>17</v>
       </c>
       <c r="B65" s="27" t="s">
-        <v>401</v>
+        <v>313</v>
       </c>
       <c r="C65" s="28">
         <v>17</v>
       </c>
       <c r="D65" s="26">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="E65" s="27" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F65" s="26" t="s">
-        <v>399</v>
-      </c>
-      <c r="G65" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E65),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F65),0)&gt;0), MAX($G$1:G64)+1, ""))</f>
-        <v/>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="G65" s="29"/>
       <c r="H65" s="21" t="b">
         <f>A65=C65</f>
         <v>1</v>
@@ -3585,19 +3579,19 @@
         <v>17</v>
       </c>
       <c r="B66" s="27" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C66" s="28">
         <v>17</v>
       </c>
       <c r="D66" s="26">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="E66" s="27" t="s">
         <v>60</v>
       </c>
       <c r="F66" s="26" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G66" s="29"/>
       <c r="H66" s="21" t="b">
@@ -3606,25 +3600,28 @@
       </c>
     </row>
     <row r="67" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A67" s="26">
+      <c r="A67" s="36">
         <v>17</v>
       </c>
-      <c r="B67" s="27" t="s">
-        <v>316</v>
-      </c>
-      <c r="C67" s="28">
+      <c r="B67" s="37" t="s">
+        <v>106</v>
+      </c>
+      <c r="C67" s="38">
         <v>17</v>
       </c>
-      <c r="D67" s="26">
-        <v>2</v>
-      </c>
-      <c r="E67" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="F67" s="26" t="s">
-        <v>322</v>
-      </c>
-      <c r="G67" s="29"/>
+      <c r="D67" s="36" t="s">
+        <v>220</v>
+      </c>
+      <c r="E67" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F67" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="G67" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F67),0)&gt;0), MAX($G$1:G66)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H67" s="21" t="b">
         <f>A67=C67</f>
         <v>1</v>
@@ -3635,19 +3632,19 @@
         <v>17</v>
       </c>
       <c r="B68" s="37" t="s">
-        <v>106</v>
+        <v>302</v>
       </c>
       <c r="C68" s="38">
         <v>17</v>
       </c>
       <c r="D68" s="36" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="E68" s="37" t="s">
-        <v>8</v>
+        <v>303</v>
       </c>
       <c r="F68" s="36" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G68" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F68),0)&gt;0), MAX($G$1:G67)+1, ""))</f>
@@ -3659,26 +3656,26 @@
       </c>
     </row>
     <row r="69" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A69" s="36">
+      <c r="A69" s="33">
         <v>17</v>
       </c>
-      <c r="B69" s="37" t="s">
-        <v>302</v>
-      </c>
-      <c r="C69" s="38">
+      <c r="B69" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="C69" s="35">
         <v>17</v>
       </c>
-      <c r="D69" s="36" t="s">
-        <v>229</v>
-      </c>
-      <c r="E69" s="37" t="s">
-        <v>303</v>
-      </c>
-      <c r="F69" s="36" t="s">
-        <v>105</v>
+      <c r="D69" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="E69" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F69" s="33" t="s">
+        <v>53</v>
       </c>
       <c r="G69" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F69),0)&gt;0), MAX($G$1:G68)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F69),0)&gt;0), MAX($G$1:G64)+1, ""))</f>
         <v/>
       </c>
       <c r="H69" s="21" t="b">
@@ -3687,26 +3684,26 @@
       </c>
     </row>
     <row r="70" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A70" s="33">
+      <c r="A70" s="26">
         <v>17</v>
       </c>
-      <c r="B70" s="34" t="s">
-        <v>52</v>
-      </c>
-      <c r="C70" s="35">
+      <c r="B70" s="27" t="s">
+        <v>366</v>
+      </c>
+      <c r="C70" s="28">
         <v>17</v>
       </c>
-      <c r="D70" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="E70" s="34" t="s">
+      <c r="D70" s="26">
+        <v>1.8</v>
+      </c>
+      <c r="E70" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F70" s="33" t="s">
-        <v>53</v>
+      <c r="F70" s="26" t="s">
+        <v>352</v>
       </c>
       <c r="G70" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F70),0)&gt;0), MAX($G$1:G65)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F70),0)&gt;0), MAX($G$1:G69)+1, ""))</f>
         <v/>
       </c>
       <c r="H70" s="21" t="b">
@@ -3719,15 +3716,15 @@
         <v>17</v>
       </c>
       <c r="B71" s="27" t="s">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="C71" s="28">
         <v>17</v>
       </c>
       <c r="D71" s="26">
-        <v>1.8</v>
-      </c>
-      <c r="E71" s="27" t="s">
+        <v>1.4</v>
+      </c>
+      <c r="E71" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F71" s="26" t="s">
@@ -3747,19 +3744,19 @@
         <v>17</v>
       </c>
       <c r="B72" s="27" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="C72" s="28">
         <v>17</v>
       </c>
       <c r="D72" s="26">
-        <v>1.4</v>
-      </c>
-      <c r="E72" s="31" t="s">
+        <v>1.2</v>
+      </c>
+      <c r="E72" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F72" s="26" t="s">
-        <v>352</v>
+        <v>378</v>
       </c>
       <c r="G72" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F72),0)&gt;0), MAX($G$1:G71)+1, ""))</f>
@@ -3771,23 +3768,23 @@
       </c>
     </row>
     <row r="73" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A73" s="26">
+      <c r="A73" s="33">
         <v>17</v>
       </c>
-      <c r="B73" s="27" t="s">
-        <v>377</v>
-      </c>
-      <c r="C73" s="28">
+      <c r="B73" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="C73" s="35">
         <v>17</v>
       </c>
-      <c r="D73" s="26">
-        <v>1.2</v>
-      </c>
-      <c r="E73" s="27" t="s">
+      <c r="D73" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="E73" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F73" s="26" t="s">
-        <v>378</v>
+      <c r="F73" s="33" t="s">
+        <v>49</v>
       </c>
       <c r="G73" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F73),0)&gt;0), MAX($G$1:G72)+1, ""))</f>
@@ -3799,23 +3796,23 @@
       </c>
     </row>
     <row r="74" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A74" s="33">
+      <c r="A74" s="36">
         <v>17</v>
       </c>
-      <c r="B74" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="C74" s="35">
+      <c r="B74" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="C74" s="38">
         <v>17</v>
       </c>
-      <c r="D74" s="33" t="s">
-        <v>211</v>
-      </c>
-      <c r="E74" s="34" t="s">
+      <c r="D74" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E74" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F74" s="33" t="s">
-        <v>49</v>
+      <c r="F74" s="36" t="s">
+        <v>98</v>
       </c>
       <c r="G74" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F74),0)&gt;0), MAX($G$1:G73)+1, ""))</f>
@@ -3827,23 +3824,23 @@
       </c>
     </row>
     <row r="75" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A75" s="36">
+      <c r="A75" s="26">
         <v>17</v>
       </c>
-      <c r="B75" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="C75" s="38">
+      <c r="B75" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C75" s="28">
         <v>17</v>
       </c>
-      <c r="D75" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="E75" s="37" t="s">
+      <c r="D75" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="E75" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F75" s="36" t="s">
-        <v>98</v>
+      <c r="F75" s="26" t="s">
+        <v>43</v>
       </c>
       <c r="G75" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F75),0)&gt;0), MAX($G$1:G74)+1, ""))</f>
@@ -3855,23 +3852,23 @@
       </c>
     </row>
     <row r="76" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A76" s="26">
+      <c r="A76" s="36">
         <v>17</v>
       </c>
-      <c r="B76" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="C76" s="28">
+      <c r="B76" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="C76" s="38">
         <v>17</v>
       </c>
-      <c r="D76" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="E76" s="27" t="s">
+      <c r="D76" s="36" t="s">
+        <v>217</v>
+      </c>
+      <c r="E76" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F76" s="26" t="s">
-        <v>43</v>
+      <c r="F76" s="36" t="s">
+        <v>94</v>
       </c>
       <c r="G76" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F76),0)&gt;0), MAX($G$1:G75)+1, ""))</f>
@@ -3883,23 +3880,23 @@
       </c>
     </row>
     <row r="77" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A77" s="36">
+      <c r="A77" s="26">
         <v>17</v>
       </c>
-      <c r="B77" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="C77" s="38">
+      <c r="B77" s="27" t="s">
+        <v>396</v>
+      </c>
+      <c r="C77" s="28">
         <v>17</v>
       </c>
-      <c r="D77" s="36" t="s">
-        <v>217</v>
-      </c>
-      <c r="E77" s="37" t="s">
+      <c r="D77" s="26">
+        <v>2</v>
+      </c>
+      <c r="E77" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F77" s="36" t="s">
-        <v>94</v>
+      <c r="F77" s="26" t="s">
+        <v>395</v>
       </c>
       <c r="G77" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F77),0)&gt;0), MAX($G$1:G76)+1, ""))</f>
@@ -3915,22 +3912,22 @@
         <v>17</v>
       </c>
       <c r="B78" s="27" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="C78" s="28">
         <v>17</v>
       </c>
       <c r="D78" s="26">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E78" s="27" t="s">
-        <v>8</v>
+        <v>244</v>
       </c>
       <c r="F78" s="26" t="s">
-        <v>397</v>
+        <v>202</v>
       </c>
       <c r="G78" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F78),0)&gt;0), MAX($G$1:G77)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F78),0)&gt;0), MAX($G$1:G76)+1, ""))</f>
         <v/>
       </c>
       <c r="H78" s="21" t="b">
@@ -3939,30 +3936,28 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A79" s="26">
+      <c r="A79" s="33">
         <v>17</v>
       </c>
-      <c r="B79" s="27" t="s">
-        <v>407</v>
-      </c>
-      <c r="C79" s="28">
+      <c r="B79" s="34" t="s">
+        <v>326</v>
+      </c>
+      <c r="C79" s="35">
         <v>17</v>
       </c>
-      <c r="D79" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E79" s="27" t="s">
-        <v>244</v>
-      </c>
-      <c r="F79" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="G79" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E79),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F79),0)&gt;0), MAX($G$1:G77)+1, ""))</f>
-        <v/>
+      <c r="D79" s="33">
+        <v>1.9</v>
+      </c>
+      <c r="E79" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="F79" s="33" t="s">
+        <v>328</v>
+      </c>
+      <c r="G79" s="29" t="s">
+        <v>325</v>
       </c>
       <c r="H79" s="21" t="b">
-        <f>A79=C79</f>
         <v>1</v>
       </c>
     </row>
@@ -3971,7 +3966,7 @@
         <v>17</v>
       </c>
       <c r="B80" s="34" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C80" s="35">
         <v>17</v>
@@ -3997,7 +3992,7 @@
         <v>17</v>
       </c>
       <c r="B81" s="34" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C81" s="35">
         <v>17</v>
@@ -4023,45 +4018,47 @@
         <v>17</v>
       </c>
       <c r="B82" s="34" t="s">
-        <v>327</v>
+        <v>36</v>
       </c>
       <c r="C82" s="35">
         <v>17</v>
       </c>
-      <c r="D82" s="33">
-        <v>1.9</v>
+      <c r="D82" s="33" t="s">
+        <v>214</v>
       </c>
       <c r="E82" s="34" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="F82" s="33" t="s">
-        <v>328</v>
-      </c>
-      <c r="G82" s="29" t="s">
-        <v>325</v>
+        <v>37</v>
+      </c>
+      <c r="G82" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F82),0)&gt;0), MAX($G$1:G81)+1, ""))</f>
+        <v/>
       </c>
       <c r="H82" s="21" t="b">
+        <f>A82=C82</f>
         <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A83" s="33">
+      <c r="A83" s="36">
         <v>17</v>
       </c>
-      <c r="B83" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="C83" s="35">
+      <c r="B83" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="C83" s="38">
         <v>17</v>
       </c>
-      <c r="D83" s="33" t="s">
-        <v>214</v>
-      </c>
-      <c r="E83" s="34" t="s">
+      <c r="D83" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E83" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F83" s="33" t="s">
-        <v>37</v>
+      <c r="F83" s="36" t="s">
+        <v>84</v>
       </c>
       <c r="G83" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F83),0)&gt;0), MAX($G$1:G82)+1, ""))</f>
@@ -4073,23 +4070,23 @@
       </c>
     </row>
     <row r="84" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A84" s="36">
+      <c r="A84" s="33">
         <v>17</v>
       </c>
-      <c r="B84" s="37" t="s">
-        <v>83</v>
-      </c>
-      <c r="C84" s="38">
+      <c r="B84" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" s="35">
         <v>17</v>
       </c>
-      <c r="D84" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="E84" s="37" t="s">
+      <c r="D84" s="33" t="s">
+        <v>208</v>
+      </c>
+      <c r="E84" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F84" s="36" t="s">
-        <v>84</v>
+      <c r="F84" s="33" t="s">
+        <v>32</v>
       </c>
       <c r="G84" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E84),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F84),0)&gt;0), MAX($G$1:G83)+1, ""))</f>
@@ -4105,52 +4102,52 @@
         <v>17</v>
       </c>
       <c r="B85" s="34" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C85" s="35">
         <v>17</v>
       </c>
       <c r="D85" s="33" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E85" s="34" t="s">
         <v>8</v>
       </c>
       <c r="F85" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="G85" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E85),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F85),0)&gt;0), MAX($G$1:G84)+1, ""))</f>
-        <v/>
+        <v>30</v>
+      </c>
+      <c r="G85" s="29" t="s">
+        <v>325</v>
       </c>
       <c r="H85" s="21" t="b">
-        <f>A85=C85</f>
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A86" s="33">
-        <v>17</v>
-      </c>
-      <c r="B86" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="C86" s="35">
-        <v>17</v>
-      </c>
-      <c r="D86" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="E86" s="34" t="s">
+      <c r="A86" s="30">
+        <v>20</v>
+      </c>
+      <c r="B86" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="C86" s="32">
+        <v>20</v>
+      </c>
+      <c r="D86" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="E86" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F86" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="G86" s="29" t="s">
-        <v>325</v>
+      <c r="F86" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="G86" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E86),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F86),0)&gt;0), MAX($G$1:G82)+1, ""))</f>
+        <v/>
       </c>
       <c r="H86" s="21" t="b">
+        <f>A86=C86</f>
         <v>1</v>
       </c>
     </row>
@@ -4159,22 +4156,22 @@
         <v>20</v>
       </c>
       <c r="B87" s="31" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C87" s="32">
         <v>20</v>
       </c>
       <c r="D87" s="30" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E87" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F87" s="30" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G87" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F87),0)&gt;0), MAX($G$1:G83)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E87),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F87),0)&gt;0), MAX($G$1:G86)+1, ""))</f>
         <v/>
       </c>
       <c r="H87" s="21" t="b">
@@ -4183,23 +4180,23 @@
       </c>
     </row>
     <row r="88" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A88" s="30">
+      <c r="A88" s="26">
         <v>20</v>
       </c>
-      <c r="B88" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="C88" s="32">
+      <c r="B88" s="27" t="s">
+        <v>382</v>
+      </c>
+      <c r="C88" s="28">
         <v>20</v>
       </c>
-      <c r="D88" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="E88" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F88" s="30" t="s">
-        <v>145</v>
+      <c r="D88" s="26">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E88" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F88" s="26" t="s">
+        <v>383</v>
       </c>
       <c r="G88" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F88),0)&gt;0), MAX($G$1:G87)+1, ""))</f>
@@ -4211,26 +4208,26 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A89" s="26">
+      <c r="A89" s="30">
         <v>20</v>
       </c>
-      <c r="B89" s="27" t="s">
-        <v>382</v>
-      </c>
-      <c r="C89" s="28">
+      <c r="B89" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="C89" s="32">
         <v>20</v>
       </c>
-      <c r="D89" s="26">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="E89" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="F89" s="26" t="s">
-        <v>383</v>
+      <c r="D89" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="E89" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F89" s="30" t="s">
+        <v>143</v>
       </c>
       <c r="G89" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F89),0)&gt;0), MAX($G$1:G88)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E89),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F89),0)&gt;0), MAX($G$1:G87)+1, ""))</f>
         <v/>
       </c>
       <c r="H89" s="21" t="b">
@@ -4243,22 +4240,22 @@
         <v>20</v>
       </c>
       <c r="B90" s="31" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C90" s="32">
         <v>20</v>
       </c>
       <c r="D90" s="30" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E90" s="31" t="s">
-        <v>8</v>
+        <v>304</v>
       </c>
       <c r="F90" s="30" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G90" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F90),0)&gt;0), MAX($G$1:G88)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E90),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F90),0)&gt;0), MAX($G$1:G89)+1, ""))</f>
         <v/>
       </c>
       <c r="H90" s="21" t="b">
@@ -4267,28 +4264,25 @@
       </c>
     </row>
     <row r="91" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A91" s="30">
+      <c r="A91" s="36">
         <v>20</v>
       </c>
-      <c r="B91" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="C91" s="32">
+      <c r="B91" s="37" t="s">
+        <v>332</v>
+      </c>
+      <c r="C91" s="38">
         <v>20</v>
       </c>
-      <c r="D91" s="30" t="s">
-        <v>216</v>
-      </c>
-      <c r="E91" s="31" t="s">
-        <v>304</v>
-      </c>
-      <c r="F91" s="30" t="s">
-        <v>141</v>
-      </c>
-      <c r="G91" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E91),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F91),0)&gt;0), MAX($G$1:G90)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D91" s="36">
+        <v>3.4</v>
+      </c>
+      <c r="E91" s="37" t="s">
+        <v>335</v>
+      </c>
+      <c r="F91" s="36" t="s">
+        <v>333</v>
+      </c>
+      <c r="G91" s="29"/>
       <c r="H91" s="21" t="b">
         <f>A91=C91</f>
         <v>1</v>
@@ -4299,19 +4293,19 @@
         <v>20</v>
       </c>
       <c r="B92" s="37" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C92" s="38">
         <v>20</v>
       </c>
       <c r="D92" s="36">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="E92" s="37" t="s">
         <v>335</v>
       </c>
       <c r="F92" s="36" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G92" s="29"/>
       <c r="H92" s="21" t="b">
@@ -4320,25 +4314,28 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A93" s="36">
+      <c r="A93" s="30">
         <v>20</v>
       </c>
-      <c r="B93" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="C93" s="38">
+      <c r="B93" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="C93" s="32">
         <v>20</v>
       </c>
-      <c r="D93" s="36">
-        <v>3.3</v>
-      </c>
-      <c r="E93" s="37" t="s">
-        <v>335</v>
-      </c>
-      <c r="F93" s="36" t="s">
-        <v>331</v>
-      </c>
-      <c r="G93" s="29"/>
+      <c r="D93" s="30" t="s">
+        <v>223</v>
+      </c>
+      <c r="E93" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F93" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="G93" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E93),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F93),0)&gt;0), MAX($G$1:G92)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H93" s="21" t="b">
         <f>A93=C93</f>
         <v>1</v>
@@ -4349,19 +4346,19 @@
         <v>20</v>
       </c>
       <c r="B94" s="31" t="s">
-        <v>138</v>
+        <v>254</v>
       </c>
       <c r="C94" s="32">
         <v>20</v>
       </c>
       <c r="D94" s="30" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E94" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F94" s="30" t="s">
-        <v>139</v>
+        <v>255</v>
       </c>
       <c r="G94" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E94),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F94),0)&gt;0), MAX($G$1:G93)+1, ""))</f>
@@ -4377,19 +4374,19 @@
         <v>20</v>
       </c>
       <c r="B95" s="31" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C95" s="32">
         <v>20</v>
       </c>
-      <c r="D95" s="30" t="s">
-        <v>225</v>
+      <c r="D95" s="30">
+        <v>4.2</v>
       </c>
       <c r="E95" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F95" s="30" t="s">
-        <v>255</v>
+        <v>304</v>
+      </c>
+      <c r="F95" s="30">
+        <v>21765430</v>
       </c>
       <c r="G95" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E95),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F95),0)&gt;0), MAX($G$1:G94)+1, ""))</f>
@@ -4405,19 +4402,19 @@
         <v>20</v>
       </c>
       <c r="B96" s="31" t="s">
-        <v>253</v>
+        <v>136</v>
       </c>
       <c r="C96" s="32">
         <v>20</v>
       </c>
-      <c r="D96" s="30">
-        <v>4.2</v>
+      <c r="D96" s="30" t="s">
+        <v>210</v>
       </c>
       <c r="E96" s="31" t="s">
-        <v>304</v>
-      </c>
-      <c r="F96" s="30">
-        <v>21765430</v>
+        <v>8</v>
+      </c>
+      <c r="F96" s="30" t="s">
+        <v>137</v>
       </c>
       <c r="G96" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E96),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F96),0)&gt;0), MAX($G$1:G95)+1, ""))</f>
@@ -4433,19 +4430,19 @@
         <v>20</v>
       </c>
       <c r="B97" s="31" t="s">
-        <v>136</v>
+        <v>264</v>
       </c>
       <c r="C97" s="32">
         <v>20</v>
       </c>
       <c r="D97" s="30" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="E97" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F97" s="30" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G97" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E97),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F97),0)&gt;0), MAX($G$1:G96)+1, ""))</f>
@@ -4461,19 +4458,19 @@
         <v>20</v>
       </c>
       <c r="B98" s="31" t="s">
-        <v>264</v>
+        <v>133</v>
       </c>
       <c r="C98" s="32">
         <v>20</v>
       </c>
       <c r="D98" s="30" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E98" s="31" t="s">
-        <v>8</v>
+        <v>304</v>
       </c>
       <c r="F98" s="30" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G98" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E98),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F98),0)&gt;0), MAX($G$1:G97)+1, ""))</f>
@@ -4489,19 +4486,19 @@
         <v>20</v>
       </c>
       <c r="B99" s="31" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C99" s="32">
         <v>20</v>
       </c>
       <c r="D99" s="30" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="E99" s="31" t="s">
-        <v>304</v>
+        <v>131</v>
       </c>
       <c r="F99" s="30" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G99" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E99),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F99),0)&gt;0), MAX($G$1:G98)+1, ""))</f>
@@ -4513,23 +4510,23 @@
       </c>
     </row>
     <row r="100" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A100" s="30">
+      <c r="A100" s="26">
         <v>20</v>
       </c>
-      <c r="B100" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="C100" s="32">
+      <c r="B100" s="27" t="s">
+        <v>311</v>
+      </c>
+      <c r="C100" s="28">
         <v>20</v>
       </c>
-      <c r="D100" s="30" t="s">
-        <v>214</v>
-      </c>
-      <c r="E100" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="F100" s="30" t="s">
-        <v>132</v>
+      <c r="D100" s="26">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E100" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="F100" s="26" t="s">
+        <v>317</v>
       </c>
       <c r="G100" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E100),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F100),0)&gt;0), MAX($G$1:G99)+1, ""))</f>
@@ -4545,19 +4542,19 @@
         <v>20</v>
       </c>
       <c r="B101" s="27" t="s">
-        <v>311</v>
+        <v>385</v>
       </c>
       <c r="C101" s="28">
         <v>20</v>
       </c>
       <c r="D101" s="26">
-        <v>2.2000000000000002</v>
+        <v>2.5</v>
       </c>
       <c r="E101" s="27" t="s">
         <v>60</v>
       </c>
       <c r="F101" s="26" t="s">
-        <v>317</v>
+        <v>384</v>
       </c>
       <c r="G101" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F101),0)&gt;0), MAX($G$1:G100)+1, ""))</f>
@@ -4569,23 +4566,23 @@
       </c>
     </row>
     <row r="102" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A102" s="26">
+      <c r="A102" s="30">
         <v>20</v>
       </c>
-      <c r="B102" s="27" t="s">
-        <v>385</v>
-      </c>
-      <c r="C102" s="28">
+      <c r="B102" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="C102" s="32">
         <v>20</v>
       </c>
-      <c r="D102" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E102" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="F102" s="26" t="s">
-        <v>384</v>
+      <c r="D102" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="E102" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F102" s="30" t="s">
+        <v>129</v>
       </c>
       <c r="G102" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E102),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F102),0)&gt;0), MAX($G$1:G101)+1, ""))</f>
@@ -4601,19 +4598,19 @@
         <v>20</v>
       </c>
       <c r="B103" s="31" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C103" s="32">
         <v>20</v>
       </c>
       <c r="D103" s="30" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="E103" s="31" t="s">
-        <v>8</v>
+        <v>304</v>
       </c>
       <c r="F103" s="30" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G103" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E103),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F103),0)&gt;0), MAX($G$1:G102)+1, ""))</f>
@@ -4625,23 +4622,23 @@
       </c>
     </row>
     <row r="104" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A104" s="30">
+      <c r="A104" s="26">
         <v>20</v>
       </c>
-      <c r="B104" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="C104" s="32">
+      <c r="B104" s="27" t="s">
+        <v>373</v>
+      </c>
+      <c r="C104" s="28">
         <v>20</v>
       </c>
-      <c r="D104" s="30" t="s">
-        <v>234</v>
-      </c>
-      <c r="E104" s="31" t="s">
-        <v>304</v>
-      </c>
-      <c r="F104" s="30" t="s">
-        <v>127</v>
+      <c r="D104" s="26">
+        <v>2.7</v>
+      </c>
+      <c r="E104" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="F104" s="26" t="s">
+        <v>349</v>
       </c>
       <c r="G104" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E104),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F104),0)&gt;0), MAX($G$1:G103)+1, ""))</f>
@@ -4653,23 +4650,23 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A105" s="26">
+      <c r="A105" s="30">
         <v>20</v>
       </c>
-      <c r="B105" s="27" t="s">
-        <v>373</v>
-      </c>
-      <c r="C105" s="28">
+      <c r="B105" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="C105" s="32">
         <v>20</v>
       </c>
-      <c r="D105" s="26">
-        <v>2.7</v>
-      </c>
-      <c r="E105" s="27" t="s">
-        <v>244</v>
-      </c>
-      <c r="F105" s="26" t="s">
-        <v>349</v>
+      <c r="D105" s="30" t="s">
+        <v>230</v>
+      </c>
+      <c r="E105" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F105" s="30" t="s">
+        <v>125</v>
       </c>
       <c r="G105" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E105),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F105),0)&gt;0), MAX($G$1:G104)+1, ""))</f>
@@ -4685,19 +4682,19 @@
         <v>20</v>
       </c>
       <c r="B106" s="31" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C106" s="32">
         <v>20</v>
       </c>
       <c r="D106" s="30" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="E106" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F106" s="30" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G106" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E106),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F106),0)&gt;0), MAX($G$1:G105)+1, ""))</f>
@@ -4713,19 +4710,19 @@
         <v>20</v>
       </c>
       <c r="B107" s="31" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C107" s="32">
         <v>20</v>
       </c>
       <c r="D107" s="30" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="E107" s="31" t="s">
-        <v>8</v>
+        <v>304</v>
       </c>
       <c r="F107" s="30" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G107" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E107),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F107),0)&gt;0), MAX($G$1:G106)+1, ""))</f>
@@ -4737,23 +4734,23 @@
       </c>
     </row>
     <row r="108" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A108" s="30">
+      <c r="A108" s="26">
         <v>20</v>
       </c>
-      <c r="B108" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="C108" s="32">
+      <c r="B108" s="27" t="s">
+        <v>367</v>
+      </c>
+      <c r="C108" s="28">
         <v>20</v>
       </c>
-      <c r="D108" s="30" t="s">
-        <v>223</v>
+      <c r="D108" s="26">
+        <v>1.5</v>
       </c>
       <c r="E108" s="31" t="s">
-        <v>304</v>
-      </c>
-      <c r="F108" s="30" t="s">
-        <v>121</v>
+        <v>298</v>
+      </c>
+      <c r="F108" s="26" t="s">
+        <v>368</v>
       </c>
       <c r="G108" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E108),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F108),0)&gt;0), MAX($G$1:G107)+1, ""))</f>
@@ -4765,23 +4762,23 @@
       </c>
     </row>
     <row r="109" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A109" s="26">
+      <c r="A109" s="30">
         <v>20</v>
       </c>
-      <c r="B109" s="27" t="s">
-        <v>367</v>
-      </c>
-      <c r="C109" s="28">
+      <c r="B109" s="31" t="s">
+        <v>256</v>
+      </c>
+      <c r="C109" s="32">
         <v>20</v>
       </c>
-      <c r="D109" s="26">
-        <v>1.5</v>
+      <c r="D109" s="30" t="s">
+        <v>225</v>
       </c>
       <c r="E109" s="31" t="s">
-        <v>298</v>
-      </c>
-      <c r="F109" s="26" t="s">
-        <v>368</v>
+        <v>8</v>
+      </c>
+      <c r="F109" s="30" t="s">
+        <v>257</v>
       </c>
       <c r="G109" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E109),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F109),0)&gt;0), MAX($G$1:G108)+1, ""))</f>
@@ -4797,19 +4794,19 @@
         <v>20</v>
       </c>
       <c r="B110" s="31" t="s">
-        <v>256</v>
+        <v>118</v>
       </c>
       <c r="C110" s="32">
         <v>20</v>
       </c>
       <c r="D110" s="30" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E110" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F110" s="30" t="s">
-        <v>257</v>
+        <v>119</v>
       </c>
       <c r="G110" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E110),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F110),0)&gt;0), MAX($G$1:G109)+1, ""))</f>
@@ -4825,19 +4822,19 @@
         <v>20</v>
       </c>
       <c r="B111" s="31" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C111" s="32">
         <v>20</v>
       </c>
       <c r="D111" s="30" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="E111" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F111" s="30" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G111" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E111),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F111),0)&gt;0), MAX($G$1:G110)+1, ""))</f>
@@ -4853,19 +4850,19 @@
         <v>20</v>
       </c>
       <c r="B112" s="31" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C112" s="32">
         <v>20</v>
       </c>
       <c r="D112" s="30" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="E112" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F112" s="30" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G112" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E112),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F112),0)&gt;0), MAX($G$1:G111)+1, ""))</f>
@@ -4877,23 +4874,23 @@
       </c>
     </row>
     <row r="113" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A113" s="30">
+      <c r="A113" s="26">
         <v>20</v>
       </c>
-      <c r="B113" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="C113" s="32">
+      <c r="B113" s="27" t="s">
+        <v>296</v>
+      </c>
+      <c r="C113" s="28">
         <v>20</v>
       </c>
-      <c r="D113" s="30" t="s">
-        <v>212</v>
-      </c>
-      <c r="E113" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F113" s="30" t="s">
-        <v>115</v>
+      <c r="D113" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E113" s="27" t="s">
+        <v>298</v>
+      </c>
+      <c r="F113" s="26" t="s">
+        <v>297</v>
       </c>
       <c r="G113" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E113),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F113),0)&gt;0), MAX($G$1:G112)+1, ""))</f>
@@ -4905,23 +4902,23 @@
       </c>
     </row>
     <row r="114" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A114" s="26">
+      <c r="A114" s="30">
         <v>20</v>
       </c>
-      <c r="B114" s="27" t="s">
-        <v>296</v>
-      </c>
-      <c r="C114" s="28">
+      <c r="B114" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="C114" s="32">
         <v>20</v>
       </c>
-      <c r="D114" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E114" s="27" t="s">
-        <v>298</v>
-      </c>
-      <c r="F114" s="26" t="s">
-        <v>297</v>
+      <c r="D114" s="30" t="s">
+        <v>219</v>
+      </c>
+      <c r="E114" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F114" s="30" t="s">
+        <v>113</v>
       </c>
       <c r="G114" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E114),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F114),0)&gt;0), MAX($G$1:G113)+1, ""))</f>
@@ -4937,19 +4934,19 @@
         <v>20</v>
       </c>
       <c r="B115" s="31" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C115" s="32">
         <v>20</v>
       </c>
       <c r="D115" s="30" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E115" s="31" t="s">
-        <v>8</v>
+        <v>298</v>
       </c>
       <c r="F115" s="30" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G115" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E115),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F115),0)&gt;0), MAX($G$1:G114)+1, ""))</f>
@@ -4965,19 +4962,19 @@
         <v>20</v>
       </c>
       <c r="B116" s="31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C116" s="32">
         <v>20</v>
       </c>
       <c r="D116" s="30" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E116" s="31" t="s">
-        <v>298</v>
+        <v>8</v>
       </c>
       <c r="F116" s="30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G116" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E116),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F116),0)&gt;0), MAX($G$1:G115)+1, ""))</f>
@@ -4989,76 +4986,76 @@
       </c>
     </row>
     <row r="117" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A117" s="30">
+      <c r="A117" s="36">
         <v>20</v>
       </c>
-      <c r="B117" s="31" t="s">
-        <v>108</v>
-      </c>
-      <c r="C117" s="32">
+      <c r="B117" s="37" t="s">
+        <v>329</v>
+      </c>
+      <c r="C117" s="38">
         <v>20</v>
       </c>
-      <c r="D117" s="30" t="s">
-        <v>218</v>
-      </c>
-      <c r="E117" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F117" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="G117" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E117),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F117),0)&gt;0), MAX($G$1:G116)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D117" s="36">
+        <v>3</v>
+      </c>
+      <c r="E117" s="37" t="s">
+        <v>303</v>
+      </c>
+      <c r="F117" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="G117" s="29"/>
       <c r="H117" s="21" t="b">
         <f>A117=C117</f>
         <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A118" s="36">
+      <c r="A118" s="26">
         <v>20</v>
       </c>
-      <c r="B118" s="37" t="s">
-        <v>329</v>
-      </c>
-      <c r="C118" s="38">
+      <c r="B118" s="27" t="s">
+        <v>301</v>
+      </c>
+      <c r="C118" s="28">
         <v>20</v>
       </c>
-      <c r="D118" s="36">
-        <v>3</v>
-      </c>
-      <c r="E118" s="37" t="s">
-        <v>303</v>
-      </c>
-      <c r="F118" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="G118" s="29"/>
+      <c r="D118" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E118" s="27" t="s">
+        <v>298</v>
+      </c>
+      <c r="F118" s="26" t="s">
+        <v>300</v>
+      </c>
+      <c r="G118" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E118),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F118),0)&gt;0), MAX($G$1:G117)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H118" s="21" t="b">
         <f>A118=C118</f>
         <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A119" s="26">
+      <c r="A119" s="30">
         <v>20</v>
       </c>
-      <c r="B119" s="27" t="s">
-        <v>301</v>
-      </c>
-      <c r="C119" s="28">
+      <c r="B119" s="31" t="s">
+        <v>364</v>
+      </c>
+      <c r="C119" s="32">
         <v>20</v>
       </c>
-      <c r="D119" s="26">
+      <c r="D119" s="30">
         <v>2.4</v>
       </c>
-      <c r="E119" s="27" t="s">
-        <v>298</v>
-      </c>
-      <c r="F119" s="26" t="s">
-        <v>300</v>
+      <c r="E119" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="F119" s="30" t="s">
+        <v>365</v>
       </c>
       <c r="G119" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E119),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F119),0)&gt;0), MAX($G$1:G118)+1, ""))</f>
@@ -5074,19 +5071,19 @@
         <v>20</v>
       </c>
       <c r="B120" s="31" t="s">
-        <v>364</v>
+        <v>103</v>
       </c>
       <c r="C120" s="32">
         <v>20</v>
       </c>
-      <c r="D120" s="30">
-        <v>2.4</v>
+      <c r="D120" s="30" t="s">
+        <v>214</v>
       </c>
       <c r="E120" s="31" t="s">
         <v>60</v>
       </c>
       <c r="F120" s="30" t="s">
-        <v>365</v>
+        <v>104</v>
       </c>
       <c r="G120" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E120),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F120),0)&gt;0), MAX($G$1:G119)+1, ""))</f>
@@ -5098,23 +5095,23 @@
       </c>
     </row>
     <row r="121" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A121" s="30">
+      <c r="A121" s="26">
         <v>20</v>
       </c>
-      <c r="B121" s="31" t="s">
-        <v>103</v>
-      </c>
-      <c r="C121" s="32">
+      <c r="B121" s="27" t="s">
+        <v>338</v>
+      </c>
+      <c r="C121" s="28">
         <v>20</v>
       </c>
-      <c r="D121" s="30" t="s">
-        <v>214</v>
-      </c>
-      <c r="E121" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="F121" s="30" t="s">
-        <v>104</v>
+      <c r="D121" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E121" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F121" s="26" t="s">
+        <v>342</v>
       </c>
       <c r="G121" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E121),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F121),0)&gt;0), MAX($G$1:G120)+1, ""))</f>
@@ -5126,53 +5123,53 @@
       </c>
     </row>
     <row r="122" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A122" s="26">
+      <c r="A122" s="36">
         <v>20</v>
       </c>
-      <c r="B122" s="27" t="s">
-        <v>338</v>
-      </c>
-      <c r="C122" s="28">
+      <c r="B122" s="37" t="s">
+        <v>334</v>
+      </c>
+      <c r="C122" s="38">
         <v>20</v>
       </c>
-      <c r="D122" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E122" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F122" s="26" t="s">
-        <v>342</v>
-      </c>
-      <c r="G122" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E122),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F122),0)&gt;0), MAX($G$1:G121)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="D122" s="36">
+        <v>3.2</v>
+      </c>
+      <c r="E122" s="37" t="s">
+        <v>335</v>
+      </c>
+      <c r="F122" s="36" t="s">
+        <v>331</v>
+      </c>
+      <c r="G122" s="29"/>
       <c r="H122" s="21" t="b">
         <f>A122=C122</f>
         <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A123" s="36">
+      <c r="A123" s="30">
         <v>20</v>
       </c>
-      <c r="B123" s="37" t="s">
-        <v>334</v>
-      </c>
-      <c r="C123" s="38">
+      <c r="B123" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="C123" s="32">
         <v>20</v>
       </c>
-      <c r="D123" s="36">
-        <v>3.2</v>
-      </c>
-      <c r="E123" s="37" t="s">
-        <v>335</v>
-      </c>
-      <c r="F123" s="36" t="s">
-        <v>331</v>
-      </c>
-      <c r="G123" s="29"/>
+      <c r="D123" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E123" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F123" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="G123" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E123),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F123),0)&gt;0), MAX($G$1:G122)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H123" s="21" t="b">
         <f>A123=C123</f>
         <v>1</v>
@@ -5183,19 +5180,19 @@
         <v>20</v>
       </c>
       <c r="B124" s="31" t="s">
-        <v>101</v>
+        <v>262</v>
       </c>
       <c r="C124" s="32">
         <v>20</v>
       </c>
-      <c r="D124" s="30" t="s">
-        <v>207</v>
+      <c r="D124" s="30">
+        <v>6.2</v>
       </c>
       <c r="E124" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F124" s="30" t="s">
-        <v>102</v>
+        <v>263</v>
       </c>
       <c r="G124" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E124),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F124),0)&gt;0), MAX($G$1:G123)+1, ""))</f>
@@ -5211,19 +5208,19 @@
         <v>20</v>
       </c>
       <c r="B125" s="31" t="s">
-        <v>262</v>
+        <v>99</v>
       </c>
       <c r="C125" s="32">
         <v>20</v>
       </c>
-      <c r="D125" s="30">
-        <v>6.2</v>
+      <c r="D125" s="30" t="s">
+        <v>215</v>
       </c>
       <c r="E125" s="31" t="s">
-        <v>8</v>
+        <v>298</v>
       </c>
       <c r="F125" s="30" t="s">
-        <v>263</v>
+        <v>100</v>
       </c>
       <c r="G125" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E125),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F125),0)&gt;0), MAX($G$1:G124)+1, ""))</f>
@@ -5235,23 +5232,23 @@
       </c>
     </row>
     <row r="126" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A126" s="30">
+      <c r="A126" s="26">
         <v>20</v>
       </c>
-      <c r="B126" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="C126" s="32">
+      <c r="B126" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="C126" s="28">
         <v>20</v>
       </c>
-      <c r="D126" s="30" t="s">
-        <v>215</v>
-      </c>
-      <c r="E126" s="31" t="s">
+      <c r="D126" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E126" s="27" t="s">
         <v>298</v>
       </c>
-      <c r="F126" s="30" t="s">
-        <v>100</v>
+      <c r="F126" s="26" t="s">
+        <v>300</v>
       </c>
       <c r="G126" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E126),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F126),0)&gt;0), MAX($G$1:G125)+1, ""))</f>
@@ -5263,23 +5260,23 @@
       </c>
     </row>
     <row r="127" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A127" s="26">
+      <c r="A127" s="30">
         <v>20</v>
       </c>
-      <c r="B127" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="C127" s="28">
+      <c r="B127" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="C127" s="32">
         <v>20</v>
       </c>
-      <c r="D127" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E127" s="27" t="s">
-        <v>298</v>
-      </c>
-      <c r="F127" s="26" t="s">
-        <v>300</v>
+      <c r="D127" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="E127" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F127" s="30" t="s">
+        <v>96</v>
       </c>
       <c r="G127" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E127),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F127),0)&gt;0), MAX($G$1:G126)+1, ""))</f>
@@ -5291,31 +5288,31 @@
       </c>
     </row>
     <row r="128" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A128" s="30">
+      <c r="A128" s="26">
         <v>20</v>
       </c>
-      <c r="B128" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="C128" s="32">
-        <v>20</v>
-      </c>
-      <c r="D128" s="30" t="s">
-        <v>216</v>
-      </c>
-      <c r="E128" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F128" s="30" t="s">
-        <v>96</v>
+      <c r="B128" s="27" t="s">
+        <v>309</v>
+      </c>
+      <c r="C128" s="28">
+        <v>23</v>
+      </c>
+      <c r="D128" s="26">
+        <v>3.9</v>
+      </c>
+      <c r="E128" s="27" t="s">
+        <v>308</v>
+      </c>
+      <c r="F128" s="26" t="s">
+        <v>310</v>
       </c>
       <c r="G128" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F128),0)&gt;0), MAX($G$1:G127)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E128),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F128),0)&gt;0), MAX($G$1:G126)+1, ""))</f>
         <v/>
       </c>
       <c r="H128" s="21" t="b">
         <f>A128=C128</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
@@ -5323,47 +5320,47 @@
         <v>20</v>
       </c>
       <c r="B129" s="27" t="s">
-        <v>309</v>
+        <v>353</v>
       </c>
       <c r="C129" s="28">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D129" s="26">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="E129" s="27" t="s">
-        <v>308</v>
+        <v>81</v>
       </c>
       <c r="F129" s="26" t="s">
-        <v>310</v>
+        <v>354</v>
       </c>
       <c r="G129" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F129),0)&gt;0), MAX($G$1:G127)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E129),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F129),0)&gt;0), MAX($G$1:G128)+1, ""))</f>
         <v/>
       </c>
       <c r="H129" s="21" t="b">
         <f>A129=C129</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A130" s="26">
+      <c r="A130" s="30">
         <v>20</v>
       </c>
-      <c r="B130" s="27" t="s">
-        <v>353</v>
-      </c>
-      <c r="C130" s="28">
+      <c r="B130" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="C130" s="32">
         <v>20</v>
       </c>
-      <c r="D130" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="E130" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F130" s="26" t="s">
-        <v>354</v>
+      <c r="D130" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="E130" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F130" s="30" t="s">
+        <v>92</v>
       </c>
       <c r="G130" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E130),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F130),0)&gt;0), MAX($G$1:G129)+1, ""))</f>
@@ -5379,19 +5376,19 @@
         <v>20</v>
       </c>
       <c r="B131" s="31" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C131" s="32">
         <v>20</v>
       </c>
       <c r="D131" s="30" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="E131" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F131" s="30" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G131" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E131),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F131),0)&gt;0), MAX($G$1:G130)+1, ""))</f>
@@ -5407,16 +5404,16 @@
         <v>20</v>
       </c>
       <c r="B132" s="31" t="s">
-        <v>89</v>
+        <v>289</v>
       </c>
       <c r="C132" s="32">
         <v>20</v>
       </c>
-      <c r="D132" s="30" t="s">
-        <v>223</v>
+      <c r="D132" s="30">
+        <v>1.8</v>
       </c>
       <c r="E132" s="31" t="s">
-        <v>8</v>
+        <v>290</v>
       </c>
       <c r="F132" s="30" t="s">
         <v>90</v>
@@ -5435,19 +5432,19 @@
         <v>20</v>
       </c>
       <c r="B133" s="31" t="s">
-        <v>289</v>
+        <v>87</v>
       </c>
       <c r="C133" s="32">
         <v>20</v>
       </c>
-      <c r="D133" s="30">
-        <v>1.8</v>
+      <c r="D133" s="30" t="s">
+        <v>222</v>
       </c>
       <c r="E133" s="31" t="s">
-        <v>290</v>
+        <v>8</v>
       </c>
       <c r="F133" s="30" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G133" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E133),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F133),0)&gt;0), MAX($G$1:G132)+1, ""))</f>
@@ -5463,19 +5460,19 @@
         <v>20</v>
       </c>
       <c r="B134" s="31" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C134" s="32">
         <v>20</v>
       </c>
       <c r="D134" s="30" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E134" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F134" s="30" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G134" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E134),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F134),0)&gt;0), MAX($G$1:G133)+1, ""))</f>
@@ -5491,19 +5488,19 @@
         <v>20</v>
       </c>
       <c r="B135" s="31" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C135" s="32">
         <v>20</v>
       </c>
       <c r="D135" s="30" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E135" s="31" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="F135" s="30" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G135" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E135),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F135),0)&gt;0), MAX($G$1:G134)+1, ""))</f>
@@ -5519,19 +5516,19 @@
         <v>20</v>
       </c>
       <c r="B136" s="31" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C136" s="32">
         <v>20</v>
       </c>
       <c r="D136" s="30" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E136" s="31" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F136" s="30" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G136" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E136),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F136),0)&gt;0), MAX($G$1:G135)+1, ""))</f>
@@ -5547,19 +5544,19 @@
         <v>20</v>
       </c>
       <c r="B137" s="31" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C137" s="32">
         <v>20</v>
       </c>
       <c r="D137" s="30" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E137" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F137" s="30" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G137" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E137),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F137),0)&gt;0), MAX($G$1:G136)+1, ""))</f>
@@ -5571,23 +5568,23 @@
       </c>
     </row>
     <row r="138" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A138" s="30">
-        <v>20</v>
-      </c>
-      <c r="B138" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="C138" s="32">
-        <v>20</v>
-      </c>
-      <c r="D138" s="30" t="s">
-        <v>216</v>
-      </c>
-      <c r="E138" s="31" t="s">
+      <c r="A138" s="26">
+        <v>25</v>
+      </c>
+      <c r="B138" s="27" t="s">
+        <v>178</v>
+      </c>
+      <c r="C138" s="28">
+        <v>25</v>
+      </c>
+      <c r="D138" s="26" t="s">
+        <v>225</v>
+      </c>
+      <c r="E138" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F138" s="30" t="s">
-        <v>77</v>
+      <c r="F138" s="26" t="s">
+        <v>179</v>
       </c>
       <c r="G138" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E138),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F138),0)&gt;0), MAX($G$1:G137)+1, ""))</f>
@@ -5603,19 +5600,19 @@
         <v>25</v>
       </c>
       <c r="B139" s="27" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C139" s="28">
         <v>25</v>
       </c>
       <c r="D139" s="26" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="E139" s="27" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F139" s="26" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G139" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E139),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F139),0)&gt;0), MAX($G$1:G138)+1, ""))</f>
@@ -5631,19 +5628,19 @@
         <v>25</v>
       </c>
       <c r="B140" s="27" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C140" s="28">
         <v>25</v>
       </c>
       <c r="D140" s="26" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="E140" s="27" t="s">
         <v>131</v>
       </c>
       <c r="F140" s="26" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G140" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E140),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F140),0)&gt;0), MAX($G$1:G139)+1, ""))</f>
@@ -5659,19 +5656,19 @@
         <v>25</v>
       </c>
       <c r="B141" s="27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C141" s="28">
         <v>25</v>
       </c>
       <c r="D141" s="26" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="E141" s="27" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="F141" s="26" t="s">
-        <v>175</v>
+        <v>323</v>
       </c>
       <c r="G141" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E141),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F141),0)&gt;0), MAX($G$1:G140)+1, ""))</f>
@@ -5687,19 +5684,19 @@
         <v>25</v>
       </c>
       <c r="B142" s="27" t="s">
-        <v>173</v>
+        <v>357</v>
       </c>
       <c r="C142" s="28">
         <v>25</v>
       </c>
-      <c r="D142" s="26" t="s">
-        <v>224</v>
+      <c r="D142" s="26">
+        <v>3</v>
       </c>
       <c r="E142" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F142" s="26" t="s">
-        <v>323</v>
+        <v>358</v>
       </c>
       <c r="G142" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E142),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F142),0)&gt;0), MAX($G$1:G141)+1, ""))</f>
@@ -5715,19 +5712,19 @@
         <v>25</v>
       </c>
       <c r="B143" s="27" t="s">
-        <v>357</v>
+        <v>172</v>
       </c>
       <c r="C143" s="28">
         <v>25</v>
       </c>
       <c r="D143" s="26">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="E143" s="27" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="F143" s="26" t="s">
-        <v>358</v>
+        <v>337</v>
       </c>
       <c r="G143" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E143),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F143),0)&gt;0), MAX($G$1:G142)+1, ""))</f>
@@ -5739,23 +5736,23 @@
       </c>
     </row>
     <row r="144" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A144" s="26">
+      <c r="A144" s="30">
         <v>25</v>
       </c>
-      <c r="B144" s="27" t="s">
-        <v>172</v>
-      </c>
-      <c r="C144" s="28">
+      <c r="B144" s="31" t="s">
+        <v>283</v>
+      </c>
+      <c r="C144" s="32">
         <v>25</v>
       </c>
-      <c r="D144" s="26">
-        <v>2.7</v>
-      </c>
-      <c r="E144" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F144" s="26" t="s">
-        <v>337</v>
+      <c r="D144" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E144" s="31" t="s">
+        <v>282</v>
+      </c>
+      <c r="F144" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G144" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E144),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F144),0)&gt;0), MAX($G$1:G143)+1, ""))</f>
@@ -5771,7 +5768,7 @@
         <v>25</v>
       </c>
       <c r="B145" s="31" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C145" s="32">
         <v>25</v>
@@ -5795,23 +5792,23 @@
       </c>
     </row>
     <row r="146" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A146" s="30">
+      <c r="A146" s="26">
         <v>25</v>
       </c>
-      <c r="B146" s="31" t="s">
-        <v>281</v>
-      </c>
-      <c r="C146" s="32">
+      <c r="B146" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="C146" s="28">
         <v>25</v>
       </c>
-      <c r="D146" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E146" s="31" t="s">
-        <v>282</v>
-      </c>
-      <c r="F146" s="30" t="s">
-        <v>102</v>
+      <c r="D146" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="E146" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="F146" s="26" t="s">
+        <v>171</v>
       </c>
       <c r="G146" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E146),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F146),0)&gt;0), MAX($G$1:G145)+1, ""))</f>
@@ -5827,19 +5824,19 @@
         <v>25</v>
       </c>
       <c r="B147" s="27" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C147" s="28">
         <v>25</v>
       </c>
       <c r="D147" s="26" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="E147" s="27" t="s">
-        <v>244</v>
+        <v>8</v>
       </c>
       <c r="F147" s="26" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G147" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E147),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F147),0)&gt;0), MAX($G$1:G146)+1, ""))</f>
@@ -5855,19 +5852,19 @@
         <v>25</v>
       </c>
       <c r="B148" s="27" t="s">
-        <v>168</v>
+        <v>355</v>
       </c>
       <c r="C148" s="28">
         <v>25</v>
       </c>
-      <c r="D148" s="26" t="s">
-        <v>217</v>
+      <c r="D148" s="26">
+        <v>3.4</v>
       </c>
       <c r="E148" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F148" s="26" t="s">
-        <v>169</v>
+        <v>356</v>
       </c>
       <c r="G148" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E148),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F148),0)&gt;0), MAX($G$1:G147)+1, ""))</f>
@@ -5879,23 +5876,23 @@
       </c>
     </row>
     <row r="149" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A149" s="26">
+      <c r="A149" s="30">
         <v>25</v>
       </c>
-      <c r="B149" s="27" t="s">
-        <v>355</v>
-      </c>
-      <c r="C149" s="28">
+      <c r="B149" s="31" t="s">
+        <v>277</v>
+      </c>
+      <c r="C149" s="32">
         <v>25</v>
       </c>
-      <c r="D149" s="26">
-        <v>3.4</v>
-      </c>
-      <c r="E149" s="27" t="s">
+      <c r="D149" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E149" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="F149" s="26" t="s">
-        <v>356</v>
+      <c r="F149" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G149" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B149),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E149),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F149),0)&gt;0), MAX($G$1:G148)+1, ""))</f>
@@ -5907,23 +5904,23 @@
       </c>
     </row>
     <row r="150" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A150" s="30">
+      <c r="A150" s="26">
         <v>25</v>
       </c>
-      <c r="B150" s="31" t="s">
-        <v>277</v>
-      </c>
-      <c r="C150" s="32">
+      <c r="B150" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="C150" s="28">
         <v>25</v>
       </c>
-      <c r="D150" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E150" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F150" s="30" t="s">
-        <v>102</v>
+      <c r="D150" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="E150" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="F150" s="26" t="s">
+        <v>167</v>
       </c>
       <c r="G150" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B150),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E150),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F150),0)&gt;0), MAX($G$1:G149)+1, ""))</f>
@@ -5939,19 +5936,19 @@
         <v>25</v>
       </c>
       <c r="B151" s="27" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C151" s="28">
         <v>25</v>
       </c>
       <c r="D151" s="26" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="E151" s="27" t="s">
         <v>131</v>
       </c>
       <c r="F151" s="26" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G151" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B151),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E151),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F151),0)&gt;0), MAX($G$1:G150)+1, ""))</f>
@@ -5967,19 +5964,19 @@
         <v>25</v>
       </c>
       <c r="B152" s="27" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C152" s="28">
         <v>25</v>
       </c>
       <c r="D152" s="26" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E152" s="27" t="s">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="F152" s="26" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G152" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B152),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E152),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F152),0)&gt;0), MAX($G$1:G151)+1, ""))</f>
@@ -5995,19 +5992,19 @@
         <v>25</v>
       </c>
       <c r="B153" s="27" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C153" s="28">
         <v>25</v>
       </c>
       <c r="D153" s="26" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="E153" s="27" t="s">
         <v>81</v>
       </c>
       <c r="F153" s="26" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G153" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B153),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E153),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F153),0)&gt;0), MAX($G$1:G152)+1, ""))</f>
@@ -6023,19 +6020,19 @@
         <v>25</v>
       </c>
       <c r="B154" s="27" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C154" s="28">
         <v>25</v>
       </c>
       <c r="D154" s="26" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="E154" s="27" t="s">
         <v>81</v>
       </c>
       <c r="F154" s="26" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G154" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B154),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E154),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F154),0)&gt;0), MAX($G$1:G153)+1, ""))</f>
@@ -6051,19 +6048,19 @@
         <v>25</v>
       </c>
       <c r="B155" s="27" t="s">
-        <v>158</v>
+        <v>389</v>
       </c>
       <c r="C155" s="28">
         <v>25</v>
       </c>
-      <c r="D155" s="26" t="s">
-        <v>228</v>
+      <c r="D155" s="26">
+        <v>3.4</v>
       </c>
       <c r="E155" s="27" t="s">
         <v>81</v>
       </c>
       <c r="F155" s="26" t="s">
-        <v>159</v>
+        <v>341</v>
       </c>
       <c r="G155" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E155),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F155),0)&gt;0), MAX($G$1:G154)+1, ""))</f>
@@ -6079,22 +6076,22 @@
         <v>25</v>
       </c>
       <c r="B156" s="27" t="s">
-        <v>391</v>
+        <v>156</v>
       </c>
       <c r="C156" s="28">
         <v>25</v>
       </c>
-      <c r="D156" s="26">
-        <v>3.4</v>
+      <c r="D156" s="26" t="s">
+        <v>227</v>
       </c>
       <c r="E156" s="27" t="s">
         <v>81</v>
       </c>
       <c r="F156" s="26" t="s">
-        <v>341</v>
+        <v>157</v>
       </c>
       <c r="G156" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B156),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E156),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F156),0)&gt;0), MAX($G$1:G155)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B156),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E156),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F156),0)&gt;0), MAX($G$1:G154)+1, ""))</f>
         <v/>
       </c>
       <c r="H156" s="21" t="b">
@@ -6107,22 +6104,22 @@
         <v>25</v>
       </c>
       <c r="B157" s="27" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C157" s="28">
         <v>25</v>
       </c>
       <c r="D157" s="26" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E157" s="27" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="F157" s="26" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G157" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F157),0)&gt;0), MAX($G$1:G155)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E157),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F157),0)&gt;0), MAX($G$1:G156)+1, ""))</f>
         <v/>
       </c>
       <c r="H157" s="21" t="b">
@@ -6135,19 +6132,19 @@
         <v>25</v>
       </c>
       <c r="B158" s="27" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C158" s="28">
         <v>25</v>
       </c>
       <c r="D158" s="26" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="E158" s="27" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F158" s="26" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G158" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B158),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E158),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F158),0)&gt;0), MAX($G$1:G157)+1, ""))</f>
@@ -6163,19 +6160,19 @@
         <v>25</v>
       </c>
       <c r="B159" s="27" t="s">
-        <v>152</v>
+        <v>246</v>
       </c>
       <c r="C159" s="28">
         <v>25</v>
       </c>
-      <c r="D159" s="26" t="s">
-        <v>230</v>
+      <c r="D159" s="39" t="s">
+        <v>229</v>
       </c>
       <c r="E159" s="27" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="F159" s="26" t="s">
-        <v>153</v>
+        <v>247</v>
       </c>
       <c r="G159" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E159),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F159),0)&gt;0), MAX($G$1:G158)+1, ""))</f>
@@ -6191,19 +6188,19 @@
         <v>25</v>
       </c>
       <c r="B160" s="27" t="s">
-        <v>246</v>
+        <v>150</v>
       </c>
       <c r="C160" s="28">
         <v>25</v>
       </c>
-      <c r="D160" s="39" t="s">
-        <v>229</v>
+      <c r="D160" s="26" t="s">
+        <v>235</v>
       </c>
       <c r="E160" s="27" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F160" s="26" t="s">
-        <v>247</v>
+        <v>151</v>
       </c>
       <c r="G160" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B160),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E160),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F160),0)&gt;0), MAX($G$1:G159)+1, ""))</f>
@@ -6215,23 +6212,23 @@
       </c>
     </row>
     <row r="161" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A161" s="26">
+      <c r="A161" s="30">
         <v>25</v>
       </c>
-      <c r="B161" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="C161" s="28">
+      <c r="B161" s="31" t="s">
+        <v>287</v>
+      </c>
+      <c r="C161" s="32">
         <v>25</v>
       </c>
-      <c r="D161" s="26" t="s">
-        <v>235</v>
-      </c>
-      <c r="E161" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="F161" s="26" t="s">
-        <v>151</v>
+      <c r="D161" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E161" s="31" t="s">
+        <v>282</v>
+      </c>
+      <c r="F161" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G161" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B161),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E161),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F161),0)&gt;0), MAX($G$1:G160)+1, ""))</f>
@@ -6247,7 +6244,7 @@
         <v>25</v>
       </c>
       <c r="B162" s="31" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C162" s="32">
         <v>25</v>
@@ -6275,7 +6272,7 @@
         <v>25</v>
       </c>
       <c r="B163" s="31" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C163" s="32">
         <v>25</v>
@@ -6299,23 +6296,23 @@
       </c>
     </row>
     <row r="164" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A164" s="30">
+      <c r="A164" s="26">
         <v>25</v>
       </c>
-      <c r="B164" s="31" t="s">
-        <v>286</v>
-      </c>
-      <c r="C164" s="32">
+      <c r="B164" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="C164" s="28">
         <v>25</v>
       </c>
-      <c r="D164" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E164" s="31" t="s">
-        <v>282</v>
-      </c>
-      <c r="F164" s="30" t="s">
-        <v>102</v>
+      <c r="D164" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E164" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="F164" s="26" t="s">
+        <v>252</v>
       </c>
       <c r="G164" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B164),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E164),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F164),0)&gt;0), MAX($G$1:G163)+1, ""))</f>
@@ -6327,23 +6324,23 @@
       </c>
     </row>
     <row r="165" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A165" s="26">
+      <c r="A165" s="30">
         <v>25</v>
       </c>
-      <c r="B165" s="27" t="s">
-        <v>251</v>
-      </c>
-      <c r="C165" s="28">
+      <c r="B165" s="31" t="s">
+        <v>284</v>
+      </c>
+      <c r="C165" s="32">
         <v>25</v>
       </c>
-      <c r="D165" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E165" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="F165" s="26" t="s">
-        <v>252</v>
+      <c r="D165" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="E165" s="31" t="s">
+        <v>282</v>
+      </c>
+      <c r="F165" s="30" t="s">
+        <v>102</v>
       </c>
       <c r="G165" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B165),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E165),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F165),0)&gt;0), MAX($G$1:G164)+1, ""))</f>
@@ -6355,26 +6352,26 @@
       </c>
     </row>
     <row r="166" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A166" s="30">
+      <c r="A166" s="26">
         <v>25</v>
       </c>
-      <c r="B166" s="31" t="s">
-        <v>284</v>
-      </c>
-      <c r="C166" s="32">
+      <c r="B166" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="C166" s="28">
         <v>25</v>
       </c>
-      <c r="D166" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="E166" s="31" t="s">
-        <v>282</v>
-      </c>
-      <c r="F166" s="30" t="s">
-        <v>102</v>
+      <c r="D166" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="E166" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F166" s="26" t="s">
+        <v>149</v>
       </c>
       <c r="G166" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B166),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E166),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F166),0)&gt;0), MAX($G$1:G165)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B166),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E166),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F166),0)&gt;0), MAX($G$1:G164)+1, ""))</f>
         <v/>
       </c>
       <c r="H166" s="21" t="b">
@@ -6383,26 +6380,26 @@
       </c>
     </row>
     <row r="167" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A167" s="26">
-        <v>25</v>
-      </c>
-      <c r="B167" s="27" t="s">
-        <v>148</v>
-      </c>
-      <c r="C167" s="28">
-        <v>25</v>
-      </c>
-      <c r="D167" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="E167" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F167" s="26" t="s">
-        <v>149</v>
+      <c r="A167" s="30">
+        <v>30</v>
+      </c>
+      <c r="B167" s="31" t="s">
+        <v>192</v>
+      </c>
+      <c r="C167" s="32">
+        <v>30</v>
+      </c>
+      <c r="D167" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="E167" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="F167" s="30" t="s">
+        <v>193</v>
       </c>
       <c r="G167" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B167),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E167),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F167),0)&gt;0), MAX($G$1:G165)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B167),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E167),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F167),0)&gt;0), MAX($G$1:G166)+1, ""))</f>
         <v/>
       </c>
       <c r="H167" s="21" t="b">
@@ -6415,19 +6412,19 @@
         <v>30</v>
       </c>
       <c r="B168" s="31" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C168" s="32">
         <v>30</v>
       </c>
       <c r="D168" s="30" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="E168" s="31" t="s">
         <v>131</v>
       </c>
       <c r="F168" s="30" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G168" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B168),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E168),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F168),0)&gt;0), MAX($G$1:G167)+1, ""))</f>
@@ -6443,13 +6440,13 @@
         <v>30</v>
       </c>
       <c r="B169" s="31" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C169" s="32">
         <v>30</v>
       </c>
       <c r="D169" s="30" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E169" s="31" t="s">
         <v>131</v>
@@ -6471,19 +6468,19 @@
         <v>30</v>
       </c>
       <c r="B170" s="31" t="s">
-        <v>189</v>
+        <v>245</v>
       </c>
       <c r="C170" s="32">
         <v>30</v>
       </c>
       <c r="D170" s="30" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="E170" s="31" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="F170" s="30" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G170" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B170),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E170),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F170),0)&gt;0), MAX($G$1:G169)+1, ""))</f>
@@ -6499,22 +6496,22 @@
         <v>30</v>
       </c>
       <c r="B171" s="31" t="s">
-        <v>245</v>
+        <v>402</v>
       </c>
       <c r="C171" s="32">
         <v>30</v>
       </c>
-      <c r="D171" s="30" t="s">
-        <v>217</v>
+      <c r="D171" s="30">
+        <v>6.2</v>
       </c>
       <c r="E171" s="31" t="s">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="F171" s="30" t="s">
-        <v>188</v>
+        <v>403</v>
       </c>
       <c r="G171" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B171),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E171),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F171),0)&gt;0), MAX($G$1:G170)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B171),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E171),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F171),0)&gt;0), MAX($G$1:G169)+1, ""))</f>
         <v/>
       </c>
       <c r="H171" s="21" t="b">
@@ -6523,26 +6520,26 @@
       </c>
     </row>
     <row r="172" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A172" s="30">
+      <c r="A172" s="26">
         <v>30</v>
       </c>
-      <c r="B172" s="31" t="s">
-        <v>404</v>
-      </c>
-      <c r="C172" s="32">
+      <c r="B172" s="27" t="s">
+        <v>390</v>
+      </c>
+      <c r="C172" s="28">
         <v>30</v>
       </c>
-      <c r="D172" s="30">
-        <v>6.2</v>
-      </c>
-      <c r="E172" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="F172" s="30" t="s">
-        <v>405</v>
+      <c r="D172" s="26">
+        <v>3.6</v>
+      </c>
+      <c r="E172" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F172" s="26" t="s">
+        <v>391</v>
       </c>
       <c r="G172" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B172),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E172),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F172),0)&gt;0), MAX($G$1:G170)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B172),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E172),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F172),0)&gt;0), MAX($G$1:G171)+1, ""))</f>
         <v/>
       </c>
       <c r="H172" s="21" t="b">
@@ -6551,23 +6548,23 @@
       </c>
     </row>
     <row r="173" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A173" s="26">
+      <c r="A173" s="30">
         <v>30</v>
       </c>
-      <c r="B173" s="27" t="s">
-        <v>392</v>
-      </c>
-      <c r="C173" s="28">
+      <c r="B173" s="31" t="s">
+        <v>186</v>
+      </c>
+      <c r="C173" s="32">
         <v>30</v>
       </c>
-      <c r="D173" s="26">
-        <v>3.6</v>
-      </c>
-      <c r="E173" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="F173" s="26" t="s">
-        <v>393</v>
+      <c r="D173" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="E173" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F173" s="30" t="s">
+        <v>187</v>
       </c>
       <c r="G173" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B173),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E173),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F173),0)&gt;0), MAX($G$1:G172)+1, ""))</f>
@@ -6583,19 +6580,19 @@
         <v>30</v>
       </c>
       <c r="B174" s="31" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C174" s="32">
         <v>30</v>
       </c>
       <c r="D174" s="30" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E174" s="31" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="F174" s="30" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G174" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B174),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E174),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F174),0)&gt;0), MAX($G$1:G173)+1, ""))</f>
@@ -6607,23 +6604,23 @@
       </c>
     </row>
     <row r="175" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A175" s="30">
+      <c r="A175" s="26">
         <v>30</v>
       </c>
-      <c r="B175" s="31" t="s">
-        <v>184</v>
-      </c>
-      <c r="C175" s="32">
+      <c r="B175" s="27" t="s">
+        <v>375</v>
+      </c>
+      <c r="C175" s="28">
         <v>30</v>
       </c>
-      <c r="D175" s="30" t="s">
-        <v>228</v>
-      </c>
-      <c r="E175" s="31" t="s">
-        <v>81</v>
-      </c>
-      <c r="F175" s="30" t="s">
-        <v>185</v>
+      <c r="D175" s="26">
+        <v>5</v>
+      </c>
+      <c r="E175" s="27" t="s">
+        <v>376</v>
+      </c>
+      <c r="F175" s="26" t="s">
+        <v>25</v>
       </c>
       <c r="G175" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B175),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E175),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F175),0)&gt;0), MAX($G$1:G174)+1, ""))</f>
@@ -6635,26 +6632,26 @@
       </c>
     </row>
     <row r="176" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A176" s="26">
+      <c r="A176" s="30">
         <v>30</v>
       </c>
-      <c r="B176" s="27" t="s">
-        <v>375</v>
-      </c>
-      <c r="C176" s="28">
+      <c r="B176" s="31" t="s">
+        <v>400</v>
+      </c>
+      <c r="C176" s="32">
         <v>30</v>
       </c>
-      <c r="D176" s="26">
-        <v>5</v>
-      </c>
-      <c r="E176" s="27" t="s">
-        <v>376</v>
-      </c>
-      <c r="F176" s="26" t="s">
-        <v>25</v>
+      <c r="D176" s="30">
+        <v>5.5</v>
+      </c>
+      <c r="E176" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="F176" s="30" t="s">
+        <v>401</v>
       </c>
       <c r="G176" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B176),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E176),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F176),0)&gt;0), MAX($G$1:G175)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B176),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E176),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F176),0)&gt;0), MAX($G$1:G174)+1, ""))</f>
         <v/>
       </c>
       <c r="H176" s="21" t="b">
@@ -6667,22 +6664,22 @@
         <v>30</v>
       </c>
       <c r="B177" s="31" t="s">
-        <v>402</v>
+        <v>182</v>
       </c>
       <c r="C177" s="32">
         <v>30</v>
       </c>
-      <c r="D177" s="30">
-        <v>5.5</v>
+      <c r="D177" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="E177" s="31" t="s">
         <v>131</v>
       </c>
       <c r="F177" s="30" t="s">
-        <v>403</v>
+        <v>183</v>
       </c>
       <c r="G177" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B177),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E177),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F177),0)&gt;0), MAX($G$1:G175)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B177),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E177),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F177),0)&gt;0), MAX($G$1:G176)+1, ""))</f>
         <v/>
       </c>
       <c r="H177" s="21" t="b">
@@ -6695,19 +6692,19 @@
         <v>30</v>
       </c>
       <c r="B178" s="31" t="s">
-        <v>182</v>
+        <v>336</v>
       </c>
       <c r="C178" s="32">
         <v>30</v>
       </c>
-      <c r="D178" s="30" t="s">
-        <v>239</v>
+      <c r="D178" s="30">
+        <v>2.9</v>
       </c>
       <c r="E178" s="31" t="s">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="F178" s="30" t="s">
-        <v>183</v>
+        <v>337</v>
       </c>
       <c r="G178" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B178),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E178),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F178),0)&gt;0), MAX($G$1:G177)+1, ""))</f>
@@ -6723,22 +6720,22 @@
         <v>30</v>
       </c>
       <c r="B179" s="31" t="s">
-        <v>336</v>
+        <v>180</v>
       </c>
       <c r="C179" s="32">
         <v>30</v>
       </c>
-      <c r="D179" s="30">
-        <v>2.9</v>
+      <c r="D179" s="30" t="s">
+        <v>238</v>
       </c>
       <c r="E179" s="31" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="F179" s="30" t="s">
-        <v>337</v>
+        <v>181</v>
       </c>
       <c r="G179" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B179),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E179),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F179),0)&gt;0), MAX($G$1:G178)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B179),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E179),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F179),0)&gt;0), MAX($G$1:G177)+1, ""))</f>
         <v/>
       </c>
       <c r="H179" s="21" t="b">
@@ -6747,26 +6744,26 @@
       </c>
     </row>
     <row r="180" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A180" s="30">
-        <v>30</v>
-      </c>
-      <c r="B180" s="31" t="s">
-        <v>180</v>
-      </c>
-      <c r="C180" s="32">
-        <v>30</v>
-      </c>
-      <c r="D180" s="30" t="s">
-        <v>238</v>
-      </c>
-      <c r="E180" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="F180" s="30" t="s">
-        <v>181</v>
+      <c r="A180" s="26">
+        <v>40</v>
+      </c>
+      <c r="B180" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="C180" s="28">
+        <v>40</v>
+      </c>
+      <c r="D180" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="E180" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="F180" s="26" t="s">
+        <v>199</v>
       </c>
       <c r="G180" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B180),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E180),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F180),0)&gt;0), MAX($G$1:G178)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B180),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E180),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F180),0)&gt;0), MAX($G$1:G177)+1, ""))</f>
         <v/>
       </c>
       <c r="H180" s="21" t="b">
@@ -6779,22 +6776,22 @@
         <v>40</v>
       </c>
       <c r="B181" s="27" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C181" s="28">
         <v>40</v>
       </c>
       <c r="D181" s="26" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E181" s="27" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F181" s="26" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="G181" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B181),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E181),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F181),0)&gt;0), MAX($G$1:G178)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B181),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E181),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F181),0)&gt;0), MAX($G$1:G180)+1, ""))</f>
         <v/>
       </c>
       <c r="H181" s="21" t="b">
@@ -6807,19 +6804,19 @@
         <v>40</v>
       </c>
       <c r="B182" s="27" t="s">
-        <v>194</v>
+        <v>248</v>
       </c>
       <c r="C182" s="28">
         <v>40</v>
       </c>
-      <c r="D182" s="26" t="s">
-        <v>242</v>
+      <c r="D182" s="26">
+        <v>8.3000000000000007</v>
       </c>
       <c r="E182" s="27" t="s">
-        <v>195</v>
+        <v>249</v>
       </c>
       <c r="F182" s="26" t="s">
-        <v>196</v>
+        <v>250</v>
       </c>
       <c r="G182" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B182),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E182),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F182),0)&gt;0), MAX($G$1:G181)+1, ""))</f>
@@ -6832,22 +6829,22 @@
     </row>
     <row r="183" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A183" s="26">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B183" s="27" t="s">
-        <v>248</v>
+        <v>293</v>
       </c>
       <c r="C183" s="28">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D183" s="26">
-        <v>8.3000000000000007</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="E183" s="27" t="s">
-        <v>249</v>
+        <v>294</v>
       </c>
       <c r="F183" s="26" t="s">
-        <v>250</v>
+        <v>295</v>
       </c>
       <c r="G183" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B183),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E183),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F183),0)&gt;0), MAX($G$1:G182)+1, ""))</f>
@@ -6859,32 +6856,10 @@
       </c>
     </row>
     <row r="184" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A184" s="26">
-        <v>45</v>
-      </c>
-      <c r="B184" s="27" t="s">
-        <v>293</v>
-      </c>
-      <c r="C184" s="28">
-        <v>45</v>
-      </c>
-      <c r="D184" s="26">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="E184" s="27" t="s">
-        <v>294</v>
-      </c>
-      <c r="F184" s="26" t="s">
-        <v>295</v>
-      </c>
-      <c r="G184" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B184),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E184),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F184),0)&gt;0), MAX($G$1:G183)+1, ""))</f>
-        <v/>
-      </c>
-      <c r="H184" s="21" t="b">
-        <f>A184=C184</f>
-        <v>1</v>
-      </c>
+      <c r="A184" s="1"/>
+      <c r="C184" s="1"/>
+      <c r="D184" s="1"/>
+      <c r="F184" s="1"/>
     </row>
     <row r="185" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
@@ -12082,14 +12057,8 @@
       <c r="D1050" s="1"/>
       <c r="F1050" s="1"/>
     </row>
-    <row r="1051" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A1051" s="1"/>
-      <c r="C1051" s="1"/>
-      <c r="D1051" s="1"/>
-      <c r="F1051" s="1"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H184">
+  <autoFilter ref="A1:H183">
     <sortState ref="A2:H184">
       <sortCondition ref="A2:A184"/>
       <sortCondition ref="B2:B184"/>

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -1146,12 +1146,6 @@
     <t>JOSE MARIA DE ABREU (RUA 1)</t>
   </si>
   <si>
-    <t>FREDERICO FAULHABER APÓS CAMPO SÃO LUIS</t>
-  </si>
-  <si>
-    <t>FREDERICO FAULHABER ANTES CAMPO SÃO LUIS</t>
-  </si>
-  <si>
     <t>POSTO VAGÃO</t>
   </si>
   <si>
@@ -1246,6 +1240,12 @@
   </si>
   <si>
     <t>PIRAPUÃ (383)</t>
+  </si>
+  <si>
+    <t>FREDERICO FAULHABER ANTES PIRPIRITUBA</t>
+  </si>
+  <si>
+    <t>FREDERICO FAULHABER APÓS PIRPIRITUBA</t>
   </si>
 </sst>
 </file>
@@ -2194,7 +2194,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C16" s="28">
         <v>13</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="G16" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B16),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E16),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F16),0)&gt;0), MAX($G$1:G15)+1, ""))</f>
@@ -2334,7 +2334,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C21" s="28">
         <v>15</v>
@@ -2346,7 +2346,7 @@
         <v>8</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G21" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F21),0)&gt;0), MAX($G$1:G19)+1, ""))</f>
@@ -2614,7 +2614,7 @@
         <v>15</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>374</v>
+        <v>405</v>
       </c>
       <c r="C31" s="28">
         <v>15</v>
@@ -2726,7 +2726,7 @@
         <v>15</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C35" s="28">
         <v>15</v>
@@ -2738,7 +2738,7 @@
         <v>8</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="G35" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F35),0)&gt;0), MAX($G$1:G34)+1, ""))</f>
@@ -3034,7 +3034,7 @@
         <v>15</v>
       </c>
       <c r="B46" s="27" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C46" s="28">
         <v>15</v>
@@ -3046,7 +3046,7 @@
         <v>8</v>
       </c>
       <c r="F46" s="26" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="G46" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F46),0)&gt;0), MAX($G$1:G45)+1, ""))</f>
@@ -3090,7 +3090,7 @@
         <v>15</v>
       </c>
       <c r="B48" s="27" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C48" s="28">
         <v>15</v>
@@ -3202,7 +3202,7 @@
         <v>15</v>
       </c>
       <c r="B52" s="27" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C52" s="28">
         <v>15</v>
@@ -3211,10 +3211,10 @@
         <v>1.2</v>
       </c>
       <c r="E52" s="27" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F52" s="26" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="G52" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F52),0)&gt;0), MAX($G$1:G51)+1, ""))</f>
@@ -3339,7 +3339,7 @@
         <v>17</v>
       </c>
       <c r="B57" s="27" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C57" s="28">
         <v>17</v>
@@ -3351,7 +3351,7 @@
         <v>60</v>
       </c>
       <c r="F57" s="26" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G57" s="29"/>
       <c r="H57" s="21" t="b">
@@ -3526,7 +3526,7 @@
         <v>17</v>
       </c>
       <c r="B64" s="27" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C64" s="28">
         <v>17</v>
@@ -3538,7 +3538,7 @@
         <v>8</v>
       </c>
       <c r="F64" s="26" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="G64" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F64),0)&gt;0), MAX($G$1:G63)+1, ""))</f>
@@ -3716,7 +3716,7 @@
         <v>17</v>
       </c>
       <c r="B71" s="27" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C71" s="28">
         <v>17</v>
@@ -3744,7 +3744,7 @@
         <v>17</v>
       </c>
       <c r="B72" s="27" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C72" s="28">
         <v>17</v>
@@ -3756,7 +3756,7 @@
         <v>8</v>
       </c>
       <c r="F72" s="26" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="G72" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F72),0)&gt;0), MAX($G$1:G71)+1, ""))</f>
@@ -3884,7 +3884,7 @@
         <v>17</v>
       </c>
       <c r="B77" s="27" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C77" s="28">
         <v>17</v>
@@ -3896,7 +3896,7 @@
         <v>8</v>
       </c>
       <c r="F77" s="26" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="G77" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F77),0)&gt;0), MAX($G$1:G76)+1, ""))</f>
@@ -3912,7 +3912,7 @@
         <v>17</v>
       </c>
       <c r="B78" s="27" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C78" s="28">
         <v>17</v>
@@ -4184,7 +4184,7 @@
         <v>20</v>
       </c>
       <c r="B88" s="27" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C88" s="28">
         <v>20</v>
@@ -4196,7 +4196,7 @@
         <v>60</v>
       </c>
       <c r="F88" s="26" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="G88" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E88),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F88),0)&gt;0), MAX($G$1:G87)+1, ""))</f>
@@ -4542,7 +4542,7 @@
         <v>20</v>
       </c>
       <c r="B101" s="27" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C101" s="28">
         <v>20</v>
@@ -4554,7 +4554,7 @@
         <v>60</v>
       </c>
       <c r="F101" s="26" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G101" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E101),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F101),0)&gt;0), MAX($G$1:G100)+1, ""))</f>
@@ -4626,7 +4626,7 @@
         <v>20</v>
       </c>
       <c r="B104" s="27" t="s">
-        <v>373</v>
+        <v>406</v>
       </c>
       <c r="C104" s="28">
         <v>20</v>
@@ -6048,7 +6048,7 @@
         <v>25</v>
       </c>
       <c r="B155" s="27" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C155" s="28">
         <v>25</v>
@@ -6496,7 +6496,7 @@
         <v>30</v>
       </c>
       <c r="B171" s="31" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C171" s="32">
         <v>30</v>
@@ -6508,7 +6508,7 @@
         <v>131</v>
       </c>
       <c r="F171" s="30" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="G171" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B171),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E171),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F171),0)&gt;0), MAX($G$1:G169)+1, ""))</f>
@@ -6524,7 +6524,7 @@
         <v>30</v>
       </c>
       <c r="B172" s="27" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C172" s="28">
         <v>30</v>
@@ -6536,7 +6536,7 @@
         <v>81</v>
       </c>
       <c r="F172" s="26" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="G172" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B172),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E172),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F172),0)&gt;0), MAX($G$1:G171)+1, ""))</f>
@@ -6608,7 +6608,7 @@
         <v>30</v>
       </c>
       <c r="B175" s="27" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C175" s="28">
         <v>30</v>
@@ -6617,7 +6617,7 @@
         <v>5</v>
       </c>
       <c r="E175" s="27" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F175" s="26" t="s">
         <v>25</v>
@@ -6636,7 +6636,7 @@
         <v>30</v>
       </c>
       <c r="B176" s="31" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C176" s="32">
         <v>30</v>
@@ -6648,7 +6648,7 @@
         <v>131</v>
       </c>
       <c r="F176" s="30" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G176" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B176),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E176),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F176),0)&gt;0), MAX($G$1:G174)+1, ""))</f>

--- a/Controle corridas NOVO.xlsx
+++ b/Controle corridas NOVO.xlsx
@@ -16,8 +16,8 @@
     <sheet name="Consulta" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$183</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$H$181</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Base!$A$1:$F$144</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Base!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="402">
   <si>
     <t>Grupo</t>
   </si>
@@ -1065,18 +1065,9 @@
     <t>21775-120</t>
   </si>
   <si>
-    <t>21760-240</t>
-  </si>
-  <si>
     <t>21765-080</t>
   </si>
   <si>
-    <t>Piraquara</t>
-  </si>
-  <si>
-    <t>21760-001</t>
-  </si>
-  <si>
     <t xml:space="preserve">LOMAS VALENTINA </t>
   </si>
   <si>
@@ -1240,12 +1231,6 @@
   </si>
   <si>
     <t>PIRAPUÃ (383)</t>
-  </si>
-  <si>
-    <t>FREDERICO FAULHABER ANTES PIRPIRITUBA</t>
-  </si>
-  <si>
-    <t>FREDERICO FAULHABER APÓS PIRPIRITUBA</t>
   </si>
 </sst>
 </file>
@@ -1763,7 +1748,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H1050"/>
+  <dimension ref="A1:H1048"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.453125" customWidth="1"/>
@@ -1830,7 +1815,7 @@
         <v>13</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C3" s="28">
         <v>13</v>
@@ -2110,7 +2095,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C13" s="32">
         <v>13</v>
@@ -2166,7 +2151,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C15" s="32">
         <v>13</v>
@@ -2178,7 +2163,7 @@
         <v>8</v>
       </c>
       <c r="F15" s="30" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="G15" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B15),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E15),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F15),0)&gt;0), MAX($G$1:G14)+1, ""))</f>
@@ -2194,7 +2179,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C16" s="28">
         <v>13</v>
@@ -2203,10 +2188,10 @@
         <v>1</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="G16" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B16),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E16),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F16),0)&gt;0), MAX($G$1:G15)+1, ""))</f>
@@ -2334,7 +2319,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C21" s="28">
         <v>15</v>
@@ -2346,7 +2331,7 @@
         <v>8</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="G21" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E21),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F21),0)&gt;0), MAX($G$1:G19)+1, ""))</f>
@@ -2390,7 +2375,7 @@
         <v>15</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C23" s="28">
         <v>15</v>
@@ -2402,7 +2387,7 @@
         <v>244</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="G23" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B23),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E23),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F23),0)&gt;0), MAX($G$1:G22)+1, ""))</f>
@@ -2446,7 +2431,7 @@
         <v>15</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C25" s="28">
         <v>15</v>
@@ -2614,19 +2599,19 @@
         <v>15</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>405</v>
+        <v>57</v>
       </c>
       <c r="C31" s="28">
         <v>15</v>
       </c>
-      <c r="D31" s="26">
-        <v>2</v>
+      <c r="D31" s="26" t="s">
+        <v>223</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>348</v>
+        <v>8</v>
       </c>
       <c r="F31" s="26" t="s">
-        <v>346</v>
+        <v>58</v>
       </c>
       <c r="G31" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B31),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E31),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F31),0)&gt;0), MAX($G$1:G30)+1, ""))</f>
@@ -2642,19 +2627,19 @@
         <v>15</v>
       </c>
       <c r="B32" s="27" t="s">
-        <v>57</v>
+        <v>267</v>
       </c>
       <c r="C32" s="28">
         <v>15</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="E32" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F32" s="26" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G32" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B32),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E32),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F32),0)&gt;0), MAX($G$1:G31)+1, ""))</f>
@@ -2670,19 +2655,19 @@
         <v>15</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>267</v>
+        <v>305</v>
       </c>
       <c r="C33" s="28">
         <v>15</v>
       </c>
-      <c r="D33" s="26" t="s">
-        <v>205</v>
+      <c r="D33" s="26">
+        <v>2.1</v>
       </c>
       <c r="E33" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F33" s="26" t="s">
-        <v>56</v>
+        <v>306</v>
       </c>
       <c r="G33" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B33),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E33),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F33),0)&gt;0), MAX($G$1:G32)+1, ""))</f>
@@ -2698,19 +2683,19 @@
         <v>15</v>
       </c>
       <c r="B34" s="27" t="s">
-        <v>305</v>
+        <v>393</v>
       </c>
       <c r="C34" s="28">
         <v>15</v>
       </c>
       <c r="D34" s="26">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E34" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F34" s="26" t="s">
-        <v>306</v>
+        <v>392</v>
       </c>
       <c r="G34" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B34),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E34),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F34),0)&gt;0), MAX($G$1:G33)+1, ""))</f>
@@ -2726,19 +2711,19 @@
         <v>15</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>396</v>
+        <v>54</v>
       </c>
       <c r="C35" s="28">
         <v>15</v>
       </c>
-      <c r="D35" s="26">
-        <v>2.2000000000000002</v>
+      <c r="D35" s="26" t="s">
+        <v>204</v>
       </c>
       <c r="E35" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>395</v>
+        <v>55</v>
       </c>
       <c r="G35" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E35),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F35),0)&gt;0), MAX($G$1:G34)+1, ""))</f>
@@ -2754,19 +2739,19 @@
         <v>15</v>
       </c>
       <c r="B36" s="27" t="s">
-        <v>54</v>
+        <v>276</v>
       </c>
       <c r="C36" s="28">
         <v>15</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="E36" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F36" s="26" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="G36" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B36),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E36),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F36),0)&gt;0), MAX($G$1:G35)+1, ""))</f>
@@ -2782,19 +2767,19 @@
         <v>15</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="C37" s="28">
         <v>15</v>
       </c>
       <c r="D37" s="26" t="s">
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="E37" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>75</v>
+        <v>261</v>
       </c>
       <c r="G37" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E37),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F37),0)&gt;0), MAX($G$1:G36)+1, ""))</f>
@@ -2810,19 +2795,19 @@
         <v>15</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>259</v>
+        <v>291</v>
       </c>
       <c r="C38" s="28">
         <v>15</v>
       </c>
-      <c r="D38" s="26" t="s">
-        <v>21</v>
+      <c r="D38" s="26">
+        <v>2.2000000000000002</v>
       </c>
       <c r="E38" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F38" s="26" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="G38" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E38),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F38),0)&gt;0), MAX($G$1:G37)+1, ""))</f>
@@ -2838,19 +2823,19 @@
         <v>15</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>291</v>
+        <v>369</v>
       </c>
       <c r="C39" s="28">
         <v>15</v>
       </c>
       <c r="D39" s="26">
-        <v>2.2000000000000002</v>
+        <v>2.1</v>
       </c>
       <c r="E39" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F39" s="26" t="s">
-        <v>292</v>
+        <v>368</v>
       </c>
       <c r="G39" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B39),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E39),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F39),0)&gt;0), MAX($G$1:G38)+1, ""))</f>
@@ -2866,19 +2851,19 @@
         <v>15</v>
       </c>
       <c r="B40" s="27" t="s">
-        <v>372</v>
+        <v>347</v>
       </c>
       <c r="C40" s="28">
         <v>15</v>
       </c>
       <c r="D40" s="26">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="E40" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F40" s="26" t="s">
-        <v>371</v>
+        <v>348</v>
       </c>
       <c r="G40" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B40),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E40),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F40),0)&gt;0), MAX($G$1:G39)+1, ""))</f>
@@ -2894,19 +2879,19 @@
         <v>15</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>350</v>
+        <v>50</v>
       </c>
       <c r="C41" s="28">
         <v>15</v>
       </c>
-      <c r="D41" s="26">
-        <v>1.5</v>
+      <c r="D41" s="26" t="s">
+        <v>213</v>
       </c>
       <c r="E41" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F41" s="26" t="s">
-        <v>351</v>
+        <v>51</v>
       </c>
       <c r="G41" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B41),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E41),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F41),0)&gt;0), MAX($G$1:G40)+1, ""))</f>
@@ -2922,19 +2907,19 @@
         <v>15</v>
       </c>
       <c r="B42" s="27" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C42" s="28">
         <v>15</v>
       </c>
       <c r="D42" s="26" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="E42" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F42" s="26" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G42" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B42),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E42),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F42),0)&gt;0), MAX($G$1:G41)+1, ""))</f>
@@ -2950,19 +2935,19 @@
         <v>15</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C43" s="28">
         <v>15</v>
       </c>
       <c r="D43" s="26" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="E43" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F43" s="26" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G43" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E43),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F43),0)&gt;0), MAX($G$1:G42)+1, ""))</f>
@@ -2978,19 +2963,19 @@
         <v>15</v>
       </c>
       <c r="B44" s="27" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C44" s="28">
         <v>15</v>
       </c>
       <c r="D44" s="26" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="E44" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F44" s="26" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G44" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E44),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F44),0)&gt;0), MAX($G$1:G43)+1, ""))</f>
@@ -3006,19 +2991,19 @@
         <v>15</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>40</v>
+        <v>389</v>
       </c>
       <c r="C45" s="28">
         <v>15</v>
       </c>
-      <c r="D45" s="26" t="s">
-        <v>212</v>
+      <c r="D45" s="26">
+        <v>1.8</v>
       </c>
       <c r="E45" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F45" s="26" t="s">
-        <v>41</v>
+        <v>390</v>
       </c>
       <c r="G45" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E45),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F45),0)&gt;0), MAX($G$1:G44)+1, ""))</f>
@@ -3034,19 +3019,19 @@
         <v>15</v>
       </c>
       <c r="B46" s="27" t="s">
-        <v>392</v>
+        <v>307</v>
       </c>
       <c r="C46" s="28">
         <v>15</v>
       </c>
       <c r="D46" s="26">
-        <v>1.8</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E46" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F46" s="26" t="s">
-        <v>393</v>
+        <v>292</v>
       </c>
       <c r="G46" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E46),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F46),0)&gt;0), MAX($G$1:G45)+1, ""))</f>
@@ -3062,22 +3047,22 @@
         <v>15</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>307</v>
+        <v>399</v>
       </c>
       <c r="C47" s="28">
         <v>15</v>
       </c>
       <c r="D47" s="26">
-        <v>2.2000000000000002</v>
+        <v>2.1</v>
       </c>
       <c r="E47" s="27" t="s">
-        <v>8</v>
+        <v>244</v>
       </c>
       <c r="F47" s="26" t="s">
-        <v>292</v>
+        <v>202</v>
       </c>
       <c r="G47" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F47),0)&gt;0), MAX($G$1:G46)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E47),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F47),0)&gt;0), MAX($G$1:G45)+1, ""))</f>
         <v/>
       </c>
       <c r="H47" s="21" t="b">
@@ -3090,22 +3075,22 @@
         <v>15</v>
       </c>
       <c r="B48" s="27" t="s">
-        <v>402</v>
+        <v>38</v>
       </c>
       <c r="C48" s="28">
         <v>15</v>
       </c>
-      <c r="D48" s="26">
-        <v>2.1</v>
+      <c r="D48" s="26" t="s">
+        <v>211</v>
       </c>
       <c r="E48" s="27" t="s">
-        <v>244</v>
+        <v>8</v>
       </c>
       <c r="F48" s="26" t="s">
-        <v>202</v>
+        <v>39</v>
       </c>
       <c r="G48" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F48),0)&gt;0), MAX($G$1:G46)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E48),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F48),0)&gt;0), MAX($G$1:G42)+1, ""))</f>
         <v/>
       </c>
       <c r="H48" s="21" t="b">
@@ -3118,22 +3103,22 @@
         <v>15</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>38</v>
+        <v>340</v>
       </c>
       <c r="C49" s="28">
         <v>15</v>
       </c>
-      <c r="D49" s="26" t="s">
-        <v>211</v>
+      <c r="D49" s="26">
+        <v>1.4</v>
       </c>
       <c r="E49" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F49" s="26" t="s">
-        <v>39</v>
+        <v>345</v>
       </c>
       <c r="G49" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F49),0)&gt;0), MAX($G$1:G43)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E49),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F49),0)&gt;0), MAX($G$1:G48)+1, ""))</f>
         <v/>
       </c>
       <c r="H49" s="21" t="b">
@@ -3146,19 +3131,19 @@
         <v>15</v>
       </c>
       <c r="B50" s="27" t="s">
-        <v>340</v>
+        <v>34</v>
       </c>
       <c r="C50" s="28">
         <v>15</v>
       </c>
-      <c r="D50" s="26">
-        <v>1.4</v>
+      <c r="D50" s="26" t="s">
+        <v>210</v>
       </c>
       <c r="E50" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F50" s="26" t="s">
-        <v>345</v>
+        <v>35</v>
       </c>
       <c r="G50" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E50),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F50),0)&gt;0), MAX($G$1:G49)+1, ""))</f>
@@ -3174,19 +3159,19 @@
         <v>15</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>34</v>
+        <v>376</v>
       </c>
       <c r="C51" s="28">
         <v>15</v>
       </c>
-      <c r="D51" s="26" t="s">
-        <v>210</v>
+      <c r="D51" s="26">
+        <v>1.2</v>
       </c>
       <c r="E51" s="27" t="s">
-        <v>8</v>
+        <v>374</v>
       </c>
       <c r="F51" s="26" t="s">
-        <v>35</v>
+        <v>375</v>
       </c>
       <c r="G51" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E51),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F51),0)&gt;0), MAX($G$1:G50)+1, ""))</f>
@@ -3202,22 +3187,22 @@
         <v>15</v>
       </c>
       <c r="B52" s="27" t="s">
-        <v>379</v>
+        <v>279</v>
       </c>
       <c r="C52" s="28">
         <v>15</v>
       </c>
-      <c r="D52" s="26">
-        <v>1.2</v>
+      <c r="D52" s="26" t="s">
+        <v>209</v>
       </c>
       <c r="E52" s="27" t="s">
-        <v>377</v>
+        <v>266</v>
       </c>
       <c r="F52" s="26" t="s">
-        <v>378</v>
+        <v>33</v>
       </c>
       <c r="G52" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F52),0)&gt;0), MAX($G$1:G51)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E52),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F52),0)&gt;0), MAX($G$1:G47)+1, ""))</f>
         <v/>
       </c>
       <c r="H52" s="21" t="b">
@@ -3226,26 +3211,26 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="26">
-        <v>15</v>
-      </c>
-      <c r="B53" s="27" t="s">
-        <v>279</v>
-      </c>
-      <c r="C53" s="28">
-        <v>15</v>
-      </c>
-      <c r="D53" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="E53" s="27" t="s">
-        <v>266</v>
-      </c>
-      <c r="F53" s="26" t="s">
-        <v>33</v>
+      <c r="A53" s="33">
+        <v>17</v>
+      </c>
+      <c r="B53" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="C53" s="35">
+        <v>17</v>
+      </c>
+      <c r="D53" s="33" t="s">
+        <v>214</v>
+      </c>
+      <c r="E53" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F53" s="33" t="s">
+        <v>71</v>
       </c>
       <c r="G53" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F53),0)&gt;0), MAX($G$1:G48)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E53),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F53),0)&gt;0), MAX($G$1:G52)+1, ""))</f>
         <v/>
       </c>
       <c r="H53" s="21" t="b">
@@ -3258,19 +3243,19 @@
         <v>17</v>
       </c>
       <c r="B54" s="34" t="s">
-        <v>70</v>
+        <v>280</v>
       </c>
       <c r="C54" s="35">
         <v>17</v>
       </c>
       <c r="D54" s="33" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E54" s="34" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F54" s="33" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G54" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E54),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F54),0)&gt;0), MAX($G$1:G53)+1, ""))</f>
@@ -3282,28 +3267,25 @@
       </c>
     </row>
     <row r="55" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="33">
+      <c r="A55" s="26">
         <v>17</v>
       </c>
-      <c r="B55" s="34" t="s">
-        <v>280</v>
-      </c>
-      <c r="C55" s="35">
+      <c r="B55" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="C55" s="28">
         <v>17</v>
       </c>
-      <c r="D55" s="33" t="s">
-        <v>222</v>
-      </c>
-      <c r="E55" s="34" t="s">
+      <c r="D55" s="26">
+        <v>1.7</v>
+      </c>
+      <c r="E55" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="F55" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="G55" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E55),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F55),0)&gt;0), MAX($G$1:G54)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="F55" s="26" t="s">
+        <v>318</v>
+      </c>
+      <c r="G55" s="29"/>
       <c r="H55" s="21" t="b">
         <f>A55=C55</f>
         <v>1</v>
@@ -3314,19 +3296,19 @@
         <v>17</v>
       </c>
       <c r="B56" s="27" t="s">
-        <v>312</v>
+        <v>387</v>
       </c>
       <c r="C56" s="28">
         <v>17</v>
       </c>
       <c r="D56" s="26">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="E56" s="27" t="s">
         <v>60</v>
       </c>
       <c r="F56" s="26" t="s">
-        <v>318</v>
+        <v>388</v>
       </c>
       <c r="G56" s="29"/>
       <c r="H56" s="21" t="b">
@@ -3335,25 +3317,28 @@
       </c>
     </row>
     <row r="57" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A57" s="26">
+      <c r="A57" s="33">
         <v>17</v>
       </c>
-      <c r="B57" s="27" t="s">
-        <v>390</v>
-      </c>
-      <c r="C57" s="28">
+      <c r="B57" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C57" s="35">
         <v>17</v>
       </c>
-      <c r="D57" s="26">
-        <v>1.3</v>
-      </c>
-      <c r="E57" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="F57" s="26" t="s">
-        <v>391</v>
-      </c>
-      <c r="G57" s="29"/>
+      <c r="D57" s="33" t="s">
+        <v>215</v>
+      </c>
+      <c r="E57" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="G57" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E57),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F57),0)&gt;0), MAX($G$1:G56)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H57" s="21" t="b">
         <f>A57=C57</f>
         <v>1</v>
@@ -3364,19 +3349,19 @@
         <v>17</v>
       </c>
       <c r="B58" s="34" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C58" s="35">
         <v>17</v>
       </c>
       <c r="D58" s="33" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E58" s="34" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F58" s="33" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G58" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E58),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F58),0)&gt;0), MAX($G$1:G57)+1, ""))</f>
@@ -3388,28 +3373,25 @@
       </c>
     </row>
     <row r="59" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A59" s="33">
+      <c r="A59" s="26">
         <v>17</v>
       </c>
-      <c r="B59" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="C59" s="35">
+      <c r="B59" s="27" t="s">
+        <v>314</v>
+      </c>
+      <c r="C59" s="28">
         <v>17</v>
       </c>
-      <c r="D59" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="E59" s="34" t="s">
+      <c r="D59" s="26">
+        <v>3</v>
+      </c>
+      <c r="E59" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="F59" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="G59" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E59),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F59),0)&gt;0), MAX($G$1:G58)+1, ""))</f>
-        <v/>
-      </c>
+      <c r="F59" s="26" t="s">
+        <v>320</v>
+      </c>
+      <c r="G59" s="29"/>
       <c r="H59" s="21" t="b">
         <f>A59=C59</f>
         <v>1</v>
@@ -3420,21 +3402,24 @@
         <v>17</v>
       </c>
       <c r="B60" s="27" t="s">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="C60" s="28">
         <v>17</v>
       </c>
       <c r="D60" s="26">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="E60" s="27" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="F60" s="26" t="s">
-        <v>320</v>
-      </c>
-      <c r="G60" s="29"/>
+        <v>346</v>
+      </c>
+      <c r="G60" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E60),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F60),0)&gt;0), MAX($G$1:G58)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H60" s="21" t="b">
         <f>A60=C60</f>
         <v>1</v>
@@ -3445,72 +3430,72 @@
         <v>17</v>
       </c>
       <c r="B61" s="27" t="s">
-        <v>339</v>
+        <v>315</v>
       </c>
       <c r="C61" s="28">
         <v>17</v>
       </c>
       <c r="D61" s="26">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="E61" s="27" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F61" s="26" t="s">
-        <v>347</v>
-      </c>
-      <c r="G61" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E61),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F61),0)&gt;0), MAX($G$1:G59)+1, ""))</f>
-        <v/>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="G61" s="29"/>
       <c r="H61" s="21" t="b">
         <f>A61=C61</f>
         <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A62" s="26">
+      <c r="A62" s="36">
         <v>17</v>
       </c>
-      <c r="B62" s="27" t="s">
-        <v>315</v>
-      </c>
-      <c r="C62" s="28">
+      <c r="B62" s="37" t="s">
+        <v>288</v>
+      </c>
+      <c r="C62" s="38">
         <v>17</v>
       </c>
-      <c r="D62" s="26">
-        <v>1.9</v>
-      </c>
-      <c r="E62" s="27" t="s">
+      <c r="D62" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E62" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="F62" s="26" t="s">
-        <v>321</v>
-      </c>
-      <c r="G62" s="29"/>
+      <c r="F62" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="G62" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E62),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F62),0)&gt;0), MAX($G$1:G61)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H62" s="21" t="b">
         <f>A62=C62</f>
         <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A63" s="36">
+      <c r="A63" s="26">
         <v>17</v>
       </c>
-      <c r="B63" s="37" t="s">
-        <v>288</v>
-      </c>
-      <c r="C63" s="38">
+      <c r="B63" s="27" t="s">
+        <v>394</v>
+      </c>
+      <c r="C63" s="28">
         <v>17</v>
       </c>
-      <c r="D63" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="E63" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="F63" s="36" t="s">
-        <v>111</v>
+      <c r="D63" s="26">
+        <v>2.4</v>
+      </c>
+      <c r="E63" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F63" s="26" t="s">
+        <v>392</v>
       </c>
       <c r="G63" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E63),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F63),0)&gt;0), MAX($G$1:G62)+1, ""))</f>
@@ -3526,24 +3511,21 @@
         <v>17</v>
       </c>
       <c r="B64" s="27" t="s">
-        <v>397</v>
+        <v>313</v>
       </c>
       <c r="C64" s="28">
         <v>17</v>
       </c>
       <c r="D64" s="26">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="E64" s="27" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="F64" s="26" t="s">
-        <v>395</v>
-      </c>
-      <c r="G64" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E64),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F64),0)&gt;0), MAX($G$1:G63)+1, ""))</f>
-        <v/>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="G64" s="29"/>
       <c r="H64" s="21" t="b">
         <f>A64=C64</f>
         <v>1</v>
@@ -3554,19 +3536,19 @@
         <v>17</v>
       </c>
       <c r="B65" s="27" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C65" s="28">
         <v>17</v>
       </c>
       <c r="D65" s="26">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="E65" s="27" t="s">
         <v>60</v>
       </c>
       <c r="F65" s="26" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G65" s="29"/>
       <c r="H65" s="21" t="b">
@@ -3575,25 +3557,28 @@
       </c>
     </row>
     <row r="66" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A66" s="26">
+      <c r="A66" s="36">
         <v>17</v>
       </c>
-      <c r="B66" s="27" t="s">
-        <v>316</v>
-      </c>
-      <c r="C66" s="28">
+      <c r="B66" s="37" t="s">
+        <v>106</v>
+      </c>
+      <c r="C66" s="38">
         <v>17</v>
       </c>
-      <c r="D66" s="26">
-        <v>2</v>
-      </c>
-      <c r="E66" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="F66" s="26" t="s">
-        <v>322</v>
-      </c>
-      <c r="G66" s="29"/>
+      <c r="D66" s="36" t="s">
+        <v>220</v>
+      </c>
+      <c r="E66" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F66" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="G66" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E66),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F66),0)&gt;0), MAX($G$1:G65)+1, ""))</f>
+        <v/>
+      </c>
       <c r="H66" s="21" t="b">
         <f>A66=C66</f>
         <v>1</v>
@@ -3604,19 +3589,19 @@
         <v>17</v>
       </c>
       <c r="B67" s="37" t="s">
-        <v>106</v>
+        <v>302</v>
       </c>
       <c r="C67" s="38">
         <v>17</v>
       </c>
       <c r="D67" s="36" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="E67" s="37" t="s">
-        <v>8</v>
+        <v>303</v>
       </c>
       <c r="F67" s="36" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G67" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E67),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F67),0)&gt;0), MAX($G$1:G66)+1, ""))</f>
@@ -3628,26 +3613,26 @@
       </c>
     </row>
     <row r="68" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A68" s="36">
+      <c r="A68" s="33">
         <v>17</v>
       </c>
-      <c r="B68" s="37" t="s">
-        <v>302</v>
-      </c>
-      <c r="C68" s="38">
+      <c r="B68" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="C68" s="35">
         <v>17</v>
       </c>
-      <c r="D68" s="36" t="s">
-        <v>229</v>
-      </c>
-      <c r="E68" s="37" t="s">
-        <v>303</v>
-      </c>
-      <c r="F68" s="36" t="s">
-        <v>105</v>
+      <c r="D68" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="E68" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F68" s="33" t="s">
+        <v>53</v>
       </c>
       <c r="G68" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F68),0)&gt;0), MAX($G$1:G67)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E68),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F68),0)&gt;0), MAX($G$1:G63)+1, ""))</f>
         <v/>
       </c>
       <c r="H68" s="21" t="b">
@@ -3656,26 +3641,26 @@
       </c>
     </row>
     <row r="69" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A69" s="33">
+      <c r="A69" s="26">
         <v>17</v>
       </c>
-      <c r="B69" s="34" t="s">
-        <v>52</v>
-      </c>
-      <c r="C69" s="35">
+      <c r="B69" s="27" t="s">
+        <v>363</v>
+      </c>
+      <c r="C69" s="28">
         <v>17</v>
       </c>
-      <c r="D69" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="E69" s="34" t="s">
+      <c r="D69" s="26">
+        <v>1.8</v>
+      </c>
+      <c r="E69" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F69" s="33" t="s">
-        <v>53</v>
+      <c r="F69" s="26" t="s">
+        <v>349</v>
       </c>
       <c r="G69" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F69),0)&gt;0), MAX($G$1:G64)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E69),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F69),0)&gt;0), MAX($G$1:G68)+1, ""))</f>
         <v/>
       </c>
       <c r="H69" s="21" t="b">
@@ -3688,19 +3673,19 @@
         <v>17</v>
       </c>
       <c r="B70" s="27" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="C70" s="28">
         <v>17</v>
       </c>
       <c r="D70" s="26">
-        <v>1.8</v>
-      </c>
-      <c r="E70" s="27" t="s">
+        <v>1.4</v>
+      </c>
+      <c r="E70" s="31" t="s">
         <v>8</v>
       </c>
       <c r="F70" s="26" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="G70" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E70),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F70),0)&gt;0), MAX($G$1:G69)+1, ""))</f>
@@ -3716,19 +3701,19 @@
         <v>17</v>
       </c>
       <c r="B71" s="27" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="C71" s="28">
         <v>17</v>
       </c>
       <c r="D71" s="26">
-        <v>1.4</v>
-      </c>
-      <c r="E71" s="31" t="s">
+        <v>1.2</v>
+      </c>
+      <c r="E71" s="27" t="s">
         <v>8</v>
       </c>
       <c r="F71" s="26" t="s">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="G71" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E71),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F71),0)&gt;0), MAX($G$1:G70)+1, ""))</f>
@@ -3740,23 +3725,23 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A72" s="26">
+      <c r="A72" s="33">
         <v>17</v>
       </c>
-      <c r="B72" s="27" t="s">
-        <v>375</v>
-      </c>
-      <c r="C72" s="28">
+      <c r="B72" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="C72" s="35">
         <v>17</v>
       </c>
-      <c r="D72" s="26">
-        <v>1.2</v>
-      </c>
-      <c r="E72" s="27" t="s">
+      <c r="D72" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="E72" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F72" s="26" t="s">
-        <v>376</v>
+      <c r="F72" s="33" t="s">
+        <v>49</v>
       </c>
       <c r="G72" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E72),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F72),0)&gt;0), MAX($G$1:G71)+1, ""))</f>
@@ -3768,23 +3753,23 @@
       </c>
     </row>
     <row r="73" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A73" s="33">
+      <c r="A73" s="36">
         <v>17</v>
       </c>
-      <c r="B73" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="C73" s="35">
+      <c r="B73" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="C73" s="38">
         <v>17</v>
       </c>
-      <c r="D73" s="33" t="s">
-        <v>211</v>
-      </c>
-      <c r="E73" s="34" t="s">
+      <c r="D73" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E73" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F73" s="33" t="s">
-        <v>49</v>
+      <c r="F73" s="36" t="s">
+        <v>98</v>
       </c>
       <c r="G73" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E73),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F73),0)&gt;0), MAX($G$1:G72)+1, ""))</f>
@@ -3796,23 +3781,23 @@
       </c>
     </row>
     <row r="74" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A74" s="36">
+      <c r="A74" s="26">
         <v>17</v>
       </c>
-      <c r="B74" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="C74" s="38">
+      <c r="B74" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C74" s="28">
         <v>17</v>
       </c>
-      <c r="D74" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="E74" s="37" t="s">
+      <c r="D74" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="E74" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F74" s="36" t="s">
-        <v>98</v>
+      <c r="F74" s="26" t="s">
+        <v>43</v>
       </c>
       <c r="G74" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E74),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F74),0)&gt;0), MAX($G$1:G73)+1, ""))</f>
@@ -3824,23 +3809,23 @@
       </c>
     </row>
     <row r="75" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A75" s="26">
+      <c r="A75" s="36">
         <v>17</v>
       </c>
-      <c r="B75" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="C75" s="28">
+      <c r="B75" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="C75" s="38">
         <v>17</v>
       </c>
-      <c r="D75" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="E75" s="27" t="s">
+      <c r="D75" s="36" t="s">
+        <v>217</v>
+      </c>
+      <c r="E75" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F75" s="26" t="s">
-        <v>43</v>
+      <c r="F75" s="36" t="s">
+        <v>94</v>
       </c>
       <c r="G75" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E75),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F75),0)&gt;0), MAX($G$1:G74)+1, ""))</f>
@@ -3852,23 +3837,23 @@
       </c>
     </row>
     <row r="76" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A76" s="36">
+      <c r="A76" s="26">
         <v>17</v>
       </c>
-      <c r="B76" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="C76" s="38">
+      <c r="B76" s="27" t="s">
+        <v>391</v>
+      </c>
+      <c r="C76" s="28">
         <v>17</v>
       </c>
-      <c r="D76" s="36" t="s">
-        <v>217</v>
-      </c>
-      <c r="E76" s="37" t="s">
+      <c r="D76" s="26">
+        <v>2</v>
+      </c>
+      <c r="E76" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F76" s="36" t="s">
-        <v>94</v>
+      <c r="F76" s="26" t="s">
+        <v>390</v>
       </c>
       <c r="G76" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E76),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F76),0)&gt;0), MAX($G$1:G75)+1, ""))</f>
@@ -3884,22 +3869,22 @@
         <v>17</v>
       </c>
       <c r="B77" s="27" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="C77" s="28">
         <v>17</v>
       </c>
       <c r="D77" s="26">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E77" s="27" t="s">
-        <v>8</v>
+        <v>244</v>
       </c>
       <c r="F77" s="26" t="s">
-        <v>393</v>
+        <v>202</v>
       </c>
       <c r="G77" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F77),0)&gt;0), MAX($G$1:G76)+1, ""))</f>
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E77),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F77),0)&gt;0), MAX($G$1:G75)+1, ""))</f>
         <v/>
       </c>
       <c r="H77" s="21" t="b">
@@ -3908,30 +3893,28 @@
       </c>
     </row>
     <row r="78" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A78" s="26">
+      <c r="A78" s="33">
         <v>17</v>
       </c>
-      <c r="B78" s="27" t="s">
-        <v>403</v>
-      </c>
-      <c r="C78" s="28">
+      <c r="B78" s="34" t="s">
+        <v>326</v>
+      </c>
+      <c r="C78" s="35">
         <v>17</v>
       </c>
-      <c r="D78" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E78" s="27" t="s">
-        <v>244</v>
-      </c>
-      <c r="F78" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="G78" s="29" t="str">
-        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E78),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F78),0)&gt;0), MAX($G$1:G76)+1, ""))</f>
-        <v/>
+      <c r="D78" s="33">
+        <v>1.9</v>
+      </c>
+      <c r="E78" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="F78" s="33" t="s">
+        <v>328</v>
+      </c>
+      <c r="G78" s="29" t="s">
+        <v>325</v>
       </c>
       <c r="H78" s="21" t="b">
-        <f>A78=C78</f>
         <v>1</v>
       </c>
     </row>
@@ -3940,7 +3923,7 @@
         <v>17</v>
       </c>
       <c r="B79" s="34" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C79" s="35">
         <v>17</v>
@@ -3966,7 +3949,7 @@
         <v>17</v>
       </c>
       <c r="B80" s="34" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C80" s="35">
         <v>17</v>
@@ -3992,45 +3975,47 @@
         <v>17</v>
       </c>
       <c r="B81" s="34" t="s">
-        <v>327</v>
+        <v>36</v>
       </c>
       <c r="C81" s="35">
         <v>17</v>
       </c>
-      <c r="D81" s="33">
-        <v>1.9</v>
+      <c r="D81" s="33" t="s">
+        <v>214</v>
       </c>
       <c r="E81" s="34" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="F81" s="33" t="s">
-        <v>328</v>
-      </c>
-      <c r="G81" s="29" t="s">
-        <v>325</v>
+        <v>37</v>
+      </c>
+      <c r="G81" s="29" t="str">
+        <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E81),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F81),0)&gt;0), MAX($G$1:G80)+1, ""))</f>
+        <v/>
       </c>
       <c r="H81" s="21" t="b">
+        <f>A81=C81</f>
         <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A82" s="33">
+      <c r="A82" s="36">
         <v>17</v>
       </c>
-      <c r="B82" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="C82" s="35">
+      <c r="B82" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="C82" s="38">
         <v>17</v>
       </c>
-      <c r="D82" s="33" t="s">
-        <v>214</v>
-      </c>
-      <c r="E82" s="34" t="s">
+      <c r="D82" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E82" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F82" s="33" t="s">
-        <v>37</v>
+      <c r="F82" s="36" t="s">
+        <v>84</v>
       </c>
       <c r="G82" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E82),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F82),0)&gt;0), MAX($G$1:G81)+1, ""))</f>
@@ -4042,23 +4027,23 @@
       </c>
     </row>
     <row r="83" spans="1:8" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A83" s="36">
+      <c r="A83" s="33">
         <v>17</v>
       </c>
-      <c r="B83" s="37" t="s">
-        <v>83</v>
-      </c>
-      <c r="C83" s="38">
+      <c r="B83" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="35">
         <v>17</v>
       </c>
-      <c r="D83" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="E83" s="37" t="s">
+      <c r="D83" s="33" t="s">
+        <v>208</v>
+      </c>
+      <c r="E83" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="F83" s="36" t="s">
-        <v>84</v>
+      <c r="F83" s="33" t="s">
+        <v>32</v>
       </c>
       <c r="G83" s="29" t="str">
         <f>IF(Consulta!$B$1="", "", IF(OR(IFERROR(SEARCH(Consulta!$B$1,B83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,E83),0)&gt;0,IFERROR(SEARCH(Consulta!$B$1,F83),0)&gt;0), MAX($G$1:G82)+1, ""))</f>
@@ -4074,52 +4059,52 @@
         <v>17</v>
       </c>
       <c r="B84" s="34" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C84" s="35">
         <v>17</v>
       </c>
       <c r="D84" s="33" t="s">
-        <v>208</v>